--- a/Produtos.xlsx
+++ b/Produtos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NOT-MARCOS\Documents\GitHub\Catalogo-Olympikus_2.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12C4E28A-4B48-442F-8B01-63050EAB2D8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1D8E06D-6CBE-442F-8687-16A681DC03A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{C851EA1D-5267-41B7-9513-D07E5A57DEF2}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Worksheet" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Worksheet!$A$1:$J$791</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Worksheet!$A$1:$J$807</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -4453,7 +4453,18 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -30620,7 +30631,10 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J791" xr:uid="{3A91E150-05DE-47E3-9A71-EF43C5F49301}"/>
+  <autoFilter ref="A1:J807" xr:uid="{3A91E150-05DE-47E3-9A71-EF43C5F49301}"/>
+  <conditionalFormatting sqref="A1:A1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
   <headerFooter alignWithMargins="0"/>

--- a/Produtos.xlsx
+++ b/Produtos.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NOT-MARCOS\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NOT-MARCOS\Documents\GitHub\Catalogo-Olympikus_2.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A930A6D6-7C06-4B53-B709-423DD686C96D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36887811-8D54-46B2-B8E5-08926B27B780}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{C851EA1D-5267-41B7-9513-D07E5A57DEF2}"/>
   </bookViews>

--- a/Produtos.xlsx
+++ b/Produtos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NOT-MARCOS\Documents\GitHub\Catalogo-Olympikus_2.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36887811-8D54-46B2-B8E5-08926B27B780}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4871435-A9F7-499E-B17C-B3634CA3A95E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{C851EA1D-5267-41B7-9513-D07E5A57DEF2}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6166" uniqueCount="1199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6166" uniqueCount="1200">
   <si>
     <t>Imagem</t>
   </si>
@@ -3633,6 +3633,9 @@
   </si>
   <si>
     <t>43447473_PTO_CH</t>
+  </si>
+  <si>
+    <t>43777397_ARTPTO</t>
   </si>
 </sst>
 </file>
@@ -4030,13 +4033,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0D1E054-7418-4233-9A16-A15E844DE850}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:L643"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="31.28515625" style="1" customWidth="1"/>
     <col min="2" max="2" width="28.28515625" style="1" customWidth="1"/>
     <col min="3" max="4" width="15.85546875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="23.7109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="39.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="10" width="15.85546875" style="1" customWidth="1"/>
     <col min="11" max="11" width="9.140625" style="1"/>
     <col min="12" max="12" width="18.140625" style="1" bestFit="1" customWidth="1"/>
@@ -4081,7 +4085,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1056</v>
       </c>
@@ -4119,7 +4123,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>1057</v>
       </c>
@@ -4157,7 +4161,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>859</v>
       </c>
@@ -4195,7 +4199,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>860</v>
       </c>
@@ -4233,7 +4237,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>861</v>
       </c>
@@ -4271,7 +4275,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>862</v>
       </c>
@@ -4309,7 +4313,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>863</v>
       </c>
@@ -4347,7 +4351,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>864</v>
       </c>
@@ -4385,7 +4389,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>865</v>
       </c>
@@ -4423,7 +4427,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>866</v>
       </c>
@@ -4461,7 +4465,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>867</v>
       </c>
@@ -4499,7 +4503,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>868</v>
       </c>
@@ -4537,7 +4541,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>869</v>
       </c>
@@ -4575,7 +4579,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>870</v>
       </c>
@@ -4613,7 +4617,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>871</v>
       </c>
@@ -4651,7 +4655,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="17" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>1058</v>
       </c>
@@ -4689,7 +4693,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>872</v>
       </c>
@@ -4727,7 +4731,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="19" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>873</v>
       </c>
@@ -4765,7 +4769,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="20" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>874</v>
       </c>
@@ -4803,7 +4807,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="21" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>1059</v>
       </c>
@@ -4841,7 +4845,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="22" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>875</v>
       </c>
@@ -4879,7 +4883,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="23" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>876</v>
       </c>
@@ -4917,7 +4921,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="24" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>877</v>
       </c>
@@ -4955,7 +4959,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="25" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>1060</v>
       </c>
@@ -4993,7 +4997,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="26" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>878</v>
       </c>
@@ -5031,7 +5035,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="27" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>879</v>
       </c>
@@ -5069,7 +5073,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="28" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>880</v>
       </c>
@@ -5107,7 +5111,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="29" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>1061</v>
       </c>
@@ -5145,7 +5149,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="30" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>881</v>
       </c>
@@ -5183,7 +5187,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="31" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>1062</v>
       </c>
@@ -5221,7 +5225,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="32" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>882</v>
       </c>
@@ -5259,7 +5263,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="33" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>883</v>
       </c>
@@ -5297,7 +5301,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="34" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>1063</v>
       </c>
@@ -5335,7 +5339,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="35" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>1064</v>
       </c>
@@ -5373,7 +5377,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="36" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>884</v>
       </c>
@@ -5411,7 +5415,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="37" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>885</v>
       </c>
@@ -5449,7 +5453,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="38" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>1065</v>
       </c>
@@ -5487,7 +5491,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="39" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>886</v>
       </c>
@@ -5525,7 +5529,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="40" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>1066</v>
       </c>
@@ -5563,7 +5567,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="41" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>887</v>
       </c>
@@ -5601,7 +5605,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="42" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>888</v>
       </c>
@@ -5639,7 +5643,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="43" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>889</v>
       </c>
@@ -5677,7 +5681,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="44" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>1067</v>
       </c>
@@ -5715,7 +5719,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="45" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>890</v>
       </c>
@@ -5753,7 +5757,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="46" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>891</v>
       </c>
@@ -5791,7 +5795,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="47" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>892</v>
       </c>
@@ -5829,7 +5833,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="48" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>893</v>
       </c>
@@ -5867,7 +5871,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="49" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>1068</v>
       </c>
@@ -5905,7 +5909,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="50" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>894</v>
       </c>
@@ -5943,7 +5947,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="51" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>895</v>
       </c>
@@ -5981,7 +5985,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="52" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>896</v>
       </c>
@@ -6019,7 +6023,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="53" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>1069</v>
       </c>
@@ -6057,7 +6061,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="54" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>1070</v>
       </c>
@@ -6095,7 +6099,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="55" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>897</v>
       </c>
@@ -6133,7 +6137,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="56" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>898</v>
       </c>
@@ -6171,7 +6175,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="57" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>899</v>
       </c>
@@ -6209,7 +6213,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="58" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>900</v>
       </c>
@@ -6247,7 +6251,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="59" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>901</v>
       </c>
@@ -6285,7 +6289,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="60" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>902</v>
       </c>
@@ -6323,7 +6327,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="61" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>903</v>
       </c>
@@ -6361,7 +6365,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="62" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>904</v>
       </c>
@@ -6399,7 +6403,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="63" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>1071</v>
       </c>
@@ -6437,7 +6441,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="64" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>905</v>
       </c>
@@ -6475,7 +6479,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="65" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>906</v>
       </c>
@@ -6513,7 +6517,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="66" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>1072</v>
       </c>
@@ -6551,7 +6555,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="67" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>907</v>
       </c>
@@ -6589,7 +6593,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="68" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>908</v>
       </c>
@@ -6627,7 +6631,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="69" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>909</v>
       </c>
@@ -6665,7 +6669,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="70" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>910</v>
       </c>
@@ -6703,7 +6707,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="71" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
         <v>911</v>
       </c>
@@ -6741,7 +6745,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="72" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>912</v>
       </c>
@@ -6779,7 +6783,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="73" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>913</v>
       </c>
@@ -6817,7 +6821,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="74" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>914</v>
       </c>
@@ -6855,7 +6859,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="75" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
         <v>915</v>
       </c>
@@ -6893,7 +6897,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="76" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
         <v>1073</v>
       </c>
@@ -6931,7 +6935,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="77" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
         <v>916</v>
       </c>
@@ -6969,7 +6973,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="78" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
         <v>917</v>
       </c>
@@ -7007,7 +7011,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="79" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
         <v>918</v>
       </c>
@@ -7045,7 +7049,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="80" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
         <v>919</v>
       </c>
@@ -7083,7 +7087,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="81" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
         <v>920</v>
       </c>
@@ -7121,7 +7125,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="82" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
         <v>921</v>
       </c>
@@ -7159,7 +7163,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="83" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
         <v>922</v>
       </c>
@@ -7197,7 +7201,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="84" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
         <v>923</v>
       </c>
@@ -7235,7 +7239,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="85" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
         <v>924</v>
       </c>
@@ -7273,7 +7277,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="86" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
         <v>925</v>
       </c>
@@ -7311,7 +7315,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="87" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
         <v>926</v>
       </c>
@@ -7349,7 +7353,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="88" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
         <v>927</v>
       </c>
@@ -7387,7 +7391,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="89" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
         <v>928</v>
       </c>
@@ -7425,7 +7429,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="90" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
         <v>929</v>
       </c>
@@ -7463,7 +7467,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="91" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
         <v>930</v>
       </c>
@@ -7501,7 +7505,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="92" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
         <v>931</v>
       </c>
@@ -7539,7 +7543,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="93" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
         <v>932</v>
       </c>
@@ -7577,7 +7581,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="94" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
         <v>933</v>
       </c>
@@ -7615,7 +7619,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="95" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
         <v>934</v>
       </c>
@@ -7653,7 +7657,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="96" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
         <v>935</v>
       </c>
@@ -7691,7 +7695,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="97" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
         <v>1074</v>
       </c>
@@ -7729,7 +7733,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="98" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
         <v>936</v>
       </c>
@@ -7767,7 +7771,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="99" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
         <v>937</v>
       </c>
@@ -7805,7 +7809,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="100" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
         <v>938</v>
       </c>
@@ -7843,7 +7847,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="101" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
         <v>939</v>
       </c>
@@ -7881,7 +7885,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="102" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
         <v>940</v>
       </c>
@@ -7919,7 +7923,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="103" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
         <v>941</v>
       </c>
@@ -7957,7 +7961,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="104" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
         <v>942</v>
       </c>
@@ -7995,7 +7999,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="105" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
         <v>943</v>
       </c>
@@ -8033,7 +8037,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="106" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
         <v>944</v>
       </c>
@@ -8071,7 +8075,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="107" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
         <v>1075</v>
       </c>
@@ -8109,7 +8113,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="108" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
         <v>945</v>
       </c>
@@ -8147,7 +8151,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="109" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
         <v>1076</v>
       </c>
@@ -8185,7 +8189,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="110" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
         <v>946</v>
       </c>
@@ -8223,7 +8227,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="111" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
         <v>1077</v>
       </c>
@@ -8261,7 +8265,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="112" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
         <v>947</v>
       </c>
@@ -8299,7 +8303,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="113" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
         <v>1078</v>
       </c>
@@ -8337,7 +8341,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="114" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
         <v>948</v>
       </c>
@@ -8375,7 +8379,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="115" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
         <v>949</v>
       </c>
@@ -8413,7 +8417,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="116" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
         <v>950</v>
       </c>
@@ -8451,7 +8455,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="117" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
         <v>951</v>
       </c>
@@ -8489,7 +8493,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="118" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
         <v>952</v>
       </c>
@@ -8527,7 +8531,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="119" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
         <v>1079</v>
       </c>
@@ -8565,7 +8569,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="120" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
         <v>953</v>
       </c>
@@ -8603,7 +8607,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="121" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
         <v>1080</v>
       </c>
@@ -8641,7 +8645,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="122" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
         <v>954</v>
       </c>
@@ -8679,7 +8683,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="123" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
         <v>1081</v>
       </c>
@@ -8717,7 +8721,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="124" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
         <v>955</v>
       </c>
@@ -8755,7 +8759,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="125" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
         <v>956</v>
       </c>
@@ -8793,7 +8797,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="126" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
         <v>1082</v>
       </c>
@@ -8831,7 +8835,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="127" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
         <v>957</v>
       </c>
@@ -8869,7 +8873,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="128" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
         <v>958</v>
       </c>
@@ -8907,7 +8911,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="129" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
         <v>959</v>
       </c>
@@ -8945,7 +8949,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="130" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
         <v>1083</v>
       </c>
@@ -8983,7 +8987,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="131" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
         <v>960</v>
       </c>
@@ -9021,7 +9025,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="132" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
         <v>961</v>
       </c>
@@ -9059,7 +9063,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="133" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
         <v>962</v>
       </c>
@@ -9097,7 +9101,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="134" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
         <v>1084</v>
       </c>
@@ -9135,7 +9139,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="135" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
         <v>963</v>
       </c>
@@ -9173,7 +9177,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="136" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
         <v>964</v>
       </c>
@@ -9211,7 +9215,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="137" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
         <v>965</v>
       </c>
@@ -9249,7 +9253,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="138" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
         <v>966</v>
       </c>
@@ -9287,7 +9291,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="139" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
         <v>1085</v>
       </c>
@@ -9325,7 +9329,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="140" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
         <v>967</v>
       </c>
@@ -9363,7 +9367,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="141" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
         <v>1086</v>
       </c>
@@ -9401,7 +9405,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="142" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
         <v>968</v>
       </c>
@@ -9439,7 +9443,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="143" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
         <v>1087</v>
       </c>
@@ -9477,7 +9481,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="144" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
         <v>969</v>
       </c>
@@ -9515,7 +9519,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="145" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
         <v>970</v>
       </c>
@@ -9553,7 +9557,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="146" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
         <v>971</v>
       </c>
@@ -9591,7 +9595,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="147" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
         <v>1088</v>
       </c>
@@ -9629,7 +9633,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="148" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
         <v>1089</v>
       </c>
@@ -9667,7 +9671,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="149" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
         <v>972</v>
       </c>
@@ -9705,7 +9709,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="150" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
         <v>973</v>
       </c>
@@ -9743,7 +9747,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="151" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
         <v>974</v>
       </c>
@@ -9781,7 +9785,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="152" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
         <v>1090</v>
       </c>
@@ -9819,7 +9823,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="153" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
         <v>975</v>
       </c>
@@ -9857,7 +9861,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="154" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
         <v>976</v>
       </c>
@@ -9895,7 +9899,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="155" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
         <v>1091</v>
       </c>
@@ -9933,7 +9937,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="156" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
         <v>977</v>
       </c>
@@ -9971,7 +9975,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="157" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
         <v>978</v>
       </c>
@@ -10009,7 +10013,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="158" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
         <v>979</v>
       </c>
@@ -10047,7 +10051,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="159" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
         <v>1092</v>
       </c>
@@ -10085,7 +10089,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="160" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
         <v>980</v>
       </c>
@@ -10123,7 +10127,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="161" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
         <v>981</v>
       </c>
@@ -10161,7 +10165,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="162" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
         <v>982</v>
       </c>
@@ -10199,7 +10203,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="163" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
         <v>1093</v>
       </c>
@@ -10237,7 +10241,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="164" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
         <v>983</v>
       </c>
@@ -10275,7 +10279,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="165" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
         <v>984</v>
       </c>
@@ -10313,7 +10317,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="166" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
         <v>1094</v>
       </c>
@@ -10351,7 +10355,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="167" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
         <v>985</v>
       </c>
@@ -10389,7 +10393,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="168" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
         <v>986</v>
       </c>
@@ -10427,7 +10431,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="169" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
         <v>987</v>
       </c>
@@ -10465,7 +10469,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="170" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
         <v>988</v>
       </c>
@@ -10503,7 +10507,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="171" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
         <v>989</v>
       </c>
@@ -10541,7 +10545,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="172" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
         <v>990</v>
       </c>
@@ -10579,7 +10583,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="173" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
         <v>991</v>
       </c>
@@ -10617,7 +10621,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="174" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
         <v>992</v>
       </c>
@@ -10655,7 +10659,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="175" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
         <v>1095</v>
       </c>
@@ -10693,7 +10697,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="176" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
         <v>993</v>
       </c>
@@ -10731,7 +10735,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="177" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
         <v>994</v>
       </c>
@@ -10769,7 +10773,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="178" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
         <v>995</v>
       </c>
@@ -10807,7 +10811,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="179" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
         <v>996</v>
       </c>
@@ -10845,7 +10849,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="180" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
         <v>997</v>
       </c>
@@ -10883,7 +10887,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="181" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
         <v>998</v>
       </c>
@@ -10921,7 +10925,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="182" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
         <v>999</v>
       </c>
@@ -10959,7 +10963,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="183" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
         <v>1096</v>
       </c>
@@ -10997,7 +11001,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="184" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
         <v>1000</v>
       </c>
@@ -11035,7 +11039,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="185" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
         <v>1001</v>
       </c>
@@ -11073,7 +11077,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="186" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
         <v>1002</v>
       </c>
@@ -11111,7 +11115,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="187" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
         <v>1003</v>
       </c>
@@ -11149,7 +11153,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="188" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
         <v>1004</v>
       </c>
@@ -11187,7 +11191,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="189" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="s">
         <v>1005</v>
       </c>
@@ -11225,7 +11229,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="190" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="1" t="s">
         <v>1006</v>
       </c>
@@ -11263,7 +11267,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="191" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="1" t="s">
         <v>1097</v>
       </c>
@@ -11301,7 +11305,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="192" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="1" t="s">
         <v>1098</v>
       </c>
@@ -11339,7 +11343,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="193" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="1" t="s">
         <v>1099</v>
       </c>
@@ -11377,7 +11381,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="194" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="s">
         <v>1007</v>
       </c>
@@ -11415,7 +11419,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="195" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
         <v>1008</v>
       </c>
@@ -11453,7 +11457,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="196" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" s="1" t="s">
         <v>1009</v>
       </c>
@@ -11491,7 +11495,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="197" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="s">
         <v>1010</v>
       </c>
@@ -11529,7 +11533,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="198" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="s">
         <v>1100</v>
       </c>
@@ -11567,7 +11571,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="199" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="s">
         <v>1011</v>
       </c>
@@ -11605,7 +11609,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="200" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="1" t="s">
         <v>1101</v>
       </c>
@@ -11643,7 +11647,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="201" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="1" t="s">
         <v>1012</v>
       </c>
@@ -11681,7 +11685,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="202" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" s="1" t="s">
         <v>1102</v>
       </c>
@@ -11719,7 +11723,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="203" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" s="1" t="s">
         <v>1013</v>
       </c>
@@ -11757,7 +11761,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="204" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
         <v>1014</v>
       </c>
@@ -11795,7 +11799,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="205" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="s">
         <v>1015</v>
       </c>
@@ -11833,7 +11837,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="206" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" s="1" t="s">
         <v>1103</v>
       </c>
@@ -11871,7 +11875,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="207" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="s">
         <v>1016</v>
       </c>
@@ -11909,7 +11913,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="208" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
         <v>1017</v>
       </c>
@@ -11947,7 +11951,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="209" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" s="1" t="s">
         <v>1018</v>
       </c>
@@ -11985,7 +11989,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="210" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A210" s="1" t="s">
         <v>1019</v>
       </c>
@@ -12023,7 +12027,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="211" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" s="1" t="s">
         <v>1020</v>
       </c>
@@ -12061,7 +12065,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="212" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" s="1" t="s">
         <v>1104</v>
       </c>
@@ -12099,7 +12103,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="213" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213" s="1" t="s">
         <v>1021</v>
       </c>
@@ -12137,7 +12141,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="214" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
         <v>1022</v>
       </c>
@@ -12175,7 +12179,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="215" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
         <v>1105</v>
       </c>
@@ -12213,7 +12217,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="216" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216" s="1" t="s">
         <v>1023</v>
       </c>
@@ -12251,9 +12255,9 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="217" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A217" s="1" t="s">
-        <v>1187</v>
+        <v>1199</v>
       </c>
       <c r="B217" s="1" t="s">
         <v>197</v>
@@ -12289,7 +12293,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="218" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A218" s="1" t="s">
         <v>1106</v>
       </c>
@@ -12327,7 +12331,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="219" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219" s="1" t="s">
         <v>1107</v>
       </c>
@@ -12365,7 +12369,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="220" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="s">
         <v>1108</v>
       </c>
@@ -12403,7 +12407,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="221" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A221" s="1" t="s">
         <v>1109</v>
       </c>
@@ -12441,7 +12445,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="222" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A222" s="1" t="s">
         <v>1024</v>
       </c>
@@ -12479,7 +12483,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="223" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A223" s="1" t="s">
         <v>1025</v>
       </c>
@@ -12517,7 +12521,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="224" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A224" s="1" t="s">
         <v>1110</v>
       </c>
@@ -12555,7 +12559,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="225" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225" s="1" t="s">
         <v>1026</v>
       </c>
@@ -12593,7 +12597,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="226" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A226" s="1" t="s">
         <v>1111</v>
       </c>
@@ -12631,7 +12635,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="227" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A227" s="1" t="s">
         <v>1027</v>
       </c>
@@ -12669,7 +12673,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="228" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A228" s="1" t="s">
         <v>1112</v>
       </c>
@@ -12707,7 +12711,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="229" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A229" s="1" t="s">
         <v>1028</v>
       </c>
@@ -12745,7 +12749,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="230" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A230" s="1" t="s">
         <v>1029</v>
       </c>
@@ -12783,7 +12787,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="231" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A231" s="1" t="s">
         <v>1030</v>
       </c>
@@ -12821,7 +12825,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="232" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A232" s="1" t="s">
         <v>1031</v>
       </c>
@@ -12859,7 +12863,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="233" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A233" s="1" t="s">
         <v>1032</v>
       </c>
@@ -12897,7 +12901,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="234" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A234" s="1" t="s">
         <v>1033</v>
       </c>
@@ -12935,7 +12939,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="235" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A235" s="1" t="s">
         <v>1034</v>
       </c>
@@ -12973,7 +12977,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="236" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A236" s="1" t="s">
         <v>1035</v>
       </c>
@@ -13011,7 +13015,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="237" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="1" t="s">
         <v>1036</v>
       </c>
@@ -13049,7 +13053,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="238" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" s="1" t="s">
         <v>1113</v>
       </c>
@@ -13087,7 +13091,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="239" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A239" s="1" t="s">
         <v>1114</v>
       </c>
@@ -13125,7 +13129,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="240" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A240" s="1" t="s">
         <v>1037</v>
       </c>
@@ -13163,7 +13167,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="241" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A241" s="1" t="s">
         <v>1115</v>
       </c>
@@ -13201,7 +13205,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="242" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A242" s="1" t="s">
         <v>1038</v>
       </c>
@@ -13239,7 +13243,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="243" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A243" s="1" t="s">
         <v>1116</v>
       </c>
@@ -13277,7 +13281,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="244" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A244" s="1" t="s">
         <v>1039</v>
       </c>
@@ -13315,7 +13319,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="245" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A245" s="1" t="s">
         <v>1040</v>
       </c>
@@ -13353,7 +13357,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="246" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A246" s="1" t="s">
         <v>1041</v>
       </c>
@@ -13391,7 +13395,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="247" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A247" s="1" t="s">
         <v>1042</v>
       </c>
@@ -13429,7 +13433,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="248" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A248" s="1" t="s">
         <v>1043</v>
       </c>
@@ -13467,7 +13471,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="249" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A249" s="1" t="s">
         <v>1044</v>
       </c>
@@ -13505,7 +13509,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="250" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A250" s="1" t="s">
         <v>1117</v>
       </c>
@@ -13543,7 +13547,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="251" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A251" s="1" t="s">
         <v>1045</v>
       </c>
@@ -13581,7 +13585,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="252" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A252" s="1" t="s">
         <v>1046</v>
       </c>
@@ -13619,7 +13623,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="253" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A253" s="1" t="s">
         <v>1047</v>
       </c>
@@ -13657,7 +13661,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="254" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A254" s="1" t="s">
         <v>1048</v>
       </c>
@@ -13695,7 +13699,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="255" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255" s="1" t="s">
         <v>1118</v>
       </c>
@@ -13733,7 +13737,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="256" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A256" s="1" t="s">
         <v>1049</v>
       </c>
@@ -13771,7 +13775,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="257" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A257" s="1" t="s">
         <v>1050</v>
       </c>
@@ -13809,7 +13813,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="258" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A258" s="1" t="s">
         <v>1051</v>
       </c>
@@ -13847,7 +13851,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="259" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A259" s="1" t="s">
         <v>1052</v>
       </c>
@@ -13885,7 +13889,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="260" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A260" s="1" t="s">
         <v>1053</v>
       </c>
@@ -13923,7 +13927,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="261" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A261" s="1" t="s">
         <v>1119</v>
       </c>
@@ -13961,7 +13965,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="262" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A262" s="1" t="s">
         <v>1054</v>
       </c>
@@ -13999,7 +14003,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="263" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A263" s="1" t="s">
         <v>1055</v>
       </c>
@@ -14037,7 +14041,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="264" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A264" s="1" t="s">
         <v>1120</v>
       </c>
@@ -14075,7 +14079,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="265" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A265" s="1" t="s">
         <v>1121</v>
       </c>
@@ -14113,7 +14117,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="266" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A266" s="1" t="s">
         <v>515</v>
       </c>
@@ -14151,7 +14155,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="267" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A267" s="1" t="s">
         <v>516</v>
       </c>
@@ -14189,7 +14193,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="268" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A268" s="1" t="s">
         <v>517</v>
       </c>
@@ -14227,7 +14231,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="269" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A269" s="1" t="s">
         <v>518</v>
       </c>
@@ -14265,7 +14269,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="270" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A270" s="1" t="s">
         <v>519</v>
       </c>
@@ -14303,7 +14307,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="271" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A271" s="1" t="s">
         <v>520</v>
       </c>
@@ -14341,7 +14345,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="272" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A272" s="1" t="s">
         <v>521</v>
       </c>
@@ -14379,7 +14383,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="273" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A273" s="1" t="s">
         <v>522</v>
       </c>
@@ -14417,7 +14421,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="274" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A274" s="1" t="s">
         <v>523</v>
       </c>
@@ -14455,7 +14459,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="275" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A275" s="1" t="s">
         <v>524</v>
       </c>
@@ -14493,7 +14497,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="276" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A276" s="1" t="s">
         <v>525</v>
       </c>
@@ -14531,7 +14535,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="277" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A277" s="1" t="s">
         <v>526</v>
       </c>
@@ -14569,7 +14573,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="278" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A278" s="1" t="s">
         <v>527</v>
       </c>
@@ -14607,7 +14611,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="279" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A279" s="1" t="s">
         <v>528</v>
       </c>
@@ -14645,7 +14649,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="280" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A280" s="1" t="s">
         <v>529</v>
       </c>
@@ -14683,7 +14687,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="281" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A281" s="1" t="s">
         <v>530</v>
       </c>
@@ -14721,7 +14725,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="282" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A282" s="1" t="s">
         <v>531</v>
       </c>
@@ -14759,7 +14763,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="283" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A283" s="1" t="s">
         <v>532</v>
       </c>
@@ -14797,7 +14801,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="284" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A284" s="1" t="s">
         <v>533</v>
       </c>
@@ -14835,7 +14839,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="285" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A285" s="1" t="s">
         <v>534</v>
       </c>
@@ -14873,7 +14877,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="286" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A286" s="1" t="s">
         <v>535</v>
       </c>
@@ -14911,7 +14915,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="287" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A287" s="1" t="s">
         <v>536</v>
       </c>
@@ -14949,7 +14953,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="288" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A288" s="1" t="s">
         <v>537</v>
       </c>
@@ -14987,7 +14991,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="289" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A289" s="1" t="s">
         <v>538</v>
       </c>
@@ -15025,7 +15029,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="290" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A290" s="1" t="s">
         <v>539</v>
       </c>
@@ -15063,7 +15067,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="291" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A291" s="1" t="s">
         <v>540</v>
       </c>
@@ -15101,7 +15105,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="292" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A292" s="1" t="s">
         <v>541</v>
       </c>
@@ -15139,7 +15143,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="293" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A293" s="1" t="s">
         <v>542</v>
       </c>
@@ -15177,7 +15181,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="294" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A294" s="1" t="s">
         <v>543</v>
       </c>
@@ -15215,7 +15219,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="295" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A295" s="1" t="s">
         <v>544</v>
       </c>
@@ -15253,7 +15257,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="296" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A296" s="1" t="s">
         <v>545</v>
       </c>
@@ -15291,7 +15295,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="297" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A297" s="1" t="s">
         <v>546</v>
       </c>
@@ -15329,7 +15333,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="298" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A298" s="1" t="s">
         <v>547</v>
       </c>
@@ -15367,7 +15371,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="299" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A299" s="1" t="s">
         <v>548</v>
       </c>
@@ -15405,7 +15409,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="300" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A300" s="1" t="s">
         <v>549</v>
       </c>
@@ -15443,7 +15447,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="301" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A301" s="1" t="s">
         <v>550</v>
       </c>
@@ -15481,7 +15485,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="302" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A302" s="1" t="s">
         <v>551</v>
       </c>
@@ -15519,7 +15523,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="303" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A303" s="1" t="s">
         <v>552</v>
       </c>
@@ -15557,7 +15561,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="304" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A304" s="1" t="s">
         <v>553</v>
       </c>
@@ -15595,7 +15599,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="305" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A305" s="1" t="s">
         <v>554</v>
       </c>
@@ -15633,7 +15637,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="306" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A306" s="1" t="s">
         <v>555</v>
       </c>
@@ -15671,7 +15675,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="307" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A307" s="1" t="s">
         <v>556</v>
       </c>
@@ -15709,7 +15713,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="308" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A308" s="1" t="s">
         <v>557</v>
       </c>
@@ -15747,7 +15751,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="309" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A309" s="1" t="s">
         <v>558</v>
       </c>
@@ -15785,7 +15789,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="310" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A310" s="1" t="s">
         <v>559</v>
       </c>
@@ -15823,7 +15827,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="311" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A311" s="1" t="s">
         <v>560</v>
       </c>
@@ -15861,7 +15865,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="312" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A312" s="1" t="s">
         <v>561</v>
       </c>
@@ -15899,7 +15903,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="313" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A313" s="1" t="s">
         <v>1122</v>
       </c>
@@ -15937,7 +15941,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="314" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A314" s="1" t="s">
         <v>1123</v>
       </c>
@@ -15975,7 +15979,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="315" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A315" s="1" t="s">
         <v>562</v>
       </c>
@@ -16013,7 +16017,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="316" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A316" s="1" t="s">
         <v>563</v>
       </c>
@@ -16051,7 +16055,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="317" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A317" s="1" t="s">
         <v>1124</v>
       </c>
@@ -16089,7 +16093,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="318" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A318" s="1" t="s">
         <v>564</v>
       </c>
@@ -16127,7 +16131,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="319" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A319" s="1" t="s">
         <v>565</v>
       </c>
@@ -16165,7 +16169,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="320" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A320" s="1" t="s">
         <v>566</v>
       </c>
@@ -16203,7 +16207,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="321" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A321" s="1" t="s">
         <v>567</v>
       </c>
@@ -16241,7 +16245,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="322" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A322" s="1" t="s">
         <v>568</v>
       </c>
@@ -16279,7 +16283,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="323" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A323" s="1" t="s">
         <v>569</v>
       </c>
@@ -16317,7 +16321,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="324" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A324" s="1" t="s">
         <v>570</v>
       </c>
@@ -16355,7 +16359,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="325" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A325" s="1" t="s">
         <v>571</v>
       </c>
@@ -16393,7 +16397,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="326" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A326" s="1" t="s">
         <v>572</v>
       </c>
@@ -16431,7 +16435,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="327" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A327" s="1" t="s">
         <v>573</v>
       </c>
@@ -16469,7 +16473,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="328" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A328" s="1" t="s">
         <v>574</v>
       </c>
@@ -16507,7 +16511,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="329" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A329" s="1" t="s">
         <v>575</v>
       </c>
@@ -16545,7 +16549,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="330" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A330" s="1" t="s">
         <v>576</v>
       </c>
@@ -16583,7 +16587,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="331" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A331" s="1" t="s">
         <v>577</v>
       </c>
@@ -16621,7 +16625,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="332" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A332" s="1" t="s">
         <v>578</v>
       </c>
@@ -16659,7 +16663,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="333" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A333" s="1" t="s">
         <v>579</v>
       </c>
@@ -16697,7 +16701,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="334" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A334" s="1" t="s">
         <v>580</v>
       </c>
@@ -16735,7 +16739,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="335" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A335" s="1" t="s">
         <v>581</v>
       </c>
@@ -16773,7 +16777,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="336" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A336" s="1" t="s">
         <v>582</v>
       </c>
@@ -16811,7 +16815,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="337" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A337" s="1" t="s">
         <v>583</v>
       </c>
@@ -16849,7 +16853,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="338" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A338" s="1" t="s">
         <v>584</v>
       </c>
@@ -16887,7 +16891,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="339" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A339" s="1" t="s">
         <v>585</v>
       </c>
@@ -16925,7 +16929,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="340" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A340" s="1" t="s">
         <v>586</v>
       </c>
@@ -16963,7 +16967,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="341" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A341" s="1" t="s">
         <v>587</v>
       </c>
@@ -17001,7 +17005,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="342" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A342" s="1" t="s">
         <v>588</v>
       </c>
@@ -17039,7 +17043,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="343" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A343" s="1" t="s">
         <v>1125</v>
       </c>
@@ -17077,7 +17081,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="344" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A344" s="1" t="s">
         <v>1126</v>
       </c>
@@ -17115,7 +17119,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="345" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A345" s="1" t="s">
         <v>589</v>
       </c>
@@ -17153,7 +17157,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="346" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A346" s="1" t="s">
         <v>590</v>
       </c>
@@ -17191,7 +17195,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="347" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A347" s="1" t="s">
         <v>1127</v>
       </c>
@@ -17229,7 +17233,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="348" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A348" s="1" t="s">
         <v>591</v>
       </c>
@@ -17267,7 +17271,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="349" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A349" s="1" t="s">
         <v>592</v>
       </c>
@@ -17305,7 +17309,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="350" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A350" s="1" t="s">
         <v>593</v>
       </c>
@@ -17343,7 +17347,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="351" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A351" s="1" t="s">
         <v>594</v>
       </c>
@@ -17381,7 +17385,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="352" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A352" s="1" t="s">
         <v>595</v>
       </c>
@@ -17419,7 +17423,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="353" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A353" s="1" t="s">
         <v>596</v>
       </c>
@@ -17457,7 +17461,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="354" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A354" s="1" t="s">
         <v>597</v>
       </c>
@@ -17495,7 +17499,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="355" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A355" s="1" t="s">
         <v>598</v>
       </c>
@@ -17533,7 +17537,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="356" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A356" s="1" t="s">
         <v>599</v>
       </c>
@@ -17571,7 +17575,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="357" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A357" s="1" t="s">
         <v>600</v>
       </c>
@@ -17609,7 +17613,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="358" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A358" s="1" t="s">
         <v>601</v>
       </c>
@@ -17647,7 +17651,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="359" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A359" s="1" t="s">
         <v>602</v>
       </c>
@@ -17685,7 +17689,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="360" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A360" s="1" t="s">
         <v>603</v>
       </c>
@@ -17723,7 +17727,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="361" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A361" s="1" t="s">
         <v>604</v>
       </c>
@@ -17761,7 +17765,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="362" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A362" s="1" t="s">
         <v>605</v>
       </c>
@@ -17799,7 +17803,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="363" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A363" s="1" t="s">
         <v>606</v>
       </c>
@@ -17837,7 +17841,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="364" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A364" s="1" t="s">
         <v>607</v>
       </c>
@@ -17875,7 +17879,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="365" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A365" s="1" t="s">
         <v>608</v>
       </c>
@@ -17913,7 +17917,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="366" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A366" s="1" t="s">
         <v>609</v>
       </c>
@@ -17951,7 +17955,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="367" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A367" s="1" t="s">
         <v>610</v>
       </c>
@@ -17989,7 +17993,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="368" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A368" s="1" t="s">
         <v>611</v>
       </c>
@@ -18027,7 +18031,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="369" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A369" s="1" t="s">
         <v>612</v>
       </c>
@@ -18065,7 +18069,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="370" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A370" s="1" t="s">
         <v>613</v>
       </c>
@@ -18103,7 +18107,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="371" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A371" s="1" t="s">
         <v>614</v>
       </c>
@@ -18141,7 +18145,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="372" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A372" s="1" t="s">
         <v>615</v>
       </c>
@@ -18179,7 +18183,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="373" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A373" s="1" t="s">
         <v>616</v>
       </c>
@@ -18217,7 +18221,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="374" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A374" s="1" t="s">
         <v>617</v>
       </c>
@@ -18255,7 +18259,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="375" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A375" s="1" t="s">
         <v>618</v>
       </c>
@@ -18293,7 +18297,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="376" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A376" s="1" t="s">
         <v>619</v>
       </c>
@@ -18331,7 +18335,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="377" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A377" s="1" t="s">
         <v>1128</v>
       </c>
@@ -18369,7 +18373,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="378" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A378" s="1" t="s">
         <v>620</v>
       </c>
@@ -18407,7 +18411,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="379" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A379" s="1" t="s">
         <v>621</v>
       </c>
@@ -18445,7 +18449,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="380" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A380" s="1" t="s">
         <v>622</v>
       </c>
@@ -18483,7 +18487,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="381" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A381" s="1" t="s">
         <v>1129</v>
       </c>
@@ -18521,7 +18525,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="382" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A382" s="1" t="s">
         <v>1130</v>
       </c>
@@ -18559,7 +18563,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="383" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A383" s="1" t="s">
         <v>623</v>
       </c>
@@ -18597,7 +18601,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="384" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A384" s="1" t="s">
         <v>624</v>
       </c>
@@ -18635,7 +18639,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="385" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A385" s="1" t="s">
         <v>625</v>
       </c>
@@ -18673,7 +18677,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="386" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A386" s="1" t="s">
         <v>626</v>
       </c>
@@ -18711,7 +18715,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="387" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A387" s="1" t="s">
         <v>1131</v>
       </c>
@@ -18749,7 +18753,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="388" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A388" s="1" t="s">
         <v>627</v>
       </c>
@@ -18863,7 +18867,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="391" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A391" s="1" t="s">
         <v>1132</v>
       </c>
@@ -18901,7 +18905,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="392" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A392" s="1" t="s">
         <v>630</v>
       </c>
@@ -18939,7 +18943,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="393" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A393" s="1" t="s">
         <v>631</v>
       </c>
@@ -18977,7 +18981,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="394" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A394" s="1" t="s">
         <v>632</v>
       </c>
@@ -19015,7 +19019,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="395" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A395" s="1" t="s">
         <v>633</v>
       </c>
@@ -19053,7 +19057,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="396" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A396" s="1" t="s">
         <v>634</v>
       </c>
@@ -19091,7 +19095,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="397" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A397" s="1" t="s">
         <v>1133</v>
       </c>
@@ -19129,7 +19133,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="398" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A398" s="1" t="s">
         <v>635</v>
       </c>
@@ -19167,7 +19171,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="399" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A399" s="1" t="s">
         <v>1134</v>
       </c>
@@ -19205,7 +19209,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="400" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A400" s="1" t="s">
         <v>636</v>
       </c>
@@ -19243,7 +19247,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="401" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A401" s="1" t="s">
         <v>637</v>
       </c>
@@ -19281,7 +19285,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="402" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A402" s="1" t="s">
         <v>1135</v>
       </c>
@@ -19395,7 +19399,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="405" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A405" s="1" t="s">
         <v>640</v>
       </c>
@@ -19433,7 +19437,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="406" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A406" s="1" t="s">
         <v>641</v>
       </c>
@@ -19471,7 +19475,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="407" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A407" s="1" t="s">
         <v>642</v>
       </c>
@@ -19509,7 +19513,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="408" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A408" s="1" t="s">
         <v>643</v>
       </c>
@@ -19547,7 +19551,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="409" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A409" s="1" t="s">
         <v>644</v>
       </c>
@@ -19585,7 +19589,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="410" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A410" s="1" t="s">
         <v>645</v>
       </c>
@@ -19623,7 +19627,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="411" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A411" s="1" t="s">
         <v>646</v>
       </c>
@@ -19661,7 +19665,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="412" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A412" s="1" t="s">
         <v>647</v>
       </c>
@@ -19699,7 +19703,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="413" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A413" s="1" t="s">
         <v>648</v>
       </c>
@@ -19737,7 +19741,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="414" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A414" s="1" t="s">
         <v>649</v>
       </c>
@@ -19775,7 +19779,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="415" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A415" s="1" t="s">
         <v>650</v>
       </c>
@@ -19813,7 +19817,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="416" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A416" s="1" t="s">
         <v>651</v>
       </c>
@@ -19851,7 +19855,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="417" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A417" s="1" t="s">
         <v>652</v>
       </c>
@@ -19889,7 +19893,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="418" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A418" s="1" t="s">
         <v>653</v>
       </c>
@@ -19927,7 +19931,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="419" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A419" s="1" t="s">
         <v>654</v>
       </c>
@@ -19965,7 +19969,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="420" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A420" s="1" t="s">
         <v>655</v>
       </c>
@@ -20003,7 +20007,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="421" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A421" s="1" t="s">
         <v>656</v>
       </c>
@@ -20041,7 +20045,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="422" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A422" s="1" t="s">
         <v>657</v>
       </c>
@@ -20079,7 +20083,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="423" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A423" s="1" t="s">
         <v>658</v>
       </c>
@@ -20117,7 +20121,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="424" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A424" s="1" t="s">
         <v>659</v>
       </c>
@@ -20155,7 +20159,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="425" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A425" s="1" t="s">
         <v>660</v>
       </c>
@@ -20193,7 +20197,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="426" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A426" s="1" t="s">
         <v>661</v>
       </c>
@@ -20231,7 +20235,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="427" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A427" s="1" t="s">
         <v>662</v>
       </c>
@@ -20269,7 +20273,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="428" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A428" s="1" t="s">
         <v>663</v>
       </c>
@@ -20307,7 +20311,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="429" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A429" s="1" t="s">
         <v>664</v>
       </c>
@@ -20345,7 +20349,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="430" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A430" s="1" t="s">
         <v>665</v>
       </c>
@@ -20383,7 +20387,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="431" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A431" s="1" t="s">
         <v>666</v>
       </c>
@@ -20421,7 +20425,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="432" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A432" s="1" t="s">
         <v>667</v>
       </c>
@@ -20459,7 +20463,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="433" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A433" s="1" t="s">
         <v>668</v>
       </c>
@@ -20497,7 +20501,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="434" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A434" s="1" t="s">
         <v>669</v>
       </c>
@@ -20535,7 +20539,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="435" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A435" s="1" t="s">
         <v>670</v>
       </c>
@@ -20573,7 +20577,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="436" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A436" s="1" t="s">
         <v>671</v>
       </c>
@@ -20611,7 +20615,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="437" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A437" s="1" t="s">
         <v>672</v>
       </c>
@@ -20649,7 +20653,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="438" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A438" s="1" t="s">
         <v>673</v>
       </c>
@@ -20687,7 +20691,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="439" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A439" s="1" t="s">
         <v>674</v>
       </c>
@@ -20725,7 +20729,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="440" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A440" s="1" t="s">
         <v>675</v>
       </c>
@@ -20763,7 +20767,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="441" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A441" s="1" t="s">
         <v>676</v>
       </c>
@@ -20801,7 +20805,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="442" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A442" s="1" t="s">
         <v>677</v>
       </c>
@@ -20839,7 +20843,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="443" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A443" s="1" t="s">
         <v>678</v>
       </c>
@@ -20877,7 +20881,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="444" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A444" s="1" t="s">
         <v>679</v>
       </c>
@@ -20915,7 +20919,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="445" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A445" s="1" t="s">
         <v>680</v>
       </c>
@@ -20953,7 +20957,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="446" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A446" s="1" t="s">
         <v>681</v>
       </c>
@@ -20991,7 +20995,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="447" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A447" s="1" t="s">
         <v>682</v>
       </c>
@@ -21029,7 +21033,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="448" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A448" s="1" t="s">
         <v>683</v>
       </c>
@@ -21067,7 +21071,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="449" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A449" s="1" t="s">
         <v>684</v>
       </c>
@@ -21105,7 +21109,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="450" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A450" s="1" t="s">
         <v>685</v>
       </c>
@@ -21143,7 +21147,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="451" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A451" s="1" t="s">
         <v>686</v>
       </c>
@@ -21181,7 +21185,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="452" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A452" s="1" t="s">
         <v>687</v>
       </c>
@@ -21219,7 +21223,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="453" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A453" s="1" t="s">
         <v>688</v>
       </c>
@@ -21257,7 +21261,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="454" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A454" s="1" t="s">
         <v>689</v>
       </c>
@@ -21295,7 +21299,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="455" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A455" s="1" t="s">
         <v>690</v>
       </c>
@@ -21333,7 +21337,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="456" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A456" s="1" t="s">
         <v>691</v>
       </c>
@@ -21371,7 +21375,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="457" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A457" s="1" t="s">
         <v>692</v>
       </c>
@@ -21409,7 +21413,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="458" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A458" s="1" t="s">
         <v>693</v>
       </c>
@@ -21447,7 +21451,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="459" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A459" s="1" t="s">
         <v>694</v>
       </c>
@@ -21485,7 +21489,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="460" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A460" s="1" t="s">
         <v>695</v>
       </c>
@@ -21523,7 +21527,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="461" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A461" s="1" t="s">
         <v>696</v>
       </c>
@@ -21561,7 +21565,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="462" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A462" s="1" t="s">
         <v>697</v>
       </c>
@@ -21599,7 +21603,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="463" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A463" s="1" t="s">
         <v>698</v>
       </c>
@@ -21637,7 +21641,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="464" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A464" s="1" t="s">
         <v>699</v>
       </c>
@@ -21675,7 +21679,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="465" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A465" s="1" t="s">
         <v>700</v>
       </c>
@@ -21713,7 +21717,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="466" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A466" s="1" t="s">
         <v>701</v>
       </c>
@@ -21751,7 +21755,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="467" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A467" s="1" t="s">
         <v>702</v>
       </c>
@@ -21789,7 +21793,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="468" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A468" s="1" t="s">
         <v>703</v>
       </c>
@@ -21827,7 +21831,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="469" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A469" s="1" t="s">
         <v>704</v>
       </c>
@@ -21865,7 +21869,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="470" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A470" s="1" t="s">
         <v>1136</v>
       </c>
@@ -21903,7 +21907,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="471" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A471" s="1" t="s">
         <v>705</v>
       </c>
@@ -21941,7 +21945,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="472" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A472" s="1" t="s">
         <v>706</v>
       </c>
@@ -21979,7 +21983,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="473" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A473" s="1" t="s">
         <v>707</v>
       </c>
@@ -22017,7 +22021,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="474" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A474" s="1" t="s">
         <v>708</v>
       </c>
@@ -22055,7 +22059,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="475" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A475" s="1" t="s">
         <v>709</v>
       </c>
@@ -22093,7 +22097,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="476" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A476" s="1" t="s">
         <v>710</v>
       </c>
@@ -22131,7 +22135,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="477" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A477" s="1" t="s">
         <v>711</v>
       </c>
@@ -22169,7 +22173,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="478" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A478" s="1" t="s">
         <v>712</v>
       </c>
@@ -22207,7 +22211,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="479" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A479" s="1" t="s">
         <v>713</v>
       </c>
@@ -22245,7 +22249,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="480" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A480" s="1" t="s">
         <v>714</v>
       </c>
@@ -22283,7 +22287,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="481" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A481" s="1" t="s">
         <v>1137</v>
       </c>
@@ -22321,7 +22325,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="482" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A482" s="1" t="s">
         <v>715</v>
       </c>
@@ -22359,7 +22363,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="483" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A483" s="1" t="s">
         <v>716</v>
       </c>
@@ -22397,7 +22401,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="484" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A484" s="1" t="s">
         <v>717</v>
       </c>
@@ -22435,7 +22439,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="485" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A485" s="1" t="s">
         <v>718</v>
       </c>
@@ -22473,7 +22477,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="486" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A486" s="1" t="s">
         <v>719</v>
       </c>
@@ -22511,7 +22515,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="487" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A487" s="1" t="s">
         <v>720</v>
       </c>
@@ -22549,7 +22553,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="488" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A488" s="1" t="s">
         <v>721</v>
       </c>
@@ -22587,7 +22591,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="489" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A489" s="1" t="s">
         <v>722</v>
       </c>
@@ -22625,7 +22629,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="490" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A490" s="1" t="s">
         <v>723</v>
       </c>
@@ -22663,7 +22667,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="491" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A491" s="1" t="s">
         <v>724</v>
       </c>
@@ -22701,7 +22705,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="492" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A492" s="1" t="s">
         <v>725</v>
       </c>
@@ -22739,7 +22743,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="493" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A493" s="1" t="s">
         <v>726</v>
       </c>
@@ -22777,7 +22781,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="494" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A494" s="1" t="s">
         <v>727</v>
       </c>
@@ -22815,7 +22819,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="495" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A495" s="1" t="s">
         <v>728</v>
       </c>
@@ -22853,7 +22857,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="496" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A496" s="1" t="s">
         <v>729</v>
       </c>
@@ -22891,7 +22895,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="497" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A497" s="1" t="s">
         <v>730</v>
       </c>
@@ -22929,7 +22933,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="498" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A498" s="1" t="s">
         <v>731</v>
       </c>
@@ -22967,7 +22971,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="499" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A499" s="1" t="s">
         <v>732</v>
       </c>
@@ -23005,7 +23009,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="500" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A500" s="1" t="s">
         <v>733</v>
       </c>
@@ -23043,7 +23047,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="501" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A501" s="1" t="s">
         <v>734</v>
       </c>
@@ -23081,7 +23085,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="502" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A502" s="1" t="s">
         <v>735</v>
       </c>
@@ -23119,7 +23123,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="503" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A503" s="1" t="s">
         <v>736</v>
       </c>
@@ -23157,7 +23161,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="504" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A504" s="1" t="s">
         <v>737</v>
       </c>
@@ -23195,7 +23199,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="505" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A505" s="1" t="s">
         <v>738</v>
       </c>
@@ -23233,7 +23237,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="506" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A506" s="1" t="s">
         <v>739</v>
       </c>
@@ -23271,7 +23275,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="507" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A507" s="1" t="s">
         <v>740</v>
       </c>
@@ -23309,7 +23313,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="508" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A508" s="1" t="s">
         <v>741</v>
       </c>
@@ -23347,7 +23351,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="509" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A509" s="1" t="s">
         <v>742</v>
       </c>
@@ -23385,7 +23389,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="510" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A510" s="1" t="s">
         <v>743</v>
       </c>
@@ -23423,7 +23427,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="511" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A511" s="1" t="s">
         <v>744</v>
       </c>
@@ -23461,7 +23465,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="512" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A512" s="1" t="s">
         <v>745</v>
       </c>
@@ -23499,7 +23503,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="513" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A513" s="1" t="s">
         <v>746</v>
       </c>
@@ -23537,7 +23541,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="514" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A514" s="1" t="s">
         <v>747</v>
       </c>
@@ -23575,7 +23579,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="515" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A515" s="1" t="s">
         <v>748</v>
       </c>
@@ -23613,7 +23617,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="516" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A516" s="1" t="s">
         <v>749</v>
       </c>
@@ -23651,7 +23655,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="517" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A517" s="1" t="s">
         <v>750</v>
       </c>
@@ -23689,7 +23693,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="518" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A518" s="1" t="s">
         <v>751</v>
       </c>
@@ -23727,7 +23731,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="519" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A519" s="1" t="s">
         <v>752</v>
       </c>
@@ -23765,7 +23769,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="520" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A520" s="1" t="s">
         <v>753</v>
       </c>
@@ -23803,7 +23807,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="521" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A521" s="1" t="s">
         <v>754</v>
       </c>
@@ -23841,7 +23845,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="522" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A522" s="1" t="s">
         <v>755</v>
       </c>
@@ -23879,7 +23883,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="523" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A523" s="1" t="s">
         <v>756</v>
       </c>
@@ -23917,7 +23921,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="524" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A524" s="1" t="s">
         <v>757</v>
       </c>
@@ -24031,7 +24035,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="527" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A527" s="1" t="s">
         <v>760</v>
       </c>
@@ -24069,7 +24073,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="528" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A528" s="1" t="s">
         <v>761</v>
       </c>
@@ -24107,7 +24111,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="529" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A529" s="1" t="s">
         <v>762</v>
       </c>
@@ -24145,7 +24149,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="530" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A530" s="1" t="s">
         <v>763</v>
       </c>
@@ -24183,7 +24187,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="531" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A531" s="1" t="s">
         <v>764</v>
       </c>
@@ -24221,7 +24225,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="532" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A532" s="1" t="s">
         <v>765</v>
       </c>
@@ -24259,7 +24263,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="533" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A533" s="1" t="s">
         <v>766</v>
       </c>
@@ -24297,7 +24301,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="534" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A534" s="1" t="s">
         <v>767</v>
       </c>
@@ -24335,7 +24339,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="535" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A535" s="1" t="s">
         <v>768</v>
       </c>
@@ -24373,7 +24377,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="536" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A536" s="1" t="s">
         <v>769</v>
       </c>
@@ -24411,7 +24415,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="537" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A537" s="1" t="s">
         <v>770</v>
       </c>
@@ -24449,7 +24453,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="538" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A538" s="1" t="s">
         <v>771</v>
       </c>
@@ -24487,7 +24491,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="539" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A539" s="1" t="s">
         <v>772</v>
       </c>
@@ -24525,7 +24529,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="540" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A540" s="1" t="s">
         <v>773</v>
       </c>
@@ -24563,7 +24567,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="541" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A541" s="1" t="s">
         <v>774</v>
       </c>
@@ -24601,7 +24605,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="542" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A542" s="1" t="s">
         <v>775</v>
       </c>
@@ -24639,7 +24643,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="543" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A543" s="1" t="s">
         <v>776</v>
       </c>
@@ -24677,7 +24681,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="544" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A544" s="1" t="s">
         <v>777</v>
       </c>
@@ -24715,7 +24719,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="545" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A545" s="1" t="s">
         <v>778</v>
       </c>
@@ -24753,7 +24757,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="546" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A546" s="1" t="s">
         <v>779</v>
       </c>
@@ -24791,7 +24795,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="547" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A547" s="1" t="s">
         <v>780</v>
       </c>
@@ -24829,7 +24833,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="548" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A548" s="1" t="s">
         <v>781</v>
       </c>
@@ -24867,7 +24871,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="549" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A549" s="1" t="s">
         <v>782</v>
       </c>
@@ -24905,7 +24909,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="550" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A550" s="1" t="s">
         <v>783</v>
       </c>
@@ -24943,7 +24947,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="551" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A551" s="1" t="s">
         <v>784</v>
       </c>
@@ -24981,7 +24985,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="552" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A552" s="1" t="s">
         <v>785</v>
       </c>
@@ -25019,7 +25023,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="553" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A553" s="1" t="s">
         <v>786</v>
       </c>
@@ -25057,7 +25061,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="554" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A554" s="1" t="s">
         <v>787</v>
       </c>
@@ -25095,7 +25099,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="555" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A555" s="1" t="s">
         <v>788</v>
       </c>
@@ -25133,7 +25137,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="556" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A556" s="1" t="s">
         <v>789</v>
       </c>
@@ -25171,7 +25175,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="557" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A557" s="1" t="s">
         <v>790</v>
       </c>
@@ -25209,7 +25213,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="558" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A558" s="1" t="s">
         <v>791</v>
       </c>
@@ -25247,7 +25251,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="559" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A559" s="1" t="s">
         <v>792</v>
       </c>
@@ -25285,7 +25289,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="560" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A560" s="1" t="s">
         <v>793</v>
       </c>
@@ -25323,7 +25327,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="561" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A561" s="1" t="s">
         <v>794</v>
       </c>
@@ -25361,7 +25365,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="562" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A562" s="1" t="s">
         <v>795</v>
       </c>
@@ -25399,7 +25403,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="563" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A563" s="1" t="s">
         <v>796</v>
       </c>
@@ -25437,7 +25441,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="564" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A564" s="1" t="s">
         <v>797</v>
       </c>
@@ -25475,7 +25479,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="565" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A565" s="1" t="s">
         <v>798</v>
       </c>
@@ -25513,7 +25517,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="566" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A566" s="1" t="s">
         <v>799</v>
       </c>
@@ -25551,7 +25555,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="567" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A567" s="1" t="s">
         <v>800</v>
       </c>
@@ -25589,7 +25593,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="568" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A568" s="1" t="s">
         <v>801</v>
       </c>
@@ -25627,7 +25631,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="569" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A569" s="1" t="s">
         <v>802</v>
       </c>
@@ -25665,7 +25669,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="570" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A570" s="1" t="s">
         <v>803</v>
       </c>
@@ -25779,7 +25783,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="573" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A573" s="1" t="s">
         <v>806</v>
       </c>
@@ -25817,7 +25821,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="574" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A574" s="1" t="s">
         <v>807</v>
       </c>
@@ -25855,7 +25859,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="575" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A575" s="1" t="s">
         <v>808</v>
       </c>
@@ -25893,7 +25897,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="576" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A576" s="1" t="s">
         <v>809</v>
       </c>
@@ -25931,7 +25935,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="577" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A577" s="1" t="s">
         <v>1138</v>
       </c>
@@ -25969,7 +25973,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="578" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A578" s="1" t="s">
         <v>1139</v>
       </c>
@@ -26007,7 +26011,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="579" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A579" s="1" t="s">
         <v>810</v>
       </c>
@@ -26045,7 +26049,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="580" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A580" s="1" t="s">
         <v>811</v>
       </c>
@@ -26083,7 +26087,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="581" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A581" s="1" t="s">
         <v>812</v>
       </c>
@@ -26121,7 +26125,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="582" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A582" s="1" t="s">
         <v>813</v>
       </c>
@@ -26159,7 +26163,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="583" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A583" s="1" t="s">
         <v>814</v>
       </c>
@@ -26197,7 +26201,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="584" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A584" s="1" t="s">
         <v>815</v>
       </c>
@@ -26235,7 +26239,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="585" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A585" s="1" t="s">
         <v>816</v>
       </c>
@@ -26273,7 +26277,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="586" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A586" s="1" t="s">
         <v>817</v>
       </c>
@@ -26311,7 +26315,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="587" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A587" s="1" t="s">
         <v>818</v>
       </c>
@@ -26349,7 +26353,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="588" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A588" s="1" t="s">
         <v>819</v>
       </c>
@@ -26387,7 +26391,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="589" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A589" s="1" t="s">
         <v>820</v>
       </c>
@@ -26425,7 +26429,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="590" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A590" s="1" t="s">
         <v>821</v>
       </c>
@@ -26463,7 +26467,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="591" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A591" s="1" t="s">
         <v>822</v>
       </c>
@@ -26501,7 +26505,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="592" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A592" s="1" t="s">
         <v>823</v>
       </c>
@@ -26539,7 +26543,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="593" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A593" s="1" t="s">
         <v>1140</v>
       </c>
@@ -26577,7 +26581,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="594" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A594" s="1" t="s">
         <v>824</v>
       </c>
@@ -26615,7 +26619,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="595" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A595" s="1" t="s">
         <v>1141</v>
       </c>
@@ -26653,7 +26657,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="596" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A596" s="1" t="s">
         <v>825</v>
       </c>
@@ -26691,7 +26695,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="597" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A597" s="1" t="s">
         <v>826</v>
       </c>
@@ -26729,7 +26733,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="598" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A598" s="1" t="s">
         <v>827</v>
       </c>
@@ -26767,7 +26771,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="599" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A599" s="1" t="s">
         <v>828</v>
       </c>
@@ -26805,7 +26809,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="600" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A600" s="1" t="s">
         <v>829</v>
       </c>
@@ -26843,7 +26847,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="601" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A601" s="1" t="s">
         <v>830</v>
       </c>
@@ -26881,7 +26885,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="602" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A602" s="1" t="s">
         <v>1142</v>
       </c>
@@ -26919,7 +26923,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="603" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A603" s="1" t="s">
         <v>831</v>
       </c>
@@ -26957,7 +26961,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="604" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A604" s="1" t="s">
         <v>832</v>
       </c>
@@ -26995,7 +26999,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="605" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A605" s="1" t="s">
         <v>833</v>
       </c>
@@ -27033,7 +27037,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="606" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A606" s="1" t="s">
         <v>834</v>
       </c>
@@ -27071,7 +27075,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="607" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A607" s="1" t="s">
         <v>835</v>
       </c>
@@ -27109,7 +27113,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="608" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A608" s="1" t="s">
         <v>836</v>
       </c>
@@ -27147,7 +27151,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="609" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A609" s="1" t="s">
         <v>837</v>
       </c>
@@ -27185,7 +27189,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="610" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A610" s="1" t="s">
         <v>838</v>
       </c>
@@ -27223,7 +27227,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="611" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A611" s="1" t="s">
         <v>839</v>
       </c>
@@ -27261,7 +27265,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="612" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A612" s="1" t="s">
         <v>840</v>
       </c>
@@ -27299,7 +27303,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="613" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A613" s="1" t="s">
         <v>841</v>
       </c>
@@ -27337,7 +27341,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="614" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A614" s="1" t="s">
         <v>842</v>
       </c>
@@ -27375,7 +27379,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="615" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A615" s="1" t="s">
         <v>843</v>
       </c>
@@ -27413,7 +27417,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="616" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A616" s="1" t="s">
         <v>844</v>
       </c>
@@ -27451,7 +27455,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="617" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A617" s="1" t="s">
         <v>845</v>
       </c>
@@ -27489,7 +27493,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="618" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A618" s="1" t="s">
         <v>846</v>
       </c>
@@ -27527,7 +27531,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="619" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A619" s="1" t="s">
         <v>847</v>
       </c>
@@ -27565,7 +27569,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="620" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A620" s="1" t="s">
         <v>848</v>
       </c>
@@ -27603,7 +27607,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="621" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A621" s="1" t="s">
         <v>849</v>
       </c>
@@ -27641,7 +27645,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="622" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A622" s="1" t="s">
         <v>850</v>
       </c>
@@ -27679,7 +27683,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="623" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A623" s="1" t="s">
         <v>851</v>
       </c>
@@ -27717,7 +27721,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="624" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A624" s="1" t="s">
         <v>852</v>
       </c>
@@ -27755,7 +27759,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="625" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A625" s="1" t="s">
         <v>853</v>
       </c>
@@ -27793,7 +27797,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="626" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A626" s="1" t="s">
         <v>854</v>
       </c>
@@ -27831,7 +27835,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="627" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A627" s="1" t="s">
         <v>855</v>
       </c>
@@ -27869,7 +27873,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="628" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A628" s="1" t="s">
         <v>1183</v>
       </c>
@@ -27907,7 +27911,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="629" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A629" s="1" t="s">
         <v>1184</v>
       </c>
@@ -27945,7 +27949,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="630" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A630" s="1" t="s">
         <v>1185</v>
       </c>
@@ -27983,7 +27987,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="631" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A631" s="1" t="s">
         <v>1186</v>
       </c>
@@ -28021,7 +28025,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="632" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A632" s="1" t="s">
         <v>1197</v>
       </c>
@@ -28059,7 +28063,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="633" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A633" s="1" t="s">
         <v>1187</v>
       </c>
@@ -28097,7 +28101,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="634" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A634" s="1" t="s">
         <v>1188</v>
       </c>
@@ -28135,7 +28139,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="635" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A635" s="1" t="s">
         <v>1189</v>
       </c>
@@ -28173,7 +28177,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="636" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A636" s="1" t="s">
         <v>1190</v>
       </c>
@@ -28211,7 +28215,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="637" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
       <c r="A637" s="1" t="s">
         <v>1191</v>
       </c>
@@ -28478,7 +28482,17 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L643" xr:uid="{E0D1E054-7418-4233-9A16-A15E844DE850}"/>
+  <autoFilter ref="A1:L643" xr:uid="{E0D1E054-7418-4233-9A16-A15E844DE850}">
+    <filterColumn colId="4">
+      <filters>
+        <filter val="CORRE VENTO 3"/>
+        <filter val="JAQUETA CORTA/VENTO CORRE F"/>
+        <filter val="JAQUETA CORTA/VENTO CORRE M"/>
+        <filter val="JAQUETA QUEBRA/VENTO ESSENTIAL F"/>
+        <filter val="JAQUETA QUEBRA/VENTO ESSENTIAL M"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>

--- a/Produtos.xlsx
+++ b/Produtos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NOT-MARCOS\Documents\GitHub\Catalogo-Olympikus_2.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4871435-A9F7-499E-B17C-B3634CA3A95E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDD6B7EB-6B60-45EC-849D-360F38686C71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{C851EA1D-5267-41B7-9513-D07E5A57DEF2}"/>
   </bookViews>
@@ -4033,7 +4033,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0D1E054-7418-4233-9A16-A15E844DE850}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:L643"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -4085,7 +4084,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1056</v>
       </c>
@@ -4123,7 +4122,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>1057</v>
       </c>
@@ -4161,7 +4160,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>859</v>
       </c>
@@ -4199,7 +4198,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>860</v>
       </c>
@@ -4237,7 +4236,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>861</v>
       </c>
@@ -4275,7 +4274,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>862</v>
       </c>
@@ -4313,7 +4312,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>863</v>
       </c>
@@ -4351,7 +4350,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>864</v>
       </c>
@@ -4389,7 +4388,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>865</v>
       </c>
@@ -4427,7 +4426,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>866</v>
       </c>
@@ -4465,7 +4464,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>867</v>
       </c>
@@ -4503,7 +4502,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>868</v>
       </c>
@@ -4541,7 +4540,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>869</v>
       </c>
@@ -4579,7 +4578,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>870</v>
       </c>
@@ -4617,7 +4616,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>871</v>
       </c>
@@ -4655,7 +4654,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="17" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>1058</v>
       </c>
@@ -4693,7 +4692,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>872</v>
       </c>
@@ -4731,7 +4730,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="19" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>873</v>
       </c>
@@ -4769,7 +4768,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="20" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>874</v>
       </c>
@@ -4807,7 +4806,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="21" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>1059</v>
       </c>
@@ -4845,7 +4844,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="22" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>875</v>
       </c>
@@ -4883,7 +4882,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="23" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
         <v>876</v>
       </c>
@@ -4921,7 +4920,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="24" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>877</v>
       </c>
@@ -4959,7 +4958,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="25" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>1060</v>
       </c>
@@ -4997,7 +4996,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="26" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>878</v>
       </c>
@@ -5035,7 +5034,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="27" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>879</v>
       </c>
@@ -5073,7 +5072,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="28" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>880</v>
       </c>
@@ -5111,7 +5110,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="29" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>1061</v>
       </c>
@@ -5149,7 +5148,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="30" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>881</v>
       </c>
@@ -5187,7 +5186,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="31" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>1062</v>
       </c>
@@ -5225,7 +5224,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="32" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>882</v>
       </c>
@@ -5263,7 +5262,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="33" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>883</v>
       </c>
@@ -5301,7 +5300,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="34" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>1063</v>
       </c>
@@ -5339,7 +5338,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="35" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>1064</v>
       </c>
@@ -5377,7 +5376,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="36" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>884</v>
       </c>
@@ -5415,7 +5414,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="37" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>885</v>
       </c>
@@ -5453,7 +5452,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="38" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>1065</v>
       </c>
@@ -5491,7 +5490,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="39" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>886</v>
       </c>
@@ -5529,7 +5528,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="40" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>1066</v>
       </c>
@@ -5567,7 +5566,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="41" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>887</v>
       </c>
@@ -5605,7 +5604,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="42" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>888</v>
       </c>
@@ -5643,7 +5642,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="43" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>889</v>
       </c>
@@ -5681,7 +5680,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="44" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>1067</v>
       </c>
@@ -5719,7 +5718,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="45" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>890</v>
       </c>
@@ -5757,7 +5756,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="46" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>891</v>
       </c>
@@ -5795,7 +5794,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="47" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>892</v>
       </c>
@@ -5833,7 +5832,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="48" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>893</v>
       </c>
@@ -5871,7 +5870,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="49" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>1068</v>
       </c>
@@ -5909,7 +5908,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="50" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>894</v>
       </c>
@@ -5947,7 +5946,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="51" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>895</v>
       </c>
@@ -5985,7 +5984,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="52" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>896</v>
       </c>
@@ -6023,7 +6022,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="53" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>1069</v>
       </c>
@@ -6061,7 +6060,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="54" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>1070</v>
       </c>
@@ -6099,7 +6098,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="55" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>897</v>
       </c>
@@ -6137,7 +6136,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="56" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>898</v>
       </c>
@@ -6175,7 +6174,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="57" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>899</v>
       </c>
@@ -6213,7 +6212,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="58" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>900</v>
       </c>
@@ -6251,7 +6250,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="59" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>901</v>
       </c>
@@ -6289,7 +6288,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="60" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>902</v>
       </c>
@@ -6327,7 +6326,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="61" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>903</v>
       </c>
@@ -6365,7 +6364,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="62" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>904</v>
       </c>
@@ -6403,7 +6402,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="63" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>1071</v>
       </c>
@@ -6441,7 +6440,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="64" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>905</v>
       </c>
@@ -6479,7 +6478,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="65" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>906</v>
       </c>
@@ -6517,7 +6516,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="66" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>1072</v>
       </c>
@@ -6555,7 +6554,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="67" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>907</v>
       </c>
@@ -6593,7 +6592,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="68" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>908</v>
       </c>
@@ -6631,7 +6630,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="69" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>909</v>
       </c>
@@ -6669,7 +6668,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="70" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>910</v>
       </c>
@@ -6707,7 +6706,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="71" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
         <v>911</v>
       </c>
@@ -6745,7 +6744,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="72" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>912</v>
       </c>
@@ -6783,7 +6782,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="73" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>913</v>
       </c>
@@ -6821,7 +6820,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="74" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>914</v>
       </c>
@@ -6859,7 +6858,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="75" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
         <v>915</v>
       </c>
@@ -6897,7 +6896,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="76" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
         <v>1073</v>
       </c>
@@ -6935,7 +6934,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="77" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
         <v>916</v>
       </c>
@@ -6973,7 +6972,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="78" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
         <v>917</v>
       </c>
@@ -7011,7 +7010,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="79" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
         <v>918</v>
       </c>
@@ -7049,7 +7048,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="80" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
         <v>919</v>
       </c>
@@ -7087,7 +7086,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="81" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
         <v>920</v>
       </c>
@@ -7125,7 +7124,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="82" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
         <v>921</v>
       </c>
@@ -7163,7 +7162,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="83" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
         <v>922</v>
       </c>
@@ -7201,7 +7200,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="84" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
         <v>923</v>
       </c>
@@ -7239,7 +7238,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="85" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
         <v>924</v>
       </c>
@@ -7277,7 +7276,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="86" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
         <v>925</v>
       </c>
@@ -7315,7 +7314,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="87" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
         <v>926</v>
       </c>
@@ -7353,7 +7352,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="88" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
         <v>927</v>
       </c>
@@ -7391,7 +7390,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="89" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
         <v>928</v>
       </c>
@@ -7429,7 +7428,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="90" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
         <v>929</v>
       </c>
@@ -7467,7 +7466,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="91" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
         <v>930</v>
       </c>
@@ -7505,7 +7504,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="92" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
         <v>931</v>
       </c>
@@ -7543,7 +7542,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="93" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
         <v>932</v>
       </c>
@@ -7581,7 +7580,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="94" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
         <v>933</v>
       </c>
@@ -7619,7 +7618,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="95" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
         <v>934</v>
       </c>
@@ -7657,7 +7656,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="96" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
         <v>935</v>
       </c>
@@ -7695,7 +7694,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="97" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
         <v>1074</v>
       </c>
@@ -7733,7 +7732,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="98" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
         <v>936</v>
       </c>
@@ -7771,7 +7770,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="99" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
         <v>937</v>
       </c>
@@ -7809,7 +7808,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="100" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
         <v>938</v>
       </c>
@@ -7847,7 +7846,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="101" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
         <v>939</v>
       </c>
@@ -7885,7 +7884,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="102" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
         <v>940</v>
       </c>
@@ -7923,7 +7922,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="103" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
         <v>941</v>
       </c>
@@ -7961,7 +7960,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="104" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
         <v>942</v>
       </c>
@@ -7999,7 +7998,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="105" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
         <v>943</v>
       </c>
@@ -8037,7 +8036,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="106" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
         <v>944</v>
       </c>
@@ -8075,7 +8074,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="107" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
         <v>1075</v>
       </c>
@@ -8113,7 +8112,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="108" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
         <v>945</v>
       </c>
@@ -8151,7 +8150,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="109" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
         <v>1076</v>
       </c>
@@ -8189,7 +8188,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="110" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
         <v>946</v>
       </c>
@@ -8227,7 +8226,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="111" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
         <v>1077</v>
       </c>
@@ -8265,7 +8264,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="112" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
         <v>947</v>
       </c>
@@ -8303,7 +8302,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="113" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
         <v>1078</v>
       </c>
@@ -8341,7 +8340,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="114" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
         <v>948</v>
       </c>
@@ -8379,7 +8378,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="115" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
         <v>949</v>
       </c>
@@ -8417,7 +8416,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="116" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
         <v>950</v>
       </c>
@@ -8455,7 +8454,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="117" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
         <v>951</v>
       </c>
@@ -8493,7 +8492,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="118" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
         <v>952</v>
       </c>
@@ -8531,7 +8530,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="119" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
         <v>1079</v>
       </c>
@@ -8569,7 +8568,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="120" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
         <v>953</v>
       </c>
@@ -8607,7 +8606,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="121" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
         <v>1080</v>
       </c>
@@ -8645,7 +8644,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="122" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
         <v>954</v>
       </c>
@@ -8683,7 +8682,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="123" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
         <v>1081</v>
       </c>
@@ -8721,7 +8720,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="124" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
         <v>955</v>
       </c>
@@ -8759,7 +8758,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="125" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
         <v>956</v>
       </c>
@@ -8797,7 +8796,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="126" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
         <v>1082</v>
       </c>
@@ -8835,7 +8834,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="127" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
         <v>957</v>
       </c>
@@ -8873,7 +8872,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="128" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
         <v>958</v>
       </c>
@@ -8911,7 +8910,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="129" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
         <v>959</v>
       </c>
@@ -8949,7 +8948,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="130" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
         <v>1083</v>
       </c>
@@ -8987,7 +8986,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="131" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
         <v>960</v>
       </c>
@@ -9025,7 +9024,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="132" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
         <v>961</v>
       </c>
@@ -9063,7 +9062,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="133" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
         <v>962</v>
       </c>
@@ -9101,7 +9100,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="134" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
         <v>1084</v>
       </c>
@@ -9139,7 +9138,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="135" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
         <v>963</v>
       </c>
@@ -9177,7 +9176,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="136" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
         <v>964</v>
       </c>
@@ -9215,7 +9214,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="137" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="s">
         <v>965</v>
       </c>
@@ -9253,7 +9252,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="138" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
         <v>966</v>
       </c>
@@ -9291,7 +9290,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="139" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
         <v>1085</v>
       </c>
@@ -9329,7 +9328,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="140" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
         <v>967</v>
       </c>
@@ -9367,7 +9366,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="141" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
         <v>1086</v>
       </c>
@@ -9405,7 +9404,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="142" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
         <v>968</v>
       </c>
@@ -9443,7 +9442,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="143" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
         <v>1087</v>
       </c>
@@ -9481,7 +9480,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="144" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
         <v>969</v>
       </c>
@@ -9519,7 +9518,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="145" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
         <v>970</v>
       </c>
@@ -9557,7 +9556,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="146" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
         <v>971</v>
       </c>
@@ -9595,7 +9594,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="147" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
         <v>1088</v>
       </c>
@@ -9633,7 +9632,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="148" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
         <v>1089</v>
       </c>
@@ -9671,7 +9670,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="149" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
         <v>972</v>
       </c>
@@ -9709,7 +9708,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="150" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
         <v>973</v>
       </c>
@@ -9747,7 +9746,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="151" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
         <v>974</v>
       </c>
@@ -9785,7 +9784,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="152" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
         <v>1090</v>
       </c>
@@ -9823,7 +9822,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="153" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
         <v>975</v>
       </c>
@@ -9861,7 +9860,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="154" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
         <v>976</v>
       </c>
@@ -9899,7 +9898,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="155" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
         <v>1091</v>
       </c>
@@ -9937,7 +9936,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="156" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
         <v>977</v>
       </c>
@@ -9975,7 +9974,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="157" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
         <v>978</v>
       </c>
@@ -10013,7 +10012,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="158" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
         <v>979</v>
       </c>
@@ -10051,7 +10050,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="159" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
         <v>1092</v>
       </c>
@@ -10089,7 +10088,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="160" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
         <v>980</v>
       </c>
@@ -10127,7 +10126,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="161" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
         <v>981</v>
       </c>
@@ -10165,7 +10164,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="162" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
         <v>982</v>
       </c>
@@ -10203,7 +10202,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="163" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
         <v>1093</v>
       </c>
@@ -10241,7 +10240,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="164" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
         <v>983</v>
       </c>
@@ -10279,7 +10278,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="165" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
         <v>984</v>
       </c>
@@ -10317,7 +10316,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="166" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
         <v>1094</v>
       </c>
@@ -10355,7 +10354,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="167" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
         <v>985</v>
       </c>
@@ -10393,7 +10392,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="168" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
         <v>986</v>
       </c>
@@ -10431,7 +10430,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="169" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
         <v>987</v>
       </c>
@@ -10469,7 +10468,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="170" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
         <v>988</v>
       </c>
@@ -10507,7 +10506,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="171" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
         <v>989</v>
       </c>
@@ -10545,7 +10544,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="172" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
         <v>990</v>
       </c>
@@ -10583,7 +10582,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="173" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
         <v>991</v>
       </c>
@@ -10621,7 +10620,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="174" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
         <v>992</v>
       </c>
@@ -10659,7 +10658,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="175" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
         <v>1095</v>
       </c>
@@ -10697,7 +10696,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="176" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="s">
         <v>993</v>
       </c>
@@ -10735,7 +10734,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="177" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
         <v>994</v>
       </c>
@@ -10773,7 +10772,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="178" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="s">
         <v>995</v>
       </c>
@@ -10811,7 +10810,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="179" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
         <v>996</v>
       </c>
@@ -10849,7 +10848,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="180" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="s">
         <v>997</v>
       </c>
@@ -10887,7 +10886,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="181" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="s">
         <v>998</v>
       </c>
@@ -10925,7 +10924,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="182" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="s">
         <v>999</v>
       </c>
@@ -10963,7 +10962,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="183" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="s">
         <v>1096</v>
       </c>
@@ -11001,7 +11000,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="184" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="s">
         <v>1000</v>
       </c>
@@ -11039,7 +11038,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="185" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
         <v>1001</v>
       </c>
@@ -11077,7 +11076,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="186" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="s">
         <v>1002</v>
       </c>
@@ -11115,7 +11114,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="187" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="s">
         <v>1003</v>
       </c>
@@ -11153,7 +11152,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="188" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
         <v>1004</v>
       </c>
@@ -11191,7 +11190,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="189" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="s">
         <v>1005</v>
       </c>
@@ -11229,7 +11228,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="190" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="1" t="s">
         <v>1006</v>
       </c>
@@ -11267,7 +11266,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="191" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="1" t="s">
         <v>1097</v>
       </c>
@@ -11305,7 +11304,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="192" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="1" t="s">
         <v>1098</v>
       </c>
@@ -11343,7 +11342,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="193" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="1" t="s">
         <v>1099</v>
       </c>
@@ -11381,7 +11380,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="194" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="s">
         <v>1007</v>
       </c>
@@ -11419,7 +11418,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="195" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="s">
         <v>1008</v>
       </c>
@@ -11457,7 +11456,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="196" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" s="1" t="s">
         <v>1009</v>
       </c>
@@ -11495,7 +11494,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="197" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="s">
         <v>1010</v>
       </c>
@@ -11533,7 +11532,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="198" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="s">
         <v>1100</v>
       </c>
@@ -11571,7 +11570,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="199" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="s">
         <v>1011</v>
       </c>
@@ -11609,7 +11608,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="200" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="1" t="s">
         <v>1101</v>
       </c>
@@ -11647,7 +11646,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="201" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="1" t="s">
         <v>1012</v>
       </c>
@@ -11685,7 +11684,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="202" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" s="1" t="s">
         <v>1102</v>
       </c>
@@ -11723,7 +11722,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="203" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" s="1" t="s">
         <v>1013</v>
       </c>
@@ -11761,7 +11760,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="204" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="s">
         <v>1014</v>
       </c>
@@ -11799,7 +11798,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="205" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="s">
         <v>1015</v>
       </c>
@@ -11837,7 +11836,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="206" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" s="1" t="s">
         <v>1103</v>
       </c>
@@ -11875,7 +11874,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="207" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="s">
         <v>1016</v>
       </c>
@@ -11913,7 +11912,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="208" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="s">
         <v>1017</v>
       </c>
@@ -11951,7 +11950,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="209" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" s="1" t="s">
         <v>1018</v>
       </c>
@@ -11989,7 +11988,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="210" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A210" s="1" t="s">
         <v>1019</v>
       </c>
@@ -12027,7 +12026,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="211" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" s="1" t="s">
         <v>1020</v>
       </c>
@@ -12065,7 +12064,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="212" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" s="1" t="s">
         <v>1104</v>
       </c>
@@ -12103,7 +12102,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="213" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213" s="1" t="s">
         <v>1021</v>
       </c>
@@ -12141,7 +12140,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="214" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="s">
         <v>1022</v>
       </c>
@@ -12179,7 +12178,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="215" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="s">
         <v>1105</v>
       </c>
@@ -12217,7 +12216,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="216" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216" s="1" t="s">
         <v>1023</v>
       </c>
@@ -12255,7 +12254,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="217" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A217" s="1" t="s">
         <v>1199</v>
       </c>
@@ -12293,7 +12292,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="218" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A218" s="1" t="s">
         <v>1106</v>
       </c>
@@ -12331,7 +12330,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="219" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219" s="1" t="s">
         <v>1107</v>
       </c>
@@ -12369,7 +12368,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="220" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="s">
         <v>1108</v>
       </c>
@@ -12407,7 +12406,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="221" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A221" s="1" t="s">
         <v>1109</v>
       </c>
@@ -12445,7 +12444,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="222" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A222" s="1" t="s">
         <v>1024</v>
       </c>
@@ -12483,7 +12482,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="223" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A223" s="1" t="s">
         <v>1025</v>
       </c>
@@ -12521,7 +12520,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="224" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A224" s="1" t="s">
         <v>1110</v>
       </c>
@@ -12559,7 +12558,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="225" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225" s="1" t="s">
         <v>1026</v>
       </c>
@@ -12597,7 +12596,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="226" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A226" s="1" t="s">
         <v>1111</v>
       </c>
@@ -12635,7 +12634,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="227" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A227" s="1" t="s">
         <v>1027</v>
       </c>
@@ -12673,7 +12672,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="228" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A228" s="1" t="s">
         <v>1112</v>
       </c>
@@ -12711,7 +12710,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="229" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A229" s="1" t="s">
         <v>1028</v>
       </c>
@@ -12749,7 +12748,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="230" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A230" s="1" t="s">
         <v>1029</v>
       </c>
@@ -12787,7 +12786,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="231" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A231" s="1" t="s">
         <v>1030</v>
       </c>
@@ -12825,7 +12824,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="232" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A232" s="1" t="s">
         <v>1031</v>
       </c>
@@ -12863,7 +12862,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="233" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A233" s="1" t="s">
         <v>1032</v>
       </c>
@@ -12901,7 +12900,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="234" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A234" s="1" t="s">
         <v>1033</v>
       </c>
@@ -12939,7 +12938,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="235" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A235" s="1" t="s">
         <v>1034</v>
       </c>
@@ -12977,7 +12976,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="236" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A236" s="1" t="s">
         <v>1035</v>
       </c>
@@ -13015,7 +13014,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="237" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="1" t="s">
         <v>1036</v>
       </c>
@@ -13053,7 +13052,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="238" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" s="1" t="s">
         <v>1113</v>
       </c>
@@ -13091,7 +13090,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="239" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A239" s="1" t="s">
         <v>1114</v>
       </c>
@@ -13129,7 +13128,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="240" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A240" s="1" t="s">
         <v>1037</v>
       </c>
@@ -13167,7 +13166,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="241" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A241" s="1" t="s">
         <v>1115</v>
       </c>
@@ -13205,7 +13204,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="242" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A242" s="1" t="s">
         <v>1038</v>
       </c>
@@ -13243,7 +13242,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="243" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A243" s="1" t="s">
         <v>1116</v>
       </c>
@@ -13281,7 +13280,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="244" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A244" s="1" t="s">
         <v>1039</v>
       </c>
@@ -13319,7 +13318,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="245" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A245" s="1" t="s">
         <v>1040</v>
       </c>
@@ -13357,7 +13356,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="246" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A246" s="1" t="s">
         <v>1041</v>
       </c>
@@ -13395,7 +13394,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="247" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A247" s="1" t="s">
         <v>1042</v>
       </c>
@@ -13433,7 +13432,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="248" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A248" s="1" t="s">
         <v>1043</v>
       </c>
@@ -13471,7 +13470,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="249" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A249" s="1" t="s">
         <v>1044</v>
       </c>
@@ -13509,7 +13508,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="250" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A250" s="1" t="s">
         <v>1117</v>
       </c>
@@ -13547,7 +13546,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="251" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A251" s="1" t="s">
         <v>1045</v>
       </c>
@@ -13585,7 +13584,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="252" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A252" s="1" t="s">
         <v>1046</v>
       </c>
@@ -13623,7 +13622,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="253" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A253" s="1" t="s">
         <v>1047</v>
       </c>
@@ -13661,7 +13660,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="254" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A254" s="1" t="s">
         <v>1048</v>
       </c>
@@ -13699,7 +13698,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="255" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255" s="1" t="s">
         <v>1118</v>
       </c>
@@ -13737,7 +13736,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="256" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A256" s="1" t="s">
         <v>1049</v>
       </c>
@@ -13775,7 +13774,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="257" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A257" s="1" t="s">
         <v>1050</v>
       </c>
@@ -13813,7 +13812,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="258" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A258" s="1" t="s">
         <v>1051</v>
       </c>
@@ -13851,7 +13850,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="259" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A259" s="1" t="s">
         <v>1052</v>
       </c>
@@ -13889,7 +13888,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="260" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A260" s="1" t="s">
         <v>1053</v>
       </c>
@@ -13927,7 +13926,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="261" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A261" s="1" t="s">
         <v>1119</v>
       </c>
@@ -13965,7 +13964,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="262" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A262" s="1" t="s">
         <v>1054</v>
       </c>
@@ -14003,7 +14002,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="263" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A263" s="1" t="s">
         <v>1055</v>
       </c>
@@ -14041,7 +14040,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="264" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A264" s="1" t="s">
         <v>1120</v>
       </c>
@@ -14079,7 +14078,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="265" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A265" s="1" t="s">
         <v>1121</v>
       </c>
@@ -14117,7 +14116,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="266" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A266" s="1" t="s">
         <v>515</v>
       </c>
@@ -14155,7 +14154,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="267" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A267" s="1" t="s">
         <v>516</v>
       </c>
@@ -14193,7 +14192,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="268" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A268" s="1" t="s">
         <v>517</v>
       </c>
@@ -14231,7 +14230,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="269" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A269" s="1" t="s">
         <v>518</v>
       </c>
@@ -14269,7 +14268,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="270" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A270" s="1" t="s">
         <v>519</v>
       </c>
@@ -14307,7 +14306,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="271" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A271" s="1" t="s">
         <v>520</v>
       </c>
@@ -14345,7 +14344,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="272" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A272" s="1" t="s">
         <v>521</v>
       </c>
@@ -14383,7 +14382,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="273" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A273" s="1" t="s">
         <v>522</v>
       </c>
@@ -14421,7 +14420,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="274" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A274" s="1" t="s">
         <v>523</v>
       </c>
@@ -14459,7 +14458,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="275" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A275" s="1" t="s">
         <v>524</v>
       </c>
@@ -14497,7 +14496,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="276" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A276" s="1" t="s">
         <v>525</v>
       </c>
@@ -14535,7 +14534,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="277" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A277" s="1" t="s">
         <v>526</v>
       </c>
@@ -14573,7 +14572,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="278" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A278" s="1" t="s">
         <v>527</v>
       </c>
@@ -14611,7 +14610,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="279" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A279" s="1" t="s">
         <v>528</v>
       </c>
@@ -14649,7 +14648,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="280" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A280" s="1" t="s">
         <v>529</v>
       </c>
@@ -14687,7 +14686,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="281" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A281" s="1" t="s">
         <v>530</v>
       </c>
@@ -14725,7 +14724,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="282" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A282" s="1" t="s">
         <v>531</v>
       </c>
@@ -14763,7 +14762,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="283" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A283" s="1" t="s">
         <v>532</v>
       </c>
@@ -14801,7 +14800,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="284" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A284" s="1" t="s">
         <v>533</v>
       </c>
@@ -14839,7 +14838,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="285" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A285" s="1" t="s">
         <v>534</v>
       </c>
@@ -14877,7 +14876,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="286" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A286" s="1" t="s">
         <v>535</v>
       </c>
@@ -14915,7 +14914,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="287" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A287" s="1" t="s">
         <v>536</v>
       </c>
@@ -14953,7 +14952,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="288" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A288" s="1" t="s">
         <v>537</v>
       </c>
@@ -14991,7 +14990,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="289" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A289" s="1" t="s">
         <v>538</v>
       </c>
@@ -15029,7 +15028,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="290" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A290" s="1" t="s">
         <v>539</v>
       </c>
@@ -15067,7 +15066,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="291" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A291" s="1" t="s">
         <v>540</v>
       </c>
@@ -15105,7 +15104,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="292" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A292" s="1" t="s">
         <v>541</v>
       </c>
@@ -15143,7 +15142,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="293" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A293" s="1" t="s">
         <v>542</v>
       </c>
@@ -15181,7 +15180,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="294" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A294" s="1" t="s">
         <v>543</v>
       </c>
@@ -15219,7 +15218,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="295" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A295" s="1" t="s">
         <v>544</v>
       </c>
@@ -15257,7 +15256,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="296" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A296" s="1" t="s">
         <v>545</v>
       </c>
@@ -15295,7 +15294,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="297" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A297" s="1" t="s">
         <v>546</v>
       </c>
@@ -15333,7 +15332,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="298" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A298" s="1" t="s">
         <v>547</v>
       </c>
@@ -15371,7 +15370,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="299" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A299" s="1" t="s">
         <v>548</v>
       </c>
@@ -15409,7 +15408,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="300" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A300" s="1" t="s">
         <v>549</v>
       </c>
@@ -15447,7 +15446,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="301" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A301" s="1" t="s">
         <v>550</v>
       </c>
@@ -15485,7 +15484,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="302" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A302" s="1" t="s">
         <v>551</v>
       </c>
@@ -15523,7 +15522,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="303" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A303" s="1" t="s">
         <v>552</v>
       </c>
@@ -15561,7 +15560,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="304" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A304" s="1" t="s">
         <v>553</v>
       </c>
@@ -15599,7 +15598,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="305" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A305" s="1" t="s">
         <v>554</v>
       </c>
@@ -15637,7 +15636,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="306" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A306" s="1" t="s">
         <v>555</v>
       </c>
@@ -15675,7 +15674,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="307" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A307" s="1" t="s">
         <v>556</v>
       </c>
@@ -15713,7 +15712,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="308" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A308" s="1" t="s">
         <v>557</v>
       </c>
@@ -15751,7 +15750,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="309" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A309" s="1" t="s">
         <v>558</v>
       </c>
@@ -15789,7 +15788,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="310" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A310" s="1" t="s">
         <v>559</v>
       </c>
@@ -15827,7 +15826,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="311" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A311" s="1" t="s">
         <v>560</v>
       </c>
@@ -15865,7 +15864,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="312" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A312" s="1" t="s">
         <v>561</v>
       </c>
@@ -15903,7 +15902,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="313" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A313" s="1" t="s">
         <v>1122</v>
       </c>
@@ -15941,7 +15940,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="314" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A314" s="1" t="s">
         <v>1123</v>
       </c>
@@ -15979,7 +15978,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="315" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A315" s="1" t="s">
         <v>562</v>
       </c>
@@ -16017,7 +16016,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="316" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A316" s="1" t="s">
         <v>563</v>
       </c>
@@ -16055,7 +16054,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="317" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A317" s="1" t="s">
         <v>1124</v>
       </c>
@@ -16093,7 +16092,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="318" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A318" s="1" t="s">
         <v>564</v>
       </c>
@@ -16131,7 +16130,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="319" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A319" s="1" t="s">
         <v>565</v>
       </c>
@@ -16169,7 +16168,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="320" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A320" s="1" t="s">
         <v>566</v>
       </c>
@@ -16207,7 +16206,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="321" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A321" s="1" t="s">
         <v>567</v>
       </c>
@@ -16245,7 +16244,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="322" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A322" s="1" t="s">
         <v>568</v>
       </c>
@@ -16283,7 +16282,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="323" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A323" s="1" t="s">
         <v>569</v>
       </c>
@@ -16321,7 +16320,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="324" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A324" s="1" t="s">
         <v>570</v>
       </c>
@@ -16359,7 +16358,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="325" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A325" s="1" t="s">
         <v>571</v>
       </c>
@@ -16397,7 +16396,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="326" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A326" s="1" t="s">
         <v>572</v>
       </c>
@@ -16435,7 +16434,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="327" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A327" s="1" t="s">
         <v>573</v>
       </c>
@@ -16473,7 +16472,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="328" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A328" s="1" t="s">
         <v>574</v>
       </c>
@@ -16511,7 +16510,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="329" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A329" s="1" t="s">
         <v>575</v>
       </c>
@@ -16549,7 +16548,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="330" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A330" s="1" t="s">
         <v>576</v>
       </c>
@@ -16587,7 +16586,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="331" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A331" s="1" t="s">
         <v>577</v>
       </c>
@@ -16625,7 +16624,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="332" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A332" s="1" t="s">
         <v>578</v>
       </c>
@@ -16663,7 +16662,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="333" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A333" s="1" t="s">
         <v>579</v>
       </c>
@@ -16701,7 +16700,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="334" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A334" s="1" t="s">
         <v>580</v>
       </c>
@@ -16739,7 +16738,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="335" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A335" s="1" t="s">
         <v>581</v>
       </c>
@@ -16777,7 +16776,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="336" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A336" s="1" t="s">
         <v>582</v>
       </c>
@@ -16815,7 +16814,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="337" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A337" s="1" t="s">
         <v>583</v>
       </c>
@@ -16853,7 +16852,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="338" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A338" s="1" t="s">
         <v>584</v>
       </c>
@@ -16891,7 +16890,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="339" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A339" s="1" t="s">
         <v>585</v>
       </c>
@@ -16929,7 +16928,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="340" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A340" s="1" t="s">
         <v>586</v>
       </c>
@@ -16967,7 +16966,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="341" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A341" s="1" t="s">
         <v>587</v>
       </c>
@@ -17005,7 +17004,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="342" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A342" s="1" t="s">
         <v>588</v>
       </c>
@@ -17043,7 +17042,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="343" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A343" s="1" t="s">
         <v>1125</v>
       </c>
@@ -17081,7 +17080,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="344" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A344" s="1" t="s">
         <v>1126</v>
       </c>
@@ -17119,7 +17118,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="345" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A345" s="1" t="s">
         <v>589</v>
       </c>
@@ -17157,7 +17156,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="346" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A346" s="1" t="s">
         <v>590</v>
       </c>
@@ -17195,7 +17194,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="347" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A347" s="1" t="s">
         <v>1127</v>
       </c>
@@ -17233,7 +17232,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="348" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A348" s="1" t="s">
         <v>591</v>
       </c>
@@ -17271,7 +17270,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="349" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A349" s="1" t="s">
         <v>592</v>
       </c>
@@ -17309,7 +17308,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="350" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A350" s="1" t="s">
         <v>593</v>
       </c>
@@ -17347,7 +17346,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="351" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A351" s="1" t="s">
         <v>594</v>
       </c>
@@ -17385,7 +17384,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="352" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A352" s="1" t="s">
         <v>595</v>
       </c>
@@ -17423,7 +17422,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="353" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A353" s="1" t="s">
         <v>596</v>
       </c>
@@ -17461,7 +17460,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="354" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A354" s="1" t="s">
         <v>597</v>
       </c>
@@ -17499,7 +17498,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="355" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A355" s="1" t="s">
         <v>598</v>
       </c>
@@ -17537,7 +17536,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="356" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A356" s="1" t="s">
         <v>599</v>
       </c>
@@ -17575,7 +17574,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="357" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A357" s="1" t="s">
         <v>600</v>
       </c>
@@ -17613,7 +17612,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="358" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A358" s="1" t="s">
         <v>601</v>
       </c>
@@ -17651,7 +17650,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="359" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A359" s="1" t="s">
         <v>602</v>
       </c>
@@ -17689,7 +17688,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="360" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A360" s="1" t="s">
         <v>603</v>
       </c>
@@ -17727,7 +17726,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="361" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A361" s="1" t="s">
         <v>604</v>
       </c>
@@ -17765,7 +17764,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="362" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A362" s="1" t="s">
         <v>605</v>
       </c>
@@ -17803,7 +17802,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="363" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A363" s="1" t="s">
         <v>606</v>
       </c>
@@ -17841,7 +17840,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="364" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A364" s="1" t="s">
         <v>607</v>
       </c>
@@ -17879,7 +17878,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="365" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A365" s="1" t="s">
         <v>608</v>
       </c>
@@ -17917,7 +17916,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="366" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A366" s="1" t="s">
         <v>609</v>
       </c>
@@ -17955,7 +17954,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="367" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A367" s="1" t="s">
         <v>610</v>
       </c>
@@ -17993,7 +17992,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="368" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A368" s="1" t="s">
         <v>611</v>
       </c>
@@ -18031,7 +18030,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="369" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A369" s="1" t="s">
         <v>612</v>
       </c>
@@ -18069,7 +18068,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="370" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A370" s="1" t="s">
         <v>613</v>
       </c>
@@ -18107,7 +18106,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="371" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A371" s="1" t="s">
         <v>614</v>
       </c>
@@ -18145,7 +18144,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="372" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A372" s="1" t="s">
         <v>615</v>
       </c>
@@ -18183,7 +18182,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="373" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A373" s="1" t="s">
         <v>616</v>
       </c>
@@ -18221,7 +18220,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="374" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A374" s="1" t="s">
         <v>617</v>
       </c>
@@ -18259,7 +18258,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="375" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A375" s="1" t="s">
         <v>618</v>
       </c>
@@ -18297,7 +18296,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="376" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A376" s="1" t="s">
         <v>619</v>
       </c>
@@ -18335,7 +18334,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="377" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A377" s="1" t="s">
         <v>1128</v>
       </c>
@@ -18373,7 +18372,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="378" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A378" s="1" t="s">
         <v>620</v>
       </c>
@@ -18411,7 +18410,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="379" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A379" s="1" t="s">
         <v>621</v>
       </c>
@@ -18449,7 +18448,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="380" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A380" s="1" t="s">
         <v>622</v>
       </c>
@@ -18487,7 +18486,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="381" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A381" s="1" t="s">
         <v>1129</v>
       </c>
@@ -18525,7 +18524,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="382" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A382" s="1" t="s">
         <v>1130</v>
       </c>
@@ -18563,7 +18562,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="383" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A383" s="1" t="s">
         <v>623</v>
       </c>
@@ -18601,7 +18600,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="384" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A384" s="1" t="s">
         <v>624</v>
       </c>
@@ -18639,7 +18638,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="385" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A385" s="1" t="s">
         <v>625</v>
       </c>
@@ -18677,7 +18676,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="386" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A386" s="1" t="s">
         <v>626</v>
       </c>
@@ -18715,7 +18714,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="387" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A387" s="1" t="s">
         <v>1131</v>
       </c>
@@ -18753,7 +18752,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="388" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A388" s="1" t="s">
         <v>627</v>
       </c>
@@ -18867,7 +18866,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="391" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A391" s="1" t="s">
         <v>1132</v>
       </c>
@@ -18905,7 +18904,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="392" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A392" s="1" t="s">
         <v>630</v>
       </c>
@@ -18943,7 +18942,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="393" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A393" s="1" t="s">
         <v>631</v>
       </c>
@@ -18981,7 +18980,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="394" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A394" s="1" t="s">
         <v>632</v>
       </c>
@@ -19019,7 +19018,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="395" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A395" s="1" t="s">
         <v>633</v>
       </c>
@@ -19057,7 +19056,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="396" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A396" s="1" t="s">
         <v>634</v>
       </c>
@@ -19095,7 +19094,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="397" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A397" s="1" t="s">
         <v>1133</v>
       </c>
@@ -19133,7 +19132,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="398" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A398" s="1" t="s">
         <v>635</v>
       </c>
@@ -19171,7 +19170,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="399" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A399" s="1" t="s">
         <v>1134</v>
       </c>
@@ -19209,7 +19208,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="400" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A400" s="1" t="s">
         <v>636</v>
       </c>
@@ -19247,7 +19246,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="401" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A401" s="1" t="s">
         <v>637</v>
       </c>
@@ -19285,7 +19284,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="402" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A402" s="1" t="s">
         <v>1135</v>
       </c>
@@ -19399,7 +19398,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="405" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A405" s="1" t="s">
         <v>640</v>
       </c>
@@ -19437,7 +19436,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="406" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A406" s="1" t="s">
         <v>641</v>
       </c>
@@ -19475,7 +19474,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="407" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A407" s="1" t="s">
         <v>642</v>
       </c>
@@ -19513,7 +19512,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="408" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A408" s="1" t="s">
         <v>643</v>
       </c>
@@ -19551,7 +19550,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="409" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A409" s="1" t="s">
         <v>644</v>
       </c>
@@ -19589,7 +19588,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="410" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A410" s="1" t="s">
         <v>645</v>
       </c>
@@ -19627,7 +19626,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="411" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A411" s="1" t="s">
         <v>646</v>
       </c>
@@ -19665,7 +19664,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="412" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A412" s="1" t="s">
         <v>647</v>
       </c>
@@ -19703,7 +19702,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="413" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A413" s="1" t="s">
         <v>648</v>
       </c>
@@ -19741,7 +19740,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="414" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A414" s="1" t="s">
         <v>649</v>
       </c>
@@ -19779,7 +19778,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="415" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A415" s="1" t="s">
         <v>650</v>
       </c>
@@ -19817,7 +19816,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="416" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A416" s="1" t="s">
         <v>651</v>
       </c>
@@ -19855,7 +19854,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="417" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A417" s="1" t="s">
         <v>652</v>
       </c>
@@ -19893,7 +19892,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="418" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A418" s="1" t="s">
         <v>653</v>
       </c>
@@ -19931,7 +19930,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="419" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A419" s="1" t="s">
         <v>654</v>
       </c>
@@ -19969,7 +19968,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="420" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A420" s="1" t="s">
         <v>655</v>
       </c>
@@ -20007,7 +20006,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="421" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A421" s="1" t="s">
         <v>656</v>
       </c>
@@ -20045,7 +20044,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="422" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A422" s="1" t="s">
         <v>657</v>
       </c>
@@ -20083,7 +20082,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="423" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A423" s="1" t="s">
         <v>658</v>
       </c>
@@ -20121,7 +20120,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="424" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A424" s="1" t="s">
         <v>659</v>
       </c>
@@ -20159,7 +20158,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="425" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A425" s="1" t="s">
         <v>660</v>
       </c>
@@ -20197,7 +20196,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="426" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A426" s="1" t="s">
         <v>661</v>
       </c>
@@ -20235,7 +20234,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="427" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A427" s="1" t="s">
         <v>662</v>
       </c>
@@ -20273,7 +20272,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="428" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A428" s="1" t="s">
         <v>663</v>
       </c>
@@ -20311,7 +20310,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="429" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A429" s="1" t="s">
         <v>664</v>
       </c>
@@ -20349,7 +20348,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="430" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A430" s="1" t="s">
         <v>665</v>
       </c>
@@ -20387,7 +20386,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="431" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A431" s="1" t="s">
         <v>666</v>
       </c>
@@ -20425,7 +20424,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="432" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A432" s="1" t="s">
         <v>667</v>
       </c>
@@ -20463,7 +20462,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="433" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A433" s="1" t="s">
         <v>668</v>
       </c>
@@ -20501,7 +20500,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="434" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A434" s="1" t="s">
         <v>669</v>
       </c>
@@ -20539,7 +20538,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="435" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A435" s="1" t="s">
         <v>670</v>
       </c>
@@ -20577,7 +20576,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="436" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A436" s="1" t="s">
         <v>671</v>
       </c>
@@ -20615,7 +20614,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="437" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A437" s="1" t="s">
         <v>672</v>
       </c>
@@ -20653,7 +20652,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="438" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A438" s="1" t="s">
         <v>673</v>
       </c>
@@ -20691,7 +20690,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="439" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A439" s="1" t="s">
         <v>674</v>
       </c>
@@ -20729,7 +20728,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="440" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A440" s="1" t="s">
         <v>675</v>
       </c>
@@ -20767,7 +20766,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="441" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A441" s="1" t="s">
         <v>676</v>
       </c>
@@ -20805,7 +20804,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="442" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A442" s="1" t="s">
         <v>677</v>
       </c>
@@ -20843,7 +20842,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="443" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A443" s="1" t="s">
         <v>678</v>
       </c>
@@ -20881,7 +20880,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="444" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A444" s="1" t="s">
         <v>679</v>
       </c>
@@ -20919,7 +20918,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="445" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A445" s="1" t="s">
         <v>680</v>
       </c>
@@ -20957,7 +20956,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="446" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A446" s="1" t="s">
         <v>681</v>
       </c>
@@ -20995,7 +20994,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="447" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A447" s="1" t="s">
         <v>682</v>
       </c>
@@ -21033,7 +21032,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="448" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A448" s="1" t="s">
         <v>683</v>
       </c>
@@ -21071,7 +21070,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="449" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A449" s="1" t="s">
         <v>684</v>
       </c>
@@ -21109,7 +21108,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="450" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A450" s="1" t="s">
         <v>685</v>
       </c>
@@ -21147,7 +21146,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="451" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A451" s="1" t="s">
         <v>686</v>
       </c>
@@ -21185,7 +21184,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="452" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A452" s="1" t="s">
         <v>687</v>
       </c>
@@ -21223,7 +21222,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="453" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A453" s="1" t="s">
         <v>688</v>
       </c>
@@ -21261,7 +21260,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="454" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A454" s="1" t="s">
         <v>689</v>
       </c>
@@ -21299,7 +21298,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="455" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A455" s="1" t="s">
         <v>690</v>
       </c>
@@ -21337,7 +21336,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="456" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A456" s="1" t="s">
         <v>691</v>
       </c>
@@ -21375,7 +21374,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="457" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A457" s="1" t="s">
         <v>692</v>
       </c>
@@ -21413,7 +21412,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="458" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A458" s="1" t="s">
         <v>693</v>
       </c>
@@ -21451,7 +21450,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="459" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A459" s="1" t="s">
         <v>694</v>
       </c>
@@ -21489,7 +21488,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="460" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A460" s="1" t="s">
         <v>695</v>
       </c>
@@ -21527,7 +21526,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="461" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A461" s="1" t="s">
         <v>696</v>
       </c>
@@ -21565,7 +21564,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="462" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A462" s="1" t="s">
         <v>697</v>
       </c>
@@ -21603,7 +21602,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="463" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A463" s="1" t="s">
         <v>698</v>
       </c>
@@ -21641,7 +21640,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="464" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A464" s="1" t="s">
         <v>699</v>
       </c>
@@ -21679,7 +21678,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="465" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A465" s="1" t="s">
         <v>700</v>
       </c>
@@ -21717,7 +21716,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="466" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A466" s="1" t="s">
         <v>701</v>
       </c>
@@ -21755,7 +21754,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="467" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A467" s="1" t="s">
         <v>702</v>
       </c>
@@ -21793,7 +21792,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="468" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A468" s="1" t="s">
         <v>703</v>
       </c>
@@ -21831,7 +21830,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="469" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A469" s="1" t="s">
         <v>704</v>
       </c>
@@ -21869,7 +21868,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="470" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A470" s="1" t="s">
         <v>1136</v>
       </c>
@@ -21907,7 +21906,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="471" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A471" s="1" t="s">
         <v>705</v>
       </c>
@@ -21945,7 +21944,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="472" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A472" s="1" t="s">
         <v>706</v>
       </c>
@@ -21983,7 +21982,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="473" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A473" s="1" t="s">
         <v>707</v>
       </c>
@@ -22021,7 +22020,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="474" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A474" s="1" t="s">
         <v>708</v>
       </c>
@@ -22059,7 +22058,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="475" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A475" s="1" t="s">
         <v>709</v>
       </c>
@@ -22097,7 +22096,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="476" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A476" s="1" t="s">
         <v>710</v>
       </c>
@@ -22135,7 +22134,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="477" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A477" s="1" t="s">
         <v>711</v>
       </c>
@@ -22173,7 +22172,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="478" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A478" s="1" t="s">
         <v>712</v>
       </c>
@@ -22211,7 +22210,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="479" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A479" s="1" t="s">
         <v>713</v>
       </c>
@@ -22249,7 +22248,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="480" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A480" s="1" t="s">
         <v>714</v>
       </c>
@@ -22287,7 +22286,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="481" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A481" s="1" t="s">
         <v>1137</v>
       </c>
@@ -22325,7 +22324,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="482" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A482" s="1" t="s">
         <v>715</v>
       </c>
@@ -22363,7 +22362,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="483" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A483" s="1" t="s">
         <v>716</v>
       </c>
@@ -22401,7 +22400,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="484" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A484" s="1" t="s">
         <v>717</v>
       </c>
@@ -22439,7 +22438,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="485" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A485" s="1" t="s">
         <v>718</v>
       </c>
@@ -22477,7 +22476,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="486" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A486" s="1" t="s">
         <v>719</v>
       </c>
@@ -22515,7 +22514,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="487" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A487" s="1" t="s">
         <v>720</v>
       </c>
@@ -22553,7 +22552,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="488" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A488" s="1" t="s">
         <v>721</v>
       </c>
@@ -22591,7 +22590,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="489" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A489" s="1" t="s">
         <v>722</v>
       </c>
@@ -22629,7 +22628,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="490" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A490" s="1" t="s">
         <v>723</v>
       </c>
@@ -22667,7 +22666,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="491" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A491" s="1" t="s">
         <v>724</v>
       </c>
@@ -22705,7 +22704,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="492" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A492" s="1" t="s">
         <v>725</v>
       </c>
@@ -22743,7 +22742,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="493" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A493" s="1" t="s">
         <v>726</v>
       </c>
@@ -22781,7 +22780,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="494" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A494" s="1" t="s">
         <v>727</v>
       </c>
@@ -22819,7 +22818,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="495" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A495" s="1" t="s">
         <v>728</v>
       </c>
@@ -22857,7 +22856,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="496" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A496" s="1" t="s">
         <v>729</v>
       </c>
@@ -22895,7 +22894,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="497" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A497" s="1" t="s">
         <v>730</v>
       </c>
@@ -22933,7 +22932,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="498" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A498" s="1" t="s">
         <v>731</v>
       </c>
@@ -22971,7 +22970,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="499" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A499" s="1" t="s">
         <v>732</v>
       </c>
@@ -23009,7 +23008,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="500" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A500" s="1" t="s">
         <v>733</v>
       </c>
@@ -23047,7 +23046,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="501" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A501" s="1" t="s">
         <v>734</v>
       </c>
@@ -23085,7 +23084,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="502" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A502" s="1" t="s">
         <v>735</v>
       </c>
@@ -23123,7 +23122,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="503" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A503" s="1" t="s">
         <v>736</v>
       </c>
@@ -23161,7 +23160,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="504" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A504" s="1" t="s">
         <v>737</v>
       </c>
@@ -23199,7 +23198,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="505" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A505" s="1" t="s">
         <v>738</v>
       </c>
@@ -23237,7 +23236,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="506" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A506" s="1" t="s">
         <v>739</v>
       </c>
@@ -23275,7 +23274,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="507" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A507" s="1" t="s">
         <v>740</v>
       </c>
@@ -23313,7 +23312,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="508" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A508" s="1" t="s">
         <v>741</v>
       </c>
@@ -23351,7 +23350,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="509" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A509" s="1" t="s">
         <v>742</v>
       </c>
@@ -23389,7 +23388,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="510" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A510" s="1" t="s">
         <v>743</v>
       </c>
@@ -23427,7 +23426,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="511" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A511" s="1" t="s">
         <v>744</v>
       </c>
@@ -23465,7 +23464,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="512" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A512" s="1" t="s">
         <v>745</v>
       </c>
@@ -23503,7 +23502,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="513" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A513" s="1" t="s">
         <v>746</v>
       </c>
@@ -23541,7 +23540,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="514" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A514" s="1" t="s">
         <v>747</v>
       </c>
@@ -23579,7 +23578,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="515" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A515" s="1" t="s">
         <v>748</v>
       </c>
@@ -23617,7 +23616,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="516" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A516" s="1" t="s">
         <v>749</v>
       </c>
@@ -23655,7 +23654,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="517" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A517" s="1" t="s">
         <v>750</v>
       </c>
@@ -23693,7 +23692,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="518" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A518" s="1" t="s">
         <v>751</v>
       </c>
@@ -23731,7 +23730,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="519" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A519" s="1" t="s">
         <v>752</v>
       </c>
@@ -23769,7 +23768,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="520" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A520" s="1" t="s">
         <v>753</v>
       </c>
@@ -23807,7 +23806,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="521" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A521" s="1" t="s">
         <v>754</v>
       </c>
@@ -23845,7 +23844,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="522" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A522" s="1" t="s">
         <v>755</v>
       </c>
@@ -23883,7 +23882,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="523" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A523" s="1" t="s">
         <v>756</v>
       </c>
@@ -23921,7 +23920,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="524" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A524" s="1" t="s">
         <v>757</v>
       </c>
@@ -24035,7 +24034,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="527" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A527" s="1" t="s">
         <v>760</v>
       </c>
@@ -24073,7 +24072,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="528" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A528" s="1" t="s">
         <v>761</v>
       </c>
@@ -24111,7 +24110,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="529" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A529" s="1" t="s">
         <v>762</v>
       </c>
@@ -24149,7 +24148,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="530" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A530" s="1" t="s">
         <v>763</v>
       </c>
@@ -24187,7 +24186,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="531" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A531" s="1" t="s">
         <v>764</v>
       </c>
@@ -24225,7 +24224,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="532" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A532" s="1" t="s">
         <v>765</v>
       </c>
@@ -24263,7 +24262,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="533" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A533" s="1" t="s">
         <v>766</v>
       </c>
@@ -24301,7 +24300,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="534" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A534" s="1" t="s">
         <v>767</v>
       </c>
@@ -24339,7 +24338,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="535" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A535" s="1" t="s">
         <v>768</v>
       </c>
@@ -24377,7 +24376,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="536" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A536" s="1" t="s">
         <v>769</v>
       </c>
@@ -24415,7 +24414,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="537" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A537" s="1" t="s">
         <v>770</v>
       </c>
@@ -24453,7 +24452,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="538" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A538" s="1" t="s">
         <v>771</v>
       </c>
@@ -24491,7 +24490,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="539" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A539" s="1" t="s">
         <v>772</v>
       </c>
@@ -24529,7 +24528,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="540" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A540" s="1" t="s">
         <v>773</v>
       </c>
@@ -24567,7 +24566,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="541" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A541" s="1" t="s">
         <v>774</v>
       </c>
@@ -24605,7 +24604,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="542" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A542" s="1" t="s">
         <v>775</v>
       </c>
@@ -24643,7 +24642,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="543" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A543" s="1" t="s">
         <v>776</v>
       </c>
@@ -24681,7 +24680,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="544" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A544" s="1" t="s">
         <v>777</v>
       </c>
@@ -24719,7 +24718,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="545" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A545" s="1" t="s">
         <v>778</v>
       </c>
@@ -24757,7 +24756,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="546" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A546" s="1" t="s">
         <v>779</v>
       </c>
@@ -24795,7 +24794,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="547" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A547" s="1" t="s">
         <v>780</v>
       </c>
@@ -24833,7 +24832,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="548" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A548" s="1" t="s">
         <v>781</v>
       </c>
@@ -24871,7 +24870,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="549" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A549" s="1" t="s">
         <v>782</v>
       </c>
@@ -24909,7 +24908,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="550" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A550" s="1" t="s">
         <v>783</v>
       </c>
@@ -24947,7 +24946,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="551" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A551" s="1" t="s">
         <v>784</v>
       </c>
@@ -24985,7 +24984,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="552" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A552" s="1" t="s">
         <v>785</v>
       </c>
@@ -25023,7 +25022,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="553" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A553" s="1" t="s">
         <v>786</v>
       </c>
@@ -25061,7 +25060,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="554" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A554" s="1" t="s">
         <v>787</v>
       </c>
@@ -25099,7 +25098,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="555" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A555" s="1" t="s">
         <v>788</v>
       </c>
@@ -25137,7 +25136,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="556" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A556" s="1" t="s">
         <v>789</v>
       </c>
@@ -25175,7 +25174,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="557" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A557" s="1" t="s">
         <v>790</v>
       </c>
@@ -25213,7 +25212,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="558" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A558" s="1" t="s">
         <v>791</v>
       </c>
@@ -25251,7 +25250,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="559" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A559" s="1" t="s">
         <v>792</v>
       </c>
@@ -25289,7 +25288,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="560" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A560" s="1" t="s">
         <v>793</v>
       </c>
@@ -25327,7 +25326,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="561" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A561" s="1" t="s">
         <v>794</v>
       </c>
@@ -25365,7 +25364,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="562" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A562" s="1" t="s">
         <v>795</v>
       </c>
@@ -25403,7 +25402,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="563" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A563" s="1" t="s">
         <v>796</v>
       </c>
@@ -25441,7 +25440,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="564" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A564" s="1" t="s">
         <v>797</v>
       </c>
@@ -25479,7 +25478,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="565" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A565" s="1" t="s">
         <v>798</v>
       </c>
@@ -25517,7 +25516,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="566" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A566" s="1" t="s">
         <v>799</v>
       </c>
@@ -25555,7 +25554,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="567" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A567" s="1" t="s">
         <v>800</v>
       </c>
@@ -25593,7 +25592,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="568" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A568" s="1" t="s">
         <v>801</v>
       </c>
@@ -25631,7 +25630,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="569" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A569" s="1" t="s">
         <v>802</v>
       </c>
@@ -25669,7 +25668,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="570" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A570" s="1" t="s">
         <v>803</v>
       </c>
@@ -25783,7 +25782,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="573" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A573" s="1" t="s">
         <v>806</v>
       </c>
@@ -25821,7 +25820,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="574" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A574" s="1" t="s">
         <v>807</v>
       </c>
@@ -25859,7 +25858,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="575" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A575" s="1" t="s">
         <v>808</v>
       </c>
@@ -25897,7 +25896,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="576" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A576" s="1" t="s">
         <v>809</v>
       </c>
@@ -25935,7 +25934,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="577" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A577" s="1" t="s">
         <v>1138</v>
       </c>
@@ -25973,7 +25972,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="578" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A578" s="1" t="s">
         <v>1139</v>
       </c>
@@ -26011,7 +26010,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="579" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A579" s="1" t="s">
         <v>810</v>
       </c>
@@ -26049,7 +26048,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="580" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A580" s="1" t="s">
         <v>811</v>
       </c>
@@ -26087,7 +26086,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="581" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A581" s="1" t="s">
         <v>812</v>
       </c>
@@ -26125,7 +26124,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="582" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A582" s="1" t="s">
         <v>813</v>
       </c>
@@ -26163,7 +26162,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="583" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A583" s="1" t="s">
         <v>814</v>
       </c>
@@ -26201,7 +26200,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="584" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A584" s="1" t="s">
         <v>815</v>
       </c>
@@ -26239,7 +26238,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="585" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A585" s="1" t="s">
         <v>816</v>
       </c>
@@ -26277,7 +26276,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="586" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A586" s="1" t="s">
         <v>817</v>
       </c>
@@ -26315,7 +26314,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="587" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A587" s="1" t="s">
         <v>818</v>
       </c>
@@ -26353,7 +26352,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="588" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A588" s="1" t="s">
         <v>819</v>
       </c>
@@ -26391,7 +26390,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="589" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A589" s="1" t="s">
         <v>820</v>
       </c>
@@ -26429,7 +26428,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="590" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A590" s="1" t="s">
         <v>821</v>
       </c>
@@ -26467,7 +26466,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="591" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A591" s="1" t="s">
         <v>822</v>
       </c>
@@ -26505,7 +26504,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="592" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A592" s="1" t="s">
         <v>823</v>
       </c>
@@ -26543,7 +26542,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="593" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A593" s="1" t="s">
         <v>1140</v>
       </c>
@@ -26581,7 +26580,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="594" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A594" s="1" t="s">
         <v>824</v>
       </c>
@@ -26619,7 +26618,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="595" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A595" s="1" t="s">
         <v>1141</v>
       </c>
@@ -26657,7 +26656,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="596" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A596" s="1" t="s">
         <v>825</v>
       </c>
@@ -26695,7 +26694,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="597" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A597" s="1" t="s">
         <v>826</v>
       </c>
@@ -26733,7 +26732,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="598" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A598" s="1" t="s">
         <v>827</v>
       </c>
@@ -26771,7 +26770,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="599" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A599" s="1" t="s">
         <v>828</v>
       </c>
@@ -26809,7 +26808,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="600" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A600" s="1" t="s">
         <v>829</v>
       </c>
@@ -26847,7 +26846,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="601" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A601" s="1" t="s">
         <v>830</v>
       </c>
@@ -26885,7 +26884,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="602" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A602" s="1" t="s">
         <v>1142</v>
       </c>
@@ -26923,7 +26922,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="603" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A603" s="1" t="s">
         <v>831</v>
       </c>
@@ -26961,7 +26960,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="604" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A604" s="1" t="s">
         <v>832</v>
       </c>
@@ -26999,7 +26998,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="605" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A605" s="1" t="s">
         <v>833</v>
       </c>
@@ -27037,7 +27036,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="606" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A606" s="1" t="s">
         <v>834</v>
       </c>
@@ -27075,7 +27074,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="607" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A607" s="1" t="s">
         <v>835</v>
       </c>
@@ -27113,7 +27112,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="608" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A608" s="1" t="s">
         <v>836</v>
       </c>
@@ -27151,7 +27150,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="609" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A609" s="1" t="s">
         <v>837</v>
       </c>
@@ -27189,7 +27188,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="610" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A610" s="1" t="s">
         <v>838</v>
       </c>
@@ -27227,7 +27226,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="611" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A611" s="1" t="s">
         <v>839</v>
       </c>
@@ -27265,7 +27264,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="612" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A612" s="1" t="s">
         <v>840</v>
       </c>
@@ -27303,7 +27302,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="613" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A613" s="1" t="s">
         <v>841</v>
       </c>
@@ -27341,7 +27340,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="614" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A614" s="1" t="s">
         <v>842</v>
       </c>
@@ -27379,7 +27378,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="615" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A615" s="1" t="s">
         <v>843</v>
       </c>
@@ -27417,7 +27416,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="616" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A616" s="1" t="s">
         <v>844</v>
       </c>
@@ -27455,7 +27454,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="617" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A617" s="1" t="s">
         <v>845</v>
       </c>
@@ -27493,7 +27492,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="618" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A618" s="1" t="s">
         <v>846</v>
       </c>
@@ -27531,7 +27530,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="619" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A619" s="1" t="s">
         <v>847</v>
       </c>
@@ -27569,7 +27568,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="620" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A620" s="1" t="s">
         <v>848</v>
       </c>
@@ -27607,7 +27606,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="621" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A621" s="1" t="s">
         <v>849</v>
       </c>
@@ -27645,7 +27644,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="622" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A622" s="1" t="s">
         <v>850</v>
       </c>
@@ -27683,7 +27682,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="623" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A623" s="1" t="s">
         <v>851</v>
       </c>
@@ -27721,7 +27720,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="624" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A624" s="1" t="s">
         <v>852</v>
       </c>
@@ -27759,7 +27758,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="625" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A625" s="1" t="s">
         <v>853</v>
       </c>
@@ -27797,7 +27796,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="626" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A626" s="1" t="s">
         <v>854</v>
       </c>
@@ -27835,7 +27834,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="627" spans="1:12" ht="17.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:12" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A627" s="1" t="s">
         <v>855</v>
       </c>
@@ -27873,7 +27872,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="628" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A628" s="1" t="s">
         <v>1183</v>
       </c>
@@ -27911,7 +27910,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="629" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A629" s="1" t="s">
         <v>1184</v>
       </c>
@@ -27949,7 +27948,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="630" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A630" s="1" t="s">
         <v>1185</v>
       </c>
@@ -27987,7 +27986,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="631" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A631" s="1" t="s">
         <v>1186</v>
       </c>
@@ -28025,7 +28024,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="632" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A632" s="1" t="s">
         <v>1197</v>
       </c>
@@ -28063,7 +28062,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="633" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A633" s="1" t="s">
         <v>1187</v>
       </c>
@@ -28101,7 +28100,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="634" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A634" s="1" t="s">
         <v>1188</v>
       </c>
@@ -28139,7 +28138,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="635" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A635" s="1" t="s">
         <v>1189</v>
       </c>
@@ -28177,7 +28176,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="636" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A636" s="1" t="s">
         <v>1190</v>
       </c>
@@ -28203,7 +28202,7 @@
         <v>147</v>
       </c>
       <c r="I636" s="1">
-        <v>549.99</v>
+        <v>599.99</v>
       </c>
       <c r="J636" s="3">
         <v>274.995</v>
@@ -28215,7 +28214,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="637" spans="1:12" hidden="1" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A637" s="1" t="s">
         <v>1191</v>
       </c>
@@ -28241,7 +28240,7 @@
         <v>147</v>
       </c>
       <c r="I637" s="1">
-        <v>549.99</v>
+        <v>599.99</v>
       </c>
       <c r="J637" s="3">
         <v>274.995</v>
@@ -28482,17 +28481,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L643" xr:uid="{E0D1E054-7418-4233-9A16-A15E844DE850}">
-    <filterColumn colId="4">
-      <filters>
-        <filter val="CORRE VENTO 3"/>
-        <filter val="JAQUETA CORTA/VENTO CORRE F"/>
-        <filter val="JAQUETA CORTA/VENTO CORRE M"/>
-        <filter val="JAQUETA QUEBRA/VENTO ESSENTIAL F"/>
-        <filter val="JAQUETA QUEBRA/VENTO ESSENTIAL M"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:L643" xr:uid="{E0D1E054-7418-4233-9A16-A15E844DE850}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>

--- a/Produtos.xlsx
+++ b/Produtos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NOT-MARCOS\Documents\GitHub\Catalogo-Olympikus_2.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDD6B7EB-6B60-45EC-849D-360F38686C71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{418A814A-F688-439D-A5D0-FD0EA6CB2A24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{C851EA1D-5267-41B7-9513-D07E5A57DEF2}"/>
   </bookViews>
@@ -28056,10 +28056,10 @@
         <v>399.995</v>
       </c>
       <c r="K632" s="1" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="L632" s="1" t="s">
-        <v>1169</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="633" spans="1:12" x14ac:dyDescent="0.25">

--- a/Produtos.xlsx
+++ b/Produtos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NOT-MARCOS\Documents\GitHub\Catalogo-Olympikus_2.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8F37E34-A718-43DF-85CC-9CF562097F07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9630D83F-13C6-44E7-B0CB-45D27AE2638A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5408,6 +5408,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:R1066"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -5475,7 +5476,7 @@
         <v>1642</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>212</v>
       </c>
@@ -5531,7 +5532,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>213</v>
       </c>
@@ -5587,7 +5588,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>214</v>
       </c>
@@ -5643,7 +5644,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>215</v>
       </c>
@@ -5699,7 +5700,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>401</v>
       </c>
@@ -5755,7 +5756,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>216</v>
       </c>
@@ -5811,7 +5812,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>217</v>
       </c>
@@ -5867,7 +5868,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>218</v>
       </c>
@@ -5923,7 +5924,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>219</v>
       </c>
@@ -5979,7 +5980,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>402</v>
       </c>
@@ -6035,7 +6036,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>220</v>
       </c>
@@ -6091,7 +6092,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>221</v>
       </c>
@@ -6147,7 +6148,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="14" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>222</v>
       </c>
@@ -6203,7 +6204,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>223</v>
       </c>
@@ -6259,7 +6260,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="16" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>224</v>
       </c>
@@ -6315,7 +6316,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="17" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>225</v>
       </c>
@@ -6371,7 +6372,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="18" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>403</v>
       </c>
@@ -6763,7 +6764,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="25" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>231</v>
       </c>
@@ -6819,7 +6820,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="26" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>232</v>
       </c>
@@ -6875,7 +6876,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="27" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>233</v>
       </c>
@@ -6931,7 +6932,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="28" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>405</v>
       </c>
@@ -6987,7 +6988,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="29" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>406</v>
       </c>
@@ -7043,7 +7044,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="30" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>234</v>
       </c>
@@ -7099,7 +7100,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="31" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>235</v>
       </c>
@@ -7155,7 +7156,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="32" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>236</v>
       </c>
@@ -7211,7 +7212,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="33" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>237</v>
       </c>
@@ -7267,7 +7268,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="34" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>238</v>
       </c>
@@ -7323,7 +7324,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="35" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>239</v>
       </c>
@@ -7379,7 +7380,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="36" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>240</v>
       </c>
@@ -7435,7 +7436,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="37" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>241</v>
       </c>
@@ -7491,7 +7492,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="38" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>242</v>
       </c>
@@ -7547,7 +7548,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="39" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>243</v>
       </c>
@@ -7603,7 +7604,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="40" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>407</v>
       </c>
@@ -7659,7 +7660,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="41" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>408</v>
       </c>
@@ -7715,7 +7716,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="42" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>244</v>
       </c>
@@ -7771,7 +7772,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="43" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>245</v>
       </c>
@@ -7827,7 +7828,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="44" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>409</v>
       </c>
@@ -7883,7 +7884,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="45" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>410</v>
       </c>
@@ -7939,7 +7940,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="46" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>246</v>
       </c>
@@ -7995,7 +7996,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="47" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>411</v>
       </c>
@@ -8051,7 +8052,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="48" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>247</v>
       </c>
@@ -8107,7 +8108,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="49" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>412</v>
       </c>
@@ -8163,7 +8164,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="50" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>413</v>
       </c>
@@ -8219,7 +8220,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="51" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>248</v>
       </c>
@@ -8275,7 +8276,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="52" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>414</v>
       </c>
@@ -8331,7 +8332,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="53" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>249</v>
       </c>
@@ -8387,7 +8388,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="54" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>250</v>
       </c>
@@ -8443,7 +8444,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="55" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>415</v>
       </c>
@@ -8499,7 +8500,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="56" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>251</v>
       </c>
@@ -8555,7 +8556,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="57" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>252</v>
       </c>
@@ -8611,7 +8612,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="58" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>416</v>
       </c>
@@ -8667,7 +8668,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="59" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>253</v>
       </c>
@@ -8723,7 +8724,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="60" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>254</v>
       </c>
@@ -8779,7 +8780,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="61" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>255</v>
       </c>
@@ -8835,7 +8836,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="62" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>417</v>
       </c>
@@ -8891,7 +8892,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="63" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>256</v>
       </c>
@@ -8947,7 +8948,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="64" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>257</v>
       </c>
@@ -9003,7 +9004,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="65" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>418</v>
       </c>
@@ -9059,7 +9060,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="66" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
         <v>258</v>
       </c>
@@ -9115,7 +9116,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="67" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>419</v>
       </c>
@@ -9171,7 +9172,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="68" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
         <v>420</v>
       </c>
@@ -9227,7 +9228,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="69" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>259</v>
       </c>
@@ -9283,7 +9284,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="70" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
         <v>260</v>
       </c>
@@ -9339,7 +9340,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="71" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
         <v>261</v>
       </c>
@@ -9395,7 +9396,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="72" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
         <v>421</v>
       </c>
@@ -9451,7 +9452,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="73" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
         <v>262</v>
       </c>
@@ -9507,7 +9508,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="74" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
         <v>263</v>
       </c>
@@ -9563,7 +9564,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="75" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
         <v>422</v>
       </c>
@@ -9619,7 +9620,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="76" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
         <v>264</v>
       </c>
@@ -9675,7 +9676,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="77" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
         <v>423</v>
       </c>
@@ -9731,7 +9732,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="78" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
         <v>265</v>
       </c>
@@ -9787,7 +9788,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="79" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
         <v>266</v>
       </c>
@@ -9843,7 +9844,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="80" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
         <v>424</v>
       </c>
@@ -9899,7 +9900,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="81" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
         <v>267</v>
       </c>
@@ -9955,7 +9956,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="82" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
         <v>268</v>
       </c>
@@ -10011,7 +10012,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="83" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
         <v>425</v>
       </c>
@@ -10067,7 +10068,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="84" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
         <v>269</v>
       </c>
@@ -10123,7 +10124,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="85" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
         <v>426</v>
       </c>
@@ -10179,7 +10180,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="86" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
         <v>270</v>
       </c>
@@ -10235,7 +10236,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="87" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
         <v>271</v>
       </c>
@@ -10291,7 +10292,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="88" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
         <v>272</v>
       </c>
@@ -10347,7 +10348,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="89" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
         <v>273</v>
       </c>
@@ -10403,7 +10404,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="90" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
         <v>274</v>
       </c>
@@ -10459,7 +10460,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="91" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
         <v>275</v>
       </c>
@@ -10515,7 +10516,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="92" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
         <v>276</v>
       </c>
@@ -10571,7 +10572,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="93" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
         <v>427</v>
       </c>
@@ -10627,7 +10628,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="94" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
         <v>277</v>
       </c>
@@ -10683,7 +10684,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="95" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
         <v>278</v>
       </c>
@@ -10739,7 +10740,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="96" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
         <v>279</v>
       </c>
@@ -10795,7 +10796,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="97" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
         <v>280</v>
       </c>
@@ -10851,7 +10852,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="98" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
         <v>428</v>
       </c>
@@ -10907,7 +10908,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="99" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
         <v>429</v>
       </c>
@@ -10963,7 +10964,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="100" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
         <v>430</v>
       </c>
@@ -11019,7 +11020,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="101" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
         <v>431</v>
       </c>
@@ -11075,7 +11076,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="102" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
         <v>281</v>
       </c>
@@ -11131,7 +11132,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="103" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
         <v>432</v>
       </c>
@@ -11187,7 +11188,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="104" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
         <v>282</v>
       </c>
@@ -11243,7 +11244,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="105" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
         <v>283</v>
       </c>
@@ -11299,7 +11300,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="106" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
         <v>284</v>
       </c>
@@ -11355,7 +11356,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="107" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
         <v>285</v>
       </c>
@@ -11411,7 +11412,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="108" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
         <v>433</v>
       </c>
@@ -11467,7 +11468,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="109" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
         <v>286</v>
       </c>
@@ -11523,7 +11524,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="110" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
         <v>434</v>
       </c>
@@ -11579,7 +11580,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="111" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
         <v>287</v>
       </c>
@@ -11635,7 +11636,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="112" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
         <v>288</v>
       </c>
@@ -11691,7 +11692,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="113" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
         <v>435</v>
       </c>
@@ -11747,7 +11748,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="114" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
         <v>289</v>
       </c>
@@ -11803,7 +11804,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="115" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
         <v>290</v>
       </c>
@@ -11859,7 +11860,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="116" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
         <v>291</v>
       </c>
@@ -11915,7 +11916,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="117" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
         <v>292</v>
       </c>
@@ -11971,7 +11972,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="118" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
         <v>293</v>
       </c>
@@ -12027,7 +12028,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="119" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
         <v>294</v>
       </c>
@@ -12083,7 +12084,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="120" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
         <v>295</v>
       </c>
@@ -12139,7 +12140,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="121" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
         <v>296</v>
       </c>
@@ -12195,7 +12196,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="122" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
         <v>297</v>
       </c>
@@ -12251,7 +12252,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="123" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
         <v>298</v>
       </c>
@@ -12307,7 +12308,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="124" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
         <v>299</v>
       </c>
@@ -12363,7 +12364,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="125" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
         <v>300</v>
       </c>
@@ -12419,7 +12420,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="126" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
         <v>301</v>
       </c>
@@ -12475,7 +12476,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="127" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
         <v>302</v>
       </c>
@@ -12531,7 +12532,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="128" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
         <v>303</v>
       </c>
@@ -12587,7 +12588,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="129" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
         <v>304</v>
       </c>
@@ -12643,7 +12644,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="130" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
         <v>436</v>
       </c>
@@ -12699,7 +12700,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="131" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
         <v>305</v>
       </c>
@@ -12755,7 +12756,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="132" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
         <v>306</v>
       </c>
@@ -12811,7 +12812,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="133" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
         <v>307</v>
       </c>
@@ -12867,7 +12868,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="134" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
         <v>308</v>
       </c>
@@ -12923,7 +12924,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="135" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
         <v>309</v>
       </c>
@@ -12979,7 +12980,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="136" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
         <v>437</v>
       </c>
@@ -13035,7 +13036,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="137" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
         <v>310</v>
       </c>
@@ -13091,7 +13092,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="138" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
         <v>311</v>
       </c>
@@ -13147,7 +13148,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="139" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
         <v>312</v>
       </c>
@@ -13203,7 +13204,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="140" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
         <v>438</v>
       </c>
@@ -13259,7 +13260,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="141" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
         <v>313</v>
       </c>
@@ -13315,7 +13316,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="142" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
         <v>314</v>
       </c>
@@ -13371,7 +13372,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="143" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
         <v>439</v>
       </c>
@@ -13427,7 +13428,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="144" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
         <v>315</v>
       </c>
@@ -13483,7 +13484,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="145" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
         <v>316</v>
       </c>
@@ -13539,7 +13540,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="146" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
         <v>317</v>
       </c>
@@ -13595,7 +13596,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="147" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
         <v>440</v>
       </c>
@@ -13651,7 +13652,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="148" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
         <v>318</v>
       </c>
@@ -13707,7 +13708,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="149" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
         <v>319</v>
       </c>
@@ -13763,7 +13764,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="150" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="2" t="s">
         <v>320</v>
       </c>
@@ -13819,7 +13820,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="151" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="s">
         <v>321</v>
       </c>
@@ -13875,7 +13876,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="152" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="2" t="s">
         <v>322</v>
       </c>
@@ -13931,7 +13932,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="153" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="s">
         <v>323</v>
       </c>
@@ -13987,7 +13988,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="154" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="s">
         <v>324</v>
       </c>
@@ -14043,7 +14044,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="155" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="2" t="s">
         <v>325</v>
       </c>
@@ -14099,7 +14100,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="156" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="2" t="s">
         <v>326</v>
       </c>
@@ -14155,7 +14156,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="157" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="2" t="s">
         <v>327</v>
       </c>
@@ -14211,7 +14212,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="158" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="2" t="s">
         <v>328</v>
       </c>
@@ -14267,7 +14268,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="159" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="s">
         <v>329</v>
       </c>
@@ -14323,7 +14324,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="160" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="2" t="s">
         <v>330</v>
       </c>
@@ -14379,7 +14380,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="161" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="2" t="s">
         <v>331</v>
       </c>
@@ -14435,7 +14436,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="162" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="2" t="s">
         <v>332</v>
       </c>
@@ -14491,7 +14492,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="163" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="2" t="s">
         <v>333</v>
       </c>
@@ -14547,7 +14548,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="164" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="2" t="s">
         <v>334</v>
       </c>
@@ -14603,7 +14604,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="165" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="2" t="s">
         <v>335</v>
       </c>
@@ -14659,7 +14660,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="166" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="2" t="s">
         <v>336</v>
       </c>
@@ -14715,7 +14716,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="167" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="2" t="s">
         <v>337</v>
       </c>
@@ -14771,7 +14772,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="168" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="2" t="s">
         <v>338</v>
       </c>
@@ -14827,7 +14828,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="169" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="2" t="s">
         <v>339</v>
       </c>
@@ -14883,7 +14884,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="170" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="2" t="s">
         <v>340</v>
       </c>
@@ -14939,7 +14940,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="171" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="2" t="s">
         <v>341</v>
       </c>
@@ -14995,7 +14996,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="172" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="2" t="s">
         <v>342</v>
       </c>
@@ -15051,7 +15052,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="173" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="2" t="s">
         <v>343</v>
       </c>
@@ -15107,7 +15108,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="174" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="2" t="s">
         <v>441</v>
       </c>
@@ -15163,7 +15164,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="175" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="2" t="s">
         <v>344</v>
       </c>
@@ -15219,7 +15220,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="176" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="2" t="s">
         <v>345</v>
       </c>
@@ -15275,7 +15276,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="177" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="2" t="s">
         <v>442</v>
       </c>
@@ -15331,7 +15332,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="178" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="2" t="s">
         <v>346</v>
       </c>
@@ -15387,7 +15388,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="179" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="2" t="s">
         <v>347</v>
       </c>
@@ -15443,7 +15444,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="180" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="2" t="s">
         <v>348</v>
       </c>
@@ -15499,7 +15500,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="181" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="2" t="s">
         <v>443</v>
       </c>
@@ -15555,7 +15556,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="182" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="2" t="s">
         <v>444</v>
       </c>
@@ -15611,7 +15612,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="183" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" s="2" t="s">
         <v>349</v>
       </c>
@@ -15667,7 +15668,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="184" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="2" t="s">
         <v>350</v>
       </c>
@@ -15723,7 +15724,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="185" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="2" t="s">
         <v>351</v>
       </c>
@@ -15779,7 +15780,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="186" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="2" t="s">
         <v>352</v>
       </c>
@@ -15835,7 +15836,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="187" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="2" t="s">
         <v>353</v>
       </c>
@@ -15891,7 +15892,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="188" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="2" t="s">
         <v>354</v>
       </c>
@@ -15947,7 +15948,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="189" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="2" t="s">
         <v>355</v>
       </c>
@@ -16003,7 +16004,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="190" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="2" t="s">
         <v>356</v>
       </c>
@@ -16059,7 +16060,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="191" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="2" t="s">
         <v>357</v>
       </c>
@@ -16115,7 +16116,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="192" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="2" t="s">
         <v>445</v>
       </c>
@@ -16171,7 +16172,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="193" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="2" t="s">
         <v>446</v>
       </c>
@@ -16227,7 +16228,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="194" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="2" t="s">
         <v>358</v>
       </c>
@@ -16283,7 +16284,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="195" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" s="2" t="s">
         <v>359</v>
       </c>
@@ -16339,7 +16340,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="196" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" s="2" t="s">
         <v>360</v>
       </c>
@@ -16395,7 +16396,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="197" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="2" t="s">
         <v>361</v>
       </c>
@@ -16451,7 +16452,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="198" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" s="2" t="s">
         <v>362</v>
       </c>
@@ -16507,7 +16508,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="199" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" s="2" t="s">
         <v>447</v>
       </c>
@@ -16563,7 +16564,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="200" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="2" t="s">
         <v>448</v>
       </c>
@@ -16619,7 +16620,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="201" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="2" t="s">
         <v>449</v>
       </c>
@@ -16675,7 +16676,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="202" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" s="2" t="s">
         <v>363</v>
       </c>
@@ -16731,7 +16732,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="203" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" s="2" t="s">
         <v>364</v>
       </c>
@@ -16787,7 +16788,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="204" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" s="2" t="s">
         <v>365</v>
       </c>
@@ -16843,7 +16844,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="205" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" s="2" t="s">
         <v>366</v>
       </c>
@@ -16899,7 +16900,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="206" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" s="2" t="s">
         <v>367</v>
       </c>
@@ -16955,7 +16956,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="207" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207" s="2" t="s">
         <v>450</v>
       </c>
@@ -17011,7 +17012,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="208" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" s="2" t="s">
         <v>368</v>
       </c>
@@ -17067,7 +17068,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="209" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" s="2" t="s">
         <v>451</v>
       </c>
@@ -17123,7 +17124,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="210" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A210" s="2" t="s">
         <v>369</v>
       </c>
@@ -17179,7 +17180,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="211" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" s="2" t="s">
         <v>452</v>
       </c>
@@ -17235,7 +17236,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="212" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" s="2" t="s">
         <v>453</v>
       </c>
@@ -17291,7 +17292,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="213" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213" s="2" t="s">
         <v>454</v>
       </c>
@@ -17347,7 +17348,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="214" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214" s="2" t="s">
         <v>455</v>
       </c>
@@ -17403,7 +17404,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="215" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" s="2" t="s">
         <v>370</v>
       </c>
@@ -17459,7 +17460,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="216" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216" s="2" t="s">
         <v>456</v>
       </c>
@@ -17515,7 +17516,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="217" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A217" s="2" t="s">
         <v>371</v>
       </c>
@@ -17571,7 +17572,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="218" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A218" s="2" t="s">
         <v>372</v>
       </c>
@@ -17627,7 +17628,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="219" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219" s="2" t="s">
         <v>373</v>
       </c>
@@ -17683,7 +17684,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="220" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="2" t="s">
         <v>457</v>
       </c>
@@ -17739,7 +17740,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="221" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A221" s="2" t="s">
         <v>374</v>
       </c>
@@ -17795,7 +17796,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="222" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A222" s="2" t="s">
         <v>458</v>
       </c>
@@ -17851,7 +17852,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="223" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A223" s="2" t="s">
         <v>375</v>
       </c>
@@ -17907,7 +17908,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="224" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A224" s="2" t="s">
         <v>376</v>
       </c>
@@ -17963,7 +17964,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="225" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225" s="2" t="s">
         <v>377</v>
       </c>
@@ -18019,7 +18020,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="226" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A226" s="2" t="s">
         <v>378</v>
       </c>
@@ -18075,7 +18076,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="227" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A227" s="2" t="s">
         <v>379</v>
       </c>
@@ -18131,7 +18132,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="228" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A228" s="2" t="s">
         <v>380</v>
       </c>
@@ -18187,7 +18188,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="229" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A229" s="2" t="s">
         <v>459</v>
       </c>
@@ -18243,7 +18244,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="230" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A230" s="2" t="s">
         <v>381</v>
       </c>
@@ -18299,7 +18300,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="231" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A231" s="2" t="s">
         <v>382</v>
       </c>
@@ -18355,7 +18356,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="232" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A232" s="2" t="s">
         <v>460</v>
       </c>
@@ -18411,7 +18412,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="233" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A233" s="2" t="s">
         <v>383</v>
       </c>
@@ -18467,7 +18468,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="234" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A234" s="2" t="s">
         <v>384</v>
       </c>
@@ -18523,7 +18524,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="235" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A235" s="2" t="s">
         <v>385</v>
       </c>
@@ -18579,7 +18580,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="236" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A236" s="2" t="s">
         <v>386</v>
       </c>
@@ -18635,7 +18636,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="237" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="2" t="s">
         <v>387</v>
       </c>
@@ -18691,7 +18692,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="238" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" s="2" t="s">
         <v>388</v>
       </c>
@@ -18747,7 +18748,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="239" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A239" s="2" t="s">
         <v>461</v>
       </c>
@@ -18803,7 +18804,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="240" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A240" s="2" t="s">
         <v>462</v>
       </c>
@@ -18859,7 +18860,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="241" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A241" s="2" t="s">
         <v>389</v>
       </c>
@@ -18915,7 +18916,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="242" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A242" s="2" t="s">
         <v>463</v>
       </c>
@@ -18971,7 +18972,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="243" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A243" s="2" t="s">
         <v>464</v>
       </c>
@@ -19027,7 +19028,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="244" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A244" s="2" t="s">
         <v>465</v>
       </c>
@@ -19083,7 +19084,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="245" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A245" s="2" t="s">
         <v>390</v>
       </c>
@@ -19139,7 +19140,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="246" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A246" s="2" t="s">
         <v>391</v>
       </c>
@@ -19195,7 +19196,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="247" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A247" s="2" t="s">
         <v>466</v>
       </c>
@@ -19251,7 +19252,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="248" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A248" s="2" t="s">
         <v>392</v>
       </c>
@@ -19307,7 +19308,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="249" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A249" s="2" t="s">
         <v>467</v>
       </c>
@@ -19363,7 +19364,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="250" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A250" s="2" t="s">
         <v>393</v>
       </c>
@@ -19419,7 +19420,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="251" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A251" s="2" t="s">
         <v>394</v>
       </c>
@@ -19475,7 +19476,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="252" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A252" s="2" t="s">
         <v>395</v>
       </c>
@@ -19531,7 +19532,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="253" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A253" s="2" t="s">
         <v>396</v>
       </c>
@@ -19587,7 +19588,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="254" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A254" s="2" t="s">
         <v>468</v>
       </c>
@@ -19643,7 +19644,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="255" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255" s="2" t="s">
         <v>397</v>
       </c>
@@ -19699,7 +19700,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="256" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A256" s="2" t="s">
         <v>398</v>
       </c>
@@ -19755,7 +19756,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="257" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A257" s="2" t="s">
         <v>399</v>
       </c>
@@ -19811,7 +19812,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="258" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A258" s="2" t="s">
         <v>400</v>
       </c>
@@ -19867,7 +19868,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="259" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A259" s="2" t="s">
         <v>1260</v>
       </c>
@@ -19911,7 +19912,7 @@
       <c r="Q259" s="4"/>
       <c r="R259" s="4"/>
     </row>
-    <row r="260" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A260" s="2" t="s">
         <v>1262</v>
       </c>
@@ -19955,7 +19956,7 @@
       <c r="Q260" s="4"/>
       <c r="R260" s="4"/>
     </row>
-    <row r="261" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A261" s="2" t="s">
         <v>1263</v>
       </c>
@@ -19999,7 +20000,7 @@
       <c r="Q261" s="4"/>
       <c r="R261" s="4"/>
     </row>
-    <row r="262" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A262" s="2" t="s">
         <v>1265</v>
       </c>
@@ -20043,7 +20044,7 @@
       <c r="Q262" s="4"/>
       <c r="R262" s="4"/>
     </row>
-    <row r="263" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A263" s="2" t="s">
         <v>1266</v>
       </c>
@@ -20087,7 +20088,7 @@
       <c r="Q263" s="4"/>
       <c r="R263" s="4"/>
     </row>
-    <row r="264" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A264" s="2" t="s">
         <v>1268</v>
       </c>
@@ -20131,7 +20132,7 @@
       <c r="Q264" s="4"/>
       <c r="R264" s="4"/>
     </row>
-    <row r="265" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A265" s="2" t="s">
         <v>1270</v>
       </c>
@@ -20175,7 +20176,7 @@
       <c r="Q265" s="4"/>
       <c r="R265" s="4"/>
     </row>
-    <row r="266" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A266" s="2" t="s">
         <v>1272</v>
       </c>
@@ -20219,7 +20220,7 @@
       <c r="Q266" s="4"/>
       <c r="R266" s="4"/>
     </row>
-    <row r="267" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A267" s="2" t="s">
         <v>1273</v>
       </c>
@@ -20263,7 +20264,7 @@
       <c r="Q267" s="4"/>
       <c r="R267" s="4"/>
     </row>
-    <row r="268" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A268" s="2" t="s">
         <v>1274</v>
       </c>
@@ -20307,7 +20308,7 @@
       <c r="Q268" s="4"/>
       <c r="R268" s="4"/>
     </row>
-    <row r="269" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A269" s="2" t="s">
         <v>1275</v>
       </c>
@@ -20351,7 +20352,7 @@
       <c r="Q269" s="4"/>
       <c r="R269" s="4"/>
     </row>
-    <row r="270" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A270" s="2" t="s">
         <v>1277</v>
       </c>
@@ -20395,7 +20396,7 @@
       <c r="Q270" s="4"/>
       <c r="R270" s="4"/>
     </row>
-    <row r="271" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A271" s="2" t="s">
         <v>1278</v>
       </c>
@@ -20439,7 +20440,7 @@
       <c r="Q271" s="4"/>
       <c r="R271" s="4"/>
     </row>
-    <row r="272" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A272" s="2" t="s">
         <v>1279</v>
       </c>
@@ -20483,7 +20484,7 @@
       <c r="Q272" s="4"/>
       <c r="R272" s="4"/>
     </row>
-    <row r="273" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A273" s="2" t="s">
         <v>473</v>
       </c>
@@ -20527,7 +20528,7 @@
       <c r="Q273" s="4"/>
       <c r="R273" s="4"/>
     </row>
-    <row r="274" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A274" s="2" t="s">
         <v>476</v>
       </c>
@@ -20571,7 +20572,7 @@
       <c r="Q274" s="4"/>
       <c r="R274" s="4"/>
     </row>
-    <row r="275" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A275" s="2" t="s">
         <v>477</v>
       </c>
@@ -20615,7 +20616,7 @@
       <c r="Q275" s="4"/>
       <c r="R275" s="4"/>
     </row>
-    <row r="276" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A276" s="2" t="s">
         <v>478</v>
       </c>
@@ -20659,7 +20660,7 @@
       <c r="Q276" s="4"/>
       <c r="R276" s="4"/>
     </row>
-    <row r="277" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A277" s="2" t="s">
         <v>479</v>
       </c>
@@ -20703,7 +20704,7 @@
       <c r="Q277" s="4"/>
       <c r="R277" s="4"/>
     </row>
-    <row r="278" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A278" s="2" t="s">
         <v>1280</v>
       </c>
@@ -20747,7 +20748,7 @@
       <c r="Q278" s="4"/>
       <c r="R278" s="4"/>
     </row>
-    <row r="279" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A279" s="2" t="s">
         <v>1282</v>
       </c>
@@ -20791,7 +20792,7 @@
       <c r="Q279" s="4"/>
       <c r="R279" s="4"/>
     </row>
-    <row r="280" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A280" s="2" t="s">
         <v>1284</v>
       </c>
@@ -20835,7 +20836,7 @@
       <c r="Q280" s="4"/>
       <c r="R280" s="4"/>
     </row>
-    <row r="281" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A281" s="2" t="s">
         <v>1285</v>
       </c>
@@ -20879,7 +20880,7 @@
       <c r="Q281" s="4"/>
       <c r="R281" s="4"/>
     </row>
-    <row r="282" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A282" s="2" t="s">
         <v>421</v>
       </c>
@@ -20923,7 +20924,7 @@
       <c r="Q282" s="4"/>
       <c r="R282" s="4"/>
     </row>
-    <row r="283" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A283" s="2" t="s">
         <v>261</v>
       </c>
@@ -20967,7 +20968,7 @@
       <c r="Q283" s="4"/>
       <c r="R283" s="4"/>
     </row>
-    <row r="284" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A284" s="2" t="s">
         <v>260</v>
       </c>
@@ -21011,7 +21012,7 @@
       <c r="Q284" s="4"/>
       <c r="R284" s="4"/>
     </row>
-    <row r="285" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A285" s="2" t="s">
         <v>259</v>
       </c>
@@ -21055,7 +21056,7 @@
       <c r="Q285" s="4"/>
       <c r="R285" s="4"/>
     </row>
-    <row r="286" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A286" s="2" t="s">
         <v>1286</v>
       </c>
@@ -21099,7 +21100,7 @@
       <c r="Q286" s="4"/>
       <c r="R286" s="4"/>
     </row>
-    <row r="287" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A287" s="2" t="s">
         <v>1288</v>
       </c>
@@ -21143,7 +21144,7 @@
       <c r="Q287" s="4"/>
       <c r="R287" s="4"/>
     </row>
-    <row r="288" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A288" s="2" t="s">
         <v>1290</v>
       </c>
@@ -21187,7 +21188,7 @@
       <c r="Q288" s="4"/>
       <c r="R288" s="4"/>
     </row>
-    <row r="289" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A289" s="2" t="s">
         <v>1291</v>
       </c>
@@ -21231,7 +21232,7 @@
       <c r="Q289" s="4"/>
       <c r="R289" s="4"/>
     </row>
-    <row r="290" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A290" s="2" t="s">
         <v>1292</v>
       </c>
@@ -21275,7 +21276,7 @@
       <c r="Q290" s="4"/>
       <c r="R290" s="4"/>
     </row>
-    <row r="291" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A291" s="2" t="s">
         <v>1294</v>
       </c>
@@ -21319,7 +21320,7 @@
       <c r="Q291" s="4"/>
       <c r="R291" s="4"/>
     </row>
-    <row r="292" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A292" s="2" t="s">
         <v>1295</v>
       </c>
@@ -21363,7 +21364,7 @@
       <c r="Q292" s="4"/>
       <c r="R292" s="4"/>
     </row>
-    <row r="293" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A293" s="2" t="s">
         <v>423</v>
       </c>
@@ -21407,7 +21408,7 @@
       <c r="Q293" s="4"/>
       <c r="R293" s="4"/>
     </row>
-    <row r="294" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A294" s="2" t="s">
         <v>481</v>
       </c>
@@ -21451,7 +21452,7 @@
       <c r="Q294" s="4"/>
       <c r="R294" s="4"/>
     </row>
-    <row r="295" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A295" s="2" t="s">
         <v>422</v>
       </c>
@@ -21495,7 +21496,7 @@
       <c r="Q295" s="4"/>
       <c r="R295" s="4"/>
     </row>
-    <row r="296" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A296" s="2" t="s">
         <v>262</v>
       </c>
@@ -21539,7 +21540,7 @@
       <c r="Q296" s="4"/>
       <c r="R296" s="4"/>
     </row>
-    <row r="297" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A297" s="2" t="s">
         <v>263</v>
       </c>
@@ -21583,7 +21584,7 @@
       <c r="Q297" s="4"/>
       <c r="R297" s="4"/>
     </row>
-    <row r="298" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A298" s="2" t="s">
         <v>1296</v>
       </c>
@@ -21627,7 +21628,7 @@
       <c r="Q298" s="4"/>
       <c r="R298" s="4"/>
     </row>
-    <row r="299" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A299" s="2" t="s">
         <v>1298</v>
       </c>
@@ -21671,7 +21672,7 @@
       <c r="Q299" s="4"/>
       <c r="R299" s="4"/>
     </row>
-    <row r="300" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A300" s="2" t="s">
         <v>1299</v>
       </c>
@@ -21715,7 +21716,7 @@
       <c r="Q300" s="4"/>
       <c r="R300" s="4"/>
     </row>
-    <row r="301" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A301" s="2" t="s">
         <v>483</v>
       </c>
@@ -21759,7 +21760,7 @@
       <c r="Q301" s="4"/>
       <c r="R301" s="4"/>
     </row>
-    <row r="302" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A302" s="2" t="s">
         <v>485</v>
       </c>
@@ -21803,7 +21804,7 @@
       <c r="Q302" s="4"/>
       <c r="R302" s="4"/>
     </row>
-    <row r="303" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A303" s="2" t="s">
         <v>486</v>
       </c>
@@ -21847,7 +21848,7 @@
       <c r="Q303" s="4"/>
       <c r="R303" s="4"/>
     </row>
-    <row r="304" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A304" s="2" t="s">
         <v>1301</v>
       </c>
@@ -21891,7 +21892,7 @@
       <c r="Q304" s="4"/>
       <c r="R304" s="4"/>
     </row>
-    <row r="305" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A305" s="2" t="s">
         <v>1304</v>
       </c>
@@ -21935,7 +21936,7 @@
       <c r="Q305" s="4"/>
       <c r="R305" s="4"/>
     </row>
-    <row r="306" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A306" s="2" t="s">
         <v>1305</v>
       </c>
@@ -21979,7 +21980,7 @@
       <c r="Q306" s="4"/>
       <c r="R306" s="4"/>
     </row>
-    <row r="307" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A307" s="2" t="s">
         <v>1307</v>
       </c>
@@ -22023,7 +22024,7 @@
       <c r="Q307" s="4"/>
       <c r="R307" s="4"/>
     </row>
-    <row r="308" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A308" s="2" t="s">
         <v>1308</v>
       </c>
@@ -22067,7 +22068,7 @@
       <c r="Q308" s="4"/>
       <c r="R308" s="4"/>
     </row>
-    <row r="309" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A309" s="2" t="s">
         <v>427</v>
       </c>
@@ -22111,7 +22112,7 @@
       <c r="Q309" s="4"/>
       <c r="R309" s="4"/>
     </row>
-    <row r="310" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A310" s="2" t="s">
         <v>277</v>
       </c>
@@ -22155,7 +22156,7 @@
       <c r="Q310" s="4"/>
       <c r="R310" s="4"/>
     </row>
-    <row r="311" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A311" s="2" t="s">
         <v>276</v>
       </c>
@@ -22199,7 +22200,7 @@
       <c r="Q311" s="4"/>
       <c r="R311" s="4"/>
     </row>
-    <row r="312" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A312" s="2" t="s">
         <v>278</v>
       </c>
@@ -22243,7 +22244,7 @@
       <c r="Q312" s="4"/>
       <c r="R312" s="4"/>
     </row>
-    <row r="313" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A313" s="2" t="s">
         <v>426</v>
       </c>
@@ -22287,7 +22288,7 @@
       <c r="Q313" s="4"/>
       <c r="R313" s="4"/>
     </row>
-    <row r="314" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A314" s="2" t="s">
         <v>269</v>
       </c>
@@ -22331,7 +22332,7 @@
       <c r="Q314" s="4"/>
       <c r="R314" s="4"/>
     </row>
-    <row r="315" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A315" s="2" t="s">
         <v>487</v>
       </c>
@@ -22375,7 +22376,7 @@
       <c r="Q315" s="4"/>
       <c r="R315" s="4"/>
     </row>
-    <row r="316" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A316" s="2" t="s">
         <v>489</v>
       </c>
@@ -22419,7 +22420,7 @@
       <c r="Q316" s="4"/>
       <c r="R316" s="4"/>
     </row>
-    <row r="317" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A317" s="2" t="s">
         <v>491</v>
       </c>
@@ -22463,7 +22464,7 @@
       <c r="Q317" s="4"/>
       <c r="R317" s="4"/>
     </row>
-    <row r="318" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A318" s="2" t="s">
         <v>434</v>
       </c>
@@ -22507,7 +22508,7 @@
       <c r="Q318" s="4"/>
       <c r="R318" s="4"/>
     </row>
-    <row r="319" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A319" s="2" t="s">
         <v>286</v>
       </c>
@@ -22551,7 +22552,7 @@
       <c r="Q319" s="4"/>
       <c r="R319" s="4"/>
     </row>
-    <row r="320" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A320" s="2" t="s">
         <v>285</v>
       </c>
@@ -22595,7 +22596,7 @@
       <c r="Q320" s="4"/>
       <c r="R320" s="4"/>
     </row>
-    <row r="321" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A321" s="2" t="s">
         <v>284</v>
       </c>
@@ -22639,7 +22640,7 @@
       <c r="Q321" s="4"/>
       <c r="R321" s="4"/>
     </row>
-    <row r="322" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A322" s="2" t="s">
         <v>433</v>
       </c>
@@ -22683,7 +22684,7 @@
       <c r="Q322" s="4"/>
       <c r="R322" s="4"/>
     </row>
-    <row r="323" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A323" s="2" t="s">
         <v>435</v>
       </c>
@@ -22727,7 +22728,7 @@
       <c r="Q323" s="4"/>
       <c r="R323" s="4"/>
     </row>
-    <row r="324" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A324" s="2" t="s">
         <v>289</v>
       </c>
@@ -22771,7 +22772,7 @@
       <c r="Q324" s="4"/>
       <c r="R324" s="4"/>
     </row>
-    <row r="325" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A325" s="2" t="s">
         <v>288</v>
       </c>
@@ -22815,7 +22816,7 @@
       <c r="Q325" s="4"/>
       <c r="R325" s="4"/>
     </row>
-    <row r="326" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A326" s="2" t="s">
         <v>287</v>
       </c>
@@ -22859,7 +22860,7 @@
       <c r="Q326" s="4"/>
       <c r="R326" s="4"/>
     </row>
-    <row r="327" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A327" s="2" t="s">
         <v>493</v>
       </c>
@@ -22903,7 +22904,7 @@
       <c r="Q327" s="4"/>
       <c r="R327" s="4"/>
     </row>
-    <row r="328" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A328" s="2" t="s">
         <v>1310</v>
       </c>
@@ -22947,7 +22948,7 @@
       <c r="Q328" s="4"/>
       <c r="R328" s="4"/>
     </row>
-    <row r="329" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A329" s="2" t="s">
         <v>1312</v>
       </c>
@@ -22991,7 +22992,7 @@
       <c r="Q329" s="4"/>
       <c r="R329" s="4"/>
     </row>
-    <row r="330" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A330" s="2" t="s">
         <v>1313</v>
       </c>
@@ -23035,7 +23036,7 @@
       <c r="Q330" s="4"/>
       <c r="R330" s="4"/>
     </row>
-    <row r="331" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A331" s="2" t="s">
         <v>1314</v>
       </c>
@@ -23079,7 +23080,7 @@
       <c r="Q331" s="4"/>
       <c r="R331" s="4"/>
     </row>
-    <row r="332" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A332" s="2" t="s">
         <v>302</v>
       </c>
@@ -23123,7 +23124,7 @@
       <c r="Q332" s="4"/>
       <c r="R332" s="4"/>
     </row>
-    <row r="333" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A333" s="2" t="s">
         <v>301</v>
       </c>
@@ -23167,7 +23168,7 @@
       <c r="Q333" s="4"/>
       <c r="R333" s="4"/>
     </row>
-    <row r="334" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A334" s="2" t="s">
         <v>300</v>
       </c>
@@ -23211,7 +23212,7 @@
       <c r="Q334" s="4"/>
       <c r="R334" s="4"/>
     </row>
-    <row r="335" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A335" s="2" t="s">
         <v>306</v>
       </c>
@@ -23255,7 +23256,7 @@
       <c r="Q335" s="4"/>
       <c r="R335" s="4"/>
     </row>
-    <row r="336" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A336" s="2" t="s">
         <v>436</v>
       </c>
@@ -23299,7 +23300,7 @@
       <c r="Q336" s="4"/>
       <c r="R336" s="4"/>
     </row>
-    <row r="337" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A337" s="2" t="s">
         <v>304</v>
       </c>
@@ -23343,7 +23344,7 @@
       <c r="Q337" s="4"/>
       <c r="R337" s="4"/>
     </row>
-    <row r="338" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A338" s="2" t="s">
         <v>305</v>
       </c>
@@ -23387,7 +23388,7 @@
       <c r="Q338" s="4"/>
       <c r="R338" s="4"/>
     </row>
-    <row r="339" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A339" s="2" t="s">
         <v>1315</v>
       </c>
@@ -23431,7 +23432,7 @@
       <c r="Q339" s="4"/>
       <c r="R339" s="4"/>
     </row>
-    <row r="340" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A340" s="2" t="s">
         <v>1317</v>
       </c>
@@ -23475,7 +23476,7 @@
       <c r="Q340" s="4"/>
       <c r="R340" s="4"/>
     </row>
-    <row r="341" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A341" s="2" t="s">
         <v>1318</v>
       </c>
@@ -23519,7 +23520,7 @@
       <c r="Q341" s="4"/>
       <c r="R341" s="4"/>
     </row>
-    <row r="342" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A342" s="2" t="s">
         <v>1320</v>
       </c>
@@ -23563,7 +23564,7 @@
       <c r="Q342" s="4"/>
       <c r="R342" s="4"/>
     </row>
-    <row r="343" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A343" s="2" t="s">
         <v>1321</v>
       </c>
@@ -23607,7 +23608,7 @@
       <c r="Q343" s="4"/>
       <c r="R343" s="4"/>
     </row>
-    <row r="344" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A344" s="2" t="s">
         <v>1323</v>
       </c>
@@ -23651,7 +23652,7 @@
       <c r="Q344" s="4"/>
       <c r="R344" s="4"/>
     </row>
-    <row r="345" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A345" s="2" t="s">
         <v>1324</v>
       </c>
@@ -23695,7 +23696,7 @@
       <c r="Q345" s="4"/>
       <c r="R345" s="4"/>
     </row>
-    <row r="346" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A346" s="2" t="s">
         <v>309</v>
       </c>
@@ -23739,7 +23740,7 @@
       <c r="Q346" s="4"/>
       <c r="R346" s="4"/>
     </row>
-    <row r="347" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A347" s="2" t="s">
         <v>308</v>
       </c>
@@ -23783,7 +23784,7 @@
       <c r="Q347" s="4"/>
       <c r="R347" s="4"/>
     </row>
-    <row r="348" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A348" s="2" t="s">
         <v>307</v>
       </c>
@@ -23827,7 +23828,7 @@
       <c r="Q348" s="4"/>
       <c r="R348" s="4"/>
     </row>
-    <row r="349" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A349" s="2" t="s">
         <v>437</v>
       </c>
@@ -23871,7 +23872,7 @@
       <c r="Q349" s="4"/>
       <c r="R349" s="4"/>
     </row>
-    <row r="350" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A350" s="2" t="s">
         <v>328</v>
       </c>
@@ -23915,7 +23916,7 @@
       <c r="Q350" s="4"/>
       <c r="R350" s="4"/>
     </row>
-    <row r="351" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A351" s="2" t="s">
         <v>326</v>
       </c>
@@ -23959,7 +23960,7 @@
       <c r="Q351" s="4"/>
       <c r="R351" s="4"/>
     </row>
-    <row r="352" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A352" s="2" t="s">
         <v>325</v>
       </c>
@@ -24003,7 +24004,7 @@
       <c r="Q352" s="4"/>
       <c r="R352" s="4"/>
     </row>
-    <row r="353" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A353" s="2" t="s">
         <v>327</v>
       </c>
@@ -24047,7 +24048,7 @@
       <c r="Q353" s="4"/>
       <c r="R353" s="4"/>
     </row>
-    <row r="354" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A354" s="2" t="s">
         <v>321</v>
       </c>
@@ -24091,7 +24092,7 @@
       <c r="Q354" s="4"/>
       <c r="R354" s="4"/>
     </row>
-    <row r="355" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A355" s="2" t="s">
         <v>323</v>
       </c>
@@ -24135,7 +24136,7 @@
       <c r="Q355" s="4"/>
       <c r="R355" s="4"/>
     </row>
-    <row r="356" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A356" s="2" t="s">
         <v>322</v>
       </c>
@@ -24179,7 +24180,7 @@
       <c r="Q356" s="4"/>
       <c r="R356" s="4"/>
     </row>
-    <row r="357" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A357" s="2" t="s">
         <v>324</v>
       </c>
@@ -24223,7 +24224,7 @@
       <c r="Q357" s="4"/>
       <c r="R357" s="4"/>
     </row>
-    <row r="358" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A358" s="2" t="s">
         <v>1326</v>
       </c>
@@ -24267,7 +24268,7 @@
       <c r="Q358" s="4"/>
       <c r="R358" s="4"/>
     </row>
-    <row r="359" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A359" s="2" t="s">
         <v>1328</v>
       </c>
@@ -24311,7 +24312,7 @@
       <c r="Q359" s="4"/>
       <c r="R359" s="4"/>
     </row>
-    <row r="360" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A360" s="2" t="s">
         <v>1329</v>
       </c>
@@ -24355,7 +24356,7 @@
       <c r="Q360" s="4"/>
       <c r="R360" s="4"/>
     </row>
-    <row r="361" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A361" s="2" t="s">
         <v>1330</v>
       </c>
@@ -24399,7 +24400,7 @@
       <c r="Q361" s="4"/>
       <c r="R361" s="4"/>
     </row>
-    <row r="362" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A362" s="2" t="s">
         <v>1331</v>
       </c>
@@ -24443,7 +24444,7 @@
       <c r="Q362" s="4"/>
       <c r="R362" s="4"/>
     </row>
-    <row r="363" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A363" s="2" t="s">
         <v>329</v>
       </c>
@@ -24487,7 +24488,7 @@
       <c r="Q363" s="4"/>
       <c r="R363" s="4"/>
     </row>
-    <row r="364" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A364" s="2" t="s">
         <v>332</v>
       </c>
@@ -24531,7 +24532,7 @@
       <c r="Q364" s="4"/>
       <c r="R364" s="4"/>
     </row>
-    <row r="365" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A365" s="2" t="s">
         <v>1333</v>
       </c>
@@ -24575,7 +24576,7 @@
       <c r="Q365" s="4"/>
       <c r="R365" s="4"/>
     </row>
-    <row r="366" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A366" s="2" t="s">
         <v>330</v>
       </c>
@@ -24619,7 +24620,7 @@
       <c r="Q366" s="4"/>
       <c r="R366" s="4"/>
     </row>
-    <row r="367" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A367" s="2" t="s">
         <v>494</v>
       </c>
@@ -24663,7 +24664,7 @@
       <c r="Q367" s="4"/>
       <c r="R367" s="4"/>
     </row>
-    <row r="368" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A368" s="2" t="s">
         <v>334</v>
       </c>
@@ -24707,7 +24708,7 @@
       <c r="Q368" s="4"/>
       <c r="R368" s="4"/>
     </row>
-    <row r="369" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A369" s="2" t="s">
         <v>336</v>
       </c>
@@ -24751,7 +24752,7 @@
       <c r="Q369" s="4"/>
       <c r="R369" s="4"/>
     </row>
-    <row r="370" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A370" s="2" t="s">
         <v>335</v>
       </c>
@@ -24795,7 +24796,7 @@
       <c r="Q370" s="4"/>
       <c r="R370" s="4"/>
     </row>
-    <row r="371" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A371" s="2" t="s">
         <v>333</v>
       </c>
@@ -24839,7 +24840,7 @@
       <c r="Q371" s="4"/>
       <c r="R371" s="4"/>
     </row>
-    <row r="372" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A372" s="2" t="s">
         <v>1334</v>
       </c>
@@ -24883,7 +24884,7 @@
       <c r="Q372" s="4"/>
       <c r="R372" s="4"/>
     </row>
-    <row r="373" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A373" s="2" t="s">
         <v>1337</v>
       </c>
@@ -24927,7 +24928,7 @@
       <c r="Q373" s="4"/>
       <c r="R373" s="4"/>
     </row>
-    <row r="374" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A374" s="2" t="s">
         <v>1338</v>
       </c>
@@ -24971,7 +24972,7 @@
       <c r="Q374" s="4"/>
       <c r="R374" s="4"/>
     </row>
-    <row r="375" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A375" s="2" t="s">
         <v>1339</v>
       </c>
@@ -25015,7 +25016,7 @@
       <c r="Q375" s="4"/>
       <c r="R375" s="4"/>
     </row>
-    <row r="376" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A376" s="2" t="s">
         <v>496</v>
       </c>
@@ -25059,7 +25060,7 @@
       <c r="Q376" s="4"/>
       <c r="R376" s="4"/>
     </row>
-    <row r="377" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A377" s="2" t="s">
         <v>498</v>
       </c>
@@ -25103,7 +25104,7 @@
       <c r="Q377" s="4"/>
       <c r="R377" s="4"/>
     </row>
-    <row r="378" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A378" s="2" t="s">
         <v>499</v>
       </c>
@@ -25147,7 +25148,7 @@
       <c r="Q378" s="4"/>
       <c r="R378" s="4"/>
     </row>
-    <row r="379" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A379" s="2" t="s">
         <v>501</v>
       </c>
@@ -25191,7 +25192,7 @@
       <c r="Q379" s="4"/>
       <c r="R379" s="4"/>
     </row>
-    <row r="380" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A380" s="2" t="s">
         <v>444</v>
       </c>
@@ -25235,7 +25236,7 @@
       <c r="Q380" s="4"/>
       <c r="R380" s="4"/>
     </row>
-    <row r="381" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A381" s="2" t="s">
         <v>349</v>
       </c>
@@ -25279,7 +25280,7 @@
       <c r="Q381" s="4"/>
       <c r="R381" s="4"/>
     </row>
-    <row r="382" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A382" s="2" t="s">
         <v>503</v>
       </c>
@@ -25323,7 +25324,7 @@
       <c r="Q382" s="4"/>
       <c r="R382" s="4"/>
     </row>
-    <row r="383" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A383" s="2" t="s">
         <v>347</v>
       </c>
@@ -25367,7 +25368,7 @@
       <c r="Q383" s="4"/>
       <c r="R383" s="4"/>
     </row>
-    <row r="384" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A384" s="2" t="s">
         <v>504</v>
       </c>
@@ -25411,7 +25412,7 @@
       <c r="Q384" s="4"/>
       <c r="R384" s="4"/>
     </row>
-    <row r="385" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A385" s="2" t="s">
         <v>346</v>
       </c>
@@ -25455,7 +25456,7 @@
       <c r="Q385" s="4"/>
       <c r="R385" s="4"/>
     </row>
-    <row r="386" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A386" s="2" t="s">
         <v>505</v>
       </c>
@@ -25499,7 +25500,7 @@
       <c r="Q386" s="4"/>
       <c r="R386" s="4"/>
     </row>
-    <row r="387" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A387" s="2" t="s">
         <v>506</v>
       </c>
@@ -25543,7 +25544,7 @@
       <c r="Q387" s="4"/>
       <c r="R387" s="4"/>
     </row>
-    <row r="388" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A388" s="2" t="s">
         <v>351</v>
       </c>
@@ -25587,7 +25588,7 @@
       <c r="Q388" s="4"/>
       <c r="R388" s="4"/>
     </row>
-    <row r="389" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A389" s="2" t="s">
         <v>250</v>
       </c>
@@ -25631,7 +25632,7 @@
       <c r="Q389" s="4"/>
       <c r="R389" s="4"/>
     </row>
-    <row r="390" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A390" s="2" t="s">
         <v>508</v>
       </c>
@@ -25675,7 +25676,7 @@
       <c r="Q390" s="4"/>
       <c r="R390" s="4"/>
     </row>
-    <row r="391" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A391" s="2" t="s">
         <v>251</v>
       </c>
@@ -25719,7 +25720,7 @@
       <c r="Q391" s="4"/>
       <c r="R391" s="4"/>
     </row>
-    <row r="392" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A392" s="2" t="s">
         <v>415</v>
       </c>
@@ -25763,7 +25764,7 @@
       <c r="Q392" s="4"/>
       <c r="R392" s="4"/>
     </row>
-    <row r="393" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A393" s="2" t="s">
         <v>1340</v>
       </c>
@@ -25807,7 +25808,7 @@
       <c r="Q393" s="4"/>
       <c r="R393" s="4"/>
     </row>
-    <row r="394" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A394" s="2" t="s">
         <v>1342</v>
       </c>
@@ -25851,7 +25852,7 @@
       <c r="Q394" s="4"/>
       <c r="R394" s="4"/>
     </row>
-    <row r="395" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A395" s="2" t="s">
         <v>1343</v>
       </c>
@@ -25895,7 +25896,7 @@
       <c r="Q395" s="4"/>
       <c r="R395" s="4"/>
     </row>
-    <row r="396" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A396" s="2" t="s">
         <v>248</v>
       </c>
@@ -25939,7 +25940,7 @@
       <c r="Q396" s="4"/>
       <c r="R396" s="4"/>
     </row>
-    <row r="397" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A397" s="2" t="s">
         <v>414</v>
       </c>
@@ -25983,7 +25984,7 @@
       <c r="Q397" s="4"/>
       <c r="R397" s="4"/>
     </row>
-    <row r="398" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A398" s="2" t="s">
         <v>249</v>
       </c>
@@ -26027,7 +26028,7 @@
       <c r="Q398" s="4"/>
       <c r="R398" s="4"/>
     </row>
-    <row r="399" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A399" s="2" t="s">
         <v>416</v>
       </c>
@@ -26071,7 +26072,7 @@
       <c r="Q399" s="4"/>
       <c r="R399" s="4"/>
     </row>
-    <row r="400" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A400" s="2" t="s">
         <v>509</v>
       </c>
@@ -26115,7 +26116,7 @@
       <c r="Q400" s="4"/>
       <c r="R400" s="4"/>
     </row>
-    <row r="401" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A401" s="2" t="s">
         <v>510</v>
       </c>
@@ -26159,7 +26160,7 @@
       <c r="Q401" s="4"/>
       <c r="R401" s="4"/>
     </row>
-    <row r="402" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A402" s="2" t="s">
         <v>511</v>
       </c>
@@ -26203,7 +26204,7 @@
       <c r="Q402" s="4"/>
       <c r="R402" s="4"/>
     </row>
-    <row r="403" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A403" s="2" t="s">
         <v>513</v>
       </c>
@@ -26247,7 +26248,7 @@
       <c r="Q403" s="4"/>
       <c r="R403" s="4"/>
     </row>
-    <row r="404" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A404" s="2" t="s">
         <v>280</v>
       </c>
@@ -26291,7 +26292,7 @@
       <c r="Q404" s="4"/>
       <c r="R404" s="4"/>
     </row>
-    <row r="405" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A405" s="2" t="s">
         <v>429</v>
       </c>
@@ -26335,7 +26336,7 @@
       <c r="Q405" s="4"/>
       <c r="R405" s="4"/>
     </row>
-    <row r="406" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A406" s="2" t="s">
         <v>279</v>
       </c>
@@ -26379,7 +26380,7 @@
       <c r="Q406" s="4"/>
       <c r="R406" s="4"/>
     </row>
-    <row r="407" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A407" s="2" t="s">
         <v>428</v>
       </c>
@@ -26423,7 +26424,7 @@
       <c r="Q407" s="4"/>
       <c r="R407" s="4"/>
     </row>
-    <row r="408" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A408" s="2" t="s">
         <v>1344</v>
       </c>
@@ -26467,7 +26468,7 @@
       <c r="Q408" s="4"/>
       <c r="R408" s="4"/>
     </row>
-    <row r="409" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A409" s="2" t="s">
         <v>1346</v>
       </c>
@@ -26511,7 +26512,7 @@
       <c r="Q409" s="4"/>
       <c r="R409" s="4"/>
     </row>
-    <row r="410" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A410" s="2" t="s">
         <v>1347</v>
       </c>
@@ -26555,7 +26556,7 @@
       <c r="Q410" s="4"/>
       <c r="R410" s="4"/>
     </row>
-    <row r="411" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A411" s="2" t="s">
         <v>317</v>
       </c>
@@ -26599,7 +26600,7 @@
       <c r="Q411" s="4"/>
       <c r="R411" s="4"/>
     </row>
-    <row r="412" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A412" s="2" t="s">
         <v>440</v>
       </c>
@@ -26643,7 +26644,7 @@
       <c r="Q412" s="4"/>
       <c r="R412" s="4"/>
     </row>
-    <row r="413" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A413" s="2" t="s">
         <v>316</v>
       </c>
@@ -26687,7 +26688,7 @@
       <c r="Q413" s="4"/>
       <c r="R413" s="4"/>
     </row>
-    <row r="414" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A414" s="2" t="s">
         <v>315</v>
       </c>
@@ -26731,7 +26732,7 @@
       <c r="Q414" s="4"/>
       <c r="R414" s="4"/>
     </row>
-    <row r="415" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A415" s="2" t="s">
         <v>1349</v>
       </c>
@@ -26775,7 +26776,7 @@
       <c r="Q415" s="4"/>
       <c r="R415" s="4"/>
     </row>
-    <row r="416" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A416" s="2" t="s">
         <v>1351</v>
       </c>
@@ -26819,7 +26820,7 @@
       <c r="Q416" s="4"/>
       <c r="R416" s="4"/>
     </row>
-    <row r="417" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A417" s="2" t="s">
         <v>1353</v>
       </c>
@@ -26863,7 +26864,7 @@
       <c r="Q417" s="4"/>
       <c r="R417" s="4"/>
     </row>
-    <row r="418" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A418" s="2" t="s">
         <v>1355</v>
       </c>
@@ -26907,7 +26908,7 @@
       <c r="Q418" s="4"/>
       <c r="R418" s="4"/>
     </row>
-    <row r="419" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A419" s="2" t="s">
         <v>458</v>
       </c>
@@ -26951,7 +26952,7 @@
       <c r="Q419" s="4"/>
       <c r="R419" s="4"/>
     </row>
-    <row r="420" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A420" s="2" t="s">
         <v>374</v>
       </c>
@@ -26995,7 +26996,7 @@
       <c r="Q420" s="4"/>
       <c r="R420" s="4"/>
     </row>
-    <row r="421" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A421" s="2" t="s">
         <v>375</v>
       </c>
@@ -27039,7 +27040,7 @@
       <c r="Q421" s="4"/>
       <c r="R421" s="4"/>
     </row>
-    <row r="422" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A422" s="2" t="s">
         <v>373</v>
       </c>
@@ -27083,7 +27084,7 @@
       <c r="Q422" s="4"/>
       <c r="R422" s="4"/>
     </row>
-    <row r="423" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A423" s="2" t="s">
         <v>457</v>
       </c>
@@ -27127,7 +27128,7 @@
       <c r="Q423" s="4"/>
       <c r="R423" s="4"/>
     </row>
-    <row r="424" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A424" s="2" t="s">
         <v>383</v>
       </c>
@@ -27171,7 +27172,7 @@
       <c r="Q424" s="4"/>
       <c r="R424" s="4"/>
     </row>
-    <row r="425" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A425" s="2" t="s">
         <v>382</v>
       </c>
@@ -27215,7 +27216,7 @@
       <c r="Q425" s="4"/>
       <c r="R425" s="4"/>
     </row>
-    <row r="426" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A426" s="2" t="s">
         <v>381</v>
       </c>
@@ -27259,7 +27260,7 @@
       <c r="Q426" s="4"/>
       <c r="R426" s="4"/>
     </row>
-    <row r="427" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A427" s="2" t="s">
         <v>1357</v>
       </c>
@@ -27303,7 +27304,7 @@
       <c r="Q427" s="4"/>
       <c r="R427" s="4"/>
     </row>
-    <row r="428" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A428" s="2" t="s">
         <v>1359</v>
       </c>
@@ -27347,7 +27348,7 @@
       <c r="Q428" s="4"/>
       <c r="R428" s="4"/>
     </row>
-    <row r="429" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A429" s="2" t="s">
         <v>1360</v>
       </c>
@@ -27391,7 +27392,7 @@
       <c r="Q429" s="4"/>
       <c r="R429" s="4"/>
     </row>
-    <row r="430" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A430" s="2" t="s">
         <v>1361</v>
       </c>
@@ -27435,7 +27436,7 @@
       <c r="Q430" s="4"/>
       <c r="R430" s="4"/>
     </row>
-    <row r="431" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A431" s="2" t="s">
         <v>1362</v>
       </c>
@@ -27479,7 +27480,7 @@
       <c r="Q431" s="4"/>
       <c r="R431" s="4"/>
     </row>
-    <row r="432" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A432" s="2" t="s">
         <v>1365</v>
       </c>
@@ -27523,7 +27524,7 @@
       <c r="Q432" s="4"/>
       <c r="R432" s="4"/>
     </row>
-    <row r="433" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A433" s="2" t="s">
         <v>1367</v>
       </c>
@@ -27567,7 +27568,7 @@
       <c r="Q433" s="4"/>
       <c r="R433" s="4"/>
     </row>
-    <row r="434" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A434" s="2" t="s">
         <v>1369</v>
       </c>
@@ -27611,7 +27612,7 @@
       <c r="Q434" s="4"/>
       <c r="R434" s="4"/>
     </row>
-    <row r="435" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A435" s="2" t="s">
         <v>354</v>
       </c>
@@ -27655,7 +27656,7 @@
       <c r="Q435" s="4"/>
       <c r="R435" s="4"/>
     </row>
-    <row r="436" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A436" s="2" t="s">
         <v>446</v>
       </c>
@@ -27699,7 +27700,7 @@
       <c r="Q436" s="4"/>
       <c r="R436" s="4"/>
     </row>
-    <row r="437" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A437" s="2" t="s">
         <v>445</v>
       </c>
@@ -27743,7 +27744,7 @@
       <c r="Q437" s="4"/>
       <c r="R437" s="4"/>
     </row>
-    <row r="438" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A438" s="2" t="s">
         <v>357</v>
       </c>
@@ -27787,7 +27788,7 @@
       <c r="Q438" s="4"/>
       <c r="R438" s="4"/>
     </row>
-    <row r="439" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A439" s="2" t="s">
         <v>355</v>
       </c>
@@ -27831,7 +27832,7 @@
       <c r="Q439" s="4"/>
       <c r="R439" s="4"/>
     </row>
-    <row r="440" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A440" s="2" t="s">
         <v>356</v>
       </c>
@@ -27875,7 +27876,7 @@
       <c r="Q440" s="4"/>
       <c r="R440" s="4"/>
     </row>
-    <row r="441" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A441" s="2" t="s">
         <v>424</v>
       </c>
@@ -27919,7 +27920,7 @@
       <c r="Q441" s="4"/>
       <c r="R441" s="4"/>
     </row>
-    <row r="442" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A442" s="2" t="s">
         <v>265</v>
       </c>
@@ -27963,7 +27964,7 @@
       <c r="Q442" s="4"/>
       <c r="R442" s="4"/>
     </row>
-    <row r="443" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A443" s="2" t="s">
         <v>266</v>
       </c>
@@ -28007,7 +28008,7 @@
       <c r="Q443" s="4"/>
       <c r="R443" s="4"/>
     </row>
-    <row r="444" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A444" s="2" t="s">
         <v>1371</v>
       </c>
@@ -28051,7 +28052,7 @@
       <c r="Q444" s="4"/>
       <c r="R444" s="4"/>
     </row>
-    <row r="445" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A445" s="2" t="s">
         <v>1373</v>
       </c>
@@ -28095,7 +28096,7 @@
       <c r="Q445" s="4"/>
       <c r="R445" s="4"/>
     </row>
-    <row r="446" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A446" s="2" t="s">
         <v>1374</v>
       </c>
@@ -28139,7 +28140,7 @@
       <c r="Q446" s="4"/>
       <c r="R446" s="4"/>
     </row>
-    <row r="447" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A447" s="2" t="s">
         <v>1375</v>
       </c>
@@ -28183,7 +28184,7 @@
       <c r="Q447" s="4"/>
       <c r="R447" s="4"/>
     </row>
-    <row r="448" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A448" s="2" t="s">
         <v>1376</v>
       </c>
@@ -28227,7 +28228,7 @@
       <c r="Q448" s="4"/>
       <c r="R448" s="4"/>
     </row>
-    <row r="449" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A449" s="2" t="s">
         <v>1378</v>
       </c>
@@ -28271,7 +28272,7 @@
       <c r="Q449" s="4"/>
       <c r="R449" s="4"/>
     </row>
-    <row r="450" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A450" s="2" t="s">
         <v>1379</v>
       </c>
@@ -28315,7 +28316,7 @@
       <c r="Q450" s="4"/>
       <c r="R450" s="4"/>
     </row>
-    <row r="451" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A451" s="2" t="s">
         <v>1380</v>
       </c>
@@ -28359,7 +28360,7 @@
       <c r="Q451" s="4"/>
       <c r="R451" s="4"/>
     </row>
-    <row r="452" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A452" s="2" t="s">
         <v>442</v>
       </c>
@@ -28403,7 +28404,7 @@
       <c r="Q452" s="4"/>
       <c r="R452" s="4"/>
     </row>
-    <row r="453" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A453" s="2" t="s">
         <v>345</v>
       </c>
@@ -28447,7 +28448,7 @@
       <c r="Q453" s="4"/>
       <c r="R453" s="4"/>
     </row>
-    <row r="454" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A454" s="2" t="s">
         <v>344</v>
       </c>
@@ -28491,7 +28492,7 @@
       <c r="Q454" s="4"/>
       <c r="R454" s="4"/>
     </row>
-    <row r="455" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A455" s="2" t="s">
         <v>441</v>
       </c>
@@ -28535,7 +28536,7 @@
       <c r="Q455" s="4"/>
       <c r="R455" s="4"/>
     </row>
-    <row r="456" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A456" s="2" t="s">
         <v>343</v>
       </c>
@@ -28579,7 +28580,7 @@
       <c r="Q456" s="4"/>
       <c r="R456" s="4"/>
     </row>
-    <row r="457" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A457" s="2" t="s">
         <v>342</v>
       </c>
@@ -28623,7 +28624,7 @@
       <c r="Q457" s="4"/>
       <c r="R457" s="4"/>
     </row>
-    <row r="458" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A458" s="2" t="s">
         <v>341</v>
       </c>
@@ -28667,7 +28668,7 @@
       <c r="Q458" s="4"/>
       <c r="R458" s="4"/>
     </row>
-    <row r="459" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A459" s="2" t="s">
         <v>1381</v>
       </c>
@@ -28711,7 +28712,7 @@
       <c r="Q459" s="4"/>
       <c r="R459" s="4"/>
     </row>
-    <row r="460" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A460" s="2" t="s">
         <v>1383</v>
       </c>
@@ -28755,7 +28756,7 @@
       <c r="Q460" s="4"/>
       <c r="R460" s="4"/>
     </row>
-    <row r="461" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A461" s="2" t="s">
         <v>1384</v>
       </c>
@@ -28799,7 +28800,7 @@
       <c r="Q461" s="4"/>
       <c r="R461" s="4"/>
     </row>
-    <row r="462" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A462" s="2" t="s">
         <v>1385</v>
       </c>
@@ -28843,7 +28844,7 @@
       <c r="Q462" s="4"/>
       <c r="R462" s="4"/>
     </row>
-    <row r="463" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A463" s="2" t="s">
         <v>1388</v>
       </c>
@@ -28887,7 +28888,7 @@
       <c r="Q463" s="4"/>
       <c r="R463" s="4"/>
     </row>
-    <row r="464" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A464" s="2" t="s">
         <v>1389</v>
       </c>
@@ -28931,7 +28932,7 @@
       <c r="Q464" s="4"/>
       <c r="R464" s="4"/>
     </row>
-    <row r="465" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A465" s="2" t="s">
         <v>1391</v>
       </c>
@@ -28975,7 +28976,7 @@
       <c r="Q465" s="4"/>
       <c r="R465" s="4"/>
     </row>
-    <row r="466" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A466" s="2" t="s">
         <v>363</v>
       </c>
@@ -29019,7 +29020,7 @@
       <c r="Q466" s="4"/>
       <c r="R466" s="4"/>
     </row>
-    <row r="467" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A467" s="2" t="s">
         <v>450</v>
       </c>
@@ -29063,7 +29064,7 @@
       <c r="Q467" s="4"/>
       <c r="R467" s="4"/>
     </row>
-    <row r="468" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A468" s="2" t="s">
         <v>367</v>
       </c>
@@ -29107,7 +29108,7 @@
       <c r="Q468" s="4"/>
       <c r="R468" s="4"/>
     </row>
-    <row r="469" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A469" s="2" t="s">
         <v>365</v>
       </c>
@@ -29151,7 +29152,7 @@
       <c r="Q469" s="4"/>
       <c r="R469" s="4"/>
     </row>
-    <row r="470" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A470" s="2" t="s">
         <v>516</v>
       </c>
@@ -29195,7 +29196,7 @@
       <c r="Q470" s="4"/>
       <c r="R470" s="4"/>
     </row>
-    <row r="471" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A471" s="2" t="s">
         <v>366</v>
       </c>
@@ -29239,7 +29240,7 @@
       <c r="Q471" s="4"/>
       <c r="R471" s="4"/>
     </row>
-    <row r="472" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A472" s="2" t="s">
         <v>359</v>
       </c>
@@ -29283,7 +29284,7 @@
       <c r="Q472" s="4"/>
       <c r="R472" s="4"/>
     </row>
-    <row r="473" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A473" s="2" t="s">
         <v>358</v>
       </c>
@@ -29327,7 +29328,7 @@
       <c r="Q473" s="4"/>
       <c r="R473" s="4"/>
     </row>
-    <row r="474" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A474" s="2" t="s">
         <v>376</v>
       </c>
@@ -29371,7 +29372,7 @@
       <c r="Q474" s="4"/>
       <c r="R474" s="4"/>
     </row>
-    <row r="475" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A475" s="2" t="s">
         <v>459</v>
       </c>
@@ -29415,7 +29416,7 @@
       <c r="Q475" s="4"/>
       <c r="R475" s="4"/>
     </row>
-    <row r="476" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A476" s="2" t="s">
         <v>380</v>
       </c>
@@ -29459,7 +29460,7 @@
       <c r="Q476" s="4"/>
       <c r="R476" s="4"/>
     </row>
-    <row r="477" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A477" s="2" t="s">
         <v>378</v>
       </c>
@@ -29503,7 +29504,7 @@
       <c r="Q477" s="4"/>
       <c r="R477" s="4"/>
     </row>
-    <row r="478" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A478" s="2" t="s">
         <v>377</v>
       </c>
@@ -29547,7 +29548,7 @@
       <c r="Q478" s="4"/>
       <c r="R478" s="4"/>
     </row>
-    <row r="479" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A479" s="2" t="s">
         <v>379</v>
       </c>
@@ -29591,7 +29592,7 @@
       <c r="Q479" s="4"/>
       <c r="R479" s="4"/>
     </row>
-    <row r="480" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A480" s="2" t="s">
         <v>400</v>
       </c>
@@ -29635,7 +29636,7 @@
       <c r="Q480" s="4"/>
       <c r="R480" s="4"/>
     </row>
-    <row r="481" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A481" s="2" t="s">
         <v>399</v>
       </c>
@@ -29679,7 +29680,7 @@
       <c r="Q481" s="4"/>
       <c r="R481" s="4"/>
     </row>
-    <row r="482" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A482" s="2" t="s">
         <v>398</v>
       </c>
@@ -29723,7 +29724,7 @@
       <c r="Q482" s="4"/>
       <c r="R482" s="4"/>
     </row>
-    <row r="483" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A483" s="2" t="s">
         <v>397</v>
       </c>
@@ -29767,7 +29768,7 @@
       <c r="Q483" s="4"/>
       <c r="R483" s="4"/>
     </row>
-    <row r="484" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A484" s="2" t="s">
         <v>468</v>
       </c>
@@ -29811,7 +29812,7 @@
       <c r="Q484" s="4"/>
       <c r="R484" s="4"/>
     </row>
-    <row r="485" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A485" s="2" t="s">
         <v>462</v>
       </c>
@@ -29855,7 +29856,7 @@
       <c r="Q485" s="4"/>
       <c r="R485" s="4"/>
     </row>
-    <row r="486" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A486" s="2" t="s">
         <v>461</v>
       </c>
@@ -29899,7 +29900,7 @@
       <c r="Q486" s="4"/>
       <c r="R486" s="4"/>
     </row>
-    <row r="487" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A487" s="2" t="s">
         <v>388</v>
       </c>
@@ -29943,7 +29944,7 @@
       <c r="Q487" s="4"/>
       <c r="R487" s="4"/>
     </row>
-    <row r="488" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A488" s="2" t="s">
         <v>386</v>
       </c>
@@ -29987,7 +29988,7 @@
       <c r="Q488" s="4"/>
       <c r="R488" s="4"/>
     </row>
-    <row r="489" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A489" s="2" t="s">
         <v>387</v>
       </c>
@@ -30031,7 +30032,7 @@
       <c r="Q489" s="4"/>
       <c r="R489" s="4"/>
     </row>
-    <row r="490" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A490" s="2" t="s">
         <v>385</v>
       </c>
@@ -30075,7 +30076,7 @@
       <c r="Q490" s="4"/>
       <c r="R490" s="4"/>
     </row>
-    <row r="491" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A491" s="2" t="s">
         <v>519</v>
       </c>
@@ -30119,7 +30120,7 @@
       <c r="Q491" s="4"/>
       <c r="R491" s="4"/>
     </row>
-    <row r="492" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A492" s="2" t="s">
         <v>521</v>
       </c>
@@ -30163,7 +30164,7 @@
       <c r="Q492" s="4"/>
       <c r="R492" s="4"/>
     </row>
-    <row r="493" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A493" s="2" t="s">
         <v>523</v>
       </c>
@@ -30207,7 +30208,7 @@
       <c r="Q493" s="4"/>
       <c r="R493" s="4"/>
     </row>
-    <row r="494" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A494" s="2" t="s">
         <v>525</v>
       </c>
@@ -30251,7 +30252,7 @@
       <c r="Q494" s="4"/>
       <c r="R494" s="4"/>
     </row>
-    <row r="495" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A495" s="2" t="s">
         <v>467</v>
       </c>
@@ -30295,7 +30296,7 @@
       <c r="Q495" s="4"/>
       <c r="R495" s="4"/>
     </row>
-    <row r="496" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A496" s="2" t="s">
         <v>392</v>
       </c>
@@ -30339,7 +30340,7 @@
       <c r="Q496" s="4"/>
       <c r="R496" s="4"/>
     </row>
-    <row r="497" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A497" s="2" t="s">
         <v>390</v>
       </c>
@@ -30383,7 +30384,7 @@
       <c r="Q497" s="4"/>
       <c r="R497" s="4"/>
     </row>
-    <row r="498" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A498" s="2" t="s">
         <v>391</v>
       </c>
@@ -30427,7 +30428,7 @@
       <c r="Q498" s="4"/>
       <c r="R498" s="4"/>
     </row>
-    <row r="499" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A499" s="2" t="s">
         <v>466</v>
       </c>
@@ -30471,7 +30472,7 @@
       <c r="Q499" s="4"/>
       <c r="R499" s="4"/>
     </row>
-    <row r="500" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A500" s="2" t="s">
         <v>526</v>
       </c>
@@ -30515,7 +30516,7 @@
       <c r="Q500" s="4"/>
       <c r="R500" s="4"/>
     </row>
-    <row r="501" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A501" s="2" t="s">
         <v>393</v>
       </c>
@@ -30559,7 +30560,7 @@
       <c r="Q501" s="4"/>
       <c r="R501" s="4"/>
     </row>
-    <row r="502" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A502" s="2" t="s">
         <v>528</v>
       </c>
@@ -30603,7 +30604,7 @@
       <c r="Q502" s="4"/>
       <c r="R502" s="4"/>
     </row>
-    <row r="503" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A503" s="2" t="s">
         <v>529</v>
       </c>
@@ -30647,7 +30648,7 @@
       <c r="Q503" s="4"/>
       <c r="R503" s="4"/>
     </row>
-    <row r="504" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A504" s="2" t="s">
         <v>530</v>
       </c>
@@ -30691,7 +30692,7 @@
       <c r="Q504" s="4"/>
       <c r="R504" s="4"/>
     </row>
-    <row r="505" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A505" s="2" t="s">
         <v>1392</v>
       </c>
@@ -30735,7 +30736,7 @@
       <c r="Q505" s="4"/>
       <c r="R505" s="4"/>
     </row>
-    <row r="506" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A506" s="2" t="s">
         <v>1394</v>
       </c>
@@ -30779,7 +30780,7 @@
       <c r="Q506" s="4"/>
       <c r="R506" s="4"/>
     </row>
-    <row r="507" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A507" s="2" t="s">
         <v>1396</v>
       </c>
@@ -30823,7 +30824,7 @@
       <c r="Q507" s="4"/>
       <c r="R507" s="4"/>
     </row>
-    <row r="508" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A508" s="2" t="s">
         <v>1398</v>
       </c>
@@ -30867,7 +30868,7 @@
       <c r="Q508" s="4"/>
       <c r="R508" s="4"/>
     </row>
-    <row r="509" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A509" s="2" t="s">
         <v>531</v>
       </c>
@@ -30911,7 +30912,7 @@
       <c r="Q509" s="4"/>
       <c r="R509" s="4"/>
     </row>
-    <row r="510" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A510" s="2" t="s">
         <v>533</v>
       </c>
@@ -30955,7 +30956,7 @@
       <c r="Q510" s="4"/>
       <c r="R510" s="4"/>
     </row>
-    <row r="511" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A511" s="2" t="s">
         <v>1400</v>
       </c>
@@ -30999,7 +31000,7 @@
       <c r="Q511" s="4"/>
       <c r="R511" s="4"/>
     </row>
-    <row r="512" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A512" s="2" t="s">
         <v>1402</v>
       </c>
@@ -31043,7 +31044,7 @@
       <c r="Q512" s="4"/>
       <c r="R512" s="4"/>
     </row>
-    <row r="513" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A513" s="2" t="s">
         <v>1403</v>
       </c>
@@ -31087,7 +31088,7 @@
       <c r="Q513" s="4"/>
       <c r="R513" s="4"/>
     </row>
-    <row r="514" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A514" s="2" t="s">
         <v>1404</v>
       </c>
@@ -31131,7 +31132,7 @@
       <c r="Q514" s="4"/>
       <c r="R514" s="4"/>
     </row>
-    <row r="515" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A515" s="2" t="s">
         <v>534</v>
       </c>
@@ -31175,7 +31176,7 @@
       <c r="Q515" s="4"/>
       <c r="R515" s="4"/>
     </row>
-    <row r="516" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A516" s="2" t="s">
         <v>536</v>
       </c>
@@ -31219,7 +31220,7 @@
       <c r="Q516" s="4"/>
       <c r="R516" s="4"/>
     </row>
-    <row r="517" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A517" s="2" t="s">
         <v>1407</v>
       </c>
@@ -31263,7 +31264,7 @@
       <c r="Q517" s="4"/>
       <c r="R517" s="4"/>
     </row>
-    <row r="518" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A518" s="2" t="s">
         <v>1409</v>
       </c>
@@ -31307,7 +31308,7 @@
       <c r="Q518" s="4"/>
       <c r="R518" s="4"/>
     </row>
-    <row r="519" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A519" s="2" t="s">
         <v>1410</v>
       </c>
@@ -31351,7 +31352,7 @@
       <c r="Q519" s="4"/>
       <c r="R519" s="4"/>
     </row>
-    <row r="520" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A520" s="2" t="s">
         <v>403</v>
       </c>
@@ -31395,7 +31396,7 @@
       <c r="Q520" s="4"/>
       <c r="R520" s="4"/>
     </row>
-    <row r="521" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A521" s="2" t="s">
         <v>225</v>
       </c>
@@ -31439,7 +31440,7 @@
       <c r="Q521" s="4"/>
       <c r="R521" s="4"/>
     </row>
-    <row r="522" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A522" s="2" t="s">
         <v>224</v>
       </c>
@@ -31483,7 +31484,7 @@
       <c r="Q522" s="4"/>
       <c r="R522" s="4"/>
     </row>
-    <row r="523" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A523" s="2" t="s">
         <v>222</v>
       </c>
@@ -31527,7 +31528,7 @@
       <c r="Q523" s="4"/>
       <c r="R523" s="4"/>
     </row>
-    <row r="524" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A524" s="2" t="s">
         <v>220</v>
       </c>
@@ -31571,7 +31572,7 @@
       <c r="Q524" s="4"/>
       <c r="R524" s="4"/>
     </row>
-    <row r="525" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A525" s="2" t="s">
         <v>223</v>
       </c>
@@ -31615,7 +31616,7 @@
       <c r="Q525" s="4"/>
       <c r="R525" s="4"/>
     </row>
-    <row r="526" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A526" s="2" t="s">
         <v>221</v>
       </c>
@@ -31659,7 +31660,7 @@
       <c r="Q526" s="4"/>
       <c r="R526" s="4"/>
     </row>
-    <row r="527" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A527" s="2" t="s">
         <v>1411</v>
       </c>
@@ -31703,7 +31704,7 @@
       <c r="Q527" s="4"/>
       <c r="R527" s="4"/>
     </row>
-    <row r="528" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A528" s="2" t="s">
         <v>1414</v>
       </c>
@@ -31747,7 +31748,7 @@
       <c r="Q528" s="4"/>
       <c r="R528" s="4"/>
     </row>
-    <row r="529" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A529" s="2" t="s">
         <v>1416</v>
       </c>
@@ -31791,7 +31792,7 @@
       <c r="Q529" s="4"/>
       <c r="R529" s="4"/>
     </row>
-    <row r="530" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A530" s="2" t="s">
         <v>1417</v>
       </c>
@@ -31835,7 +31836,7 @@
       <c r="Q530" s="4"/>
       <c r="R530" s="4"/>
     </row>
-    <row r="531" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A531" s="2" t="s">
         <v>1418</v>
       </c>
@@ -31879,7 +31880,7 @@
       <c r="Q531" s="4"/>
       <c r="R531" s="4"/>
     </row>
-    <row r="532" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A532" s="2" t="s">
         <v>1420</v>
       </c>
@@ -31923,7 +31924,7 @@
       <c r="Q532" s="4"/>
       <c r="R532" s="4"/>
     </row>
-    <row r="533" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A533" s="2" t="s">
         <v>538</v>
       </c>
@@ -31967,7 +31968,7 @@
       <c r="Q533" s="4"/>
       <c r="R533" s="4"/>
     </row>
-    <row r="534" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A534" s="2" t="s">
         <v>540</v>
       </c>
@@ -32011,7 +32012,7 @@
       <c r="Q534" s="4"/>
       <c r="R534" s="4"/>
     </row>
-    <row r="535" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A535" s="2" t="s">
         <v>542</v>
       </c>
@@ -32055,7 +32056,7 @@
       <c r="Q535" s="4"/>
       <c r="R535" s="4"/>
     </row>
-    <row r="536" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A536" s="2" t="s">
         <v>544</v>
       </c>
@@ -32099,7 +32100,7 @@
       <c r="Q536" s="4"/>
       <c r="R536" s="4"/>
     </row>
-    <row r="537" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A537" s="2" t="s">
         <v>543</v>
       </c>
@@ -32143,7 +32144,7 @@
       <c r="Q537" s="4"/>
       <c r="R537" s="4"/>
     </row>
-    <row r="538" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A538" s="2" t="s">
         <v>545</v>
       </c>
@@ -32187,7 +32188,7 @@
       <c r="Q538" s="4"/>
       <c r="R538" s="4"/>
     </row>
-    <row r="539" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A539" s="2" t="s">
         <v>546</v>
       </c>
@@ -32231,7 +32232,7 @@
       <c r="Q539" s="4"/>
       <c r="R539" s="4"/>
     </row>
-    <row r="540" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A540" s="2" t="s">
         <v>547</v>
       </c>
@@ -32275,7 +32276,7 @@
       <c r="Q540" s="4"/>
       <c r="R540" s="4"/>
     </row>
-    <row r="541" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A541" s="2" t="s">
         <v>549</v>
       </c>
@@ -32319,7 +32320,7 @@
       <c r="Q541" s="4"/>
       <c r="R541" s="4"/>
     </row>
-    <row r="542" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A542" s="2" t="s">
         <v>550</v>
       </c>
@@ -32363,7 +32364,7 @@
       <c r="Q542" s="4"/>
       <c r="R542" s="4"/>
     </row>
-    <row r="543" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A543" s="2" t="s">
         <v>551</v>
       </c>
@@ -32407,7 +32408,7 @@
       <c r="Q543" s="4"/>
       <c r="R543" s="4"/>
     </row>
-    <row r="544" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A544" s="2" t="s">
         <v>295</v>
       </c>
@@ -32451,7 +32452,7 @@
       <c r="Q544" s="4"/>
       <c r="R544" s="4"/>
     </row>
-    <row r="545" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A545" s="2" t="s">
         <v>293</v>
       </c>
@@ -32495,7 +32496,7 @@
       <c r="Q545" s="4"/>
       <c r="R545" s="4"/>
     </row>
-    <row r="546" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A546" s="2" t="s">
         <v>294</v>
       </c>
@@ -32539,7 +32540,7 @@
       <c r="Q546" s="4"/>
       <c r="R546" s="4"/>
     </row>
-    <row r="547" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A547" s="2" t="s">
         <v>291</v>
       </c>
@@ -32583,7 +32584,7 @@
       <c r="Q547" s="4"/>
       <c r="R547" s="4"/>
     </row>
-    <row r="548" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A548" s="2" t="s">
         <v>292</v>
       </c>
@@ -32803,7 +32804,7 @@
       <c r="Q552" s="4"/>
       <c r="R552" s="4"/>
     </row>
-    <row r="553" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A553" s="2" t="s">
         <v>552</v>
       </c>
@@ -32847,7 +32848,7 @@
       <c r="Q553" s="4"/>
       <c r="R553" s="4"/>
     </row>
-    <row r="554" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A554" s="2" t="s">
         <v>232</v>
       </c>
@@ -32891,7 +32892,7 @@
       <c r="Q554" s="4"/>
       <c r="R554" s="4"/>
     </row>
-    <row r="555" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A555" s="2" t="s">
         <v>231</v>
       </c>
@@ -32935,7 +32936,7 @@
       <c r="Q555" s="4"/>
       <c r="R555" s="4"/>
     </row>
-    <row r="556" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A556" s="2" t="s">
         <v>554</v>
       </c>
@@ -32979,7 +32980,7 @@
       <c r="Q556" s="4"/>
       <c r="R556" s="4"/>
     </row>
-    <row r="557" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A557" s="2" t="s">
         <v>556</v>
       </c>
@@ -33023,7 +33024,7 @@
       <c r="Q557" s="4"/>
       <c r="R557" s="4"/>
     </row>
-    <row r="558" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A558" s="2" t="s">
         <v>557</v>
       </c>
@@ -33067,7 +33068,7 @@
       <c r="Q558" s="4"/>
       <c r="R558" s="4"/>
     </row>
-    <row r="559" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A559" s="2" t="s">
         <v>1427</v>
       </c>
@@ -33111,7 +33112,7 @@
       <c r="Q559" s="4"/>
       <c r="R559" s="4"/>
     </row>
-    <row r="560" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A560" s="2" t="s">
         <v>1429</v>
       </c>
@@ -33155,7 +33156,7 @@
       <c r="Q560" s="4"/>
       <c r="R560" s="4"/>
     </row>
-    <row r="561" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A561" s="2" t="s">
         <v>1431</v>
       </c>
@@ -33199,7 +33200,7 @@
       <c r="Q561" s="4"/>
       <c r="R561" s="4"/>
     </row>
-    <row r="562" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A562" s="2" t="s">
         <v>1433</v>
       </c>
@@ -33243,7 +33244,7 @@
       <c r="Q562" s="4"/>
       <c r="R562" s="4"/>
     </row>
-    <row r="563" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A563" s="2" t="s">
         <v>1434</v>
       </c>
@@ -33287,7 +33288,7 @@
       <c r="Q563" s="4"/>
       <c r="R563" s="4"/>
     </row>
-    <row r="564" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A564" s="2" t="s">
         <v>558</v>
       </c>
@@ -33331,7 +33332,7 @@
       <c r="Q564" s="4"/>
       <c r="R564" s="4"/>
     </row>
-    <row r="565" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A565" s="2" t="s">
         <v>560</v>
       </c>
@@ -33375,7 +33376,7 @@
       <c r="Q565" s="4"/>
       <c r="R565" s="4"/>
     </row>
-    <row r="566" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A566" s="2" t="s">
         <v>561</v>
       </c>
@@ -33419,7 +33420,7 @@
       <c r="Q566" s="4"/>
       <c r="R566" s="4"/>
     </row>
-    <row r="567" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A567" s="2" t="s">
         <v>563</v>
       </c>
@@ -33463,7 +33464,7 @@
       <c r="Q567" s="4"/>
       <c r="R567" s="4"/>
     </row>
-    <row r="568" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A568" s="2" t="s">
         <v>564</v>
       </c>
@@ -33507,7 +33508,7 @@
       <c r="Q568" s="4"/>
       <c r="R568" s="4"/>
     </row>
-    <row r="569" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A569" s="2" t="s">
         <v>1435</v>
       </c>
@@ -33551,7 +33552,7 @@
       <c r="Q569" s="4"/>
       <c r="R569" s="4"/>
     </row>
-    <row r="570" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A570" s="2" t="s">
         <v>1439</v>
       </c>
@@ -33595,7 +33596,7 @@
       <c r="Q570" s="4"/>
       <c r="R570" s="4"/>
     </row>
-    <row r="571" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A571" s="2" t="s">
         <v>1440</v>
       </c>
@@ -33639,7 +33640,7 @@
       <c r="Q571" s="4"/>
       <c r="R571" s="4"/>
     </row>
-    <row r="572" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A572" s="2" t="s">
         <v>1442</v>
       </c>
@@ -33683,7 +33684,7 @@
       <c r="Q572" s="4"/>
       <c r="R572" s="4"/>
     </row>
-    <row r="573" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A573" s="2" t="s">
         <v>1445</v>
       </c>
@@ -33727,7 +33728,7 @@
       <c r="Q573" s="4"/>
       <c r="R573" s="4"/>
     </row>
-    <row r="574" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A574" s="2" t="s">
         <v>1446</v>
       </c>
@@ -33771,7 +33772,7 @@
       <c r="Q574" s="4"/>
       <c r="R574" s="4"/>
     </row>
-    <row r="575" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A575" s="2" t="s">
         <v>1447</v>
       </c>
@@ -33815,7 +33816,7 @@
       <c r="Q575" s="4"/>
       <c r="R575" s="4"/>
     </row>
-    <row r="576" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A576" s="2" t="s">
         <v>566</v>
       </c>
@@ -33859,7 +33860,7 @@
       <c r="Q576" s="4"/>
       <c r="R576" s="4"/>
     </row>
-    <row r="577" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A577" s="2" t="s">
         <v>1450</v>
       </c>
@@ -33903,7 +33904,7 @@
       <c r="Q577" s="4"/>
       <c r="R577" s="4"/>
     </row>
-    <row r="578" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A578" s="2" t="s">
         <v>1454</v>
       </c>
@@ -33947,7 +33948,7 @@
       <c r="Q578" s="4"/>
       <c r="R578" s="4"/>
     </row>
-    <row r="579" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A579" s="2" t="s">
         <v>1455</v>
       </c>
@@ -33991,7 +33992,7 @@
       <c r="Q579" s="4"/>
       <c r="R579" s="4"/>
     </row>
-    <row r="580" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A580" s="2" t="s">
         <v>1456</v>
       </c>
@@ -34035,7 +34036,7 @@
       <c r="Q580" s="4"/>
       <c r="R580" s="4"/>
     </row>
-    <row r="581" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A581" s="2" t="s">
         <v>1459</v>
       </c>
@@ -34079,7 +34080,7 @@
       <c r="Q581" s="4"/>
       <c r="R581" s="4"/>
     </row>
-    <row r="582" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A582" s="2" t="s">
         <v>1460</v>
       </c>
@@ -34123,7 +34124,7 @@
       <c r="Q582" s="4"/>
       <c r="R582" s="4"/>
     </row>
-    <row r="583" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A583" s="2" t="s">
         <v>571</v>
       </c>
@@ -34167,7 +34168,7 @@
       <c r="Q583" s="4"/>
       <c r="R583" s="4"/>
     </row>
-    <row r="584" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A584" s="2" t="s">
         <v>575</v>
       </c>
@@ -34211,7 +34212,7 @@
       <c r="Q584" s="4"/>
       <c r="R584" s="4"/>
     </row>
-    <row r="585" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A585" s="2" t="s">
         <v>1461</v>
       </c>
@@ -34255,7 +34256,7 @@
       <c r="Q585" s="4"/>
       <c r="R585" s="4"/>
     </row>
-    <row r="586" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A586" s="2" t="s">
         <v>1464</v>
       </c>
@@ -34299,7 +34300,7 @@
       <c r="Q586" s="4"/>
       <c r="R586" s="4"/>
     </row>
-    <row r="587" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A587" s="2" t="s">
         <v>1465</v>
       </c>
@@ -34343,7 +34344,7 @@
       <c r="Q587" s="4"/>
       <c r="R587" s="4"/>
     </row>
-    <row r="588" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A588" s="2" t="s">
         <v>1468</v>
       </c>
@@ -34387,7 +34388,7 @@
       <c r="Q588" s="4"/>
       <c r="R588" s="4"/>
     </row>
-    <row r="589" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A589" s="2" t="s">
         <v>1469</v>
       </c>
@@ -34431,7 +34432,7 @@
       <c r="Q589" s="4"/>
       <c r="R589" s="4"/>
     </row>
-    <row r="590" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A590" s="2" t="s">
         <v>1472</v>
       </c>
@@ -34475,7 +34476,7 @@
       <c r="Q590" s="4"/>
       <c r="R590" s="4"/>
     </row>
-    <row r="591" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A591" s="2" t="s">
         <v>577</v>
       </c>
@@ -34519,7 +34520,7 @@
       <c r="Q591" s="4"/>
       <c r="R591" s="4"/>
     </row>
-    <row r="592" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A592" s="2" t="s">
         <v>580</v>
       </c>
@@ -34563,7 +34564,7 @@
       <c r="Q592" s="4"/>
       <c r="R592" s="4"/>
     </row>
-    <row r="593" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A593" s="2" t="s">
         <v>581</v>
       </c>
@@ -34607,7 +34608,7 @@
       <c r="Q593" s="4"/>
       <c r="R593" s="4"/>
     </row>
-    <row r="594" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A594" s="2" t="s">
         <v>1473</v>
       </c>
@@ -34651,7 +34652,7 @@
       <c r="Q594" s="4"/>
       <c r="R594" s="4"/>
     </row>
-    <row r="595" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A595" s="2" t="s">
         <v>1476</v>
       </c>
@@ -34695,7 +34696,7 @@
       <c r="Q595" s="4"/>
       <c r="R595" s="4"/>
     </row>
-    <row r="596" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A596" s="2" t="s">
         <v>1479</v>
       </c>
@@ -34739,7 +34740,7 @@
       <c r="Q596" s="4"/>
       <c r="R596" s="4"/>
     </row>
-    <row r="597" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A597" s="2" t="s">
         <v>582</v>
       </c>
@@ -34783,7 +34784,7 @@
       <c r="Q597" s="4"/>
       <c r="R597" s="4"/>
     </row>
-    <row r="598" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A598" s="2" t="s">
         <v>585</v>
       </c>
@@ -34827,7 +34828,7 @@
       <c r="Q598" s="4"/>
       <c r="R598" s="4"/>
     </row>
-    <row r="599" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A599" s="2" t="s">
         <v>586</v>
       </c>
@@ -34871,7 +34872,7 @@
       <c r="Q599" s="4"/>
       <c r="R599" s="4"/>
     </row>
-    <row r="600" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A600" s="2" t="s">
         <v>589</v>
       </c>
@@ -34915,7 +34916,7 @@
       <c r="Q600" s="4"/>
       <c r="R600" s="4"/>
     </row>
-    <row r="601" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A601" s="2" t="s">
         <v>592</v>
       </c>
@@ -34959,7 +34960,7 @@
       <c r="Q601" s="4"/>
       <c r="R601" s="4"/>
     </row>
-    <row r="602" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A602" s="2" t="s">
         <v>593</v>
       </c>
@@ -35003,7 +35004,7 @@
       <c r="Q602" s="4"/>
       <c r="R602" s="4"/>
     </row>
-    <row r="603" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A603" s="2" t="s">
         <v>595</v>
       </c>
@@ -35047,7 +35048,7 @@
       <c r="Q603" s="4"/>
       <c r="R603" s="4"/>
     </row>
-    <row r="604" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A604" s="2" t="s">
         <v>596</v>
       </c>
@@ -35091,7 +35092,7 @@
       <c r="Q604" s="4"/>
       <c r="R604" s="4"/>
     </row>
-    <row r="605" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A605" s="2" t="s">
         <v>599</v>
       </c>
@@ -35135,7 +35136,7 @@
       <c r="Q605" s="4"/>
       <c r="R605" s="4"/>
     </row>
-    <row r="606" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A606" s="2" t="s">
         <v>600</v>
       </c>
@@ -35179,7 +35180,7 @@
       <c r="Q606" s="4"/>
       <c r="R606" s="4"/>
     </row>
-    <row r="607" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A607" s="2" t="s">
         <v>1480</v>
       </c>
@@ -35223,7 +35224,7 @@
       <c r="Q607" s="4"/>
       <c r="R607" s="4"/>
     </row>
-    <row r="608" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A608" s="2" t="s">
         <v>1483</v>
       </c>
@@ -35267,7 +35268,7 @@
       <c r="Q608" s="4"/>
       <c r="R608" s="4"/>
     </row>
-    <row r="609" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A609" s="2" t="s">
         <v>1484</v>
       </c>
@@ -35311,7 +35312,7 @@
       <c r="Q609" s="4"/>
       <c r="R609" s="4"/>
     </row>
-    <row r="610" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A610" s="2" t="s">
         <v>1487</v>
       </c>
@@ -35355,7 +35356,7 @@
       <c r="Q610" s="4"/>
       <c r="R610" s="4"/>
     </row>
-    <row r="611" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A611" s="2" t="s">
         <v>1488</v>
       </c>
@@ -35399,7 +35400,7 @@
       <c r="Q611" s="4"/>
       <c r="R611" s="4"/>
     </row>
-    <row r="612" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A612" s="2" t="s">
         <v>1491</v>
       </c>
@@ -35443,7 +35444,7 @@
       <c r="Q612" s="4"/>
       <c r="R612" s="4"/>
     </row>
-    <row r="613" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A613" s="2" t="s">
         <v>601</v>
       </c>
@@ -35487,7 +35488,7 @@
       <c r="Q613" s="4"/>
       <c r="R613" s="4"/>
     </row>
-    <row r="614" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A614" s="2" t="s">
         <v>605</v>
       </c>
@@ -35531,7 +35532,7 @@
       <c r="Q614" s="4"/>
       <c r="R614" s="4"/>
     </row>
-    <row r="615" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A615" s="2" t="s">
         <v>1492</v>
       </c>
@@ -35575,7 +35576,7 @@
       <c r="Q615" s="4"/>
       <c r="R615" s="4"/>
     </row>
-    <row r="616" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A616" s="2" t="s">
         <v>607</v>
       </c>
@@ -35619,7 +35620,7 @@
       <c r="Q616" s="4"/>
       <c r="R616" s="4"/>
     </row>
-    <row r="617" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A617" s="2" t="s">
         <v>608</v>
       </c>
@@ -35663,7 +35664,7 @@
       <c r="Q617" s="4"/>
       <c r="R617" s="4"/>
     </row>
-    <row r="618" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A618" s="2" t="s">
         <v>612</v>
       </c>
@@ -35707,7 +35708,7 @@
       <c r="Q618" s="4"/>
       <c r="R618" s="4"/>
     </row>
-    <row r="619" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A619" s="2" t="s">
         <v>615</v>
       </c>
@@ -35751,7 +35752,7 @@
       <c r="Q619" s="4"/>
       <c r="R619" s="4"/>
     </row>
-    <row r="620" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A620" s="2" t="s">
         <v>617</v>
       </c>
@@ -35795,7 +35796,7 @@
       <c r="Q620" s="4"/>
       <c r="R620" s="4"/>
     </row>
-    <row r="621" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A621" s="2" t="s">
         <v>619</v>
       </c>
@@ -35839,7 +35840,7 @@
       <c r="Q621" s="4"/>
       <c r="R621" s="4"/>
     </row>
-    <row r="622" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A622" s="2" t="s">
         <v>621</v>
       </c>
@@ -35883,7 +35884,7 @@
       <c r="Q622" s="4"/>
       <c r="R622" s="4"/>
     </row>
-    <row r="623" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A623" s="2" t="s">
         <v>622</v>
       </c>
@@ -35927,7 +35928,7 @@
       <c r="Q623" s="4"/>
       <c r="R623" s="4"/>
     </row>
-    <row r="624" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A624" s="2" t="s">
         <v>623</v>
       </c>
@@ -35971,7 +35972,7 @@
       <c r="Q624" s="4"/>
       <c r="R624" s="4"/>
     </row>
-    <row r="625" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A625" s="2" t="s">
         <v>626</v>
       </c>
@@ -36015,7 +36016,7 @@
       <c r="Q625" s="4"/>
       <c r="R625" s="4"/>
     </row>
-    <row r="626" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A626" s="2" t="s">
         <v>627</v>
       </c>
@@ -36059,7 +36060,7 @@
       <c r="Q626" s="4"/>
       <c r="R626" s="4"/>
     </row>
-    <row r="627" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A627" s="2" t="s">
         <v>629</v>
       </c>
@@ -36103,7 +36104,7 @@
       <c r="Q627" s="4"/>
       <c r="R627" s="4"/>
     </row>
-    <row r="628" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A628" s="2" t="s">
         <v>631</v>
       </c>
@@ -36147,7 +36148,7 @@
       <c r="Q628" s="4"/>
       <c r="R628" s="4"/>
     </row>
-    <row r="629" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A629" s="2" t="s">
         <v>632</v>
       </c>
@@ -36191,7 +36192,7 @@
       <c r="Q629" s="4"/>
       <c r="R629" s="4"/>
     </row>
-    <row r="630" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A630" s="2" t="s">
         <v>634</v>
       </c>
@@ -36235,7 +36236,7 @@
       <c r="Q630" s="4"/>
       <c r="R630" s="4"/>
     </row>
-    <row r="631" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A631" s="2" t="s">
         <v>636</v>
       </c>
@@ -36279,7 +36280,7 @@
       <c r="Q631" s="4"/>
       <c r="R631" s="4"/>
     </row>
-    <row r="632" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A632" s="2" t="s">
         <v>639</v>
       </c>
@@ -36323,7 +36324,7 @@
       <c r="Q632" s="4"/>
       <c r="R632" s="4"/>
     </row>
-    <row r="633" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A633" s="2" t="s">
         <v>641</v>
       </c>
@@ -36367,7 +36368,7 @@
       <c r="Q633" s="4"/>
       <c r="R633" s="4"/>
     </row>
-    <row r="634" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A634" s="2" t="s">
         <v>642</v>
       </c>
@@ -36411,7 +36412,7 @@
       <c r="Q634" s="4"/>
       <c r="R634" s="4"/>
     </row>
-    <row r="635" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A635" s="2" t="s">
         <v>645</v>
       </c>
@@ -36455,7 +36456,7 @@
       <c r="Q635" s="4"/>
       <c r="R635" s="4"/>
     </row>
-    <row r="636" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A636" s="2" t="s">
         <v>1493</v>
       </c>
@@ -36499,7 +36500,7 @@
       <c r="Q636" s="4"/>
       <c r="R636" s="4"/>
     </row>
-    <row r="637" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A637" s="2" t="s">
         <v>1494</v>
       </c>
@@ -36543,7 +36544,7 @@
       <c r="Q637" s="4"/>
       <c r="R637" s="4"/>
     </row>
-    <row r="638" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A638" s="2" t="s">
         <v>1495</v>
       </c>
@@ -36587,7 +36588,7 @@
       <c r="Q638" s="4"/>
       <c r="R638" s="4"/>
     </row>
-    <row r="639" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A639" s="2" t="s">
         <v>1496</v>
       </c>
@@ -36631,7 +36632,7 @@
       <c r="Q639" s="4"/>
       <c r="R639" s="4"/>
     </row>
-    <row r="640" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A640" s="2" t="s">
         <v>646</v>
       </c>
@@ -36675,7 +36676,7 @@
       <c r="Q640" s="4"/>
       <c r="R640" s="4"/>
     </row>
-    <row r="641" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A641" s="2" t="s">
         <v>649</v>
       </c>
@@ -36719,7 +36720,7 @@
       <c r="Q641" s="4"/>
       <c r="R641" s="4"/>
     </row>
-    <row r="642" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A642" s="2" t="s">
         <v>650</v>
       </c>
@@ -36763,7 +36764,7 @@
       <c r="Q642" s="4"/>
       <c r="R642" s="4"/>
     </row>
-    <row r="643" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A643" s="2" t="s">
         <v>1497</v>
       </c>
@@ -36807,7 +36808,7 @@
       <c r="Q643" s="4"/>
       <c r="R643" s="4"/>
     </row>
-    <row r="644" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A644" s="2" t="s">
         <v>652</v>
       </c>
@@ -36851,7 +36852,7 @@
       <c r="Q644" s="4"/>
       <c r="R644" s="4"/>
     </row>
-    <row r="645" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A645" s="2" t="s">
         <v>655</v>
       </c>
@@ -36895,7 +36896,7 @@
       <c r="Q645" s="4"/>
       <c r="R645" s="4"/>
     </row>
-    <row r="646" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A646" s="2" t="s">
         <v>656</v>
       </c>
@@ -36939,7 +36940,7 @@
       <c r="Q646" s="4"/>
       <c r="R646" s="4"/>
     </row>
-    <row r="647" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A647" s="2" t="s">
         <v>659</v>
       </c>
@@ -36983,7 +36984,7 @@
       <c r="Q647" s="4"/>
       <c r="R647" s="4"/>
     </row>
-    <row r="648" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A648" s="2" t="s">
         <v>660</v>
       </c>
@@ -37027,7 +37028,7 @@
       <c r="Q648" s="4"/>
       <c r="R648" s="4"/>
     </row>
-    <row r="649" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A649" s="2" t="s">
         <v>664</v>
       </c>
@@ -37071,7 +37072,7 @@
       <c r="Q649" s="4"/>
       <c r="R649" s="4"/>
     </row>
-    <row r="650" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A650" s="2" t="s">
         <v>1498</v>
       </c>
@@ -37115,7 +37116,7 @@
       <c r="Q650" s="4"/>
       <c r="R650" s="4"/>
     </row>
-    <row r="651" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A651" s="2" t="s">
         <v>667</v>
       </c>
@@ -37159,7 +37160,7 @@
       <c r="Q651" s="4"/>
       <c r="R651" s="4"/>
     </row>
-    <row r="652" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A652" s="2" t="s">
         <v>672</v>
       </c>
@@ -37203,7 +37204,7 @@
       <c r="Q652" s="4"/>
       <c r="R652" s="4"/>
     </row>
-    <row r="653" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A653" s="2" t="s">
         <v>673</v>
       </c>
@@ -37247,7 +37248,7 @@
       <c r="Q653" s="4"/>
       <c r="R653" s="4"/>
     </row>
-    <row r="654" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A654" s="2" t="s">
         <v>675</v>
       </c>
@@ -37291,7 +37292,7 @@
       <c r="Q654" s="4"/>
       <c r="R654" s="4"/>
     </row>
-    <row r="655" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A655" s="2" t="s">
         <v>677</v>
       </c>
@@ -37335,7 +37336,7 @@
       <c r="Q655" s="4"/>
       <c r="R655" s="4"/>
     </row>
-    <row r="656" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A656" s="2" t="s">
         <v>679</v>
       </c>
@@ -37379,7 +37380,7 @@
       <c r="Q656" s="4"/>
       <c r="R656" s="4"/>
     </row>
-    <row r="657" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A657" s="2" t="s">
         <v>682</v>
       </c>
@@ -37423,7 +37424,7 @@
       <c r="Q657" s="4"/>
       <c r="R657" s="4"/>
     </row>
-    <row r="658" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A658" s="2" t="s">
         <v>683</v>
       </c>
@@ -37467,7 +37468,7 @@
       <c r="Q658" s="4"/>
       <c r="R658" s="4"/>
     </row>
-    <row r="659" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A659" s="2" t="s">
         <v>684</v>
       </c>
@@ -37511,7 +37512,7 @@
       <c r="Q659" s="4"/>
       <c r="R659" s="4"/>
     </row>
-    <row r="660" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A660" s="2" t="s">
         <v>687</v>
       </c>
@@ -37555,7 +37556,7 @@
       <c r="Q660" s="4"/>
       <c r="R660" s="4"/>
     </row>
-    <row r="661" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A661" s="2" t="s">
         <v>688</v>
       </c>
@@ -37599,7 +37600,7 @@
       <c r="Q661" s="4"/>
       <c r="R661" s="4"/>
     </row>
-    <row r="662" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A662" s="2" t="s">
         <v>689</v>
       </c>
@@ -37643,7 +37644,7 @@
       <c r="Q662" s="4"/>
       <c r="R662" s="4"/>
     </row>
-    <row r="663" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A663" s="2" t="s">
         <v>692</v>
       </c>
@@ -37687,7 +37688,7 @@
       <c r="Q663" s="4"/>
       <c r="R663" s="4"/>
     </row>
-    <row r="664" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A664" s="2" t="s">
         <v>693</v>
       </c>
@@ -37731,7 +37732,7 @@
       <c r="Q664" s="4"/>
       <c r="R664" s="4"/>
     </row>
-    <row r="665" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A665" s="2" t="s">
         <v>694</v>
       </c>
@@ -37775,7 +37776,7 @@
       <c r="Q665" s="4"/>
       <c r="R665" s="4"/>
     </row>
-    <row r="666" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A666" s="2" t="s">
         <v>697</v>
       </c>
@@ -37819,7 +37820,7 @@
       <c r="Q666" s="4"/>
       <c r="R666" s="4"/>
     </row>
-    <row r="667" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="667" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A667" s="2" t="s">
         <v>698</v>
       </c>
@@ -37863,7 +37864,7 @@
       <c r="Q667" s="4"/>
       <c r="R667" s="4"/>
     </row>
-    <row r="668" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A668" s="2" t="s">
         <v>699</v>
       </c>
@@ -37907,7 +37908,7 @@
       <c r="Q668" s="4"/>
       <c r="R668" s="4"/>
     </row>
-    <row r="669" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A669" s="2" t="s">
         <v>703</v>
       </c>
@@ -37951,7 +37952,7 @@
       <c r="Q669" s="4"/>
       <c r="R669" s="4"/>
     </row>
-    <row r="670" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="670" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A670" s="2" t="s">
         <v>704</v>
       </c>
@@ -37995,7 +37996,7 @@
       <c r="Q670" s="4"/>
       <c r="R670" s="4"/>
     </row>
-    <row r="671" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A671" s="2" t="s">
         <v>705</v>
       </c>
@@ -38039,7 +38040,7 @@
       <c r="Q671" s="4"/>
       <c r="R671" s="4"/>
     </row>
-    <row r="672" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="672" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A672" s="2" t="s">
         <v>708</v>
       </c>
@@ -38083,7 +38084,7 @@
       <c r="Q672" s="4"/>
       <c r="R672" s="4"/>
     </row>
-    <row r="673" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A673" s="2" t="s">
         <v>709</v>
       </c>
@@ -38127,7 +38128,7 @@
       <c r="Q673" s="4"/>
       <c r="R673" s="4"/>
     </row>
-    <row r="674" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A674" s="2" t="s">
         <v>1499</v>
       </c>
@@ -38171,7 +38172,7 @@
       <c r="Q674" s="4"/>
       <c r="R674" s="4"/>
     </row>
-    <row r="675" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="675" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A675" s="2" t="s">
         <v>1502</v>
       </c>
@@ -38215,7 +38216,7 @@
       <c r="Q675" s="4"/>
       <c r="R675" s="4"/>
     </row>
-    <row r="676" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="676" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A676" s="2" t="s">
         <v>1503</v>
       </c>
@@ -38259,7 +38260,7 @@
       <c r="Q676" s="4"/>
       <c r="R676" s="4"/>
     </row>
-    <row r="677" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A677" s="2" t="s">
         <v>710</v>
       </c>
@@ -38303,7 +38304,7 @@
       <c r="Q677" s="4"/>
       <c r="R677" s="4"/>
     </row>
-    <row r="678" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="678" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A678" s="2" t="s">
         <v>713</v>
       </c>
@@ -38347,7 +38348,7 @@
       <c r="Q678" s="4"/>
       <c r="R678" s="4"/>
     </row>
-    <row r="679" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A679" s="2" t="s">
         <v>714</v>
       </c>
@@ -38391,7 +38392,7 @@
       <c r="Q679" s="4"/>
       <c r="R679" s="4"/>
     </row>
-    <row r="680" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="680" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A680" s="2" t="s">
         <v>715</v>
       </c>
@@ -38435,7 +38436,7 @@
       <c r="Q680" s="4"/>
       <c r="R680" s="4"/>
     </row>
-    <row r="681" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="681" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A681" s="2" t="s">
         <v>718</v>
       </c>
@@ -38479,7 +38480,7 @@
       <c r="Q681" s="4"/>
       <c r="R681" s="4"/>
     </row>
-    <row r="682" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="682" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A682" s="2" t="s">
         <v>719</v>
       </c>
@@ -38523,7 +38524,7 @@
       <c r="Q682" s="4"/>
       <c r="R682" s="4"/>
     </row>
-    <row r="683" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="683" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A683" s="2" t="s">
         <v>720</v>
       </c>
@@ -38567,7 +38568,7 @@
       <c r="Q683" s="4"/>
       <c r="R683" s="4"/>
     </row>
-    <row r="684" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="684" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A684" s="2" t="s">
         <v>721</v>
       </c>
@@ -38611,7 +38612,7 @@
       <c r="Q684" s="4"/>
       <c r="R684" s="4"/>
     </row>
-    <row r="685" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="685" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A685" s="2" t="s">
         <v>724</v>
       </c>
@@ -38655,7 +38656,7 @@
       <c r="Q685" s="4"/>
       <c r="R685" s="4"/>
     </row>
-    <row r="686" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="686" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A686" s="2" t="s">
         <v>725</v>
       </c>
@@ -38699,7 +38700,7 @@
       <c r="Q686" s="4"/>
       <c r="R686" s="4"/>
     </row>
-    <row r="687" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="687" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A687" s="2" t="s">
         <v>726</v>
       </c>
@@ -38743,7 +38744,7 @@
       <c r="Q687" s="4"/>
       <c r="R687" s="4"/>
     </row>
-    <row r="688" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="688" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A688" s="2" t="s">
         <v>727</v>
       </c>
@@ -38787,7 +38788,7 @@
       <c r="Q688" s="4"/>
       <c r="R688" s="4"/>
     </row>
-    <row r="689" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A689" s="2" t="s">
         <v>728</v>
       </c>
@@ -38831,7 +38832,7 @@
       <c r="Q689" s="4"/>
       <c r="R689" s="4"/>
     </row>
-    <row r="690" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A690" s="2" t="s">
         <v>731</v>
       </c>
@@ -38875,7 +38876,7 @@
       <c r="Q690" s="4"/>
       <c r="R690" s="4"/>
     </row>
-    <row r="691" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A691" s="2" t="s">
         <v>732</v>
       </c>
@@ -38919,7 +38920,7 @@
       <c r="Q691" s="4"/>
       <c r="R691" s="4"/>
     </row>
-    <row r="692" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="692" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A692" s="2" t="s">
         <v>733</v>
       </c>
@@ -38963,7 +38964,7 @@
       <c r="Q692" s="4"/>
       <c r="R692" s="4"/>
     </row>
-    <row r="693" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A693" s="2" t="s">
         <v>736</v>
       </c>
@@ -39007,7 +39008,7 @@
       <c r="Q693" s="4"/>
       <c r="R693" s="4"/>
     </row>
-    <row r="694" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="694" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A694" s="2" t="s">
         <v>737</v>
       </c>
@@ -39051,7 +39052,7 @@
       <c r="Q694" s="4"/>
       <c r="R694" s="4"/>
     </row>
-    <row r="695" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="695" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A695" s="2" t="s">
         <v>1504</v>
       </c>
@@ -39095,7 +39096,7 @@
       <c r="Q695" s="4"/>
       <c r="R695" s="4"/>
     </row>
-    <row r="696" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="696" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A696" s="2" t="s">
         <v>1507</v>
       </c>
@@ -39139,7 +39140,7 @@
       <c r="Q696" s="4"/>
       <c r="R696" s="4"/>
     </row>
-    <row r="697" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="697" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A697" s="2" t="s">
         <v>1508</v>
       </c>
@@ -39183,7 +39184,7 @@
       <c r="Q697" s="4"/>
       <c r="R697" s="4"/>
     </row>
-    <row r="698" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="698" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A698" s="2" t="s">
         <v>738</v>
       </c>
@@ -39227,7 +39228,7 @@
       <c r="Q698" s="4"/>
       <c r="R698" s="4"/>
     </row>
-    <row r="699" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="699" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A699" s="2" t="s">
         <v>741</v>
       </c>
@@ -39271,7 +39272,7 @@
       <c r="Q699" s="4"/>
       <c r="R699" s="4"/>
     </row>
-    <row r="700" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="700" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A700" s="2" t="s">
         <v>742</v>
       </c>
@@ -39315,7 +39316,7 @@
       <c r="Q700" s="4"/>
       <c r="R700" s="4"/>
     </row>
-    <row r="701" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="701" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A701" s="2" t="s">
         <v>743</v>
       </c>
@@ -39359,7 +39360,7 @@
       <c r="Q701" s="4"/>
       <c r="R701" s="4"/>
     </row>
-    <row r="702" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="702" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A702" s="2" t="s">
         <v>746</v>
       </c>
@@ -39403,7 +39404,7 @@
       <c r="Q702" s="4"/>
       <c r="R702" s="4"/>
     </row>
-    <row r="703" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="703" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A703" s="2" t="s">
         <v>747</v>
       </c>
@@ -39447,7 +39448,7 @@
       <c r="Q703" s="4"/>
       <c r="R703" s="4"/>
     </row>
-    <row r="704" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="704" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A704" s="2" t="s">
         <v>748</v>
       </c>
@@ -39491,7 +39492,7 @@
       <c r="Q704" s="4"/>
       <c r="R704" s="4"/>
     </row>
-    <row r="705" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="705" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A705" s="2" t="s">
         <v>751</v>
       </c>
@@ -39535,7 +39536,7 @@
       <c r="Q705" s="4"/>
       <c r="R705" s="4"/>
     </row>
-    <row r="706" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="706" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A706" s="2" t="s">
         <v>752</v>
       </c>
@@ -39579,7 +39580,7 @@
       <c r="Q706" s="4"/>
       <c r="R706" s="4"/>
     </row>
-    <row r="707" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="707" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A707" s="2" t="s">
         <v>753</v>
       </c>
@@ -39623,7 +39624,7 @@
       <c r="Q707" s="4"/>
       <c r="R707" s="4"/>
     </row>
-    <row r="708" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="708" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A708" s="2" t="s">
         <v>756</v>
       </c>
@@ -39667,7 +39668,7 @@
       <c r="Q708" s="4"/>
       <c r="R708" s="4"/>
     </row>
-    <row r="709" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="709" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A709" s="2" t="s">
         <v>757</v>
       </c>
@@ -39711,7 +39712,7 @@
       <c r="Q709" s="4"/>
       <c r="R709" s="4"/>
     </row>
-    <row r="710" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="710" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A710" s="2" t="s">
         <v>1509</v>
       </c>
@@ -39755,7 +39756,7 @@
       <c r="Q710" s="4"/>
       <c r="R710" s="4"/>
     </row>
-    <row r="711" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="711" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A711" s="2" t="s">
         <v>1512</v>
       </c>
@@ -39799,7 +39800,7 @@
       <c r="Q711" s="4"/>
       <c r="R711" s="4"/>
     </row>
-    <row r="712" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="712" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A712" s="2" t="s">
         <v>1513</v>
       </c>
@@ -39843,7 +39844,7 @@
       <c r="Q712" s="4"/>
       <c r="R712" s="4"/>
     </row>
-    <row r="713" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="713" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A713" s="2" t="s">
         <v>758</v>
       </c>
@@ -39887,7 +39888,7 @@
       <c r="Q713" s="4"/>
       <c r="R713" s="4"/>
     </row>
-    <row r="714" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="714" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A714" s="2" t="s">
         <v>761</v>
       </c>
@@ -39931,7 +39932,7 @@
       <c r="Q714" s="4"/>
       <c r="R714" s="4"/>
     </row>
-    <row r="715" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="715" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A715" s="2" t="s">
         <v>762</v>
       </c>
@@ -39975,7 +39976,7 @@
       <c r="Q715" s="4"/>
       <c r="R715" s="4"/>
     </row>
-    <row r="716" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="716" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A716" s="2" t="s">
         <v>763</v>
       </c>
@@ -40019,7 +40020,7 @@
       <c r="Q716" s="4"/>
       <c r="R716" s="4"/>
     </row>
-    <row r="717" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="717" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A717" s="2" t="s">
         <v>766</v>
       </c>
@@ -40063,7 +40064,7 @@
       <c r="Q717" s="4"/>
       <c r="R717" s="4"/>
     </row>
-    <row r="718" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="718" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A718" s="2" t="s">
         <v>767</v>
       </c>
@@ -40107,7 +40108,7 @@
       <c r="Q718" s="4"/>
       <c r="R718" s="4"/>
     </row>
-    <row r="719" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="719" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A719" s="2" t="s">
         <v>768</v>
       </c>
@@ -40151,7 +40152,7 @@
       <c r="Q719" s="4"/>
       <c r="R719" s="4"/>
     </row>
-    <row r="720" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="720" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A720" s="2" t="s">
         <v>769</v>
       </c>
@@ -40195,7 +40196,7 @@
       <c r="Q720" s="4"/>
       <c r="R720" s="4"/>
     </row>
-    <row r="721" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="721" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A721" s="2" t="s">
         <v>773</v>
       </c>
@@ -40239,7 +40240,7 @@
       <c r="Q721" s="4"/>
       <c r="R721" s="4"/>
     </row>
-    <row r="722" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="722" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A722" s="2" t="s">
         <v>774</v>
       </c>
@@ -40283,7 +40284,7 @@
       <c r="Q722" s="4"/>
       <c r="R722" s="4"/>
     </row>
-    <row r="723" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="723" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A723" s="2" t="s">
         <v>778</v>
       </c>
@@ -40327,7 +40328,7 @@
       <c r="Q723" s="4"/>
       <c r="R723" s="4"/>
     </row>
-    <row r="724" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="724" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A724" s="2" t="s">
         <v>780</v>
       </c>
@@ -40371,7 +40372,7 @@
       <c r="Q724" s="4"/>
       <c r="R724" s="4"/>
     </row>
-    <row r="725" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="725" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A725" s="2" t="s">
         <v>782</v>
       </c>
@@ -40415,7 +40416,7 @@
       <c r="Q725" s="4"/>
       <c r="R725" s="4"/>
     </row>
-    <row r="726" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="726" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A726" s="2" t="s">
         <v>786</v>
       </c>
@@ -40459,7 +40460,7 @@
       <c r="Q726" s="4"/>
       <c r="R726" s="4"/>
     </row>
-    <row r="727" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="727" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A727" s="2" t="s">
         <v>787</v>
       </c>
@@ -40503,7 +40504,7 @@
       <c r="Q727" s="4"/>
       <c r="R727" s="4"/>
     </row>
-    <row r="728" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="728" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A728" s="2" t="s">
         <v>788</v>
       </c>
@@ -40547,7 +40548,7 @@
       <c r="Q728" s="4"/>
       <c r="R728" s="4"/>
     </row>
-    <row r="729" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="729" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A729" s="2" t="s">
         <v>789</v>
       </c>
@@ -40591,7 +40592,7 @@
       <c r="Q729" s="4"/>
       <c r="R729" s="4"/>
     </row>
-    <row r="730" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="730" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A730" s="2" t="s">
         <v>792</v>
       </c>
@@ -40635,7 +40636,7 @@
       <c r="Q730" s="4"/>
       <c r="R730" s="4"/>
     </row>
-    <row r="731" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="731" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A731" s="2" t="s">
         <v>793</v>
       </c>
@@ -40679,7 +40680,7 @@
       <c r="Q731" s="4"/>
       <c r="R731" s="4"/>
     </row>
-    <row r="732" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="732" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A732" s="2" t="s">
         <v>794</v>
       </c>
@@ -40723,7 +40724,7 @@
       <c r="Q732" s="4"/>
       <c r="R732" s="4"/>
     </row>
-    <row r="733" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="733" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A733" s="2" t="s">
         <v>797</v>
       </c>
@@ -40767,7 +40768,7 @@
       <c r="Q733" s="4"/>
       <c r="R733" s="4"/>
     </row>
-    <row r="734" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="734" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A734" s="2" t="s">
         <v>798</v>
       </c>
@@ -40811,7 +40812,7 @@
       <c r="Q734" s="4"/>
       <c r="R734" s="4"/>
     </row>
-    <row r="735" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="735" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A735" s="2" t="s">
         <v>801</v>
       </c>
@@ -40855,7 +40856,7 @@
       <c r="Q735" s="4"/>
       <c r="R735" s="4"/>
     </row>
-    <row r="736" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="736" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A736" s="2" t="s">
         <v>802</v>
       </c>
@@ -40899,7 +40900,7 @@
       <c r="Q736" s="4"/>
       <c r="R736" s="4"/>
     </row>
-    <row r="737" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="737" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A737" s="2" t="s">
         <v>805</v>
       </c>
@@ -40943,7 +40944,7 @@
       <c r="Q737" s="4"/>
       <c r="R737" s="4"/>
     </row>
-    <row r="738" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="738" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A738" s="2" t="s">
         <v>806</v>
       </c>
@@ -40987,7 +40988,7 @@
       <c r="Q738" s="4"/>
       <c r="R738" s="4"/>
     </row>
-    <row r="739" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="739" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A739" s="2" t="s">
         <v>809</v>
       </c>
@@ -41031,7 +41032,7 @@
       <c r="Q739" s="4"/>
       <c r="R739" s="4"/>
     </row>
-    <row r="740" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="740" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A740" s="2" t="s">
         <v>810</v>
       </c>
@@ -41075,7 +41076,7 @@
       <c r="Q740" s="4"/>
       <c r="R740" s="4"/>
     </row>
-    <row r="741" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="741" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A741" s="2" t="s">
         <v>811</v>
       </c>
@@ -41119,7 +41120,7 @@
       <c r="Q741" s="4"/>
       <c r="R741" s="4"/>
     </row>
-    <row r="742" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="742" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A742" s="2" t="s">
         <v>813</v>
       </c>
@@ -41163,7 +41164,7 @@
       <c r="Q742" s="4"/>
       <c r="R742" s="4"/>
     </row>
-    <row r="743" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="743" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A743" s="2" t="s">
         <v>816</v>
       </c>
@@ -41207,7 +41208,7 @@
       <c r="Q743" s="4"/>
       <c r="R743" s="4"/>
     </row>
-    <row r="744" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="744" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A744" s="2" t="s">
         <v>817</v>
       </c>
@@ -41251,7 +41252,7 @@
       <c r="Q744" s="4"/>
       <c r="R744" s="4"/>
     </row>
-    <row r="745" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="745" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A745" s="2" t="s">
         <v>819</v>
       </c>
@@ -41295,7 +41296,7 @@
       <c r="Q745" s="4"/>
       <c r="R745" s="4"/>
     </row>
-    <row r="746" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="746" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A746" s="2" t="s">
         <v>820</v>
       </c>
@@ -41339,7 +41340,7 @@
       <c r="Q746" s="4"/>
       <c r="R746" s="4"/>
     </row>
-    <row r="747" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="747" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A747" s="2" t="s">
         <v>823</v>
       </c>
@@ -41383,7 +41384,7 @@
       <c r="Q747" s="4"/>
       <c r="R747" s="4"/>
     </row>
-    <row r="748" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="748" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A748" s="2" t="s">
         <v>824</v>
       </c>
@@ -41427,7 +41428,7 @@
       <c r="Q748" s="4"/>
       <c r="R748" s="4"/>
     </row>
-    <row r="749" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="749" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A749" s="2" t="s">
         <v>825</v>
       </c>
@@ -41471,7 +41472,7 @@
       <c r="Q749" s="4"/>
       <c r="R749" s="4"/>
     </row>
-    <row r="750" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="750" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A750" s="2" t="s">
         <v>828</v>
       </c>
@@ -41515,7 +41516,7 @@
       <c r="Q750" s="4"/>
       <c r="R750" s="4"/>
     </row>
-    <row r="751" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="751" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A751" s="2" t="s">
         <v>831</v>
       </c>
@@ -41559,7 +41560,7 @@
       <c r="Q751" s="4"/>
       <c r="R751" s="4"/>
     </row>
-    <row r="752" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="752" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A752" s="2" t="s">
         <v>832</v>
       </c>
@@ -41603,7 +41604,7 @@
       <c r="Q752" s="4"/>
       <c r="R752" s="4"/>
     </row>
-    <row r="753" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="753" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A753" s="2" t="s">
         <v>835</v>
       </c>
@@ -41647,7 +41648,7 @@
       <c r="Q753" s="4"/>
       <c r="R753" s="4"/>
     </row>
-    <row r="754" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="754" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A754" s="2" t="s">
         <v>837</v>
       </c>
@@ -41691,7 +41692,7 @@
       <c r="Q754" s="4"/>
       <c r="R754" s="4"/>
     </row>
-    <row r="755" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="755" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A755" s="2" t="s">
         <v>840</v>
       </c>
@@ -41735,7 +41736,7 @@
       <c r="Q755" s="4"/>
       <c r="R755" s="4"/>
     </row>
-    <row r="756" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="756" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A756" s="2" t="s">
         <v>842</v>
       </c>
@@ -41779,7 +41780,7 @@
       <c r="Q756" s="4"/>
       <c r="R756" s="4"/>
     </row>
-    <row r="757" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="757" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A757" s="2" t="s">
         <v>844</v>
       </c>
@@ -41823,7 +41824,7 @@
       <c r="Q757" s="4"/>
       <c r="R757" s="4"/>
     </row>
-    <row r="758" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="758" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A758" s="2" t="s">
         <v>1514</v>
       </c>
@@ -41867,7 +41868,7 @@
       <c r="Q758" s="4"/>
       <c r="R758" s="4"/>
     </row>
-    <row r="759" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="759" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A759" s="2" t="s">
         <v>1516</v>
       </c>
@@ -41911,7 +41912,7 @@
       <c r="Q759" s="4"/>
       <c r="R759" s="4"/>
     </row>
-    <row r="760" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="760" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A760" s="2" t="s">
         <v>846</v>
       </c>
@@ -41955,7 +41956,7 @@
       <c r="Q760" s="4"/>
       <c r="R760" s="4"/>
     </row>
-    <row r="761" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="761" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A761" s="2" t="s">
         <v>850</v>
       </c>
@@ -41999,7 +42000,7 @@
       <c r="Q761" s="4"/>
       <c r="R761" s="4"/>
     </row>
-    <row r="762" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="762" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A762" s="2" t="s">
         <v>852</v>
       </c>
@@ -42043,7 +42044,7 @@
       <c r="Q762" s="4"/>
       <c r="R762" s="4"/>
     </row>
-    <row r="763" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="763" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A763" s="2" t="s">
         <v>854</v>
       </c>
@@ -42087,7 +42088,7 @@
       <c r="Q763" s="4"/>
       <c r="R763" s="4"/>
     </row>
-    <row r="764" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="764" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A764" s="2" t="s">
         <v>856</v>
       </c>
@@ -42131,7 +42132,7 @@
       <c r="Q764" s="4"/>
       <c r="R764" s="4"/>
     </row>
-    <row r="765" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="765" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A765" s="2" t="s">
         <v>1518</v>
       </c>
@@ -42175,7 +42176,7 @@
       <c r="Q765" s="4"/>
       <c r="R765" s="4"/>
     </row>
-    <row r="766" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="766" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A766" s="2" t="s">
         <v>1519</v>
       </c>
@@ -42219,7 +42220,7 @@
       <c r="Q766" s="4"/>
       <c r="R766" s="4"/>
     </row>
-    <row r="767" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="767" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A767" s="2" t="s">
         <v>858</v>
       </c>
@@ -42263,7 +42264,7 @@
       <c r="Q767" s="4"/>
       <c r="R767" s="4"/>
     </row>
-    <row r="768" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="768" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A768" s="2" t="s">
         <v>861</v>
       </c>
@@ -42307,7 +42308,7 @@
       <c r="Q768" s="4"/>
       <c r="R768" s="4"/>
     </row>
-    <row r="769" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="769" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A769" s="2" t="s">
         <v>862</v>
       </c>
@@ -42351,7 +42352,7 @@
       <c r="Q769" s="4"/>
       <c r="R769" s="4"/>
     </row>
-    <row r="770" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="770" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A770" s="2" t="s">
         <v>863</v>
       </c>
@@ -42395,7 +42396,7 @@
       <c r="Q770" s="4"/>
       <c r="R770" s="4"/>
     </row>
-    <row r="771" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="771" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A771" s="2" t="s">
         <v>864</v>
       </c>
@@ -42439,7 +42440,7 @@
       <c r="Q771" s="4"/>
       <c r="R771" s="4"/>
     </row>
-    <row r="772" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="772" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A772" s="2" t="s">
         <v>865</v>
       </c>
@@ -42483,7 +42484,7 @@
       <c r="Q772" s="4"/>
       <c r="R772" s="4"/>
     </row>
-    <row r="773" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="773" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A773" s="2" t="s">
         <v>868</v>
       </c>
@@ -42527,7 +42528,7 @@
       <c r="Q773" s="4"/>
       <c r="R773" s="4"/>
     </row>
-    <row r="774" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="774" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A774" s="2" t="s">
         <v>872</v>
       </c>
@@ -42571,7 +42572,7 @@
       <c r="Q774" s="4"/>
       <c r="R774" s="4"/>
     </row>
-    <row r="775" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="775" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A775" s="2" t="s">
         <v>873</v>
       </c>
@@ -42615,7 +42616,7 @@
       <c r="Q775" s="4"/>
       <c r="R775" s="4"/>
     </row>
-    <row r="776" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="776" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A776" s="2" t="s">
         <v>876</v>
       </c>
@@ -42659,7 +42660,7 @@
       <c r="Q776" s="4"/>
       <c r="R776" s="4"/>
     </row>
-    <row r="777" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="777" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A777" s="2" t="s">
         <v>877</v>
       </c>
@@ -42703,7 +42704,7 @@
       <c r="Q777" s="4"/>
       <c r="R777" s="4"/>
     </row>
-    <row r="778" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="778" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A778" s="2" t="s">
         <v>1520</v>
       </c>
@@ -42747,7 +42748,7 @@
       <c r="Q778" s="4"/>
       <c r="R778" s="4"/>
     </row>
-    <row r="779" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="779" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A779" s="2" t="s">
         <v>880</v>
       </c>
@@ -42791,7 +42792,7 @@
       <c r="Q779" s="4"/>
       <c r="R779" s="4"/>
     </row>
-    <row r="780" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="780" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A780" s="2" t="s">
         <v>1521</v>
       </c>
@@ -42835,7 +42836,7 @@
       <c r="Q780" s="4"/>
       <c r="R780" s="4"/>
     </row>
-    <row r="781" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="781" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A781" s="2" t="s">
         <v>1522</v>
       </c>
@@ -42879,7 +42880,7 @@
       <c r="Q781" s="4"/>
       <c r="R781" s="4"/>
     </row>
-    <row r="782" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="782" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A782" s="2" t="s">
         <v>883</v>
       </c>
@@ -42923,7 +42924,7 @@
       <c r="Q782" s="4"/>
       <c r="R782" s="4"/>
     </row>
-    <row r="783" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="783" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A783" s="2" t="s">
         <v>885</v>
       </c>
@@ -42967,7 +42968,7 @@
       <c r="Q783" s="4"/>
       <c r="R783" s="4"/>
     </row>
-    <row r="784" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="784" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A784" s="2" t="s">
         <v>888</v>
       </c>
@@ -43011,7 +43012,7 @@
       <c r="Q784" s="4"/>
       <c r="R784" s="4"/>
     </row>
-    <row r="785" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="785" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A785" s="2" t="s">
         <v>891</v>
       </c>
@@ -43055,7 +43056,7 @@
       <c r="Q785" s="4"/>
       <c r="R785" s="4"/>
     </row>
-    <row r="786" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="786" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A786" s="2" t="s">
         <v>894</v>
       </c>
@@ -43099,7 +43100,7 @@
       <c r="Q786" s="4"/>
       <c r="R786" s="4"/>
     </row>
-    <row r="787" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="787" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A787" s="2" t="s">
         <v>895</v>
       </c>
@@ -43143,7 +43144,7 @@
       <c r="Q787" s="4"/>
       <c r="R787" s="4"/>
     </row>
-    <row r="788" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="788" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A788" s="2" t="s">
         <v>1523</v>
       </c>
@@ -43187,7 +43188,7 @@
       <c r="Q788" s="4"/>
       <c r="R788" s="4"/>
     </row>
-    <row r="789" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="789" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A789" s="2" t="s">
         <v>896</v>
       </c>
@@ -43231,7 +43232,7 @@
       <c r="Q789" s="4"/>
       <c r="R789" s="4"/>
     </row>
-    <row r="790" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="790" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A790" s="2" t="s">
         <v>899</v>
       </c>
@@ -43275,7 +43276,7 @@
       <c r="Q790" s="4"/>
       <c r="R790" s="4"/>
     </row>
-    <row r="791" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="791" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A791" s="2" t="s">
         <v>900</v>
       </c>
@@ -43319,7 +43320,7 @@
       <c r="Q791" s="4"/>
       <c r="R791" s="4"/>
     </row>
-    <row r="792" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="792" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A792" s="2" t="s">
         <v>901</v>
       </c>
@@ -43363,7 +43364,7 @@
       <c r="Q792" s="4"/>
       <c r="R792" s="4"/>
     </row>
-    <row r="793" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="793" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A793" s="2" t="s">
         <v>902</v>
       </c>
@@ -43407,7 +43408,7 @@
       <c r="Q793" s="4"/>
       <c r="R793" s="4"/>
     </row>
-    <row r="794" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="794" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A794" s="2" t="s">
         <v>903</v>
       </c>
@@ -43451,7 +43452,7 @@
       <c r="Q794" s="4"/>
       <c r="R794" s="4"/>
     </row>
-    <row r="795" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="795" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A795" s="2" t="s">
         <v>906</v>
       </c>
@@ -43495,7 +43496,7 @@
       <c r="Q795" s="4"/>
       <c r="R795" s="4"/>
     </row>
-    <row r="796" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="796" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A796" s="2" t="s">
         <v>907</v>
       </c>
@@ -43539,7 +43540,7 @@
       <c r="Q796" s="4"/>
       <c r="R796" s="4"/>
     </row>
-    <row r="797" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="797" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A797" s="2" t="s">
         <v>909</v>
       </c>
@@ -43583,7 +43584,7 @@
       <c r="Q797" s="4"/>
       <c r="R797" s="4"/>
     </row>
-    <row r="798" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="798" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A798" s="2" t="s">
         <v>910</v>
       </c>
@@ -43627,7 +43628,7 @@
       <c r="Q798" s="4"/>
       <c r="R798" s="4"/>
     </row>
-    <row r="799" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="799" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A799" s="2" t="s">
         <v>1524</v>
       </c>
@@ -43671,7 +43672,7 @@
       <c r="Q799" s="4"/>
       <c r="R799" s="4"/>
     </row>
-    <row r="800" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="800" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A800" s="2" t="s">
         <v>1528</v>
       </c>
@@ -43715,7 +43716,7 @@
       <c r="Q800" s="4"/>
       <c r="R800" s="4"/>
     </row>
-    <row r="801" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="801" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A801" s="2" t="s">
         <v>1531</v>
       </c>
@@ -43759,7 +43760,7 @@
       <c r="Q801" s="4"/>
       <c r="R801" s="4"/>
     </row>
-    <row r="802" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="802" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A802" s="2" t="s">
         <v>911</v>
       </c>
@@ -43803,7 +43804,7 @@
       <c r="Q802" s="4"/>
       <c r="R802" s="4"/>
     </row>
-    <row r="803" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="803" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A803" s="2" t="s">
         <v>914</v>
       </c>
@@ -43847,7 +43848,7 @@
       <c r="Q803" s="4"/>
       <c r="R803" s="4"/>
     </row>
-    <row r="804" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="804" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A804" s="2" t="s">
         <v>916</v>
       </c>
@@ -43891,7 +43892,7 @@
       <c r="Q804" s="4"/>
       <c r="R804" s="4"/>
     </row>
-    <row r="805" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="805" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A805" s="2" t="s">
         <v>1534</v>
       </c>
@@ -43935,7 +43936,7 @@
       <c r="Q805" s="4"/>
       <c r="R805" s="4"/>
     </row>
-    <row r="806" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="806" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A806" s="2" t="s">
         <v>1537</v>
       </c>
@@ -43979,7 +43980,7 @@
       <c r="Q806" s="4"/>
       <c r="R806" s="4"/>
     </row>
-    <row r="807" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="807" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A807" s="2" t="s">
         <v>1538</v>
       </c>
@@ -44023,7 +44024,7 @@
       <c r="Q807" s="4"/>
       <c r="R807" s="4"/>
     </row>
-    <row r="808" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="808" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A808" s="2" t="s">
         <v>918</v>
       </c>
@@ -44067,7 +44068,7 @@
       <c r="Q808" s="4"/>
       <c r="R808" s="4"/>
     </row>
-    <row r="809" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="809" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A809" s="2" t="s">
         <v>921</v>
       </c>
@@ -44111,7 +44112,7 @@
       <c r="Q809" s="4"/>
       <c r="R809" s="4"/>
     </row>
-    <row r="810" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="810" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A810" s="2" t="s">
         <v>924</v>
       </c>
@@ -44155,7 +44156,7 @@
       <c r="Q810" s="4"/>
       <c r="R810" s="4"/>
     </row>
-    <row r="811" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="811" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A811" s="2" t="s">
         <v>927</v>
       </c>
@@ -44199,7 +44200,7 @@
       <c r="Q811" s="4"/>
       <c r="R811" s="4"/>
     </row>
-    <row r="812" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="812" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A812" s="2" t="s">
         <v>928</v>
       </c>
@@ -44243,7 +44244,7 @@
       <c r="Q812" s="4"/>
       <c r="R812" s="4"/>
     </row>
-    <row r="813" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="813" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A813" s="2" t="s">
         <v>931</v>
       </c>
@@ -44287,7 +44288,7 @@
       <c r="Q813" s="4"/>
       <c r="R813" s="4"/>
     </row>
-    <row r="814" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="814" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A814" s="2" t="s">
         <v>932</v>
       </c>
@@ -44331,7 +44332,7 @@
       <c r="Q814" s="4"/>
       <c r="R814" s="4"/>
     </row>
-    <row r="815" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="815" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A815" s="2" t="s">
         <v>933</v>
       </c>
@@ -44375,7 +44376,7 @@
       <c r="Q815" s="4"/>
       <c r="R815" s="4"/>
     </row>
-    <row r="816" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="816" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A816" s="2" t="s">
         <v>934</v>
       </c>
@@ -44419,7 +44420,7 @@
       <c r="Q816" s="4"/>
       <c r="R816" s="4"/>
     </row>
-    <row r="817" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="817" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A817" s="2" t="s">
         <v>937</v>
       </c>
@@ -44463,7 +44464,7 @@
       <c r="Q817" s="4"/>
       <c r="R817" s="4"/>
     </row>
-    <row r="818" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="818" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A818" s="2" t="s">
         <v>938</v>
       </c>
@@ -44507,7 +44508,7 @@
       <c r="Q818" s="4"/>
       <c r="R818" s="4"/>
     </row>
-    <row r="819" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="819" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A819" s="2" t="s">
         <v>939</v>
       </c>
@@ -44551,7 +44552,7 @@
       <c r="Q819" s="4"/>
       <c r="R819" s="4"/>
     </row>
-    <row r="820" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="820" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A820" s="2" t="s">
         <v>940</v>
       </c>
@@ -44595,7 +44596,7 @@
       <c r="Q820" s="4"/>
       <c r="R820" s="4"/>
     </row>
-    <row r="821" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="821" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A821" s="2" t="s">
         <v>943</v>
       </c>
@@ -44639,7 +44640,7 @@
       <c r="Q821" s="4"/>
       <c r="R821" s="4"/>
     </row>
-    <row r="822" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="822" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A822" s="2" t="s">
         <v>946</v>
       </c>
@@ -44683,7 +44684,7 @@
       <c r="Q822" s="4"/>
       <c r="R822" s="4"/>
     </row>
-    <row r="823" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="823" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A823" s="2" t="s">
         <v>947</v>
       </c>
@@ -44727,7 +44728,7 @@
       <c r="Q823" s="4"/>
       <c r="R823" s="4"/>
     </row>
-    <row r="824" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="824" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A824" s="2" t="s">
         <v>948</v>
       </c>
@@ -44771,7 +44772,7 @@
       <c r="Q824" s="4"/>
       <c r="R824" s="4"/>
     </row>
-    <row r="825" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="825" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A825" s="2" t="s">
         <v>949</v>
       </c>
@@ -44815,7 +44816,7 @@
       <c r="Q825" s="4"/>
       <c r="R825" s="4"/>
     </row>
-    <row r="826" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="826" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A826" s="2" t="s">
         <v>950</v>
       </c>
@@ -44859,7 +44860,7 @@
       <c r="Q826" s="4"/>
       <c r="R826" s="4"/>
     </row>
-    <row r="827" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="827" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A827" s="2" t="s">
         <v>953</v>
       </c>
@@ -44903,7 +44904,7 @@
       <c r="Q827" s="4"/>
       <c r="R827" s="4"/>
     </row>
-    <row r="828" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="828" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A828" s="2" t="s">
         <v>954</v>
       </c>
@@ -44947,7 +44948,7 @@
       <c r="Q828" s="4"/>
       <c r="R828" s="4"/>
     </row>
-    <row r="829" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="829" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A829" s="2" t="s">
         <v>957</v>
       </c>
@@ -44991,7 +44992,7 @@
       <c r="Q829" s="4"/>
       <c r="R829" s="4"/>
     </row>
-    <row r="830" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="830" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A830" s="2" t="s">
         <v>958</v>
       </c>
@@ -45035,7 +45036,7 @@
       <c r="Q830" s="4"/>
       <c r="R830" s="4"/>
     </row>
-    <row r="831" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="831" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A831" s="2" t="s">
         <v>960</v>
       </c>
@@ -45079,7 +45080,7 @@
       <c r="Q831" s="4"/>
       <c r="R831" s="4"/>
     </row>
-    <row r="832" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="832" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A832" s="2" t="s">
         <v>965</v>
       </c>
@@ -45123,7 +45124,7 @@
       <c r="Q832" s="4"/>
       <c r="R832" s="4"/>
     </row>
-    <row r="833" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="833" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A833" s="2" t="s">
         <v>1541</v>
       </c>
@@ -45167,7 +45168,7 @@
       <c r="Q833" s="4"/>
       <c r="R833" s="4"/>
     </row>
-    <row r="834" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="834" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A834" s="2" t="s">
         <v>1542</v>
       </c>
@@ -45211,7 +45212,7 @@
       <c r="Q834" s="4"/>
       <c r="R834" s="4"/>
     </row>
-    <row r="835" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="835" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A835" s="2" t="s">
         <v>1544</v>
       </c>
@@ -45255,7 +45256,7 @@
       <c r="Q835" s="4"/>
       <c r="R835" s="4"/>
     </row>
-    <row r="836" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="836" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A836" s="2" t="s">
         <v>967</v>
       </c>
@@ -45299,7 +45300,7 @@
       <c r="Q836" s="4"/>
       <c r="R836" s="4"/>
     </row>
-    <row r="837" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="837" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A837" s="2" t="s">
         <v>971</v>
       </c>
@@ -45343,7 +45344,7 @@
       <c r="Q837" s="4"/>
       <c r="R837" s="4"/>
     </row>
-    <row r="838" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="838" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A838" s="2" t="s">
         <v>972</v>
       </c>
@@ -45387,7 +45388,7 @@
       <c r="Q838" s="4"/>
       <c r="R838" s="4"/>
     </row>
-    <row r="839" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="839" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A839" s="2" t="s">
         <v>1545</v>
       </c>
@@ -45431,7 +45432,7 @@
       <c r="Q839" s="4"/>
       <c r="R839" s="4"/>
     </row>
-    <row r="840" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="840" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A840" s="2" t="s">
         <v>1547</v>
       </c>
@@ -45475,7 +45476,7 @@
       <c r="Q840" s="4"/>
       <c r="R840" s="4"/>
     </row>
-    <row r="841" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="841" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A841" s="2" t="s">
         <v>974</v>
       </c>
@@ -45519,7 +45520,7 @@
       <c r="Q841" s="4"/>
       <c r="R841" s="4"/>
     </row>
-    <row r="842" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="842" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A842" s="2" t="s">
         <v>977</v>
       </c>
@@ -45563,7 +45564,7 @@
       <c r="Q842" s="4"/>
       <c r="R842" s="4"/>
     </row>
-    <row r="843" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="843" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A843" s="2" t="s">
         <v>978</v>
       </c>
@@ -45607,7 +45608,7 @@
       <c r="Q843" s="4"/>
       <c r="R843" s="4"/>
     </row>
-    <row r="844" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="844" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A844" s="2" t="s">
         <v>979</v>
       </c>
@@ -45651,7 +45652,7 @@
       <c r="Q844" s="4"/>
       <c r="R844" s="4"/>
     </row>
-    <row r="845" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="845" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A845" s="2" t="s">
         <v>1549</v>
       </c>
@@ -45695,7 +45696,7 @@
       <c r="Q845" s="4"/>
       <c r="R845" s="4"/>
     </row>
-    <row r="846" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="846" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A846" s="2" t="s">
         <v>1553</v>
       </c>
@@ -45739,7 +45740,7 @@
       <c r="Q846" s="4"/>
       <c r="R846" s="4"/>
     </row>
-    <row r="847" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="847" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A847" s="2" t="s">
         <v>1555</v>
       </c>
@@ -45783,7 +45784,7 @@
       <c r="Q847" s="4"/>
       <c r="R847" s="4"/>
     </row>
-    <row r="848" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="848" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A848" s="2" t="s">
         <v>1557</v>
       </c>
@@ -45827,7 +45828,7 @@
       <c r="Q848" s="4"/>
       <c r="R848" s="4"/>
     </row>
-    <row r="849" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="849" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A849" s="2" t="s">
         <v>1559</v>
       </c>
@@ -45871,7 +45872,7 @@
       <c r="Q849" s="4"/>
       <c r="R849" s="4"/>
     </row>
-    <row r="850" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="850" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A850" s="2" t="s">
         <v>1560</v>
       </c>
@@ -45915,7 +45916,7 @@
       <c r="Q850" s="4"/>
       <c r="R850" s="4"/>
     </row>
-    <row r="851" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="851" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A851" s="2" t="s">
         <v>981</v>
       </c>
@@ -45959,7 +45960,7 @@
       <c r="Q851" s="4"/>
       <c r="R851" s="4"/>
     </row>
-    <row r="852" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="852" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A852" s="2" t="s">
         <v>985</v>
       </c>
@@ -46003,7 +46004,7 @@
       <c r="Q852" s="4"/>
       <c r="R852" s="4"/>
     </row>
-    <row r="853" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="853" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A853" s="2" t="s">
         <v>987</v>
       </c>
@@ -46047,7 +46048,7 @@
       <c r="Q853" s="4"/>
       <c r="R853" s="4"/>
     </row>
-    <row r="854" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="854" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A854" s="2" t="s">
         <v>989</v>
       </c>
@@ -46091,7 +46092,7 @@
       <c r="Q854" s="4"/>
       <c r="R854" s="4"/>
     </row>
-    <row r="855" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="855" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A855" s="2" t="s">
         <v>1562</v>
       </c>
@@ -46135,7 +46136,7 @@
       <c r="Q855" s="4"/>
       <c r="R855" s="4"/>
     </row>
-    <row r="856" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="856" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A856" s="2" t="s">
         <v>1564</v>
       </c>
@@ -46179,7 +46180,7 @@
       <c r="Q856" s="4"/>
       <c r="R856" s="4"/>
     </row>
-    <row r="857" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="857" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A857" s="2" t="s">
         <v>1565</v>
       </c>
@@ -46223,7 +46224,7 @@
       <c r="Q857" s="4"/>
       <c r="R857" s="4"/>
     </row>
-    <row r="858" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="858" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A858" s="2" t="s">
         <v>990</v>
       </c>
@@ -46267,7 +46268,7 @@
       <c r="Q858" s="4"/>
       <c r="R858" s="4"/>
     </row>
-    <row r="859" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="859" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A859" s="2" t="s">
         <v>992</v>
       </c>
@@ -46311,7 +46312,7 @@
       <c r="Q859" s="4"/>
       <c r="R859" s="4"/>
     </row>
-    <row r="860" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="860" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A860" s="2" t="s">
         <v>993</v>
       </c>
@@ -46355,7 +46356,7 @@
       <c r="Q860" s="4"/>
       <c r="R860" s="4"/>
     </row>
-    <row r="861" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="861" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A861" s="2" t="s">
         <v>1566</v>
       </c>
@@ -46399,7 +46400,7 @@
       <c r="Q861" s="4"/>
       <c r="R861" s="4"/>
     </row>
-    <row r="862" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="862" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A862" s="2" t="s">
         <v>1567</v>
       </c>
@@ -46443,7 +46444,7 @@
       <c r="Q862" s="4"/>
       <c r="R862" s="4"/>
     </row>
-    <row r="863" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="863" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A863" s="2" t="s">
         <v>994</v>
       </c>
@@ -46487,7 +46488,7 @@
       <c r="Q863" s="4"/>
       <c r="R863" s="4"/>
     </row>
-    <row r="864" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="864" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A864" s="2" t="s">
         <v>996</v>
       </c>
@@ -46531,7 +46532,7 @@
       <c r="Q864" s="4"/>
       <c r="R864" s="4"/>
     </row>
-    <row r="865" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="865" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A865" s="2" t="s">
         <v>997</v>
       </c>
@@ -46575,7 +46576,7 @@
       <c r="Q865" s="4"/>
       <c r="R865" s="4"/>
     </row>
-    <row r="866" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="866" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A866" s="2" t="s">
         <v>1568</v>
       </c>
@@ -46619,7 +46620,7 @@
       <c r="Q866" s="4"/>
       <c r="R866" s="4"/>
     </row>
-    <row r="867" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="867" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A867" s="2" t="s">
         <v>1569</v>
       </c>
@@ -46663,7 +46664,7 @@
       <c r="Q867" s="4"/>
       <c r="R867" s="4"/>
     </row>
-    <row r="868" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="868" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A868" s="2" t="s">
         <v>1571</v>
       </c>
@@ -46707,7 +46708,7 @@
       <c r="Q868" s="4"/>
       <c r="R868" s="4"/>
     </row>
-    <row r="869" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="869" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A869" s="2" t="s">
         <v>1572</v>
       </c>
@@ -46751,7 +46752,7 @@
       <c r="Q869" s="4"/>
       <c r="R869" s="4"/>
     </row>
-    <row r="870" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="870" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A870" s="2" t="s">
         <v>1573</v>
       </c>
@@ -46795,7 +46796,7 @@
       <c r="Q870" s="4"/>
       <c r="R870" s="4"/>
     </row>
-    <row r="871" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="871" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A871" s="2" t="s">
         <v>998</v>
       </c>
@@ -46839,7 +46840,7 @@
       <c r="Q871" s="4"/>
       <c r="R871" s="4"/>
     </row>
-    <row r="872" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="872" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A872" s="2" t="s">
         <v>1001</v>
       </c>
@@ -46883,7 +46884,7 @@
       <c r="Q872" s="4"/>
       <c r="R872" s="4"/>
     </row>
-    <row r="873" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="873" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A873" s="2" t="s">
         <v>1003</v>
       </c>
@@ -46927,7 +46928,7 @@
       <c r="Q873" s="4"/>
       <c r="R873" s="4"/>
     </row>
-    <row r="874" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="874" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A874" s="2" t="s">
         <v>1005</v>
       </c>
@@ -46971,7 +46972,7 @@
       <c r="Q874" s="4"/>
       <c r="R874" s="4"/>
     </row>
-    <row r="875" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="875" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A875" s="2" t="s">
         <v>1006</v>
       </c>
@@ -47015,7 +47016,7 @@
       <c r="Q875" s="4"/>
       <c r="R875" s="4"/>
     </row>
-    <row r="876" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="876" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A876" s="2" t="s">
         <v>1575</v>
       </c>
@@ -47059,7 +47060,7 @@
       <c r="Q876" s="4"/>
       <c r="R876" s="4"/>
     </row>
-    <row r="877" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="877" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A877" s="2" t="s">
         <v>1009</v>
       </c>
@@ -47103,7 +47104,7 @@
       <c r="Q877" s="4"/>
       <c r="R877" s="4"/>
     </row>
-    <row r="878" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="878" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A878" s="2" t="s">
         <v>1012</v>
       </c>
@@ -47147,7 +47148,7 @@
       <c r="Q878" s="4"/>
       <c r="R878" s="4"/>
     </row>
-    <row r="879" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="879" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A879" s="2" t="s">
         <v>1013</v>
       </c>
@@ -47191,7 +47192,7 @@
       <c r="Q879" s="4"/>
       <c r="R879" s="4"/>
     </row>
-    <row r="880" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="880" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A880" s="2" t="s">
         <v>1016</v>
       </c>
@@ -47235,7 +47236,7 @@
       <c r="Q880" s="4"/>
       <c r="R880" s="4"/>
     </row>
-    <row r="881" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="881" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A881" s="2" t="s">
         <v>1020</v>
       </c>
@@ -47279,7 +47280,7 @@
       <c r="Q881" s="4"/>
       <c r="R881" s="4"/>
     </row>
-    <row r="882" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="882" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A882" s="2" t="s">
         <v>1578</v>
       </c>
@@ -47323,7 +47324,7 @@
       <c r="Q882" s="4"/>
       <c r="R882" s="4"/>
     </row>
-    <row r="883" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="883" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A883" s="2" t="s">
         <v>1021</v>
       </c>
@@ -47367,7 +47368,7 @@
       <c r="Q883" s="4"/>
       <c r="R883" s="4"/>
     </row>
-    <row r="884" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="884" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A884" s="2" t="s">
         <v>1022</v>
       </c>
@@ -47411,7 +47412,7 @@
       <c r="Q884" s="4"/>
       <c r="R884" s="4"/>
     </row>
-    <row r="885" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="885" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A885" s="2" t="s">
         <v>1024</v>
       </c>
@@ -47455,7 +47456,7 @@
       <c r="Q885" s="4"/>
       <c r="R885" s="4"/>
     </row>
-    <row r="886" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="886" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A886" s="2" t="s">
         <v>1027</v>
       </c>
@@ -47499,7 +47500,7 @@
       <c r="Q886" s="4"/>
       <c r="R886" s="4"/>
     </row>
-    <row r="887" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="887" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A887" s="2" t="s">
         <v>1028</v>
       </c>
@@ -47543,7 +47544,7 @@
       <c r="Q887" s="4"/>
       <c r="R887" s="4"/>
     </row>
-    <row r="888" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="888" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A888" s="2" t="s">
         <v>1579</v>
       </c>
@@ -47587,7 +47588,7 @@
       <c r="Q888" s="4"/>
       <c r="R888" s="4"/>
     </row>
-    <row r="889" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="889" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A889" s="2" t="s">
         <v>1029</v>
       </c>
@@ -47631,7 +47632,7 @@
       <c r="Q889" s="4"/>
       <c r="R889" s="4"/>
     </row>
-    <row r="890" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="890" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A890" s="2" t="s">
         <v>1031</v>
       </c>
@@ -47675,7 +47676,7 @@
       <c r="Q890" s="4"/>
       <c r="R890" s="4"/>
     </row>
-    <row r="891" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="891" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A891" s="2" t="s">
         <v>1032</v>
       </c>
@@ -47719,7 +47720,7 @@
       <c r="Q891" s="4"/>
       <c r="R891" s="4"/>
     </row>
-    <row r="892" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="892" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A892" s="2" t="s">
         <v>1033</v>
       </c>
@@ -47763,7 +47764,7 @@
       <c r="Q892" s="4"/>
       <c r="R892" s="4"/>
     </row>
-    <row r="893" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="893" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A893" s="2" t="s">
         <v>1034</v>
       </c>
@@ -47807,7 +47808,7 @@
       <c r="Q893" s="4"/>
       <c r="R893" s="4"/>
     </row>
-    <row r="894" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="894" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A894" s="2" t="s">
         <v>1035</v>
       </c>
@@ -47851,7 +47852,7 @@
       <c r="Q894" s="4"/>
       <c r="R894" s="4"/>
     </row>
-    <row r="895" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="895" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A895" s="2" t="s">
         <v>1038</v>
       </c>
@@ -47895,7 +47896,7 @@
       <c r="Q895" s="4"/>
       <c r="R895" s="4"/>
     </row>
-    <row r="896" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="896" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A896" s="2" t="s">
         <v>1039</v>
       </c>
@@ -47939,7 +47940,7 @@
       <c r="Q896" s="4"/>
       <c r="R896" s="4"/>
     </row>
-    <row r="897" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="897" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A897" s="2" t="s">
         <v>1581</v>
       </c>
@@ -47983,7 +47984,7 @@
       <c r="Q897" s="4"/>
       <c r="R897" s="4"/>
     </row>
-    <row r="898" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="898" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A898" s="2" t="s">
         <v>1583</v>
       </c>
@@ -48027,7 +48028,7 @@
       <c r="Q898" s="4"/>
       <c r="R898" s="4"/>
     </row>
-    <row r="899" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="899" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A899" s="2" t="s">
         <v>1584</v>
       </c>
@@ -48071,7 +48072,7 @@
       <c r="Q899" s="4"/>
       <c r="R899" s="4"/>
     </row>
-    <row r="900" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="900" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A900" s="2" t="s">
         <v>1585</v>
       </c>
@@ -48115,7 +48116,7 @@
       <c r="Q900" s="4"/>
       <c r="R900" s="4"/>
     </row>
-    <row r="901" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="901" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A901" s="2" t="s">
         <v>1586</v>
       </c>
@@ -48159,7 +48160,7 @@
       <c r="Q901" s="4"/>
       <c r="R901" s="4"/>
     </row>
-    <row r="902" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="902" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A902" s="2" t="s">
         <v>1589</v>
       </c>
@@ -48203,7 +48204,7 @@
       <c r="Q902" s="4"/>
       <c r="R902" s="4"/>
     </row>
-    <row r="903" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="903" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A903" s="2" t="s">
         <v>1590</v>
       </c>
@@ -48247,7 +48248,7 @@
       <c r="Q903" s="4"/>
       <c r="R903" s="4"/>
     </row>
-    <row r="904" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="904" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A904" s="2" t="s">
         <v>1591</v>
       </c>
@@ -48291,7 +48292,7 @@
       <c r="Q904" s="4"/>
       <c r="R904" s="4"/>
     </row>
-    <row r="905" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="905" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A905" s="2" t="s">
         <v>1593</v>
       </c>
@@ -48335,7 +48336,7 @@
       <c r="Q905" s="4"/>
       <c r="R905" s="4"/>
     </row>
-    <row r="906" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="906" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A906" s="2" t="s">
         <v>1595</v>
       </c>
@@ -48379,7 +48380,7 @@
       <c r="Q906" s="4"/>
       <c r="R906" s="4"/>
     </row>
-    <row r="907" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="907" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A907" s="2" t="s">
         <v>1596</v>
       </c>
@@ -48423,7 +48424,7 @@
       <c r="Q907" s="4"/>
       <c r="R907" s="4"/>
     </row>
-    <row r="908" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="908" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A908" s="2" t="s">
         <v>1040</v>
       </c>
@@ -48467,7 +48468,7 @@
       <c r="Q908" s="4"/>
       <c r="R908" s="4"/>
     </row>
-    <row r="909" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="909" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A909" s="2" t="s">
         <v>1043</v>
       </c>
@@ -48511,7 +48512,7 @@
       <c r="Q909" s="4"/>
       <c r="R909" s="4"/>
     </row>
-    <row r="910" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="910" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A910" s="2" t="s">
         <v>1045</v>
       </c>
@@ -48555,7 +48556,7 @@
       <c r="Q910" s="4"/>
       <c r="R910" s="4"/>
     </row>
-    <row r="911" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="911" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A911" s="2" t="s">
         <v>1597</v>
       </c>
@@ -48599,7 +48600,7 @@
       <c r="Q911" s="4"/>
       <c r="R911" s="4"/>
     </row>
-    <row r="912" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="912" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A912" s="2" t="s">
         <v>1046</v>
       </c>
@@ -48643,7 +48644,7 @@
       <c r="Q912" s="4"/>
       <c r="R912" s="4"/>
     </row>
-    <row r="913" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="913" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A913" s="2" t="s">
         <v>1049</v>
       </c>
@@ -48687,7 +48688,7 @@
       <c r="Q913" s="4"/>
       <c r="R913" s="4"/>
     </row>
-    <row r="914" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="914" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A914" s="2" t="s">
         <v>1051</v>
       </c>
@@ -48731,7 +48732,7 @@
       <c r="Q914" s="4"/>
       <c r="R914" s="4"/>
     </row>
-    <row r="915" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="915" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A915" s="2" t="s">
         <v>1052</v>
       </c>
@@ -48775,7 +48776,7 @@
       <c r="Q915" s="4"/>
       <c r="R915" s="4"/>
     </row>
-    <row r="916" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="916" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A916" s="2" t="s">
         <v>1053</v>
       </c>
@@ -48819,7 +48820,7 @@
       <c r="Q916" s="4"/>
       <c r="R916" s="4"/>
     </row>
-    <row r="917" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="917" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A917" s="2" t="s">
         <v>1056</v>
       </c>
@@ -48863,7 +48864,7 @@
       <c r="Q917" s="4"/>
       <c r="R917" s="4"/>
     </row>
-    <row r="918" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="918" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A918" s="2" t="s">
         <v>1057</v>
       </c>
@@ -48907,7 +48908,7 @@
       <c r="Q918" s="4"/>
       <c r="R918" s="4"/>
     </row>
-    <row r="919" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="919" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A919" s="2" t="s">
         <v>1060</v>
       </c>
@@ -48951,7 +48952,7 @@
       <c r="Q919" s="4"/>
       <c r="R919" s="4"/>
     </row>
-    <row r="920" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="920" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A920" s="2" t="s">
         <v>1061</v>
       </c>
@@ -48995,7 +48996,7 @@
       <c r="Q920" s="4"/>
       <c r="R920" s="4"/>
     </row>
-    <row r="921" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="921" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A921" s="2" t="s">
         <v>1064</v>
       </c>
@@ -49039,7 +49040,7 @@
       <c r="Q921" s="4"/>
       <c r="R921" s="4"/>
     </row>
-    <row r="922" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="922" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A922" s="2" t="s">
         <v>1066</v>
       </c>
@@ -49083,7 +49084,7 @@
       <c r="Q922" s="4"/>
       <c r="R922" s="4"/>
     </row>
-    <row r="923" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="923" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A923" s="2" t="s">
         <v>1069</v>
       </c>
@@ -49127,7 +49128,7 @@
       <c r="Q923" s="4"/>
       <c r="R923" s="4"/>
     </row>
-    <row r="924" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="924" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A924" s="2" t="s">
         <v>1070</v>
       </c>
@@ -49171,7 +49172,7 @@
       <c r="Q924" s="4"/>
       <c r="R924" s="4"/>
     </row>
-    <row r="925" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="925" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A925" s="2" t="s">
         <v>1073</v>
       </c>
@@ -49215,7 +49216,7 @@
       <c r="Q925" s="4"/>
       <c r="R925" s="4"/>
     </row>
-    <row r="926" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="926" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A926" s="2" t="s">
         <v>1074</v>
       </c>
@@ -49259,7 +49260,7 @@
       <c r="Q926" s="4"/>
       <c r="R926" s="4"/>
     </row>
-    <row r="927" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="927" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A927" s="2" t="s">
         <v>1077</v>
       </c>
@@ -49303,7 +49304,7 @@
       <c r="Q927" s="4"/>
       <c r="R927" s="4"/>
     </row>
-    <row r="928" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="928" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A928" s="2" t="s">
         <v>1078</v>
       </c>
@@ -49347,7 +49348,7 @@
       <c r="Q928" s="4"/>
       <c r="R928" s="4"/>
     </row>
-    <row r="929" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="929" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A929" s="2" t="s">
         <v>1079</v>
       </c>
@@ -49391,7 +49392,7 @@
       <c r="Q929" s="4"/>
       <c r="R929" s="4"/>
     </row>
-    <row r="930" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="930" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A930" s="2" t="s">
         <v>1081</v>
       </c>
@@ -49435,7 +49436,7 @@
       <c r="Q930" s="4"/>
       <c r="R930" s="4"/>
     </row>
-    <row r="931" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="931" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A931" s="2" t="s">
         <v>1082</v>
       </c>
@@ -49479,7 +49480,7 @@
       <c r="Q931" s="4"/>
       <c r="R931" s="4"/>
     </row>
-    <row r="932" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="932" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A932" s="2" t="s">
         <v>1084</v>
       </c>
@@ -49523,7 +49524,7 @@
       <c r="Q932" s="4"/>
       <c r="R932" s="4"/>
     </row>
-    <row r="933" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="933" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A933" s="2" t="s">
         <v>1085</v>
       </c>
@@ -49567,7 +49568,7 @@
       <c r="Q933" s="4"/>
       <c r="R933" s="4"/>
     </row>
-    <row r="934" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="934" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A934" s="2" t="s">
         <v>1088</v>
       </c>
@@ -49611,7 +49612,7 @@
       <c r="Q934" s="4"/>
       <c r="R934" s="4"/>
     </row>
-    <row r="935" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="935" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A935" s="2" t="s">
         <v>1090</v>
       </c>
@@ -49655,7 +49656,7 @@
       <c r="Q935" s="4"/>
       <c r="R935" s="4"/>
     </row>
-    <row r="936" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="936" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A936" s="2" t="s">
         <v>1091</v>
       </c>
@@ -49699,7 +49700,7 @@
       <c r="Q936" s="4"/>
       <c r="R936" s="4"/>
     </row>
-    <row r="937" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="937" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A937" s="2" t="s">
         <v>1094</v>
       </c>
@@ -49743,7 +49744,7 @@
       <c r="Q937" s="4"/>
       <c r="R937" s="4"/>
     </row>
-    <row r="938" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="938" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A938" s="2" t="s">
         <v>1095</v>
       </c>
@@ -49787,7 +49788,7 @@
       <c r="Q938" s="4"/>
       <c r="R938" s="4"/>
     </row>
-    <row r="939" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="939" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A939" s="2" t="s">
         <v>1096</v>
       </c>
@@ -49831,7 +49832,7 @@
       <c r="Q939" s="4"/>
       <c r="R939" s="4"/>
     </row>
-    <row r="940" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="940" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A940" s="2" t="s">
         <v>1098</v>
       </c>
@@ -49875,7 +49876,7 @@
       <c r="Q940" s="4"/>
       <c r="R940" s="4"/>
     </row>
-    <row r="941" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="941" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A941" s="2" t="s">
         <v>1099</v>
       </c>
@@ -49919,7 +49920,7 @@
       <c r="Q941" s="4"/>
       <c r="R941" s="4"/>
     </row>
-    <row r="942" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="942" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A942" s="2" t="s">
         <v>1102</v>
       </c>
@@ -49963,7 +49964,7 @@
       <c r="Q942" s="4"/>
       <c r="R942" s="4"/>
     </row>
-    <row r="943" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="943" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A943" s="2" t="s">
         <v>1103</v>
       </c>
@@ -50007,7 +50008,7 @@
       <c r="Q943" s="4"/>
       <c r="R943" s="4"/>
     </row>
-    <row r="944" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="944" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A944" s="2" t="s">
         <v>1104</v>
       </c>
@@ -50051,7 +50052,7 @@
       <c r="Q944" s="4"/>
       <c r="R944" s="4"/>
     </row>
-    <row r="945" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="945" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A945" s="2" t="s">
         <v>1598</v>
       </c>
@@ -50095,7 +50096,7 @@
       <c r="Q945" s="4"/>
       <c r="R945" s="4"/>
     </row>
-    <row r="946" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="946" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A946" s="2" t="s">
         <v>1106</v>
       </c>
@@ -50139,7 +50140,7 @@
       <c r="Q946" s="4"/>
       <c r="R946" s="4"/>
     </row>
-    <row r="947" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="947" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A947" s="2" t="s">
         <v>1599</v>
       </c>
@@ -50183,7 +50184,7 @@
       <c r="Q947" s="4"/>
       <c r="R947" s="4"/>
     </row>
-    <row r="948" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="948" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A948" s="2" t="s">
         <v>1107</v>
       </c>
@@ -50227,7 +50228,7 @@
       <c r="Q948" s="4"/>
       <c r="R948" s="4"/>
     </row>
-    <row r="949" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="949" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A949" s="2" t="s">
         <v>1108</v>
       </c>
@@ -50271,7 +50272,7 @@
       <c r="Q949" s="4"/>
       <c r="R949" s="4"/>
     </row>
-    <row r="950" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="950" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A950" s="2" t="s">
         <v>1111</v>
       </c>
@@ -50315,7 +50316,7 @@
       <c r="Q950" s="4"/>
       <c r="R950" s="4"/>
     </row>
-    <row r="951" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="951" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A951" s="2" t="s">
         <v>1112</v>
       </c>
@@ -50359,7 +50360,7 @@
       <c r="Q951" s="4"/>
       <c r="R951" s="4"/>
     </row>
-    <row r="952" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="952" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A952" s="2" t="s">
         <v>1113</v>
       </c>
@@ -50403,7 +50404,7 @@
       <c r="Q952" s="4"/>
       <c r="R952" s="4"/>
     </row>
-    <row r="953" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="953" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A953" s="2" t="s">
         <v>1114</v>
       </c>
@@ -50447,7 +50448,7 @@
       <c r="Q953" s="4"/>
       <c r="R953" s="4"/>
     </row>
-    <row r="954" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="954" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A954" s="2" t="s">
         <v>1117</v>
       </c>
@@ -50491,7 +50492,7 @@
       <c r="Q954" s="4"/>
       <c r="R954" s="4"/>
     </row>
-    <row r="955" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="955" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A955" s="2" t="s">
         <v>1118</v>
       </c>
@@ -50535,7 +50536,7 @@
       <c r="Q955" s="4"/>
       <c r="R955" s="4"/>
     </row>
-    <row r="956" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="956" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A956" s="2" t="s">
         <v>1119</v>
       </c>
@@ -50579,7 +50580,7 @@
       <c r="Q956" s="4"/>
       <c r="R956" s="4"/>
     </row>
-    <row r="957" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="957" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A957" s="2" t="s">
         <v>1120</v>
       </c>
@@ -50623,7 +50624,7 @@
       <c r="Q957" s="4"/>
       <c r="R957" s="4"/>
     </row>
-    <row r="958" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="958" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A958" s="2" t="s">
         <v>1121</v>
       </c>
@@ -50667,7 +50668,7 @@
       <c r="Q958" s="4"/>
       <c r="R958" s="4"/>
     </row>
-    <row r="959" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="959" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A959" s="2" t="s">
         <v>1122</v>
       </c>
@@ -50711,7 +50712,7 @@
       <c r="Q959" s="4"/>
       <c r="R959" s="4"/>
     </row>
-    <row r="960" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="960" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A960" s="2" t="s">
         <v>1600</v>
       </c>
@@ -50755,7 +50756,7 @@
       <c r="Q960" s="4"/>
       <c r="R960" s="4"/>
     </row>
-    <row r="961" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="961" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A961" s="2" t="s">
         <v>1601</v>
       </c>
@@ -50799,7 +50800,7 @@
       <c r="Q961" s="4"/>
       <c r="R961" s="4"/>
     </row>
-    <row r="962" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="962" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A962" s="2" t="s">
         <v>1604</v>
       </c>
@@ -50843,7 +50844,7 @@
       <c r="Q962" s="4"/>
       <c r="R962" s="4"/>
     </row>
-    <row r="963" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="963" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A963" s="2" t="s">
         <v>1605</v>
       </c>
@@ -50887,7 +50888,7 @@
       <c r="Q963" s="4"/>
       <c r="R963" s="4"/>
     </row>
-    <row r="964" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="964" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A964" s="2" t="s">
         <v>1607</v>
       </c>
@@ -50931,7 +50932,7 @@
       <c r="Q964" s="4"/>
       <c r="R964" s="4"/>
     </row>
-    <row r="965" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="965" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A965" s="2" t="s">
         <v>1608</v>
       </c>
@@ -50975,7 +50976,7 @@
       <c r="Q965" s="4"/>
       <c r="R965" s="4"/>
     </row>
-    <row r="966" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="966" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A966" s="2" t="s">
         <v>1609</v>
       </c>
@@ -51019,7 +51020,7 @@
       <c r="Q966" s="4"/>
       <c r="R966" s="4"/>
     </row>
-    <row r="967" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="967" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A967" s="2" t="s">
         <v>1125</v>
       </c>
@@ -51063,7 +51064,7 @@
       <c r="Q967" s="4"/>
       <c r="R967" s="4"/>
     </row>
-    <row r="968" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="968" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A968" s="2" t="s">
         <v>1128</v>
       </c>
@@ -51107,7 +51108,7 @@
       <c r="Q968" s="4"/>
       <c r="R968" s="4"/>
     </row>
-    <row r="969" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="969" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A969" s="2" t="s">
         <v>1129</v>
       </c>
@@ -51151,7 +51152,7 @@
       <c r="Q969" s="4"/>
       <c r="R969" s="4"/>
     </row>
-    <row r="970" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="970" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A970" s="2" t="s">
         <v>1130</v>
       </c>
@@ -51195,7 +51196,7 @@
       <c r="Q970" s="4"/>
       <c r="R970" s="4"/>
     </row>
-    <row r="971" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="971" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A971" s="2" t="s">
         <v>1610</v>
       </c>
@@ -51239,7 +51240,7 @@
       <c r="Q971" s="4"/>
       <c r="R971" s="4"/>
     </row>
-    <row r="972" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="972" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A972" s="2" t="s">
         <v>1613</v>
       </c>
@@ -51283,7 +51284,7 @@
       <c r="Q972" s="4"/>
       <c r="R972" s="4"/>
     </row>
-    <row r="973" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="973" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A973" s="2" t="s">
         <v>1131</v>
       </c>
@@ -51327,7 +51328,7 @@
       <c r="Q973" s="4"/>
       <c r="R973" s="4"/>
     </row>
-    <row r="974" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="974" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A974" s="2" t="s">
         <v>1134</v>
       </c>
@@ -51371,7 +51372,7 @@
       <c r="Q974" s="4"/>
       <c r="R974" s="4"/>
     </row>
-    <row r="975" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="975" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A975" s="2" t="s">
         <v>1135</v>
       </c>
@@ -51415,7 +51416,7 @@
       <c r="Q975" s="4"/>
       <c r="R975" s="4"/>
     </row>
-    <row r="976" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="976" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A976" s="2" t="s">
         <v>1136</v>
       </c>
@@ -51459,7 +51460,7 @@
       <c r="Q976" s="4"/>
       <c r="R976" s="4"/>
     </row>
-    <row r="977" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="977" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A977" s="2" t="s">
         <v>1137</v>
       </c>
@@ -51503,7 +51504,7 @@
       <c r="Q977" s="4"/>
       <c r="R977" s="4"/>
     </row>
-    <row r="978" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="978" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A978" s="2" t="s">
         <v>1614</v>
       </c>
@@ -51547,7 +51548,7 @@
       <c r="Q978" s="4"/>
       <c r="R978" s="4"/>
     </row>
-    <row r="979" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="979" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A979" s="2" t="s">
         <v>1140</v>
       </c>
@@ -51591,7 +51592,7 @@
       <c r="Q979" s="4"/>
       <c r="R979" s="4"/>
     </row>
-    <row r="980" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="980" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A980" s="2" t="s">
         <v>1141</v>
       </c>
@@ -51635,7 +51636,7 @@
       <c r="Q980" s="4"/>
       <c r="R980" s="4"/>
     </row>
-    <row r="981" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="981" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A981" s="2" t="s">
         <v>1144</v>
       </c>
@@ -51679,7 +51680,7 @@
       <c r="Q981" s="4"/>
       <c r="R981" s="4"/>
     </row>
-    <row r="982" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="982" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A982" s="2" t="s">
         <v>1615</v>
       </c>
@@ -51723,7 +51724,7 @@
       <c r="Q982" s="4"/>
       <c r="R982" s="4"/>
     </row>
-    <row r="983" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="983" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A983" s="2" t="s">
         <v>1145</v>
       </c>
@@ -51767,7 +51768,7 @@
       <c r="Q983" s="4"/>
       <c r="R983" s="4"/>
     </row>
-    <row r="984" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="984" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A984" s="2" t="s">
         <v>1148</v>
       </c>
@@ -51811,7 +51812,7 @@
       <c r="Q984" s="4"/>
       <c r="R984" s="4"/>
     </row>
-    <row r="985" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="985" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A985" s="2" t="s">
         <v>1151</v>
       </c>
@@ -51855,7 +51856,7 @@
       <c r="Q985" s="4"/>
       <c r="R985" s="4"/>
     </row>
-    <row r="986" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="986" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A986" s="2" t="s">
         <v>1616</v>
       </c>
@@ -51899,7 +51900,7 @@
       <c r="Q986" s="4"/>
       <c r="R986" s="4"/>
     </row>
-    <row r="987" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="987" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A987" s="2" t="s">
         <v>1152</v>
       </c>
@@ -51943,7 +51944,7 @@
       <c r="Q987" s="4"/>
       <c r="R987" s="4"/>
     </row>
-    <row r="988" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="988" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A988" s="2" t="s">
         <v>1156</v>
       </c>
@@ -51987,7 +51988,7 @@
       <c r="Q988" s="4"/>
       <c r="R988" s="4"/>
     </row>
-    <row r="989" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="989" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A989" s="2" t="s">
         <v>1617</v>
       </c>
@@ -52031,7 +52032,7 @@
       <c r="Q989" s="4"/>
       <c r="R989" s="4"/>
     </row>
-    <row r="990" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="990" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A990" s="2" t="s">
         <v>1157</v>
       </c>
@@ -52075,7 +52076,7 @@
       <c r="Q990" s="4"/>
       <c r="R990" s="4"/>
     </row>
-    <row r="991" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="991" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A991" s="2" t="s">
         <v>1159</v>
       </c>
@@ -52119,7 +52120,7 @@
       <c r="Q991" s="4"/>
       <c r="R991" s="4"/>
     </row>
-    <row r="992" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="992" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A992" s="2" t="s">
         <v>1162</v>
       </c>
@@ -52163,7 +52164,7 @@
       <c r="Q992" s="4"/>
       <c r="R992" s="4"/>
     </row>
-    <row r="993" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="993" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A993" s="2" t="s">
         <v>1163</v>
       </c>
@@ -52207,7 +52208,7 @@
       <c r="Q993" s="4"/>
       <c r="R993" s="4"/>
     </row>
-    <row r="994" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="994" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A994" s="2" t="s">
         <v>1164</v>
       </c>
@@ -52251,7 +52252,7 @@
       <c r="Q994" s="4"/>
       <c r="R994" s="4"/>
     </row>
-    <row r="995" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="995" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A995" s="2" t="s">
         <v>1165</v>
       </c>
@@ -52295,7 +52296,7 @@
       <c r="Q995" s="4"/>
       <c r="R995" s="4"/>
     </row>
-    <row r="996" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="996" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A996" s="2" t="s">
         <v>1168</v>
       </c>
@@ -52339,7 +52340,7 @@
       <c r="Q996" s="4"/>
       <c r="R996" s="4"/>
     </row>
-    <row r="997" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="997" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A997" s="2" t="s">
         <v>1169</v>
       </c>
@@ -52383,7 +52384,7 @@
       <c r="Q997" s="4"/>
       <c r="R997" s="4"/>
     </row>
-    <row r="998" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="998" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A998" s="2" t="s">
         <v>1170</v>
       </c>
@@ -52427,7 +52428,7 @@
       <c r="Q998" s="4"/>
       <c r="R998" s="4"/>
     </row>
-    <row r="999" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="999" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A999" s="2" t="s">
         <v>1173</v>
       </c>
@@ -52471,7 +52472,7 @@
       <c r="Q999" s="4"/>
       <c r="R999" s="4"/>
     </row>
-    <row r="1000" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1000" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1000" s="2" t="s">
         <v>1174</v>
       </c>
@@ -52515,7 +52516,7 @@
       <c r="Q1000" s="4"/>
       <c r="R1000" s="4"/>
     </row>
-    <row r="1001" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1001" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1001" s="2" t="s">
         <v>1618</v>
       </c>
@@ -52559,7 +52560,7 @@
       <c r="Q1001" s="4"/>
       <c r="R1001" s="4"/>
     </row>
-    <row r="1002" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1002" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1002" s="2" t="s">
         <v>1619</v>
       </c>
@@ -52603,7 +52604,7 @@
       <c r="Q1002" s="4"/>
       <c r="R1002" s="4"/>
     </row>
-    <row r="1003" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1003" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1003" s="2" t="s">
         <v>1175</v>
       </c>
@@ -52647,7 +52648,7 @@
       <c r="Q1003" s="4"/>
       <c r="R1003" s="4"/>
     </row>
-    <row r="1004" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1004" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1004" s="2" t="s">
         <v>1178</v>
       </c>
@@ -52691,7 +52692,7 @@
       <c r="Q1004" s="4"/>
       <c r="R1004" s="4"/>
     </row>
-    <row r="1005" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1005" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1005" s="2" t="s">
         <v>1179</v>
       </c>
@@ -52735,7 +52736,7 @@
       <c r="Q1005" s="4"/>
       <c r="R1005" s="4"/>
     </row>
-    <row r="1006" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1006" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1006" s="2" t="s">
         <v>1181</v>
       </c>
@@ -52779,7 +52780,7 @@
       <c r="Q1006" s="4"/>
       <c r="R1006" s="4"/>
     </row>
-    <row r="1007" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1007" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1007" s="2" t="s">
         <v>1182</v>
       </c>
@@ -52823,7 +52824,7 @@
       <c r="Q1007" s="4"/>
       <c r="R1007" s="4"/>
     </row>
-    <row r="1008" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1008" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1008" s="2" t="s">
         <v>1185</v>
       </c>
@@ -52867,7 +52868,7 @@
       <c r="Q1008" s="4"/>
       <c r="R1008" s="4"/>
     </row>
-    <row r="1009" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1009" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1009" s="2" t="s">
         <v>1186</v>
       </c>
@@ -52911,7 +52912,7 @@
       <c r="Q1009" s="4"/>
       <c r="R1009" s="4"/>
     </row>
-    <row r="1010" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1010" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1010" s="2" t="s">
         <v>1188</v>
       </c>
@@ -52955,7 +52956,7 @@
       <c r="Q1010" s="4"/>
       <c r="R1010" s="4"/>
     </row>
-    <row r="1011" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1011" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1011" s="2" t="s">
         <v>1189</v>
       </c>
@@ -52999,7 +53000,7 @@
       <c r="Q1011" s="4"/>
       <c r="R1011" s="4"/>
     </row>
-    <row r="1012" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1012" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1012" s="2" t="s">
         <v>1190</v>
       </c>
@@ -53043,7 +53044,7 @@
       <c r="Q1012" s="4"/>
       <c r="R1012" s="4"/>
     </row>
-    <row r="1013" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1013" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1013" s="2" t="s">
         <v>1191</v>
       </c>
@@ -53087,7 +53088,7 @@
       <c r="Q1013" s="4"/>
       <c r="R1013" s="4"/>
     </row>
-    <row r="1014" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1014" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1014" s="2" t="s">
         <v>1194</v>
       </c>
@@ -53131,7 +53132,7 @@
       <c r="Q1014" s="4"/>
       <c r="R1014" s="4"/>
     </row>
-    <row r="1015" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1015" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1015" s="2" t="s">
         <v>1195</v>
       </c>
@@ -53175,7 +53176,7 @@
       <c r="Q1015" s="4"/>
       <c r="R1015" s="4"/>
     </row>
-    <row r="1016" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1016" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1016" s="2" t="s">
         <v>1196</v>
       </c>
@@ -53219,7 +53220,7 @@
       <c r="Q1016" s="4"/>
       <c r="R1016" s="4"/>
     </row>
-    <row r="1017" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1017" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1017" s="2" t="s">
         <v>1199</v>
       </c>
@@ -53263,7 +53264,7 @@
       <c r="Q1017" s="4"/>
       <c r="R1017" s="4"/>
     </row>
-    <row r="1018" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1018" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1018" s="2" t="s">
         <v>1201</v>
       </c>
@@ -53307,7 +53308,7 @@
       <c r="Q1018" s="4"/>
       <c r="R1018" s="4"/>
     </row>
-    <row r="1019" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1019" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1019" s="2" t="s">
         <v>1620</v>
       </c>
@@ -53351,7 +53352,7 @@
       <c r="Q1019" s="4"/>
       <c r="R1019" s="4"/>
     </row>
-    <row r="1020" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1020" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1020" s="2" t="s">
         <v>1202</v>
       </c>
@@ -53395,7 +53396,7 @@
       <c r="Q1020" s="4"/>
       <c r="R1020" s="4"/>
     </row>
-    <row r="1021" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1021" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1021" s="2" t="s">
         <v>1205</v>
       </c>
@@ -53439,7 +53440,7 @@
       <c r="Q1021" s="4"/>
       <c r="R1021" s="4"/>
     </row>
-    <row r="1022" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1022" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1022" s="2" t="s">
         <v>1206</v>
       </c>
@@ -53483,7 +53484,7 @@
       <c r="Q1022" s="4"/>
       <c r="R1022" s="4"/>
     </row>
-    <row r="1023" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1023" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1023" s="2" t="s">
         <v>1209</v>
       </c>
@@ -53527,7 +53528,7 @@
       <c r="Q1023" s="4"/>
       <c r="R1023" s="4"/>
     </row>
-    <row r="1024" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1024" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1024" s="2" t="s">
         <v>1210</v>
       </c>
@@ -53571,7 +53572,7 @@
       <c r="Q1024" s="4"/>
       <c r="R1024" s="4"/>
     </row>
-    <row r="1025" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1025" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1025" s="2" t="s">
         <v>1212</v>
       </c>
@@ -53615,7 +53616,7 @@
       <c r="Q1025" s="4"/>
       <c r="R1025" s="4"/>
     </row>
-    <row r="1026" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1026" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1026" s="2" t="s">
         <v>1213</v>
       </c>
@@ -53659,7 +53660,7 @@
       <c r="Q1026" s="4"/>
       <c r="R1026" s="4"/>
     </row>
-    <row r="1027" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1027" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1027" s="2" t="s">
         <v>1214</v>
       </c>
@@ -53703,7 +53704,7 @@
       <c r="Q1027" s="4"/>
       <c r="R1027" s="4"/>
     </row>
-    <row r="1028" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1028" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1028" s="2" t="s">
         <v>1215</v>
       </c>
@@ -53747,7 +53748,7 @@
       <c r="Q1028" s="4"/>
       <c r="R1028" s="4"/>
     </row>
-    <row r="1029" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1029" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1029" s="2" t="s">
         <v>1621</v>
       </c>
@@ -53791,7 +53792,7 @@
       <c r="Q1029" s="4"/>
       <c r="R1029" s="4"/>
     </row>
-    <row r="1030" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1030" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1030" s="2" t="s">
         <v>1216</v>
       </c>
@@ -53835,7 +53836,7 @@
       <c r="Q1030" s="4"/>
       <c r="R1030" s="4"/>
     </row>
-    <row r="1031" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1031" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1031" s="2" t="s">
         <v>1219</v>
       </c>
@@ -53879,7 +53880,7 @@
       <c r="Q1031" s="4"/>
       <c r="R1031" s="4"/>
     </row>
-    <row r="1032" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1032" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1032" s="2" t="s">
         <v>1623</v>
       </c>
@@ -53923,7 +53924,7 @@
       <c r="Q1032" s="4"/>
       <c r="R1032" s="4"/>
     </row>
-    <row r="1033" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1033" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1033" s="2" t="s">
         <v>1625</v>
       </c>
@@ -53967,7 +53968,7 @@
       <c r="Q1033" s="4"/>
       <c r="R1033" s="4"/>
     </row>
-    <row r="1034" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1034" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1034" s="2" t="s">
         <v>1626</v>
       </c>
@@ -54011,7 +54012,7 @@
       <c r="Q1034" s="4"/>
       <c r="R1034" s="4"/>
     </row>
-    <row r="1035" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1035" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1035" s="2" t="s">
         <v>1627</v>
       </c>
@@ -54055,7 +54056,7 @@
       <c r="Q1035" s="4"/>
       <c r="R1035" s="4"/>
     </row>
-    <row r="1036" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1036" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1036" s="2" t="s">
         <v>1222</v>
       </c>
@@ -54099,7 +54100,7 @@
       <c r="Q1036" s="4"/>
       <c r="R1036" s="4"/>
     </row>
-    <row r="1037" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1037" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1037" s="2" t="s">
         <v>1223</v>
       </c>
@@ -54143,7 +54144,7 @@
       <c r="Q1037" s="4"/>
       <c r="R1037" s="4"/>
     </row>
-    <row r="1038" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1038" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1038" s="2" t="s">
         <v>1224</v>
       </c>
@@ -54187,7 +54188,7 @@
       <c r="Q1038" s="4"/>
       <c r="R1038" s="4"/>
     </row>
-    <row r="1039" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1039" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1039" s="2" t="s">
         <v>1225</v>
       </c>
@@ -54231,7 +54232,7 @@
       <c r="Q1039" s="4"/>
       <c r="R1039" s="4"/>
     </row>
-    <row r="1040" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1040" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1040" s="2" t="s">
         <v>1628</v>
       </c>
@@ -54275,7 +54276,7 @@
       <c r="Q1040" s="4"/>
       <c r="R1040" s="4"/>
     </row>
-    <row r="1041" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1041" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1041" s="2" t="s">
         <v>1226</v>
       </c>
@@ -54319,7 +54320,7 @@
       <c r="Q1041" s="4"/>
       <c r="R1041" s="4"/>
     </row>
-    <row r="1042" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1042" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1042" s="2" t="s">
         <v>1629</v>
       </c>
@@ -54363,7 +54364,7 @@
       <c r="Q1042" s="4"/>
       <c r="R1042" s="4"/>
     </row>
-    <row r="1043" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1043" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1043" s="2" t="s">
         <v>1230</v>
       </c>
@@ -54407,7 +54408,7 @@
       <c r="Q1043" s="4"/>
       <c r="R1043" s="4"/>
     </row>
-    <row r="1044" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1044" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1044" s="2" t="s">
         <v>1231</v>
       </c>
@@ -54451,7 +54452,7 @@
       <c r="Q1044" s="4"/>
       <c r="R1044" s="4"/>
     </row>
-    <row r="1045" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1045" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1045" s="2" t="s">
         <v>1232</v>
       </c>
@@ -54495,7 +54496,7 @@
       <c r="Q1045" s="4"/>
       <c r="R1045" s="4"/>
     </row>
-    <row r="1046" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1046" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1046" s="2" t="s">
         <v>1233</v>
       </c>
@@ -54539,7 +54540,7 @@
       <c r="Q1046" s="4"/>
       <c r="R1046" s="4"/>
     </row>
-    <row r="1047" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1047" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1047" s="2" t="s">
         <v>1234</v>
       </c>
@@ -54583,7 +54584,7 @@
       <c r="Q1047" s="4"/>
       <c r="R1047" s="4"/>
     </row>
-    <row r="1048" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1048" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1048" s="2" t="s">
         <v>1235</v>
       </c>
@@ -54627,7 +54628,7 @@
       <c r="Q1048" s="4"/>
       <c r="R1048" s="4"/>
     </row>
-    <row r="1049" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1049" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1049" s="2" t="s">
         <v>1236</v>
       </c>
@@ -54671,7 +54672,7 @@
       <c r="Q1049" s="4"/>
       <c r="R1049" s="4"/>
     </row>
-    <row r="1050" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1050" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1050" s="2" t="s">
         <v>1630</v>
       </c>
@@ -54715,7 +54716,7 @@
       <c r="Q1050" s="4"/>
       <c r="R1050" s="4"/>
     </row>
-    <row r="1051" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1051" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1051" s="2" t="s">
         <v>1631</v>
       </c>
@@ -54759,7 +54760,7 @@
       <c r="Q1051" s="4"/>
       <c r="R1051" s="4"/>
     </row>
-    <row r="1052" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1052" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1052" s="2" t="s">
         <v>1632</v>
       </c>
@@ -54803,7 +54804,7 @@
       <c r="Q1052" s="4"/>
       <c r="R1052" s="4"/>
     </row>
-    <row r="1053" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1053" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1053" s="2" t="s">
         <v>1633</v>
       </c>
@@ -54847,7 +54848,7 @@
       <c r="Q1053" s="4"/>
       <c r="R1053" s="4"/>
     </row>
-    <row r="1054" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1054" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1054" s="2" t="s">
         <v>1634</v>
       </c>
@@ -54891,7 +54892,7 @@
       <c r="Q1054" s="4"/>
       <c r="R1054" s="4"/>
     </row>
-    <row r="1055" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1055" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1055" s="2" t="s">
         <v>1635</v>
       </c>
@@ -54935,7 +54936,7 @@
       <c r="Q1055" s="4"/>
       <c r="R1055" s="4"/>
     </row>
-    <row r="1056" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1056" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1056" s="2" t="s">
         <v>1239</v>
       </c>
@@ -54979,7 +54980,7 @@
       <c r="Q1056" s="4"/>
       <c r="R1056" s="4"/>
     </row>
-    <row r="1057" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1057" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1057" s="2" t="s">
         <v>1241</v>
       </c>
@@ -55023,7 +55024,7 @@
       <c r="Q1057" s="4"/>
       <c r="R1057" s="4"/>
     </row>
-    <row r="1058" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1058" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1058" s="2" t="s">
         <v>1243</v>
       </c>
@@ -55067,7 +55068,7 @@
       <c r="Q1058" s="4"/>
       <c r="R1058" s="4"/>
     </row>
-    <row r="1059" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1059" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1059" s="2" t="s">
         <v>1245</v>
       </c>
@@ -55111,7 +55112,7 @@
       <c r="Q1059" s="4"/>
       <c r="R1059" s="4"/>
     </row>
-    <row r="1060" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1060" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1060" s="2" t="s">
         <v>1248</v>
       </c>
@@ -55155,7 +55156,7 @@
       <c r="Q1060" s="4"/>
       <c r="R1060" s="4"/>
     </row>
-    <row r="1061" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1061" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1061" s="2" t="s">
         <v>1250</v>
       </c>
@@ -55199,7 +55200,7 @@
       <c r="Q1061" s="4"/>
       <c r="R1061" s="4"/>
     </row>
-    <row r="1062" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1062" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1062" s="2" t="s">
         <v>1252</v>
       </c>
@@ -55243,7 +55244,7 @@
       <c r="Q1062" s="4"/>
       <c r="R1062" s="4"/>
     </row>
-    <row r="1063" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1063" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1063" s="2" t="s">
         <v>1253</v>
       </c>
@@ -55287,7 +55288,7 @@
       <c r="Q1063" s="4"/>
       <c r="R1063" s="4"/>
     </row>
-    <row r="1064" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1064" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1064" s="2" t="s">
         <v>1255</v>
       </c>
@@ -55331,7 +55332,7 @@
       <c r="Q1064" s="4"/>
       <c r="R1064" s="4"/>
     </row>
-    <row r="1065" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1065" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1065" s="2" t="s">
         <v>1256</v>
       </c>
@@ -55375,7 +55376,7 @@
       <c r="Q1065" s="4"/>
       <c r="R1065" s="4"/>
     </row>
-    <row r="1066" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1066" spans="1:18" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1066" s="2" t="s">
         <v>1258</v>
       </c>
@@ -55420,7 +55421,14 @@
       <c r="R1066" s="4"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R1066" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:R1066" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="4">
+      <filters>
+        <filter val="VELOZ 3"/>
+        <filter val="VELOZ 4"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Produtos.xlsx
+++ b/Produtos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NOT-MARCOS\Documents\GitHub\Catalogo-Olympikus_2.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5581F0EF-4D31-4F28-8B33-2EE7FCBB2321}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF8354EB-69D3-4779-93AA-7CA0B081CEFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10936" uniqueCount="1396">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12146" uniqueCount="1620">
   <si>
     <t>CODIGO</t>
   </si>
@@ -4224,6 +4224,678 @@
   </si>
   <si>
     <t>PP-P-M-G-GG</t>
+  </si>
+  <si>
+    <t>OIWSC26101_PTPRT</t>
+  </si>
+  <si>
+    <t>T-SHIRT RUNNER MC 2.0 F</t>
+  </si>
+  <si>
+    <t>OCRE</t>
+  </si>
+  <si>
+    <t>OIWSC26101_FLOTAL</t>
+  </si>
+  <si>
+    <t>OIWSC26103_PTPRT</t>
+  </si>
+  <si>
+    <t>T-SHIRT ULTRA M</t>
+  </si>
+  <si>
+    <t>FLOTAL</t>
+  </si>
+  <si>
+    <t>OIWSC26103_VIOLET</t>
+  </si>
+  <si>
+    <t>T-SHIRT RUNNER MC 2.0 M</t>
+  </si>
+  <si>
+    <t>PSTCHE</t>
+  </si>
+  <si>
+    <t>OIWSC26102_PTPRT</t>
+  </si>
+  <si>
+    <t>OIWSC26102_FLOTAL</t>
+  </si>
+  <si>
+    <t>TAPTRY</t>
+  </si>
+  <si>
+    <t>OIWSC26701_PTBCO</t>
+  </si>
+  <si>
+    <t>LIRIO</t>
+  </si>
+  <si>
+    <t>OIWSC26701_FLOTAL</t>
+  </si>
+  <si>
+    <t>OIWSR25161</t>
+  </si>
+  <si>
+    <t>TOP KNIT MINIMAL F</t>
+  </si>
+  <si>
+    <t>OIWSC26601_PTPRT</t>
+  </si>
+  <si>
+    <t>OIWSC26601_VIOLET</t>
+  </si>
+  <si>
+    <t>BERMUDA KNIT MINIMAL 6&amp;quot; F</t>
+  </si>
+  <si>
+    <t>OIWSC26601_FLOTAL</t>
+  </si>
+  <si>
+    <t>TAPPTC</t>
+  </si>
+  <si>
+    <t>OIWSC26801_PTPRT</t>
+  </si>
+  <si>
+    <t>SGRPTO</t>
+  </si>
+  <si>
+    <t>OIWSC26801_FLOTAL</t>
+  </si>
+  <si>
+    <t>T-SHIRT ESSENTIAL ML F</t>
+  </si>
+  <si>
+    <t>P-M-G-GG-G1-G2-G3</t>
+  </si>
+  <si>
+    <t>OIWSC26802_PTPRT</t>
+  </si>
+  <si>
+    <t>T-SHIRT ESSENTIAL MC F</t>
+  </si>
+  <si>
+    <t>OIWSC26802_VIOLET</t>
+  </si>
+  <si>
+    <t>OIWSC26301_PTPRT</t>
+  </si>
+  <si>
+    <t>OIWSC26301_FLOTAL</t>
+  </si>
+  <si>
+    <t>OIWSC26111_FLOTAL</t>
+  </si>
+  <si>
+    <t>OIWWT26715</t>
+  </si>
+  <si>
+    <t>REGATA ESSENTIAL F</t>
+  </si>
+  <si>
+    <t>OIMSC26704_PTBCO</t>
+  </si>
+  <si>
+    <t>OIMSC26704_FLOTAL</t>
+  </si>
+  <si>
+    <t>OIMSC26608_PRETO</t>
+  </si>
+  <si>
+    <t>OIMSC26608_FLOTAL</t>
+  </si>
+  <si>
+    <t>JAQUETA QUEBRA-VENTO ESSENTIAL F</t>
+  </si>
+  <si>
+    <t>OIMSC26608_PSTCHE</t>
+  </si>
+  <si>
+    <t>T-SHIRT ESSENTIAL ML M</t>
+  </si>
+  <si>
+    <t>SILGRE</t>
+  </si>
+  <si>
+    <t>OIMSC26804_PTPRT</t>
+  </si>
+  <si>
+    <t>T-SHIRT ESSENTIAL MC M</t>
+  </si>
+  <si>
+    <t>OIMSC26804_FLOTAL</t>
+  </si>
+  <si>
+    <t>OIMWT26719</t>
+  </si>
+  <si>
+    <t>REGATA ESSENTIAL M</t>
+  </si>
+  <si>
+    <t>OIMSC26806_PTPRT</t>
+  </si>
+  <si>
+    <t>OIMSC26806_FLOTAL</t>
+  </si>
+  <si>
+    <t>OIMSC26805_PTPRT</t>
+  </si>
+  <si>
+    <t>JAQUETA QUEBRA-VENTO ESSENTIAL M</t>
+  </si>
+  <si>
+    <t>OIMSC26805_FLOTAL</t>
+  </si>
+  <si>
+    <t>OIMWT25640</t>
+  </si>
+  <si>
+    <t>T-SHIRT LINE MC M</t>
+  </si>
+  <si>
+    <t>OIMSC26303_PTPRT</t>
+  </si>
+  <si>
+    <t>OIMSC26114_FLOTAL</t>
+  </si>
+  <si>
+    <t>MEIA PERFORMANCE BPC CANO MÉDIO 33/38</t>
+  </si>
+  <si>
+    <t>PTCAAL</t>
+  </si>
+  <si>
+    <t>OIWSC26104_PTPRT</t>
+  </si>
+  <si>
+    <t>BCOVDA</t>
+  </si>
+  <si>
+    <t>OIWSC26104_OCRE</t>
+  </si>
+  <si>
+    <t>TRIPACK MEIA NEON CANO INVISÍVEL 33/38</t>
+  </si>
+  <si>
+    <t>BBABAB</t>
+  </si>
+  <si>
+    <t>OIWSC26602_PTPRT</t>
+  </si>
+  <si>
+    <t>BFCBPO</t>
+  </si>
+  <si>
+    <t>OIWSC26602_MOCCA</t>
+  </si>
+  <si>
+    <t>MEIA PERFORMANCE BPC CANO MÉDIO 39/44</t>
+  </si>
+  <si>
+    <t>OIWSC26156_PTPRT</t>
+  </si>
+  <si>
+    <t>OIWSC26156_FLOTAL</t>
+  </si>
+  <si>
+    <t>TRIPACK MEIA NEON CANO INVISÍVEL 39/44</t>
+  </si>
+  <si>
+    <t>FBLBOB</t>
+  </si>
+  <si>
+    <t>OIWSC26302_PTPRT</t>
+  </si>
+  <si>
+    <t>OIWSC26302_FLOTAL</t>
+  </si>
+  <si>
+    <t>OIWSC26101</t>
+  </si>
+  <si>
+    <t>TOP CORRE FOCO ALONGADO F</t>
+  </si>
+  <si>
+    <t>PTPRT</t>
+  </si>
+  <si>
+    <t>OIWSC26302_OCRE</t>
+  </si>
+  <si>
+    <t>OIWSC26211_PTPRT</t>
+  </si>
+  <si>
+    <t>OIWSC26103</t>
+  </si>
+  <si>
+    <t>TOP CORRE FOCO ALTO IMPACTO F</t>
+  </si>
+  <si>
+    <t>OIWSC26211_FLOTAL</t>
+  </si>
+  <si>
+    <t>VIOLET</t>
+  </si>
+  <si>
+    <t>OIMSC26609_PTPRT</t>
+  </si>
+  <si>
+    <t>OIWSC26102</t>
+  </si>
+  <si>
+    <t>TOP CORRE FOCO MÉDIO IMPACTO F</t>
+  </si>
+  <si>
+    <t>OIMSC26609_MOCCA</t>
+  </si>
+  <si>
+    <t>OIMSC26808_PTPRT</t>
+  </si>
+  <si>
+    <t>OIWSC26701</t>
+  </si>
+  <si>
+    <t>REGATA CORRE FOCO F</t>
+  </si>
+  <si>
+    <t>PTBCO</t>
+  </si>
+  <si>
+    <t>OIMSC26808_FLOTAL</t>
+  </si>
+  <si>
+    <t>OICR261714_PTPRT</t>
+  </si>
+  <si>
+    <t>OIWSC26601</t>
+  </si>
+  <si>
+    <t>T-SHIRT CORRE FOCO F</t>
+  </si>
+  <si>
+    <t>OICR261714_FLPSPT</t>
+  </si>
+  <si>
+    <t>OIUSC26191_NAVAL</t>
+  </si>
+  <si>
+    <t>OIUSC26191_PRETO</t>
+  </si>
+  <si>
+    <t>OIWSC26801</t>
+  </si>
+  <si>
+    <t>SHORT CORRE FOCO 3 F</t>
+  </si>
+  <si>
+    <t>OIUR261920_FLRPTO</t>
+  </si>
+  <si>
+    <t>OIUR261920_CREPTO</t>
+  </si>
+  <si>
+    <t>OIWSC26802</t>
+  </si>
+  <si>
+    <t>SHORT CORRE FOCO 2 EM 1 3 F</t>
+  </si>
+  <si>
+    <t>OIUR261920_PTBCO</t>
+  </si>
+  <si>
+    <t>OBWA261922_VCOWMH</t>
+  </si>
+  <si>
+    <t>OIWSC26301</t>
+  </si>
+  <si>
+    <t>BERMUDA BOLSO CORRE FOCO 7 F</t>
+  </si>
+  <si>
+    <t>OBWA261922_OWALPT</t>
+  </si>
+  <si>
+    <t>OBWA261922_PTOWAL</t>
+  </si>
+  <si>
+    <t>OIWSC26111</t>
+  </si>
+  <si>
+    <t>JAQUETA CORRE FOCO F</t>
+  </si>
+  <si>
+    <t>OBWA261922_COARPT</t>
+  </si>
+  <si>
+    <t>OIMSC26704</t>
+  </si>
+  <si>
+    <t>REGATA CORRE FOCO M</t>
+  </si>
+  <si>
+    <t>OBMA261923_VCOWMH</t>
+  </si>
+  <si>
+    <t>OBMA261923_OWALPT</t>
+  </si>
+  <si>
+    <t>OIMSC26608</t>
+  </si>
+  <si>
+    <t>T-SHIRT CORRE FOCO M</t>
+  </si>
+  <si>
+    <t>OBMA261923_PTOWAL</t>
+  </si>
+  <si>
+    <t>OBMA261923_COARPT</t>
+  </si>
+  <si>
+    <t>OIWWR25602_OCRE</t>
+  </si>
+  <si>
+    <t>OIMSC26804</t>
+  </si>
+  <si>
+    <t>SHORT CORRE FOCO 3 M</t>
+  </si>
+  <si>
+    <t>OIWWR25701_OCRE</t>
+  </si>
+  <si>
+    <t>OIMSR23605_FLOTAL</t>
+  </si>
+  <si>
+    <t>OIMSC26806</t>
+  </si>
+  <si>
+    <t>BERMUDA CORRE FOCO 2 EM 1 5 M</t>
+  </si>
+  <si>
+    <t>OIMWR25606_PSTCHE</t>
+  </si>
+  <si>
+    <t>OIMSR25706_PSTCHE</t>
+  </si>
+  <si>
+    <t>OIMSC26805</t>
+  </si>
+  <si>
+    <t>BERMUDA CORRE FOCO 5 M</t>
+  </si>
+  <si>
+    <t>OIWST25702_TAPTRY</t>
+  </si>
+  <si>
+    <t>OIWST25702_LIRIO</t>
+  </si>
+  <si>
+    <t>OIMSC26303</t>
+  </si>
+  <si>
+    <t>BERMUDA BOLSO CORRE FOCO 8 M</t>
+  </si>
+  <si>
+    <t>OIWSR25161_TAPTRY</t>
+  </si>
+  <si>
+    <t>OIMSC26114</t>
+  </si>
+  <si>
+    <t>JAQUETA CORRE FOCO M</t>
+  </si>
+  <si>
+    <t>OIWSR25152_TAPTRY</t>
+  </si>
+  <si>
+    <t>OIWSC26104</t>
+  </si>
+  <si>
+    <t>TOP CORRE FORÇA BAIXO IMPACTO F</t>
+  </si>
+  <si>
+    <t>OIWSR25801_TAPTRY</t>
+  </si>
+  <si>
+    <t>OIMWT25320_TAPPTC</t>
+  </si>
+  <si>
+    <t>OIWSC26602</t>
+  </si>
+  <si>
+    <t>T-SHIRT CORRE FORÇA F</t>
+  </si>
+  <si>
+    <t>OIMWT25320_SGRPTO</t>
+  </si>
+  <si>
+    <t>MOCCA</t>
+  </si>
+  <si>
+    <t>OIWWT26616_TAPTRY</t>
+  </si>
+  <si>
+    <t>OIWSC26156</t>
+  </si>
+  <si>
+    <t>LEGGING CORRE FORÇA F</t>
+  </si>
+  <si>
+    <t>OIWWT26615_PRETO</t>
+  </si>
+  <si>
+    <t>OIWWT26615_TAPTRY</t>
+  </si>
+  <si>
+    <t>OIWSC26302</t>
+  </si>
+  <si>
+    <t>BERMUDA CORRE FORÇA 5 F</t>
+  </si>
+  <si>
+    <t>OIWWT26615_LIRIO</t>
+  </si>
+  <si>
+    <t>OIWWT26615_BRANCO</t>
+  </si>
+  <si>
+    <t>OIWWT26715_TAPTRY</t>
+  </si>
+  <si>
+    <t>OIWSC26211</t>
+  </si>
+  <si>
+    <t>MACACÃO CORRE FORÇA F</t>
+  </si>
+  <si>
+    <t>OIWWT26715_LIRIO</t>
+  </si>
+  <si>
+    <t>OIWST26168_PRETO</t>
+  </si>
+  <si>
+    <t>OIMSC26609</t>
+  </si>
+  <si>
+    <t>T-SHIRT CORRE FORÇA M</t>
+  </si>
+  <si>
+    <t>OIWST26168_LIRIO</t>
+  </si>
+  <si>
+    <t>OIWST26153_PRETO</t>
+  </si>
+  <si>
+    <t>OIMSC26808</t>
+  </si>
+  <si>
+    <t>BERMUDA CORRE FORÇA 5 M</t>
+  </si>
+  <si>
+    <t>OIWST26153_LIRIO</t>
+  </si>
+  <si>
+    <t>OIWWT26307_TAPTRY</t>
+  </si>
+  <si>
+    <t>OICR261714</t>
+  </si>
+  <si>
+    <t>BONÉ CORRE FOCO</t>
+  </si>
+  <si>
+    <t>OIWWT26307_LIRIO</t>
+  </si>
+  <si>
+    <t>cc</t>
+  </si>
+  <si>
+    <t>FLPSPT</t>
+  </si>
+  <si>
+    <t>OIWWT25115_TAPTRY</t>
+  </si>
+  <si>
+    <t>OIUSC26191</t>
+  </si>
+  <si>
+    <t>MANGUITO CORRE FOCO</t>
+  </si>
+  <si>
+    <t>OIMWT26618_SILGRE</t>
+  </si>
+  <si>
+    <t>OIMWT26619_SILGRE</t>
+  </si>
+  <si>
+    <t>OIUR261920</t>
+  </si>
+  <si>
+    <t>MEIA CORRE FOCO 33/44</t>
+  </si>
+  <si>
+    <t>FLRPTO</t>
+  </si>
+  <si>
+    <t>OIMWT26719_SILGRE</t>
+  </si>
+  <si>
+    <t>CREPTO</t>
+  </si>
+  <si>
+    <t>OIMWT22304_SILGRE</t>
+  </si>
+  <si>
+    <t>OIMST22309_SILGRE</t>
+  </si>
+  <si>
+    <t>OBWA261922</t>
+  </si>
+  <si>
+    <t>MEIA CORRE ADPT 33/38</t>
+  </si>
+  <si>
+    <t>VCOWMH</t>
+  </si>
+  <si>
+    <t>OIMWT25114_SILGRE</t>
+  </si>
+  <si>
+    <t>OWALPT</t>
+  </si>
+  <si>
+    <t>OIMST26645_PRETO</t>
+  </si>
+  <si>
+    <t>PTOWAL</t>
+  </si>
+  <si>
+    <t>OIMST26645_SILGRE</t>
+  </si>
+  <si>
+    <t>COARPT</t>
+  </si>
+  <si>
+    <t>OIMST26645_TAPTRY</t>
+  </si>
+  <si>
+    <t>OBMA261923</t>
+  </si>
+  <si>
+    <t>MEIA CORRE ADPT 39/44</t>
+  </si>
+  <si>
+    <t>OIMWT25640_TAPTRY</t>
+  </si>
+  <si>
+    <t>OIMST25312_TAPTRY</t>
+  </si>
+  <si>
+    <t>OIWSL26635_PRETO</t>
+  </si>
+  <si>
+    <t>OIWSL26635_ARNITO</t>
+  </si>
+  <si>
+    <t>OIWST26168</t>
+  </si>
+  <si>
+    <t>TOP ESSENTIAL 2.0 F</t>
+  </si>
+  <si>
+    <t>OIMSL26638_PRETO</t>
+  </si>
+  <si>
+    <t>OIMSL26638_ARNITO</t>
+  </si>
+  <si>
+    <t>OIWST26153</t>
+  </si>
+  <si>
+    <t>LEGGING ESSENTIAL 2.0 F</t>
+  </si>
+  <si>
+    <t>OBWA231911_PTCAAL</t>
+  </si>
+  <si>
+    <t>OBWA231911_BCOVDA</t>
+  </si>
+  <si>
+    <t>OIMST26645</t>
+  </si>
+  <si>
+    <t>T-SHIRT BASIC LOGO MC M</t>
+  </si>
+  <si>
+    <t>OBWSR241921_BBABAB</t>
+  </si>
+  <si>
+    <t>OBWSR241921_BFCBPO</t>
+  </si>
+  <si>
+    <t>OBWA231912_PTCAAL</t>
+  </si>
+  <si>
+    <t>OIWSL26635</t>
+  </si>
+  <si>
+    <t>CAMISETA CORRE PISTA F</t>
+  </si>
+  <si>
+    <t>OBWA231912_BCOVDA</t>
+  </si>
+  <si>
+    <t>OBMSR241922_FBLBOB</t>
+  </si>
+  <si>
+    <t>OIMSL26638</t>
+  </si>
+  <si>
+    <t>CAMISETA CORRE PISTA M</t>
+  </si>
+  <si>
+    <t>OBMSR241922_BFCBPO</t>
   </si>
 </sst>
 </file>
@@ -4667,7 +5339,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R899"/>
+  <dimension ref="A1:R1009"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.7109375" bestFit="1" customWidth="1"/>
@@ -30733,7 +31405,7 @@
         <v>6</v>
       </c>
       <c r="L522" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M522" s="4"/>
       <c r="N522" s="4"/>
@@ -30777,7 +31449,7 @@
         <v>6</v>
       </c>
       <c r="L523" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M523" s="4"/>
       <c r="N523" s="4"/>
@@ -30821,7 +31493,7 @@
         <v>6</v>
       </c>
       <c r="L524" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M524" s="4"/>
       <c r="N524" s="4"/>
@@ -30865,7 +31537,7 @@
         <v>6</v>
       </c>
       <c r="L525" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M525" s="4"/>
       <c r="N525" s="4"/>
@@ -30953,7 +31625,7 @@
         <v>6</v>
       </c>
       <c r="L527" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M527" s="4"/>
       <c r="N527" s="4"/>
@@ -31129,7 +31801,7 @@
         <v>6</v>
       </c>
       <c r="L531" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M531" s="4"/>
       <c r="N531" s="4"/>
@@ -31217,7 +31889,7 @@
         <v>6</v>
       </c>
       <c r="L533" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M533" s="4"/>
       <c r="N533" s="4"/>
@@ -31261,7 +31933,7 @@
         <v>6</v>
       </c>
       <c r="L534" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M534" s="4"/>
       <c r="N534" s="4"/>
@@ -31305,7 +31977,7 @@
         <v>6</v>
       </c>
       <c r="L535" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M535" s="4"/>
       <c r="N535" s="4"/>
@@ -31349,7 +32021,7 @@
         <v>6</v>
       </c>
       <c r="L536" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M536" s="4"/>
       <c r="N536" s="4"/>
@@ -31393,7 +32065,7 @@
         <v>6</v>
       </c>
       <c r="L537" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M537" s="4"/>
       <c r="N537" s="4"/>
@@ -31437,7 +32109,7 @@
         <v>6</v>
       </c>
       <c r="L538" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M538" s="4"/>
       <c r="N538" s="4"/>
@@ -31525,7 +32197,7 @@
         <v>6</v>
       </c>
       <c r="L540" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M540" s="4"/>
       <c r="N540" s="4"/>
@@ -31569,7 +32241,7 @@
         <v>6</v>
       </c>
       <c r="L541" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M541" s="4"/>
       <c r="N541" s="4"/>
@@ -31613,7 +32285,7 @@
         <v>6</v>
       </c>
       <c r="L542" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M542" s="4"/>
       <c r="N542" s="4"/>
@@ -31789,7 +32461,7 @@
         <v>6</v>
       </c>
       <c r="L546" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M546" s="4"/>
       <c r="N546" s="4"/>
@@ -31833,7 +32505,7 @@
         <v>6</v>
       </c>
       <c r="L547" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M547" s="4"/>
       <c r="N547" s="4"/>
@@ -31877,7 +32549,7 @@
         <v>6</v>
       </c>
       <c r="L548" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M548" s="4"/>
       <c r="N548" s="4"/>
@@ -31921,7 +32593,7 @@
         <v>6</v>
       </c>
       <c r="L549" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M549" s="4"/>
       <c r="N549" s="4"/>
@@ -32053,7 +32725,7 @@
         <v>6</v>
       </c>
       <c r="L552" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M552" s="4"/>
       <c r="N552" s="4"/>
@@ -32141,7 +32813,7 @@
         <v>6</v>
       </c>
       <c r="L554" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M554" s="4"/>
       <c r="N554" s="4"/>
@@ -32317,7 +32989,7 @@
         <v>6</v>
       </c>
       <c r="L558" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M558" s="4"/>
       <c r="N558" s="4"/>
@@ -32361,7 +33033,7 @@
         <v>6</v>
       </c>
       <c r="L559" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M559" s="4"/>
       <c r="N559" s="4"/>
@@ -32405,7 +33077,7 @@
         <v>6</v>
       </c>
       <c r="L560" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M560" s="4"/>
       <c r="N560" s="4"/>
@@ -32449,7 +33121,7 @@
         <v>6</v>
       </c>
       <c r="L561" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M561" s="4"/>
       <c r="N561" s="4"/>
@@ -32493,7 +33165,7 @@
         <v>6</v>
       </c>
       <c r="L562" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M562" s="4"/>
       <c r="N562" s="4"/>
@@ -32537,7 +33209,7 @@
         <v>6</v>
       </c>
       <c r="L563" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M563" s="4"/>
       <c r="N563" s="4"/>
@@ -32581,7 +33253,7 @@
         <v>6</v>
       </c>
       <c r="L564" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M564" s="4"/>
       <c r="N564" s="4"/>
@@ -32669,7 +33341,7 @@
         <v>6</v>
       </c>
       <c r="L566" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M566" s="4"/>
       <c r="N566" s="4"/>
@@ -32889,7 +33561,7 @@
         <v>6</v>
       </c>
       <c r="L571" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M571" s="4"/>
       <c r="N571" s="4"/>
@@ -32933,7 +33605,7 @@
         <v>6</v>
       </c>
       <c r="L572" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M572" s="4"/>
       <c r="N572" s="4"/>
@@ -33021,7 +33693,7 @@
         <v>6</v>
       </c>
       <c r="L574" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M574" s="4"/>
       <c r="N574" s="4"/>
@@ -33065,7 +33737,7 @@
         <v>6</v>
       </c>
       <c r="L575" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M575" s="4"/>
       <c r="N575" s="4"/>
@@ -33109,7 +33781,7 @@
         <v>6</v>
       </c>
       <c r="L576" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M576" s="4"/>
       <c r="N576" s="4"/>
@@ -33153,7 +33825,7 @@
         <v>6</v>
       </c>
       <c r="L577" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M577" s="4"/>
       <c r="N577" s="4"/>
@@ -33197,7 +33869,7 @@
         <v>6</v>
       </c>
       <c r="L578" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M578" s="4"/>
       <c r="N578" s="4"/>
@@ -33241,7 +33913,7 @@
         <v>6</v>
       </c>
       <c r="L579" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M579" s="4"/>
       <c r="N579" s="4"/>
@@ -33285,7 +33957,7 @@
         <v>6</v>
       </c>
       <c r="L580" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M580" s="4"/>
       <c r="N580" s="4"/>
@@ -33329,7 +34001,7 @@
         <v>6</v>
       </c>
       <c r="L581" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M581" s="4"/>
       <c r="N581" s="4"/>
@@ -33373,7 +34045,7 @@
         <v>6</v>
       </c>
       <c r="L582" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M582" s="4"/>
       <c r="N582" s="4"/>
@@ -33417,7 +34089,7 @@
         <v>6</v>
       </c>
       <c r="L583" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M583" s="4"/>
       <c r="N583" s="4"/>
@@ -33461,7 +34133,7 @@
         <v>6</v>
       </c>
       <c r="L584" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M584" s="4"/>
       <c r="N584" s="4"/>
@@ -33505,7 +34177,7 @@
         <v>6</v>
       </c>
       <c r="L585" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M585" s="4"/>
       <c r="N585" s="4"/>
@@ -33549,7 +34221,7 @@
         <v>6</v>
       </c>
       <c r="L586" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M586" s="4"/>
       <c r="N586" s="4"/>
@@ -33593,7 +34265,7 @@
         <v>6</v>
       </c>
       <c r="L587" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M587" s="4"/>
       <c r="N587" s="4"/>
@@ -33637,7 +34309,7 @@
         <v>6</v>
       </c>
       <c r="L588" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M588" s="4"/>
       <c r="N588" s="4"/>
@@ -33681,7 +34353,7 @@
         <v>6</v>
       </c>
       <c r="L589" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M589" s="4"/>
       <c r="N589" s="4"/>
@@ -33725,7 +34397,7 @@
         <v>6</v>
       </c>
       <c r="L590" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M590" s="4"/>
       <c r="N590" s="4"/>
@@ -33769,7 +34441,7 @@
         <v>6</v>
       </c>
       <c r="L591" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M591" s="4"/>
       <c r="N591" s="4"/>
@@ -33813,7 +34485,7 @@
         <v>6</v>
       </c>
       <c r="L592" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M592" s="4"/>
       <c r="N592" s="4"/>
@@ -33857,7 +34529,7 @@
         <v>6</v>
       </c>
       <c r="L593" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M593" s="4"/>
       <c r="N593" s="4"/>
@@ -33901,7 +34573,7 @@
         <v>6</v>
       </c>
       <c r="L594" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M594" s="4"/>
       <c r="N594" s="4"/>
@@ -33945,7 +34617,7 @@
         <v>6</v>
       </c>
       <c r="L595" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M595" s="4"/>
       <c r="N595" s="4"/>
@@ -33989,7 +34661,7 @@
         <v>6</v>
       </c>
       <c r="L596" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M596" s="4"/>
       <c r="N596" s="4"/>
@@ -34033,7 +34705,7 @@
         <v>6</v>
       </c>
       <c r="L597" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M597" s="4"/>
       <c r="N597" s="4"/>
@@ -34077,7 +34749,7 @@
         <v>6</v>
       </c>
       <c r="L598" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M598" s="4"/>
       <c r="N598" s="4"/>
@@ -34209,7 +34881,7 @@
         <v>6</v>
       </c>
       <c r="L601" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M601" s="4"/>
       <c r="N601" s="4"/>
@@ -34253,7 +34925,7 @@
         <v>6</v>
       </c>
       <c r="L602" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M602" s="4"/>
       <c r="N602" s="4"/>
@@ -34341,7 +35013,7 @@
         <v>6</v>
       </c>
       <c r="L604" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M604" s="4"/>
       <c r="N604" s="4"/>
@@ -34385,7 +35057,7 @@
         <v>6</v>
       </c>
       <c r="L605" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M605" s="4"/>
       <c r="N605" s="4"/>
@@ -34429,7 +35101,7 @@
         <v>6</v>
       </c>
       <c r="L606" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M606" s="4"/>
       <c r="N606" s="4"/>
@@ -34473,7 +35145,7 @@
         <v>6</v>
       </c>
       <c r="L607" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M607" s="4"/>
       <c r="N607" s="4"/>
@@ -34517,7 +35189,7 @@
         <v>6</v>
       </c>
       <c r="L608" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M608" s="4"/>
       <c r="N608" s="4"/>
@@ -34561,7 +35233,7 @@
         <v>6</v>
       </c>
       <c r="L609" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M609" s="4"/>
       <c r="N609" s="4"/>
@@ -34605,7 +35277,7 @@
         <v>6</v>
       </c>
       <c r="L610" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M610" s="4"/>
       <c r="N610" s="4"/>
@@ -34649,7 +35321,7 @@
         <v>6</v>
       </c>
       <c r="L611" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M611" s="4"/>
       <c r="N611" s="4"/>
@@ -34693,7 +35365,7 @@
         <v>6</v>
       </c>
       <c r="L612" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M612" s="4"/>
       <c r="N612" s="4"/>
@@ -34737,7 +35409,7 @@
         <v>6</v>
       </c>
       <c r="L613" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M613" s="4"/>
       <c r="N613" s="4"/>
@@ -34781,7 +35453,7 @@
         <v>6</v>
       </c>
       <c r="L614" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M614" s="4"/>
       <c r="N614" s="4"/>
@@ -34825,7 +35497,7 @@
         <v>6</v>
       </c>
       <c r="L615" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M615" s="4"/>
       <c r="N615" s="4"/>
@@ -34869,7 +35541,7 @@
         <v>6</v>
       </c>
       <c r="L616" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M616" s="4"/>
       <c r="N616" s="4"/>
@@ -34913,7 +35585,7 @@
         <v>6</v>
       </c>
       <c r="L617" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M617" s="4"/>
       <c r="N617" s="4"/>
@@ -34957,7 +35629,7 @@
         <v>6</v>
       </c>
       <c r="L618" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M618" s="4"/>
       <c r="N618" s="4"/>
@@ -35001,7 +35673,7 @@
         <v>6</v>
       </c>
       <c r="L619" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M619" s="4"/>
       <c r="N619" s="4"/>
@@ -35045,7 +35717,7 @@
         <v>6</v>
       </c>
       <c r="L620" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M620" s="4"/>
       <c r="N620" s="4"/>
@@ -35089,7 +35761,7 @@
         <v>6</v>
       </c>
       <c r="L621" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M621" s="4"/>
       <c r="N621" s="4"/>
@@ -35133,7 +35805,7 @@
         <v>6</v>
       </c>
       <c r="L622" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M622" s="4"/>
       <c r="N622" s="4"/>
@@ -35177,7 +35849,7 @@
         <v>6</v>
       </c>
       <c r="L623" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M623" s="4"/>
       <c r="N623" s="4"/>
@@ -35221,7 +35893,7 @@
         <v>6</v>
       </c>
       <c r="L624" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M624" s="4"/>
       <c r="N624" s="4"/>
@@ -35265,7 +35937,7 @@
         <v>6</v>
       </c>
       <c r="L625" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M625" s="4"/>
       <c r="N625" s="4"/>
@@ -35309,7 +35981,7 @@
         <v>6</v>
       </c>
       <c r="L626" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M626" s="4"/>
       <c r="N626" s="4"/>
@@ -35353,7 +36025,7 @@
         <v>6</v>
       </c>
       <c r="L627" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M627" s="4"/>
       <c r="N627" s="4"/>
@@ -35397,7 +36069,7 @@
         <v>6</v>
       </c>
       <c r="L628" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M628" s="4"/>
       <c r="N628" s="4"/>
@@ -37553,7 +38225,7 @@
         <v>6</v>
       </c>
       <c r="L677" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M677" s="4"/>
       <c r="N677" s="4"/>
@@ -37641,7 +38313,7 @@
         <v>6</v>
       </c>
       <c r="L679" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M679" s="4"/>
       <c r="N679" s="4"/>
@@ -37685,7 +38357,7 @@
         <v>6</v>
       </c>
       <c r="L680" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M680" s="4"/>
       <c r="N680" s="4"/>
@@ -37773,7 +38445,7 @@
         <v>6</v>
       </c>
       <c r="L682" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M682" s="4"/>
       <c r="N682" s="4"/>
@@ -37817,7 +38489,7 @@
         <v>6</v>
       </c>
       <c r="L683" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M683" s="4"/>
       <c r="N683" s="4"/>
@@ -37861,7 +38533,7 @@
         <v>6</v>
       </c>
       <c r="L684" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M684" s="4"/>
       <c r="N684" s="4"/>
@@ -37993,7 +38665,7 @@
         <v>6</v>
       </c>
       <c r="L687" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M687" s="4"/>
       <c r="N687" s="4"/>
@@ -38037,7 +38709,7 @@
         <v>6</v>
       </c>
       <c r="L688" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M688" s="4"/>
       <c r="N688" s="4"/>
@@ -38081,7 +38753,7 @@
         <v>6</v>
       </c>
       <c r="L689" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M689" s="4"/>
       <c r="N689" s="4"/>
@@ -38125,7 +38797,7 @@
         <v>6</v>
       </c>
       <c r="L690" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M690" s="4"/>
       <c r="N690" s="4"/>
@@ -38169,7 +38841,7 @@
         <v>6</v>
       </c>
       <c r="L691" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M691" s="4"/>
       <c r="N691" s="4"/>
@@ -38257,7 +38929,7 @@
         <v>6</v>
       </c>
       <c r="L693" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M693" s="4"/>
       <c r="N693" s="4"/>
@@ -38301,7 +38973,7 @@
         <v>6</v>
       </c>
       <c r="L694" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M694" s="4"/>
       <c r="N694" s="4"/>
@@ -38345,7 +39017,7 @@
         <v>6</v>
       </c>
       <c r="L695" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M695" s="4"/>
       <c r="N695" s="4"/>
@@ -38477,7 +39149,7 @@
         <v>6</v>
       </c>
       <c r="L698" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M698" s="4"/>
       <c r="N698" s="4"/>
@@ -38565,7 +39237,7 @@
         <v>6</v>
       </c>
       <c r="L700" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M700" s="4"/>
       <c r="N700" s="4"/>
@@ -38609,7 +39281,7 @@
         <v>6</v>
       </c>
       <c r="L701" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M701" s="4"/>
       <c r="N701" s="4"/>
@@ -38653,7 +39325,7 @@
         <v>6</v>
       </c>
       <c r="L702" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M702" s="4"/>
       <c r="N702" s="4"/>
@@ -38741,7 +39413,7 @@
         <v>6</v>
       </c>
       <c r="L704" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M704" s="4"/>
       <c r="N704" s="4"/>
@@ -38829,7 +39501,7 @@
         <v>6</v>
       </c>
       <c r="L706" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M706" s="4"/>
       <c r="N706" s="4"/>
@@ -38873,7 +39545,7 @@
         <v>6</v>
       </c>
       <c r="L707" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M707" s="4"/>
       <c r="N707" s="4"/>
@@ -39005,7 +39677,7 @@
         <v>6</v>
       </c>
       <c r="L710" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M710" s="4"/>
       <c r="N710" s="4"/>
@@ -39049,7 +39721,7 @@
         <v>6</v>
       </c>
       <c r="L711" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M711" s="4"/>
       <c r="N711" s="4"/>
@@ -39137,7 +39809,7 @@
         <v>6</v>
       </c>
       <c r="L713" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M713" s="4"/>
       <c r="N713" s="4"/>
@@ -39181,7 +39853,7 @@
         <v>6</v>
       </c>
       <c r="L714" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M714" s="4"/>
       <c r="N714" s="4"/>
@@ -39225,7 +39897,7 @@
         <v>6</v>
       </c>
       <c r="L715" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M715" s="4"/>
       <c r="N715" s="4"/>
@@ -39269,7 +39941,7 @@
         <v>6</v>
       </c>
       <c r="L716" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M716" s="4"/>
       <c r="N716" s="4"/>
@@ -39313,7 +39985,7 @@
         <v>6</v>
       </c>
       <c r="L717" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M717" s="4"/>
       <c r="N717" s="4"/>
@@ -39357,7 +40029,7 @@
         <v>6</v>
       </c>
       <c r="L718" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M718" s="4"/>
       <c r="N718" s="4"/>
@@ -39401,7 +40073,7 @@
         <v>6</v>
       </c>
       <c r="L719" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M719" s="4"/>
       <c r="N719" s="4"/>
@@ -39445,7 +40117,7 @@
         <v>6</v>
       </c>
       <c r="L720" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M720" s="4"/>
       <c r="N720" s="4"/>
@@ -39489,7 +40161,7 @@
         <v>6</v>
       </c>
       <c r="L721" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M721" s="4"/>
       <c r="N721" s="4"/>
@@ -39533,7 +40205,7 @@
         <v>6</v>
       </c>
       <c r="L722" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M722" s="4"/>
       <c r="N722" s="4"/>
@@ -39577,7 +40249,7 @@
         <v>6</v>
       </c>
       <c r="L723" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M723" s="4"/>
       <c r="N723" s="4"/>
@@ -39621,7 +40293,7 @@
         <v>6</v>
       </c>
       <c r="L724" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M724" s="4"/>
       <c r="N724" s="4"/>
@@ -39753,7 +40425,7 @@
         <v>6</v>
       </c>
       <c r="L727" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M727" s="4"/>
       <c r="N727" s="4"/>
@@ -39797,7 +40469,7 @@
         <v>6</v>
       </c>
       <c r="L728" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M728" s="4"/>
       <c r="N728" s="4"/>
@@ -39841,7 +40513,7 @@
         <v>6</v>
       </c>
       <c r="L729" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M729" s="4"/>
       <c r="N729" s="4"/>
@@ -39885,7 +40557,7 @@
         <v>6</v>
       </c>
       <c r="L730" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M730" s="4"/>
       <c r="N730" s="4"/>
@@ -40237,7 +40909,7 @@
         <v>6</v>
       </c>
       <c r="L738" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M738" s="4"/>
       <c r="N738" s="4"/>
@@ -40281,7 +40953,7 @@
         <v>6</v>
       </c>
       <c r="L739" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M739" s="4"/>
       <c r="N739" s="4"/>
@@ -40325,7 +40997,7 @@
         <v>6</v>
       </c>
       <c r="L740" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M740" s="4"/>
       <c r="N740" s="4"/>
@@ -40369,7 +41041,7 @@
         <v>6</v>
       </c>
       <c r="L741" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M741" s="4"/>
       <c r="N741" s="4"/>
@@ -40809,7 +41481,7 @@
         <v>6</v>
       </c>
       <c r="L751" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M751" s="4"/>
       <c r="N751" s="4"/>
@@ -40853,7 +41525,7 @@
         <v>6</v>
       </c>
       <c r="L752" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M752" s="4"/>
       <c r="N752" s="4"/>
@@ -40897,7 +41569,7 @@
         <v>6</v>
       </c>
       <c r="L753" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M753" s="4"/>
       <c r="N753" s="4"/>
@@ -40941,7 +41613,7 @@
         <v>6</v>
       </c>
       <c r="L754" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M754" s="4"/>
       <c r="N754" s="4"/>
@@ -40985,7 +41657,7 @@
         <v>6</v>
       </c>
       <c r="L755" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M755" s="4"/>
       <c r="N755" s="4"/>
@@ -41073,7 +41745,7 @@
         <v>6</v>
       </c>
       <c r="L757" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M757" s="4"/>
       <c r="N757" s="4"/>
@@ -41117,7 +41789,7 @@
         <v>6</v>
       </c>
       <c r="L758" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M758" s="4"/>
       <c r="N758" s="4"/>
@@ -41161,7 +41833,7 @@
         <v>6</v>
       </c>
       <c r="L759" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M759" s="4"/>
       <c r="N759" s="4"/>
@@ -41205,7 +41877,7 @@
         <v>6</v>
       </c>
       <c r="L760" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M760" s="4"/>
       <c r="N760" s="4"/>
@@ -41249,7 +41921,7 @@
         <v>6</v>
       </c>
       <c r="L761" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M761" s="4"/>
       <c r="N761" s="4"/>
@@ -41293,7 +41965,7 @@
         <v>6</v>
       </c>
       <c r="L762" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M762" s="4"/>
       <c r="N762" s="4"/>
@@ -41381,7 +42053,7 @@
         <v>6</v>
       </c>
       <c r="L764" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M764" s="4"/>
       <c r="N764" s="4"/>
@@ -41513,7 +42185,7 @@
         <v>6</v>
       </c>
       <c r="L767" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M767" s="4"/>
       <c r="N767" s="4"/>
@@ -41557,7 +42229,7 @@
         <v>6</v>
       </c>
       <c r="L768" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M768" s="4"/>
       <c r="N768" s="4"/>
@@ -41601,7 +42273,7 @@
         <v>6</v>
       </c>
       <c r="L769" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M769" s="4"/>
       <c r="N769" s="4"/>
@@ -41645,7 +42317,7 @@
         <v>6</v>
       </c>
       <c r="L770" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M770" s="4"/>
       <c r="N770" s="4"/>
@@ -41689,7 +42361,7 @@
         <v>6</v>
       </c>
       <c r="L771" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M771" s="4"/>
       <c r="N771" s="4"/>
@@ -41733,7 +42405,7 @@
         <v>6</v>
       </c>
       <c r="L772" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M772" s="4"/>
       <c r="N772" s="4"/>
@@ -41865,7 +42537,7 @@
         <v>6</v>
       </c>
       <c r="L775" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M775" s="4"/>
       <c r="N775" s="4"/>
@@ -41909,7 +42581,7 @@
         <v>6</v>
       </c>
       <c r="L776" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M776" s="4"/>
       <c r="N776" s="4"/>
@@ -41953,7 +42625,7 @@
         <v>6</v>
       </c>
       <c r="L777" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M777" s="4"/>
       <c r="N777" s="4"/>
@@ -41997,7 +42669,7 @@
         <v>6</v>
       </c>
       <c r="L778" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M778" s="4"/>
       <c r="N778" s="4"/>
@@ -42041,7 +42713,7 @@
         <v>6</v>
       </c>
       <c r="L779" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M779" s="4"/>
       <c r="N779" s="4"/>
@@ -42085,7 +42757,7 @@
         <v>6</v>
       </c>
       <c r="L780" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M780" s="4"/>
       <c r="N780" s="4"/>
@@ -42129,7 +42801,7 @@
         <v>6</v>
       </c>
       <c r="L781" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M781" s="4"/>
       <c r="N781" s="4"/>
@@ -42437,7 +43109,7 @@
         <v>6</v>
       </c>
       <c r="L788" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M788" s="4"/>
       <c r="N788" s="4"/>
@@ -42481,7 +43153,7 @@
         <v>6</v>
       </c>
       <c r="L789" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M789" s="4"/>
       <c r="N789" s="4"/>
@@ -42525,7 +43197,7 @@
         <v>6</v>
       </c>
       <c r="L790" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M790" s="4"/>
       <c r="N790" s="4"/>
@@ -42569,7 +43241,7 @@
         <v>6</v>
       </c>
       <c r="L791" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M791" s="4"/>
       <c r="N791" s="4"/>
@@ -42657,7 +43329,7 @@
         <v>6</v>
       </c>
       <c r="L793" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M793" s="4"/>
       <c r="N793" s="4"/>
@@ -42701,7 +43373,7 @@
         <v>6</v>
       </c>
       <c r="L794" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M794" s="4"/>
       <c r="N794" s="4"/>
@@ -42745,7 +43417,7 @@
         <v>6</v>
       </c>
       <c r="L795" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M795" s="4"/>
       <c r="N795" s="4"/>
@@ -42789,7 +43461,7 @@
         <v>6</v>
       </c>
       <c r="L796" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M796" s="4"/>
       <c r="N796" s="4"/>
@@ -42833,7 +43505,7 @@
         <v>6</v>
       </c>
       <c r="L797" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M797" s="4"/>
       <c r="N797" s="4"/>
@@ -42877,7 +43549,7 @@
         <v>6</v>
       </c>
       <c r="L798" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M798" s="4"/>
       <c r="N798" s="4"/>
@@ -42921,7 +43593,7 @@
         <v>6</v>
       </c>
       <c r="L799" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M799" s="4"/>
       <c r="N799" s="4"/>
@@ -42965,7 +43637,7 @@
         <v>6</v>
       </c>
       <c r="L800" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M800" s="4"/>
       <c r="N800" s="4"/>
@@ -43009,7 +43681,7 @@
         <v>6</v>
       </c>
       <c r="L801" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M801" s="4"/>
       <c r="N801" s="4"/>
@@ -43053,7 +43725,7 @@
         <v>6</v>
       </c>
       <c r="L802" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M802" s="4"/>
       <c r="N802" s="4"/>
@@ -43097,7 +43769,7 @@
         <v>6</v>
       </c>
       <c r="L803" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M803" s="4"/>
       <c r="N803" s="4"/>
@@ -43185,7 +43857,7 @@
         <v>6</v>
       </c>
       <c r="L805" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M805" s="4"/>
       <c r="N805" s="4"/>
@@ -43229,7 +43901,7 @@
         <v>6</v>
       </c>
       <c r="L806" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M806" s="4"/>
       <c r="N806" s="4"/>
@@ -43273,7 +43945,7 @@
         <v>6</v>
       </c>
       <c r="L807" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M807" s="4"/>
       <c r="N807" s="4"/>
@@ -43317,7 +43989,7 @@
         <v>6</v>
       </c>
       <c r="L808" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M808" s="4"/>
       <c r="N808" s="4"/>
@@ -43405,7 +44077,7 @@
         <v>6</v>
       </c>
       <c r="L810" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M810" s="4"/>
       <c r="N810" s="4"/>
@@ -43449,7 +44121,7 @@
         <v>6</v>
       </c>
       <c r="L811" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M811" s="4"/>
       <c r="N811" s="4"/>
@@ -43493,7 +44165,7 @@
         <v>6</v>
       </c>
       <c r="L812" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M812" s="4"/>
       <c r="N812" s="4"/>
@@ -43537,7 +44209,7 @@
         <v>6</v>
       </c>
       <c r="L813" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M813" s="4"/>
       <c r="N813" s="4"/>
@@ -43581,7 +44253,7 @@
         <v>6</v>
       </c>
       <c r="L814" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M814" s="4"/>
       <c r="N814" s="4"/>
@@ -43625,7 +44297,7 @@
         <v>6</v>
       </c>
       <c r="L815" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M815" s="4"/>
       <c r="N815" s="4"/>
@@ -43669,7 +44341,7 @@
         <v>6</v>
       </c>
       <c r="L816" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M816" s="4"/>
       <c r="N816" s="4"/>
@@ -43757,7 +44429,7 @@
         <v>6</v>
       </c>
       <c r="L818" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M818" s="4"/>
       <c r="N818" s="4"/>
@@ -43801,7 +44473,7 @@
         <v>6</v>
       </c>
       <c r="L819" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M819" s="4"/>
       <c r="N819" s="4"/>
@@ -43845,7 +44517,7 @@
         <v>6</v>
       </c>
       <c r="L820" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M820" s="4"/>
       <c r="N820" s="4"/>
@@ -43889,7 +44561,7 @@
         <v>6</v>
       </c>
       <c r="L821" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M821" s="4"/>
       <c r="N821" s="4"/>
@@ -43933,7 +44605,7 @@
         <v>6</v>
       </c>
       <c r="L822" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M822" s="4"/>
       <c r="N822" s="4"/>
@@ -43977,7 +44649,7 @@
         <v>6</v>
       </c>
       <c r="L823" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M823" s="4"/>
       <c r="N823" s="4"/>
@@ -44021,7 +44693,7 @@
         <v>6</v>
       </c>
       <c r="L824" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M824" s="4"/>
       <c r="N824" s="4"/>
@@ -44153,7 +44825,7 @@
         <v>6</v>
       </c>
       <c r="L827" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M827" s="4"/>
       <c r="N827" s="4"/>
@@ -44285,7 +44957,7 @@
         <v>6</v>
       </c>
       <c r="L830" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M830" s="4"/>
       <c r="N830" s="4"/>
@@ -44329,7 +45001,7 @@
         <v>6</v>
       </c>
       <c r="L831" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M831" s="4"/>
       <c r="N831" s="4"/>
@@ -44373,7 +45045,7 @@
         <v>6</v>
       </c>
       <c r="L832" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M832" s="4"/>
       <c r="N832" s="4"/>
@@ -44505,7 +45177,7 @@
         <v>6</v>
       </c>
       <c r="L835" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M835" s="4"/>
       <c r="N835" s="4"/>
@@ -44549,7 +45221,7 @@
         <v>6</v>
       </c>
       <c r="L836" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M836" s="4"/>
       <c r="N836" s="4"/>
@@ -44593,7 +45265,7 @@
         <v>6</v>
       </c>
       <c r="L837" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M837" s="4"/>
       <c r="N837" s="4"/>
@@ -44637,7 +45309,7 @@
         <v>6</v>
       </c>
       <c r="L838" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M838" s="4"/>
       <c r="N838" s="4"/>
@@ -44681,7 +45353,7 @@
         <v>6</v>
       </c>
       <c r="L839" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M839" s="4"/>
       <c r="N839" s="4"/>
@@ -44725,7 +45397,7 @@
         <v>6</v>
       </c>
       <c r="L840" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M840" s="4"/>
       <c r="N840" s="4"/>
@@ -44769,7 +45441,7 @@
         <v>6</v>
       </c>
       <c r="L841" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M841" s="4"/>
       <c r="N841" s="4"/>
@@ -44813,7 +45485,7 @@
         <v>6</v>
       </c>
       <c r="L842" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M842" s="4"/>
       <c r="N842" s="4"/>
@@ -44857,7 +45529,7 @@
         <v>6</v>
       </c>
       <c r="L843" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M843" s="4"/>
       <c r="N843" s="4"/>
@@ -44901,7 +45573,7 @@
         <v>6</v>
       </c>
       <c r="L844" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M844" s="4"/>
       <c r="N844" s="4"/>
@@ -44945,7 +45617,7 @@
         <v>6</v>
       </c>
       <c r="L845" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M845" s="4"/>
       <c r="N845" s="4"/>
@@ -44989,7 +45661,7 @@
         <v>6</v>
       </c>
       <c r="L846" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M846" s="4"/>
       <c r="N846" s="4"/>
@@ -45033,7 +45705,7 @@
         <v>6</v>
       </c>
       <c r="L847" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M847" s="4"/>
       <c r="N847" s="4"/>
@@ -45077,7 +45749,7 @@
         <v>6</v>
       </c>
       <c r="L848" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M848" s="4"/>
       <c r="N848" s="4"/>
@@ -45165,7 +45837,7 @@
         <v>6</v>
       </c>
       <c r="L850" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M850" s="4"/>
       <c r="N850" s="4"/>
@@ -45253,7 +45925,7 @@
         <v>6</v>
       </c>
       <c r="L852" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M852" s="4"/>
       <c r="N852" s="4"/>
@@ -45297,7 +45969,7 @@
         <v>6</v>
       </c>
       <c r="L853" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M853" s="4"/>
       <c r="N853" s="4"/>
@@ -45341,7 +46013,7 @@
         <v>6</v>
       </c>
       <c r="L854" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M854" s="4"/>
       <c r="N854" s="4"/>
@@ -45429,7 +46101,7 @@
         <v>6</v>
       </c>
       <c r="L856" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M856" s="4"/>
       <c r="N856" s="4"/>
@@ -45473,7 +46145,7 @@
         <v>6</v>
       </c>
       <c r="L857" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M857" s="4"/>
       <c r="N857" s="4"/>
@@ -45561,7 +46233,7 @@
         <v>6</v>
       </c>
       <c r="L859" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M859" s="4"/>
       <c r="N859" s="4"/>
@@ -45737,7 +46409,7 @@
         <v>6</v>
       </c>
       <c r="L863" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M863" s="4"/>
       <c r="N863" s="4"/>
@@ -45781,7 +46453,7 @@
         <v>6</v>
       </c>
       <c r="L864" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M864" s="4"/>
       <c r="N864" s="4"/>
@@ -45825,7 +46497,7 @@
         <v>6</v>
       </c>
       <c r="L865" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M865" s="4"/>
       <c r="N865" s="4"/>
@@ -45913,7 +46585,7 @@
         <v>6</v>
       </c>
       <c r="L867" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M867" s="4"/>
       <c r="N867" s="4"/>
@@ -45957,7 +46629,7 @@
         <v>6</v>
       </c>
       <c r="L868" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M868" s="4"/>
       <c r="N868" s="4"/>
@@ -46001,7 +46673,7 @@
         <v>6</v>
       </c>
       <c r="L869" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M869" s="4"/>
       <c r="N869" s="4"/>
@@ -46045,7 +46717,7 @@
         <v>6</v>
       </c>
       <c r="L870" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M870" s="4"/>
       <c r="N870" s="4"/>
@@ -46089,7 +46761,7 @@
         <v>6</v>
       </c>
       <c r="L871" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M871" s="4"/>
       <c r="N871" s="4"/>
@@ -46133,7 +46805,7 @@
         <v>6</v>
       </c>
       <c r="L872" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M872" s="4"/>
       <c r="N872" s="4"/>
@@ -46177,7 +46849,7 @@
         <v>6</v>
       </c>
       <c r="L873" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M873" s="4"/>
       <c r="N873" s="4"/>
@@ -46221,7 +46893,7 @@
         <v>6</v>
       </c>
       <c r="L874" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M874" s="4"/>
       <c r="N874" s="4"/>
@@ -46265,7 +46937,7 @@
         <v>6</v>
       </c>
       <c r="L875" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M875" s="4"/>
       <c r="N875" s="4"/>
@@ -46353,7 +47025,7 @@
         <v>6</v>
       </c>
       <c r="L877" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M877" s="4"/>
       <c r="N877" s="4"/>
@@ -46397,7 +47069,7 @@
         <v>6</v>
       </c>
       <c r="L878" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M878" s="4"/>
       <c r="N878" s="4"/>
@@ -46441,7 +47113,7 @@
         <v>6</v>
       </c>
       <c r="L879" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M879" s="4"/>
       <c r="N879" s="4"/>
@@ -46485,7 +47157,7 @@
         <v>6</v>
       </c>
       <c r="L880" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M880" s="4"/>
       <c r="N880" s="4"/>
@@ -46529,7 +47201,7 @@
         <v>6</v>
       </c>
       <c r="L881" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M881" s="4"/>
       <c r="N881" s="4"/>
@@ -46573,7 +47245,7 @@
         <v>6</v>
       </c>
       <c r="L882" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M882" s="4"/>
       <c r="N882" s="4"/>
@@ -46617,7 +47289,7 @@
         <v>6</v>
       </c>
       <c r="L883" s="4" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="M883" s="4"/>
       <c r="N883" s="4"/>
@@ -47330,6 +48002,4846 @@
       <c r="Q899" s="4"/>
       <c r="R899" s="4"/>
     </row>
+    <row r="900" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A900" s="2" t="s">
+        <v>1396</v>
+      </c>
+      <c r="B900" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="C900" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D900" s="4" t="s">
+        <v>895</v>
+      </c>
+      <c r="E900" s="5" t="s">
+        <v>1397</v>
+      </c>
+      <c r="F900" s="4" t="s">
+        <v>1390</v>
+      </c>
+      <c r="G900" s="4" t="s">
+        <v>1398</v>
+      </c>
+      <c r="H900" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I900" s="4">
+        <v>119.99</v>
+      </c>
+      <c r="J900" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K900" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="L900" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="M900" s="4"/>
+      <c r="N900" s="4"/>
+      <c r="O900" s="4"/>
+      <c r="P900" s="4"/>
+      <c r="Q900" s="4"/>
+      <c r="R900" s="4"/>
+    </row>
+    <row r="901" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A901" s="2" t="s">
+        <v>1399</v>
+      </c>
+      <c r="B901" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="C901" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D901" s="4" t="s">
+        <v>902</v>
+      </c>
+      <c r="E901" s="5" t="s">
+        <v>903</v>
+      </c>
+      <c r="F901" s="4" t="s">
+        <v>1390</v>
+      </c>
+      <c r="G901" s="4" t="s">
+        <v>1398</v>
+      </c>
+      <c r="H901" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I901" s="4">
+        <v>109.99</v>
+      </c>
+      <c r="J901" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K901" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="L901" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="M901" s="4"/>
+      <c r="N901" s="4"/>
+      <c r="O901" s="4"/>
+      <c r="P901" s="4"/>
+      <c r="Q901" s="4"/>
+      <c r="R901" s="4"/>
+    </row>
+    <row r="902" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A902" s="2" t="s">
+        <v>1400</v>
+      </c>
+      <c r="B902" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="C902" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D902" s="4" t="s">
+        <v>910</v>
+      </c>
+      <c r="E902" s="5" t="s">
+        <v>1401</v>
+      </c>
+      <c r="F902" s="4" t="s">
+        <v>1390</v>
+      </c>
+      <c r="G902" s="4" t="s">
+        <v>1402</v>
+      </c>
+      <c r="H902" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="I902" s="4">
+        <v>169.99</v>
+      </c>
+      <c r="J902" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K902" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="L902" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="M902" s="4"/>
+      <c r="N902" s="4"/>
+      <c r="O902" s="4"/>
+      <c r="P902" s="4"/>
+      <c r="Q902" s="4"/>
+      <c r="R902" s="4"/>
+    </row>
+    <row r="903" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A903" s="2" t="s">
+        <v>1403</v>
+      </c>
+      <c r="B903" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="C903" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D903" s="4" t="s">
+        <v>927</v>
+      </c>
+      <c r="E903" s="5" t="s">
+        <v>1404</v>
+      </c>
+      <c r="F903" s="4" t="s">
+        <v>1390</v>
+      </c>
+      <c r="G903" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="H903" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="I903" s="4">
+        <v>119.99</v>
+      </c>
+      <c r="J903" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K903" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="L903" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="M903" s="4"/>
+      <c r="N903" s="4"/>
+      <c r="O903" s="4"/>
+      <c r="P903" s="4"/>
+      <c r="Q903" s="4"/>
+      <c r="R903" s="4"/>
+    </row>
+    <row r="904" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A904" s="2" t="s">
+        <v>1406</v>
+      </c>
+      <c r="B904" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="C904" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D904" s="4" t="s">
+        <v>933</v>
+      </c>
+      <c r="E904" s="5" t="s">
+        <v>934</v>
+      </c>
+      <c r="F904" s="4" t="s">
+        <v>1390</v>
+      </c>
+      <c r="G904" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="H904" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="I904" s="4">
+        <v>109.99</v>
+      </c>
+      <c r="J904" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K904" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="L904" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="M904" s="4"/>
+      <c r="N904" s="4"/>
+      <c r="O904" s="4"/>
+      <c r="P904" s="4"/>
+      <c r="Q904" s="4"/>
+      <c r="R904" s="4"/>
+    </row>
+    <row r="905" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A905" s="2" t="s">
+        <v>1407</v>
+      </c>
+      <c r="B905" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="C905" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D905" s="4" t="s">
+        <v>1005</v>
+      </c>
+      <c r="E905" s="5" t="s">
+        <v>1006</v>
+      </c>
+      <c r="F905" s="4" t="s">
+        <v>1390</v>
+      </c>
+      <c r="G905" s="4" t="s">
+        <v>1408</v>
+      </c>
+      <c r="H905" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I905" s="4">
+        <v>119.99</v>
+      </c>
+      <c r="J905" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K905" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="L905" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="M905" s="4"/>
+      <c r="N905" s="4"/>
+      <c r="O905" s="4"/>
+      <c r="P905" s="4"/>
+      <c r="Q905" s="4"/>
+      <c r="R905" s="4"/>
+    </row>
+    <row r="906" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A906" s="2" t="s">
+        <v>1409</v>
+      </c>
+      <c r="B906" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="C906" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D906" s="4" t="s">
+        <v>1005</v>
+      </c>
+      <c r="E906" s="5" t="s">
+        <v>1006</v>
+      </c>
+      <c r="F906" s="4" t="s">
+        <v>1390</v>
+      </c>
+      <c r="G906" s="4" t="s">
+        <v>1410</v>
+      </c>
+      <c r="H906" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I906" s="4">
+        <v>119.99</v>
+      </c>
+      <c r="J906" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K906" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="L906" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="M906" s="4"/>
+      <c r="N906" s="4"/>
+      <c r="O906" s="4"/>
+      <c r="P906" s="4"/>
+      <c r="Q906" s="4"/>
+      <c r="R906" s="4"/>
+    </row>
+    <row r="907" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A907" s="2" t="s">
+        <v>1411</v>
+      </c>
+      <c r="B907" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="C907" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D907" s="4" t="s">
+        <v>1412</v>
+      </c>
+      <c r="E907" s="5" t="s">
+        <v>1413</v>
+      </c>
+      <c r="F907" s="4" t="s">
+        <v>1390</v>
+      </c>
+      <c r="G907" s="4" t="s">
+        <v>1408</v>
+      </c>
+      <c r="H907" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I907" s="4">
+        <v>149.99</v>
+      </c>
+      <c r="J907" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K907" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="L907" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="M907" s="4"/>
+      <c r="N907" s="4"/>
+      <c r="O907" s="4"/>
+      <c r="P907" s="4"/>
+      <c r="Q907" s="4"/>
+      <c r="R907" s="4"/>
+    </row>
+    <row r="908" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A908" s="2" t="s">
+        <v>1414</v>
+      </c>
+      <c r="B908" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="C908" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D908" s="4" t="s">
+        <v>1012</v>
+      </c>
+      <c r="E908" s="5" t="s">
+        <v>1013</v>
+      </c>
+      <c r="F908" s="4" t="s">
+        <v>1390</v>
+      </c>
+      <c r="G908" s="4" t="s">
+        <v>1408</v>
+      </c>
+      <c r="H908" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I908" s="4">
+        <v>159.99</v>
+      </c>
+      <c r="J908" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K908" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="L908" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="M908" s="4"/>
+      <c r="N908" s="4"/>
+      <c r="O908" s="4"/>
+      <c r="P908" s="4"/>
+      <c r="Q908" s="4"/>
+      <c r="R908" s="4"/>
+    </row>
+    <row r="909" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A909" s="2" t="s">
+        <v>1415</v>
+      </c>
+      <c r="B909" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="C909" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D909" s="4" t="s">
+        <v>1008</v>
+      </c>
+      <c r="E909" s="5" t="s">
+        <v>1416</v>
+      </c>
+      <c r="F909" s="4" t="s">
+        <v>1390</v>
+      </c>
+      <c r="G909" s="4" t="s">
+        <v>1408</v>
+      </c>
+      <c r="H909" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I909" s="4">
+        <v>139.99</v>
+      </c>
+      <c r="J909" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K909" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="L909" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="M909" s="4"/>
+      <c r="N909" s="4"/>
+      <c r="O909" s="4"/>
+      <c r="P909" s="4"/>
+      <c r="Q909" s="4"/>
+      <c r="R909" s="4"/>
+    </row>
+    <row r="910" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A910" s="2" t="s">
+        <v>1417</v>
+      </c>
+      <c r="B910" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="C910" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D910" s="4" t="s">
+        <v>1015</v>
+      </c>
+      <c r="E910" s="5" t="s">
+        <v>1016</v>
+      </c>
+      <c r="F910" s="4" t="s">
+        <v>1390</v>
+      </c>
+      <c r="G910" s="4" t="s">
+        <v>1418</v>
+      </c>
+      <c r="H910" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="I910" s="4">
+        <v>139.99</v>
+      </c>
+      <c r="J910" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K910" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="L910" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="M910" s="4"/>
+      <c r="N910" s="4"/>
+      <c r="O910" s="4"/>
+      <c r="P910" s="4"/>
+      <c r="Q910" s="4"/>
+      <c r="R910" s="4"/>
+    </row>
+    <row r="911" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A911" s="2" t="s">
+        <v>1419</v>
+      </c>
+      <c r="B911" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="C911" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D911" s="4" t="s">
+        <v>1015</v>
+      </c>
+      <c r="E911" s="5" t="s">
+        <v>1016</v>
+      </c>
+      <c r="F911" s="4" t="s">
+        <v>1390</v>
+      </c>
+      <c r="G911" s="4" t="s">
+        <v>1420</v>
+      </c>
+      <c r="H911" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="I911" s="4">
+        <v>139.99</v>
+      </c>
+      <c r="J911" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K911" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="L911" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="M911" s="4"/>
+      <c r="N911" s="4"/>
+      <c r="O911" s="4"/>
+      <c r="P911" s="4"/>
+      <c r="Q911" s="4"/>
+      <c r="R911" s="4"/>
+    </row>
+    <row r="912" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A912" s="2" t="s">
+        <v>1421</v>
+      </c>
+      <c r="B912" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="C912" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D912" s="4" t="s">
+        <v>1023</v>
+      </c>
+      <c r="E912" s="5" t="s">
+        <v>1422</v>
+      </c>
+      <c r="F912" s="4" t="s">
+        <v>1423</v>
+      </c>
+      <c r="G912" s="4" t="s">
+        <v>1408</v>
+      </c>
+      <c r="H912" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I912" s="4">
+        <v>99.99</v>
+      </c>
+      <c r="J912" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K912" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="L912" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="M912" s="4"/>
+      <c r="N912" s="4"/>
+      <c r="O912" s="4"/>
+      <c r="P912" s="4"/>
+      <c r="Q912" s="4"/>
+      <c r="R912" s="4"/>
+    </row>
+    <row r="913" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A913" s="2" t="s">
+        <v>1424</v>
+      </c>
+      <c r="B913" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="C913" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D913" s="4" t="s">
+        <v>1034</v>
+      </c>
+      <c r="E913" s="5" t="s">
+        <v>1425</v>
+      </c>
+      <c r="F913" s="4" t="s">
+        <v>1423</v>
+      </c>
+      <c r="G913" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="H913" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I913" s="4">
+        <v>89.99</v>
+      </c>
+      <c r="J913" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K913" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="L913" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="M913" s="4"/>
+      <c r="N913" s="4"/>
+      <c r="O913" s="4"/>
+      <c r="P913" s="4"/>
+      <c r="Q913" s="4"/>
+      <c r="R913" s="4"/>
+    </row>
+    <row r="914" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A914" s="2" t="s">
+        <v>1426</v>
+      </c>
+      <c r="B914" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="C914" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D914" s="4" t="s">
+        <v>1034</v>
+      </c>
+      <c r="E914" s="5" t="s">
+        <v>1425</v>
+      </c>
+      <c r="F914" s="4" t="s">
+        <v>1423</v>
+      </c>
+      <c r="G914" s="4" t="s">
+        <v>1408</v>
+      </c>
+      <c r="H914" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I914" s="4">
+        <v>89.99</v>
+      </c>
+      <c r="J914" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K914" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="L914" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="M914" s="4"/>
+      <c r="N914" s="4"/>
+      <c r="O914" s="4"/>
+      <c r="P914" s="4"/>
+      <c r="Q914" s="4"/>
+      <c r="R914" s="4"/>
+    </row>
+    <row r="915" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A915" s="2" t="s">
+        <v>1427</v>
+      </c>
+      <c r="B915" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="C915" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D915" s="4" t="s">
+        <v>1034</v>
+      </c>
+      <c r="E915" s="5" t="s">
+        <v>1425</v>
+      </c>
+      <c r="F915" s="4" t="s">
+        <v>1423</v>
+      </c>
+      <c r="G915" s="4" t="s">
+        <v>1410</v>
+      </c>
+      <c r="H915" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I915" s="4">
+        <v>89.99</v>
+      </c>
+      <c r="J915" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K915" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="L915" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="M915" s="4"/>
+      <c r="N915" s="4"/>
+      <c r="O915" s="4"/>
+      <c r="P915" s="4"/>
+      <c r="Q915" s="4"/>
+      <c r="R915" s="4"/>
+    </row>
+    <row r="916" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A916" s="2" t="s">
+        <v>1428</v>
+      </c>
+      <c r="B916" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="C916" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D916" s="4" t="s">
+        <v>1034</v>
+      </c>
+      <c r="E916" s="5" t="s">
+        <v>1425</v>
+      </c>
+      <c r="F916" s="4" t="s">
+        <v>1390</v>
+      </c>
+      <c r="G916" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="H916" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I916" s="4">
+        <v>89.99</v>
+      </c>
+      <c r="J916" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K916" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="L916" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="M916" s="4"/>
+      <c r="N916" s="4"/>
+      <c r="O916" s="4"/>
+      <c r="P916" s="4"/>
+      <c r="Q916" s="4"/>
+      <c r="R916" s="4"/>
+    </row>
+    <row r="917" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A917" s="2" t="s">
+        <v>1429</v>
+      </c>
+      <c r="B917" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="C917" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D917" s="4" t="s">
+        <v>1430</v>
+      </c>
+      <c r="E917" s="5" t="s">
+        <v>1431</v>
+      </c>
+      <c r="F917" s="4" t="s">
+        <v>1423</v>
+      </c>
+      <c r="G917" s="4" t="s">
+        <v>1408</v>
+      </c>
+      <c r="H917" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I917" s="4">
+        <v>79.989999999999995</v>
+      </c>
+      <c r="J917" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K917" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="L917" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="M917" s="4"/>
+      <c r="N917" s="4"/>
+      <c r="O917" s="4"/>
+      <c r="P917" s="4"/>
+      <c r="Q917" s="4"/>
+      <c r="R917" s="4"/>
+    </row>
+    <row r="918" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A918" s="2" t="s">
+        <v>1432</v>
+      </c>
+      <c r="B918" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="C918" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D918" s="4" t="s">
+        <v>1430</v>
+      </c>
+      <c r="E918" s="5" t="s">
+        <v>1431</v>
+      </c>
+      <c r="F918" s="4" t="s">
+        <v>1423</v>
+      </c>
+      <c r="G918" s="4" t="s">
+        <v>1410</v>
+      </c>
+      <c r="H918" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I918" s="4">
+        <v>79.989999999999995</v>
+      </c>
+      <c r="J918" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K918" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="L918" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="M918" s="4"/>
+      <c r="N918" s="4"/>
+      <c r="O918" s="4"/>
+      <c r="P918" s="4"/>
+      <c r="Q918" s="4"/>
+      <c r="R918" s="4"/>
+    </row>
+    <row r="919" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A919" s="2" t="s">
+        <v>1433</v>
+      </c>
+      <c r="B919" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="C919" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D919" s="4" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E919" s="5" t="s">
+        <v>1057</v>
+      </c>
+      <c r="F919" s="4" t="s">
+        <v>1390</v>
+      </c>
+      <c r="G919" s="4" t="s">
+        <v>1408</v>
+      </c>
+      <c r="H919" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I919" s="4">
+        <v>169.99</v>
+      </c>
+      <c r="J919" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K919" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="L919" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="M919" s="4"/>
+      <c r="N919" s="4"/>
+      <c r="O919" s="4"/>
+      <c r="P919" s="4"/>
+      <c r="Q919" s="4"/>
+      <c r="R919" s="4"/>
+    </row>
+    <row r="920" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A920" s="2" t="s">
+        <v>1434</v>
+      </c>
+      <c r="B920" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="C920" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D920" s="4" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E920" s="5" t="s">
+        <v>1057</v>
+      </c>
+      <c r="F920" s="4" t="s">
+        <v>1390</v>
+      </c>
+      <c r="G920" s="4" t="s">
+        <v>1410</v>
+      </c>
+      <c r="H920" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I920" s="4">
+        <v>169.99</v>
+      </c>
+      <c r="J920" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K920" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="L920" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="M920" s="4"/>
+      <c r="N920" s="4"/>
+      <c r="O920" s="4"/>
+      <c r="P920" s="4"/>
+      <c r="Q920" s="4"/>
+      <c r="R920" s="4"/>
+    </row>
+    <row r="921" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A921" s="2" t="s">
+        <v>1435</v>
+      </c>
+      <c r="B921" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="C921" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D921" s="4" t="s">
+        <v>1065</v>
+      </c>
+      <c r="E921" s="5" t="s">
+        <v>1436</v>
+      </c>
+      <c r="F921" s="4" t="s">
+        <v>1390</v>
+      </c>
+      <c r="G921" s="4" t="s">
+        <v>1408</v>
+      </c>
+      <c r="H921" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I921" s="4">
+        <v>199.99</v>
+      </c>
+      <c r="J921" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K921" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="L921" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="M921" s="4"/>
+      <c r="N921" s="4"/>
+      <c r="O921" s="4"/>
+      <c r="P921" s="4"/>
+      <c r="Q921" s="4"/>
+      <c r="R921" s="4"/>
+    </row>
+    <row r="922" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A922" s="2" t="s">
+        <v>1437</v>
+      </c>
+      <c r="B922" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="C922" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D922" s="4" t="s">
+        <v>1098</v>
+      </c>
+      <c r="E922" s="5" t="s">
+        <v>1438</v>
+      </c>
+      <c r="F922" s="4" t="s">
+        <v>1423</v>
+      </c>
+      <c r="G922" s="4" t="s">
+        <v>1439</v>
+      </c>
+      <c r="H922" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="I922" s="4">
+        <v>99.99</v>
+      </c>
+      <c r="J922" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K922" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="L922" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="M922" s="4"/>
+      <c r="N922" s="4"/>
+      <c r="O922" s="4"/>
+      <c r="P922" s="4"/>
+      <c r="Q922" s="4"/>
+      <c r="R922" s="4"/>
+    </row>
+    <row r="923" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A923" s="2" t="s">
+        <v>1440</v>
+      </c>
+      <c r="B923" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="C923" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D923" s="4" t="s">
+        <v>1113</v>
+      </c>
+      <c r="E923" s="5" t="s">
+        <v>1441</v>
+      </c>
+      <c r="F923" s="4" t="s">
+        <v>1423</v>
+      </c>
+      <c r="G923" s="4" t="s">
+        <v>1439</v>
+      </c>
+      <c r="H923" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="I923" s="4">
+        <v>89.99</v>
+      </c>
+      <c r="J923" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K923" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="L923" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="M923" s="4"/>
+      <c r="N923" s="4"/>
+      <c r="O923" s="4"/>
+      <c r="P923" s="4"/>
+      <c r="Q923" s="4"/>
+      <c r="R923" s="4"/>
+    </row>
+    <row r="924" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A924" s="2" t="s">
+        <v>1442</v>
+      </c>
+      <c r="B924" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="C924" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D924" s="4" t="s">
+        <v>1443</v>
+      </c>
+      <c r="E924" s="5" t="s">
+        <v>1444</v>
+      </c>
+      <c r="F924" s="4" t="s">
+        <v>1423</v>
+      </c>
+      <c r="G924" s="4" t="s">
+        <v>1439</v>
+      </c>
+      <c r="H924" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="I924" s="4">
+        <v>79.989999999999995</v>
+      </c>
+      <c r="J924" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K924" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="L924" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="M924" s="4"/>
+      <c r="N924" s="4"/>
+      <c r="O924" s="4"/>
+      <c r="P924" s="4"/>
+      <c r="Q924" s="4"/>
+      <c r="R924" s="4"/>
+    </row>
+    <row r="925" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A925" s="2" t="s">
+        <v>1445</v>
+      </c>
+      <c r="B925" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="C925" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D925" s="4" t="s">
+        <v>1130</v>
+      </c>
+      <c r="E925" s="5" t="s">
+        <v>1131</v>
+      </c>
+      <c r="F925" s="4" t="s">
+        <v>1423</v>
+      </c>
+      <c r="G925" s="4" t="s">
+        <v>1439</v>
+      </c>
+      <c r="H925" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="I925" s="4">
+        <v>119.99</v>
+      </c>
+      <c r="J925" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K925" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="L925" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="M925" s="4"/>
+      <c r="N925" s="4"/>
+      <c r="O925" s="4"/>
+      <c r="P925" s="4"/>
+      <c r="Q925" s="4"/>
+      <c r="R925" s="4"/>
+    </row>
+    <row r="926" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A926" s="2" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B926" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="C926" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D926" s="4" t="s">
+        <v>1136</v>
+      </c>
+      <c r="E926" s="5" t="s">
+        <v>1137</v>
+      </c>
+      <c r="F926" s="4" t="s">
+        <v>1390</v>
+      </c>
+      <c r="G926" s="4" t="s">
+        <v>1439</v>
+      </c>
+      <c r="H926" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="I926" s="4">
+        <v>109.99</v>
+      </c>
+      <c r="J926" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K926" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="L926" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="M926" s="4"/>
+      <c r="N926" s="4"/>
+      <c r="O926" s="4"/>
+      <c r="P926" s="4"/>
+      <c r="Q926" s="4"/>
+      <c r="R926" s="4"/>
+    </row>
+    <row r="927" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A927" s="2" t="s">
+        <v>1447</v>
+      </c>
+      <c r="B927" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="C927" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D927" s="4" t="s">
+        <v>1140</v>
+      </c>
+      <c r="E927" s="5" t="s">
+        <v>1448</v>
+      </c>
+      <c r="F927" s="4" t="s">
+        <v>1390</v>
+      </c>
+      <c r="G927" s="4" t="s">
+        <v>1439</v>
+      </c>
+      <c r="H927" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="I927" s="4">
+        <v>199.99</v>
+      </c>
+      <c r="J927" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K927" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="L927" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="M927" s="4"/>
+      <c r="N927" s="4"/>
+      <c r="O927" s="4"/>
+      <c r="P927" s="4"/>
+      <c r="Q927" s="4"/>
+      <c r="R927" s="4"/>
+    </row>
+    <row r="928" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A928" s="2" t="s">
+        <v>1449</v>
+      </c>
+      <c r="B928" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="C928" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D928" s="4" t="s">
+        <v>1450</v>
+      </c>
+      <c r="E928" s="5" t="s">
+        <v>1451</v>
+      </c>
+      <c r="F928" s="4" t="s">
+        <v>1390</v>
+      </c>
+      <c r="G928" s="4" t="s">
+        <v>1408</v>
+      </c>
+      <c r="H928" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="I928" s="4">
+        <v>119.99</v>
+      </c>
+      <c r="J928" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K928" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="L928" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="M928" s="4"/>
+      <c r="N928" s="4"/>
+      <c r="O928" s="4"/>
+      <c r="P928" s="4"/>
+      <c r="Q928" s="4"/>
+      <c r="R928" s="4"/>
+    </row>
+    <row r="929" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A929" s="2" t="s">
+        <v>1452</v>
+      </c>
+      <c r="B929" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="C929" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D929" s="4" t="s">
+        <v>1158</v>
+      </c>
+      <c r="E929" s="5" t="s">
+        <v>1159</v>
+      </c>
+      <c r="F929" s="4" t="s">
+        <v>1390</v>
+      </c>
+      <c r="G929" s="4" t="s">
+        <v>1408</v>
+      </c>
+      <c r="H929" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="I929" s="4">
+        <v>109.99</v>
+      </c>
+      <c r="J929" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K929" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="L929" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="M929" s="4"/>
+      <c r="N929" s="4"/>
+      <c r="O929" s="4"/>
+      <c r="P929" s="4"/>
+      <c r="Q929" s="4"/>
+      <c r="R929" s="4"/>
+    </row>
+    <row r="930" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A930" s="2" t="s">
+        <v>1453</v>
+      </c>
+      <c r="B930" s="2" t="s">
+        <v>666</v>
+      </c>
+      <c r="C930" s="2" t="s">
+        <v>959</v>
+      </c>
+      <c r="D930" s="4" t="s">
+        <v>973</v>
+      </c>
+      <c r="E930" s="5" t="s">
+        <v>1454</v>
+      </c>
+      <c r="F930" s="4" t="s">
+        <v>1393</v>
+      </c>
+      <c r="G930" s="4" t="s">
+        <v>1455</v>
+      </c>
+      <c r="H930" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I930" s="4">
+        <v>59.99</v>
+      </c>
+      <c r="J930" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K930" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="L930" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="M930" s="4"/>
+      <c r="N930" s="4"/>
+      <c r="O930" s="4"/>
+      <c r="P930" s="4"/>
+      <c r="Q930" s="4"/>
+      <c r="R930" s="4"/>
+    </row>
+    <row r="931" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A931" s="2" t="s">
+        <v>1456</v>
+      </c>
+      <c r="B931" s="2" t="s">
+        <v>666</v>
+      </c>
+      <c r="C931" s="2" t="s">
+        <v>959</v>
+      </c>
+      <c r="D931" s="4" t="s">
+        <v>973</v>
+      </c>
+      <c r="E931" s="5" t="s">
+        <v>1454</v>
+      </c>
+      <c r="F931" s="4" t="s">
+        <v>1393</v>
+      </c>
+      <c r="G931" s="4" t="s">
+        <v>1457</v>
+      </c>
+      <c r="H931" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I931" s="4">
+        <v>59.99</v>
+      </c>
+      <c r="J931" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K931" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="L931" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="M931" s="4"/>
+      <c r="N931" s="4"/>
+      <c r="O931" s="4"/>
+      <c r="P931" s="4"/>
+      <c r="Q931" s="4"/>
+      <c r="R931" s="4"/>
+    </row>
+    <row r="932" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A932" s="2" t="s">
+        <v>1458</v>
+      </c>
+      <c r="B932" s="2" t="s">
+        <v>666</v>
+      </c>
+      <c r="C932" s="2" t="s">
+        <v>959</v>
+      </c>
+      <c r="D932" s="4" t="s">
+        <v>980</v>
+      </c>
+      <c r="E932" s="5" t="s">
+        <v>1459</v>
+      </c>
+      <c r="F932" s="4" t="s">
+        <v>1393</v>
+      </c>
+      <c r="G932" s="4" t="s">
+        <v>1460</v>
+      </c>
+      <c r="H932" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I932" s="4">
+        <v>59.99</v>
+      </c>
+      <c r="J932" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K932" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="L932" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="M932" s="4"/>
+      <c r="N932" s="4"/>
+      <c r="O932" s="4"/>
+      <c r="P932" s="4"/>
+      <c r="Q932" s="4"/>
+      <c r="R932" s="4"/>
+    </row>
+    <row r="933" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A933" s="2" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B933" s="2" t="s">
+        <v>666</v>
+      </c>
+      <c r="C933" s="2" t="s">
+        <v>959</v>
+      </c>
+      <c r="D933" s="4" t="s">
+        <v>980</v>
+      </c>
+      <c r="E933" s="5" t="s">
+        <v>1459</v>
+      </c>
+      <c r="F933" s="4" t="s">
+        <v>1393</v>
+      </c>
+      <c r="G933" s="4" t="s">
+        <v>1462</v>
+      </c>
+      <c r="H933" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I933" s="4">
+        <v>59.99</v>
+      </c>
+      <c r="J933" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K933" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="L933" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="M933" s="4"/>
+      <c r="N933" s="4"/>
+      <c r="O933" s="4"/>
+      <c r="P933" s="4"/>
+      <c r="Q933" s="4"/>
+      <c r="R933" s="4"/>
+    </row>
+    <row r="934" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A934" s="2" t="s">
+        <v>1463</v>
+      </c>
+      <c r="B934" s="2" t="s">
+        <v>666</v>
+      </c>
+      <c r="C934" s="2" t="s">
+        <v>959</v>
+      </c>
+      <c r="D934" s="4" t="s">
+        <v>993</v>
+      </c>
+      <c r="E934" s="5" t="s">
+        <v>1464</v>
+      </c>
+      <c r="F934" s="4" t="s">
+        <v>1394</v>
+      </c>
+      <c r="G934" s="4" t="s">
+        <v>1455</v>
+      </c>
+      <c r="H934" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="I934" s="4">
+        <v>59.99</v>
+      </c>
+      <c r="J934" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K934" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="L934" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="M934" s="4"/>
+      <c r="N934" s="4"/>
+      <c r="O934" s="4"/>
+      <c r="P934" s="4"/>
+      <c r="Q934" s="4"/>
+      <c r="R934" s="4"/>
+    </row>
+    <row r="935" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A935" s="2" t="s">
+        <v>1465</v>
+      </c>
+      <c r="B935" s="2" t="s">
+        <v>666</v>
+      </c>
+      <c r="C935" s="2" t="s">
+        <v>959</v>
+      </c>
+      <c r="D935" s="4" t="s">
+        <v>993</v>
+      </c>
+      <c r="E935" s="5" t="s">
+        <v>1464</v>
+      </c>
+      <c r="F935" s="4" t="s">
+        <v>1394</v>
+      </c>
+      <c r="G935" s="4" t="s">
+        <v>1457</v>
+      </c>
+      <c r="H935" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="I935" s="4">
+        <v>59.99</v>
+      </c>
+      <c r="J935" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K935" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="L935" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="M935" s="4"/>
+      <c r="N935" s="4"/>
+      <c r="O935" s="4"/>
+      <c r="P935" s="4"/>
+      <c r="Q935" s="4"/>
+      <c r="R935" s="4"/>
+    </row>
+    <row r="936" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A936" s="2" t="s">
+        <v>1466</v>
+      </c>
+      <c r="B936" s="2" t="s">
+        <v>666</v>
+      </c>
+      <c r="C936" s="2" t="s">
+        <v>959</v>
+      </c>
+      <c r="D936" s="4" t="s">
+        <v>997</v>
+      </c>
+      <c r="E936" s="5" t="s">
+        <v>1467</v>
+      </c>
+      <c r="F936" s="4" t="s">
+        <v>1394</v>
+      </c>
+      <c r="G936" s="4" t="s">
+        <v>1468</v>
+      </c>
+      <c r="H936" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="I936" s="4">
+        <v>59.99</v>
+      </c>
+      <c r="J936" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K936" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="L936" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="M936" s="4"/>
+      <c r="N936" s="4"/>
+      <c r="O936" s="4"/>
+      <c r="P936" s="4"/>
+      <c r="Q936" s="4"/>
+      <c r="R936" s="4"/>
+    </row>
+    <row r="937" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A937" s="2" t="s">
+        <v>1469</v>
+      </c>
+      <c r="B937" s="2" t="s">
+        <v>666</v>
+      </c>
+      <c r="C937" s="2" t="s">
+        <v>959</v>
+      </c>
+      <c r="D937" s="4" t="s">
+        <v>997</v>
+      </c>
+      <c r="E937" s="5" t="s">
+        <v>1467</v>
+      </c>
+      <c r="F937" s="4" t="s">
+        <v>1394</v>
+      </c>
+      <c r="G937" s="4" t="s">
+        <v>1462</v>
+      </c>
+      <c r="H937" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="I937" s="4">
+        <v>59.99</v>
+      </c>
+      <c r="J937" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="K937" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="L937" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="M937" s="4"/>
+      <c r="N937" s="4"/>
+      <c r="O937" s="4"/>
+      <c r="P937" s="4"/>
+      <c r="Q937" s="4"/>
+      <c r="R937" s="4"/>
+    </row>
+    <row r="938" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A938" s="2" t="s">
+        <v>1470</v>
+      </c>
+      <c r="B938" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="C938" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D938" s="4" t="s">
+        <v>1471</v>
+      </c>
+      <c r="E938" s="5" t="s">
+        <v>1472</v>
+      </c>
+      <c r="F938" s="4" t="s">
+        <v>1395</v>
+      </c>
+      <c r="G938" s="4" t="s">
+        <v>1473</v>
+      </c>
+      <c r="H938" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I938" s="4">
+        <v>229.99</v>
+      </c>
+      <c r="J938" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K938" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="L938" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="M938" s="4"/>
+      <c r="N938" s="4"/>
+      <c r="O938" s="4"/>
+      <c r="P938" s="4"/>
+      <c r="Q938" s="4"/>
+      <c r="R938" s="4"/>
+    </row>
+    <row r="939" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A939" s="2" t="s">
+        <v>1474</v>
+      </c>
+      <c r="B939" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="C939" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D939" s="4" t="s">
+        <v>1471</v>
+      </c>
+      <c r="E939" s="5" t="s">
+        <v>1472</v>
+      </c>
+      <c r="F939" s="4" t="s">
+        <v>1395</v>
+      </c>
+      <c r="G939" s="4" t="s">
+        <v>1402</v>
+      </c>
+      <c r="H939" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I939" s="4">
+        <v>229.99</v>
+      </c>
+      <c r="J939" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K939" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="L939" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="M939" s="4"/>
+      <c r="N939" s="4"/>
+      <c r="O939" s="4"/>
+      <c r="P939" s="4"/>
+      <c r="Q939" s="4"/>
+      <c r="R939" s="4"/>
+    </row>
+    <row r="940" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A940" s="2" t="s">
+        <v>1475</v>
+      </c>
+      <c r="B940" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="C940" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D940" s="4" t="s">
+        <v>1476</v>
+      </c>
+      <c r="E940" s="5" t="s">
+        <v>1477</v>
+      </c>
+      <c r="F940" s="4" t="s">
+        <v>1395</v>
+      </c>
+      <c r="G940" s="4" t="s">
+        <v>1473</v>
+      </c>
+      <c r="H940" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I940" s="4">
+        <v>229.99</v>
+      </c>
+      <c r="J940" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K940" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="L940" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="M940" s="4"/>
+      <c r="N940" s="4"/>
+      <c r="O940" s="4"/>
+      <c r="P940" s="4"/>
+      <c r="Q940" s="4"/>
+      <c r="R940" s="4"/>
+    </row>
+    <row r="941" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A941" s="2" t="s">
+        <v>1478</v>
+      </c>
+      <c r="B941" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="C941" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D941" s="4" t="s">
+        <v>1476</v>
+      </c>
+      <c r="E941" s="5" t="s">
+        <v>1477</v>
+      </c>
+      <c r="F941" s="4" t="s">
+        <v>1395</v>
+      </c>
+      <c r="G941" s="4" t="s">
+        <v>1479</v>
+      </c>
+      <c r="H941" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I941" s="4">
+        <v>229.99</v>
+      </c>
+      <c r="J941" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K941" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="L941" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="M941" s="4"/>
+      <c r="N941" s="4"/>
+      <c r="O941" s="4"/>
+      <c r="P941" s="4"/>
+      <c r="Q941" s="4"/>
+      <c r="R941" s="4"/>
+    </row>
+    <row r="942" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A942" s="2" t="s">
+        <v>1480</v>
+      </c>
+      <c r="B942" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="C942" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D942" s="4" t="s">
+        <v>1481</v>
+      </c>
+      <c r="E942" s="5" t="s">
+        <v>1482</v>
+      </c>
+      <c r="F942" s="4" t="s">
+        <v>1395</v>
+      </c>
+      <c r="G942" s="4" t="s">
+        <v>1473</v>
+      </c>
+      <c r="H942" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I942" s="4">
+        <v>199.99</v>
+      </c>
+      <c r="J942" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K942" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="L942" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="M942" s="4"/>
+      <c r="N942" s="4"/>
+      <c r="O942" s="4"/>
+      <c r="P942" s="4"/>
+      <c r="Q942" s="4"/>
+      <c r="R942" s="4"/>
+    </row>
+    <row r="943" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A943" s="2" t="s">
+        <v>1483</v>
+      </c>
+      <c r="B943" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="C943" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D943" s="4" t="s">
+        <v>1481</v>
+      </c>
+      <c r="E943" s="5" t="s">
+        <v>1482</v>
+      </c>
+      <c r="F943" s="4" t="s">
+        <v>1395</v>
+      </c>
+      <c r="G943" s="4" t="s">
+        <v>1402</v>
+      </c>
+      <c r="H943" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I943" s="4">
+        <v>199.99</v>
+      </c>
+      <c r="J943" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K943" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="L943" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="M943" s="4"/>
+      <c r="N943" s="4"/>
+      <c r="O943" s="4"/>
+      <c r="P943" s="4"/>
+      <c r="Q943" s="4"/>
+      <c r="R943" s="4"/>
+    </row>
+    <row r="944" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A944" s="2" t="s">
+        <v>1484</v>
+      </c>
+      <c r="B944" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="C944" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D944" s="4" t="s">
+        <v>1485</v>
+      </c>
+      <c r="E944" s="5" t="s">
+        <v>1486</v>
+      </c>
+      <c r="F944" s="4" t="s">
+        <v>1395</v>
+      </c>
+      <c r="G944" s="4" t="s">
+        <v>1487</v>
+      </c>
+      <c r="H944" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I944" s="4">
+        <v>229.99</v>
+      </c>
+      <c r="J944" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K944" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="L944" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="M944" s="4"/>
+      <c r="N944" s="4"/>
+      <c r="O944" s="4"/>
+      <c r="P944" s="4"/>
+      <c r="Q944" s="4"/>
+      <c r="R944" s="4"/>
+    </row>
+    <row r="945" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A945" s="2" t="s">
+        <v>1488</v>
+      </c>
+      <c r="B945" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="C945" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D945" s="4" t="s">
+        <v>1485</v>
+      </c>
+      <c r="E945" s="5" t="s">
+        <v>1486</v>
+      </c>
+      <c r="F945" s="4" t="s">
+        <v>1395</v>
+      </c>
+      <c r="G945" s="4" t="s">
+        <v>1402</v>
+      </c>
+      <c r="H945" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I945" s="4">
+        <v>229.99</v>
+      </c>
+      <c r="J945" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K945" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="L945" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="M945" s="4"/>
+      <c r="N945" s="4"/>
+      <c r="O945" s="4"/>
+      <c r="P945" s="4"/>
+      <c r="Q945" s="4"/>
+      <c r="R945" s="4"/>
+    </row>
+    <row r="946" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A946" s="2" t="s">
+        <v>1489</v>
+      </c>
+      <c r="B946" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="C946" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D946" s="4" t="s">
+        <v>1490</v>
+      </c>
+      <c r="E946" s="5" t="s">
+        <v>1491</v>
+      </c>
+      <c r="F946" s="4" t="s">
+        <v>1395</v>
+      </c>
+      <c r="G946" s="4" t="s">
+        <v>1473</v>
+      </c>
+      <c r="H946" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I946" s="4">
+        <v>199.99</v>
+      </c>
+      <c r="J946" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K946" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="L946" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="M946" s="4"/>
+      <c r="N946" s="4"/>
+      <c r="O946" s="4"/>
+      <c r="P946" s="4"/>
+      <c r="Q946" s="4"/>
+      <c r="R946" s="4"/>
+    </row>
+    <row r="947" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A947" s="2" t="s">
+        <v>1492</v>
+      </c>
+      <c r="B947" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="C947" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D947" s="4" t="s">
+        <v>1490</v>
+      </c>
+      <c r="E947" s="5" t="s">
+        <v>1491</v>
+      </c>
+      <c r="F947" s="4" t="s">
+        <v>1395</v>
+      </c>
+      <c r="G947" s="4" t="s">
+        <v>1479</v>
+      </c>
+      <c r="H947" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I947" s="4">
+        <v>199.99</v>
+      </c>
+      <c r="J947" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K947" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="L947" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="M947" s="4"/>
+      <c r="N947" s="4"/>
+      <c r="O947" s="4"/>
+      <c r="P947" s="4"/>
+      <c r="Q947" s="4"/>
+      <c r="R947" s="4"/>
+    </row>
+    <row r="948" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A948" s="2" t="s">
+        <v>1493</v>
+      </c>
+      <c r="B948" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="C948" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D948" s="4" t="s">
+        <v>1490</v>
+      </c>
+      <c r="E948" s="5" t="s">
+        <v>1491</v>
+      </c>
+      <c r="F948" s="4" t="s">
+        <v>1395</v>
+      </c>
+      <c r="G948" s="4" t="s">
+        <v>1402</v>
+      </c>
+      <c r="H948" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I948" s="4">
+        <v>199.99</v>
+      </c>
+      <c r="J948" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K948" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="L948" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="M948" s="4"/>
+      <c r="N948" s="4"/>
+      <c r="O948" s="4"/>
+      <c r="P948" s="4"/>
+      <c r="Q948" s="4"/>
+      <c r="R948" s="4"/>
+    </row>
+    <row r="949" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A949" s="2" t="s">
+        <v>1494</v>
+      </c>
+      <c r="B949" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="C949" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D949" s="4" t="s">
+        <v>1495</v>
+      </c>
+      <c r="E949" s="5" t="s">
+        <v>1496</v>
+      </c>
+      <c r="F949" s="4" t="s">
+        <v>1395</v>
+      </c>
+      <c r="G949" s="4" t="s">
+        <v>1473</v>
+      </c>
+      <c r="H949" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I949" s="4">
+        <v>259.99</v>
+      </c>
+      <c r="J949" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K949" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="L949" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="M949" s="4"/>
+      <c r="N949" s="4"/>
+      <c r="O949" s="4"/>
+      <c r="P949" s="4"/>
+      <c r="Q949" s="4"/>
+      <c r="R949" s="4"/>
+    </row>
+    <row r="950" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A950" s="2" t="s">
+        <v>1497</v>
+      </c>
+      <c r="B950" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="C950" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D950" s="4" t="s">
+        <v>1495</v>
+      </c>
+      <c r="E950" s="5" t="s">
+        <v>1496</v>
+      </c>
+      <c r="F950" s="4" t="s">
+        <v>1395</v>
+      </c>
+      <c r="G950" s="4" t="s">
+        <v>1402</v>
+      </c>
+      <c r="H950" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I950" s="4">
+        <v>259.99</v>
+      </c>
+      <c r="J950" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K950" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="L950" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="M950" s="4"/>
+      <c r="N950" s="4"/>
+      <c r="O950" s="4"/>
+      <c r="P950" s="4"/>
+      <c r="Q950" s="4"/>
+      <c r="R950" s="4"/>
+    </row>
+    <row r="951" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A951" s="2" t="s">
+        <v>1498</v>
+      </c>
+      <c r="B951" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="C951" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D951" s="4" t="s">
+        <v>1499</v>
+      </c>
+      <c r="E951" s="5" t="s">
+        <v>1500</v>
+      </c>
+      <c r="F951" s="4" t="s">
+        <v>1395</v>
+      </c>
+      <c r="G951" s="4" t="s">
+        <v>1473</v>
+      </c>
+      <c r="H951" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I951" s="4">
+        <v>249.99</v>
+      </c>
+      <c r="J951" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K951" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="L951" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="M951" s="4"/>
+      <c r="N951" s="4"/>
+      <c r="O951" s="4"/>
+      <c r="P951" s="4"/>
+      <c r="Q951" s="4"/>
+      <c r="R951" s="4"/>
+    </row>
+    <row r="952" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A952" s="2" t="s">
+        <v>1501</v>
+      </c>
+      <c r="B952" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="C952" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D952" s="4" t="s">
+        <v>1499</v>
+      </c>
+      <c r="E952" s="5" t="s">
+        <v>1500</v>
+      </c>
+      <c r="F952" s="4" t="s">
+        <v>1395</v>
+      </c>
+      <c r="G952" s="4" t="s">
+        <v>1479</v>
+      </c>
+      <c r="H952" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I952" s="4">
+        <v>249.99</v>
+      </c>
+      <c r="J952" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K952" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="L952" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="M952" s="4"/>
+      <c r="N952" s="4"/>
+      <c r="O952" s="4"/>
+      <c r="P952" s="4"/>
+      <c r="Q952" s="4"/>
+      <c r="R952" s="4"/>
+    </row>
+    <row r="953" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A953" s="2" t="s">
+        <v>1502</v>
+      </c>
+      <c r="B953" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="C953" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D953" s="4" t="s">
+        <v>1503</v>
+      </c>
+      <c r="E953" s="5" t="s">
+        <v>1504</v>
+      </c>
+      <c r="F953" s="4" t="s">
+        <v>1395</v>
+      </c>
+      <c r="G953" s="4" t="s">
+        <v>1473</v>
+      </c>
+      <c r="H953" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I953" s="4">
+        <v>229.99</v>
+      </c>
+      <c r="J953" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K953" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="L953" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="M953" s="4"/>
+      <c r="N953" s="4"/>
+      <c r="O953" s="4"/>
+      <c r="P953" s="4"/>
+      <c r="Q953" s="4"/>
+      <c r="R953" s="4"/>
+    </row>
+    <row r="954" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A954" s="2" t="s">
+        <v>1505</v>
+      </c>
+      <c r="B954" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="C954" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D954" s="4" t="s">
+        <v>1503</v>
+      </c>
+      <c r="E954" s="5" t="s">
+        <v>1504</v>
+      </c>
+      <c r="F954" s="4" t="s">
+        <v>1395</v>
+      </c>
+      <c r="G954" s="4" t="s">
+        <v>1402</v>
+      </c>
+      <c r="H954" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I954" s="4">
+        <v>229.99</v>
+      </c>
+      <c r="J954" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K954" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="L954" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="M954" s="4"/>
+      <c r="N954" s="4"/>
+      <c r="O954" s="4"/>
+      <c r="P954" s="4"/>
+      <c r="Q954" s="4"/>
+      <c r="R954" s="4"/>
+    </row>
+    <row r="955" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A955" s="2" t="s">
+        <v>1506</v>
+      </c>
+      <c r="B955" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="C955" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D955" s="4" t="s">
+        <v>1507</v>
+      </c>
+      <c r="E955" s="5" t="s">
+        <v>1508</v>
+      </c>
+      <c r="F955" s="4" t="s">
+        <v>1395</v>
+      </c>
+      <c r="G955" s="4" t="s">
+        <v>1402</v>
+      </c>
+      <c r="H955" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I955" s="4">
+        <v>379.99</v>
+      </c>
+      <c r="J955" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K955" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="L955" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="M955" s="4"/>
+      <c r="N955" s="4"/>
+      <c r="O955" s="4"/>
+      <c r="P955" s="4"/>
+      <c r="Q955" s="4"/>
+      <c r="R955" s="4"/>
+    </row>
+    <row r="956" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A956" s="2" t="s">
+        <v>1509</v>
+      </c>
+      <c r="B956" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="C956" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D956" s="4" t="s">
+        <v>1510</v>
+      </c>
+      <c r="E956" s="5" t="s">
+        <v>1511</v>
+      </c>
+      <c r="F956" s="4" t="s">
+        <v>1395</v>
+      </c>
+      <c r="G956" s="4" t="s">
+        <v>1487</v>
+      </c>
+      <c r="H956" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="I956" s="4">
+        <v>229.99</v>
+      </c>
+      <c r="J956" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K956" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="L956" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="M956" s="4"/>
+      <c r="N956" s="4"/>
+      <c r="O956" s="4"/>
+      <c r="P956" s="4"/>
+      <c r="Q956" s="4"/>
+      <c r="R956" s="4"/>
+    </row>
+    <row r="957" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A957" s="2" t="s">
+        <v>1512</v>
+      </c>
+      <c r="B957" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="C957" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D957" s="4" t="s">
+        <v>1510</v>
+      </c>
+      <c r="E957" s="5" t="s">
+        <v>1511</v>
+      </c>
+      <c r="F957" s="4" t="s">
+        <v>1395</v>
+      </c>
+      <c r="G957" s="4" t="s">
+        <v>1402</v>
+      </c>
+      <c r="H957" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="I957" s="4">
+        <v>229.99</v>
+      </c>
+      <c r="J957" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K957" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="L957" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="M957" s="4"/>
+      <c r="N957" s="4"/>
+      <c r="O957" s="4"/>
+      <c r="P957" s="4"/>
+      <c r="Q957" s="4"/>
+      <c r="R957" s="4"/>
+    </row>
+    <row r="958" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A958" s="2" t="s">
+        <v>1513</v>
+      </c>
+      <c r="B958" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="C958" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D958" s="4" t="s">
+        <v>1514</v>
+      </c>
+      <c r="E958" s="5" t="s">
+        <v>1515</v>
+      </c>
+      <c r="F958" s="4" t="s">
+        <v>1395</v>
+      </c>
+      <c r="G958" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="H958" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="I958" s="4">
+        <v>199.99</v>
+      </c>
+      <c r="J958" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K958" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="L958" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="M958" s="4"/>
+      <c r="N958" s="4"/>
+      <c r="O958" s="4"/>
+      <c r="P958" s="4"/>
+      <c r="Q958" s="4"/>
+      <c r="R958" s="4"/>
+    </row>
+    <row r="959" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A959" s="2" t="s">
+        <v>1516</v>
+      </c>
+      <c r="B959" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="C959" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D959" s="4" t="s">
+        <v>1514</v>
+      </c>
+      <c r="E959" s="5" t="s">
+        <v>1515</v>
+      </c>
+      <c r="F959" s="4" t="s">
+        <v>1395</v>
+      </c>
+      <c r="G959" s="4" t="s">
+        <v>1402</v>
+      </c>
+      <c r="H959" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="I959" s="4">
+        <v>199.99</v>
+      </c>
+      <c r="J959" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K959" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="L959" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="M959" s="4"/>
+      <c r="N959" s="4"/>
+      <c r="O959" s="4"/>
+      <c r="P959" s="4"/>
+      <c r="Q959" s="4"/>
+      <c r="R959" s="4"/>
+    </row>
+    <row r="960" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A960" s="2" t="s">
+        <v>1517</v>
+      </c>
+      <c r="B960" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="C960" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D960" s="4" t="s">
+        <v>1514</v>
+      </c>
+      <c r="E960" s="5" t="s">
+        <v>1515</v>
+      </c>
+      <c r="F960" s="4" t="s">
+        <v>1395</v>
+      </c>
+      <c r="G960" s="4" t="s">
+        <v>1405</v>
+      </c>
+      <c r="H960" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="I960" s="4">
+        <v>199.99</v>
+      </c>
+      <c r="J960" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K960" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="L960" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="M960" s="4"/>
+      <c r="N960" s="4"/>
+      <c r="O960" s="4"/>
+      <c r="P960" s="4"/>
+      <c r="Q960" s="4"/>
+      <c r="R960" s="4"/>
+    </row>
+    <row r="961" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A961" s="2" t="s">
+        <v>1518</v>
+      </c>
+      <c r="B961" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="C961" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D961" s="4" t="s">
+        <v>1519</v>
+      </c>
+      <c r="E961" s="5" t="s">
+        <v>1520</v>
+      </c>
+      <c r="F961" s="4" t="s">
+        <v>1395</v>
+      </c>
+      <c r="G961" s="4" t="s">
+        <v>1473</v>
+      </c>
+      <c r="H961" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="I961" s="4">
+        <v>259.99</v>
+      </c>
+      <c r="J961" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K961" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="L961" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="M961" s="4"/>
+      <c r="N961" s="4"/>
+      <c r="O961" s="4"/>
+      <c r="P961" s="4"/>
+      <c r="Q961" s="4"/>
+      <c r="R961" s="4"/>
+    </row>
+    <row r="962" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A962" s="2" t="s">
+        <v>1521</v>
+      </c>
+      <c r="B962" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="C962" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D962" s="4" t="s">
+        <v>1519</v>
+      </c>
+      <c r="E962" s="5" t="s">
+        <v>1520</v>
+      </c>
+      <c r="F962" s="4" t="s">
+        <v>1395</v>
+      </c>
+      <c r="G962" s="4" t="s">
+        <v>1402</v>
+      </c>
+      <c r="H962" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="I962" s="4">
+        <v>259.99</v>
+      </c>
+      <c r="J962" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K962" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="L962" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="M962" s="4"/>
+      <c r="N962" s="4"/>
+      <c r="O962" s="4"/>
+      <c r="P962" s="4"/>
+      <c r="Q962" s="4"/>
+      <c r="R962" s="4"/>
+    </row>
+    <row r="963" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A963" s="2" t="s">
+        <v>1522</v>
+      </c>
+      <c r="B963" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="C963" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D963" s="4" t="s">
+        <v>1523</v>
+      </c>
+      <c r="E963" s="5" t="s">
+        <v>1524</v>
+      </c>
+      <c r="F963" s="4" t="s">
+        <v>1395</v>
+      </c>
+      <c r="G963" s="4" t="s">
+        <v>1473</v>
+      </c>
+      <c r="H963" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="I963" s="4">
+        <v>249.99</v>
+      </c>
+      <c r="J963" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K963" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="L963" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="M963" s="4"/>
+      <c r="N963" s="4"/>
+      <c r="O963" s="4"/>
+      <c r="P963" s="4"/>
+      <c r="Q963" s="4"/>
+      <c r="R963" s="4"/>
+    </row>
+    <row r="964" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A964" s="2" t="s">
+        <v>1525</v>
+      </c>
+      <c r="B964" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="C964" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D964" s="4" t="s">
+        <v>1523</v>
+      </c>
+      <c r="E964" s="5" t="s">
+        <v>1524</v>
+      </c>
+      <c r="F964" s="4" t="s">
+        <v>1395</v>
+      </c>
+      <c r="G964" s="4" t="s">
+        <v>1402</v>
+      </c>
+      <c r="H964" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="I964" s="4">
+        <v>249.99</v>
+      </c>
+      <c r="J964" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K964" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="L964" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="M964" s="4"/>
+      <c r="N964" s="4"/>
+      <c r="O964" s="4"/>
+      <c r="P964" s="4"/>
+      <c r="Q964" s="4"/>
+      <c r="R964" s="4"/>
+    </row>
+    <row r="965" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A965" s="2" t="s">
+        <v>1526</v>
+      </c>
+      <c r="B965" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="C965" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D965" s="4" t="s">
+        <v>1527</v>
+      </c>
+      <c r="E965" s="5" t="s">
+        <v>1528</v>
+      </c>
+      <c r="F965" s="4" t="s">
+        <v>1395</v>
+      </c>
+      <c r="G965" s="4" t="s">
+        <v>1473</v>
+      </c>
+      <c r="H965" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="I965" s="4">
+        <v>239.99</v>
+      </c>
+      <c r="J965" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K965" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="L965" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="M965" s="4"/>
+      <c r="N965" s="4"/>
+      <c r="O965" s="4"/>
+      <c r="P965" s="4"/>
+      <c r="Q965" s="4"/>
+      <c r="R965" s="4"/>
+    </row>
+    <row r="966" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A966" s="2" t="s">
+        <v>1529</v>
+      </c>
+      <c r="B966" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="C966" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D966" s="4" t="s">
+        <v>1527</v>
+      </c>
+      <c r="E966" s="5" t="s">
+        <v>1528</v>
+      </c>
+      <c r="F966" s="4" t="s">
+        <v>1395</v>
+      </c>
+      <c r="G966" s="4" t="s">
+        <v>1402</v>
+      </c>
+      <c r="H966" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="I966" s="4">
+        <v>239.99</v>
+      </c>
+      <c r="J966" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K966" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="L966" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="M966" s="4"/>
+      <c r="N966" s="4"/>
+      <c r="O966" s="4"/>
+      <c r="P966" s="4"/>
+      <c r="Q966" s="4"/>
+      <c r="R966" s="4"/>
+    </row>
+    <row r="967" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A967" s="2" t="s">
+        <v>1530</v>
+      </c>
+      <c r="B967" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="C967" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D967" s="4" t="s">
+        <v>1531</v>
+      </c>
+      <c r="E967" s="5" t="s">
+        <v>1532</v>
+      </c>
+      <c r="F967" s="4" t="s">
+        <v>1395</v>
+      </c>
+      <c r="G967" s="4" t="s">
+        <v>1473</v>
+      </c>
+      <c r="H967" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="I967" s="4">
+        <v>219.99</v>
+      </c>
+      <c r="J967" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K967" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="L967" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="M967" s="4"/>
+      <c r="N967" s="4"/>
+      <c r="O967" s="4"/>
+      <c r="P967" s="4"/>
+      <c r="Q967" s="4"/>
+      <c r="R967" s="4"/>
+    </row>
+    <row r="968" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A968" s="2" t="s">
+        <v>1533</v>
+      </c>
+      <c r="B968" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="C968" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D968" s="4" t="s">
+        <v>1534</v>
+      </c>
+      <c r="E968" s="5" t="s">
+        <v>1535</v>
+      </c>
+      <c r="F968" s="4" t="s">
+        <v>1395</v>
+      </c>
+      <c r="G968" s="4" t="s">
+        <v>1402</v>
+      </c>
+      <c r="H968" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="I968" s="4">
+        <v>379.99</v>
+      </c>
+      <c r="J968" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K968" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="L968" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="M968" s="4"/>
+      <c r="N968" s="4"/>
+      <c r="O968" s="4"/>
+      <c r="P968" s="4"/>
+      <c r="Q968" s="4"/>
+      <c r="R968" s="4"/>
+    </row>
+    <row r="969" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A969" s="2" t="s">
+        <v>1536</v>
+      </c>
+      <c r="B969" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="C969" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D969" s="4" t="s">
+        <v>1537</v>
+      </c>
+      <c r="E969" s="5" t="s">
+        <v>1538</v>
+      </c>
+      <c r="F969" s="4" t="s">
+        <v>1395</v>
+      </c>
+      <c r="G969" s="4" t="s">
+        <v>1473</v>
+      </c>
+      <c r="H969" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I969" s="4">
+        <v>169.99</v>
+      </c>
+      <c r="J969" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K969" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="L969" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="M969" s="4"/>
+      <c r="N969" s="4"/>
+      <c r="O969" s="4"/>
+      <c r="P969" s="4"/>
+      <c r="Q969" s="4"/>
+      <c r="R969" s="4"/>
+    </row>
+    <row r="970" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A970" s="2" t="s">
+        <v>1539</v>
+      </c>
+      <c r="B970" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="C970" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D970" s="4" t="s">
+        <v>1537</v>
+      </c>
+      <c r="E970" s="5" t="s">
+        <v>1538</v>
+      </c>
+      <c r="F970" s="4" t="s">
+        <v>1395</v>
+      </c>
+      <c r="G970" s="4" t="s">
+        <v>1398</v>
+      </c>
+      <c r="H970" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I970" s="4">
+        <v>169.99</v>
+      </c>
+      <c r="J970" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K970" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="L970" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="M970" s="4"/>
+      <c r="N970" s="4"/>
+      <c r="O970" s="4"/>
+      <c r="P970" s="4"/>
+      <c r="Q970" s="4"/>
+      <c r="R970" s="4"/>
+    </row>
+    <row r="971" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A971" s="2" t="s">
+        <v>1540</v>
+      </c>
+      <c r="B971" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="C971" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D971" s="4" t="s">
+        <v>1541</v>
+      </c>
+      <c r="E971" s="5" t="s">
+        <v>1542</v>
+      </c>
+      <c r="F971" s="4" t="s">
+        <v>1395</v>
+      </c>
+      <c r="G971" s="4" t="s">
+        <v>1473</v>
+      </c>
+      <c r="H971" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I971" s="4">
+        <v>149.99</v>
+      </c>
+      <c r="J971" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K971" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="L971" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="M971" s="4"/>
+      <c r="N971" s="4"/>
+      <c r="O971" s="4"/>
+      <c r="P971" s="4"/>
+      <c r="Q971" s="4"/>
+      <c r="R971" s="4"/>
+    </row>
+    <row r="972" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A972" s="2" t="s">
+        <v>1543</v>
+      </c>
+      <c r="B972" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="C972" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D972" s="4" t="s">
+        <v>1541</v>
+      </c>
+      <c r="E972" s="5" t="s">
+        <v>1542</v>
+      </c>
+      <c r="F972" s="4" t="s">
+        <v>1395</v>
+      </c>
+      <c r="G972" s="4" t="s">
+        <v>1544</v>
+      </c>
+      <c r="H972" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I972" s="4">
+        <v>149.99</v>
+      </c>
+      <c r="J972" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K972" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="L972" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="M972" s="4"/>
+      <c r="N972" s="4"/>
+      <c r="O972" s="4"/>
+      <c r="P972" s="4"/>
+      <c r="Q972" s="4"/>
+      <c r="R972" s="4"/>
+    </row>
+    <row r="973" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A973" s="2" t="s">
+        <v>1545</v>
+      </c>
+      <c r="B973" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="C973" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D973" s="4" t="s">
+        <v>1546</v>
+      </c>
+      <c r="E973" s="5" t="s">
+        <v>1547</v>
+      </c>
+      <c r="F973" s="4" t="s">
+        <v>1395</v>
+      </c>
+      <c r="G973" s="4" t="s">
+        <v>1473</v>
+      </c>
+      <c r="H973" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I973" s="4">
+        <v>249.99</v>
+      </c>
+      <c r="J973" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K973" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="L973" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="M973" s="4"/>
+      <c r="N973" s="4"/>
+      <c r="O973" s="4"/>
+      <c r="P973" s="4"/>
+      <c r="Q973" s="4"/>
+      <c r="R973" s="4"/>
+    </row>
+    <row r="974" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A974" s="2" t="s">
+        <v>1548</v>
+      </c>
+      <c r="B974" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="C974" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D974" s="4" t="s">
+        <v>1546</v>
+      </c>
+      <c r="E974" s="5" t="s">
+        <v>1547</v>
+      </c>
+      <c r="F974" s="4" t="s">
+        <v>1395</v>
+      </c>
+      <c r="G974" s="4" t="s">
+        <v>1402</v>
+      </c>
+      <c r="H974" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I974" s="4">
+        <v>249.99</v>
+      </c>
+      <c r="J974" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K974" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="L974" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="M974" s="4"/>
+      <c r="N974" s="4"/>
+      <c r="O974" s="4"/>
+      <c r="P974" s="4"/>
+      <c r="Q974" s="4"/>
+      <c r="R974" s="4"/>
+    </row>
+    <row r="975" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A975" s="2" t="s">
+        <v>1549</v>
+      </c>
+      <c r="B975" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="C975" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D975" s="4" t="s">
+        <v>1550</v>
+      </c>
+      <c r="E975" s="5" t="s">
+        <v>1551</v>
+      </c>
+      <c r="F975" s="4" t="s">
+        <v>1395</v>
+      </c>
+      <c r="G975" s="4" t="s">
+        <v>1473</v>
+      </c>
+      <c r="H975" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I975" s="4">
+        <v>179.99</v>
+      </c>
+      <c r="J975" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K975" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="L975" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="M975" s="4"/>
+      <c r="N975" s="4"/>
+      <c r="O975" s="4"/>
+      <c r="P975" s="4"/>
+      <c r="Q975" s="4"/>
+      <c r="R975" s="4"/>
+    </row>
+    <row r="976" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A976" s="2" t="s">
+        <v>1552</v>
+      </c>
+      <c r="B976" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="C976" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D976" s="4" t="s">
+        <v>1550</v>
+      </c>
+      <c r="E976" s="5" t="s">
+        <v>1551</v>
+      </c>
+      <c r="F976" s="4" t="s">
+        <v>1395</v>
+      </c>
+      <c r="G976" s="4" t="s">
+        <v>1402</v>
+      </c>
+      <c r="H976" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I976" s="4">
+        <v>179.99</v>
+      </c>
+      <c r="J976" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K976" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="L976" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="M976" s="4"/>
+      <c r="N976" s="4"/>
+      <c r="O976" s="4"/>
+      <c r="P976" s="4"/>
+      <c r="Q976" s="4"/>
+      <c r="R976" s="4"/>
+    </row>
+    <row r="977" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A977" s="2" t="s">
+        <v>1553</v>
+      </c>
+      <c r="B977" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="C977" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D977" s="4" t="s">
+        <v>1550</v>
+      </c>
+      <c r="E977" s="5" t="s">
+        <v>1551</v>
+      </c>
+      <c r="F977" s="4" t="s">
+        <v>1395</v>
+      </c>
+      <c r="G977" s="4" t="s">
+        <v>1398</v>
+      </c>
+      <c r="H977" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I977" s="4">
+        <v>179.99</v>
+      </c>
+      <c r="J977" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K977" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="L977" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="M977" s="4"/>
+      <c r="N977" s="4"/>
+      <c r="O977" s="4"/>
+      <c r="P977" s="4"/>
+      <c r="Q977" s="4"/>
+      <c r="R977" s="4"/>
+    </row>
+    <row r="978" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A978" s="2" t="s">
+        <v>1554</v>
+      </c>
+      <c r="B978" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="C978" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D978" s="4" t="s">
+        <v>1555</v>
+      </c>
+      <c r="E978" s="5" t="s">
+        <v>1556</v>
+      </c>
+      <c r="F978" s="4" t="s">
+        <v>1395</v>
+      </c>
+      <c r="G978" s="4" t="s">
+        <v>1473</v>
+      </c>
+      <c r="H978" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I978" s="4">
+        <v>249.99</v>
+      </c>
+      <c r="J978" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K978" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="L978" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="M978" s="4"/>
+      <c r="N978" s="4"/>
+      <c r="O978" s="4"/>
+      <c r="P978" s="4"/>
+      <c r="Q978" s="4"/>
+      <c r="R978" s="4"/>
+    </row>
+    <row r="979" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A979" s="2" t="s">
+        <v>1557</v>
+      </c>
+      <c r="B979" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="C979" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D979" s="4" t="s">
+        <v>1555</v>
+      </c>
+      <c r="E979" s="5" t="s">
+        <v>1556</v>
+      </c>
+      <c r="F979" s="4" t="s">
+        <v>1395</v>
+      </c>
+      <c r="G979" s="4" t="s">
+        <v>1402</v>
+      </c>
+      <c r="H979" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I979" s="4">
+        <v>249.99</v>
+      </c>
+      <c r="J979" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K979" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="L979" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="M979" s="4"/>
+      <c r="N979" s="4"/>
+      <c r="O979" s="4"/>
+      <c r="P979" s="4"/>
+      <c r="Q979" s="4"/>
+      <c r="R979" s="4"/>
+    </row>
+    <row r="980" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A980" s="2" t="s">
+        <v>1558</v>
+      </c>
+      <c r="B980" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="C980" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D980" s="4" t="s">
+        <v>1559</v>
+      </c>
+      <c r="E980" s="5" t="s">
+        <v>1560</v>
+      </c>
+      <c r="F980" s="4" t="s">
+        <v>1395</v>
+      </c>
+      <c r="G980" s="4" t="s">
+        <v>1473</v>
+      </c>
+      <c r="H980" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="I980" s="4">
+        <v>149.99</v>
+      </c>
+      <c r="J980" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K980" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="L980" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="M980" s="4"/>
+      <c r="N980" s="4"/>
+      <c r="O980" s="4"/>
+      <c r="P980" s="4"/>
+      <c r="Q980" s="4"/>
+      <c r="R980" s="4"/>
+    </row>
+    <row r="981" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A981" s="2" t="s">
+        <v>1561</v>
+      </c>
+      <c r="B981" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="C981" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D981" s="4" t="s">
+        <v>1559</v>
+      </c>
+      <c r="E981" s="5" t="s">
+        <v>1560</v>
+      </c>
+      <c r="F981" s="4" t="s">
+        <v>1395</v>
+      </c>
+      <c r="G981" s="4" t="s">
+        <v>1544</v>
+      </c>
+      <c r="H981" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="I981" s="4">
+        <v>149.99</v>
+      </c>
+      <c r="J981" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K981" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="L981" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="M981" s="4"/>
+      <c r="N981" s="4"/>
+      <c r="O981" s="4"/>
+      <c r="P981" s="4"/>
+      <c r="Q981" s="4"/>
+      <c r="R981" s="4"/>
+    </row>
+    <row r="982" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A982" s="2" t="s">
+        <v>1562</v>
+      </c>
+      <c r="B982" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="C982" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D982" s="4" t="s">
+        <v>1563</v>
+      </c>
+      <c r="E982" s="5" t="s">
+        <v>1564</v>
+      </c>
+      <c r="F982" s="4" t="s">
+        <v>1395</v>
+      </c>
+      <c r="G982" s="4" t="s">
+        <v>1473</v>
+      </c>
+      <c r="H982" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="I982" s="4">
+        <v>219.99</v>
+      </c>
+      <c r="J982" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K982" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="L982" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="M982" s="4"/>
+      <c r="N982" s="4"/>
+      <c r="O982" s="4"/>
+      <c r="P982" s="4"/>
+      <c r="Q982" s="4"/>
+      <c r="R982" s="4"/>
+    </row>
+    <row r="983" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A983" s="2" t="s">
+        <v>1565</v>
+      </c>
+      <c r="B983" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="C983" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D983" s="4" t="s">
+        <v>1563</v>
+      </c>
+      <c r="E983" s="5" t="s">
+        <v>1564</v>
+      </c>
+      <c r="F983" s="4" t="s">
+        <v>1395</v>
+      </c>
+      <c r="G983" s="4" t="s">
+        <v>1402</v>
+      </c>
+      <c r="H983" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="I983" s="4">
+        <v>219.99</v>
+      </c>
+      <c r="J983" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K983" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="L983" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="M983" s="4"/>
+      <c r="N983" s="4"/>
+      <c r="O983" s="4"/>
+      <c r="P983" s="4"/>
+      <c r="Q983" s="4"/>
+      <c r="R983" s="4"/>
+    </row>
+    <row r="984" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A984" s="2" t="s">
+        <v>1566</v>
+      </c>
+      <c r="B984" s="2" t="s">
+        <v>600</v>
+      </c>
+      <c r="C984" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D984" s="4" t="s">
+        <v>1567</v>
+      </c>
+      <c r="E984" s="5" t="s">
+        <v>1568</v>
+      </c>
+      <c r="F984" s="4" t="s">
+        <v>1392</v>
+      </c>
+      <c r="G984" s="4" t="s">
+        <v>1473</v>
+      </c>
+      <c r="H984" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="I984" s="4">
+        <v>119.99</v>
+      </c>
+      <c r="J984" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K984" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="L984" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="M984" s="4"/>
+      <c r="N984" s="4"/>
+      <c r="O984" s="4"/>
+      <c r="P984" s="4"/>
+      <c r="Q984" s="4"/>
+      <c r="R984" s="4"/>
+    </row>
+    <row r="985" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A985" s="2" t="s">
+        <v>1569</v>
+      </c>
+      <c r="B985" s="2" t="s">
+        <v>1570</v>
+      </c>
+      <c r="C985" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D985" s="4" t="s">
+        <v>1567</v>
+      </c>
+      <c r="E985" s="5" t="s">
+        <v>1568</v>
+      </c>
+      <c r="F985" s="4" t="s">
+        <v>1392</v>
+      </c>
+      <c r="G985" s="4" t="s">
+        <v>1571</v>
+      </c>
+      <c r="H985" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="I985" s="4">
+        <v>119.99</v>
+      </c>
+      <c r="J985" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K985" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="L985" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="M985" s="4"/>
+      <c r="N985" s="4"/>
+      <c r="O985" s="4"/>
+      <c r="P985" s="4"/>
+      <c r="Q985" s="4"/>
+      <c r="R985" s="4"/>
+    </row>
+    <row r="986" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A986" s="2" t="s">
+        <v>1572</v>
+      </c>
+      <c r="B986" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="C986" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D986" s="4" t="s">
+        <v>1573</v>
+      </c>
+      <c r="E986" s="5" t="s">
+        <v>1574</v>
+      </c>
+      <c r="F986" s="4" t="s">
+        <v>1392</v>
+      </c>
+      <c r="G986" s="4" t="s">
+        <v>649</v>
+      </c>
+      <c r="H986" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="I986" s="4">
+        <v>79.989999999999995</v>
+      </c>
+      <c r="J986" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K986" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="L986" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="M986" s="4"/>
+      <c r="N986" s="4"/>
+      <c r="O986" s="4"/>
+      <c r="P986" s="4"/>
+      <c r="Q986" s="4"/>
+      <c r="R986" s="4"/>
+    </row>
+    <row r="987" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A987" s="2" t="s">
+        <v>1575</v>
+      </c>
+      <c r="B987" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="C987" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D987" s="4" t="s">
+        <v>1573</v>
+      </c>
+      <c r="E987" s="5" t="s">
+        <v>1574</v>
+      </c>
+      <c r="F987" s="4" t="s">
+        <v>1392</v>
+      </c>
+      <c r="G987" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="H987" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="I987" s="4">
+        <v>79.989999999999995</v>
+      </c>
+      <c r="J987" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K987" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="L987" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="M987" s="4"/>
+      <c r="N987" s="4"/>
+      <c r="O987" s="4"/>
+      <c r="P987" s="4"/>
+      <c r="Q987" s="4"/>
+      <c r="R987" s="4"/>
+    </row>
+    <row r="988" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A988" s="2" t="s">
+        <v>1576</v>
+      </c>
+      <c r="B988" s="2" t="s">
+        <v>666</v>
+      </c>
+      <c r="C988" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D988" s="4" t="s">
+        <v>1577</v>
+      </c>
+      <c r="E988" s="5" t="s">
+        <v>1578</v>
+      </c>
+      <c r="F988" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="G988" s="4" t="s">
+        <v>1579</v>
+      </c>
+      <c r="H988" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="I988" s="4">
+        <v>99.99</v>
+      </c>
+      <c r="J988" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K988" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="L988" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="M988" s="4"/>
+      <c r="N988" s="4"/>
+      <c r="O988" s="4"/>
+      <c r="P988" s="4"/>
+      <c r="Q988" s="4"/>
+      <c r="R988" s="4"/>
+    </row>
+    <row r="989" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A989" s="2" t="s">
+        <v>1580</v>
+      </c>
+      <c r="B989" s="2" t="s">
+        <v>666</v>
+      </c>
+      <c r="C989" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D989" s="4" t="s">
+        <v>1577</v>
+      </c>
+      <c r="E989" s="5" t="s">
+        <v>1578</v>
+      </c>
+      <c r="F989" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="G989" s="4" t="s">
+        <v>1581</v>
+      </c>
+      <c r="H989" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="I989" s="4">
+        <v>99.99</v>
+      </c>
+      <c r="J989" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K989" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="L989" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="M989" s="4"/>
+      <c r="N989" s="4"/>
+      <c r="O989" s="4"/>
+      <c r="P989" s="4"/>
+      <c r="Q989" s="4"/>
+      <c r="R989" s="4"/>
+    </row>
+    <row r="990" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A990" s="2" t="s">
+        <v>1582</v>
+      </c>
+      <c r="B990" s="2" t="s">
+        <v>666</v>
+      </c>
+      <c r="C990" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D990" s="4" t="s">
+        <v>1577</v>
+      </c>
+      <c r="E990" s="5" t="s">
+        <v>1578</v>
+      </c>
+      <c r="F990" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="G990" s="4" t="s">
+        <v>1487</v>
+      </c>
+      <c r="H990" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="I990" s="4">
+        <v>99.99</v>
+      </c>
+      <c r="J990" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K990" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="L990" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="M990" s="4"/>
+      <c r="N990" s="4"/>
+      <c r="O990" s="4"/>
+      <c r="P990" s="4"/>
+      <c r="Q990" s="4"/>
+      <c r="R990" s="4"/>
+    </row>
+    <row r="991" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A991" s="2" t="s">
+        <v>1583</v>
+      </c>
+      <c r="B991" s="2" t="s">
+        <v>666</v>
+      </c>
+      <c r="C991" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D991" s="4" t="s">
+        <v>1584</v>
+      </c>
+      <c r="E991" s="5" t="s">
+        <v>1585</v>
+      </c>
+      <c r="F991" s="4" t="s">
+        <v>1393</v>
+      </c>
+      <c r="G991" s="4" t="s">
+        <v>1586</v>
+      </c>
+      <c r="H991" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I991" s="4">
+        <v>59.99</v>
+      </c>
+      <c r="J991" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K991" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="L991" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="M991" s="4"/>
+      <c r="N991" s="4"/>
+      <c r="O991" s="4"/>
+      <c r="P991" s="4"/>
+      <c r="Q991" s="4"/>
+      <c r="R991" s="4"/>
+    </row>
+    <row r="992" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A992" s="2" t="s">
+        <v>1587</v>
+      </c>
+      <c r="B992" s="2" t="s">
+        <v>666</v>
+      </c>
+      <c r="C992" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D992" s="4" t="s">
+        <v>1584</v>
+      </c>
+      <c r="E992" s="5" t="s">
+        <v>1585</v>
+      </c>
+      <c r="F992" s="4" t="s">
+        <v>1393</v>
+      </c>
+      <c r="G992" s="4" t="s">
+        <v>1588</v>
+      </c>
+      <c r="H992" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I992" s="4">
+        <v>59.99</v>
+      </c>
+      <c r="J992" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K992" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="L992" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="M992" s="4"/>
+      <c r="N992" s="4"/>
+      <c r="O992" s="4"/>
+      <c r="P992" s="4"/>
+      <c r="Q992" s="4"/>
+      <c r="R992" s="4"/>
+    </row>
+    <row r="993" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A993" s="2" t="s">
+        <v>1589</v>
+      </c>
+      <c r="B993" s="2" t="s">
+        <v>666</v>
+      </c>
+      <c r="C993" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D993" s="4" t="s">
+        <v>1584</v>
+      </c>
+      <c r="E993" s="5" t="s">
+        <v>1585</v>
+      </c>
+      <c r="F993" s="4" t="s">
+        <v>1393</v>
+      </c>
+      <c r="G993" s="4" t="s">
+        <v>1590</v>
+      </c>
+      <c r="H993" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I993" s="4">
+        <v>59.99</v>
+      </c>
+      <c r="J993" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K993" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="L993" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="M993" s="4"/>
+      <c r="N993" s="4"/>
+      <c r="O993" s="4"/>
+      <c r="P993" s="4"/>
+      <c r="Q993" s="4"/>
+      <c r="R993" s="4"/>
+    </row>
+    <row r="994" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A994" s="2" t="s">
+        <v>1591</v>
+      </c>
+      <c r="B994" s="2" t="s">
+        <v>666</v>
+      </c>
+      <c r="C994" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D994" s="4" t="s">
+        <v>1584</v>
+      </c>
+      <c r="E994" s="5" t="s">
+        <v>1585</v>
+      </c>
+      <c r="F994" s="4" t="s">
+        <v>1393</v>
+      </c>
+      <c r="G994" s="4" t="s">
+        <v>1592</v>
+      </c>
+      <c r="H994" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I994" s="4">
+        <v>59.99</v>
+      </c>
+      <c r="J994" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K994" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="L994" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="M994" s="4"/>
+      <c r="N994" s="4"/>
+      <c r="O994" s="4"/>
+      <c r="P994" s="4"/>
+      <c r="Q994" s="4"/>
+      <c r="R994" s="4"/>
+    </row>
+    <row r="995" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A995" s="2" t="s">
+        <v>1593</v>
+      </c>
+      <c r="B995" s="2" t="s">
+        <v>666</v>
+      </c>
+      <c r="C995" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D995" s="4" t="s">
+        <v>1594</v>
+      </c>
+      <c r="E995" s="5" t="s">
+        <v>1595</v>
+      </c>
+      <c r="F995" s="4" t="s">
+        <v>1394</v>
+      </c>
+      <c r="G995" s="4" t="s">
+        <v>1586</v>
+      </c>
+      <c r="H995" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="I995" s="4">
+        <v>59.99</v>
+      </c>
+      <c r="J995" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K995" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="L995" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="M995" s="4"/>
+      <c r="N995" s="4"/>
+      <c r="O995" s="4"/>
+      <c r="P995" s="4"/>
+      <c r="Q995" s="4"/>
+      <c r="R995" s="4"/>
+    </row>
+    <row r="996" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A996" s="2" t="s">
+        <v>1596</v>
+      </c>
+      <c r="B996" s="2" t="s">
+        <v>666</v>
+      </c>
+      <c r="C996" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D996" s="4" t="s">
+        <v>1594</v>
+      </c>
+      <c r="E996" s="5" t="s">
+        <v>1595</v>
+      </c>
+      <c r="F996" s="4" t="s">
+        <v>1394</v>
+      </c>
+      <c r="G996" s="4" t="s">
+        <v>1588</v>
+      </c>
+      <c r="H996" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="I996" s="4">
+        <v>59.99</v>
+      </c>
+      <c r="J996" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K996" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="L996" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="M996" s="4"/>
+      <c r="N996" s="4"/>
+      <c r="O996" s="4"/>
+      <c r="P996" s="4"/>
+      <c r="Q996" s="4"/>
+      <c r="R996" s="4"/>
+    </row>
+    <row r="997" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A997" s="2" t="s">
+        <v>1597</v>
+      </c>
+      <c r="B997" s="2" t="s">
+        <v>666</v>
+      </c>
+      <c r="C997" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D997" s="4" t="s">
+        <v>1594</v>
+      </c>
+      <c r="E997" s="5" t="s">
+        <v>1595</v>
+      </c>
+      <c r="F997" s="4" t="s">
+        <v>1394</v>
+      </c>
+      <c r="G997" s="4" t="s">
+        <v>1590</v>
+      </c>
+      <c r="H997" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="I997" s="4">
+        <v>59.99</v>
+      </c>
+      <c r="J997" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K997" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="L997" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="M997" s="4"/>
+      <c r="N997" s="4"/>
+      <c r="O997" s="4"/>
+      <c r="P997" s="4"/>
+      <c r="Q997" s="4"/>
+      <c r="R997" s="4"/>
+    </row>
+    <row r="998" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A998" s="2" t="s">
+        <v>1598</v>
+      </c>
+      <c r="B998" s="2" t="s">
+        <v>666</v>
+      </c>
+      <c r="C998" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D998" s="4" t="s">
+        <v>1594</v>
+      </c>
+      <c r="E998" s="5" t="s">
+        <v>1595</v>
+      </c>
+      <c r="F998" s="4" t="s">
+        <v>1394</v>
+      </c>
+      <c r="G998" s="4" t="s">
+        <v>1592</v>
+      </c>
+      <c r="H998" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="I998" s="4">
+        <v>59.99</v>
+      </c>
+      <c r="J998" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K998" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="L998" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="M998" s="4"/>
+      <c r="N998" s="4"/>
+      <c r="O998" s="4"/>
+      <c r="P998" s="4"/>
+      <c r="Q998" s="4"/>
+      <c r="R998" s="4"/>
+    </row>
+    <row r="999" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A999" s="2" t="s">
+        <v>1599</v>
+      </c>
+      <c r="B999" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="C999" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D999" s="4" t="s">
+        <v>1600</v>
+      </c>
+      <c r="E999" s="5" t="s">
+        <v>1601</v>
+      </c>
+      <c r="F999" s="4" t="s">
+        <v>1423</v>
+      </c>
+      <c r="G999" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="H999" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I999" s="4">
+        <v>159.99</v>
+      </c>
+      <c r="J999" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K999" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="L999" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="M999" s="4"/>
+      <c r="N999" s="4"/>
+      <c r="O999" s="4"/>
+      <c r="P999" s="4"/>
+      <c r="Q999" s="4"/>
+      <c r="R999" s="4"/>
+    </row>
+    <row r="1000" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1000" s="2" t="s">
+        <v>1602</v>
+      </c>
+      <c r="B1000" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="C1000" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D1000" s="4" t="s">
+        <v>1600</v>
+      </c>
+      <c r="E1000" s="5" t="s">
+        <v>1601</v>
+      </c>
+      <c r="F1000" s="4" t="s">
+        <v>1423</v>
+      </c>
+      <c r="G1000" s="4" t="s">
+        <v>1410</v>
+      </c>
+      <c r="H1000" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I1000" s="4">
+        <v>159.99</v>
+      </c>
+      <c r="J1000" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1000" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1000" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="M1000" s="4"/>
+      <c r="N1000" s="4"/>
+      <c r="O1000" s="4"/>
+      <c r="P1000" s="4"/>
+      <c r="Q1000" s="4"/>
+      <c r="R1000" s="4"/>
+    </row>
+    <row r="1001" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1001" s="2" t="s">
+        <v>1603</v>
+      </c>
+      <c r="B1001" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="C1001" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D1001" s="4" t="s">
+        <v>1604</v>
+      </c>
+      <c r="E1001" s="5" t="s">
+        <v>1605</v>
+      </c>
+      <c r="F1001" s="4" t="s">
+        <v>1423</v>
+      </c>
+      <c r="G1001" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="H1001" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I1001" s="4">
+        <v>189.99</v>
+      </c>
+      <c r="J1001" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1001" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1001" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="M1001" s="4"/>
+      <c r="N1001" s="4"/>
+      <c r="O1001" s="4"/>
+      <c r="P1001" s="4"/>
+      <c r="Q1001" s="4"/>
+      <c r="R1001" s="4"/>
+    </row>
+    <row r="1002" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1002" s="2" t="s">
+        <v>1606</v>
+      </c>
+      <c r="B1002" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="C1002" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D1002" s="4" t="s">
+        <v>1604</v>
+      </c>
+      <c r="E1002" s="5" t="s">
+        <v>1605</v>
+      </c>
+      <c r="F1002" s="4" t="s">
+        <v>1423</v>
+      </c>
+      <c r="G1002" s="4" t="s">
+        <v>1410</v>
+      </c>
+      <c r="H1002" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I1002" s="4">
+        <v>189.99</v>
+      </c>
+      <c r="J1002" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1002" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1002" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="M1002" s="4"/>
+      <c r="N1002" s="4"/>
+      <c r="O1002" s="4"/>
+      <c r="P1002" s="4"/>
+      <c r="Q1002" s="4"/>
+      <c r="R1002" s="4"/>
+    </row>
+    <row r="1003" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1003" s="2" t="s">
+        <v>1607</v>
+      </c>
+      <c r="B1003" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="C1003" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D1003" s="4" t="s">
+        <v>1608</v>
+      </c>
+      <c r="E1003" s="5" t="s">
+        <v>1609</v>
+      </c>
+      <c r="F1003" s="4" t="s">
+        <v>1390</v>
+      </c>
+      <c r="G1003" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="H1003" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1003" s="4">
+        <v>109.99</v>
+      </c>
+      <c r="J1003" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1003" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1003" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="M1003" s="4"/>
+      <c r="N1003" s="4"/>
+      <c r="O1003" s="4"/>
+      <c r="P1003" s="4"/>
+      <c r="Q1003" s="4"/>
+      <c r="R1003" s="4"/>
+    </row>
+    <row r="1004" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1004" s="2" t="s">
+        <v>1610</v>
+      </c>
+      <c r="B1004" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="C1004" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D1004" s="4" t="s">
+        <v>1608</v>
+      </c>
+      <c r="E1004" s="5" t="s">
+        <v>1609</v>
+      </c>
+      <c r="F1004" s="4" t="s">
+        <v>1390</v>
+      </c>
+      <c r="G1004" s="4" t="s">
+        <v>1439</v>
+      </c>
+      <c r="H1004" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1004" s="4">
+        <v>109.99</v>
+      </c>
+      <c r="J1004" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1004" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1004" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="M1004" s="4"/>
+      <c r="N1004" s="4"/>
+      <c r="O1004" s="4"/>
+      <c r="P1004" s="4"/>
+      <c r="Q1004" s="4"/>
+      <c r="R1004" s="4"/>
+    </row>
+    <row r="1005" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1005" s="2" t="s">
+        <v>1611</v>
+      </c>
+      <c r="B1005" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="C1005" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D1005" s="4" t="s">
+        <v>1608</v>
+      </c>
+      <c r="E1005" s="5" t="s">
+        <v>1609</v>
+      </c>
+      <c r="F1005" s="4" t="s">
+        <v>1390</v>
+      </c>
+      <c r="G1005" s="4" t="s">
+        <v>1408</v>
+      </c>
+      <c r="H1005" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1005" s="4">
+        <v>109.99</v>
+      </c>
+      <c r="J1005" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1005" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1005" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="M1005" s="4"/>
+      <c r="N1005" s="4"/>
+      <c r="O1005" s="4"/>
+      <c r="P1005" s="4"/>
+      <c r="Q1005" s="4"/>
+      <c r="R1005" s="4"/>
+    </row>
+    <row r="1006" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1006" s="2" t="s">
+        <v>1612</v>
+      </c>
+      <c r="B1006" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="C1006" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="D1006" s="4" t="s">
+        <v>1613</v>
+      </c>
+      <c r="E1006" s="5" t="s">
+        <v>1614</v>
+      </c>
+      <c r="F1006" s="4" t="s">
+        <v>1390</v>
+      </c>
+      <c r="G1006" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="H1006" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I1006" s="4">
+        <v>149.99</v>
+      </c>
+      <c r="J1006" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1006" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1006" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="M1006" s="4"/>
+      <c r="N1006" s="4"/>
+      <c r="O1006" s="4"/>
+      <c r="P1006" s="4"/>
+      <c r="Q1006" s="4"/>
+      <c r="R1006" s="4"/>
+    </row>
+    <row r="1007" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1007" s="2" t="s">
+        <v>1615</v>
+      </c>
+      <c r="B1007" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="C1007" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="D1007" s="4" t="s">
+        <v>1613</v>
+      </c>
+      <c r="E1007" s="5" t="s">
+        <v>1614</v>
+      </c>
+      <c r="F1007" s="4" t="s">
+        <v>1390</v>
+      </c>
+      <c r="G1007" s="4" t="s">
+        <v>633</v>
+      </c>
+      <c r="H1007" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I1007" s="4">
+        <v>149.99</v>
+      </c>
+      <c r="J1007" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1007" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1007" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="M1007" s="4"/>
+      <c r="N1007" s="4"/>
+      <c r="O1007" s="4"/>
+      <c r="P1007" s="4"/>
+      <c r="Q1007" s="4"/>
+      <c r="R1007" s="4"/>
+    </row>
+    <row r="1008" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1008" s="2" t="s">
+        <v>1616</v>
+      </c>
+      <c r="B1008" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="C1008" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="D1008" s="4" t="s">
+        <v>1617</v>
+      </c>
+      <c r="E1008" s="5" t="s">
+        <v>1618</v>
+      </c>
+      <c r="F1008" s="4" t="s">
+        <v>1390</v>
+      </c>
+      <c r="G1008" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="H1008" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1008" s="4">
+        <v>149.99</v>
+      </c>
+      <c r="J1008" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1008" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1008" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="M1008" s="4"/>
+      <c r="N1008" s="4"/>
+      <c r="O1008" s="4"/>
+      <c r="P1008" s="4"/>
+      <c r="Q1008" s="4"/>
+      <c r="R1008" s="4"/>
+    </row>
+    <row r="1009" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1009" s="2" t="s">
+        <v>1619</v>
+      </c>
+      <c r="B1009" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="C1009" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="D1009" s="4" t="s">
+        <v>1617</v>
+      </c>
+      <c r="E1009" s="5" t="s">
+        <v>1618</v>
+      </c>
+      <c r="F1009" s="4" t="s">
+        <v>1390</v>
+      </c>
+      <c r="G1009" s="4" t="s">
+        <v>633</v>
+      </c>
+      <c r="H1009" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1009" s="4">
+        <v>149.99</v>
+      </c>
+      <c r="J1009" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1009" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1009" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="M1009" s="4"/>
+      <c r="N1009" s="4"/>
+      <c r="O1009" s="4"/>
+      <c r="P1009" s="4"/>
+      <c r="Q1009" s="4"/>
+      <c r="R1009" s="4"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:R899" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Produtos.xlsx
+++ b/Produtos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NOT-MARCOS\Documents\GitHub\Catalogo-Olympikus_2.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF8354EB-69D3-4779-93AA-7CA0B081CEFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C420C5A-14E2-401B-8927-7194F891583B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Produtos" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Produtos!$A$1:$R$899</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Produtos!$A$1:$R$1009</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -4280,9 +4280,6 @@
     <t>TOP KNIT MINIMAL F</t>
   </si>
   <si>
-    <t>OIWSC26601_PTPRT</t>
-  </si>
-  <si>
     <t>OIWSC26601_VIOLET</t>
   </si>
   <si>
@@ -4896,6 +4893,9 @@
   </si>
   <si>
     <t>OBMSR241922_BFCBPO</t>
+  </si>
+  <si>
+    <t>OIWSC26601_TAPTRY</t>
   </si>
 </sst>
 </file>
@@ -5342,7 +5342,7 @@
   <dimension ref="A1:R1009"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.140625" customWidth="1"/>
     <col min="2" max="4" width="15" customWidth="1"/>
     <col min="5" max="5" width="19" style="6" customWidth="1"/>
     <col min="6" max="9" width="15" customWidth="1"/>
@@ -48356,7 +48356,7 @@
     </row>
     <row r="908" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A908" s="2" t="s">
-        <v>1414</v>
+        <v>1619</v>
       </c>
       <c r="B908" s="2" t="s">
         <v>565</v>
@@ -48400,7 +48400,7 @@
     </row>
     <row r="909" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A909" s="2" t="s">
-        <v>1415</v>
+        <v>1414</v>
       </c>
       <c r="B909" s="2" t="s">
         <v>565</v>
@@ -48412,7 +48412,7 @@
         <v>1008</v>
       </c>
       <c r="E909" s="5" t="s">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="F909" s="4" t="s">
         <v>1390</v>
@@ -48444,7 +48444,7 @@
     </row>
     <row r="910" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A910" s="2" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="B910" s="2" t="s">
         <v>565</v>
@@ -48462,7 +48462,7 @@
         <v>1390</v>
       </c>
       <c r="G910" s="4" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="H910" s="4" t="s">
         <v>32</v>
@@ -48488,7 +48488,7 @@
     </row>
     <row r="911" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A911" s="2" t="s">
-        <v>1419</v>
+        <v>1418</v>
       </c>
       <c r="B911" s="2" t="s">
         <v>565</v>
@@ -48506,7 +48506,7 @@
         <v>1390</v>
       </c>
       <c r="G911" s="4" t="s">
-        <v>1420</v>
+        <v>1419</v>
       </c>
       <c r="H911" s="4" t="s">
         <v>32</v>
@@ -48532,7 +48532,7 @@
     </row>
     <row r="912" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A912" s="2" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="B912" s="2" t="s">
         <v>565</v>
@@ -48544,10 +48544,10 @@
         <v>1023</v>
       </c>
       <c r="E912" s="5" t="s">
+        <v>1421</v>
+      </c>
+      <c r="F912" s="4" t="s">
         <v>1422</v>
-      </c>
-      <c r="F912" s="4" t="s">
-        <v>1423</v>
       </c>
       <c r="G912" s="4" t="s">
         <v>1408</v>
@@ -48576,7 +48576,7 @@
     </row>
     <row r="913" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A913" s="2" t="s">
-        <v>1424</v>
+        <v>1423</v>
       </c>
       <c r="B913" s="2" t="s">
         <v>565</v>
@@ -48588,10 +48588,10 @@
         <v>1034</v>
       </c>
       <c r="E913" s="5" t="s">
-        <v>1425</v>
+        <v>1424</v>
       </c>
       <c r="F913" s="4" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
       <c r="G913" s="4" t="s">
         <v>29</v>
@@ -48620,7 +48620,7 @@
     </row>
     <row r="914" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A914" s="2" t="s">
-        <v>1426</v>
+        <v>1425</v>
       </c>
       <c r="B914" s="2" t="s">
         <v>565</v>
@@ -48632,10 +48632,10 @@
         <v>1034</v>
       </c>
       <c r="E914" s="5" t="s">
-        <v>1425</v>
+        <v>1424</v>
       </c>
       <c r="F914" s="4" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
       <c r="G914" s="4" t="s">
         <v>1408</v>
@@ -48664,7 +48664,7 @@
     </row>
     <row r="915" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A915" s="2" t="s">
-        <v>1427</v>
+        <v>1426</v>
       </c>
       <c r="B915" s="2" t="s">
         <v>565</v>
@@ -48676,10 +48676,10 @@
         <v>1034</v>
       </c>
       <c r="E915" s="5" t="s">
-        <v>1425</v>
+        <v>1424</v>
       </c>
       <c r="F915" s="4" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
       <c r="G915" s="4" t="s">
         <v>1410</v>
@@ -48708,7 +48708,7 @@
     </row>
     <row r="916" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A916" s="2" t="s">
-        <v>1428</v>
+        <v>1427</v>
       </c>
       <c r="B916" s="2" t="s">
         <v>565</v>
@@ -48720,7 +48720,7 @@
         <v>1034</v>
       </c>
       <c r="E916" s="5" t="s">
-        <v>1425</v>
+        <v>1424</v>
       </c>
       <c r="F916" s="4" t="s">
         <v>1390</v>
@@ -48752,7 +48752,7 @@
     </row>
     <row r="917" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A917" s="2" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="B917" s="2" t="s">
         <v>565</v>
@@ -48761,13 +48761,13 @@
         <v>51</v>
       </c>
       <c r="D917" s="4" t="s">
+        <v>1429</v>
+      </c>
+      <c r="E917" s="5" t="s">
         <v>1430</v>
       </c>
-      <c r="E917" s="5" t="s">
-        <v>1431</v>
-      </c>
       <c r="F917" s="4" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
       <c r="G917" s="4" t="s">
         <v>1408</v>
@@ -48796,7 +48796,7 @@
     </row>
     <row r="918" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A918" s="2" t="s">
-        <v>1432</v>
+        <v>1431</v>
       </c>
       <c r="B918" s="2" t="s">
         <v>565</v>
@@ -48805,13 +48805,13 @@
         <v>51</v>
       </c>
       <c r="D918" s="4" t="s">
+        <v>1429</v>
+      </c>
+      <c r="E918" s="5" t="s">
         <v>1430</v>
       </c>
-      <c r="E918" s="5" t="s">
-        <v>1431</v>
-      </c>
       <c r="F918" s="4" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
       <c r="G918" s="4" t="s">
         <v>1410</v>
@@ -48840,7 +48840,7 @@
     </row>
     <row r="919" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A919" s="2" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
       <c r="B919" s="2" t="s">
         <v>565</v>
@@ -48884,7 +48884,7 @@
     </row>
     <row r="920" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A920" s="2" t="s">
-        <v>1434</v>
+        <v>1433</v>
       </c>
       <c r="B920" s="2" t="s">
         <v>565</v>
@@ -48928,7 +48928,7 @@
     </row>
     <row r="921" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A921" s="2" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="B921" s="2" t="s">
         <v>565</v>
@@ -48940,7 +48940,7 @@
         <v>1065</v>
       </c>
       <c r="E921" s="5" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="F921" s="4" t="s">
         <v>1390</v>
@@ -48972,7 +48972,7 @@
     </row>
     <row r="922" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A922" s="2" t="s">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="B922" s="2" t="s">
         <v>565</v>
@@ -48984,13 +48984,13 @@
         <v>1098</v>
       </c>
       <c r="E922" s="5" t="s">
+        <v>1437</v>
+      </c>
+      <c r="F922" s="4" t="s">
+        <v>1422</v>
+      </c>
+      <c r="G922" s="4" t="s">
         <v>1438</v>
-      </c>
-      <c r="F922" s="4" t="s">
-        <v>1423</v>
-      </c>
-      <c r="G922" s="4" t="s">
-        <v>1439</v>
       </c>
       <c r="H922" s="4" t="s">
         <v>32</v>
@@ -49016,7 +49016,7 @@
     </row>
     <row r="923" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A923" s="2" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="B923" s="2" t="s">
         <v>565</v>
@@ -49028,13 +49028,13 @@
         <v>1113</v>
       </c>
       <c r="E923" s="5" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="F923" s="4" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
       <c r="G923" s="4" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="H923" s="4" t="s">
         <v>32</v>
@@ -49060,7 +49060,7 @@
     </row>
     <row r="924" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A924" s="2" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="B924" s="2" t="s">
         <v>565</v>
@@ -49069,16 +49069,16 @@
         <v>51</v>
       </c>
       <c r="D924" s="4" t="s">
+        <v>1442</v>
+      </c>
+      <c r="E924" s="5" t="s">
         <v>1443</v>
       </c>
-      <c r="E924" s="5" t="s">
-        <v>1444</v>
-      </c>
       <c r="F924" s="4" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
       <c r="G924" s="4" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="H924" s="4" t="s">
         <v>32</v>
@@ -49104,7 +49104,7 @@
     </row>
     <row r="925" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A925" s="2" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="B925" s="2" t="s">
         <v>565</v>
@@ -49119,10 +49119,10 @@
         <v>1131</v>
       </c>
       <c r="F925" s="4" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
       <c r="G925" s="4" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="H925" s="4" t="s">
         <v>32</v>
@@ -49148,7 +49148,7 @@
     </row>
     <row r="926" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A926" s="2" t="s">
-        <v>1446</v>
+        <v>1445</v>
       </c>
       <c r="B926" s="2" t="s">
         <v>565</v>
@@ -49166,7 +49166,7 @@
         <v>1390</v>
       </c>
       <c r="G926" s="4" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="H926" s="4" t="s">
         <v>32</v>
@@ -49192,7 +49192,7 @@
     </row>
     <row r="927" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A927" s="2" t="s">
-        <v>1447</v>
+        <v>1446</v>
       </c>
       <c r="B927" s="2" t="s">
         <v>565</v>
@@ -49204,13 +49204,13 @@
         <v>1140</v>
       </c>
       <c r="E927" s="5" t="s">
-        <v>1448</v>
+        <v>1447</v>
       </c>
       <c r="F927" s="4" t="s">
         <v>1390</v>
       </c>
       <c r="G927" s="4" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="H927" s="4" t="s">
         <v>32</v>
@@ -49236,7 +49236,7 @@
     </row>
     <row r="928" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A928" s="2" t="s">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="B928" s="2" t="s">
         <v>565</v>
@@ -49245,10 +49245,10 @@
         <v>51</v>
       </c>
       <c r="D928" s="4" t="s">
+        <v>1449</v>
+      </c>
+      <c r="E928" s="5" t="s">
         <v>1450</v>
-      </c>
-      <c r="E928" s="5" t="s">
-        <v>1451</v>
       </c>
       <c r="F928" s="4" t="s">
         <v>1390</v>
@@ -49280,7 +49280,7 @@
     </row>
     <row r="929" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A929" s="2" t="s">
-        <v>1452</v>
+        <v>1451</v>
       </c>
       <c r="B929" s="2" t="s">
         <v>565</v>
@@ -49324,7 +49324,7 @@
     </row>
     <row r="930" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A930" s="2" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="B930" s="2" t="s">
         <v>666</v>
@@ -49336,13 +49336,13 @@
         <v>973</v>
       </c>
       <c r="E930" s="5" t="s">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="F930" s="4" t="s">
         <v>1393</v>
       </c>
       <c r="G930" s="4" t="s">
-        <v>1455</v>
+        <v>1454</v>
       </c>
       <c r="H930" s="4" t="s">
         <v>10</v>
@@ -49368,7 +49368,7 @@
     </row>
     <row r="931" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A931" s="2" t="s">
-        <v>1456</v>
+        <v>1455</v>
       </c>
       <c r="B931" s="2" t="s">
         <v>666</v>
@@ -49380,13 +49380,13 @@
         <v>973</v>
       </c>
       <c r="E931" s="5" t="s">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="F931" s="4" t="s">
         <v>1393</v>
       </c>
       <c r="G931" s="4" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
       <c r="H931" s="4" t="s">
         <v>10</v>
@@ -49412,7 +49412,7 @@
     </row>
     <row r="932" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A932" s="2" t="s">
-        <v>1458</v>
+        <v>1457</v>
       </c>
       <c r="B932" s="2" t="s">
         <v>666</v>
@@ -49424,13 +49424,13 @@
         <v>980</v>
       </c>
       <c r="E932" s="5" t="s">
-        <v>1459</v>
+        <v>1458</v>
       </c>
       <c r="F932" s="4" t="s">
         <v>1393</v>
       </c>
       <c r="G932" s="4" t="s">
-        <v>1460</v>
+        <v>1459</v>
       </c>
       <c r="H932" s="4" t="s">
         <v>10</v>
@@ -49456,7 +49456,7 @@
     </row>
     <row r="933" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A933" s="2" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
       <c r="B933" s="2" t="s">
         <v>666</v>
@@ -49468,13 +49468,13 @@
         <v>980</v>
       </c>
       <c r="E933" s="5" t="s">
-        <v>1459</v>
+        <v>1458</v>
       </c>
       <c r="F933" s="4" t="s">
         <v>1393</v>
       </c>
       <c r="G933" s="4" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
       <c r="H933" s="4" t="s">
         <v>10</v>
@@ -49500,7 +49500,7 @@
     </row>
     <row r="934" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A934" s="2" t="s">
-        <v>1463</v>
+        <v>1462</v>
       </c>
       <c r="B934" s="2" t="s">
         <v>666</v>
@@ -49512,13 +49512,13 @@
         <v>993</v>
       </c>
       <c r="E934" s="5" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
       <c r="F934" s="4" t="s">
         <v>1394</v>
       </c>
       <c r="G934" s="4" t="s">
-        <v>1455</v>
+        <v>1454</v>
       </c>
       <c r="H934" s="4" t="s">
         <v>32</v>
@@ -49544,7 +49544,7 @@
     </row>
     <row r="935" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A935" s="2" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="B935" s="2" t="s">
         <v>666</v>
@@ -49556,13 +49556,13 @@
         <v>993</v>
       </c>
       <c r="E935" s="5" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
       <c r="F935" s="4" t="s">
         <v>1394</v>
       </c>
       <c r="G935" s="4" t="s">
-        <v>1457</v>
+        <v>1456</v>
       </c>
       <c r="H935" s="4" t="s">
         <v>32</v>
@@ -49588,7 +49588,7 @@
     </row>
     <row r="936" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A936" s="2" t="s">
-        <v>1466</v>
+        <v>1465</v>
       </c>
       <c r="B936" s="2" t="s">
         <v>666</v>
@@ -49600,13 +49600,13 @@
         <v>997</v>
       </c>
       <c r="E936" s="5" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
       <c r="F936" s="4" t="s">
         <v>1394</v>
       </c>
       <c r="G936" s="4" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
       <c r="H936" s="4" t="s">
         <v>32</v>
@@ -49632,7 +49632,7 @@
     </row>
     <row r="937" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A937" s="2" t="s">
-        <v>1469</v>
+        <v>1468</v>
       </c>
       <c r="B937" s="2" t="s">
         <v>666</v>
@@ -49644,13 +49644,13 @@
         <v>997</v>
       </c>
       <c r="E937" s="5" t="s">
-        <v>1467</v>
+        <v>1466</v>
       </c>
       <c r="F937" s="4" t="s">
         <v>1394</v>
       </c>
       <c r="G937" s="4" t="s">
-        <v>1462</v>
+        <v>1461</v>
       </c>
       <c r="H937" s="4" t="s">
         <v>32</v>
@@ -49676,7 +49676,7 @@
     </row>
     <row r="938" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A938" s="2" t="s">
-        <v>1470</v>
+        <v>1469</v>
       </c>
       <c r="B938" s="2" t="s">
         <v>565</v>
@@ -49685,16 +49685,16 @@
         <v>9</v>
       </c>
       <c r="D938" s="4" t="s">
+        <v>1470</v>
+      </c>
+      <c r="E938" s="5" t="s">
         <v>1471</v>
-      </c>
-      <c r="E938" s="5" t="s">
-        <v>1472</v>
       </c>
       <c r="F938" s="4" t="s">
         <v>1395</v>
       </c>
       <c r="G938" s="4" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="H938" s="4" t="s">
         <v>10</v>
@@ -49720,7 +49720,7 @@
     </row>
     <row r="939" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A939" s="2" t="s">
-        <v>1474</v>
+        <v>1473</v>
       </c>
       <c r="B939" s="2" t="s">
         <v>565</v>
@@ -49729,10 +49729,10 @@
         <v>9</v>
       </c>
       <c r="D939" s="4" t="s">
+        <v>1470</v>
+      </c>
+      <c r="E939" s="5" t="s">
         <v>1471</v>
-      </c>
-      <c r="E939" s="5" t="s">
-        <v>1472</v>
       </c>
       <c r="F939" s="4" t="s">
         <v>1395</v>
@@ -49764,7 +49764,7 @@
     </row>
     <row r="940" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A940" s="2" t="s">
-        <v>1475</v>
+        <v>1474</v>
       </c>
       <c r="B940" s="2" t="s">
         <v>565</v>
@@ -49773,16 +49773,16 @@
         <v>9</v>
       </c>
       <c r="D940" s="4" t="s">
+        <v>1475</v>
+      </c>
+      <c r="E940" s="5" t="s">
         <v>1476</v>
-      </c>
-      <c r="E940" s="5" t="s">
-        <v>1477</v>
       </c>
       <c r="F940" s="4" t="s">
         <v>1395</v>
       </c>
       <c r="G940" s="4" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="H940" s="4" t="s">
         <v>10</v>
@@ -49808,7 +49808,7 @@
     </row>
     <row r="941" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A941" s="2" t="s">
-        <v>1478</v>
+        <v>1477</v>
       </c>
       <c r="B941" s="2" t="s">
         <v>565</v>
@@ -49817,16 +49817,16 @@
         <v>9</v>
       </c>
       <c r="D941" s="4" t="s">
+        <v>1475</v>
+      </c>
+      <c r="E941" s="5" t="s">
         <v>1476</v>
-      </c>
-      <c r="E941" s="5" t="s">
-        <v>1477</v>
       </c>
       <c r="F941" s="4" t="s">
         <v>1395</v>
       </c>
       <c r="G941" s="4" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="H941" s="4" t="s">
         <v>10</v>
@@ -49852,7 +49852,7 @@
     </row>
     <row r="942" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A942" s="2" t="s">
-        <v>1480</v>
+        <v>1479</v>
       </c>
       <c r="B942" s="2" t="s">
         <v>565</v>
@@ -49861,16 +49861,16 @@
         <v>9</v>
       </c>
       <c r="D942" s="4" t="s">
+        <v>1480</v>
+      </c>
+      <c r="E942" s="5" t="s">
         <v>1481</v>
-      </c>
-      <c r="E942" s="5" t="s">
-        <v>1482</v>
       </c>
       <c r="F942" s="4" t="s">
         <v>1395</v>
       </c>
       <c r="G942" s="4" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="H942" s="4" t="s">
         <v>10</v>
@@ -49896,7 +49896,7 @@
     </row>
     <row r="943" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A943" s="2" t="s">
-        <v>1483</v>
+        <v>1482</v>
       </c>
       <c r="B943" s="2" t="s">
         <v>565</v>
@@ -49905,10 +49905,10 @@
         <v>9</v>
       </c>
       <c r="D943" s="4" t="s">
+        <v>1480</v>
+      </c>
+      <c r="E943" s="5" t="s">
         <v>1481</v>
-      </c>
-      <c r="E943" s="5" t="s">
-        <v>1482</v>
       </c>
       <c r="F943" s="4" t="s">
         <v>1395</v>
@@ -49940,7 +49940,7 @@
     </row>
     <row r="944" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A944" s="2" t="s">
-        <v>1484</v>
+        <v>1483</v>
       </c>
       <c r="B944" s="2" t="s">
         <v>565</v>
@@ -49949,16 +49949,16 @@
         <v>9</v>
       </c>
       <c r="D944" s="4" t="s">
+        <v>1484</v>
+      </c>
+      <c r="E944" s="5" t="s">
         <v>1485</v>
-      </c>
-      <c r="E944" s="5" t="s">
-        <v>1486</v>
       </c>
       <c r="F944" s="4" t="s">
         <v>1395</v>
       </c>
       <c r="G944" s="4" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="H944" s="4" t="s">
         <v>10</v>
@@ -49984,7 +49984,7 @@
     </row>
     <row r="945" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A945" s="2" t="s">
-        <v>1488</v>
+        <v>1487</v>
       </c>
       <c r="B945" s="2" t="s">
         <v>565</v>
@@ -49993,10 +49993,10 @@
         <v>9</v>
       </c>
       <c r="D945" s="4" t="s">
+        <v>1484</v>
+      </c>
+      <c r="E945" s="5" t="s">
         <v>1485</v>
-      </c>
-      <c r="E945" s="5" t="s">
-        <v>1486</v>
       </c>
       <c r="F945" s="4" t="s">
         <v>1395</v>
@@ -50028,7 +50028,7 @@
     </row>
     <row r="946" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A946" s="2" t="s">
-        <v>1489</v>
+        <v>1488</v>
       </c>
       <c r="B946" s="2" t="s">
         <v>565</v>
@@ -50037,16 +50037,16 @@
         <v>9</v>
       </c>
       <c r="D946" s="4" t="s">
+        <v>1489</v>
+      </c>
+      <c r="E946" s="5" t="s">
         <v>1490</v>
-      </c>
-      <c r="E946" s="5" t="s">
-        <v>1491</v>
       </c>
       <c r="F946" s="4" t="s">
         <v>1395</v>
       </c>
       <c r="G946" s="4" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="H946" s="4" t="s">
         <v>10</v>
@@ -50072,7 +50072,7 @@
     </row>
     <row r="947" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A947" s="2" t="s">
-        <v>1492</v>
+        <v>1491</v>
       </c>
       <c r="B947" s="2" t="s">
         <v>565</v>
@@ -50081,16 +50081,16 @@
         <v>9</v>
       </c>
       <c r="D947" s="4" t="s">
+        <v>1489</v>
+      </c>
+      <c r="E947" s="5" t="s">
         <v>1490</v>
-      </c>
-      <c r="E947" s="5" t="s">
-        <v>1491</v>
       </c>
       <c r="F947" s="4" t="s">
         <v>1395</v>
       </c>
       <c r="G947" s="4" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="H947" s="4" t="s">
         <v>10</v>
@@ -50116,7 +50116,7 @@
     </row>
     <row r="948" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A948" s="2" t="s">
-        <v>1493</v>
+        <v>1492</v>
       </c>
       <c r="B948" s="2" t="s">
         <v>565</v>
@@ -50125,10 +50125,10 @@
         <v>9</v>
       </c>
       <c r="D948" s="4" t="s">
+        <v>1489</v>
+      </c>
+      <c r="E948" s="5" t="s">
         <v>1490</v>
-      </c>
-      <c r="E948" s="5" t="s">
-        <v>1491</v>
       </c>
       <c r="F948" s="4" t="s">
         <v>1395</v>
@@ -50160,7 +50160,7 @@
     </row>
     <row r="949" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A949" s="2" t="s">
-        <v>1494</v>
+        <v>1493</v>
       </c>
       <c r="B949" s="2" t="s">
         <v>565</v>
@@ -50169,16 +50169,16 @@
         <v>9</v>
       </c>
       <c r="D949" s="4" t="s">
+        <v>1494</v>
+      </c>
+      <c r="E949" s="5" t="s">
         <v>1495</v>
-      </c>
-      <c r="E949" s="5" t="s">
-        <v>1496</v>
       </c>
       <c r="F949" s="4" t="s">
         <v>1395</v>
       </c>
       <c r="G949" s="4" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="H949" s="4" t="s">
         <v>10</v>
@@ -50204,7 +50204,7 @@
     </row>
     <row r="950" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A950" s="2" t="s">
-        <v>1497</v>
+        <v>1496</v>
       </c>
       <c r="B950" s="2" t="s">
         <v>565</v>
@@ -50213,10 +50213,10 @@
         <v>9</v>
       </c>
       <c r="D950" s="4" t="s">
+        <v>1494</v>
+      </c>
+      <c r="E950" s="5" t="s">
         <v>1495</v>
-      </c>
-      <c r="E950" s="5" t="s">
-        <v>1496</v>
       </c>
       <c r="F950" s="4" t="s">
         <v>1395</v>
@@ -50248,7 +50248,7 @@
     </row>
     <row r="951" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A951" s="2" t="s">
-        <v>1498</v>
+        <v>1497</v>
       </c>
       <c r="B951" s="2" t="s">
         <v>565</v>
@@ -50257,16 +50257,16 @@
         <v>9</v>
       </c>
       <c r="D951" s="4" t="s">
+        <v>1498</v>
+      </c>
+      <c r="E951" s="5" t="s">
         <v>1499</v>
-      </c>
-      <c r="E951" s="5" t="s">
-        <v>1500</v>
       </c>
       <c r="F951" s="4" t="s">
         <v>1395</v>
       </c>
       <c r="G951" s="4" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="H951" s="4" t="s">
         <v>10</v>
@@ -50292,7 +50292,7 @@
     </row>
     <row r="952" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A952" s="2" t="s">
-        <v>1501</v>
+        <v>1500</v>
       </c>
       <c r="B952" s="2" t="s">
         <v>565</v>
@@ -50301,16 +50301,16 @@
         <v>9</v>
       </c>
       <c r="D952" s="4" t="s">
+        <v>1498</v>
+      </c>
+      <c r="E952" s="5" t="s">
         <v>1499</v>
-      </c>
-      <c r="E952" s="5" t="s">
-        <v>1500</v>
       </c>
       <c r="F952" s="4" t="s">
         <v>1395</v>
       </c>
       <c r="G952" s="4" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="H952" s="4" t="s">
         <v>10</v>
@@ -50336,7 +50336,7 @@
     </row>
     <row r="953" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A953" s="2" t="s">
-        <v>1502</v>
+        <v>1501</v>
       </c>
       <c r="B953" s="2" t="s">
         <v>565</v>
@@ -50345,16 +50345,16 @@
         <v>9</v>
       </c>
       <c r="D953" s="4" t="s">
+        <v>1502</v>
+      </c>
+      <c r="E953" s="5" t="s">
         <v>1503</v>
-      </c>
-      <c r="E953" s="5" t="s">
-        <v>1504</v>
       </c>
       <c r="F953" s="4" t="s">
         <v>1395</v>
       </c>
       <c r="G953" s="4" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="H953" s="4" t="s">
         <v>10</v>
@@ -50380,7 +50380,7 @@
     </row>
     <row r="954" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A954" s="2" t="s">
-        <v>1505</v>
+        <v>1504</v>
       </c>
       <c r="B954" s="2" t="s">
         <v>565</v>
@@ -50389,10 +50389,10 @@
         <v>9</v>
       </c>
       <c r="D954" s="4" t="s">
+        <v>1502</v>
+      </c>
+      <c r="E954" s="5" t="s">
         <v>1503</v>
-      </c>
-      <c r="E954" s="5" t="s">
-        <v>1504</v>
       </c>
       <c r="F954" s="4" t="s">
         <v>1395</v>
@@ -50424,7 +50424,7 @@
     </row>
     <row r="955" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A955" s="2" t="s">
-        <v>1506</v>
+        <v>1505</v>
       </c>
       <c r="B955" s="2" t="s">
         <v>565</v>
@@ -50433,10 +50433,10 @@
         <v>9</v>
       </c>
       <c r="D955" s="4" t="s">
+        <v>1506</v>
+      </c>
+      <c r="E955" s="5" t="s">
         <v>1507</v>
-      </c>
-      <c r="E955" s="5" t="s">
-        <v>1508</v>
       </c>
       <c r="F955" s="4" t="s">
         <v>1395</v>
@@ -50468,7 +50468,7 @@
     </row>
     <row r="956" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A956" s="2" t="s">
-        <v>1509</v>
+        <v>1508</v>
       </c>
       <c r="B956" s="2" t="s">
         <v>565</v>
@@ -50477,16 +50477,16 @@
         <v>9</v>
       </c>
       <c r="D956" s="4" t="s">
+        <v>1509</v>
+      </c>
+      <c r="E956" s="5" t="s">
         <v>1510</v>
-      </c>
-      <c r="E956" s="5" t="s">
-        <v>1511</v>
       </c>
       <c r="F956" s="4" t="s">
         <v>1395</v>
       </c>
       <c r="G956" s="4" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="H956" s="4" t="s">
         <v>32</v>
@@ -50512,7 +50512,7 @@
     </row>
     <row r="957" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A957" s="2" t="s">
-        <v>1512</v>
+        <v>1511</v>
       </c>
       <c r="B957" s="2" t="s">
         <v>565</v>
@@ -50521,10 +50521,10 @@
         <v>9</v>
       </c>
       <c r="D957" s="4" t="s">
+        <v>1509</v>
+      </c>
+      <c r="E957" s="5" t="s">
         <v>1510</v>
-      </c>
-      <c r="E957" s="5" t="s">
-        <v>1511</v>
       </c>
       <c r="F957" s="4" t="s">
         <v>1395</v>
@@ -50556,7 +50556,7 @@
     </row>
     <row r="958" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A958" s="2" t="s">
-        <v>1513</v>
+        <v>1512</v>
       </c>
       <c r="B958" s="2" t="s">
         <v>565</v>
@@ -50565,10 +50565,10 @@
         <v>9</v>
       </c>
       <c r="D958" s="4" t="s">
+        <v>1513</v>
+      </c>
+      <c r="E958" s="5" t="s">
         <v>1514</v>
-      </c>
-      <c r="E958" s="5" t="s">
-        <v>1515</v>
       </c>
       <c r="F958" s="4" t="s">
         <v>1395</v>
@@ -50600,7 +50600,7 @@
     </row>
     <row r="959" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A959" s="2" t="s">
-        <v>1516</v>
+        <v>1515</v>
       </c>
       <c r="B959" s="2" t="s">
         <v>565</v>
@@ -50609,10 +50609,10 @@
         <v>9</v>
       </c>
       <c r="D959" s="4" t="s">
+        <v>1513</v>
+      </c>
+      <c r="E959" s="5" t="s">
         <v>1514</v>
-      </c>
-      <c r="E959" s="5" t="s">
-        <v>1515</v>
       </c>
       <c r="F959" s="4" t="s">
         <v>1395</v>
@@ -50644,7 +50644,7 @@
     </row>
     <row r="960" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A960" s="2" t="s">
-        <v>1517</v>
+        <v>1516</v>
       </c>
       <c r="B960" s="2" t="s">
         <v>565</v>
@@ -50653,10 +50653,10 @@
         <v>9</v>
       </c>
       <c r="D960" s="4" t="s">
+        <v>1513</v>
+      </c>
+      <c r="E960" s="5" t="s">
         <v>1514</v>
-      </c>
-      <c r="E960" s="5" t="s">
-        <v>1515</v>
       </c>
       <c r="F960" s="4" t="s">
         <v>1395</v>
@@ -50688,7 +50688,7 @@
     </row>
     <row r="961" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A961" s="2" t="s">
-        <v>1518</v>
+        <v>1517</v>
       </c>
       <c r="B961" s="2" t="s">
         <v>565</v>
@@ -50697,16 +50697,16 @@
         <v>9</v>
       </c>
       <c r="D961" s="4" t="s">
+        <v>1518</v>
+      </c>
+      <c r="E961" s="5" t="s">
         <v>1519</v>
-      </c>
-      <c r="E961" s="5" t="s">
-        <v>1520</v>
       </c>
       <c r="F961" s="4" t="s">
         <v>1395</v>
       </c>
       <c r="G961" s="4" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="H961" s="4" t="s">
         <v>32</v>
@@ -50732,7 +50732,7 @@
     </row>
     <row r="962" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A962" s="2" t="s">
-        <v>1521</v>
+        <v>1520</v>
       </c>
       <c r="B962" s="2" t="s">
         <v>565</v>
@@ -50741,10 +50741,10 @@
         <v>9</v>
       </c>
       <c r="D962" s="4" t="s">
+        <v>1518</v>
+      </c>
+      <c r="E962" s="5" t="s">
         <v>1519</v>
-      </c>
-      <c r="E962" s="5" t="s">
-        <v>1520</v>
       </c>
       <c r="F962" s="4" t="s">
         <v>1395</v>
@@ -50776,7 +50776,7 @@
     </row>
     <row r="963" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A963" s="2" t="s">
-        <v>1522</v>
+        <v>1521</v>
       </c>
       <c r="B963" s="2" t="s">
         <v>565</v>
@@ -50785,16 +50785,16 @@
         <v>9</v>
       </c>
       <c r="D963" s="4" t="s">
+        <v>1522</v>
+      </c>
+      <c r="E963" s="5" t="s">
         <v>1523</v>
-      </c>
-      <c r="E963" s="5" t="s">
-        <v>1524</v>
       </c>
       <c r="F963" s="4" t="s">
         <v>1395</v>
       </c>
       <c r="G963" s="4" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="H963" s="4" t="s">
         <v>32</v>
@@ -50820,7 +50820,7 @@
     </row>
     <row r="964" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A964" s="2" t="s">
-        <v>1525</v>
+        <v>1524</v>
       </c>
       <c r="B964" s="2" t="s">
         <v>565</v>
@@ -50829,10 +50829,10 @@
         <v>9</v>
       </c>
       <c r="D964" s="4" t="s">
+        <v>1522</v>
+      </c>
+      <c r="E964" s="5" t="s">
         <v>1523</v>
-      </c>
-      <c r="E964" s="5" t="s">
-        <v>1524</v>
       </c>
       <c r="F964" s="4" t="s">
         <v>1395</v>
@@ -50864,7 +50864,7 @@
     </row>
     <row r="965" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A965" s="2" t="s">
-        <v>1526</v>
+        <v>1525</v>
       </c>
       <c r="B965" s="2" t="s">
         <v>565</v>
@@ -50873,16 +50873,16 @@
         <v>9</v>
       </c>
       <c r="D965" s="4" t="s">
+        <v>1526</v>
+      </c>
+      <c r="E965" s="5" t="s">
         <v>1527</v>
-      </c>
-      <c r="E965" s="5" t="s">
-        <v>1528</v>
       </c>
       <c r="F965" s="4" t="s">
         <v>1395</v>
       </c>
       <c r="G965" s="4" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="H965" s="4" t="s">
         <v>32</v>
@@ -50908,7 +50908,7 @@
     </row>
     <row r="966" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A966" s="2" t="s">
-        <v>1529</v>
+        <v>1528</v>
       </c>
       <c r="B966" s="2" t="s">
         <v>565</v>
@@ -50917,10 +50917,10 @@
         <v>9</v>
       </c>
       <c r="D966" s="4" t="s">
+        <v>1526</v>
+      </c>
+      <c r="E966" s="5" t="s">
         <v>1527</v>
-      </c>
-      <c r="E966" s="5" t="s">
-        <v>1528</v>
       </c>
       <c r="F966" s="4" t="s">
         <v>1395</v>
@@ -50952,7 +50952,7 @@
     </row>
     <row r="967" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A967" s="2" t="s">
-        <v>1530</v>
+        <v>1529</v>
       </c>
       <c r="B967" s="2" t="s">
         <v>565</v>
@@ -50961,16 +50961,16 @@
         <v>9</v>
       </c>
       <c r="D967" s="4" t="s">
+        <v>1530</v>
+      </c>
+      <c r="E967" s="5" t="s">
         <v>1531</v>
-      </c>
-      <c r="E967" s="5" t="s">
-        <v>1532</v>
       </c>
       <c r="F967" s="4" t="s">
         <v>1395</v>
       </c>
       <c r="G967" s="4" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="H967" s="4" t="s">
         <v>32</v>
@@ -50996,7 +50996,7 @@
     </row>
     <row r="968" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A968" s="2" t="s">
-        <v>1533</v>
+        <v>1532</v>
       </c>
       <c r="B968" s="2" t="s">
         <v>565</v>
@@ -51005,10 +51005,10 @@
         <v>9</v>
       </c>
       <c r="D968" s="4" t="s">
+        <v>1533</v>
+      </c>
+      <c r="E968" s="5" t="s">
         <v>1534</v>
-      </c>
-      <c r="E968" s="5" t="s">
-        <v>1535</v>
       </c>
       <c r="F968" s="4" t="s">
         <v>1395</v>
@@ -51040,7 +51040,7 @@
     </row>
     <row r="969" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A969" s="2" t="s">
-        <v>1536</v>
+        <v>1535</v>
       </c>
       <c r="B969" s="2" t="s">
         <v>565</v>
@@ -51049,16 +51049,16 @@
         <v>9</v>
       </c>
       <c r="D969" s="4" t="s">
+        <v>1536</v>
+      </c>
+      <c r="E969" s="5" t="s">
         <v>1537</v>
-      </c>
-      <c r="E969" s="5" t="s">
-        <v>1538</v>
       </c>
       <c r="F969" s="4" t="s">
         <v>1395</v>
       </c>
       <c r="G969" s="4" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="H969" s="4" t="s">
         <v>10</v>
@@ -51084,7 +51084,7 @@
     </row>
     <row r="970" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A970" s="2" t="s">
-        <v>1539</v>
+        <v>1538</v>
       </c>
       <c r="B970" s="2" t="s">
         <v>565</v>
@@ -51093,10 +51093,10 @@
         <v>9</v>
       </c>
       <c r="D970" s="4" t="s">
+        <v>1536</v>
+      </c>
+      <c r="E970" s="5" t="s">
         <v>1537</v>
-      </c>
-      <c r="E970" s="5" t="s">
-        <v>1538</v>
       </c>
       <c r="F970" s="4" t="s">
         <v>1395</v>
@@ -51128,7 +51128,7 @@
     </row>
     <row r="971" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A971" s="2" t="s">
-        <v>1540</v>
+        <v>1539</v>
       </c>
       <c r="B971" s="2" t="s">
         <v>565</v>
@@ -51137,16 +51137,16 @@
         <v>9</v>
       </c>
       <c r="D971" s="4" t="s">
+        <v>1540</v>
+      </c>
+      <c r="E971" s="5" t="s">
         <v>1541</v>
-      </c>
-      <c r="E971" s="5" t="s">
-        <v>1542</v>
       </c>
       <c r="F971" s="4" t="s">
         <v>1395</v>
       </c>
       <c r="G971" s="4" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="H971" s="4" t="s">
         <v>10</v>
@@ -51172,7 +51172,7 @@
     </row>
     <row r="972" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A972" s="2" t="s">
-        <v>1543</v>
+        <v>1542</v>
       </c>
       <c r="B972" s="2" t="s">
         <v>565</v>
@@ -51181,16 +51181,16 @@
         <v>9</v>
       </c>
       <c r="D972" s="4" t="s">
+        <v>1540</v>
+      </c>
+      <c r="E972" s="5" t="s">
         <v>1541</v>
-      </c>
-      <c r="E972" s="5" t="s">
-        <v>1542</v>
       </c>
       <c r="F972" s="4" t="s">
         <v>1395</v>
       </c>
       <c r="G972" s="4" t="s">
-        <v>1544</v>
+        <v>1543</v>
       </c>
       <c r="H972" s="4" t="s">
         <v>10</v>
@@ -51216,7 +51216,7 @@
     </row>
     <row r="973" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A973" s="2" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
       <c r="B973" s="2" t="s">
         <v>565</v>
@@ -51225,16 +51225,16 @@
         <v>9</v>
       </c>
       <c r="D973" s="4" t="s">
+        <v>1545</v>
+      </c>
+      <c r="E973" s="5" t="s">
         <v>1546</v>
-      </c>
-      <c r="E973" s="5" t="s">
-        <v>1547</v>
       </c>
       <c r="F973" s="4" t="s">
         <v>1395</v>
       </c>
       <c r="G973" s="4" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="H973" s="4" t="s">
         <v>10</v>
@@ -51260,7 +51260,7 @@
     </row>
     <row r="974" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A974" s="2" t="s">
-        <v>1548</v>
+        <v>1547</v>
       </c>
       <c r="B974" s="2" t="s">
         <v>565</v>
@@ -51269,10 +51269,10 @@
         <v>9</v>
       </c>
       <c r="D974" s="4" t="s">
+        <v>1545</v>
+      </c>
+      <c r="E974" s="5" t="s">
         <v>1546</v>
-      </c>
-      <c r="E974" s="5" t="s">
-        <v>1547</v>
       </c>
       <c r="F974" s="4" t="s">
         <v>1395</v>
@@ -51304,7 +51304,7 @@
     </row>
     <row r="975" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A975" s="2" t="s">
-        <v>1549</v>
+        <v>1548</v>
       </c>
       <c r="B975" s="2" t="s">
         <v>565</v>
@@ -51313,16 +51313,16 @@
         <v>9</v>
       </c>
       <c r="D975" s="4" t="s">
+        <v>1549</v>
+      </c>
+      <c r="E975" s="5" t="s">
         <v>1550</v>
-      </c>
-      <c r="E975" s="5" t="s">
-        <v>1551</v>
       </c>
       <c r="F975" s="4" t="s">
         <v>1395</v>
       </c>
       <c r="G975" s="4" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="H975" s="4" t="s">
         <v>10</v>
@@ -51348,7 +51348,7 @@
     </row>
     <row r="976" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A976" s="2" t="s">
-        <v>1552</v>
+        <v>1551</v>
       </c>
       <c r="B976" s="2" t="s">
         <v>565</v>
@@ -51357,10 +51357,10 @@
         <v>9</v>
       </c>
       <c r="D976" s="4" t="s">
+        <v>1549</v>
+      </c>
+      <c r="E976" s="5" t="s">
         <v>1550</v>
-      </c>
-      <c r="E976" s="5" t="s">
-        <v>1551</v>
       </c>
       <c r="F976" s="4" t="s">
         <v>1395</v>
@@ -51392,7 +51392,7 @@
     </row>
     <row r="977" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A977" s="2" t="s">
-        <v>1553</v>
+        <v>1552</v>
       </c>
       <c r="B977" s="2" t="s">
         <v>565</v>
@@ -51401,10 +51401,10 @@
         <v>9</v>
       </c>
       <c r="D977" s="4" t="s">
+        <v>1549</v>
+      </c>
+      <c r="E977" s="5" t="s">
         <v>1550</v>
-      </c>
-      <c r="E977" s="5" t="s">
-        <v>1551</v>
       </c>
       <c r="F977" s="4" t="s">
         <v>1395</v>
@@ -51436,7 +51436,7 @@
     </row>
     <row r="978" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A978" s="2" t="s">
-        <v>1554</v>
+        <v>1553</v>
       </c>
       <c r="B978" s="2" t="s">
         <v>565</v>
@@ -51445,16 +51445,16 @@
         <v>9</v>
       </c>
       <c r="D978" s="4" t="s">
+        <v>1554</v>
+      </c>
+      <c r="E978" s="5" t="s">
         <v>1555</v>
-      </c>
-      <c r="E978" s="5" t="s">
-        <v>1556</v>
       </c>
       <c r="F978" s="4" t="s">
         <v>1395</v>
       </c>
       <c r="G978" s="4" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="H978" s="4" t="s">
         <v>10</v>
@@ -51480,7 +51480,7 @@
     </row>
     <row r="979" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A979" s="2" t="s">
-        <v>1557</v>
+        <v>1556</v>
       </c>
       <c r="B979" s="2" t="s">
         <v>565</v>
@@ -51489,10 +51489,10 @@
         <v>9</v>
       </c>
       <c r="D979" s="4" t="s">
+        <v>1554</v>
+      </c>
+      <c r="E979" s="5" t="s">
         <v>1555</v>
-      </c>
-      <c r="E979" s="5" t="s">
-        <v>1556</v>
       </c>
       <c r="F979" s="4" t="s">
         <v>1395</v>
@@ -51524,7 +51524,7 @@
     </row>
     <row r="980" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A980" s="2" t="s">
-        <v>1558</v>
+        <v>1557</v>
       </c>
       <c r="B980" s="2" t="s">
         <v>565</v>
@@ -51533,16 +51533,16 @@
         <v>9</v>
       </c>
       <c r="D980" s="4" t="s">
+        <v>1558</v>
+      </c>
+      <c r="E980" s="5" t="s">
         <v>1559</v>
-      </c>
-      <c r="E980" s="5" t="s">
-        <v>1560</v>
       </c>
       <c r="F980" s="4" t="s">
         <v>1395</v>
       </c>
       <c r="G980" s="4" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="H980" s="4" t="s">
         <v>32</v>
@@ -51568,7 +51568,7 @@
     </row>
     <row r="981" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A981" s="2" t="s">
-        <v>1561</v>
+        <v>1560</v>
       </c>
       <c r="B981" s="2" t="s">
         <v>565</v>
@@ -51577,16 +51577,16 @@
         <v>9</v>
       </c>
       <c r="D981" s="4" t="s">
+        <v>1558</v>
+      </c>
+      <c r="E981" s="5" t="s">
         <v>1559</v>
-      </c>
-      <c r="E981" s="5" t="s">
-        <v>1560</v>
       </c>
       <c r="F981" s="4" t="s">
         <v>1395</v>
       </c>
       <c r="G981" s="4" t="s">
-        <v>1544</v>
+        <v>1543</v>
       </c>
       <c r="H981" s="4" t="s">
         <v>32</v>
@@ -51612,7 +51612,7 @@
     </row>
     <row r="982" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A982" s="2" t="s">
-        <v>1562</v>
+        <v>1561</v>
       </c>
       <c r="B982" s="2" t="s">
         <v>565</v>
@@ -51621,16 +51621,16 @@
         <v>9</v>
       </c>
       <c r="D982" s="4" t="s">
+        <v>1562</v>
+      </c>
+      <c r="E982" s="5" t="s">
         <v>1563</v>
-      </c>
-      <c r="E982" s="5" t="s">
-        <v>1564</v>
       </c>
       <c r="F982" s="4" t="s">
         <v>1395</v>
       </c>
       <c r="G982" s="4" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="H982" s="4" t="s">
         <v>32</v>
@@ -51656,7 +51656,7 @@
     </row>
     <row r="983" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A983" s="2" t="s">
-        <v>1565</v>
+        <v>1564</v>
       </c>
       <c r="B983" s="2" t="s">
         <v>565</v>
@@ -51665,10 +51665,10 @@
         <v>9</v>
       </c>
       <c r="D983" s="4" t="s">
+        <v>1562</v>
+      </c>
+      <c r="E983" s="5" t="s">
         <v>1563</v>
-      </c>
-      <c r="E983" s="5" t="s">
-        <v>1564</v>
       </c>
       <c r="F983" s="4" t="s">
         <v>1395</v>
@@ -51700,7 +51700,7 @@
     </row>
     <row r="984" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A984" s="2" t="s">
-        <v>1566</v>
+        <v>1565</v>
       </c>
       <c r="B984" s="2" t="s">
         <v>600</v>
@@ -51709,16 +51709,16 @@
         <v>9</v>
       </c>
       <c r="D984" s="4" t="s">
+        <v>1566</v>
+      </c>
+      <c r="E984" s="5" t="s">
         <v>1567</v>
-      </c>
-      <c r="E984" s="5" t="s">
-        <v>1568</v>
       </c>
       <c r="F984" s="4" t="s">
         <v>1392</v>
       </c>
       <c r="G984" s="4" t="s">
-        <v>1473</v>
+        <v>1472</v>
       </c>
       <c r="H984" s="4" t="s">
         <v>13</v>
@@ -51744,25 +51744,25 @@
     </row>
     <row r="985" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A985" s="2" t="s">
+        <v>1568</v>
+      </c>
+      <c r="B985" s="2" t="s">
         <v>1569</v>
-      </c>
-      <c r="B985" s="2" t="s">
-        <v>1570</v>
       </c>
       <c r="C985" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D985" s="4" t="s">
+        <v>1566</v>
+      </c>
+      <c r="E985" s="5" t="s">
         <v>1567</v>
-      </c>
-      <c r="E985" s="5" t="s">
-        <v>1568</v>
       </c>
       <c r="F985" s="4" t="s">
         <v>1392</v>
       </c>
       <c r="G985" s="4" t="s">
-        <v>1571</v>
+        <v>1570</v>
       </c>
       <c r="H985" s="4" t="s">
         <v>13</v>
@@ -51788,7 +51788,7 @@
     </row>
     <row r="986" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A986" s="2" t="s">
-        <v>1572</v>
+        <v>1571</v>
       </c>
       <c r="B986" s="2" t="s">
         <v>565</v>
@@ -51797,10 +51797,10 @@
         <v>9</v>
       </c>
       <c r="D986" s="4" t="s">
+        <v>1572</v>
+      </c>
+      <c r="E986" s="5" t="s">
         <v>1573</v>
-      </c>
-      <c r="E986" s="5" t="s">
-        <v>1574</v>
       </c>
       <c r="F986" s="4" t="s">
         <v>1392</v>
@@ -51832,7 +51832,7 @@
     </row>
     <row r="987" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A987" s="2" t="s">
-        <v>1575</v>
+        <v>1574</v>
       </c>
       <c r="B987" s="2" t="s">
         <v>565</v>
@@ -51841,10 +51841,10 @@
         <v>9</v>
       </c>
       <c r="D987" s="4" t="s">
+        <v>1572</v>
+      </c>
+      <c r="E987" s="5" t="s">
         <v>1573</v>
-      </c>
-      <c r="E987" s="5" t="s">
-        <v>1574</v>
       </c>
       <c r="F987" s="4" t="s">
         <v>1392</v>
@@ -51876,7 +51876,7 @@
     </row>
     <row r="988" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A988" s="2" t="s">
-        <v>1576</v>
+        <v>1575</v>
       </c>
       <c r="B988" s="2" t="s">
         <v>666</v>
@@ -51885,16 +51885,16 @@
         <v>9</v>
       </c>
       <c r="D988" s="4" t="s">
+        <v>1576</v>
+      </c>
+      <c r="E988" s="5" t="s">
         <v>1577</v>
-      </c>
-      <c r="E988" s="5" t="s">
-        <v>1578</v>
       </c>
       <c r="F988" s="4" t="s">
         <v>68</v>
       </c>
       <c r="G988" s="4" t="s">
-        <v>1579</v>
+        <v>1578</v>
       </c>
       <c r="H988" s="4" t="s">
         <v>13</v>
@@ -51920,7 +51920,7 @@
     </row>
     <row r="989" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A989" s="2" t="s">
-        <v>1580</v>
+        <v>1579</v>
       </c>
       <c r="B989" s="2" t="s">
         <v>666</v>
@@ -51929,16 +51929,16 @@
         <v>9</v>
       </c>
       <c r="D989" s="4" t="s">
+        <v>1576</v>
+      </c>
+      <c r="E989" s="5" t="s">
         <v>1577</v>
-      </c>
-      <c r="E989" s="5" t="s">
-        <v>1578</v>
       </c>
       <c r="F989" s="4" t="s">
         <v>68</v>
       </c>
       <c r="G989" s="4" t="s">
-        <v>1581</v>
+        <v>1580</v>
       </c>
       <c r="H989" s="4" t="s">
         <v>13</v>
@@ -51964,7 +51964,7 @@
     </row>
     <row r="990" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A990" s="2" t="s">
-        <v>1582</v>
+        <v>1581</v>
       </c>
       <c r="B990" s="2" t="s">
         <v>666</v>
@@ -51973,16 +51973,16 @@
         <v>9</v>
       </c>
       <c r="D990" s="4" t="s">
+        <v>1576</v>
+      </c>
+      <c r="E990" s="5" t="s">
         <v>1577</v>
-      </c>
-      <c r="E990" s="5" t="s">
-        <v>1578</v>
       </c>
       <c r="F990" s="4" t="s">
         <v>68</v>
       </c>
       <c r="G990" s="4" t="s">
-        <v>1487</v>
+        <v>1486</v>
       </c>
       <c r="H990" s="4" t="s">
         <v>13</v>
@@ -52008,7 +52008,7 @@
     </row>
     <row r="991" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A991" s="2" t="s">
-        <v>1583</v>
+        <v>1582</v>
       </c>
       <c r="B991" s="2" t="s">
         <v>666</v>
@@ -52017,16 +52017,16 @@
         <v>9</v>
       </c>
       <c r="D991" s="4" t="s">
+        <v>1583</v>
+      </c>
+      <c r="E991" s="5" t="s">
         <v>1584</v>
-      </c>
-      <c r="E991" s="5" t="s">
-        <v>1585</v>
       </c>
       <c r="F991" s="4" t="s">
         <v>1393</v>
       </c>
       <c r="G991" s="4" t="s">
-        <v>1586</v>
+        <v>1585</v>
       </c>
       <c r="H991" s="4" t="s">
         <v>10</v>
@@ -52052,7 +52052,7 @@
     </row>
     <row r="992" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A992" s="2" t="s">
-        <v>1587</v>
+        <v>1586</v>
       </c>
       <c r="B992" s="2" t="s">
         <v>666</v>
@@ -52061,16 +52061,16 @@
         <v>9</v>
       </c>
       <c r="D992" s="4" t="s">
+        <v>1583</v>
+      </c>
+      <c r="E992" s="5" t="s">
         <v>1584</v>
-      </c>
-      <c r="E992" s="5" t="s">
-        <v>1585</v>
       </c>
       <c r="F992" s="4" t="s">
         <v>1393</v>
       </c>
       <c r="G992" s="4" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="H992" s="4" t="s">
         <v>10</v>
@@ -52096,7 +52096,7 @@
     </row>
     <row r="993" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A993" s="2" t="s">
-        <v>1589</v>
+        <v>1588</v>
       </c>
       <c r="B993" s="2" t="s">
         <v>666</v>
@@ -52105,16 +52105,16 @@
         <v>9</v>
       </c>
       <c r="D993" s="4" t="s">
+        <v>1583</v>
+      </c>
+      <c r="E993" s="5" t="s">
         <v>1584</v>
-      </c>
-      <c r="E993" s="5" t="s">
-        <v>1585</v>
       </c>
       <c r="F993" s="4" t="s">
         <v>1393</v>
       </c>
       <c r="G993" s="4" t="s">
-        <v>1590</v>
+        <v>1589</v>
       </c>
       <c r="H993" s="4" t="s">
         <v>10</v>
@@ -52140,7 +52140,7 @@
     </row>
     <row r="994" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A994" s="2" t="s">
-        <v>1591</v>
+        <v>1590</v>
       </c>
       <c r="B994" s="2" t="s">
         <v>666</v>
@@ -52149,16 +52149,16 @@
         <v>9</v>
       </c>
       <c r="D994" s="4" t="s">
+        <v>1583</v>
+      </c>
+      <c r="E994" s="5" t="s">
         <v>1584</v>
-      </c>
-      <c r="E994" s="5" t="s">
-        <v>1585</v>
       </c>
       <c r="F994" s="4" t="s">
         <v>1393</v>
       </c>
       <c r="G994" s="4" t="s">
-        <v>1592</v>
+        <v>1591</v>
       </c>
       <c r="H994" s="4" t="s">
         <v>10</v>
@@ -52184,7 +52184,7 @@
     </row>
     <row r="995" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A995" s="2" t="s">
-        <v>1593</v>
+        <v>1592</v>
       </c>
       <c r="B995" s="2" t="s">
         <v>666</v>
@@ -52193,16 +52193,16 @@
         <v>9</v>
       </c>
       <c r="D995" s="4" t="s">
+        <v>1593</v>
+      </c>
+      <c r="E995" s="5" t="s">
         <v>1594</v>
-      </c>
-      <c r="E995" s="5" t="s">
-        <v>1595</v>
       </c>
       <c r="F995" s="4" t="s">
         <v>1394</v>
       </c>
       <c r="G995" s="4" t="s">
-        <v>1586</v>
+        <v>1585</v>
       </c>
       <c r="H995" s="4" t="s">
         <v>32</v>
@@ -52228,7 +52228,7 @@
     </row>
     <row r="996" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A996" s="2" t="s">
-        <v>1596</v>
+        <v>1595</v>
       </c>
       <c r="B996" s="2" t="s">
         <v>666</v>
@@ -52237,16 +52237,16 @@
         <v>9</v>
       </c>
       <c r="D996" s="4" t="s">
+        <v>1593</v>
+      </c>
+      <c r="E996" s="5" t="s">
         <v>1594</v>
-      </c>
-      <c r="E996" s="5" t="s">
-        <v>1595</v>
       </c>
       <c r="F996" s="4" t="s">
         <v>1394</v>
       </c>
       <c r="G996" s="4" t="s">
-        <v>1588</v>
+        <v>1587</v>
       </c>
       <c r="H996" s="4" t="s">
         <v>32</v>
@@ -52272,7 +52272,7 @@
     </row>
     <row r="997" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A997" s="2" t="s">
-        <v>1597</v>
+        <v>1596</v>
       </c>
       <c r="B997" s="2" t="s">
         <v>666</v>
@@ -52281,16 +52281,16 @@
         <v>9</v>
       </c>
       <c r="D997" s="4" t="s">
+        <v>1593</v>
+      </c>
+      <c r="E997" s="5" t="s">
         <v>1594</v>
-      </c>
-      <c r="E997" s="5" t="s">
-        <v>1595</v>
       </c>
       <c r="F997" s="4" t="s">
         <v>1394</v>
       </c>
       <c r="G997" s="4" t="s">
-        <v>1590</v>
+        <v>1589</v>
       </c>
       <c r="H997" s="4" t="s">
         <v>32</v>
@@ -52316,7 +52316,7 @@
     </row>
     <row r="998" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A998" s="2" t="s">
-        <v>1598</v>
+        <v>1597</v>
       </c>
       <c r="B998" s="2" t="s">
         <v>666</v>
@@ -52325,16 +52325,16 @@
         <v>9</v>
       </c>
       <c r="D998" s="4" t="s">
+        <v>1593</v>
+      </c>
+      <c r="E998" s="5" t="s">
         <v>1594</v>
-      </c>
-      <c r="E998" s="5" t="s">
-        <v>1595</v>
       </c>
       <c r="F998" s="4" t="s">
         <v>1394</v>
       </c>
       <c r="G998" s="4" t="s">
-        <v>1592</v>
+        <v>1591</v>
       </c>
       <c r="H998" s="4" t="s">
         <v>32</v>
@@ -52360,7 +52360,7 @@
     </row>
     <row r="999" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A999" s="2" t="s">
-        <v>1599</v>
+        <v>1598</v>
       </c>
       <c r="B999" s="2" t="s">
         <v>565</v>
@@ -52369,13 +52369,13 @@
         <v>51</v>
       </c>
       <c r="D999" s="4" t="s">
+        <v>1599</v>
+      </c>
+      <c r="E999" s="5" t="s">
         <v>1600</v>
       </c>
-      <c r="E999" s="5" t="s">
-        <v>1601</v>
-      </c>
       <c r="F999" s="4" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
       <c r="G999" s="4" t="s">
         <v>29</v>
@@ -52404,7 +52404,7 @@
     </row>
     <row r="1000" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1000" s="2" t="s">
-        <v>1602</v>
+        <v>1601</v>
       </c>
       <c r="B1000" s="2" t="s">
         <v>565</v>
@@ -52413,13 +52413,13 @@
         <v>51</v>
       </c>
       <c r="D1000" s="4" t="s">
+        <v>1599</v>
+      </c>
+      <c r="E1000" s="5" t="s">
         <v>1600</v>
       </c>
-      <c r="E1000" s="5" t="s">
-        <v>1601</v>
-      </c>
       <c r="F1000" s="4" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
       <c r="G1000" s="4" t="s">
         <v>1410</v>
@@ -52448,7 +52448,7 @@
     </row>
     <row r="1001" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1001" s="2" t="s">
-        <v>1603</v>
+        <v>1602</v>
       </c>
       <c r="B1001" s="2" t="s">
         <v>565</v>
@@ -52457,13 +52457,13 @@
         <v>51</v>
       </c>
       <c r="D1001" s="4" t="s">
+        <v>1603</v>
+      </c>
+      <c r="E1001" s="5" t="s">
         <v>1604</v>
       </c>
-      <c r="E1001" s="5" t="s">
-        <v>1605</v>
-      </c>
       <c r="F1001" s="4" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
       <c r="G1001" s="4" t="s">
         <v>29</v>
@@ -52492,7 +52492,7 @@
     </row>
     <row r="1002" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1002" s="2" t="s">
-        <v>1606</v>
+        <v>1605</v>
       </c>
       <c r="B1002" s="2" t="s">
         <v>565</v>
@@ -52501,13 +52501,13 @@
         <v>51</v>
       </c>
       <c r="D1002" s="4" t="s">
+        <v>1603</v>
+      </c>
+      <c r="E1002" s="5" t="s">
         <v>1604</v>
       </c>
-      <c r="E1002" s="5" t="s">
-        <v>1605</v>
-      </c>
       <c r="F1002" s="4" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
       <c r="G1002" s="4" t="s">
         <v>1410</v>
@@ -52536,7 +52536,7 @@
     </row>
     <row r="1003" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1003" s="2" t="s">
-        <v>1607</v>
+        <v>1606</v>
       </c>
       <c r="B1003" s="2" t="s">
         <v>565</v>
@@ -52545,10 +52545,10 @@
         <v>51</v>
       </c>
       <c r="D1003" s="4" t="s">
+        <v>1607</v>
+      </c>
+      <c r="E1003" s="5" t="s">
         <v>1608</v>
-      </c>
-      <c r="E1003" s="5" t="s">
-        <v>1609</v>
       </c>
       <c r="F1003" s="4" t="s">
         <v>1390</v>
@@ -52580,7 +52580,7 @@
     </row>
     <row r="1004" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1004" s="2" t="s">
-        <v>1610</v>
+        <v>1609</v>
       </c>
       <c r="B1004" s="2" t="s">
         <v>565</v>
@@ -52589,16 +52589,16 @@
         <v>51</v>
       </c>
       <c r="D1004" s="4" t="s">
+        <v>1607</v>
+      </c>
+      <c r="E1004" s="5" t="s">
         <v>1608</v>
-      </c>
-      <c r="E1004" s="5" t="s">
-        <v>1609</v>
       </c>
       <c r="F1004" s="4" t="s">
         <v>1390</v>
       </c>
       <c r="G1004" s="4" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="H1004" s="4" t="s">
         <v>32</v>
@@ -52624,7 +52624,7 @@
     </row>
     <row r="1005" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1005" s="2" t="s">
-        <v>1611</v>
+        <v>1610</v>
       </c>
       <c r="B1005" s="2" t="s">
         <v>565</v>
@@ -52633,10 +52633,10 @@
         <v>51</v>
       </c>
       <c r="D1005" s="4" t="s">
+        <v>1607</v>
+      </c>
+      <c r="E1005" s="5" t="s">
         <v>1608</v>
-      </c>
-      <c r="E1005" s="5" t="s">
-        <v>1609</v>
       </c>
       <c r="F1005" s="4" t="s">
         <v>1390</v>
@@ -52668,7 +52668,7 @@
     </row>
     <row r="1006" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1006" s="2" t="s">
-        <v>1612</v>
+        <v>1611</v>
       </c>
       <c r="B1006" s="2" t="s">
         <v>565</v>
@@ -52677,10 +52677,10 @@
         <v>514</v>
       </c>
       <c r="D1006" s="4" t="s">
+        <v>1612</v>
+      </c>
+      <c r="E1006" s="5" t="s">
         <v>1613</v>
-      </c>
-      <c r="E1006" s="5" t="s">
-        <v>1614</v>
       </c>
       <c r="F1006" s="4" t="s">
         <v>1390</v>
@@ -52712,7 +52712,7 @@
     </row>
     <row r="1007" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1007" s="2" t="s">
-        <v>1615</v>
+        <v>1614</v>
       </c>
       <c r="B1007" s="2" t="s">
         <v>565</v>
@@ -52721,10 +52721,10 @@
         <v>514</v>
       </c>
       <c r="D1007" s="4" t="s">
+        <v>1612</v>
+      </c>
+      <c r="E1007" s="5" t="s">
         <v>1613</v>
-      </c>
-      <c r="E1007" s="5" t="s">
-        <v>1614</v>
       </c>
       <c r="F1007" s="4" t="s">
         <v>1390</v>
@@ -52756,7 +52756,7 @@
     </row>
     <row r="1008" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1008" s="2" t="s">
-        <v>1616</v>
+        <v>1615</v>
       </c>
       <c r="B1008" s="2" t="s">
         <v>565</v>
@@ -52765,10 +52765,10 @@
         <v>514</v>
       </c>
       <c r="D1008" s="4" t="s">
+        <v>1616</v>
+      </c>
+      <c r="E1008" s="5" t="s">
         <v>1617</v>
-      </c>
-      <c r="E1008" s="5" t="s">
-        <v>1618</v>
       </c>
       <c r="F1008" s="4" t="s">
         <v>1390</v>
@@ -52800,7 +52800,7 @@
     </row>
     <row r="1009" spans="1:18" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1009" s="2" t="s">
-        <v>1619</v>
+        <v>1618</v>
       </c>
       <c r="B1009" s="2" t="s">
         <v>565</v>
@@ -52809,10 +52809,10 @@
         <v>514</v>
       </c>
       <c r="D1009" s="4" t="s">
+        <v>1616</v>
+      </c>
+      <c r="E1009" s="5" t="s">
         <v>1617</v>
-      </c>
-      <c r="E1009" s="5" t="s">
-        <v>1618</v>
       </c>
       <c r="F1009" s="4" t="s">
         <v>1390</v>
@@ -52843,7 +52843,7 @@
       <c r="R1009" s="4"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R899" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:R1009" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Produtos.xlsx
+++ b/Produtos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NOT-MARCOS\Documents\GitHub\Catalogo-Olympikus_2.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63A20402-B549-45F8-8B7E-0D2EA092D60A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3650CB52-9F97-4C2B-8A69-21B6AA6DCE49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,7 +19,20 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Produtos!$A$1:$R$921</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -5114,6 +5127,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:AI921"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -5235,7 +5249,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>35</v>
       </c>
@@ -5342,7 +5356,7 @@
         <v>265.43</v>
       </c>
     </row>
-    <row r="3" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>45</v>
       </c>
@@ -5449,7 +5463,7 @@
         <v>265.43</v>
       </c>
     </row>
-    <row r="4" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>49</v>
       </c>
@@ -5556,7 +5570,7 @@
         <v>265.43</v>
       </c>
     </row>
-    <row r="5" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>51</v>
       </c>
@@ -5663,7 +5677,7 @@
         <v>265.43</v>
       </c>
     </row>
-    <row r="6" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>53</v>
       </c>
@@ -5770,7 +5784,7 @@
         <v>265.43</v>
       </c>
     </row>
-    <row r="7" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>55</v>
       </c>
@@ -5877,7 +5891,7 @@
         <v>238.88</v>
       </c>
     </row>
-    <row r="8" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>58</v>
       </c>
@@ -5984,7 +5998,7 @@
         <v>238.88</v>
       </c>
     </row>
-    <row r="9" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>60</v>
       </c>
@@ -6091,7 +6105,7 @@
         <v>238.88</v>
       </c>
     </row>
-    <row r="10" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>62</v>
       </c>
@@ -6198,7 +6212,7 @@
         <v>238.88</v>
       </c>
     </row>
-    <row r="11" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>64</v>
       </c>
@@ -6305,7 +6319,7 @@
         <v>238.88</v>
       </c>
     </row>
-    <row r="12" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>66</v>
       </c>
@@ -6412,7 +6426,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="13" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>69</v>
       </c>
@@ -6519,7 +6533,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="14" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>71</v>
       </c>
@@ -6626,7 +6640,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="15" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>73</v>
       </c>
@@ -6733,7 +6747,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="16" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>75</v>
       </c>
@@ -6840,7 +6854,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="17" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>77</v>
       </c>
@@ -6947,7 +6961,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="18" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>79</v>
       </c>
@@ -7054,7 +7068,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="19" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>81</v>
       </c>
@@ -7161,7 +7175,7 @@
         <v>201.72</v>
       </c>
     </row>
-    <row r="20" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>84</v>
       </c>
@@ -7268,7 +7282,7 @@
         <v>201.72</v>
       </c>
     </row>
-    <row r="21" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>85</v>
       </c>
@@ -7375,7 +7389,7 @@
         <v>201.72</v>
       </c>
     </row>
-    <row r="22" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>87</v>
       </c>
@@ -7482,7 +7496,7 @@
         <v>201.72</v>
       </c>
     </row>
-    <row r="23" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>89</v>
       </c>
@@ -7589,7 +7603,7 @@
         <v>201.72</v>
       </c>
     </row>
-    <row r="24" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>90</v>
       </c>
@@ -7696,7 +7710,7 @@
         <v>201.72</v>
       </c>
     </row>
-    <row r="25" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>91</v>
       </c>
@@ -7803,7 +7817,7 @@
         <v>185.8</v>
       </c>
     </row>
-    <row r="26" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>95</v>
       </c>
@@ -7910,7 +7924,7 @@
         <v>185.8</v>
       </c>
     </row>
-    <row r="27" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>98</v>
       </c>
@@ -8017,7 +8031,7 @@
         <v>185.8</v>
       </c>
     </row>
-    <row r="28" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>100</v>
       </c>
@@ -8124,7 +8138,7 @@
         <v>185.8</v>
       </c>
     </row>
-    <row r="29" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>102</v>
       </c>
@@ -8231,7 +8245,7 @@
         <v>185.8</v>
       </c>
     </row>
-    <row r="30" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>103</v>
       </c>
@@ -8338,7 +8352,7 @@
         <v>185.8</v>
       </c>
     </row>
-    <row r="31" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>105</v>
       </c>
@@ -8445,7 +8459,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="32" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>107</v>
       </c>
@@ -8552,7 +8566,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="33" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>108</v>
       </c>
@@ -8659,7 +8673,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="34" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>110</v>
       </c>
@@ -8766,7 +8780,7 @@
         <v>291.97000000000003</v>
       </c>
     </row>
-    <row r="35" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>115</v>
       </c>
@@ -8873,7 +8887,7 @@
         <v>291.97000000000003</v>
       </c>
     </row>
-    <row r="36" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>116</v>
       </c>
@@ -8980,7 +8994,7 @@
         <v>291.97000000000003</v>
       </c>
     </row>
-    <row r="37" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>118</v>
       </c>
@@ -9087,7 +9101,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="38" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>119</v>
       </c>
@@ -9194,7 +9208,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="39" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>120</v>
       </c>
@@ -9301,7 +9315,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="40" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>122</v>
       </c>
@@ -9408,7 +9422,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="41" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>124</v>
       </c>
@@ -9515,7 +9529,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="42" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>128</v>
       </c>
@@ -9622,7 +9636,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="43" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>130</v>
       </c>
@@ -9729,7 +9743,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="44" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>131</v>
       </c>
@@ -9836,7 +9850,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="45" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>133</v>
       </c>
@@ -9943,7 +9957,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="46" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>134</v>
       </c>
@@ -10050,7 +10064,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="47" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>136</v>
       </c>
@@ -10157,7 +10171,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="48" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>138</v>
       </c>
@@ -10264,7 +10278,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="49" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>140</v>
       </c>
@@ -10371,7 +10385,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="50" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>142</v>
       </c>
@@ -10478,7 +10492,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="51" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>143</v>
       </c>
@@ -10585,7 +10599,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="52" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>147</v>
       </c>
@@ -10692,7 +10706,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="53" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>148</v>
       </c>
@@ -10799,7 +10813,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="54" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>149</v>
       </c>
@@ -10906,7 +10920,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="55" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>151</v>
       </c>
@@ -11013,7 +11027,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="56" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>152</v>
       </c>
@@ -11120,7 +11134,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="57" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>154</v>
       </c>
@@ -11227,7 +11241,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="58" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>156</v>
       </c>
@@ -11334,7 +11348,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="59" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>158</v>
       </c>
@@ -11441,7 +11455,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="60" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>160</v>
       </c>
@@ -11548,7 +11562,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="61" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>162</v>
       </c>
@@ -11655,7 +11669,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="62" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>163</v>
       </c>
@@ -11762,7 +11776,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="63" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>165</v>
       </c>
@@ -11869,7 +11883,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="64" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>168</v>
       </c>
@@ -11976,7 +11990,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="65" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>170</v>
       </c>
@@ -12083,7 +12097,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="66" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
         <v>172</v>
       </c>
@@ -12190,7 +12204,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="67" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>174</v>
       </c>
@@ -12297,7 +12311,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="68" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
         <v>175</v>
       </c>
@@ -12404,7 +12418,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="69" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>177</v>
       </c>
@@ -12511,7 +12525,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="70" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
         <v>180</v>
       </c>
@@ -12618,7 +12632,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="71" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
         <v>181</v>
       </c>
@@ -12725,7 +12739,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="72" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
         <v>182</v>
       </c>
@@ -12832,7 +12846,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="73" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
         <v>183</v>
       </c>
@@ -12939,7 +12953,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="74" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
         <v>186</v>
       </c>
@@ -13046,7 +13060,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="75" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
         <v>188</v>
       </c>
@@ -13153,7 +13167,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="76" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
         <v>190</v>
       </c>
@@ -13260,7 +13274,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="77" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
         <v>192</v>
       </c>
@@ -13367,7 +13381,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="78" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
         <v>193</v>
       </c>
@@ -13474,7 +13488,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="79" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
         <v>196</v>
       </c>
@@ -13581,7 +13595,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="80" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
         <v>198</v>
       </c>
@@ -13688,7 +13702,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="81" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
         <v>199</v>
       </c>
@@ -13795,7 +13809,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="82" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
         <v>202</v>
       </c>
@@ -13902,7 +13916,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="83" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
         <v>203</v>
       </c>
@@ -14009,7 +14023,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="84" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
         <v>204</v>
       </c>
@@ -14116,7 +14130,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="85" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
         <v>207</v>
       </c>
@@ -14223,7 +14237,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="86" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
         <v>208</v>
       </c>
@@ -14330,7 +14344,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="87" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
         <v>210</v>
       </c>
@@ -14437,7 +14451,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="88" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
         <v>212</v>
       </c>
@@ -14544,7 +14558,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="89" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
         <v>215</v>
       </c>
@@ -14651,7 +14665,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="90" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
         <v>217</v>
       </c>
@@ -14758,7 +14772,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="91" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
         <v>218</v>
       </c>
@@ -14865,7 +14879,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="92" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
         <v>219</v>
       </c>
@@ -14972,7 +14986,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="93" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
         <v>222</v>
       </c>
@@ -15079,7 +15093,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="94" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
         <v>223</v>
       </c>
@@ -15186,7 +15200,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="95" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
         <v>225</v>
       </c>
@@ -15293,7 +15307,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="96" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
         <v>227</v>
       </c>
@@ -15400,7 +15414,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="97" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
         <v>231</v>
       </c>
@@ -15507,7 +15521,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="98" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
         <v>233</v>
       </c>
@@ -15614,7 +15628,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="99" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
         <v>235</v>
       </c>
@@ -15721,7 +15735,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="100" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
         <v>236</v>
       </c>
@@ -15828,7 +15842,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="101" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
         <v>239</v>
       </c>
@@ -15935,7 +15949,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="102" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
         <v>241</v>
       </c>
@@ -16042,7 +16056,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="103" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
         <v>242</v>
       </c>
@@ -16149,7 +16163,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="104" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
         <v>243</v>
       </c>
@@ -16256,7 +16270,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="105" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
         <v>245</v>
       </c>
@@ -16363,7 +16377,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="106" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
         <v>247</v>
       </c>
@@ -16470,7 +16484,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="107" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
         <v>250</v>
       </c>
@@ -16577,7 +16591,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="108" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
         <v>251</v>
       </c>
@@ -16684,7 +16698,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="109" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
         <v>252</v>
       </c>
@@ -16791,7 +16805,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="110" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
         <v>254</v>
       </c>
@@ -16898,7 +16912,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="111" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
         <v>255</v>
       </c>
@@ -17005,7 +17019,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="112" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
         <v>257</v>
       </c>
@@ -17112,7 +17126,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="113" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
         <v>259</v>
       </c>
@@ -17219,7 +17233,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="114" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
         <v>261</v>
       </c>
@@ -17326,7 +17340,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="115" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
         <v>262</v>
       </c>
@@ -17433,7 +17447,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="116" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
         <v>264</v>
       </c>
@@ -17540,7 +17554,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="117" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
         <v>266</v>
       </c>
@@ -17647,7 +17661,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="118" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
         <v>268</v>
       </c>
@@ -17754,7 +17768,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="119" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
         <v>270</v>
       </c>
@@ -17861,7 +17875,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="120" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
         <v>272</v>
       </c>
@@ -17968,7 +17982,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="121" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
         <v>273</v>
       </c>
@@ -18075,7 +18089,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="122" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
         <v>275</v>
       </c>
@@ -18182,7 +18196,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="123" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
         <v>277</v>
       </c>
@@ -18289,7 +18303,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="124" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
         <v>279</v>
       </c>
@@ -18396,7 +18410,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="125" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
         <v>280</v>
       </c>
@@ -18503,7 +18517,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="126" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
         <v>283</v>
       </c>
@@ -18610,7 +18624,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="127" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
         <v>284</v>
       </c>
@@ -18717,7 +18731,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="128" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
         <v>285</v>
       </c>
@@ -18824,7 +18838,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="129" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
         <v>286</v>
       </c>
@@ -18931,7 +18945,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="130" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
         <v>288</v>
       </c>
@@ -19038,7 +19052,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="131" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
         <v>290</v>
       </c>
@@ -19145,7 +19159,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="132" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
         <v>292</v>
       </c>
@@ -19252,7 +19266,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="133" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
         <v>293</v>
       </c>
@@ -19359,7 +19373,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="134" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
         <v>295</v>
       </c>
@@ -19466,7 +19480,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="135" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
         <v>296</v>
       </c>
@@ -19573,7 +19587,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="136" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
         <v>297</v>
       </c>
@@ -19680,7 +19694,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="137" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
         <v>298</v>
       </c>
@@ -19787,7 +19801,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="138" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
         <v>301</v>
       </c>
@@ -19894,7 +19908,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="139" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
         <v>302</v>
       </c>
@@ -20001,7 +20015,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="140" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
         <v>303</v>
       </c>
@@ -20108,7 +20122,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="141" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
         <v>304</v>
       </c>
@@ -20215,7 +20229,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="142" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
         <v>307</v>
       </c>
@@ -20322,7 +20336,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="143" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
         <v>309</v>
       </c>
@@ -20429,7 +20443,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="144" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
         <v>310</v>
       </c>
@@ -20536,7 +20550,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="145" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
         <v>312</v>
       </c>
@@ -20643,7 +20657,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="146" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
         <v>314</v>
       </c>
@@ -20750,7 +20764,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="147" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
         <v>315</v>
       </c>
@@ -20857,7 +20871,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="148" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
         <v>316</v>
       </c>
@@ -20964,7 +20978,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="149" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
         <v>318</v>
       </c>
@@ -21071,7 +21085,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="150" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="2" t="s">
         <v>319</v>
       </c>
@@ -21178,7 +21192,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="151" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="s">
         <v>320</v>
       </c>
@@ -21285,7 +21299,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="152" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="2" t="s">
         <v>323</v>
       </c>
@@ -21392,7 +21406,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="153" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="s">
         <v>324</v>
       </c>
@@ -21499,7 +21513,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="154" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="s">
         <v>326</v>
       </c>
@@ -21606,7 +21620,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="155" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="2" t="s">
         <v>327</v>
       </c>
@@ -21713,7 +21727,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="156" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="2" t="s">
         <v>329</v>
       </c>
@@ -21820,7 +21834,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="157" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="2" t="s">
         <v>330</v>
       </c>
@@ -21927,7 +21941,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="158" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="2" t="s">
         <v>331</v>
       </c>
@@ -22034,7 +22048,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="159" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="s">
         <v>332</v>
       </c>
@@ -22141,7 +22155,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="160" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="2" t="s">
         <v>334</v>
       </c>
@@ -22248,7 +22262,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="161" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="2" t="s">
         <v>336</v>
       </c>
@@ -22355,7 +22369,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="162" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="2" t="s">
         <v>338</v>
       </c>
@@ -22462,7 +22476,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="163" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="2" t="s">
         <v>339</v>
       </c>
@@ -22569,7 +22583,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="164" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="2" t="s">
         <v>342</v>
       </c>
@@ -22676,7 +22690,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="165" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="2" t="s">
         <v>344</v>
       </c>
@@ -22783,7 +22797,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="166" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="2" t="s">
         <v>346</v>
       </c>
@@ -22890,7 +22904,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="167" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="2" t="s">
         <v>348</v>
       </c>
@@ -22997,7 +23011,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="168" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="2" t="s">
         <v>350</v>
       </c>
@@ -23104,7 +23118,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="169" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="2" t="s">
         <v>351</v>
       </c>
@@ -23211,7 +23225,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="170" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="2" t="s">
         <v>353</v>
       </c>
@@ -23318,7 +23332,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="171" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="2" t="s">
         <v>354</v>
       </c>
@@ -23425,7 +23439,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="172" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="2" t="s">
         <v>357</v>
       </c>
@@ -23532,7 +23546,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="173" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="2" t="s">
         <v>358</v>
       </c>
@@ -23639,7 +23653,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="174" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="2" t="s">
         <v>359</v>
       </c>
@@ -23746,7 +23760,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="175" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="2" t="s">
         <v>360</v>
       </c>
@@ -23853,7 +23867,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="176" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="2" t="s">
         <v>362</v>
       </c>
@@ -23960,7 +23974,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="177" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="2" t="s">
         <v>363</v>
       </c>
@@ -24067,7 +24081,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="178" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="2" t="s">
         <v>364</v>
       </c>
@@ -24174,7 +24188,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="179" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="2" t="s">
         <v>367</v>
       </c>
@@ -24281,7 +24295,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="180" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="2" t="s">
         <v>369</v>
       </c>
@@ -24388,7 +24402,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="181" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="2" t="s">
         <v>370</v>
       </c>
@@ -24816,7 +24830,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="185" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="2" t="s">
         <v>378</v>
       </c>
@@ -24923,7 +24937,7 @@
         <v>100.86</v>
       </c>
     </row>
-    <row r="186" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="2" t="s">
         <v>381</v>
       </c>
@@ -25030,7 +25044,7 @@
         <v>100.86</v>
       </c>
     </row>
-    <row r="187" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="2" t="s">
         <v>382</v>
       </c>
@@ -25137,7 +25151,7 @@
         <v>100.86</v>
       </c>
     </row>
-    <row r="188" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="2" t="s">
         <v>383</v>
       </c>
@@ -25244,7 +25258,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="189" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="2" t="s">
         <v>387</v>
       </c>
@@ -25351,7 +25365,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="190" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="2" t="s">
         <v>389</v>
       </c>
@@ -25458,7 +25472,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="191" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="2" t="s">
         <v>391</v>
       </c>
@@ -25565,7 +25579,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="192" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="2" t="s">
         <v>393</v>
       </c>
@@ -25672,7 +25686,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="193" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="2" t="s">
         <v>394</v>
       </c>
@@ -25779,7 +25793,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="194" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="2" t="s">
         <v>395</v>
       </c>
@@ -25886,7 +25900,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="195" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" s="2" t="s">
         <v>398</v>
       </c>
@@ -25993,7 +26007,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="196" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" s="2" t="s">
         <v>399</v>
       </c>
@@ -26100,7 +26114,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="197" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="2" t="s">
         <v>402</v>
       </c>
@@ -26207,7 +26221,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="198" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" s="2" t="s">
         <v>403</v>
       </c>
@@ -26314,7 +26328,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="199" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" s="2" t="s">
         <v>404</v>
       </c>
@@ -26421,7 +26435,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="200" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="2" t="s">
         <v>405</v>
       </c>
@@ -26528,7 +26542,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="201" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="2" t="s">
         <v>406</v>
       </c>
@@ -26635,7 +26649,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="202" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" s="2" t="s">
         <v>408</v>
       </c>
@@ -26742,7 +26756,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="203" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" s="2" t="s">
         <v>410</v>
       </c>
@@ -26849,7 +26863,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="204" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" s="2" t="s">
         <v>411</v>
       </c>
@@ -26956,7 +26970,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="205" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" s="2" t="s">
         <v>412</v>
       </c>
@@ -27063,7 +27077,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="206" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" s="2" t="s">
         <v>413</v>
       </c>
@@ -27170,7 +27184,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="207" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207" s="2" t="s">
         <v>414</v>
       </c>
@@ -27277,7 +27291,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="208" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" s="2" t="s">
         <v>415</v>
       </c>
@@ -27384,7 +27398,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="209" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" s="2" t="s">
         <v>419</v>
       </c>
@@ -27491,7 +27505,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="210" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A210" s="2" t="s">
         <v>420</v>
       </c>
@@ -27598,7 +27612,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="211" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" s="2" t="s">
         <v>421</v>
       </c>
@@ -27705,7 +27719,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="212" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" s="2" t="s">
         <v>422</v>
       </c>
@@ -27812,7 +27826,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="213" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213" s="2" t="s">
         <v>423</v>
       </c>
@@ -27919,7 +27933,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="214" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214" s="2" t="s">
         <v>425</v>
       </c>
@@ -28026,7 +28040,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="215" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" s="2" t="s">
         <v>426</v>
       </c>
@@ -28133,7 +28147,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="216" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216" s="2" t="s">
         <v>427</v>
       </c>
@@ -28240,7 +28254,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="217" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A217" s="2" t="s">
         <v>428</v>
       </c>
@@ -28347,7 +28361,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="218" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A218" s="2" t="s">
         <v>429</v>
       </c>
@@ -28454,7 +28468,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="219" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219" s="2" t="s">
         <v>430</v>
       </c>
@@ -28561,7 +28575,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="220" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="2" t="s">
         <v>432</v>
       </c>
@@ -28668,7 +28682,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="221" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A221" s="2" t="s">
         <v>434</v>
       </c>
@@ -28775,7 +28789,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="222" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A222" s="2" t="s">
         <v>436</v>
       </c>
@@ -28882,7 +28896,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="223" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A223" s="2" t="s">
         <v>437</v>
       </c>
@@ -28989,7 +29003,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="224" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A224" s="2" t="s">
         <v>438</v>
       </c>
@@ -29096,7 +29110,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="225" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225" s="2" t="s">
         <v>440</v>
       </c>
@@ -29203,7 +29217,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="226" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A226" s="2" t="s">
         <v>441</v>
       </c>
@@ -29310,7 +29324,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="227" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A227" s="2" t="s">
         <v>442</v>
       </c>
@@ -29417,7 +29431,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="228" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A228" s="2" t="s">
         <v>443</v>
       </c>
@@ -29524,7 +29538,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="229" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A229" s="2" t="s">
         <v>444</v>
       </c>
@@ -29631,7 +29645,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="230" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A230" s="2" t="s">
         <v>445</v>
       </c>
@@ -29738,7 +29752,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="231" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A231" s="2" t="s">
         <v>448</v>
       </c>
@@ -29845,7 +29859,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="232" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A232" s="2" t="s">
         <v>449</v>
       </c>
@@ -29952,7 +29966,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="233" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A233" s="2" t="s">
         <v>450</v>
       </c>
@@ -30059,7 +30073,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="234" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A234" s="2" t="s">
         <v>451</v>
       </c>
@@ -30166,7 +30180,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="235" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A235" s="2" t="s">
         <v>452</v>
       </c>
@@ -30273,7 +30287,7 @@
         <v>95.55</v>
       </c>
     </row>
-    <row r="236" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A236" s="2" t="s">
         <v>458</v>
       </c>
@@ -30380,7 +30394,7 @@
         <v>95.55</v>
       </c>
     </row>
-    <row r="237" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="2" t="s">
         <v>459</v>
       </c>
@@ -30487,7 +30501,7 @@
         <v>95.55</v>
       </c>
     </row>
-    <row r="238" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" s="2" t="s">
         <v>461</v>
       </c>
@@ -30594,7 +30608,7 @@
         <v>95.55</v>
       </c>
     </row>
-    <row r="239" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A239" s="2" t="s">
         <v>463</v>
       </c>
@@ -30701,7 +30715,7 @@
         <v>95.55</v>
       </c>
     </row>
-    <row r="240" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A240" s="2" t="s">
         <v>464</v>
       </c>
@@ -30808,7 +30822,7 @@
         <v>95.55</v>
       </c>
     </row>
-    <row r="241" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A241" s="2" t="s">
         <v>465</v>
       </c>
@@ -30915,7 +30929,7 @@
         <v>84.94</v>
       </c>
     </row>
-    <row r="242" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A242" s="2" t="s">
         <v>468</v>
       </c>
@@ -31022,7 +31036,7 @@
         <v>84.94</v>
       </c>
     </row>
-    <row r="243" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A243" s="2" t="s">
         <v>469</v>
       </c>
@@ -31129,7 +31143,7 @@
         <v>84.94</v>
       </c>
     </row>
-    <row r="244" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A244" s="2" t="s">
         <v>471</v>
       </c>
@@ -31236,7 +31250,7 @@
         <v>84.94</v>
       </c>
     </row>
-    <row r="245" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A245" s="2" t="s">
         <v>472</v>
       </c>
@@ -31343,7 +31357,7 @@
         <v>79.63</v>
       </c>
     </row>
-    <row r="246" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A246" s="2" t="s">
         <v>474</v>
       </c>
@@ -31450,7 +31464,7 @@
         <v>79.63</v>
       </c>
     </row>
-    <row r="247" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A247" s="2" t="s">
         <v>475</v>
       </c>
@@ -31557,7 +31571,7 @@
         <v>79.63</v>
       </c>
     </row>
-    <row r="248" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A248" s="2" t="s">
         <v>476</v>
       </c>
@@ -31664,7 +31678,7 @@
         <v>79.63</v>
       </c>
     </row>
-    <row r="249" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A249" s="2" t="s">
         <v>477</v>
       </c>
@@ -31771,7 +31785,7 @@
         <v>79.63</v>
       </c>
     </row>
-    <row r="250" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A250" s="2" t="s">
         <v>478</v>
       </c>
@@ -31878,7 +31892,7 @@
         <v>69.010000000000005</v>
       </c>
     </row>
-    <row r="251" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A251" s="2" t="s">
         <v>481</v>
       </c>
@@ -31985,7 +31999,7 @@
         <v>69.010000000000005</v>
       </c>
     </row>
-    <row r="252" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A252" s="2" t="s">
         <v>482</v>
       </c>
@@ -32092,7 +32106,7 @@
         <v>69.010000000000005</v>
       </c>
     </row>
-    <row r="253" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A253" s="2" t="s">
         <v>484</v>
       </c>
@@ -32199,7 +32213,7 @@
         <v>69.010000000000005</v>
       </c>
     </row>
-    <row r="254" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A254" s="2" t="s">
         <v>485</v>
       </c>
@@ -32306,7 +32320,7 @@
         <v>53.09</v>
       </c>
     </row>
-    <row r="255" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255" s="2" t="s">
         <v>488</v>
       </c>
@@ -32413,7 +32427,7 @@
         <v>53.09</v>
       </c>
     </row>
-    <row r="256" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A256" s="2" t="s">
         <v>490</v>
       </c>
@@ -32520,7 +32534,7 @@
         <v>53.09</v>
       </c>
     </row>
-    <row r="257" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A257" s="2" t="s">
         <v>492</v>
       </c>
@@ -32627,7 +32641,7 @@
         <v>53.09</v>
       </c>
     </row>
-    <row r="258" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A258" s="2" t="s">
         <v>493</v>
       </c>
@@ -32734,7 +32748,7 @@
         <v>53.09</v>
       </c>
     </row>
-    <row r="259" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A259" s="2" t="s">
         <v>495</v>
       </c>
@@ -32829,7 +32843,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="260" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A260" s="2" t="s">
         <v>498</v>
       </c>
@@ -32924,7 +32938,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="261" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A261" s="2" t="s">
         <v>499</v>
       </c>
@@ -33019,7 +33033,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="262" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A262" s="2" t="s">
         <v>501</v>
       </c>
@@ -33114,7 +33128,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="263" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A263" s="2" t="s">
         <v>502</v>
       </c>
@@ -33209,7 +33223,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="264" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A264" s="2" t="s">
         <v>504</v>
       </c>
@@ -33304,7 +33318,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="265" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A265" s="2" t="s">
         <v>506</v>
       </c>
@@ -33399,7 +33413,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="266" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A266" s="2" t="s">
         <v>508</v>
       </c>
@@ -33494,7 +33508,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="267" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A267" s="2" t="s">
         <v>509</v>
       </c>
@@ -33589,7 +33603,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="268" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A268" s="2" t="s">
         <v>510</v>
       </c>
@@ -33684,7 +33698,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="269" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A269" s="2" t="s">
         <v>511</v>
       </c>
@@ -33779,7 +33793,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="270" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A270" s="2" t="s">
         <v>513</v>
       </c>
@@ -33874,7 +33888,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="271" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A271" s="2" t="s">
         <v>514</v>
       </c>
@@ -33969,7 +33983,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="272" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A272" s="2" t="s">
         <v>515</v>
       </c>
@@ -34064,7 +34078,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="273" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A273" s="2" t="s">
         <v>516</v>
       </c>
@@ -34125,7 +34139,7 @@
       <c r="AH273" s="4"/>
       <c r="AI273" s="4"/>
     </row>
-    <row r="274" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A274" s="2" t="s">
         <v>518</v>
       </c>
@@ -34186,7 +34200,7 @@
       <c r="AH274" s="4"/>
       <c r="AI274" s="4"/>
     </row>
-    <row r="275" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A275" s="2" t="s">
         <v>519</v>
       </c>
@@ -34247,7 +34261,7 @@
       <c r="AH275" s="4"/>
       <c r="AI275" s="4"/>
     </row>
-    <row r="276" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A276" s="2" t="s">
         <v>520</v>
       </c>
@@ -34308,7 +34322,7 @@
       <c r="AH276" s="4"/>
       <c r="AI276" s="4"/>
     </row>
-    <row r="277" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A277" s="2" t="s">
         <v>521</v>
       </c>
@@ -34369,7 +34383,7 @@
       <c r="AH277" s="4"/>
       <c r="AI277" s="4"/>
     </row>
-    <row r="278" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A278" s="2" t="s">
         <v>523</v>
       </c>
@@ -34464,7 +34478,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="279" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A279" s="2" t="s">
         <v>525</v>
       </c>
@@ -34559,7 +34573,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="280" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A280" s="2" t="s">
         <v>527</v>
       </c>
@@ -34654,7 +34668,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="281" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A281" s="2" t="s">
         <v>528</v>
       </c>
@@ -34749,7 +34763,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="282" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A282" s="2" t="s">
         <v>182</v>
       </c>
@@ -34844,7 +34858,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="283" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A283" s="2" t="s">
         <v>181</v>
       </c>
@@ -34939,7 +34953,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="284" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A284" s="2" t="s">
         <v>180</v>
       </c>
@@ -35034,7 +35048,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="285" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A285" s="2" t="s">
         <v>177</v>
       </c>
@@ -35129,7 +35143,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="286" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A286" s="2" t="s">
         <v>192</v>
       </c>
@@ -35224,7 +35238,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="287" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A287" s="2" t="s">
         <v>529</v>
       </c>
@@ -35319,7 +35333,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="288" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A288" s="2" t="s">
         <v>188</v>
       </c>
@@ -35414,7 +35428,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="289" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A289" s="2" t="s">
         <v>183</v>
       </c>
@@ -35509,7 +35523,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="290" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A290" s="2" t="s">
         <v>186</v>
       </c>
@@ -35604,7 +35618,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="291" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A291" s="2" t="s">
         <v>531</v>
       </c>
@@ -35699,7 +35713,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="292" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A292" s="2" t="s">
         <v>533</v>
       </c>
@@ -35794,7 +35808,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="293" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A293" s="2" t="s">
         <v>534</v>
       </c>
@@ -35889,7 +35903,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="294" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A294" s="2" t="s">
         <v>536</v>
       </c>
@@ -35950,7 +35964,7 @@
       <c r="AH294" s="4"/>
       <c r="AI294" s="4"/>
     </row>
-    <row r="295" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A295" s="2" t="s">
         <v>538</v>
       </c>
@@ -36011,7 +36025,7 @@
       <c r="AH295" s="4"/>
       <c r="AI295" s="4"/>
     </row>
-    <row r="296" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A296" s="2" t="s">
         <v>539</v>
       </c>
@@ -36072,7 +36086,7 @@
       <c r="AH296" s="4"/>
       <c r="AI296" s="4"/>
     </row>
-    <row r="297" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A297" s="2" t="s">
         <v>222</v>
       </c>
@@ -36167,7 +36181,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="298" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A298" s="2" t="s">
         <v>223</v>
       </c>
@@ -36262,7 +36276,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="299" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A299" s="2" t="s">
         <v>219</v>
       </c>
@@ -36357,7 +36371,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="300" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A300" s="2" t="s">
         <v>225</v>
       </c>
@@ -36452,7 +36466,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="301" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A301" s="2" t="s">
         <v>207</v>
       </c>
@@ -36547,7 +36561,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="302" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A302" s="2" t="s">
         <v>204</v>
       </c>
@@ -36642,7 +36656,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="303" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A303" s="2" t="s">
         <v>540</v>
       </c>
@@ -36737,7 +36751,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="304" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A304" s="2" t="s">
         <v>542</v>
       </c>
@@ -36832,7 +36846,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="305" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A305" s="2" t="s">
         <v>544</v>
       </c>
@@ -36927,7 +36941,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="306" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A306" s="2" t="s">
         <v>254</v>
       </c>
@@ -37022,7 +37036,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="307" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A307" s="2" t="s">
         <v>252</v>
       </c>
@@ -37117,7 +37131,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="308" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A308" s="2" t="s">
         <v>250</v>
       </c>
@@ -37212,7 +37226,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="309" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A309" s="2" t="s">
         <v>247</v>
       </c>
@@ -37307,7 +37321,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="310" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A310" s="2" t="s">
         <v>251</v>
       </c>
@@ -37402,7 +37416,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="311" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A311" s="2" t="s">
         <v>259</v>
       </c>
@@ -37497,7 +37511,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="312" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A312" s="2" t="s">
         <v>261</v>
       </c>
@@ -37592,7 +37606,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="313" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A313" s="2" t="s">
         <v>257</v>
       </c>
@@ -37687,7 +37701,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="314" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A314" s="2" t="s">
         <v>255</v>
       </c>
@@ -37782,7 +37796,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="315" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A315" s="2" t="s">
         <v>546</v>
       </c>
@@ -37877,7 +37891,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="316" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A316" s="2" t="s">
         <v>284</v>
       </c>
@@ -37972,7 +37986,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="317" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A317" s="2" t="s">
         <v>283</v>
       </c>
@@ -38067,7 +38081,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="318" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A318" s="2" t="s">
         <v>280</v>
       </c>
@@ -38162,7 +38176,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="319" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A319" s="2" t="s">
         <v>292</v>
       </c>
@@ -38257,7 +38271,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="320" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A320" s="2" t="s">
         <v>288</v>
       </c>
@@ -38352,7 +38366,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="321" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A321" s="2" t="s">
         <v>286</v>
       </c>
@@ -38447,7 +38461,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="322" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A322" s="2" t="s">
         <v>290</v>
       </c>
@@ -38542,7 +38556,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="323" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A323" s="2" t="s">
         <v>547</v>
       </c>
@@ -38637,7 +38651,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="324" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A324" s="2" t="s">
         <v>549</v>
       </c>
@@ -38732,7 +38746,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="325" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A325" s="2" t="s">
         <v>551</v>
       </c>
@@ -38827,7 +38841,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="326" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A326" s="2" t="s">
         <v>553</v>
       </c>
@@ -38922,7 +38936,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="327" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A327" s="2" t="s">
         <v>554</v>
       </c>
@@ -39017,7 +39031,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="328" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A328" s="2" t="s">
         <v>557</v>
       </c>
@@ -39112,7 +39126,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="329" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A329" s="2" t="s">
         <v>558</v>
       </c>
@@ -39207,7 +39221,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="330" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A330" s="2" t="s">
         <v>296</v>
       </c>
@@ -39302,7 +39316,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="331" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A331" s="2" t="s">
         <v>295</v>
       </c>
@@ -39397,7 +39411,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="332" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A332" s="2" t="s">
         <v>293</v>
       </c>
@@ -39492,7 +39506,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="333" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A333" s="2" t="s">
         <v>297</v>
       </c>
@@ -39587,7 +39601,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="334" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A334" s="2" t="s">
         <v>331</v>
       </c>
@@ -39682,7 +39696,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="335" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A335" s="2" t="s">
         <v>329</v>
       </c>
@@ -39777,7 +39791,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="336" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A336" s="2" t="s">
         <v>327</v>
       </c>
@@ -39872,7 +39886,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="337" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A337" s="2" t="s">
         <v>330</v>
       </c>
@@ -39967,7 +39981,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="338" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A338" s="2" t="s">
         <v>320</v>
       </c>
@@ -40062,7 +40076,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="339" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A339" s="2" t="s">
         <v>324</v>
       </c>
@@ -40157,7 +40171,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="340" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A340" s="2" t="s">
         <v>323</v>
       </c>
@@ -40252,7 +40266,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="341" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A341" s="2" t="s">
         <v>326</v>
       </c>
@@ -40347,7 +40361,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="342" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A342" s="2" t="s">
         <v>332</v>
       </c>
@@ -40442,7 +40456,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="343" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A343" s="2" t="s">
         <v>338</v>
       </c>
@@ -40537,7 +40551,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="344" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A344" s="2" t="s">
         <v>334</v>
       </c>
@@ -40632,7 +40646,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="345" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A345" s="2" t="s">
         <v>560</v>
       </c>
@@ -40727,7 +40741,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="346" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A346" s="2" t="s">
         <v>342</v>
       </c>
@@ -40822,7 +40836,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="347" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A347" s="2" t="s">
         <v>346</v>
       </c>
@@ -40917,7 +40931,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="348" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A348" s="2" t="s">
         <v>344</v>
       </c>
@@ -41012,7 +41026,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="349" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A349" s="2" t="s">
         <v>339</v>
       </c>
@@ -41107,7 +41121,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="350" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A350" s="2" t="s">
         <v>562</v>
       </c>
@@ -41214,7 +41228,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="351" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A351" s="2" t="s">
         <v>564</v>
       </c>
@@ -41321,7 +41335,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="352" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A352" s="2" t="s">
         <v>565</v>
       </c>
@@ -41808,7 +41822,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="357" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A357" s="2" t="s">
         <v>367</v>
       </c>
@@ -41903,7 +41917,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="358" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A358" s="2" t="s">
         <v>569</v>
       </c>
@@ -41998,7 +42012,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="359" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A359" s="2" t="s">
         <v>364</v>
       </c>
@@ -42093,7 +42107,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="360" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A360" s="2" t="s">
         <v>570</v>
       </c>
@@ -42188,7 +42202,7 @@
         <v>100.86</v>
       </c>
     </row>
-    <row r="361" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A361" s="2" t="s">
         <v>571</v>
       </c>
@@ -42283,7 +42297,7 @@
         <v>100.86</v>
       </c>
     </row>
-    <row r="362" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A362" s="2" t="s">
         <v>378</v>
       </c>
@@ -42378,7 +42392,7 @@
         <v>100.86</v>
       </c>
     </row>
-    <row r="363" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A363" s="2" t="s">
         <v>149</v>
       </c>
@@ -42473,7 +42487,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="364" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A364" s="2" t="s">
         <v>573</v>
       </c>
@@ -42568,7 +42582,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="365" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A365" s="2" t="s">
         <v>152</v>
       </c>
@@ -42663,7 +42677,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="366" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A366" s="2" t="s">
         <v>151</v>
       </c>
@@ -42758,7 +42772,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="367" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A367" s="2" t="s">
         <v>143</v>
       </c>
@@ -42853,7 +42867,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="368" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A368" s="2" t="s">
         <v>147</v>
       </c>
@@ -42948,7 +42962,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="369" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A369" s="2" t="s">
         <v>148</v>
       </c>
@@ -43043,7 +43057,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="370" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A370" s="2" t="s">
         <v>156</v>
       </c>
@@ -43138,7 +43152,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="371" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A371" s="2" t="s">
         <v>574</v>
       </c>
@@ -43233,7 +43247,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="372" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A372" s="2" t="s">
         <v>575</v>
       </c>
@@ -43328,7 +43342,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="373" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A373" s="2" t="s">
         <v>576</v>
       </c>
@@ -43423,7 +43437,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="374" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A374" s="2" t="s">
         <v>579</v>
       </c>
@@ -43518,7 +43532,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="375" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A375" s="2" t="s">
         <v>231</v>
       </c>
@@ -43613,7 +43627,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="376" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A376" s="2" t="s">
         <v>235</v>
       </c>
@@ -43708,7 +43722,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="377" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A377" s="2" t="s">
         <v>227</v>
       </c>
@@ -43803,7 +43817,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="378" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A378" s="2" t="s">
         <v>233</v>
       </c>
@@ -43898,7 +43912,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="379" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A379" s="2" t="s">
         <v>314</v>
       </c>
@@ -43993,7 +44007,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="380" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A380" s="2" t="s">
         <v>315</v>
       </c>
@@ -44088,7 +44102,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="381" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A381" s="2" t="s">
         <v>312</v>
       </c>
@@ -44183,7 +44197,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="382" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A382" s="2" t="s">
         <v>310</v>
       </c>
@@ -44278,7 +44292,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="383" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A383" s="2" t="s">
         <v>581</v>
       </c>
@@ -44373,7 +44387,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="384" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A384" s="2" t="s">
         <v>583</v>
       </c>
@@ -44468,7 +44482,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="385" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A385" s="2" t="s">
         <v>585</v>
       </c>
@@ -44563,7 +44577,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="386" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A386" s="2" t="s">
         <v>587</v>
       </c>
@@ -44658,7 +44672,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="387" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A387" s="2" t="s">
         <v>436</v>
       </c>
@@ -44753,7 +44767,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="388" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A388" s="2" t="s">
         <v>434</v>
       </c>
@@ -44848,7 +44862,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="389" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A389" s="2" t="s">
         <v>437</v>
       </c>
@@ -44943,7 +44957,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="390" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A390" s="2" t="s">
         <v>430</v>
       </c>
@@ -45038,7 +45052,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="391" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A391" s="2" t="s">
         <v>432</v>
       </c>
@@ -45133,7 +45147,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="392" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A392" s="2" t="s">
         <v>450</v>
       </c>
@@ -45228,7 +45242,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="393" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A393" s="2" t="s">
         <v>448</v>
       </c>
@@ -45323,7 +45337,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="394" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A394" s="2" t="s">
         <v>445</v>
       </c>
@@ -45418,7 +45432,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="395" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A395" s="2" t="s">
         <v>589</v>
       </c>
@@ -45513,7 +45527,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="396" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A396" s="2" t="s">
         <v>591</v>
       </c>
@@ -45608,7 +45622,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="397" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A397" s="2" t="s">
         <v>592</v>
       </c>
@@ -45703,7 +45717,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="398" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A398" s="2" t="s">
         <v>593</v>
       </c>
@@ -45798,7 +45812,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="399" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A399" s="2" t="s">
         <v>594</v>
       </c>
@@ -45859,7 +45873,7 @@
       <c r="AH399" s="4"/>
       <c r="AI399" s="4"/>
     </row>
-    <row r="400" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A400" s="2" t="s">
         <v>598</v>
       </c>
@@ -45920,7 +45934,7 @@
       <c r="AH400" s="4"/>
       <c r="AI400" s="4"/>
     </row>
-    <row r="401" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A401" s="2" t="s">
         <v>600</v>
       </c>
@@ -45981,7 +45995,7 @@
       <c r="AH401" s="4"/>
       <c r="AI401" s="4"/>
     </row>
-    <row r="402" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A402" s="2" t="s">
         <v>602</v>
       </c>
@@ -46042,7 +46056,7 @@
       <c r="AH402" s="4"/>
       <c r="AI402" s="4"/>
     </row>
-    <row r="403" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A403" s="2" t="s">
         <v>383</v>
       </c>
@@ -46137,7 +46151,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="404" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A404" s="2" t="s">
         <v>394</v>
       </c>
@@ -46232,7 +46246,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="405" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A405" s="2" t="s">
         <v>393</v>
       </c>
@@ -46327,7 +46341,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="406" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A406" s="2" t="s">
         <v>391</v>
       </c>
@@ -46422,7 +46436,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="407" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A407" s="2" t="s">
         <v>387</v>
       </c>
@@ -46517,7 +46531,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="408" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A408" s="2" t="s">
         <v>389</v>
       </c>
@@ -46612,7 +46626,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="409" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A409" s="2" t="s">
         <v>198</v>
       </c>
@@ -46707,7 +46721,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="410" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A410" s="2" t="s">
         <v>193</v>
       </c>
@@ -46802,7 +46816,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="411" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A411" s="2" t="s">
         <v>196</v>
       </c>
@@ -46897,7 +46911,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="412" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A412" s="2" t="s">
         <v>604</v>
       </c>
@@ -46992,7 +47006,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="413" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A413" s="2" t="s">
         <v>606</v>
       </c>
@@ -47087,7 +47101,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="414" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A414" s="2" t="s">
         <v>607</v>
       </c>
@@ -47182,7 +47196,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="415" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A415" s="2" t="s">
         <v>608</v>
       </c>
@@ -47277,7 +47291,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="416" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A416" s="2" t="s">
         <v>609</v>
       </c>
@@ -47372,7 +47386,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="417" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A417" s="2" t="s">
         <v>611</v>
       </c>
@@ -47467,7 +47481,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="418" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A418" s="2" t="s">
         <v>612</v>
       </c>
@@ -47562,7 +47576,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="419" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A419" s="2" t="s">
         <v>613</v>
       </c>
@@ -47657,7 +47671,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="420" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A420" s="2" t="s">
         <v>363</v>
       </c>
@@ -47752,7 +47766,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="421" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A421" s="2" t="s">
         <v>362</v>
       </c>
@@ -47847,7 +47861,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="422" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A422" s="2" t="s">
         <v>360</v>
       </c>
@@ -47942,7 +47956,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="423" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A423" s="2" t="s">
         <v>359</v>
       </c>
@@ -48037,7 +48051,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="424" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A424" s="2" t="s">
         <v>358</v>
       </c>
@@ -48132,7 +48146,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="425" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A425" s="2" t="s">
         <v>357</v>
       </c>
@@ -48227,7 +48241,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="426" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A426" s="2" t="s">
         <v>354</v>
       </c>
@@ -48322,7 +48336,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="427" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A427" s="2" t="s">
         <v>614</v>
       </c>
@@ -48417,7 +48431,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="428" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A428" s="2" t="s">
         <v>617</v>
       </c>
@@ -48512,7 +48526,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="429" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A429" s="2" t="s">
         <v>618</v>
       </c>
@@ -48607,7 +48621,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="430" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A430" s="2" t="s">
         <v>620</v>
       </c>
@@ -48702,7 +48716,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="431" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A431" s="2" t="s">
         <v>408</v>
       </c>
@@ -48797,7 +48811,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="432" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A432" s="2" t="s">
         <v>414</v>
       </c>
@@ -48892,7 +48906,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="433" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A433" s="2" t="s">
         <v>413</v>
       </c>
@@ -48987,7 +49001,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="434" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A434" s="2" t="s">
         <v>411</v>
       </c>
@@ -49082,7 +49096,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="435" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A435" s="2" t="s">
         <v>621</v>
       </c>
@@ -49177,7 +49191,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="436" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A436" s="2" t="s">
         <v>412</v>
       </c>
@@ -49272,7 +49286,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="437" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A437" s="2" t="s">
         <v>398</v>
       </c>
@@ -49367,7 +49381,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="438" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A438" s="2" t="s">
         <v>395</v>
       </c>
@@ -49462,7 +49476,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="439" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A439" s="2" t="s">
         <v>438</v>
       </c>
@@ -49557,7 +49571,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="440" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A440" s="2" t="s">
         <v>444</v>
       </c>
@@ -49652,7 +49666,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="441" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A441" s="2" t="s">
         <v>443</v>
       </c>
@@ -49747,7 +49761,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="442" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A442" s="2" t="s">
         <v>441</v>
       </c>
@@ -49842,7 +49856,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="443" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A443" s="2" t="s">
         <v>442</v>
       </c>
@@ -49937,7 +49951,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="444" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A444" s="2" t="s">
         <v>493</v>
       </c>
@@ -50032,7 +50046,7 @@
         <v>53.09</v>
       </c>
     </row>
-    <row r="445" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A445" s="2" t="s">
         <v>492</v>
       </c>
@@ -50127,7 +50141,7 @@
         <v>53.09</v>
       </c>
     </row>
-    <row r="446" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A446" s="2" t="s">
         <v>490</v>
       </c>
@@ -50222,7 +50236,7 @@
         <v>53.09</v>
       </c>
     </row>
-    <row r="447" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A447" s="2" t="s">
         <v>488</v>
       </c>
@@ -50317,7 +50331,7 @@
         <v>53.09</v>
       </c>
     </row>
-    <row r="448" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A448" s="2" t="s">
         <v>485</v>
       </c>
@@ -50412,7 +50426,7 @@
         <v>53.09</v>
       </c>
     </row>
-    <row r="449" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A449" s="2" t="s">
         <v>464</v>
       </c>
@@ -50507,7 +50521,7 @@
         <v>95.55</v>
       </c>
     </row>
-    <row r="450" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A450" s="2" t="s">
         <v>463</v>
       </c>
@@ -50602,7 +50616,7 @@
         <v>95.55</v>
       </c>
     </row>
-    <row r="451" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A451" s="2" t="s">
         <v>461</v>
       </c>
@@ -50697,7 +50711,7 @@
         <v>95.55</v>
       </c>
     </row>
-    <row r="452" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A452" s="2" t="s">
         <v>458</v>
       </c>
@@ -50792,7 +50806,7 @@
         <v>95.55</v>
       </c>
     </row>
-    <row r="453" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A453" s="2" t="s">
         <v>459</v>
       </c>
@@ -50887,7 +50901,7 @@
         <v>95.55</v>
       </c>
     </row>
-    <row r="454" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A454" s="2" t="s">
         <v>452</v>
       </c>
@@ -50982,7 +50996,7 @@
         <v>95.55</v>
       </c>
     </row>
-    <row r="455" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A455" s="2" t="s">
         <v>624</v>
       </c>
@@ -51043,7 +51057,7 @@
       <c r="AH455" s="4"/>
       <c r="AI455" s="4"/>
     </row>
-    <row r="456" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A456" s="2" t="s">
         <v>627</v>
       </c>
@@ -51104,7 +51118,7 @@
       <c r="AH456" s="4"/>
       <c r="AI456" s="4"/>
     </row>
-    <row r="457" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A457" s="2" t="s">
         <v>629</v>
       </c>
@@ -51165,7 +51179,7 @@
       <c r="AH457" s="4"/>
       <c r="AI457" s="4"/>
     </row>
-    <row r="458" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A458" s="2" t="s">
         <v>631</v>
       </c>
@@ -51226,7 +51240,7 @@
       <c r="AH458" s="4"/>
       <c r="AI458" s="4"/>
     </row>
-    <row r="459" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A459" s="2" t="s">
         <v>477</v>
       </c>
@@ -51321,7 +51335,7 @@
         <v>79.63</v>
       </c>
     </row>
-    <row r="460" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A460" s="2" t="s">
         <v>476</v>
       </c>
@@ -51416,7 +51430,7 @@
         <v>79.63</v>
       </c>
     </row>
-    <row r="461" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A461" s="2" t="s">
         <v>472</v>
       </c>
@@ -51511,7 +51525,7 @@
         <v>79.63</v>
       </c>
     </row>
-    <row r="462" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A462" s="2" t="s">
         <v>474</v>
       </c>
@@ -51606,7 +51620,7 @@
         <v>79.63</v>
       </c>
     </row>
-    <row r="463" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A463" s="2" t="s">
         <v>475</v>
       </c>
@@ -51701,7 +51715,7 @@
         <v>79.63</v>
       </c>
     </row>
-    <row r="464" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A464" s="2" t="s">
         <v>632</v>
       </c>
@@ -51796,7 +51810,7 @@
         <v>69.010000000000005</v>
       </c>
     </row>
-    <row r="465" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A465" s="2" t="s">
         <v>478</v>
       </c>
@@ -51891,7 +51905,7 @@
         <v>69.010000000000005</v>
       </c>
     </row>
-    <row r="466" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A466" s="2" t="s">
         <v>634</v>
       </c>
@@ -51986,7 +52000,7 @@
         <v>69.010000000000005</v>
       </c>
     </row>
-    <row r="467" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A467" s="2" t="s">
         <v>635</v>
       </c>
@@ -52081,7 +52095,7 @@
         <v>69.010000000000005</v>
       </c>
     </row>
-    <row r="468" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A468" s="2" t="s">
         <v>636</v>
       </c>
@@ -52176,7 +52190,7 @@
         <v>69.010000000000005</v>
       </c>
     </row>
-    <row r="469" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A469" s="2" t="s">
         <v>637</v>
       </c>
@@ -52271,7 +52285,7 @@
         <v>74.319999999999993</v>
       </c>
     </row>
-    <row r="470" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A470" s="2" t="s">
         <v>639</v>
       </c>
@@ -52366,7 +52380,7 @@
         <v>74.319999999999993</v>
       </c>
     </row>
-    <row r="471" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A471" s="2" t="s">
         <v>641</v>
       </c>
@@ -52461,7 +52475,7 @@
         <v>74.319999999999993</v>
       </c>
     </row>
-    <row r="472" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A472" s="2" t="s">
         <v>643</v>
       </c>
@@ -52556,7 +52570,7 @@
         <v>74.319999999999993</v>
       </c>
     </row>
-    <row r="473" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A473" s="2" t="s">
         <v>645</v>
       </c>
@@ -52617,7 +52631,7 @@
       <c r="AH473" s="4"/>
       <c r="AI473" s="4"/>
     </row>
-    <row r="474" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A474" s="2" t="s">
         <v>648</v>
       </c>
@@ -52678,7 +52692,7 @@
       <c r="AH474" s="4"/>
       <c r="AI474" s="4"/>
     </row>
-    <row r="475" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A475" s="2" t="s">
         <v>649</v>
       </c>
@@ -52739,7 +52753,7 @@
       <c r="AH475" s="4"/>
       <c r="AI475" s="4"/>
     </row>
-    <row r="476" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A476" s="2" t="s">
         <v>651</v>
       </c>
@@ -52800,7 +52814,7 @@
       <c r="AH476" s="4"/>
       <c r="AI476" s="4"/>
     </row>
-    <row r="477" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A477" s="2" t="s">
         <v>653</v>
       </c>
@@ -52861,7 +52875,7 @@
       <c r="AH477" s="4"/>
       <c r="AI477" s="4"/>
     </row>
-    <row r="478" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A478" s="2" t="s">
         <v>654</v>
       </c>
@@ -52922,7 +52936,7 @@
       <c r="AH478" s="4"/>
       <c r="AI478" s="4"/>
     </row>
-    <row r="479" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A479" s="2" t="s">
         <v>658</v>
       </c>
@@ -52983,7 +52997,7 @@
       <c r="AH479" s="4"/>
       <c r="AI479" s="4"/>
     </row>
-    <row r="480" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A480" s="2" t="s">
         <v>661</v>
       </c>
@@ -53044,7 +53058,7 @@
       <c r="AH480" s="4"/>
       <c r="AI480" s="4"/>
     </row>
-    <row r="481" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A481" s="2" t="s">
         <v>663</v>
       </c>
@@ -53105,7 +53119,7 @@
       <c r="AH481" s="4"/>
       <c r="AI481" s="4"/>
     </row>
-    <row r="482" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A482" s="2" t="s">
         <v>665</v>
       </c>
@@ -53166,7 +53180,7 @@
       <c r="AH482" s="4"/>
       <c r="AI482" s="4"/>
     </row>
-    <row r="483" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A483" s="2" t="s">
         <v>666</v>
       </c>
@@ -53227,7 +53241,7 @@
       <c r="AH483" s="4"/>
       <c r="AI483" s="4"/>
     </row>
-    <row r="484" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A484" s="2" t="s">
         <v>79</v>
       </c>
@@ -53322,7 +53336,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="485" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A485" s="2" t="s">
         <v>77</v>
       </c>
@@ -53417,7 +53431,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="486" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A486" s="2" t="s">
         <v>75</v>
       </c>
@@ -53512,7 +53526,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="487" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A487" s="2" t="s">
         <v>71</v>
       </c>
@@ -53607,7 +53621,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="488" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A488" s="2" t="s">
         <v>66</v>
       </c>
@@ -53702,7 +53716,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="489" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A489" s="2" t="s">
         <v>73</v>
       </c>
@@ -53797,7 +53811,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="490" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A490" s="2" t="s">
         <v>69</v>
       </c>
@@ -53892,7 +53906,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="491" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A491" s="2" t="s">
         <v>667</v>
       </c>
@@ -53953,7 +53967,7 @@
       <c r="AH491" s="4"/>
       <c r="AI491" s="4"/>
     </row>
-    <row r="492" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A492" s="2" t="s">
         <v>669</v>
       </c>
@@ -54014,7 +54028,7 @@
       <c r="AH492" s="4"/>
       <c r="AI492" s="4"/>
     </row>
-    <row r="493" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A493" s="2" t="s">
         <v>671</v>
       </c>
@@ -54075,7 +54089,7 @@
       <c r="AH493" s="4"/>
       <c r="AI493" s="4"/>
     </row>
-    <row r="494" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A494" s="2" t="s">
         <v>672</v>
       </c>
@@ -54136,7 +54150,7 @@
       <c r="AH494" s="4"/>
       <c r="AI494" s="4"/>
     </row>
-    <row r="495" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A495" s="2" t="s">
         <v>673</v>
       </c>
@@ -54197,7 +54211,7 @@
       <c r="AH495" s="4"/>
       <c r="AI495" s="4"/>
     </row>
-    <row r="496" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A496" s="2" t="s">
         <v>674</v>
       </c>
@@ -54258,7 +54272,7 @@
       <c r="AH496" s="4"/>
       <c r="AI496" s="4"/>
     </row>
-    <row r="497" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A497" s="2" t="s">
         <v>675</v>
       </c>
@@ -54319,7 +54333,7 @@
       <c r="AH497" s="4"/>
       <c r="AI497" s="4"/>
     </row>
-    <row r="498" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A498" s="2" t="s">
         <v>677</v>
       </c>
@@ -54380,7 +54394,7 @@
       <c r="AH498" s="4"/>
       <c r="AI498" s="4"/>
     </row>
-    <row r="499" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A499" s="2" t="s">
         <v>678</v>
       </c>
@@ -54441,7 +54455,7 @@
       <c r="AH499" s="4"/>
       <c r="AI499" s="4"/>
     </row>
-    <row r="500" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A500" s="2" t="s">
         <v>679</v>
       </c>
@@ -54502,7 +54516,7 @@
       <c r="AH500" s="4"/>
       <c r="AI500" s="4"/>
     </row>
-    <row r="501" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A501" s="2" t="s">
         <v>272</v>
       </c>
@@ -54597,7 +54611,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="502" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A502" s="2" t="s">
         <v>268</v>
       </c>
@@ -54692,7 +54706,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="503" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A503" s="2" t="s">
         <v>270</v>
       </c>
@@ -54787,7 +54801,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="504" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A504" s="2" t="s">
         <v>264</v>
       </c>
@@ -54882,7 +54896,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="505" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A505" s="2" t="s">
         <v>266</v>
       </c>
@@ -54977,7 +54991,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="506" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A506" s="2" t="s">
         <v>680</v>
       </c>
@@ -55072,7 +55086,7 @@
         <v>185.8</v>
       </c>
     </row>
-    <row r="507" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A507" s="2" t="s">
         <v>95</v>
       </c>
@@ -55167,7 +55181,7 @@
         <v>185.8</v>
       </c>
     </row>
-    <row r="508" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A508" s="2" t="s">
         <v>91</v>
       </c>
@@ -55262,7 +55276,7 @@
         <v>185.8</v>
       </c>
     </row>
-    <row r="509" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A509" s="2" t="s">
         <v>681</v>
       </c>
@@ -55357,7 +55371,7 @@
         <v>185.8</v>
       </c>
     </row>
-    <row r="510" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A510" s="2" t="s">
         <v>683</v>
       </c>
@@ -55452,7 +55466,7 @@
         <v>185.8</v>
       </c>
     </row>
-    <row r="511" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A511" s="2" t="s">
         <v>684</v>
       </c>
@@ -55547,7 +55561,7 @@
         <v>185.8</v>
       </c>
     </row>
-    <row r="512" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A512" s="2" t="s">
         <v>685</v>
       </c>
@@ -55642,7 +55656,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="513" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A513" s="2" t="s">
         <v>687</v>
       </c>
@@ -55737,7 +55751,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="514" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A514" s="2" t="s">
         <v>689</v>
       </c>
@@ -55832,7 +55846,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="515" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A515" s="2" t="s">
         <v>691</v>
       </c>
@@ -55927,7 +55941,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="516" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A516" s="2" t="s">
         <v>692</v>
       </c>
@@ -56022,7 +56036,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="517" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A517" s="2" t="s">
         <v>693</v>
       </c>
@@ -56117,7 +56131,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="518" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A518" s="2" t="s">
         <v>695</v>
       </c>
@@ -56212,7 +56226,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="519" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A519" s="2" t="s">
         <v>696</v>
       </c>
@@ -56307,7 +56321,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="520" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A520" s="2" t="s">
         <v>698</v>
       </c>
@@ -56402,7 +56416,7 @@
         <v>291.97000000000003</v>
       </c>
     </row>
-    <row r="521" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A521" s="2" t="s">
         <v>699</v>
       </c>
@@ -56497,7 +56511,7 @@
         <v>291.97000000000003</v>
       </c>
     </row>
-    <row r="522" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A522" s="2" t="s">
         <v>701</v>
       </c>
@@ -56558,7 +56572,7 @@
       <c r="AH522" s="4"/>
       <c r="AI522" s="4"/>
     </row>
-    <row r="523" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A523" s="2" t="s">
         <v>707</v>
       </c>
@@ -56619,7 +56633,7 @@
       <c r="AH523" s="4"/>
       <c r="AI523" s="4"/>
     </row>
-    <row r="524" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A524" s="2" t="s">
         <v>709</v>
       </c>
@@ -56680,7 +56694,7 @@
       <c r="AH524" s="4"/>
       <c r="AI524" s="4"/>
     </row>
-    <row r="525" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A525" s="2" t="s">
         <v>714</v>
       </c>
@@ -56741,7 +56755,7 @@
       <c r="AH525" s="4"/>
       <c r="AI525" s="4"/>
     </row>
-    <row r="526" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A526" s="2" t="s">
         <v>715</v>
       </c>
@@ -56802,7 +56816,7 @@
       <c r="AH526" s="4"/>
       <c r="AI526" s="4"/>
     </row>
-    <row r="527" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A527" s="2" t="s">
         <v>716</v>
       </c>
@@ -56863,7 +56877,7 @@
       <c r="AH527" s="4"/>
       <c r="AI527" s="4"/>
     </row>
-    <row r="528" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A528" s="2" t="s">
         <v>719</v>
       </c>
@@ -56924,7 +56938,7 @@
       <c r="AH528" s="4"/>
       <c r="AI528" s="4"/>
     </row>
-    <row r="529" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A529" s="2" t="s">
         <v>720</v>
       </c>
@@ -56985,7 +56999,7 @@
       <c r="AH529" s="4"/>
       <c r="AI529" s="4"/>
     </row>
-    <row r="530" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A530" s="2" t="s">
         <v>723</v>
       </c>
@@ -57046,7 +57060,7 @@
       <c r="AH530" s="4"/>
       <c r="AI530" s="4"/>
     </row>
-    <row r="531" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A531" s="2" t="s">
         <v>724</v>
       </c>
@@ -57107,7 +57121,7 @@
       <c r="AH531" s="4"/>
       <c r="AI531" s="4"/>
     </row>
-    <row r="532" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A532" s="2" t="s">
         <v>726</v>
       </c>
@@ -57168,7 +57182,7 @@
       <c r="AH532" s="4"/>
       <c r="AI532" s="4"/>
     </row>
-    <row r="533" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A533" s="2" t="s">
         <v>727</v>
       </c>
@@ -57229,7 +57243,7 @@
       <c r="AH533" s="4"/>
       <c r="AI533" s="4"/>
     </row>
-    <row r="534" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A534" s="2" t="s">
         <v>730</v>
       </c>
@@ -57290,7 +57304,7 @@
       <c r="AH534" s="4"/>
       <c r="AI534" s="4"/>
     </row>
-    <row r="535" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A535" s="2" t="s">
         <v>731</v>
       </c>
@@ -57351,7 +57365,7 @@
       <c r="AH535" s="4"/>
       <c r="AI535" s="4"/>
     </row>
-    <row r="536" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A536" s="2" t="s">
         <v>732</v>
       </c>
@@ -57412,7 +57426,7 @@
       <c r="AH536" s="4"/>
       <c r="AI536" s="4"/>
     </row>
-    <row r="537" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A537" s="2" t="s">
         <v>737</v>
       </c>
@@ -57473,7 +57487,7 @@
       <c r="AH537" s="4"/>
       <c r="AI537" s="4"/>
     </row>
-    <row r="538" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A538" s="2" t="s">
         <v>739</v>
       </c>
@@ -57534,7 +57548,7 @@
       <c r="AH538" s="4"/>
       <c r="AI538" s="4"/>
     </row>
-    <row r="539" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A539" s="2" t="s">
         <v>740</v>
       </c>
@@ -57595,7 +57609,7 @@
       <c r="AH539" s="4"/>
       <c r="AI539" s="4"/>
     </row>
-    <row r="540" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A540" s="2" t="s">
         <v>744</v>
       </c>
@@ -57656,7 +57670,7 @@
       <c r="AH540" s="4"/>
       <c r="AI540" s="4"/>
     </row>
-    <row r="541" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A541" s="2" t="s">
         <v>747</v>
       </c>
@@ -57717,7 +57731,7 @@
       <c r="AH541" s="4"/>
       <c r="AI541" s="4"/>
     </row>
-    <row r="542" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A542" s="2" t="s">
         <v>749</v>
       </c>
@@ -57778,7 +57792,7 @@
       <c r="AH542" s="4"/>
       <c r="AI542" s="4"/>
     </row>
-    <row r="543" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A543" s="2" t="s">
         <v>751</v>
       </c>
@@ -57839,7 +57853,7 @@
       <c r="AH543" s="4"/>
       <c r="AI543" s="4"/>
     </row>
-    <row r="544" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A544" s="2" t="s">
         <v>753</v>
       </c>
@@ -57900,7 +57914,7 @@
       <c r="AH544" s="4"/>
       <c r="AI544" s="4"/>
     </row>
-    <row r="545" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A545" s="2" t="s">
         <v>754</v>
       </c>
@@ -57961,7 +57975,7 @@
       <c r="AH545" s="4"/>
       <c r="AI545" s="4"/>
     </row>
-    <row r="546" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A546" s="2" t="s">
         <v>755</v>
       </c>
@@ -58022,7 +58036,7 @@
       <c r="AH546" s="4"/>
       <c r="AI546" s="4"/>
     </row>
-    <row r="547" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A547" s="2" t="s">
         <v>758</v>
       </c>
@@ -58083,7 +58097,7 @@
       <c r="AH547" s="4"/>
       <c r="AI547" s="4"/>
     </row>
-    <row r="548" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A548" s="2" t="s">
         <v>759</v>
       </c>
@@ -58144,7 +58158,7 @@
       <c r="AH548" s="4"/>
       <c r="AI548" s="4"/>
     </row>
-    <row r="549" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A549" s="2" t="s">
         <v>761</v>
       </c>
@@ -58205,7 +58219,7 @@
       <c r="AH549" s="4"/>
       <c r="AI549" s="4"/>
     </row>
-    <row r="550" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A550" s="2" t="s">
         <v>763</v>
       </c>
@@ -58266,7 +58280,7 @@
       <c r="AH550" s="4"/>
       <c r="AI550" s="4"/>
     </row>
-    <row r="551" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A551" s="2" t="s">
         <v>764</v>
       </c>
@@ -58327,7 +58341,7 @@
       <c r="AH551" s="4"/>
       <c r="AI551" s="4"/>
     </row>
-    <row r="552" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A552" s="2" t="s">
         <v>766</v>
       </c>
@@ -58388,7 +58402,7 @@
       <c r="AH552" s="4"/>
       <c r="AI552" s="4"/>
     </row>
-    <row r="553" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A553" s="2" t="s">
         <v>768</v>
       </c>
@@ -58449,7 +58463,7 @@
       <c r="AH553" s="4"/>
       <c r="AI553" s="4"/>
     </row>
-    <row r="554" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A554" s="2" t="s">
         <v>771</v>
       </c>
@@ -58510,7 +58524,7 @@
       <c r="AH554" s="4"/>
       <c r="AI554" s="4"/>
     </row>
-    <row r="555" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A555" s="2" t="s">
         <v>773</v>
       </c>
@@ -58571,7 +58585,7 @@
       <c r="AH555" s="4"/>
       <c r="AI555" s="4"/>
     </row>
-    <row r="556" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A556" s="2" t="s">
         <v>774</v>
       </c>
@@ -58632,7 +58646,7 @@
       <c r="AH556" s="4"/>
       <c r="AI556" s="4"/>
     </row>
-    <row r="557" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A557" s="2" t="s">
         <v>777</v>
       </c>
@@ -58693,7 +58707,7 @@
       <c r="AH557" s="4"/>
       <c r="AI557" s="4"/>
     </row>
-    <row r="558" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A558" s="2" t="s">
         <v>778</v>
       </c>
@@ -58754,7 +58768,7 @@
       <c r="AH558" s="4"/>
       <c r="AI558" s="4"/>
     </row>
-    <row r="559" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A559" s="2" t="s">
         <v>781</v>
       </c>
@@ -58815,7 +58829,7 @@
       <c r="AH559" s="4"/>
       <c r="AI559" s="4"/>
     </row>
-    <row r="560" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A560" s="2" t="s">
         <v>782</v>
       </c>
@@ -58876,7 +58890,7 @@
       <c r="AH560" s="4"/>
       <c r="AI560" s="4"/>
     </row>
-    <row r="561" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A561" s="2" t="s">
         <v>784</v>
       </c>
@@ -58937,7 +58951,7 @@
       <c r="AH561" s="4"/>
       <c r="AI561" s="4"/>
     </row>
-    <row r="562" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A562" s="2" t="s">
         <v>787</v>
       </c>
@@ -58998,7 +59012,7 @@
       <c r="AH562" s="4"/>
       <c r="AI562" s="4"/>
     </row>
-    <row r="563" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A563" s="2" t="s">
         <v>788</v>
       </c>
@@ -59059,7 +59073,7 @@
       <c r="AH563" s="4"/>
       <c r="AI563" s="4"/>
     </row>
-    <row r="564" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A564" s="2" t="s">
         <v>791</v>
       </c>
@@ -59120,7 +59134,7 @@
       <c r="AH564" s="4"/>
       <c r="AI564" s="4"/>
     </row>
-    <row r="565" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A565" s="2" t="s">
         <v>792</v>
       </c>
@@ -59181,7 +59195,7 @@
       <c r="AH565" s="4"/>
       <c r="AI565" s="4"/>
     </row>
-    <row r="566" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A566" s="2" t="s">
         <v>796</v>
       </c>
@@ -59242,7 +59256,7 @@
       <c r="AH566" s="4"/>
       <c r="AI566" s="4"/>
     </row>
-    <row r="567" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A567" s="2" t="s">
         <v>799</v>
       </c>
@@ -59303,7 +59317,7 @@
       <c r="AH567" s="4"/>
       <c r="AI567" s="4"/>
     </row>
-    <row r="568" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A568" s="2" t="s">
         <v>805</v>
       </c>
@@ -59364,7 +59378,7 @@
       <c r="AH568" s="4"/>
       <c r="AI568" s="4"/>
     </row>
-    <row r="569" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A569" s="2" t="s">
         <v>806</v>
       </c>
@@ -59425,7 +59439,7 @@
       <c r="AH569" s="4"/>
       <c r="AI569" s="4"/>
     </row>
-    <row r="570" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A570" s="2" t="s">
         <v>808</v>
       </c>
@@ -59486,7 +59500,7 @@
       <c r="AH570" s="4"/>
       <c r="AI570" s="4"/>
     </row>
-    <row r="571" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A571" s="2" t="s">
         <v>810</v>
       </c>
@@ -59547,7 +59561,7 @@
       <c r="AH571" s="4"/>
       <c r="AI571" s="4"/>
     </row>
-    <row r="572" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A572" s="2" t="s">
         <v>812</v>
       </c>
@@ -59608,7 +59622,7 @@
       <c r="AH572" s="4"/>
       <c r="AI572" s="4"/>
     </row>
-    <row r="573" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A573" s="2" t="s">
         <v>815</v>
       </c>
@@ -59669,7 +59683,7 @@
       <c r="AH573" s="4"/>
       <c r="AI573" s="4"/>
     </row>
-    <row r="574" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A574" s="2" t="s">
         <v>816</v>
       </c>
@@ -59730,7 +59744,7 @@
       <c r="AH574" s="4"/>
       <c r="AI574" s="4"/>
     </row>
-    <row r="575" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A575" s="2" t="s">
         <v>817</v>
       </c>
@@ -59791,7 +59805,7 @@
       <c r="AH575" s="4"/>
       <c r="AI575" s="4"/>
     </row>
-    <row r="576" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A576" s="2" t="s">
         <v>820</v>
       </c>
@@ -59852,7 +59866,7 @@
       <c r="AH576" s="4"/>
       <c r="AI576" s="4"/>
     </row>
-    <row r="577" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A577" s="2" t="s">
         <v>821</v>
       </c>
@@ -59913,7 +59927,7 @@
       <c r="AH577" s="4"/>
       <c r="AI577" s="4"/>
     </row>
-    <row r="578" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A578" s="2" t="s">
         <v>822</v>
       </c>
@@ -59974,7 +59988,7 @@
       <c r="AH578" s="4"/>
       <c r="AI578" s="4"/>
     </row>
-    <row r="579" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A579" s="2" t="s">
         <v>825</v>
       </c>
@@ -60035,7 +60049,7 @@
       <c r="AH579" s="4"/>
       <c r="AI579" s="4"/>
     </row>
-    <row r="580" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A580" s="2" t="s">
         <v>826</v>
       </c>
@@ -60096,7 +60110,7 @@
       <c r="AH580" s="4"/>
       <c r="AI580" s="4"/>
     </row>
-    <row r="581" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A581" s="2" t="s">
         <v>827</v>
       </c>
@@ -60157,7 +60171,7 @@
       <c r="AH581" s="4"/>
       <c r="AI581" s="4"/>
     </row>
-    <row r="582" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A582" s="2" t="s">
         <v>830</v>
       </c>
@@ -60218,7 +60232,7 @@
       <c r="AH582" s="4"/>
       <c r="AI582" s="4"/>
     </row>
-    <row r="583" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A583" s="2" t="s">
         <v>831</v>
       </c>
@@ -60279,7 +60293,7 @@
       <c r="AH583" s="4"/>
       <c r="AI583" s="4"/>
     </row>
-    <row r="584" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A584" s="2" t="s">
         <v>832</v>
       </c>
@@ -60340,7 +60354,7 @@
       <c r="AH584" s="4"/>
       <c r="AI584" s="4"/>
     </row>
-    <row r="585" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A585" s="2" t="s">
         <v>836</v>
       </c>
@@ -60401,7 +60415,7 @@
       <c r="AH585" s="4"/>
       <c r="AI585" s="4"/>
     </row>
-    <row r="586" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A586" s="2" t="s">
         <v>837</v>
       </c>
@@ -60462,7 +60476,7 @@
       <c r="AH586" s="4"/>
       <c r="AI586" s="4"/>
     </row>
-    <row r="587" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A587" s="2" t="s">
         <v>838</v>
       </c>
@@ -60523,7 +60537,7 @@
       <c r="AH587" s="4"/>
       <c r="AI587" s="4"/>
     </row>
-    <row r="588" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A588" s="2" t="s">
         <v>841</v>
       </c>
@@ -60584,7 +60598,7 @@
       <c r="AH588" s="4"/>
       <c r="AI588" s="4"/>
     </row>
-    <row r="589" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A589" s="2" t="s">
         <v>842</v>
       </c>
@@ -60645,7 +60659,7 @@
       <c r="AH589" s="4"/>
       <c r="AI589" s="4"/>
     </row>
-    <row r="590" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A590" s="2" t="s">
         <v>843</v>
       </c>
@@ -60706,7 +60720,7 @@
       <c r="AH590" s="4"/>
       <c r="AI590" s="4"/>
     </row>
-    <row r="591" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A591" s="2" t="s">
         <v>846</v>
       </c>
@@ -60767,7 +60781,7 @@
       <c r="AH591" s="4"/>
       <c r="AI591" s="4"/>
     </row>
-    <row r="592" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A592" s="2" t="s">
         <v>847</v>
       </c>
@@ -60828,7 +60842,7 @@
       <c r="AH592" s="4"/>
       <c r="AI592" s="4"/>
     </row>
-    <row r="593" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A593" s="2" t="s">
         <v>848</v>
       </c>
@@ -60889,7 +60903,7 @@
       <c r="AH593" s="4"/>
       <c r="AI593" s="4"/>
     </row>
-    <row r="594" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A594" s="2" t="s">
         <v>851</v>
       </c>
@@ -60950,7 +60964,7 @@
       <c r="AH594" s="4"/>
       <c r="AI594" s="4"/>
     </row>
-    <row r="595" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A595" s="2" t="s">
         <v>852</v>
       </c>
@@ -61011,7 +61025,7 @@
       <c r="AH595" s="4"/>
       <c r="AI595" s="4"/>
     </row>
-    <row r="596" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A596" s="2" t="s">
         <v>853</v>
       </c>
@@ -61072,7 +61086,7 @@
       <c r="AH596" s="4"/>
       <c r="AI596" s="4"/>
     </row>
-    <row r="597" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A597" s="2" t="s">
         <v>854</v>
       </c>
@@ -61133,7 +61147,7 @@
       <c r="AH597" s="4"/>
       <c r="AI597" s="4"/>
     </row>
-    <row r="598" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A598" s="2" t="s">
         <v>858</v>
       </c>
@@ -61194,7 +61208,7 @@
       <c r="AH598" s="4"/>
       <c r="AI598" s="4"/>
     </row>
-    <row r="599" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A599" s="2" t="s">
         <v>859</v>
       </c>
@@ -61255,7 +61269,7 @@
       <c r="AH599" s="4"/>
       <c r="AI599" s="4"/>
     </row>
-    <row r="600" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A600" s="2" t="s">
         <v>860</v>
       </c>
@@ -61316,7 +61330,7 @@
       <c r="AH600" s="4"/>
       <c r="AI600" s="4"/>
     </row>
-    <row r="601" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A601" s="2" t="s">
         <v>861</v>
       </c>
@@ -61377,7 +61391,7 @@
       <c r="AH601" s="4"/>
       <c r="AI601" s="4"/>
     </row>
-    <row r="602" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A602" s="2" t="s">
         <v>862</v>
       </c>
@@ -61438,7 +61452,7 @@
       <c r="AH602" s="4"/>
       <c r="AI602" s="4"/>
     </row>
-    <row r="603" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A603" s="2" t="s">
         <v>865</v>
       </c>
@@ -61499,7 +61513,7 @@
       <c r="AH603" s="4"/>
       <c r="AI603" s="4"/>
     </row>
-    <row r="604" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A604" s="2" t="s">
         <v>866</v>
       </c>
@@ -61560,7 +61574,7 @@
       <c r="AH604" s="4"/>
       <c r="AI604" s="4"/>
     </row>
-    <row r="605" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A605" s="2" t="s">
         <v>867</v>
       </c>
@@ -61621,7 +61635,7 @@
       <c r="AH605" s="4"/>
       <c r="AI605" s="4"/>
     </row>
-    <row r="606" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A606" s="2" t="s">
         <v>870</v>
       </c>
@@ -61682,7 +61696,7 @@
       <c r="AH606" s="4"/>
       <c r="AI606" s="4"/>
     </row>
-    <row r="607" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A607" s="2" t="s">
         <v>871</v>
       </c>
@@ -61743,7 +61757,7 @@
       <c r="AH607" s="4"/>
       <c r="AI607" s="4"/>
     </row>
-    <row r="608" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A608" s="2" t="s">
         <v>872</v>
       </c>
@@ -61804,7 +61818,7 @@
       <c r="AH608" s="4"/>
       <c r="AI608" s="4"/>
     </row>
-    <row r="609" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A609" s="2" t="s">
         <v>875</v>
       </c>
@@ -61865,7 +61879,7 @@
       <c r="AH609" s="4"/>
       <c r="AI609" s="4"/>
     </row>
-    <row r="610" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A610" s="2" t="s">
         <v>876</v>
       </c>
@@ -61926,7 +61940,7 @@
       <c r="AH610" s="4"/>
       <c r="AI610" s="4"/>
     </row>
-    <row r="611" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A611" s="2" t="s">
         <v>877</v>
       </c>
@@ -61987,7 +62001,7 @@
       <c r="AH611" s="4"/>
       <c r="AI611" s="4"/>
     </row>
-    <row r="612" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A612" s="2" t="s">
         <v>880</v>
       </c>
@@ -62048,7 +62062,7 @@
       <c r="AH612" s="4"/>
       <c r="AI612" s="4"/>
     </row>
-    <row r="613" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A613" s="2" t="s">
         <v>881</v>
       </c>
@@ -62109,7 +62123,7 @@
       <c r="AH613" s="4"/>
       <c r="AI613" s="4"/>
     </row>
-    <row r="614" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A614" s="2" t="s">
         <v>882</v>
       </c>
@@ -62170,7 +62184,7 @@
       <c r="AH614" s="4"/>
       <c r="AI614" s="4"/>
     </row>
-    <row r="615" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A615" s="2" t="s">
         <v>885</v>
       </c>
@@ -62231,7 +62245,7 @@
       <c r="AH615" s="4"/>
       <c r="AI615" s="4"/>
     </row>
-    <row r="616" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A616" s="2" t="s">
         <v>886</v>
       </c>
@@ -62292,7 +62306,7 @@
       <c r="AH616" s="4"/>
       <c r="AI616" s="4"/>
     </row>
-    <row r="617" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A617" s="2" t="s">
         <v>887</v>
       </c>
@@ -62353,7 +62367,7 @@
       <c r="AH617" s="4"/>
       <c r="AI617" s="4"/>
     </row>
-    <row r="618" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A618" s="2" t="s">
         <v>890</v>
       </c>
@@ -62414,7 +62428,7 @@
       <c r="AH618" s="4"/>
       <c r="AI618" s="4"/>
     </row>
-    <row r="619" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A619" s="2" t="s">
         <v>891</v>
       </c>
@@ -62475,7 +62489,7 @@
       <c r="AH619" s="4"/>
       <c r="AI619" s="4"/>
     </row>
-    <row r="620" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A620" s="2" t="s">
         <v>892</v>
       </c>
@@ -62536,7 +62550,7 @@
       <c r="AH620" s="4"/>
       <c r="AI620" s="4"/>
     </row>
-    <row r="621" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A621" s="2" t="s">
         <v>895</v>
       </c>
@@ -62597,7 +62611,7 @@
       <c r="AH621" s="4"/>
       <c r="AI621" s="4"/>
     </row>
-    <row r="622" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A622" s="2" t="s">
         <v>896</v>
       </c>
@@ -62658,7 +62672,7 @@
       <c r="AH622" s="4"/>
       <c r="AI622" s="4"/>
     </row>
-    <row r="623" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A623" s="2" t="s">
         <v>897</v>
       </c>
@@ -62719,7 +62733,7 @@
       <c r="AH623" s="4"/>
       <c r="AI623" s="4"/>
     </row>
-    <row r="624" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A624" s="2" t="s">
         <v>900</v>
       </c>
@@ -62780,7 +62794,7 @@
       <c r="AH624" s="4"/>
       <c r="AI624" s="4"/>
     </row>
-    <row r="625" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A625" s="2" t="s">
         <v>901</v>
       </c>
@@ -62841,7 +62855,7 @@
       <c r="AH625" s="4"/>
       <c r="AI625" s="4"/>
     </row>
-    <row r="626" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A626" s="2" t="s">
         <v>902</v>
       </c>
@@ -62902,7 +62916,7 @@
       <c r="AH626" s="4"/>
       <c r="AI626" s="4"/>
     </row>
-    <row r="627" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A627" s="2" t="s">
         <v>903</v>
       </c>
@@ -62963,7 +62977,7 @@
       <c r="AH627" s="4"/>
       <c r="AI627" s="4"/>
     </row>
-    <row r="628" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A628" s="2" t="s">
         <v>906</v>
       </c>
@@ -63024,7 +63038,7 @@
       <c r="AH628" s="4"/>
       <c r="AI628" s="4"/>
     </row>
-    <row r="629" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A629" s="2" t="s">
         <v>908</v>
       </c>
@@ -63085,7 +63099,7 @@
       <c r="AH629" s="4"/>
       <c r="AI629" s="4"/>
     </row>
-    <row r="630" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A630" s="2" t="s">
         <v>910</v>
       </c>
@@ -63146,7 +63160,7 @@
       <c r="AH630" s="4"/>
       <c r="AI630" s="4"/>
     </row>
-    <row r="631" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A631" s="2" t="s">
         <v>912</v>
       </c>
@@ -63207,7 +63221,7 @@
       <c r="AH631" s="4"/>
       <c r="AI631" s="4"/>
     </row>
-    <row r="632" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A632" s="2" t="s">
         <v>916</v>
       </c>
@@ -63268,7 +63282,7 @@
       <c r="AH632" s="4"/>
       <c r="AI632" s="4"/>
     </row>
-    <row r="633" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A633" s="2" t="s">
         <v>918</v>
       </c>
@@ -63329,7 +63343,7 @@
       <c r="AH633" s="4"/>
       <c r="AI633" s="4"/>
     </row>
-    <row r="634" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A634" s="2" t="s">
         <v>920</v>
       </c>
@@ -63390,7 +63404,7 @@
       <c r="AH634" s="4"/>
       <c r="AI634" s="4"/>
     </row>
-    <row r="635" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A635" s="2" t="s">
         <v>922</v>
       </c>
@@ -63451,7 +63465,7 @@
       <c r="AH635" s="4"/>
       <c r="AI635" s="4"/>
     </row>
-    <row r="636" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A636" s="2" t="s">
         <v>924</v>
       </c>
@@ -63512,7 +63526,7 @@
       <c r="AH636" s="4"/>
       <c r="AI636" s="4"/>
     </row>
-    <row r="637" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A637" s="2" t="s">
         <v>927</v>
       </c>
@@ -63573,7 +63587,7 @@
       <c r="AH637" s="4"/>
       <c r="AI637" s="4"/>
     </row>
-    <row r="638" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A638" s="2" t="s">
         <v>928</v>
       </c>
@@ -63634,7 +63648,7 @@
       <c r="AH638" s="4"/>
       <c r="AI638" s="4"/>
     </row>
-    <row r="639" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A639" s="2" t="s">
         <v>929</v>
       </c>
@@ -63695,7 +63709,7 @@
       <c r="AH639" s="4"/>
       <c r="AI639" s="4"/>
     </row>
-    <row r="640" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A640" s="2" t="s">
         <v>930</v>
       </c>
@@ -63756,7 +63770,7 @@
       <c r="AH640" s="4"/>
       <c r="AI640" s="4"/>
     </row>
-    <row r="641" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A641" s="2" t="s">
         <v>931</v>
       </c>
@@ -63817,7 +63831,7 @@
       <c r="AH641" s="4"/>
       <c r="AI641" s="4"/>
     </row>
-    <row r="642" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A642" s="2" t="s">
         <v>934</v>
       </c>
@@ -63878,7 +63892,7 @@
       <c r="AH642" s="4"/>
       <c r="AI642" s="4"/>
     </row>
-    <row r="643" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A643" s="2" t="s">
         <v>938</v>
       </c>
@@ -63939,7 +63953,7 @@
       <c r="AH643" s="4"/>
       <c r="AI643" s="4"/>
     </row>
-    <row r="644" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A644" s="2" t="s">
         <v>939</v>
       </c>
@@ -64000,7 +64014,7 @@
       <c r="AH644" s="4"/>
       <c r="AI644" s="4"/>
     </row>
-    <row r="645" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A645" s="2" t="s">
         <v>942</v>
       </c>
@@ -64061,7 +64075,7 @@
       <c r="AH645" s="4"/>
       <c r="AI645" s="4"/>
     </row>
-    <row r="646" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A646" s="2" t="s">
         <v>943</v>
       </c>
@@ -64122,7 +64136,7 @@
       <c r="AH646" s="4"/>
       <c r="AI646" s="4"/>
     </row>
-    <row r="647" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A647" s="2" t="s">
         <v>946</v>
       </c>
@@ -64183,7 +64197,7 @@
       <c r="AH647" s="4"/>
       <c r="AI647" s="4"/>
     </row>
-    <row r="648" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A648" s="2" t="s">
         <v>949</v>
       </c>
@@ -64244,7 +64258,7 @@
       <c r="AH648" s="4"/>
       <c r="AI648" s="4"/>
     </row>
-    <row r="649" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A649" s="2" t="s">
         <v>951</v>
       </c>
@@ -64305,7 +64319,7 @@
       <c r="AH649" s="4"/>
       <c r="AI649" s="4"/>
     </row>
-    <row r="650" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A650" s="2" t="s">
         <v>954</v>
       </c>
@@ -64366,7 +64380,7 @@
       <c r="AH650" s="4"/>
       <c r="AI650" s="4"/>
     </row>
-    <row r="651" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A651" s="2" t="s">
         <v>957</v>
       </c>
@@ -64427,7 +64441,7 @@
       <c r="AH651" s="4"/>
       <c r="AI651" s="4"/>
     </row>
-    <row r="652" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A652" s="2" t="s">
         <v>960</v>
       </c>
@@ -64488,7 +64502,7 @@
       <c r="AH652" s="4"/>
       <c r="AI652" s="4"/>
     </row>
-    <row r="653" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A653" s="2" t="s">
         <v>961</v>
       </c>
@@ -64549,7 +64563,7 @@
       <c r="AH653" s="4"/>
       <c r="AI653" s="4"/>
     </row>
-    <row r="654" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A654" s="2" t="s">
         <v>962</v>
       </c>
@@ -64610,7 +64624,7 @@
       <c r="AH654" s="4"/>
       <c r="AI654" s="4"/>
     </row>
-    <row r="655" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A655" s="2" t="s">
         <v>965</v>
       </c>
@@ -64671,7 +64685,7 @@
       <c r="AH655" s="4"/>
       <c r="AI655" s="4"/>
     </row>
-    <row r="656" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A656" s="2" t="s">
         <v>967</v>
       </c>
@@ -64732,7 +64746,7 @@
       <c r="AH656" s="4"/>
       <c r="AI656" s="4"/>
     </row>
-    <row r="657" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A657" s="2" t="s">
         <v>968</v>
       </c>
@@ -64793,7 +64807,7 @@
       <c r="AH657" s="4"/>
       <c r="AI657" s="4"/>
     </row>
-    <row r="658" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A658" s="2" t="s">
         <v>969</v>
       </c>
@@ -64854,7 +64868,7 @@
       <c r="AH658" s="4"/>
       <c r="AI658" s="4"/>
     </row>
-    <row r="659" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A659" s="2" t="s">
         <v>970</v>
       </c>
@@ -64915,7 +64929,7 @@
       <c r="AH659" s="4"/>
       <c r="AI659" s="4"/>
     </row>
-    <row r="660" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A660" s="2" t="s">
         <v>973</v>
       </c>
@@ -64976,7 +64990,7 @@
       <c r="AH660" s="4"/>
       <c r="AI660" s="4"/>
     </row>
-    <row r="661" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A661" s="2" t="s">
         <v>974</v>
       </c>
@@ -65037,7 +65051,7 @@
       <c r="AH661" s="4"/>
       <c r="AI661" s="4"/>
     </row>
-    <row r="662" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A662" s="2" t="s">
         <v>976</v>
       </c>
@@ -65098,7 +65112,7 @@
       <c r="AH662" s="4"/>
       <c r="AI662" s="4"/>
     </row>
-    <row r="663" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A663" s="2" t="s">
         <v>977</v>
       </c>
@@ -65159,7 +65173,7 @@
       <c r="AH663" s="4"/>
       <c r="AI663" s="4"/>
     </row>
-    <row r="664" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A664" s="2" t="s">
         <v>978</v>
       </c>
@@ -65220,7 +65234,7 @@
       <c r="AH664" s="4"/>
       <c r="AI664" s="4"/>
     </row>
-    <row r="665" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A665" s="2" t="s">
         <v>981</v>
       </c>
@@ -65281,7 +65295,7 @@
       <c r="AH665" s="4"/>
       <c r="AI665" s="4"/>
     </row>
-    <row r="666" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A666" s="2" t="s">
         <v>983</v>
       </c>
@@ -65342,7 +65356,7 @@
       <c r="AH666" s="4"/>
       <c r="AI666" s="4"/>
     </row>
-    <row r="667" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="667" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A667" s="2" t="s">
         <v>985</v>
       </c>
@@ -65403,7 +65417,7 @@
       <c r="AH667" s="4"/>
       <c r="AI667" s="4"/>
     </row>
-    <row r="668" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A668" s="2" t="s">
         <v>988</v>
       </c>
@@ -65464,7 +65478,7 @@
       <c r="AH668" s="4"/>
       <c r="AI668" s="4"/>
     </row>
-    <row r="669" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A669" s="2" t="s">
         <v>991</v>
       </c>
@@ -65525,7 +65539,7 @@
       <c r="AH669" s="4"/>
       <c r="AI669" s="4"/>
     </row>
-    <row r="670" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="670" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A670" s="2" t="s">
         <v>994</v>
       </c>
@@ -65586,7 +65600,7 @@
       <c r="AH670" s="4"/>
       <c r="AI670" s="4"/>
     </row>
-    <row r="671" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A671" s="2" t="s">
         <v>995</v>
       </c>
@@ -65647,7 +65661,7 @@
       <c r="AH671" s="4"/>
       <c r="AI671" s="4"/>
     </row>
-    <row r="672" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="672" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A672" s="2" t="s">
         <v>998</v>
       </c>
@@ -65708,7 +65722,7 @@
       <c r="AH672" s="4"/>
       <c r="AI672" s="4"/>
     </row>
-    <row r="673" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A673" s="2" t="s">
         <v>999</v>
       </c>
@@ -65769,7 +65783,7 @@
       <c r="AH673" s="4"/>
       <c r="AI673" s="4"/>
     </row>
-    <row r="674" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A674" s="2" t="s">
         <v>1000</v>
       </c>
@@ -65830,7 +65844,7 @@
       <c r="AH674" s="4"/>
       <c r="AI674" s="4"/>
     </row>
-    <row r="675" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="675" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A675" s="2" t="s">
         <v>1001</v>
       </c>
@@ -65891,7 +65905,7 @@
       <c r="AH675" s="4"/>
       <c r="AI675" s="4"/>
     </row>
-    <row r="676" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="676" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A676" s="2" t="s">
         <v>1004</v>
       </c>
@@ -65952,7 +65966,7 @@
       <c r="AH676" s="4"/>
       <c r="AI676" s="4"/>
     </row>
-    <row r="677" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A677" s="2" t="s">
         <v>1005</v>
       </c>
@@ -66013,7 +66027,7 @@
       <c r="AH677" s="4"/>
       <c r="AI677" s="4"/>
     </row>
-    <row r="678" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="678" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A678" s="2" t="s">
         <v>1006</v>
       </c>
@@ -66074,7 +66088,7 @@
       <c r="AH678" s="4"/>
       <c r="AI678" s="4"/>
     </row>
-    <row r="679" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A679" s="2" t="s">
         <v>1007</v>
       </c>
@@ -66135,7 +66149,7 @@
       <c r="AH679" s="4"/>
       <c r="AI679" s="4"/>
     </row>
-    <row r="680" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="680" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A680" s="2" t="s">
         <v>1010</v>
       </c>
@@ -66196,7 +66210,7 @@
       <c r="AH680" s="4"/>
       <c r="AI680" s="4"/>
     </row>
-    <row r="681" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="681" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A681" s="2" t="s">
         <v>1013</v>
       </c>
@@ -66257,7 +66271,7 @@
       <c r="AH681" s="4"/>
       <c r="AI681" s="4"/>
     </row>
-    <row r="682" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="682" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A682" s="2" t="s">
         <v>1014</v>
       </c>
@@ -66318,7 +66332,7 @@
       <c r="AH682" s="4"/>
       <c r="AI682" s="4"/>
     </row>
-    <row r="683" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="683" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A683" s="2" t="s">
         <v>1015</v>
       </c>
@@ -66379,7 +66393,7 @@
       <c r="AH683" s="4"/>
       <c r="AI683" s="4"/>
     </row>
-    <row r="684" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="684" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A684" s="2" t="s">
         <v>1016</v>
       </c>
@@ -66440,7 +66454,7 @@
       <c r="AH684" s="4"/>
       <c r="AI684" s="4"/>
     </row>
-    <row r="685" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="685" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A685" s="2" t="s">
         <v>1017</v>
       </c>
@@ -66501,7 +66515,7 @@
       <c r="AH685" s="4"/>
       <c r="AI685" s="4"/>
     </row>
-    <row r="686" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="686" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A686" s="2" t="s">
         <v>1020</v>
       </c>
@@ -66562,7 +66576,7 @@
       <c r="AH686" s="4"/>
       <c r="AI686" s="4"/>
     </row>
-    <row r="687" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="687" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A687" s="2" t="s">
         <v>1021</v>
       </c>
@@ -66623,7 +66637,7 @@
       <c r="AH687" s="4"/>
       <c r="AI687" s="4"/>
     </row>
-    <row r="688" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="688" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A688" s="2" t="s">
         <v>1024</v>
       </c>
@@ -66684,7 +66698,7 @@
       <c r="AH688" s="4"/>
       <c r="AI688" s="4"/>
     </row>
-    <row r="689" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A689" s="2" t="s">
         <v>1025</v>
       </c>
@@ -66745,7 +66759,7 @@
       <c r="AH689" s="4"/>
       <c r="AI689" s="4"/>
     </row>
-    <row r="690" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A690" s="2" t="s">
         <v>1027</v>
       </c>
@@ -66806,7 +66820,7 @@
       <c r="AH690" s="4"/>
       <c r="AI690" s="4"/>
     </row>
-    <row r="691" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A691" s="2" t="s">
         <v>1032</v>
       </c>
@@ -66867,7 +66881,7 @@
       <c r="AH691" s="4"/>
       <c r="AI691" s="4"/>
     </row>
-    <row r="692" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="692" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A692" s="2" t="s">
         <v>1034</v>
       </c>
@@ -66928,7 +66942,7 @@
       <c r="AH692" s="4"/>
       <c r="AI692" s="4"/>
     </row>
-    <row r="693" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A693" s="2" t="s">
         <v>1038</v>
       </c>
@@ -66989,7 +67003,7 @@
       <c r="AH693" s="4"/>
       <c r="AI693" s="4"/>
     </row>
-    <row r="694" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="694" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A694" s="2" t="s">
         <v>1039</v>
       </c>
@@ -67050,7 +67064,7 @@
       <c r="AH694" s="4"/>
       <c r="AI694" s="4"/>
     </row>
-    <row r="695" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="695" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A695" s="2" t="s">
         <v>1041</v>
       </c>
@@ -67111,7 +67125,7 @@
       <c r="AH695" s="4"/>
       <c r="AI695" s="4"/>
     </row>
-    <row r="696" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="696" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A696" s="2" t="s">
         <v>1044</v>
       </c>
@@ -67172,7 +67186,7 @@
       <c r="AH696" s="4"/>
       <c r="AI696" s="4"/>
     </row>
-    <row r="697" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="697" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A697" s="2" t="s">
         <v>1045</v>
       </c>
@@ -67233,7 +67247,7 @@
       <c r="AH697" s="4"/>
       <c r="AI697" s="4"/>
     </row>
-    <row r="698" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="698" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A698" s="2" t="s">
         <v>1046</v>
       </c>
@@ -67294,7 +67308,7 @@
       <c r="AH698" s="4"/>
       <c r="AI698" s="4"/>
     </row>
-    <row r="699" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="699" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A699" s="2" t="s">
         <v>1048</v>
       </c>
@@ -67355,7 +67369,7 @@
       <c r="AH699" s="4"/>
       <c r="AI699" s="4"/>
     </row>
-    <row r="700" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="700" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A700" s="2" t="s">
         <v>1052</v>
       </c>
@@ -67416,7 +67430,7 @@
       <c r="AH700" s="4"/>
       <c r="AI700" s="4"/>
     </row>
-    <row r="701" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="701" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A701" s="2" t="s">
         <v>1054</v>
       </c>
@@ -67477,7 +67491,7 @@
       <c r="AH701" s="4"/>
       <c r="AI701" s="4"/>
     </row>
-    <row r="702" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="702" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A702" s="2" t="s">
         <v>1057</v>
       </c>
@@ -67538,7 +67552,7 @@
       <c r="AH702" s="4"/>
       <c r="AI702" s="4"/>
     </row>
-    <row r="703" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="703" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A703" s="2" t="s">
         <v>1058</v>
       </c>
@@ -67599,7 +67613,7 @@
       <c r="AH703" s="4"/>
       <c r="AI703" s="4"/>
     </row>
-    <row r="704" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="704" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A704" s="2" t="s">
         <v>1061</v>
       </c>
@@ -67660,7 +67674,7 @@
       <c r="AH704" s="4"/>
       <c r="AI704" s="4"/>
     </row>
-    <row r="705" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="705" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A705" s="2" t="s">
         <v>1062</v>
       </c>
@@ -67721,7 +67735,7 @@
       <c r="AH705" s="4"/>
       <c r="AI705" s="4"/>
     </row>
-    <row r="706" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="706" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A706" s="2" t="s">
         <v>1063</v>
       </c>
@@ -67782,7 +67796,7 @@
       <c r="AH706" s="4"/>
       <c r="AI706" s="4"/>
     </row>
-    <row r="707" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="707" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A707" s="2" t="s">
         <v>1065</v>
       </c>
@@ -67843,7 +67857,7 @@
       <c r="AH707" s="4"/>
       <c r="AI707" s="4"/>
     </row>
-    <row r="708" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="708" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A708" s="2" t="s">
         <v>1066</v>
       </c>
@@ -67904,7 +67918,7 @@
       <c r="AH708" s="4"/>
       <c r="AI708" s="4"/>
     </row>
-    <row r="709" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="709" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A709" s="2" t="s">
         <v>1067</v>
       </c>
@@ -67965,7 +67979,7 @@
       <c r="AH709" s="4"/>
       <c r="AI709" s="4"/>
     </row>
-    <row r="710" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="710" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A710" s="2" t="s">
         <v>1071</v>
       </c>
@@ -68026,7 +68040,7 @@
       <c r="AH710" s="4"/>
       <c r="AI710" s="4"/>
     </row>
-    <row r="711" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="711" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A711" s="2" t="s">
         <v>1073</v>
       </c>
@@ -68087,7 +68101,7 @@
       <c r="AH711" s="4"/>
       <c r="AI711" s="4"/>
     </row>
-    <row r="712" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="712" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A712" s="2" t="s">
         <v>1075</v>
       </c>
@@ -68148,7 +68162,7 @@
       <c r="AH712" s="4"/>
       <c r="AI712" s="4"/>
     </row>
-    <row r="713" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="713" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A713" s="2" t="s">
         <v>1076</v>
       </c>
@@ -68209,7 +68223,7 @@
       <c r="AH713" s="4"/>
       <c r="AI713" s="4"/>
     </row>
-    <row r="714" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="714" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A714" s="2" t="s">
         <v>1079</v>
       </c>
@@ -68270,7 +68284,7 @@
       <c r="AH714" s="4"/>
       <c r="AI714" s="4"/>
     </row>
-    <row r="715" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="715" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A715" s="2" t="s">
         <v>1082</v>
       </c>
@@ -68331,7 +68345,7 @@
       <c r="AH715" s="4"/>
       <c r="AI715" s="4"/>
     </row>
-    <row r="716" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="716" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A716" s="2" t="s">
         <v>1083</v>
       </c>
@@ -68392,7 +68406,7 @@
       <c r="AH716" s="4"/>
       <c r="AI716" s="4"/>
     </row>
-    <row r="717" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="717" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A717" s="2" t="s">
         <v>1086</v>
       </c>
@@ -68453,7 +68467,7 @@
       <c r="AH717" s="4"/>
       <c r="AI717" s="4"/>
     </row>
-    <row r="718" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="718" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A718" s="2" t="s">
         <v>1090</v>
       </c>
@@ -68514,7 +68528,7 @@
       <c r="AH718" s="4"/>
       <c r="AI718" s="4"/>
     </row>
-    <row r="719" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="719" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A719" s="2" t="s">
         <v>1091</v>
       </c>
@@ -68575,7 +68589,7 @@
       <c r="AH719" s="4"/>
       <c r="AI719" s="4"/>
     </row>
-    <row r="720" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="720" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A720" s="2" t="s">
         <v>1092</v>
       </c>
@@ -68636,7 +68650,7 @@
       <c r="AH720" s="4"/>
       <c r="AI720" s="4"/>
     </row>
-    <row r="721" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="721" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A721" s="2" t="s">
         <v>1094</v>
       </c>
@@ -68697,7 +68711,7 @@
       <c r="AH721" s="4"/>
       <c r="AI721" s="4"/>
     </row>
-    <row r="722" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="722" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A722" s="2" t="s">
         <v>1097</v>
       </c>
@@ -68758,7 +68772,7 @@
       <c r="AH722" s="4"/>
       <c r="AI722" s="4"/>
     </row>
-    <row r="723" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="723" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A723" s="2" t="s">
         <v>1098</v>
       </c>
@@ -68819,7 +68833,7 @@
       <c r="AH723" s="4"/>
       <c r="AI723" s="4"/>
     </row>
-    <row r="724" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="724" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A724" s="2" t="s">
         <v>1099</v>
       </c>
@@ -68880,7 +68894,7 @@
       <c r="AH724" s="4"/>
       <c r="AI724" s="4"/>
     </row>
-    <row r="725" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="725" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A725" s="2" t="s">
         <v>1101</v>
       </c>
@@ -68941,7 +68955,7 @@
       <c r="AH725" s="4"/>
       <c r="AI725" s="4"/>
     </row>
-    <row r="726" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="726" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A726" s="2" t="s">
         <v>1102</v>
       </c>
@@ -69002,7 +69016,7 @@
       <c r="AH726" s="4"/>
       <c r="AI726" s="4"/>
     </row>
-    <row r="727" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="727" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A727" s="2" t="s">
         <v>1103</v>
       </c>
@@ -69063,7 +69077,7 @@
       <c r="AH727" s="4"/>
       <c r="AI727" s="4"/>
     </row>
-    <row r="728" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="728" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A728" s="2" t="s">
         <v>1104</v>
       </c>
@@ -69124,7 +69138,7 @@
       <c r="AH728" s="4"/>
       <c r="AI728" s="4"/>
     </row>
-    <row r="729" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="729" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A729" s="2" t="s">
         <v>1105</v>
       </c>
@@ -69185,7 +69199,7 @@
       <c r="AH729" s="4"/>
       <c r="AI729" s="4"/>
     </row>
-    <row r="730" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="730" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A730" s="2" t="s">
         <v>1108</v>
       </c>
@@ -69246,7 +69260,7 @@
       <c r="AH730" s="4"/>
       <c r="AI730" s="4"/>
     </row>
-    <row r="731" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="731" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A731" s="2" t="s">
         <v>1109</v>
       </c>
@@ -69307,7 +69321,7 @@
       <c r="AH731" s="4"/>
       <c r="AI731" s="4"/>
     </row>
-    <row r="732" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="732" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A732" s="2" t="s">
         <v>1110</v>
       </c>
@@ -69368,7 +69382,7 @@
       <c r="AH732" s="4"/>
       <c r="AI732" s="4"/>
     </row>
-    <row r="733" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="733" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A733" s="2" t="s">
         <v>1113</v>
       </c>
@@ -69429,7 +69443,7 @@
       <c r="AH733" s="4"/>
       <c r="AI733" s="4"/>
     </row>
-    <row r="734" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="734" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A734" s="2" t="s">
         <v>1115</v>
       </c>
@@ -69490,7 +69504,7 @@
       <c r="AH734" s="4"/>
       <c r="AI734" s="4"/>
     </row>
-    <row r="735" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="735" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A735" s="2" t="s">
         <v>1116</v>
       </c>
@@ -69551,7 +69565,7 @@
       <c r="AH735" s="4"/>
       <c r="AI735" s="4"/>
     </row>
-    <row r="736" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="736" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A736" s="2" t="s">
         <v>1119</v>
       </c>
@@ -69612,7 +69626,7 @@
       <c r="AH736" s="4"/>
       <c r="AI736" s="4"/>
     </row>
-    <row r="737" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="737" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A737" s="2" t="s">
         <v>1121</v>
       </c>
@@ -69673,7 +69687,7 @@
       <c r="AH737" s="4"/>
       <c r="AI737" s="4"/>
     </row>
-    <row r="738" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="738" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A738" s="2" t="s">
         <v>1122</v>
       </c>
@@ -69734,7 +69748,7 @@
       <c r="AH738" s="4"/>
       <c r="AI738" s="4"/>
     </row>
-    <row r="739" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="739" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A739" s="2" t="s">
         <v>1123</v>
       </c>
@@ -69795,7 +69809,7 @@
       <c r="AH739" s="4"/>
       <c r="AI739" s="4"/>
     </row>
-    <row r="740" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="740" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A740" s="2" t="s">
         <v>1126</v>
       </c>
@@ -69856,7 +69870,7 @@
       <c r="AH740" s="4"/>
       <c r="AI740" s="4"/>
     </row>
-    <row r="741" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="741" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A741" s="2" t="s">
         <v>1127</v>
       </c>
@@ -69917,7 +69931,7 @@
       <c r="AH741" s="4"/>
       <c r="AI741" s="4"/>
     </row>
-    <row r="742" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="742" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A742" s="2" t="s">
         <v>1130</v>
       </c>
@@ -69978,7 +69992,7 @@
       <c r="AH742" s="4"/>
       <c r="AI742" s="4"/>
     </row>
-    <row r="743" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="743" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A743" s="2" t="s">
         <v>1131</v>
       </c>
@@ -70039,7 +70053,7 @@
       <c r="AH743" s="4"/>
       <c r="AI743" s="4"/>
     </row>
-    <row r="744" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="744" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A744" s="2" t="s">
         <v>1134</v>
       </c>
@@ -70100,7 +70114,7 @@
       <c r="AH744" s="4"/>
       <c r="AI744" s="4"/>
     </row>
-    <row r="745" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="745" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A745" s="2" t="s">
         <v>1136</v>
       </c>
@@ -70161,7 +70175,7 @@
       <c r="AH745" s="4"/>
       <c r="AI745" s="4"/>
     </row>
-    <row r="746" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="746" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A746" s="2" t="s">
         <v>1139</v>
       </c>
@@ -70222,7 +70236,7 @@
       <c r="AH746" s="4"/>
       <c r="AI746" s="4"/>
     </row>
-    <row r="747" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="747" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A747" s="2" t="s">
         <v>1140</v>
       </c>
@@ -70283,7 +70297,7 @@
       <c r="AH747" s="4"/>
       <c r="AI747" s="4"/>
     </row>
-    <row r="748" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="748" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A748" s="2" t="s">
         <v>1143</v>
       </c>
@@ -70344,7 +70358,7 @@
       <c r="AH748" s="4"/>
       <c r="AI748" s="4"/>
     </row>
-    <row r="749" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="749" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A749" s="2" t="s">
         <v>1144</v>
       </c>
@@ -70405,7 +70419,7 @@
       <c r="AH749" s="4"/>
       <c r="AI749" s="4"/>
     </row>
-    <row r="750" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="750" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A750" s="2" t="s">
         <v>1148</v>
       </c>
@@ -70466,7 +70480,7 @@
       <c r="AH750" s="4"/>
       <c r="AI750" s="4"/>
     </row>
-    <row r="751" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="751" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A751" s="2" t="s">
         <v>1149</v>
       </c>
@@ -70527,7 +70541,7 @@
       <c r="AH751" s="4"/>
       <c r="AI751" s="4"/>
     </row>
-    <row r="752" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="752" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A752" s="2" t="s">
         <v>1150</v>
       </c>
@@ -70588,7 +70602,7 @@
       <c r="AH752" s="4"/>
       <c r="AI752" s="4"/>
     </row>
-    <row r="753" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="753" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A753" s="2" t="s">
         <v>1152</v>
       </c>
@@ -70649,7 +70663,7 @@
       <c r="AH753" s="4"/>
       <c r="AI753" s="4"/>
     </row>
-    <row r="754" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="754" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A754" s="2" t="s">
         <v>1153</v>
       </c>
@@ -70710,7 +70724,7 @@
       <c r="AH754" s="4"/>
       <c r="AI754" s="4"/>
     </row>
-    <row r="755" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="755" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A755" s="2" t="s">
         <v>1155</v>
       </c>
@@ -70771,7 +70785,7 @@
       <c r="AH755" s="4"/>
       <c r="AI755" s="4"/>
     </row>
-    <row r="756" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="756" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A756" s="2" t="s">
         <v>1156</v>
       </c>
@@ -70832,7 +70846,7 @@
       <c r="AH756" s="4"/>
       <c r="AI756" s="4"/>
     </row>
-    <row r="757" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="757" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A757" s="2" t="s">
         <v>1159</v>
       </c>
@@ -70893,7 +70907,7 @@
       <c r="AH757" s="4"/>
       <c r="AI757" s="4"/>
     </row>
-    <row r="758" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="758" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A758" s="2" t="s">
         <v>1161</v>
       </c>
@@ -70954,7 +70968,7 @@
       <c r="AH758" s="4"/>
       <c r="AI758" s="4"/>
     </row>
-    <row r="759" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="759" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A759" s="2" t="s">
         <v>1162</v>
       </c>
@@ -71015,7 +71029,7 @@
       <c r="AH759" s="4"/>
       <c r="AI759" s="4"/>
     </row>
-    <row r="760" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="760" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A760" s="2" t="s">
         <v>1165</v>
       </c>
@@ -71076,7 +71090,7 @@
       <c r="AH760" s="4"/>
       <c r="AI760" s="4"/>
     </row>
-    <row r="761" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="761" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A761" s="2" t="s">
         <v>1166</v>
       </c>
@@ -71137,7 +71151,7 @@
       <c r="AH761" s="4"/>
       <c r="AI761" s="4"/>
     </row>
-    <row r="762" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="762" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A762" s="2" t="s">
         <v>1167</v>
       </c>
@@ -71198,7 +71212,7 @@
       <c r="AH762" s="4"/>
       <c r="AI762" s="4"/>
     </row>
-    <row r="763" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="763" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A763" s="2" t="s">
         <v>1169</v>
       </c>
@@ -71259,7 +71273,7 @@
       <c r="AH763" s="4"/>
       <c r="AI763" s="4"/>
     </row>
-    <row r="764" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="764" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A764" s="2" t="s">
         <v>1170</v>
       </c>
@@ -71320,7 +71334,7 @@
       <c r="AH764" s="4"/>
       <c r="AI764" s="4"/>
     </row>
-    <row r="765" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="765" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A765" s="2" t="s">
         <v>1173</v>
       </c>
@@ -71381,7 +71395,7 @@
       <c r="AH765" s="4"/>
       <c r="AI765" s="4"/>
     </row>
-    <row r="766" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="766" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A766" s="2" t="s">
         <v>1174</v>
       </c>
@@ -71442,7 +71456,7 @@
       <c r="AH766" s="4"/>
       <c r="AI766" s="4"/>
     </row>
-    <row r="767" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="767" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A767" s="2" t="s">
         <v>1175</v>
       </c>
@@ -71503,7 +71517,7 @@
       <c r="AH767" s="4"/>
       <c r="AI767" s="4"/>
     </row>
-    <row r="768" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="768" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A768" s="2" t="s">
         <v>1177</v>
       </c>
@@ -71564,7 +71578,7 @@
       <c r="AH768" s="4"/>
       <c r="AI768" s="4"/>
     </row>
-    <row r="769" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="769" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A769" s="2" t="s">
         <v>1178</v>
       </c>
@@ -71625,7 +71639,7 @@
       <c r="AH769" s="4"/>
       <c r="AI769" s="4"/>
     </row>
-    <row r="770" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="770" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A770" s="2" t="s">
         <v>1179</v>
       </c>
@@ -71686,7 +71700,7 @@
       <c r="AH770" s="4"/>
       <c r="AI770" s="4"/>
     </row>
-    <row r="771" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="771" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A771" s="2" t="s">
         <v>1182</v>
       </c>
@@ -71747,7 +71761,7 @@
       <c r="AH771" s="4"/>
       <c r="AI771" s="4"/>
     </row>
-    <row r="772" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="772" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A772" s="2" t="s">
         <v>1183</v>
       </c>
@@ -71808,7 +71822,7 @@
       <c r="AH772" s="4"/>
       <c r="AI772" s="4"/>
     </row>
-    <row r="773" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="773" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A773" s="2" t="s">
         <v>1184</v>
       </c>
@@ -71869,7 +71883,7 @@
       <c r="AH773" s="4"/>
       <c r="AI773" s="4"/>
     </row>
-    <row r="774" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="774" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A774" s="2" t="s">
         <v>1185</v>
       </c>
@@ -71930,7 +71944,7 @@
       <c r="AH774" s="4"/>
       <c r="AI774" s="4"/>
     </row>
-    <row r="775" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="775" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A775" s="2" t="s">
         <v>1188</v>
       </c>
@@ -71991,7 +72005,7 @@
       <c r="AH775" s="4"/>
       <c r="AI775" s="4"/>
     </row>
-    <row r="776" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="776" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A776" s="2" t="s">
         <v>1189</v>
       </c>
@@ -72052,7 +72066,7 @@
       <c r="AH776" s="4"/>
       <c r="AI776" s="4"/>
     </row>
-    <row r="777" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="777" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A777" s="2" t="s">
         <v>1190</v>
       </c>
@@ -72113,7 +72127,7 @@
       <c r="AH777" s="4"/>
       <c r="AI777" s="4"/>
     </row>
-    <row r="778" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="778" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A778" s="2" t="s">
         <v>1191</v>
       </c>
@@ -72174,7 +72188,7 @@
       <c r="AH778" s="4"/>
       <c r="AI778" s="4"/>
     </row>
-    <row r="779" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="779" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A779" s="2" t="s">
         <v>1192</v>
       </c>
@@ -72235,7 +72249,7 @@
       <c r="AH779" s="4"/>
       <c r="AI779" s="4"/>
     </row>
-    <row r="780" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="780" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A780" s="2" t="s">
         <v>1193</v>
       </c>
@@ -72296,7 +72310,7 @@
       <c r="AH780" s="4"/>
       <c r="AI780" s="4"/>
     </row>
-    <row r="781" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="781" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A781" s="2" t="s">
         <v>1196</v>
       </c>
@@ -72357,7 +72371,7 @@
       <c r="AH781" s="4"/>
       <c r="AI781" s="4"/>
     </row>
-    <row r="782" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="782" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A782" s="2" t="s">
         <v>1199</v>
       </c>
@@ -72418,7 +72432,7 @@
       <c r="AH782" s="4"/>
       <c r="AI782" s="4"/>
     </row>
-    <row r="783" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="783" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A783" s="2" t="s">
         <v>1200</v>
       </c>
@@ -72479,7 +72493,7 @@
       <c r="AH783" s="4"/>
       <c r="AI783" s="4"/>
     </row>
-    <row r="784" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="784" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A784" s="2" t="s">
         <v>1201</v>
       </c>
@@ -72540,7 +72554,7 @@
       <c r="AH784" s="4"/>
       <c r="AI784" s="4"/>
     </row>
-    <row r="785" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="785" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A785" s="2" t="s">
         <v>1202</v>
       </c>
@@ -72601,7 +72615,7 @@
       <c r="AH785" s="4"/>
       <c r="AI785" s="4"/>
     </row>
-    <row r="786" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="786" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A786" s="2" t="s">
         <v>1205</v>
       </c>
@@ -72662,7 +72676,7 @@
       <c r="AH786" s="4"/>
       <c r="AI786" s="4"/>
     </row>
-    <row r="787" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="787" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A787" s="2" t="s">
         <v>1206</v>
       </c>
@@ -72723,7 +72737,7 @@
       <c r="AH787" s="4"/>
       <c r="AI787" s="4"/>
     </row>
-    <row r="788" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="788" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A788" s="2" t="s">
         <v>1207</v>
       </c>
@@ -72784,7 +72798,7 @@
       <c r="AH788" s="4"/>
       <c r="AI788" s="4"/>
     </row>
-    <row r="789" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="789" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A789" s="2" t="s">
         <v>1208</v>
       </c>
@@ -72845,7 +72859,7 @@
       <c r="AH789" s="4"/>
       <c r="AI789" s="4"/>
     </row>
-    <row r="790" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="790" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A790" s="2" t="s">
         <v>1211</v>
       </c>
@@ -72906,7 +72920,7 @@
       <c r="AH790" s="4"/>
       <c r="AI790" s="4"/>
     </row>
-    <row r="791" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="791" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A791" s="2" t="s">
         <v>1212</v>
       </c>
@@ -72967,7 +72981,7 @@
       <c r="AH791" s="4"/>
       <c r="AI791" s="4"/>
     </row>
-    <row r="792" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="792" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A792" s="2" t="s">
         <v>1215</v>
       </c>
@@ -73028,7 +73042,7 @@
       <c r="AH792" s="4"/>
       <c r="AI792" s="4"/>
     </row>
-    <row r="793" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="793" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A793" s="2" t="s">
         <v>1216</v>
       </c>
@@ -73089,7 +73103,7 @@
       <c r="AH793" s="4"/>
       <c r="AI793" s="4"/>
     </row>
-    <row r="794" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="794" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A794" s="2" t="s">
         <v>1219</v>
       </c>
@@ -73150,7 +73164,7 @@
       <c r="AH794" s="4"/>
       <c r="AI794" s="4"/>
     </row>
-    <row r="795" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="795" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A795" s="2" t="s">
         <v>1222</v>
       </c>
@@ -73211,7 +73225,7 @@
       <c r="AH795" s="4"/>
       <c r="AI795" s="4"/>
     </row>
-    <row r="796" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="796" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A796" s="2" t="s">
         <v>1223</v>
       </c>
@@ -73272,7 +73286,7 @@
       <c r="AH796" s="4"/>
       <c r="AI796" s="4"/>
     </row>
-    <row r="797" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="797" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A797" s="2" t="s">
         <v>1227</v>
       </c>
@@ -73333,7 +73347,7 @@
       <c r="AH797" s="4"/>
       <c r="AI797" s="4"/>
     </row>
-    <row r="798" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="798" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A798" s="2" t="s">
         <v>1228</v>
       </c>
@@ -73394,7 +73408,7 @@
       <c r="AH798" s="4"/>
       <c r="AI798" s="4"/>
     </row>
-    <row r="799" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="799" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A799" s="2" t="s">
         <v>1230</v>
       </c>
@@ -73455,7 +73469,7 @@
       <c r="AH799" s="4"/>
       <c r="AI799" s="4"/>
     </row>
-    <row r="800" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="800" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A800" s="2" t="s">
         <v>1233</v>
       </c>
@@ -73516,7 +73530,7 @@
       <c r="AH800" s="4"/>
       <c r="AI800" s="4"/>
     </row>
-    <row r="801" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="801" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A801" s="2" t="s">
         <v>1234</v>
       </c>
@@ -73577,7 +73591,7 @@
       <c r="AH801" s="4"/>
       <c r="AI801" s="4"/>
     </row>
-    <row r="802" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="802" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A802" s="2" t="s">
         <v>1235</v>
       </c>
@@ -73638,7 +73652,7 @@
       <c r="AH802" s="4"/>
       <c r="AI802" s="4"/>
     </row>
-    <row r="803" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="803" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A803" s="2" t="s">
         <v>1236</v>
       </c>
@@ -73699,7 +73713,7 @@
       <c r="AH803" s="4"/>
       <c r="AI803" s="4"/>
     </row>
-    <row r="804" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="804" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A804" s="2" t="s">
         <v>1239</v>
       </c>
@@ -73760,7 +73774,7 @@
       <c r="AH804" s="4"/>
       <c r="AI804" s="4"/>
     </row>
-    <row r="805" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="805" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A805" s="2" t="s">
         <v>1240</v>
       </c>
@@ -73821,7 +73835,7 @@
       <c r="AH805" s="4"/>
       <c r="AI805" s="4"/>
     </row>
-    <row r="806" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="806" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A806" s="2" t="s">
         <v>1241</v>
       </c>
@@ -73882,7 +73896,7 @@
       <c r="AH806" s="4"/>
       <c r="AI806" s="4"/>
     </row>
-    <row r="807" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="807" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A807" s="2" t="s">
         <v>1244</v>
       </c>
@@ -73943,7 +73957,7 @@
       <c r="AH807" s="4"/>
       <c r="AI807" s="4"/>
     </row>
-    <row r="808" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="808" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A808" s="2" t="s">
         <v>1245</v>
       </c>
@@ -74004,7 +74018,7 @@
       <c r="AH808" s="4"/>
       <c r="AI808" s="4"/>
     </row>
-    <row r="809" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="809" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A809" s="2" t="s">
         <v>1246</v>
       </c>
@@ -74065,7 +74079,7 @@
       <c r="AH809" s="4"/>
       <c r="AI809" s="4"/>
     </row>
-    <row r="810" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="810" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A810" s="2" t="s">
         <v>1249</v>
       </c>
@@ -74126,7 +74140,7 @@
       <c r="AH810" s="4"/>
       <c r="AI810" s="4"/>
     </row>
-    <row r="811" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="811" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A811" s="2" t="s">
         <v>1250</v>
       </c>
@@ -74187,7 +74201,7 @@
       <c r="AH811" s="4"/>
       <c r="AI811" s="4"/>
     </row>
-    <row r="812" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="812" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A812" s="2" t="s">
         <v>1252</v>
       </c>
@@ -74248,7 +74262,7 @@
       <c r="AH812" s="4"/>
       <c r="AI812" s="4"/>
     </row>
-    <row r="813" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="813" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A813" s="2" t="s">
         <v>1253</v>
       </c>
@@ -74309,7 +74323,7 @@
       <c r="AH813" s="4"/>
       <c r="AI813" s="4"/>
     </row>
-    <row r="814" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="814" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A814" s="2" t="s">
         <v>1257</v>
       </c>
@@ -74370,7 +74384,7 @@
       <c r="AH814" s="4"/>
       <c r="AI814" s="4"/>
     </row>
-    <row r="815" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="815" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A815" s="2" t="s">
         <v>1258</v>
       </c>
@@ -74431,7 +74445,7 @@
       <c r="AH815" s="4"/>
       <c r="AI815" s="4"/>
     </row>
-    <row r="816" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="816" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A816" s="2" t="s">
         <v>1260</v>
       </c>
@@ -74492,7 +74506,7 @@
       <c r="AH816" s="4"/>
       <c r="AI816" s="4"/>
     </row>
-    <row r="817" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="817" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A817" s="2" t="s">
         <v>1261</v>
       </c>
@@ -74553,7 +74567,7 @@
       <c r="AH817" s="4"/>
       <c r="AI817" s="4"/>
     </row>
-    <row r="818" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="818" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A818" s="2" t="s">
         <v>1262</v>
       </c>
@@ -74614,7 +74628,7 @@
       <c r="AH818" s="4"/>
       <c r="AI818" s="4"/>
     </row>
-    <row r="819" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="819" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A819" s="2" t="s">
         <v>1263</v>
       </c>
@@ -74675,7 +74689,7 @@
       <c r="AH819" s="4"/>
       <c r="AI819" s="4"/>
     </row>
-    <row r="820" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="820" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A820" s="2" t="s">
         <v>1266</v>
       </c>
@@ -74736,7 +74750,7 @@
       <c r="AH820" s="4"/>
       <c r="AI820" s="4"/>
     </row>
-    <row r="821" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="821" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A821" s="2" t="s">
         <v>1267</v>
       </c>
@@ -74797,7 +74811,7 @@
       <c r="AH821" s="4"/>
       <c r="AI821" s="4"/>
     </row>
-    <row r="822" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="822" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A822" s="2" t="s">
         <v>1268</v>
       </c>
@@ -74858,7 +74872,7 @@
       <c r="AH822" s="4"/>
       <c r="AI822" s="4"/>
     </row>
-    <row r="823" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="823" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A823" s="2" t="s">
         <v>1271</v>
       </c>
@@ -74919,7 +74933,7 @@
       <c r="AH823" s="4"/>
       <c r="AI823" s="4"/>
     </row>
-    <row r="824" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="824" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A824" s="2" t="s">
         <v>1273</v>
       </c>
@@ -74980,7 +74994,7 @@
       <c r="AH824" s="4"/>
       <c r="AI824" s="4"/>
     </row>
-    <row r="825" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="825" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A825" s="2" t="s">
         <v>1274</v>
       </c>
@@ -75041,7 +75055,7 @@
       <c r="AH825" s="4"/>
       <c r="AI825" s="4"/>
     </row>
-    <row r="826" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="826" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A826" s="2" t="s">
         <v>1277</v>
       </c>
@@ -75102,7 +75116,7 @@
       <c r="AH826" s="4"/>
       <c r="AI826" s="4"/>
     </row>
-    <row r="827" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="827" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A827" s="2" t="s">
         <v>1278</v>
       </c>
@@ -75163,7 +75177,7 @@
       <c r="AH827" s="4"/>
       <c r="AI827" s="4"/>
     </row>
-    <row r="828" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="828" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A828" s="2" t="s">
         <v>1281</v>
       </c>
@@ -75224,7 +75238,7 @@
       <c r="AH828" s="4"/>
       <c r="AI828" s="4"/>
     </row>
-    <row r="829" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="829" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A829" s="2" t="s">
         <v>1282</v>
       </c>
@@ -75285,7 +75299,7 @@
       <c r="AH829" s="4"/>
       <c r="AI829" s="4"/>
     </row>
-    <row r="830" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="830" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A830" s="2" t="s">
         <v>1284</v>
       </c>
@@ -75346,7 +75360,7 @@
       <c r="AH830" s="4"/>
       <c r="AI830" s="4"/>
     </row>
-    <row r="831" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="831" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A831" s="2" t="s">
         <v>1285</v>
       </c>
@@ -75407,7 +75421,7 @@
       <c r="AH831" s="4"/>
       <c r="AI831" s="4"/>
     </row>
-    <row r="832" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="832" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A832" s="2" t="s">
         <v>1286</v>
       </c>
@@ -75468,7 +75482,7 @@
       <c r="AH832" s="4"/>
       <c r="AI832" s="4"/>
     </row>
-    <row r="833" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="833" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A833" s="2" t="s">
         <v>1287</v>
       </c>
@@ -75529,7 +75543,7 @@
       <c r="AH833" s="4"/>
       <c r="AI833" s="4"/>
     </row>
-    <row r="834" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="834" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A834" s="2" t="s">
         <v>1288</v>
       </c>
@@ -75590,7 +75604,7 @@
       <c r="AH834" s="4"/>
       <c r="AI834" s="4"/>
     </row>
-    <row r="835" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="835" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A835" s="2" t="s">
         <v>1291</v>
       </c>
@@ -75651,7 +75665,7 @@
       <c r="AH835" s="4"/>
       <c r="AI835" s="4"/>
     </row>
-    <row r="836" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="836" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A836" s="2" t="s">
         <v>1294</v>
       </c>
@@ -75712,7 +75726,7 @@
       <c r="AH836" s="4"/>
       <c r="AI836" s="4"/>
     </row>
-    <row r="837" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="837" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A837" s="2" t="s">
         <v>1295</v>
       </c>
@@ -75773,7 +75787,7 @@
       <c r="AH837" s="4"/>
       <c r="AI837" s="4"/>
     </row>
-    <row r="838" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="838" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A838" s="2" t="s">
         <v>1296</v>
       </c>
@@ -75834,7 +75848,7 @@
       <c r="AH838" s="4"/>
       <c r="AI838" s="4"/>
     </row>
-    <row r="839" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="839" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A839" s="2" t="s">
         <v>1297</v>
       </c>
@@ -75895,7 +75909,7 @@
       <c r="AH839" s="4"/>
       <c r="AI839" s="4"/>
     </row>
-    <row r="840" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="840" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A840" s="2" t="s">
         <v>1298</v>
       </c>
@@ -75956,7 +75970,7 @@
       <c r="AH840" s="4"/>
       <c r="AI840" s="4"/>
     </row>
-    <row r="841" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="841" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A841" s="2" t="s">
         <v>1302</v>
       </c>
@@ -76017,7 +76031,7 @@
       <c r="AH841" s="4"/>
       <c r="AI841" s="4"/>
     </row>
-    <row r="842" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="842" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A842" s="2" t="s">
         <v>1303</v>
       </c>
@@ -76078,7 +76092,7 @@
       <c r="AH842" s="4"/>
       <c r="AI842" s="4"/>
     </row>
-    <row r="843" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="843" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A843" s="2" t="s">
         <v>1304</v>
       </c>
@@ -76139,7 +76153,7 @@
       <c r="AH843" s="4"/>
       <c r="AI843" s="4"/>
     </row>
-    <row r="844" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="844" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A844" s="2" t="s">
         <v>1305</v>
       </c>
@@ -76200,7 +76214,7 @@
       <c r="AH844" s="4"/>
       <c r="AI844" s="4"/>
     </row>
-    <row r="845" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="845" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A845" s="2" t="s">
         <v>1306</v>
       </c>
@@ -76261,7 +76275,7 @@
       <c r="AH845" s="4"/>
       <c r="AI845" s="4"/>
     </row>
-    <row r="846" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="846" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A846" s="2" t="s">
         <v>1307</v>
       </c>
@@ -76322,7 +76336,7 @@
       <c r="AH846" s="4"/>
       <c r="AI846" s="4"/>
     </row>
-    <row r="847" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="847" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A847" s="2" t="s">
         <v>1308</v>
       </c>
@@ -76383,7 +76397,7 @@
       <c r="AH847" s="4"/>
       <c r="AI847" s="4"/>
     </row>
-    <row r="848" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="848" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A848" s="2" t="s">
         <v>1311</v>
       </c>
@@ -76444,7 +76458,7 @@
       <c r="AH848" s="4"/>
       <c r="AI848" s="4"/>
     </row>
-    <row r="849" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="849" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A849" s="2" t="s">
         <v>1313</v>
       </c>
@@ -76505,7 +76519,7 @@
       <c r="AH849" s="4"/>
       <c r="AI849" s="4"/>
     </row>
-    <row r="850" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="850" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A850" s="2" t="s">
         <v>1314</v>
       </c>
@@ -76566,7 +76580,7 @@
       <c r="AH850" s="4"/>
       <c r="AI850" s="4"/>
     </row>
-    <row r="851" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="851" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A851" s="2" t="s">
         <v>1316</v>
       </c>
@@ -76627,7 +76641,7 @@
       <c r="AH851" s="4"/>
       <c r="AI851" s="4"/>
     </row>
-    <row r="852" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="852" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A852" s="2" t="s">
         <v>1317</v>
       </c>
@@ -76688,7 +76702,7 @@
       <c r="AH852" s="4"/>
       <c r="AI852" s="4"/>
     </row>
-    <row r="853" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="853" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A853" s="2" t="s">
         <v>1319</v>
       </c>
@@ -76749,7 +76763,7 @@
       <c r="AH853" s="4"/>
       <c r="AI853" s="4"/>
     </row>
-    <row r="854" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="854" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A854" s="2" t="s">
         <v>1320</v>
       </c>
@@ -76810,7 +76824,7 @@
       <c r="AH854" s="4"/>
       <c r="AI854" s="4"/>
     </row>
-    <row r="855" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="855" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A855" s="2" t="s">
         <v>1322</v>
       </c>
@@ -76871,7 +76885,7 @@
       <c r="AH855" s="4"/>
       <c r="AI855" s="4"/>
     </row>
-    <row r="856" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="856" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A856" s="2" t="s">
         <v>1324</v>
       </c>
@@ -76932,7 +76946,7 @@
       <c r="AH856" s="4"/>
       <c r="AI856" s="4"/>
     </row>
-    <row r="857" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="857" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A857" s="2" t="s">
         <v>1327</v>
       </c>
@@ -76993,7 +77007,7 @@
       <c r="AH857" s="4"/>
       <c r="AI857" s="4"/>
     </row>
-    <row r="858" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="858" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A858" s="2" t="s">
         <v>1329</v>
       </c>
@@ -77054,7 +77068,7 @@
       <c r="AH858" s="4"/>
       <c r="AI858" s="4"/>
     </row>
-    <row r="859" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="859" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A859" s="2" t="s">
         <v>1331</v>
       </c>
@@ -77115,7 +77129,7 @@
       <c r="AH859" s="4"/>
       <c r="AI859" s="4"/>
     </row>
-    <row r="860" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="860" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A860" s="2" t="s">
         <v>1332</v>
       </c>
@@ -77176,7 +77190,7 @@
       <c r="AH860" s="4"/>
       <c r="AI860" s="4"/>
     </row>
-    <row r="861" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="861" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A861" s="2" t="s">
         <v>1334</v>
       </c>
@@ -77237,7 +77251,7 @@
       <c r="AH861" s="4"/>
       <c r="AI861" s="4"/>
     </row>
-    <row r="862" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="862" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A862" s="2" t="s">
         <v>1335</v>
       </c>
@@ -77298,7 +77312,7 @@
       <c r="AH862" s="4"/>
       <c r="AI862" s="4"/>
     </row>
-    <row r="863" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="863" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A863" s="2" t="s">
         <v>1337</v>
       </c>
@@ -77359,7 +77373,7 @@
       <c r="AH863" s="4"/>
       <c r="AI863" s="4"/>
     </row>
-    <row r="864" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="864" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A864" s="2" t="s">
         <v>1339</v>
       </c>
@@ -77420,7 +77434,7 @@
       <c r="AH864" s="4"/>
       <c r="AI864" s="4"/>
     </row>
-    <row r="865" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="865" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A865" s="2" t="s">
         <v>1342</v>
       </c>
@@ -77481,7 +77495,7 @@
       <c r="AH865" s="4"/>
       <c r="AI865" s="4"/>
     </row>
-    <row r="866" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="866" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A866" s="2" t="s">
         <v>1343</v>
       </c>
@@ -77542,7 +77556,7 @@
       <c r="AH866" s="4"/>
       <c r="AI866" s="4"/>
     </row>
-    <row r="867" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="867" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A867" s="2" t="s">
         <v>1346</v>
       </c>
@@ -77603,7 +77617,7 @@
       <c r="AH867" s="4"/>
       <c r="AI867" s="4"/>
     </row>
-    <row r="868" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="868" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A868" s="2" t="s">
         <v>1349</v>
       </c>
@@ -77664,7 +77678,7 @@
       <c r="AH868" s="4"/>
       <c r="AI868" s="4"/>
     </row>
-    <row r="869" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="869" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A869" s="2" t="s">
         <v>1350</v>
       </c>
@@ -77725,7 +77739,7 @@
       <c r="AH869" s="4"/>
       <c r="AI869" s="4"/>
     </row>
-    <row r="870" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="870" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A870" s="2" t="s">
         <v>1352</v>
       </c>
@@ -77786,7 +77800,7 @@
       <c r="AH870" s="4"/>
       <c r="AI870" s="4"/>
     </row>
-    <row r="871" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="871" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A871" s="2" t="s">
         <v>1354</v>
       </c>
@@ -77847,7 +77861,7 @@
       <c r="AH871" s="4"/>
       <c r="AI871" s="4"/>
     </row>
-    <row r="872" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="872" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A872" s="2" t="s">
         <v>1357</v>
       </c>
@@ -77908,7 +77922,7 @@
       <c r="AH872" s="4"/>
       <c r="AI872" s="4"/>
     </row>
-    <row r="873" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="873" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A873" s="2" t="s">
         <v>1358</v>
       </c>
@@ -77969,7 +77983,7 @@
       <c r="AH873" s="4"/>
       <c r="AI873" s="4"/>
     </row>
-    <row r="874" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="874" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A874" s="2" t="s">
         <v>1360</v>
       </c>
@@ -78030,7 +78044,7 @@
       <c r="AH874" s="4"/>
       <c r="AI874" s="4"/>
     </row>
-    <row r="875" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="875" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A875" s="2" t="s">
         <v>1362</v>
       </c>
@@ -78091,7 +78105,7 @@
       <c r="AH875" s="4"/>
       <c r="AI875" s="4"/>
     </row>
-    <row r="876" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="876" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A876" s="2" t="s">
         <v>1364</v>
       </c>
@@ -78152,7 +78166,7 @@
       <c r="AH876" s="4"/>
       <c r="AI876" s="4"/>
     </row>
-    <row r="877" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="877" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A877" s="2" t="s">
         <v>1367</v>
       </c>
@@ -78213,7 +78227,7 @@
       <c r="AH877" s="4"/>
       <c r="AI877" s="4"/>
     </row>
-    <row r="878" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="878" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A878" s="2" t="s">
         <v>1369</v>
       </c>
@@ -78274,7 +78288,7 @@
       <c r="AH878" s="4"/>
       <c r="AI878" s="4"/>
     </row>
-    <row r="879" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="879" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A879" s="2" t="s">
         <v>1370</v>
       </c>
@@ -78335,7 +78349,7 @@
       <c r="AH879" s="4"/>
       <c r="AI879" s="4"/>
     </row>
-    <row r="880" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="880" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A880" s="2" t="s">
         <v>1371</v>
       </c>
@@ -78396,7 +78410,7 @@
       <c r="AH880" s="4"/>
       <c r="AI880" s="4"/>
     </row>
-    <row r="881" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="881" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A881" s="2" t="s">
         <v>1372</v>
       </c>
@@ -78457,7 +78471,7 @@
       <c r="AH881" s="4"/>
       <c r="AI881" s="4"/>
     </row>
-    <row r="882" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="882" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A882" s="2" t="s">
         <v>1375</v>
       </c>
@@ -78518,7 +78532,7 @@
       <c r="AH882" s="4"/>
       <c r="AI882" s="4"/>
     </row>
-    <row r="883" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="883" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A883" s="2" t="s">
         <v>1376</v>
       </c>
@@ -78579,7 +78593,7 @@
       <c r="AH883" s="4"/>
       <c r="AI883" s="4"/>
     </row>
-    <row r="884" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="884" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A884" s="2" t="s">
         <v>1377</v>
       </c>
@@ -78640,7 +78654,7 @@
       <c r="AH884" s="4"/>
       <c r="AI884" s="4"/>
     </row>
-    <row r="885" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="885" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A885" s="2" t="s">
         <v>1378</v>
       </c>
@@ -78701,7 +78715,7 @@
       <c r="AH885" s="4"/>
       <c r="AI885" s="4"/>
     </row>
-    <row r="886" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="886" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A886" s="2" t="s">
         <v>1380</v>
       </c>
@@ -78762,7 +78776,7 @@
       <c r="AH886" s="4"/>
       <c r="AI886" s="4"/>
     </row>
-    <row r="887" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="887" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A887" s="2" t="s">
         <v>1383</v>
       </c>
@@ -78823,7 +78837,7 @@
       <c r="AH887" s="4"/>
       <c r="AI887" s="4"/>
     </row>
-    <row r="888" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="888" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A888" s="2" t="s">
         <v>1385</v>
       </c>
@@ -78884,7 +78898,7 @@
       <c r="AH888" s="4"/>
       <c r="AI888" s="4"/>
     </row>
-    <row r="889" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="889" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A889" s="2" t="s">
         <v>1388</v>
       </c>
@@ -78945,7 +78959,7 @@
       <c r="AH889" s="4"/>
       <c r="AI889" s="4"/>
     </row>
-    <row r="890" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="890" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A890" s="2" t="s">
         <v>1389</v>
       </c>
@@ -79006,7 +79020,7 @@
       <c r="AH890" s="4"/>
       <c r="AI890" s="4"/>
     </row>
-    <row r="891" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="891" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A891" s="2" t="s">
         <v>1390</v>
       </c>
@@ -79067,7 +79081,7 @@
       <c r="AH891" s="4"/>
       <c r="AI891" s="4"/>
     </row>
-    <row r="892" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="892" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A892" s="2" t="s">
         <v>1392</v>
       </c>
@@ -79128,7 +79142,7 @@
       <c r="AH892" s="4"/>
       <c r="AI892" s="4"/>
     </row>
-    <row r="893" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="893" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A893" s="2" t="s">
         <v>1395</v>
       </c>
@@ -79189,7 +79203,7 @@
       <c r="AH893" s="4"/>
       <c r="AI893" s="4"/>
     </row>
-    <row r="894" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="894" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A894" s="2" t="s">
         <v>1396</v>
       </c>
@@ -79250,7 +79264,7 @@
       <c r="AH894" s="4"/>
       <c r="AI894" s="4"/>
     </row>
-    <row r="895" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="895" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A895" s="2" t="s">
         <v>1399</v>
       </c>
@@ -79311,7 +79325,7 @@
       <c r="AH895" s="4"/>
       <c r="AI895" s="4"/>
     </row>
-    <row r="896" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="896" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A896" s="2" t="s">
         <v>1401</v>
       </c>
@@ -79372,7 +79386,7 @@
       <c r="AH896" s="4"/>
       <c r="AI896" s="4"/>
     </row>
-    <row r="897" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="897" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A897" s="2" t="s">
         <v>1404</v>
       </c>
@@ -79433,7 +79447,7 @@
       <c r="AH897" s="4"/>
       <c r="AI897" s="4"/>
     </row>
-    <row r="898" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="898" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A898" s="2" t="s">
         <v>1406</v>
       </c>
@@ -79494,7 +79508,7 @@
       <c r="AH898" s="4"/>
       <c r="AI898" s="4"/>
     </row>
-    <row r="899" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="899" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A899" s="2" t="s">
         <v>1408</v>
       </c>
@@ -79555,7 +79569,7 @@
       <c r="AH899" s="4"/>
       <c r="AI899" s="4"/>
     </row>
-    <row r="900" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="900" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A900" s="2" t="s">
         <v>1409</v>
       </c>
@@ -79616,7 +79630,7 @@
       <c r="AH900" s="4"/>
       <c r="AI900" s="4"/>
     </row>
-    <row r="901" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="901" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A901" s="2" t="s">
         <v>1412</v>
       </c>
@@ -79677,7 +79691,7 @@
       <c r="AH901" s="4"/>
       <c r="AI901" s="4"/>
     </row>
-    <row r="902" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="902" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A902" s="2" t="s">
         <v>1413</v>
       </c>
@@ -79738,7 +79752,7 @@
       <c r="AH902" s="4"/>
       <c r="AI902" s="4"/>
     </row>
-    <row r="903" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="903" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A903" s="2" t="s">
         <v>1417</v>
       </c>
@@ -79799,7 +79813,7 @@
       <c r="AH903" s="4"/>
       <c r="AI903" s="4"/>
     </row>
-    <row r="904" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="904" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A904" s="2" t="s">
         <v>1420</v>
       </c>
@@ -79860,7 +79874,7 @@
       <c r="AH904" s="4"/>
       <c r="AI904" s="4"/>
     </row>
-    <row r="905" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="905" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A905" s="2" t="s">
         <v>1424</v>
       </c>
@@ -79921,7 +79935,7 @@
       <c r="AH905" s="4"/>
       <c r="AI905" s="4"/>
     </row>
-    <row r="906" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="906" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A906" s="2" t="s">
         <v>1426</v>
       </c>
@@ -79982,7 +79996,7 @@
       <c r="AH906" s="4"/>
       <c r="AI906" s="4"/>
     </row>
-    <row r="907" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="907" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A907" s="2" t="s">
         <v>1428</v>
       </c>
@@ -80043,7 +80057,7 @@
       <c r="AH907" s="4"/>
       <c r="AI907" s="4"/>
     </row>
-    <row r="908" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="908" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A908" s="2" t="s">
         <v>1432</v>
       </c>
@@ -80104,7 +80118,7 @@
       <c r="AH908" s="4"/>
       <c r="AI908" s="4"/>
     </row>
-    <row r="909" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="909" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A909" s="2" t="s">
         <v>1434</v>
       </c>
@@ -80165,7 +80179,7 @@
       <c r="AH909" s="4"/>
       <c r="AI909" s="4"/>
     </row>
-    <row r="910" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="910" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A910" s="2" t="s">
         <v>1436</v>
       </c>
@@ -80226,7 +80240,7 @@
       <c r="AH910" s="4"/>
       <c r="AI910" s="4"/>
     </row>
-    <row r="911" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="911" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A911" s="2" t="s">
         <v>1438</v>
       </c>
@@ -80287,7 +80301,7 @@
       <c r="AH911" s="4"/>
       <c r="AI911" s="4"/>
     </row>
-    <row r="912" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="912" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A912" s="2" t="s">
         <v>1441</v>
       </c>
@@ -80348,7 +80362,7 @@
       <c r="AH912" s="4"/>
       <c r="AI912" s="4"/>
     </row>
-    <row r="913" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="913" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A913" s="2" t="s">
         <v>1442</v>
       </c>
@@ -80409,7 +80423,7 @@
       <c r="AH913" s="4"/>
       <c r="AI913" s="4"/>
     </row>
-    <row r="914" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="914" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A914" s="2" t="s">
         <v>1443</v>
       </c>
@@ -80470,7 +80484,7 @@
       <c r="AH914" s="4"/>
       <c r="AI914" s="4"/>
     </row>
-    <row r="915" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="915" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A915" s="2" t="s">
         <v>1444</v>
       </c>
@@ -80531,7 +80545,7 @@
       <c r="AH915" s="4"/>
       <c r="AI915" s="4"/>
     </row>
-    <row r="916" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="916" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A916" s="2" t="s">
         <v>1447</v>
       </c>
@@ -80592,7 +80606,7 @@
       <c r="AH916" s="4"/>
       <c r="AI916" s="4"/>
     </row>
-    <row r="917" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="917" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A917" s="2" t="s">
         <v>1448</v>
       </c>
@@ -80653,7 +80667,7 @@
       <c r="AH917" s="4"/>
       <c r="AI917" s="4"/>
     </row>
-    <row r="918" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="918" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A918" s="2" t="s">
         <v>1451</v>
       </c>
@@ -80714,7 +80728,7 @@
       <c r="AH918" s="4"/>
       <c r="AI918" s="4"/>
     </row>
-    <row r="919" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="919" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A919" s="2" t="s">
         <v>1452</v>
       </c>
@@ -80775,7 +80789,7 @@
       <c r="AH919" s="4"/>
       <c r="AI919" s="4"/>
     </row>
-    <row r="920" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="920" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A920" s="2" t="s">
         <v>1455</v>
       </c>
@@ -80836,7 +80850,7 @@
       <c r="AH920" s="4"/>
       <c r="AI920" s="4"/>
     </row>
-    <row r="921" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="921" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A921" s="2" t="s">
         <v>1456</v>
       </c>
@@ -80898,7 +80912,13 @@
       <c r="AI921" s="4"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R921" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:R921" xr:uid="{00000000-0009-0000-0000-000000000000}">
+    <filterColumn colId="4">
+      <filters>
+        <filter val="CITRUS 2"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/Produtos.xlsx
+++ b/Produtos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NOT-MARCOS\Documents\GitHub\Catalogo-Olympikus_2.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8754B9BD-CDB5-4E3B-80A8-2B4F42986356}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08FFE9F6-6F0A-4990-BF8A-721008F252C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12111" uniqueCount="1547">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12111" uniqueCount="1546">
   <si>
     <t>IMAGEM</t>
   </si>
@@ -4285,9 +4285,6 @@
   </si>
   <si>
     <t>OICR261714_FLPSPT</t>
-  </si>
-  <si>
-    <t>cc</t>
   </si>
   <si>
     <t>FLPSPT</t>
@@ -5243,7 +5240,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>35</v>
       </c>
@@ -5350,7 +5347,7 @@
         <v>265.43</v>
       </c>
     </row>
-    <row r="3" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>45</v>
       </c>
@@ -5457,7 +5454,7 @@
         <v>265.43</v>
       </c>
     </row>
-    <row r="4" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>48</v>
       </c>
@@ -5564,7 +5561,7 @@
         <v>265.43</v>
       </c>
     </row>
-    <row r="5" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>50</v>
       </c>
@@ -5671,7 +5668,7 @@
         <v>265.43</v>
       </c>
     </row>
-    <row r="6" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>52</v>
       </c>
@@ -9002,7 +8999,7 @@
         <v>43210417</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
       <c r="F37" s="4" t="s">
         <v>46</v>
@@ -9109,7 +9106,7 @@
         <v>43210417</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
       <c r="F38" s="2" t="s">
         <v>46</v>
@@ -9216,7 +9213,7 @@
         <v>43210417</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>1546</v>
+        <v>1545</v>
       </c>
       <c r="F39" s="4" t="s">
         <v>39</v>
@@ -9323,7 +9320,7 @@
         <v>43210417</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>1545</v>
+        <v>1544</v>
       </c>
       <c r="F40" s="2" t="s">
         <v>46</v>
@@ -59250,7 +59247,7 @@
       <c r="AH566" s="4"/>
       <c r="AI566" s="4"/>
     </row>
-    <row r="567" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A567" s="2" t="s">
         <v>797</v>
       </c>
@@ -59311,7 +59308,7 @@
       <c r="AH567" s="4"/>
       <c r="AI567" s="4"/>
     </row>
-    <row r="568" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A568" s="2" t="s">
         <v>803</v>
       </c>
@@ -59372,7 +59369,7 @@
       <c r="AH568" s="4"/>
       <c r="AI568" s="4"/>
     </row>
-    <row r="569" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A569" s="2" t="s">
         <v>804</v>
       </c>
@@ -59433,7 +59430,7 @@
       <c r="AH569" s="4"/>
       <c r="AI569" s="4"/>
     </row>
-    <row r="570" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A570" s="2" t="s">
         <v>806</v>
       </c>
@@ -59494,7 +59491,7 @@
       <c r="AH570" s="4"/>
       <c r="AI570" s="4"/>
     </row>
-    <row r="571" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A571" s="2" t="s">
         <v>808</v>
       </c>
@@ -59555,7 +59552,7 @@
       <c r="AH571" s="4"/>
       <c r="AI571" s="4"/>
     </row>
-    <row r="572" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A572" s="2" t="s">
         <v>810</v>
       </c>
@@ -59616,7 +59613,7 @@
       <c r="AH572" s="4"/>
       <c r="AI572" s="4"/>
     </row>
-    <row r="573" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A573" s="2" t="s">
         <v>813</v>
       </c>
@@ -59677,7 +59674,7 @@
       <c r="AH573" s="4"/>
       <c r="AI573" s="4"/>
     </row>
-    <row r="574" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A574" s="2" t="s">
         <v>814</v>
       </c>
@@ -59738,7 +59735,7 @@
       <c r="AH574" s="4"/>
       <c r="AI574" s="4"/>
     </row>
-    <row r="575" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A575" s="2" t="s">
         <v>815</v>
       </c>
@@ -59799,7 +59796,7 @@
       <c r="AH575" s="4"/>
       <c r="AI575" s="4"/>
     </row>
-    <row r="576" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A576" s="2" t="s">
         <v>818</v>
       </c>
@@ -59860,7 +59857,7 @@
       <c r="AH576" s="4"/>
       <c r="AI576" s="4"/>
     </row>
-    <row r="577" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A577" s="2" t="s">
         <v>819</v>
       </c>
@@ -59921,7 +59918,7 @@
       <c r="AH577" s="4"/>
       <c r="AI577" s="4"/>
     </row>
-    <row r="578" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A578" s="2" t="s">
         <v>820</v>
       </c>
@@ -59982,7 +59979,7 @@
       <c r="AH578" s="4"/>
       <c r="AI578" s="4"/>
     </row>
-    <row r="579" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A579" s="2" t="s">
         <v>823</v>
       </c>
@@ -60043,7 +60040,7 @@
       <c r="AH579" s="4"/>
       <c r="AI579" s="4"/>
     </row>
-    <row r="580" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A580" s="2" t="s">
         <v>824</v>
       </c>
@@ -60104,7 +60101,7 @@
       <c r="AH580" s="4"/>
       <c r="AI580" s="4"/>
     </row>
-    <row r="581" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A581" s="2" t="s">
         <v>825</v>
       </c>
@@ -60165,7 +60162,7 @@
       <c r="AH581" s="4"/>
       <c r="AI581" s="4"/>
     </row>
-    <row r="582" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A582" s="2" t="s">
         <v>828</v>
       </c>
@@ -60226,7 +60223,7 @@
       <c r="AH582" s="4"/>
       <c r="AI582" s="4"/>
     </row>
-    <row r="583" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A583" s="2" t="s">
         <v>829</v>
       </c>
@@ -60287,7 +60284,7 @@
       <c r="AH583" s="4"/>
       <c r="AI583" s="4"/>
     </row>
-    <row r="584" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A584" s="2" t="s">
         <v>830</v>
       </c>
@@ -60348,7 +60345,7 @@
       <c r="AH584" s="4"/>
       <c r="AI584" s="4"/>
     </row>
-    <row r="585" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A585" s="2" t="s">
         <v>834</v>
       </c>
@@ -60409,7 +60406,7 @@
       <c r="AH585" s="4"/>
       <c r="AI585" s="4"/>
     </row>
-    <row r="586" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A586" s="2" t="s">
         <v>835</v>
       </c>
@@ -60470,7 +60467,7 @@
       <c r="AH586" s="4"/>
       <c r="AI586" s="4"/>
     </row>
-    <row r="587" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A587" s="2" t="s">
         <v>836</v>
       </c>
@@ -60531,7 +60528,7 @@
       <c r="AH587" s="4"/>
       <c r="AI587" s="4"/>
     </row>
-    <row r="588" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A588" s="2" t="s">
         <v>839</v>
       </c>
@@ -60592,7 +60589,7 @@
       <c r="AH588" s="4"/>
       <c r="AI588" s="4"/>
     </row>
-    <row r="589" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A589" s="2" t="s">
         <v>840</v>
       </c>
@@ -60653,7 +60650,7 @@
       <c r="AH589" s="4"/>
       <c r="AI589" s="4"/>
     </row>
-    <row r="590" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A590" s="2" t="s">
         <v>841</v>
       </c>
@@ -60714,7 +60711,7 @@
       <c r="AH590" s="4"/>
       <c r="AI590" s="4"/>
     </row>
-    <row r="591" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A591" s="2" t="s">
         <v>844</v>
       </c>
@@ -60775,7 +60772,7 @@
       <c r="AH591" s="4"/>
       <c r="AI591" s="4"/>
     </row>
-    <row r="592" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A592" s="2" t="s">
         <v>845</v>
       </c>
@@ -60836,7 +60833,7 @@
       <c r="AH592" s="4"/>
       <c r="AI592" s="4"/>
     </row>
-    <row r="593" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A593" s="2" t="s">
         <v>846</v>
       </c>
@@ -60897,7 +60894,7 @@
       <c r="AH593" s="4"/>
       <c r="AI593" s="4"/>
     </row>
-    <row r="594" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A594" s="2" t="s">
         <v>849</v>
       </c>
@@ -60958,7 +60955,7 @@
       <c r="AH594" s="4"/>
       <c r="AI594" s="4"/>
     </row>
-    <row r="595" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A595" s="2" t="s">
         <v>850</v>
       </c>
@@ -61019,7 +61016,7 @@
       <c r="AH595" s="4"/>
       <c r="AI595" s="4"/>
     </row>
-    <row r="596" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A596" s="2" t="s">
         <v>851</v>
       </c>
@@ -61080,7 +61077,7 @@
       <c r="AH596" s="4"/>
       <c r="AI596" s="4"/>
     </row>
-    <row r="597" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A597" s="2" t="s">
         <v>852</v>
       </c>
@@ -61141,7 +61138,7 @@
       <c r="AH597" s="4"/>
       <c r="AI597" s="4"/>
     </row>
-    <row r="598" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A598" s="2" t="s">
         <v>856</v>
       </c>
@@ -61202,7 +61199,7 @@
       <c r="AH598" s="4"/>
       <c r="AI598" s="4"/>
     </row>
-    <row r="599" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A599" s="2" t="s">
         <v>857</v>
       </c>
@@ -61263,7 +61260,7 @@
       <c r="AH599" s="4"/>
       <c r="AI599" s="4"/>
     </row>
-    <row r="600" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A600" s="2" t="s">
         <v>858</v>
       </c>
@@ -61324,7 +61321,7 @@
       <c r="AH600" s="4"/>
       <c r="AI600" s="4"/>
     </row>
-    <row r="601" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A601" s="2" t="s">
         <v>859</v>
       </c>
@@ -61385,7 +61382,7 @@
       <c r="AH601" s="4"/>
       <c r="AI601" s="4"/>
     </row>
-    <row r="602" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A602" s="2" t="s">
         <v>860</v>
       </c>
@@ -61446,7 +61443,7 @@
       <c r="AH602" s="4"/>
       <c r="AI602" s="4"/>
     </row>
-    <row r="603" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A603" s="2" t="s">
         <v>863</v>
       </c>
@@ -61507,7 +61504,7 @@
       <c r="AH603" s="4"/>
       <c r="AI603" s="4"/>
     </row>
-    <row r="604" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A604" s="2" t="s">
         <v>864</v>
       </c>
@@ -61568,7 +61565,7 @@
       <c r="AH604" s="4"/>
       <c r="AI604" s="4"/>
     </row>
-    <row r="605" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A605" s="2" t="s">
         <v>865</v>
       </c>
@@ -61629,7 +61626,7 @@
       <c r="AH605" s="4"/>
       <c r="AI605" s="4"/>
     </row>
-    <row r="606" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A606" s="2" t="s">
         <v>868</v>
       </c>
@@ -61690,7 +61687,7 @@
       <c r="AH606" s="4"/>
       <c r="AI606" s="4"/>
     </row>
-    <row r="607" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A607" s="2" t="s">
         <v>869</v>
       </c>
@@ -61751,7 +61748,7 @@
       <c r="AH607" s="4"/>
       <c r="AI607" s="4"/>
     </row>
-    <row r="608" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A608" s="2" t="s">
         <v>870</v>
       </c>
@@ -61812,7 +61809,7 @@
       <c r="AH608" s="4"/>
       <c r="AI608" s="4"/>
     </row>
-    <row r="609" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A609" s="2" t="s">
         <v>873</v>
       </c>
@@ -61873,7 +61870,7 @@
       <c r="AH609" s="4"/>
       <c r="AI609" s="4"/>
     </row>
-    <row r="610" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A610" s="2" t="s">
         <v>874</v>
       </c>
@@ -61934,7 +61931,7 @@
       <c r="AH610" s="4"/>
       <c r="AI610" s="4"/>
     </row>
-    <row r="611" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A611" s="2" t="s">
         <v>875</v>
       </c>
@@ -61995,7 +61992,7 @@
       <c r="AH611" s="4"/>
       <c r="AI611" s="4"/>
     </row>
-    <row r="612" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A612" s="2" t="s">
         <v>878</v>
       </c>
@@ -62056,7 +62053,7 @@
       <c r="AH612" s="4"/>
       <c r="AI612" s="4"/>
     </row>
-    <row r="613" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A613" s="2" t="s">
         <v>879</v>
       </c>
@@ -62117,7 +62114,7 @@
       <c r="AH613" s="4"/>
       <c r="AI613" s="4"/>
     </row>
-    <row r="614" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A614" s="2" t="s">
         <v>880</v>
       </c>
@@ -62178,7 +62175,7 @@
       <c r="AH614" s="4"/>
       <c r="AI614" s="4"/>
     </row>
-    <row r="615" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A615" s="2" t="s">
         <v>883</v>
       </c>
@@ -62239,7 +62236,7 @@
       <c r="AH615" s="4"/>
       <c r="AI615" s="4"/>
     </row>
-    <row r="616" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A616" s="2" t="s">
         <v>884</v>
       </c>
@@ -62300,7 +62297,7 @@
       <c r="AH616" s="4"/>
       <c r="AI616" s="4"/>
     </row>
-    <row r="617" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A617" s="2" t="s">
         <v>885</v>
       </c>
@@ -62361,7 +62358,7 @@
       <c r="AH617" s="4"/>
       <c r="AI617" s="4"/>
     </row>
-    <row r="618" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A618" s="2" t="s">
         <v>888</v>
       </c>
@@ -62422,7 +62419,7 @@
       <c r="AH618" s="4"/>
       <c r="AI618" s="4"/>
     </row>
-    <row r="619" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A619" s="2" t="s">
         <v>889</v>
       </c>
@@ -62483,7 +62480,7 @@
       <c r="AH619" s="4"/>
       <c r="AI619" s="4"/>
     </row>
-    <row r="620" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A620" s="2" t="s">
         <v>890</v>
       </c>
@@ -62544,7 +62541,7 @@
       <c r="AH620" s="4"/>
       <c r="AI620" s="4"/>
     </row>
-    <row r="621" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A621" s="2" t="s">
         <v>893</v>
       </c>
@@ -62605,7 +62602,7 @@
       <c r="AH621" s="4"/>
       <c r="AI621" s="4"/>
     </row>
-    <row r="622" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A622" s="2" t="s">
         <v>894</v>
       </c>
@@ -62666,7 +62663,7 @@
       <c r="AH622" s="4"/>
       <c r="AI622" s="4"/>
     </row>
-    <row r="623" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A623" s="2" t="s">
         <v>895</v>
       </c>
@@ -62727,7 +62724,7 @@
       <c r="AH623" s="4"/>
       <c r="AI623" s="4"/>
     </row>
-    <row r="624" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A624" s="2" t="s">
         <v>898</v>
       </c>
@@ -62788,7 +62785,7 @@
       <c r="AH624" s="4"/>
       <c r="AI624" s="4"/>
     </row>
-    <row r="625" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A625" s="2" t="s">
         <v>899</v>
       </c>
@@ -62849,7 +62846,7 @@
       <c r="AH625" s="4"/>
       <c r="AI625" s="4"/>
     </row>
-    <row r="626" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A626" s="2" t="s">
         <v>900</v>
       </c>
@@ -63154,7 +63151,7 @@
       <c r="AH630" s="4"/>
       <c r="AI630" s="4"/>
     </row>
-    <row r="631" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A631" s="2" t="s">
         <v>910</v>
       </c>
@@ -63215,7 +63212,7 @@
       <c r="AH631" s="4"/>
       <c r="AI631" s="4"/>
     </row>
-    <row r="632" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A632" s="2" t="s">
         <v>914</v>
       </c>
@@ -63276,7 +63273,7 @@
       <c r="AH632" s="4"/>
       <c r="AI632" s="4"/>
     </row>
-    <row r="633" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A633" s="2" t="s">
         <v>916</v>
       </c>
@@ -63337,7 +63334,7 @@
       <c r="AH633" s="4"/>
       <c r="AI633" s="4"/>
     </row>
-    <row r="634" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A634" s="2" t="s">
         <v>918</v>
       </c>
@@ -63398,7 +63395,7 @@
       <c r="AH634" s="4"/>
       <c r="AI634" s="4"/>
     </row>
-    <row r="635" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A635" s="2" t="s">
         <v>920</v>
       </c>
@@ -63459,7 +63456,7 @@
       <c r="AH635" s="4"/>
       <c r="AI635" s="4"/>
     </row>
-    <row r="636" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A636" s="2" t="s">
         <v>922</v>
       </c>
@@ -63520,7 +63517,7 @@
       <c r="AH636" s="4"/>
       <c r="AI636" s="4"/>
     </row>
-    <row r="637" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A637" s="2" t="s">
         <v>925</v>
       </c>
@@ -63581,7 +63578,7 @@
       <c r="AH637" s="4"/>
       <c r="AI637" s="4"/>
     </row>
-    <row r="638" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A638" s="2" t="s">
         <v>926</v>
       </c>
@@ -63642,7 +63639,7 @@
       <c r="AH638" s="4"/>
       <c r="AI638" s="4"/>
     </row>
-    <row r="639" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A639" s="2" t="s">
         <v>927</v>
       </c>
@@ -63703,7 +63700,7 @@
       <c r="AH639" s="4"/>
       <c r="AI639" s="4"/>
     </row>
-    <row r="640" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A640" s="2" t="s">
         <v>928</v>
       </c>
@@ -66753,7 +66750,7 @@
       <c r="AH689" s="4"/>
       <c r="AI689" s="4"/>
     </row>
-    <row r="690" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A690" s="2" t="s">
         <v>1025</v>
       </c>
@@ -66814,7 +66811,7 @@
       <c r="AH690" s="4"/>
       <c r="AI690" s="4"/>
     </row>
-    <row r="691" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A691" s="2" t="s">
         <v>1030</v>
       </c>
@@ -66875,7 +66872,7 @@
       <c r="AH691" s="4"/>
       <c r="AI691" s="4"/>
     </row>
-    <row r="692" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="692" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A692" s="2" t="s">
         <v>1032</v>
       </c>
@@ -66936,7 +66933,7 @@
       <c r="AH692" s="4"/>
       <c r="AI692" s="4"/>
     </row>
-    <row r="693" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A693" s="2" t="s">
         <v>1036</v>
       </c>
@@ -66997,7 +66994,7 @@
       <c r="AH693" s="4"/>
       <c r="AI693" s="4"/>
     </row>
-    <row r="694" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="694" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A694" s="2" t="s">
         <v>1037</v>
       </c>
@@ -67058,7 +67055,7 @@
       <c r="AH694" s="4"/>
       <c r="AI694" s="4"/>
     </row>
-    <row r="695" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="695" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A695" s="2" t="s">
         <v>1039</v>
       </c>
@@ -67119,7 +67116,7 @@
       <c r="AH695" s="4"/>
       <c r="AI695" s="4"/>
     </row>
-    <row r="696" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="696" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A696" s="2" t="s">
         <v>1042</v>
       </c>
@@ -67180,7 +67177,7 @@
       <c r="AH696" s="4"/>
       <c r="AI696" s="4"/>
     </row>
-    <row r="697" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="697" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A697" s="2" t="s">
         <v>1043</v>
       </c>
@@ -67241,7 +67238,7 @@
       <c r="AH697" s="4"/>
       <c r="AI697" s="4"/>
     </row>
-    <row r="698" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="698" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A698" s="2" t="s">
         <v>1044</v>
       </c>
@@ -67302,7 +67299,7 @@
       <c r="AH698" s="4"/>
       <c r="AI698" s="4"/>
     </row>
-    <row r="699" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="699" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A699" s="2" t="s">
         <v>1046</v>
       </c>
@@ -67363,7 +67360,7 @@
       <c r="AH699" s="4"/>
       <c r="AI699" s="4"/>
     </row>
-    <row r="700" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="700" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A700" s="2" t="s">
         <v>1050</v>
       </c>
@@ -67424,7 +67421,7 @@
       <c r="AH700" s="4"/>
       <c r="AI700" s="4"/>
     </row>
-    <row r="701" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="701" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A701" s="2" t="s">
         <v>1052</v>
       </c>
@@ -67485,7 +67482,7 @@
       <c r="AH701" s="4"/>
       <c r="AI701" s="4"/>
     </row>
-    <row r="702" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="702" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A702" s="2" t="s">
         <v>1055</v>
       </c>
@@ -67546,7 +67543,7 @@
       <c r="AH702" s="4"/>
       <c r="AI702" s="4"/>
     </row>
-    <row r="703" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="703" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A703" s="2" t="s">
         <v>1056</v>
       </c>
@@ -67607,7 +67604,7 @@
       <c r="AH703" s="4"/>
       <c r="AI703" s="4"/>
     </row>
-    <row r="704" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="704" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A704" s="2" t="s">
         <v>1059</v>
       </c>
@@ -67668,7 +67665,7 @@
       <c r="AH704" s="4"/>
       <c r="AI704" s="4"/>
     </row>
-    <row r="705" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="705" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A705" s="2" t="s">
         <v>1060</v>
       </c>
@@ -67685,7 +67682,7 @@
         <v>1034</v>
       </c>
       <c r="F705" s="4" t="s">
-        <v>6</v>
+        <v>855</v>
       </c>
       <c r="G705" s="4" t="s">
         <v>1038</v>
@@ -67729,7 +67726,7 @@
       <c r="AH705" s="4"/>
       <c r="AI705" s="4"/>
     </row>
-    <row r="706" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="706" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A706" s="2" t="s">
         <v>1061</v>
       </c>
@@ -67790,7 +67787,7 @@
       <c r="AH706" s="4"/>
       <c r="AI706" s="4"/>
     </row>
-    <row r="707" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="707" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A707" s="2" t="s">
         <v>1063</v>
       </c>
@@ -67851,7 +67848,7 @@
       <c r="AH707" s="4"/>
       <c r="AI707" s="4"/>
     </row>
-    <row r="708" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="708" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A708" s="2" t="s">
         <v>1064</v>
       </c>
@@ -67912,7 +67909,7 @@
       <c r="AH708" s="4"/>
       <c r="AI708" s="4"/>
     </row>
-    <row r="709" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="709" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A709" s="2" t="s">
         <v>1065</v>
       </c>
@@ -67973,7 +67970,7 @@
       <c r="AH709" s="4"/>
       <c r="AI709" s="4"/>
     </row>
-    <row r="710" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="710" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A710" s="2" t="s">
         <v>1069</v>
       </c>
@@ -68034,7 +68031,7 @@
       <c r="AH710" s="4"/>
       <c r="AI710" s="4"/>
     </row>
-    <row r="711" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="711" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A711" s="2" t="s">
         <v>1071</v>
       </c>
@@ -68095,7 +68092,7 @@
       <c r="AH711" s="4"/>
       <c r="AI711" s="4"/>
     </row>
-    <row r="712" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="712" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A712" s="2" t="s">
         <v>1073</v>
       </c>
@@ -79197,7 +79194,7 @@
       <c r="AH893" s="4"/>
       <c r="AI893" s="4"/>
     </row>
-    <row r="894" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="894" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A894" s="2" t="s">
         <v>1394</v>
       </c>
@@ -79258,7 +79255,7 @@
       <c r="AH894" s="4"/>
       <c r="AI894" s="4"/>
     </row>
-    <row r="895" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="895" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A895" s="2" t="s">
         <v>1397</v>
       </c>
@@ -79319,7 +79316,7 @@
       <c r="AH895" s="4"/>
       <c r="AI895" s="4"/>
     </row>
-    <row r="896" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="896" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A896" s="2" t="s">
         <v>1399</v>
       </c>
@@ -79380,7 +79377,7 @@
       <c r="AH896" s="4"/>
       <c r="AI896" s="4"/>
     </row>
-    <row r="897" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="897" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A897" s="2" t="s">
         <v>1402</v>
       </c>
@@ -79441,7 +79438,7 @@
       <c r="AH897" s="4"/>
       <c r="AI897" s="4"/>
     </row>
-    <row r="898" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="898" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A898" s="2" t="s">
         <v>1404</v>
       </c>
@@ -79502,7 +79499,7 @@
       <c r="AH898" s="4"/>
       <c r="AI898" s="4"/>
     </row>
-    <row r="899" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="899" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A899" s="2" t="s">
         <v>1406</v>
       </c>
@@ -79563,7 +79560,7 @@
       <c r="AH899" s="4"/>
       <c r="AI899" s="4"/>
     </row>
-    <row r="900" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="900" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A900" s="2" t="s">
         <v>1407</v>
       </c>
@@ -79624,7 +79621,7 @@
       <c r="AH900" s="4"/>
       <c r="AI900" s="4"/>
     </row>
-    <row r="901" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="901" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A901" s="2" t="s">
         <v>1410</v>
       </c>
@@ -79751,7 +79748,7 @@
         <v>1415</v>
       </c>
       <c r="B903" s="2" t="s">
-        <v>1416</v>
+        <v>731</v>
       </c>
       <c r="C903" s="2" t="s">
         <v>37</v>
@@ -79766,7 +79763,7 @@
         <v>734</v>
       </c>
       <c r="G903" s="4" t="s">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="H903" s="4" t="s">
         <v>47</v>
@@ -79807,9 +79804,9 @@
       <c r="AH903" s="4"/>
       <c r="AI903" s="4"/>
     </row>
-    <row r="904" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="904" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A904" s="2" t="s">
-        <v>1418</v>
+        <v>1417</v>
       </c>
       <c r="B904" s="2" t="s">
         <v>798</v>
@@ -79818,16 +79815,16 @@
         <v>37</v>
       </c>
       <c r="D904" s="4" t="s">
+        <v>1418</v>
+      </c>
+      <c r="E904" s="5" t="s">
         <v>1419</v>
-      </c>
-      <c r="E904" s="5" t="s">
-        <v>1420</v>
       </c>
       <c r="F904" s="4" t="s">
         <v>144</v>
       </c>
       <c r="G904" s="4" t="s">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="H904" s="4" t="s">
         <v>47</v>
@@ -79868,9 +79865,9 @@
       <c r="AH904" s="4"/>
       <c r="AI904" s="4"/>
     </row>
-    <row r="905" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="905" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A905" s="2" t="s">
-        <v>1422</v>
+        <v>1421</v>
       </c>
       <c r="B905" s="2" t="s">
         <v>798</v>
@@ -79879,16 +79876,16 @@
         <v>37</v>
       </c>
       <c r="D905" s="4" t="s">
+        <v>1418</v>
+      </c>
+      <c r="E905" s="5" t="s">
         <v>1419</v>
-      </c>
-      <c r="E905" s="5" t="s">
-        <v>1420</v>
       </c>
       <c r="F905" s="4" t="s">
         <v>144</v>
       </c>
       <c r="G905" s="4" t="s">
-        <v>1423</v>
+        <v>1422</v>
       </c>
       <c r="H905" s="4" t="s">
         <v>47</v>
@@ -79929,9 +79926,9 @@
       <c r="AH905" s="4"/>
       <c r="AI905" s="4"/>
     </row>
-    <row r="906" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="906" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A906" s="2" t="s">
-        <v>1424</v>
+        <v>1423</v>
       </c>
       <c r="B906" s="2" t="s">
         <v>798</v>
@@ -79940,16 +79937,16 @@
         <v>37</v>
       </c>
       <c r="D906" s="4" t="s">
+        <v>1418</v>
+      </c>
+      <c r="E906" s="5" t="s">
         <v>1419</v>
-      </c>
-      <c r="E906" s="5" t="s">
-        <v>1420</v>
       </c>
       <c r="F906" s="4" t="s">
         <v>144</v>
       </c>
       <c r="G906" s="4" t="s">
-        <v>1425</v>
+        <v>1424</v>
       </c>
       <c r="H906" s="4" t="s">
         <v>47</v>
@@ -79990,9 +79987,9 @@
       <c r="AH906" s="4"/>
       <c r="AI906" s="4"/>
     </row>
-    <row r="907" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="907" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A907" s="2" t="s">
-        <v>1426</v>
+        <v>1425</v>
       </c>
       <c r="B907" s="2" t="s">
         <v>798</v>
@@ -80001,16 +79998,16 @@
         <v>37</v>
       </c>
       <c r="D907" s="4" t="s">
+        <v>1426</v>
+      </c>
+      <c r="E907" s="5" t="s">
         <v>1427</v>
-      </c>
-      <c r="E907" s="5" t="s">
-        <v>1428</v>
       </c>
       <c r="F907" s="4" t="s">
         <v>801</v>
       </c>
       <c r="G907" s="4" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="H907" s="4" t="s">
         <v>41</v>
@@ -80051,9 +80048,9 @@
       <c r="AH907" s="4"/>
       <c r="AI907" s="4"/>
     </row>
-    <row r="908" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="908" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A908" s="2" t="s">
-        <v>1430</v>
+        <v>1429</v>
       </c>
       <c r="B908" s="2" t="s">
         <v>798</v>
@@ -80062,16 +80059,16 @@
         <v>37</v>
       </c>
       <c r="D908" s="4" t="s">
+        <v>1426</v>
+      </c>
+      <c r="E908" s="5" t="s">
         <v>1427</v>
-      </c>
-      <c r="E908" s="5" t="s">
-        <v>1428</v>
       </c>
       <c r="F908" s="4" t="s">
         <v>801</v>
       </c>
       <c r="G908" s="4" t="s">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="H908" s="4" t="s">
         <v>41</v>
@@ -80112,9 +80109,9 @@
       <c r="AH908" s="4"/>
       <c r="AI908" s="4"/>
     </row>
-    <row r="909" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="909" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A909" s="2" t="s">
-        <v>1432</v>
+        <v>1431</v>
       </c>
       <c r="B909" s="2" t="s">
         <v>798</v>
@@ -80123,16 +80120,16 @@
         <v>37</v>
       </c>
       <c r="D909" s="4" t="s">
+        <v>1426</v>
+      </c>
+      <c r="E909" s="5" t="s">
         <v>1427</v>
-      </c>
-      <c r="E909" s="5" t="s">
-        <v>1428</v>
       </c>
       <c r="F909" s="4" t="s">
         <v>801</v>
       </c>
       <c r="G909" s="4" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
       <c r="H909" s="4" t="s">
         <v>41</v>
@@ -80173,9 +80170,9 @@
       <c r="AH909" s="4"/>
       <c r="AI909" s="4"/>
     </row>
-    <row r="910" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="910" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A910" s="2" t="s">
-        <v>1434</v>
+        <v>1433</v>
       </c>
       <c r="B910" s="2" t="s">
         <v>798</v>
@@ -80184,16 +80181,16 @@
         <v>37</v>
       </c>
       <c r="D910" s="4" t="s">
+        <v>1426</v>
+      </c>
+      <c r="E910" s="5" t="s">
         <v>1427</v>
-      </c>
-      <c r="E910" s="5" t="s">
-        <v>1428</v>
       </c>
       <c r="F910" s="4" t="s">
         <v>801</v>
       </c>
       <c r="G910" s="4" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="H910" s="4" t="s">
         <v>41</v>
@@ -80234,9 +80231,9 @@
       <c r="AH910" s="4"/>
       <c r="AI910" s="4"/>
     </row>
-    <row r="911" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="911" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A911" s="2" t="s">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="B911" s="2" t="s">
         <v>798</v>
@@ -80245,16 +80242,16 @@
         <v>37</v>
       </c>
       <c r="D911" s="4" t="s">
+        <v>1436</v>
+      </c>
+      <c r="E911" s="5" t="s">
         <v>1437</v>
-      </c>
-      <c r="E911" s="5" t="s">
-        <v>1438</v>
       </c>
       <c r="F911" s="4" t="s">
         <v>855</v>
       </c>
       <c r="G911" s="4" t="s">
-        <v>1429</v>
+        <v>1428</v>
       </c>
       <c r="H911" s="4" t="s">
         <v>96</v>
@@ -80295,9 +80292,9 @@
       <c r="AH911" s="4"/>
       <c r="AI911" s="4"/>
     </row>
-    <row r="912" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="912" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A912" s="2" t="s">
-        <v>1439</v>
+        <v>1438</v>
       </c>
       <c r="B912" s="2" t="s">
         <v>798</v>
@@ -80306,16 +80303,16 @@
         <v>37</v>
       </c>
       <c r="D912" s="4" t="s">
+        <v>1436</v>
+      </c>
+      <c r="E912" s="5" t="s">
         <v>1437</v>
-      </c>
-      <c r="E912" s="5" t="s">
-        <v>1438</v>
       </c>
       <c r="F912" s="4" t="s">
         <v>855</v>
       </c>
       <c r="G912" s="4" t="s">
-        <v>1431</v>
+        <v>1430</v>
       </c>
       <c r="H912" s="4" t="s">
         <v>96</v>
@@ -80356,9 +80353,9 @@
       <c r="AH912" s="4"/>
       <c r="AI912" s="4"/>
     </row>
-    <row r="913" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="913" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A913" s="2" t="s">
-        <v>1440</v>
+        <v>1439</v>
       </c>
       <c r="B913" s="2" t="s">
         <v>798</v>
@@ -80367,16 +80364,16 @@
         <v>37</v>
       </c>
       <c r="D913" s="4" t="s">
+        <v>1436</v>
+      </c>
+      <c r="E913" s="5" t="s">
         <v>1437</v>
-      </c>
-      <c r="E913" s="5" t="s">
-        <v>1438</v>
       </c>
       <c r="F913" s="4" t="s">
         <v>855</v>
       </c>
       <c r="G913" s="4" t="s">
-        <v>1433</v>
+        <v>1432</v>
       </c>
       <c r="H913" s="4" t="s">
         <v>96</v>
@@ -80417,9 +80414,9 @@
       <c r="AH913" s="4"/>
       <c r="AI913" s="4"/>
     </row>
-    <row r="914" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="914" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A914" s="2" t="s">
-        <v>1441</v>
+        <v>1440</v>
       </c>
       <c r="B914" s="2" t="s">
         <v>798</v>
@@ -80428,16 +80425,16 @@
         <v>37</v>
       </c>
       <c r="D914" s="4" t="s">
+        <v>1436</v>
+      </c>
+      <c r="E914" s="5" t="s">
         <v>1437</v>
-      </c>
-      <c r="E914" s="5" t="s">
-        <v>1438</v>
       </c>
       <c r="F914" s="4" t="s">
         <v>855</v>
       </c>
       <c r="G914" s="4" t="s">
-        <v>1435</v>
+        <v>1434</v>
       </c>
       <c r="H914" s="4" t="s">
         <v>96</v>
@@ -80480,7 +80477,7 @@
     </row>
     <row r="915" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A915" s="2" t="s">
-        <v>1442</v>
+        <v>1441</v>
       </c>
       <c r="B915" s="2" t="s">
         <v>700</v>
@@ -80489,10 +80486,10 @@
         <v>110</v>
       </c>
       <c r="D915" s="4" t="s">
+        <v>1442</v>
+      </c>
+      <c r="E915" s="5" t="s">
         <v>1443</v>
-      </c>
-      <c r="E915" s="5" t="s">
-        <v>1444</v>
       </c>
       <c r="F915" s="4" t="s">
         <v>1364</v>
@@ -80541,7 +80538,7 @@
     </row>
     <row r="916" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A916" s="2" t="s">
-        <v>1445</v>
+        <v>1444</v>
       </c>
       <c r="B916" s="2" t="s">
         <v>700</v>
@@ -80550,10 +80547,10 @@
         <v>110</v>
       </c>
       <c r="D916" s="4" t="s">
+        <v>1442</v>
+      </c>
+      <c r="E916" s="5" t="s">
         <v>1443</v>
-      </c>
-      <c r="E916" s="5" t="s">
-        <v>1444</v>
       </c>
       <c r="F916" s="4" t="s">
         <v>1364</v>
@@ -80602,7 +80599,7 @@
     </row>
     <row r="917" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A917" s="2" t="s">
-        <v>1446</v>
+        <v>1445</v>
       </c>
       <c r="B917" s="2" t="s">
         <v>700</v>
@@ -80611,10 +80608,10 @@
         <v>110</v>
       </c>
       <c r="D917" s="4" t="s">
+        <v>1446</v>
+      </c>
+      <c r="E917" s="5" t="s">
         <v>1447</v>
-      </c>
-      <c r="E917" s="5" t="s">
-        <v>1448</v>
       </c>
       <c r="F917" s="4" t="s">
         <v>1364</v>
@@ -80663,7 +80660,7 @@
     </row>
     <row r="918" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A918" s="2" t="s">
-        <v>1449</v>
+        <v>1448</v>
       </c>
       <c r="B918" s="2" t="s">
         <v>700</v>
@@ -80672,10 +80669,10 @@
         <v>110</v>
       </c>
       <c r="D918" s="4" t="s">
+        <v>1446</v>
+      </c>
+      <c r="E918" s="5" t="s">
         <v>1447</v>
-      </c>
-      <c r="E918" s="5" t="s">
-        <v>1448</v>
       </c>
       <c r="F918" s="4" t="s">
         <v>1364</v>
@@ -80724,7 +80721,7 @@
     </row>
     <row r="919" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A919" s="2" t="s">
-        <v>1450</v>
+        <v>1449</v>
       </c>
       <c r="B919" s="2" t="s">
         <v>700</v>
@@ -80733,10 +80730,10 @@
         <v>110</v>
       </c>
       <c r="D919" s="4" t="s">
+        <v>1450</v>
+      </c>
+      <c r="E919" s="5" t="s">
         <v>1451</v>
-      </c>
-      <c r="E919" s="5" t="s">
-        <v>1452</v>
       </c>
       <c r="F919" s="4" t="s">
         <v>710</v>
@@ -80785,7 +80782,7 @@
     </row>
     <row r="920" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A920" s="2" t="s">
-        <v>1453</v>
+        <v>1452</v>
       </c>
       <c r="B920" s="2" t="s">
         <v>700</v>
@@ -80794,10 +80791,10 @@
         <v>110</v>
       </c>
       <c r="D920" s="4" t="s">
+        <v>1450</v>
+      </c>
+      <c r="E920" s="5" t="s">
         <v>1451</v>
-      </c>
-      <c r="E920" s="5" t="s">
-        <v>1452</v>
       </c>
       <c r="F920" s="4" t="s">
         <v>710</v>
@@ -80846,7 +80843,7 @@
     </row>
     <row r="921" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A921" s="2" t="s">
-        <v>1454</v>
+        <v>1453</v>
       </c>
       <c r="B921" s="2" t="s">
         <v>700</v>
@@ -80855,10 +80852,10 @@
         <v>110</v>
       </c>
       <c r="D921" s="4" t="s">
+        <v>1450</v>
+      </c>
+      <c r="E921" s="5" t="s">
         <v>1451</v>
-      </c>
-      <c r="E921" s="5" t="s">
-        <v>1452</v>
       </c>
       <c r="F921" s="4" t="s">
         <v>710</v>
@@ -80907,9 +80904,9 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:R921" xr:uid="{00000000-0009-0000-0000-000000000000}">
-    <filterColumn colId="4">
+    <filterColumn colId="1">
       <filters>
-        <filter val="CARDIO"/>
+        <filter val="MEIA"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -80987,10 +80984,10 @@
         <v>593</v>
       </c>
       <c r="D2" s="4" t="s">
+        <v>1454</v>
+      </c>
+      <c r="E2" s="5" t="s">
         <v>1455</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>1456</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>710</v>
@@ -81029,10 +81026,10 @@
         <v>593</v>
       </c>
       <c r="D3" s="4" t="s">
+        <v>1456</v>
+      </c>
+      <c r="E3" s="5" t="s">
         <v>1457</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>1458</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>710</v>
@@ -81071,16 +81068,16 @@
         <v>37</v>
       </c>
       <c r="D4" s="4" t="s">
+        <v>1458</v>
+      </c>
+      <c r="E4" s="5" t="s">
         <v>1459</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>1460</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>1145</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
       <c r="H4" s="4" t="s">
         <v>41</v>
@@ -81113,10 +81110,10 @@
         <v>37</v>
       </c>
       <c r="D5" s="4" t="s">
+        <v>1458</v>
+      </c>
+      <c r="E5" s="5" t="s">
         <v>1459</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>1460</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>1145</v>
@@ -81155,16 +81152,16 @@
         <v>37</v>
       </c>
       <c r="D6" s="4" t="s">
+        <v>1461</v>
+      </c>
+      <c r="E6" s="5" t="s">
         <v>1462</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>1463</v>
       </c>
       <c r="F6" s="4" t="s">
         <v>1145</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
       <c r="H6" s="4" t="s">
         <v>41</v>
@@ -81197,16 +81194,16 @@
         <v>37</v>
       </c>
       <c r="D7" s="4" t="s">
+        <v>1461</v>
+      </c>
+      <c r="E7" s="5" t="s">
         <v>1462</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>1463</v>
       </c>
       <c r="F7" s="4" t="s">
         <v>1145</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="H7" s="4" t="s">
         <v>41</v>
@@ -81239,10 +81236,10 @@
         <v>37</v>
       </c>
       <c r="D8" s="4" t="s">
+        <v>1461</v>
+      </c>
+      <c r="E8" s="5" t="s">
         <v>1462</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>1463</v>
       </c>
       <c r="F8" s="4" t="s">
         <v>1145</v>
@@ -81281,16 +81278,16 @@
         <v>37</v>
       </c>
       <c r="D9" s="4" t="s">
+        <v>1465</v>
+      </c>
+      <c r="E9" s="5" t="s">
         <v>1466</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>1467</v>
       </c>
       <c r="F9" s="4" t="s">
         <v>1145</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
       <c r="H9" s="4" t="s">
         <v>41</v>
@@ -81323,16 +81320,16 @@
         <v>37</v>
       </c>
       <c r="D10" s="4" t="s">
+        <v>1465</v>
+      </c>
+      <c r="E10" s="5" t="s">
         <v>1466</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>1467</v>
       </c>
       <c r="F10" s="4" t="s">
         <v>1145</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="H10" s="4" t="s">
         <v>41</v>
@@ -81365,16 +81362,16 @@
         <v>37</v>
       </c>
       <c r="D11" s="4" t="s">
+        <v>1465</v>
+      </c>
+      <c r="E11" s="5" t="s">
         <v>1466</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>1467</v>
       </c>
       <c r="F11" s="4" t="s">
         <v>1145</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
       <c r="H11" s="4" t="s">
         <v>41</v>
@@ -81407,10 +81404,10 @@
         <v>37</v>
       </c>
       <c r="D12" s="4" t="s">
+        <v>1465</v>
+      </c>
+      <c r="E12" s="5" t="s">
         <v>1466</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>1467</v>
       </c>
       <c r="F12" s="4" t="s">
         <v>1145</v>
@@ -81449,10 +81446,10 @@
         <v>37</v>
       </c>
       <c r="D13" s="4" t="s">
+        <v>1468</v>
+      </c>
+      <c r="E13" s="5" t="s">
         <v>1469</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>1470</v>
       </c>
       <c r="F13" s="4" t="s">
         <v>1145</v>
@@ -81491,16 +81488,16 @@
         <v>37</v>
       </c>
       <c r="D14" s="4" t="s">
+        <v>1468</v>
+      </c>
+      <c r="E14" s="5" t="s">
         <v>1469</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>1470</v>
       </c>
       <c r="F14" s="4" t="s">
         <v>1145</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
       <c r="H14" s="4" t="s">
         <v>41</v>
@@ -81533,16 +81530,16 @@
         <v>37</v>
       </c>
       <c r="D15" s="4" t="s">
+        <v>1468</v>
+      </c>
+      <c r="E15" s="5" t="s">
         <v>1469</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>1470</v>
       </c>
       <c r="F15" s="4" t="s">
         <v>1145</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="H15" s="4" t="s">
         <v>41</v>
@@ -81575,16 +81572,16 @@
         <v>37</v>
       </c>
       <c r="D16" s="4" t="s">
+        <v>1470</v>
+      </c>
+      <c r="E16" s="5" t="s">
         <v>1471</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>1472</v>
       </c>
       <c r="F16" s="4" t="s">
         <v>1145</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
       <c r="H16" s="4" t="s">
         <v>41</v>
@@ -81617,16 +81614,16 @@
         <v>37</v>
       </c>
       <c r="D17" s="4" t="s">
+        <v>1470</v>
+      </c>
+      <c r="E17" s="5" t="s">
         <v>1471</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>1472</v>
       </c>
       <c r="F17" s="4" t="s">
         <v>1145</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>1465</v>
+        <v>1464</v>
       </c>
       <c r="H17" s="4" t="s">
         <v>41</v>
@@ -81659,10 +81656,10 @@
         <v>37</v>
       </c>
       <c r="D18" s="4" t="s">
+        <v>1472</v>
+      </c>
+      <c r="E18" s="5" t="s">
         <v>1473</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>1474</v>
       </c>
       <c r="F18" s="4" t="s">
         <v>1145</v>
@@ -81701,16 +81698,16 @@
         <v>37</v>
       </c>
       <c r="D19" s="4" t="s">
+        <v>1472</v>
+      </c>
+      <c r="E19" s="5" t="s">
         <v>1473</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>1474</v>
       </c>
       <c r="F19" s="4" t="s">
         <v>1145</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
       <c r="H19" s="4" t="s">
         <v>41</v>
@@ -81743,10 +81740,10 @@
         <v>37</v>
       </c>
       <c r="D20" s="4" t="s">
+        <v>1474</v>
+      </c>
+      <c r="E20" s="5" t="s">
         <v>1475</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>1476</v>
       </c>
       <c r="F20" s="4" t="s">
         <v>1145</v>
@@ -81785,10 +81782,10 @@
         <v>37</v>
       </c>
       <c r="D21" s="4" t="s">
+        <v>1474</v>
+      </c>
+      <c r="E21" s="5" t="s">
         <v>1475</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>1476</v>
       </c>
       <c r="F21" s="4" t="s">
         <v>1145</v>
@@ -81827,10 +81824,10 @@
         <v>37</v>
       </c>
       <c r="D22" s="4" t="s">
+        <v>1476</v>
+      </c>
+      <c r="E22" s="5" t="s">
         <v>1477</v>
-      </c>
-      <c r="E22" s="5" t="s">
-        <v>1478</v>
       </c>
       <c r="F22" s="4" t="s">
         <v>1145</v>
@@ -81869,16 +81866,16 @@
         <v>37</v>
       </c>
       <c r="D23" s="4" t="s">
+        <v>1476</v>
+      </c>
+      <c r="E23" s="5" t="s">
         <v>1477</v>
-      </c>
-      <c r="E23" s="5" t="s">
-        <v>1478</v>
       </c>
       <c r="F23" s="4" t="s">
         <v>1145</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>1468</v>
+        <v>1467</v>
       </c>
       <c r="H23" s="4" t="s">
         <v>96</v>
@@ -81911,16 +81908,16 @@
         <v>37</v>
       </c>
       <c r="D24" s="4" t="s">
+        <v>1476</v>
+      </c>
+      <c r="E24" s="5" t="s">
         <v>1477</v>
-      </c>
-      <c r="E24" s="5" t="s">
-        <v>1478</v>
       </c>
       <c r="F24" s="4" t="s">
         <v>1145</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>1464</v>
+        <v>1463</v>
       </c>
       <c r="H24" s="4" t="s">
         <v>96</v>
@@ -81953,16 +81950,16 @@
         <v>37</v>
       </c>
       <c r="D25" s="4" t="s">
+        <v>1476</v>
+      </c>
+      <c r="E25" s="5" t="s">
         <v>1477</v>
-      </c>
-      <c r="E25" s="5" t="s">
-        <v>1478</v>
       </c>
       <c r="F25" s="4" t="s">
         <v>1145</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="H25" s="4" t="s">
         <v>96</v>
@@ -81995,16 +81992,16 @@
         <v>37</v>
       </c>
       <c r="D26" s="4" t="s">
+        <v>1479</v>
+      </c>
+      <c r="E26" s="5" t="s">
         <v>1480</v>
-      </c>
-      <c r="E26" s="5" t="s">
-        <v>1481</v>
       </c>
       <c r="F26" s="4" t="s">
         <v>1145</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
       <c r="H26" s="4" t="s">
         <v>96</v>
@@ -82037,16 +82034,16 @@
         <v>37</v>
       </c>
       <c r="D27" s="4" t="s">
+        <v>1479</v>
+      </c>
+      <c r="E27" s="5" t="s">
         <v>1480</v>
-      </c>
-      <c r="E27" s="5" t="s">
-        <v>1481</v>
       </c>
       <c r="F27" s="4" t="s">
         <v>1145</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>1479</v>
+        <v>1478</v>
       </c>
       <c r="H27" s="4" t="s">
         <v>96</v>
@@ -82079,16 +82076,16 @@
         <v>37</v>
       </c>
       <c r="D28" s="4" t="s">
+        <v>1479</v>
+      </c>
+      <c r="E28" s="5" t="s">
         <v>1480</v>
-      </c>
-      <c r="E28" s="5" t="s">
-        <v>1481</v>
       </c>
       <c r="F28" s="4" t="s">
         <v>1145</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>1482</v>
+        <v>1481</v>
       </c>
       <c r="H28" s="4" t="s">
         <v>96</v>
@@ -82121,10 +82118,10 @@
         <v>37</v>
       </c>
       <c r="D29" s="4" t="s">
+        <v>1479</v>
+      </c>
+      <c r="E29" s="5" t="s">
         <v>1480</v>
-      </c>
-      <c r="E29" s="5" t="s">
-        <v>1481</v>
       </c>
       <c r="F29" s="4" t="s">
         <v>1145</v>
@@ -82163,10 +82160,10 @@
         <v>37</v>
       </c>
       <c r="D30" s="4" t="s">
+        <v>1482</v>
+      </c>
+      <c r="E30" s="5" t="s">
         <v>1483</v>
-      </c>
-      <c r="E30" s="5" t="s">
-        <v>1484</v>
       </c>
       <c r="F30" s="4" t="s">
         <v>1145</v>
@@ -82205,10 +82202,10 @@
         <v>37</v>
       </c>
       <c r="D31" s="4" t="s">
+        <v>1482</v>
+      </c>
+      <c r="E31" s="5" t="s">
         <v>1483</v>
-      </c>
-      <c r="E31" s="5" t="s">
-        <v>1484</v>
       </c>
       <c r="F31" s="4" t="s">
         <v>1145</v>
@@ -82247,16 +82244,16 @@
         <v>37</v>
       </c>
       <c r="D32" s="4" t="s">
+        <v>1482</v>
+      </c>
+      <c r="E32" s="5" t="s">
         <v>1483</v>
-      </c>
-      <c r="E32" s="5" t="s">
-        <v>1484</v>
       </c>
       <c r="F32" s="4" t="s">
         <v>1145</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>1461</v>
+        <v>1460</v>
       </c>
       <c r="H32" s="4" t="s">
         <v>96</v>
@@ -82289,10 +82286,10 @@
         <v>37</v>
       </c>
       <c r="D33" s="4" t="s">
+        <v>1484</v>
+      </c>
+      <c r="E33" s="5" t="s">
         <v>1485</v>
-      </c>
-      <c r="E33" s="5" t="s">
-        <v>1486</v>
       </c>
       <c r="F33" s="4" t="s">
         <v>6</v>
@@ -82331,10 +82328,10 @@
         <v>37</v>
       </c>
       <c r="D34" s="4" t="s">
+        <v>1486</v>
+      </c>
+      <c r="E34" s="5" t="s">
         <v>1487</v>
-      </c>
-      <c r="E34" s="5" t="s">
-        <v>1488</v>
       </c>
       <c r="F34" s="4" t="s">
         <v>1145</v>
@@ -82373,10 +82370,10 @@
         <v>37</v>
       </c>
       <c r="D35" s="4" t="s">
+        <v>1486</v>
+      </c>
+      <c r="E35" s="5" t="s">
         <v>1487</v>
-      </c>
-      <c r="E35" s="5" t="s">
-        <v>1488</v>
       </c>
       <c r="F35" s="4" t="s">
         <v>1145</v>
@@ -82415,10 +82412,10 @@
         <v>37</v>
       </c>
       <c r="D36" s="4" t="s">
+        <v>1488</v>
+      </c>
+      <c r="E36" s="5" t="s">
         <v>1489</v>
-      </c>
-      <c r="E36" s="5" t="s">
-        <v>1490</v>
       </c>
       <c r="F36" s="4" t="s">
         <v>734</v>
@@ -82457,10 +82454,10 @@
         <v>37</v>
       </c>
       <c r="D37" s="4" t="s">
+        <v>1488</v>
+      </c>
+      <c r="E37" s="5" t="s">
         <v>1489</v>
-      </c>
-      <c r="E37" s="5" t="s">
-        <v>1490</v>
       </c>
       <c r="F37" s="4" t="s">
         <v>734</v>
@@ -82499,10 +82496,10 @@
         <v>37</v>
       </c>
       <c r="D38" s="4" t="s">
+        <v>1490</v>
+      </c>
+      <c r="E38" s="5" t="s">
         <v>1491</v>
-      </c>
-      <c r="E38" s="5" t="s">
-        <v>1492</v>
       </c>
       <c r="F38" s="4" t="s">
         <v>1145</v>
@@ -82541,10 +82538,10 @@
         <v>37</v>
       </c>
       <c r="D39" s="4" t="s">
+        <v>1490</v>
+      </c>
+      <c r="E39" s="5" t="s">
         <v>1491</v>
-      </c>
-      <c r="E39" s="5" t="s">
-        <v>1492</v>
       </c>
       <c r="F39" s="4" t="s">
         <v>1145</v>
@@ -82583,10 +82580,10 @@
         <v>37</v>
       </c>
       <c r="D40" s="4" t="s">
+        <v>1492</v>
+      </c>
+      <c r="E40" s="5" t="s">
         <v>1493</v>
-      </c>
-      <c r="E40" s="5" t="s">
-        <v>1494</v>
       </c>
       <c r="F40" s="4" t="s">
         <v>1145</v>
@@ -82625,16 +82622,16 @@
         <v>37</v>
       </c>
       <c r="D41" s="4" t="s">
+        <v>1492</v>
+      </c>
+      <c r="E41" s="5" t="s">
         <v>1493</v>
-      </c>
-      <c r="E41" s="5" t="s">
-        <v>1494</v>
       </c>
       <c r="F41" s="4" t="s">
         <v>1145</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="H41" s="4" t="s">
         <v>41</v>
@@ -82667,10 +82664,10 @@
         <v>37</v>
       </c>
       <c r="D42" s="4" t="s">
+        <v>1495</v>
+      </c>
+      <c r="E42" s="5" t="s">
         <v>1496</v>
-      </c>
-      <c r="E42" s="5" t="s">
-        <v>1497</v>
       </c>
       <c r="F42" s="4" t="s">
         <v>1145</v>
@@ -82709,10 +82706,10 @@
         <v>37</v>
       </c>
       <c r="D43" s="4" t="s">
+        <v>1495</v>
+      </c>
+      <c r="E43" s="5" t="s">
         <v>1496</v>
-      </c>
-      <c r="E43" s="5" t="s">
-        <v>1497</v>
       </c>
       <c r="F43" s="4" t="s">
         <v>1145</v>
@@ -82751,16 +82748,16 @@
         <v>37</v>
       </c>
       <c r="D44" s="4" t="s">
+        <v>1497</v>
+      </c>
+      <c r="E44" s="5" t="s">
         <v>1498</v>
-      </c>
-      <c r="E44" s="5" t="s">
-        <v>1499</v>
       </c>
       <c r="F44" s="4" t="s">
         <v>1145</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>1425</v>
+        <v>1424</v>
       </c>
       <c r="H44" s="4" t="s">
         <v>41</v>
@@ -82793,10 +82790,10 @@
         <v>37</v>
       </c>
       <c r="D45" s="4" t="s">
+        <v>1497</v>
+      </c>
+      <c r="E45" s="5" t="s">
         <v>1498</v>
-      </c>
-      <c r="E45" s="5" t="s">
-        <v>1499</v>
       </c>
       <c r="F45" s="4" t="s">
         <v>1145</v>
@@ -82835,10 +82832,10 @@
         <v>37</v>
       </c>
       <c r="D46" s="4" t="s">
+        <v>1499</v>
+      </c>
+      <c r="E46" s="5" t="s">
         <v>1500</v>
-      </c>
-      <c r="E46" s="5" t="s">
-        <v>1501</v>
       </c>
       <c r="F46" s="4" t="s">
         <v>1145</v>
@@ -82877,16 +82874,16 @@
         <v>37</v>
       </c>
       <c r="D47" s="4" t="s">
+        <v>1499</v>
+      </c>
+      <c r="E47" s="5" t="s">
         <v>1500</v>
-      </c>
-      <c r="E47" s="5" t="s">
-        <v>1501</v>
       </c>
       <c r="F47" s="4" t="s">
         <v>1145</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="H47" s="4" t="s">
         <v>41</v>
@@ -82919,10 +82916,10 @@
         <v>37</v>
       </c>
       <c r="D48" s="4" t="s">
+        <v>1499</v>
+      </c>
+      <c r="E48" s="5" t="s">
         <v>1500</v>
-      </c>
-      <c r="E48" s="5" t="s">
-        <v>1501</v>
       </c>
       <c r="F48" s="4" t="s">
         <v>1145</v>
@@ -82961,10 +82958,10 @@
         <v>37</v>
       </c>
       <c r="D49" s="4" t="s">
+        <v>1501</v>
+      </c>
+      <c r="E49" s="5" t="s">
         <v>1502</v>
-      </c>
-      <c r="E49" s="5" t="s">
-        <v>1503</v>
       </c>
       <c r="F49" s="4" t="s">
         <v>1145</v>
@@ -83003,10 +83000,10 @@
         <v>37</v>
       </c>
       <c r="D50" s="4" t="s">
+        <v>1501</v>
+      </c>
+      <c r="E50" s="5" t="s">
         <v>1502</v>
-      </c>
-      <c r="E50" s="5" t="s">
-        <v>1503</v>
       </c>
       <c r="F50" s="4" t="s">
         <v>1145</v>
@@ -83045,10 +83042,10 @@
         <v>37</v>
       </c>
       <c r="D51" s="4" t="s">
+        <v>1503</v>
+      </c>
+      <c r="E51" s="5" t="s">
         <v>1504</v>
-      </c>
-      <c r="E51" s="5" t="s">
-        <v>1505</v>
       </c>
       <c r="F51" s="4" t="s">
         <v>1145</v>
@@ -83087,16 +83084,16 @@
         <v>37</v>
       </c>
       <c r="D52" s="4" t="s">
+        <v>1503</v>
+      </c>
+      <c r="E52" s="5" t="s">
         <v>1504</v>
-      </c>
-      <c r="E52" s="5" t="s">
-        <v>1505</v>
       </c>
       <c r="F52" s="4" t="s">
         <v>1145</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>1495</v>
+        <v>1494</v>
       </c>
       <c r="H52" s="4" t="s">
         <v>41</v>
@@ -83129,10 +83126,10 @@
         <v>37</v>
       </c>
       <c r="D53" s="4" t="s">
+        <v>1505</v>
+      </c>
+      <c r="E53" s="5" t="s">
         <v>1506</v>
-      </c>
-      <c r="E53" s="5" t="s">
-        <v>1507</v>
       </c>
       <c r="F53" s="4" t="s">
         <v>1145</v>
@@ -83171,10 +83168,10 @@
         <v>37</v>
       </c>
       <c r="D54" s="4" t="s">
+        <v>1505</v>
+      </c>
+      <c r="E54" s="5" t="s">
         <v>1506</v>
-      </c>
-      <c r="E54" s="5" t="s">
-        <v>1507</v>
       </c>
       <c r="F54" s="4" t="s">
         <v>1145</v>
@@ -83213,10 +83210,10 @@
         <v>37</v>
       </c>
       <c r="D55" s="4" t="s">
+        <v>1507</v>
+      </c>
+      <c r="E55" s="5" t="s">
         <v>1508</v>
-      </c>
-      <c r="E55" s="5" t="s">
-        <v>1509</v>
       </c>
       <c r="F55" s="4" t="s">
         <v>1145</v>
@@ -83255,16 +83252,16 @@
         <v>37</v>
       </c>
       <c r="D56" s="4" t="s">
+        <v>1509</v>
+      </c>
+      <c r="E56" s="5" t="s">
         <v>1510</v>
-      </c>
-      <c r="E56" s="5" t="s">
-        <v>1511</v>
       </c>
       <c r="F56" s="4" t="s">
         <v>1145</v>
       </c>
       <c r="G56" s="4" t="s">
-        <v>1425</v>
+        <v>1424</v>
       </c>
       <c r="H56" s="4" t="s">
         <v>96</v>
@@ -83297,10 +83294,10 @@
         <v>37</v>
       </c>
       <c r="D57" s="4" t="s">
+        <v>1509</v>
+      </c>
+      <c r="E57" s="5" t="s">
         <v>1510</v>
-      </c>
-      <c r="E57" s="5" t="s">
-        <v>1511</v>
       </c>
       <c r="F57" s="4" t="s">
         <v>1145</v>
@@ -83339,10 +83336,10 @@
         <v>37</v>
       </c>
       <c r="D58" s="4" t="s">
+        <v>1511</v>
+      </c>
+      <c r="E58" s="5" t="s">
         <v>1512</v>
-      </c>
-      <c r="E58" s="5" t="s">
-        <v>1513</v>
       </c>
       <c r="F58" s="4" t="s">
         <v>1145</v>
@@ -83381,10 +83378,10 @@
         <v>37</v>
       </c>
       <c r="D59" s="4" t="s">
+        <v>1511</v>
+      </c>
+      <c r="E59" s="5" t="s">
         <v>1512</v>
-      </c>
-      <c r="E59" s="5" t="s">
-        <v>1513</v>
       </c>
       <c r="F59" s="4" t="s">
         <v>1145</v>
@@ -83423,10 +83420,10 @@
         <v>37</v>
       </c>
       <c r="D60" s="4" t="s">
+        <v>1511</v>
+      </c>
+      <c r="E60" s="5" t="s">
         <v>1512</v>
-      </c>
-      <c r="E60" s="5" t="s">
-        <v>1513</v>
       </c>
       <c r="F60" s="4" t="s">
         <v>1145</v>
@@ -83465,10 +83462,10 @@
         <v>37</v>
       </c>
       <c r="D61" s="4" t="s">
+        <v>1513</v>
+      </c>
+      <c r="E61" s="5" t="s">
         <v>1514</v>
-      </c>
-      <c r="E61" s="5" t="s">
-        <v>1515</v>
       </c>
       <c r="F61" s="4" t="s">
         <v>1145</v>
@@ -83507,10 +83504,10 @@
         <v>37</v>
       </c>
       <c r="D62" s="4" t="s">
+        <v>1513</v>
+      </c>
+      <c r="E62" s="5" t="s">
         <v>1514</v>
-      </c>
-      <c r="E62" s="5" t="s">
-        <v>1515</v>
       </c>
       <c r="F62" s="4" t="s">
         <v>1145</v>
@@ -83549,10 +83546,10 @@
         <v>37</v>
       </c>
       <c r="D63" s="4" t="s">
+        <v>1515</v>
+      </c>
+      <c r="E63" s="5" t="s">
         <v>1516</v>
-      </c>
-      <c r="E63" s="5" t="s">
-        <v>1517</v>
       </c>
       <c r="F63" s="4" t="s">
         <v>1145</v>
@@ -83591,10 +83588,10 @@
         <v>37</v>
       </c>
       <c r="D64" s="4" t="s">
+        <v>1515</v>
+      </c>
+      <c r="E64" s="5" t="s">
         <v>1516</v>
-      </c>
-      <c r="E64" s="5" t="s">
-        <v>1517</v>
       </c>
       <c r="F64" s="4" t="s">
         <v>1145</v>
@@ -83633,10 +83630,10 @@
         <v>37</v>
       </c>
       <c r="D65" s="4" t="s">
+        <v>1517</v>
+      </c>
+      <c r="E65" s="5" t="s">
         <v>1518</v>
-      </c>
-      <c r="E65" s="5" t="s">
-        <v>1519</v>
       </c>
       <c r="F65" s="4" t="s">
         <v>1145</v>
@@ -83675,10 +83672,10 @@
         <v>37</v>
       </c>
       <c r="D66" s="4" t="s">
+        <v>1517</v>
+      </c>
+      <c r="E66" s="5" t="s">
         <v>1518</v>
-      </c>
-      <c r="E66" s="5" t="s">
-        <v>1519</v>
       </c>
       <c r="F66" s="4" t="s">
         <v>1145</v>
@@ -83717,10 +83714,10 @@
         <v>37</v>
       </c>
       <c r="D67" s="4" t="s">
+        <v>1519</v>
+      </c>
+      <c r="E67" s="5" t="s">
         <v>1520</v>
-      </c>
-      <c r="E67" s="5" t="s">
-        <v>1521</v>
       </c>
       <c r="F67" s="4" t="s">
         <v>1145</v>
@@ -83759,10 +83756,10 @@
         <v>37</v>
       </c>
       <c r="D68" s="4" t="s">
+        <v>1521</v>
+      </c>
+      <c r="E68" s="5" t="s">
         <v>1522</v>
-      </c>
-      <c r="E68" s="5" t="s">
-        <v>1523</v>
       </c>
       <c r="F68" s="4" t="s">
         <v>1145</v>
@@ -83801,10 +83798,10 @@
         <v>37</v>
       </c>
       <c r="D69" s="4" t="s">
+        <v>1523</v>
+      </c>
+      <c r="E69" s="5" t="s">
         <v>1524</v>
-      </c>
-      <c r="E69" s="5" t="s">
-        <v>1525</v>
       </c>
       <c r="F69" s="4" t="s">
         <v>1145</v>
@@ -83843,10 +83840,10 @@
         <v>37</v>
       </c>
       <c r="D70" s="4" t="s">
+        <v>1523</v>
+      </c>
+      <c r="E70" s="5" t="s">
         <v>1524</v>
-      </c>
-      <c r="E70" s="5" t="s">
-        <v>1525</v>
       </c>
       <c r="F70" s="4" t="s">
         <v>1145</v>
@@ -83885,10 +83882,10 @@
         <v>37</v>
       </c>
       <c r="D71" s="4" t="s">
+        <v>1525</v>
+      </c>
+      <c r="E71" s="5" t="s">
         <v>1526</v>
-      </c>
-      <c r="E71" s="5" t="s">
-        <v>1527</v>
       </c>
       <c r="F71" s="4" t="s">
         <v>1145</v>
@@ -83927,16 +83924,16 @@
         <v>37</v>
       </c>
       <c r="D72" s="4" t="s">
+        <v>1525</v>
+      </c>
+      <c r="E72" s="5" t="s">
         <v>1526</v>
-      </c>
-      <c r="E72" s="5" t="s">
-        <v>1527</v>
       </c>
       <c r="F72" s="4" t="s">
         <v>1145</v>
       </c>
       <c r="G72" s="4" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
       <c r="H72" s="4" t="s">
         <v>41</v>
@@ -83969,10 +83966,10 @@
         <v>37</v>
       </c>
       <c r="D73" s="4" t="s">
+        <v>1528</v>
+      </c>
+      <c r="E73" s="5" t="s">
         <v>1529</v>
-      </c>
-      <c r="E73" s="5" t="s">
-        <v>1530</v>
       </c>
       <c r="F73" s="4" t="s">
         <v>1145</v>
@@ -84011,10 +84008,10 @@
         <v>37</v>
       </c>
       <c r="D74" s="4" t="s">
+        <v>1528</v>
+      </c>
+      <c r="E74" s="5" t="s">
         <v>1529</v>
-      </c>
-      <c r="E74" s="5" t="s">
-        <v>1530</v>
       </c>
       <c r="F74" s="4" t="s">
         <v>1145</v>
@@ -84053,10 +84050,10 @@
         <v>37</v>
       </c>
       <c r="D75" s="4" t="s">
+        <v>1530</v>
+      </c>
+      <c r="E75" s="5" t="s">
         <v>1531</v>
-      </c>
-      <c r="E75" s="5" t="s">
-        <v>1532</v>
       </c>
       <c r="F75" s="4" t="s">
         <v>1145</v>
@@ -84095,10 +84092,10 @@
         <v>37</v>
       </c>
       <c r="D76" s="4" t="s">
+        <v>1530</v>
+      </c>
+      <c r="E76" s="5" t="s">
         <v>1531</v>
-      </c>
-      <c r="E76" s="5" t="s">
-        <v>1532</v>
       </c>
       <c r="F76" s="4" t="s">
         <v>1145</v>
@@ -84137,10 +84134,10 @@
         <v>37</v>
       </c>
       <c r="D77" s="4" t="s">
+        <v>1530</v>
+      </c>
+      <c r="E77" s="5" t="s">
         <v>1531</v>
-      </c>
-      <c r="E77" s="5" t="s">
-        <v>1532</v>
       </c>
       <c r="F77" s="4" t="s">
         <v>1145</v>
@@ -84179,10 +84176,10 @@
         <v>37</v>
       </c>
       <c r="D78" s="4" t="s">
+        <v>1532</v>
+      </c>
+      <c r="E78" s="5" t="s">
         <v>1533</v>
-      </c>
-      <c r="E78" s="5" t="s">
-        <v>1534</v>
       </c>
       <c r="F78" s="4" t="s">
         <v>1145</v>
@@ -84221,10 +84218,10 @@
         <v>37</v>
       </c>
       <c r="D79" s="4" t="s">
+        <v>1532</v>
+      </c>
+      <c r="E79" s="5" t="s">
         <v>1533</v>
-      </c>
-      <c r="E79" s="5" t="s">
-        <v>1534</v>
       </c>
       <c r="F79" s="4" t="s">
         <v>1145</v>
@@ -84263,10 +84260,10 @@
         <v>37</v>
       </c>
       <c r="D80" s="4" t="s">
+        <v>1534</v>
+      </c>
+      <c r="E80" s="5" t="s">
         <v>1535</v>
-      </c>
-      <c r="E80" s="5" t="s">
-        <v>1536</v>
       </c>
       <c r="F80" s="4" t="s">
         <v>1145</v>
@@ -84305,16 +84302,16 @@
         <v>37</v>
       </c>
       <c r="D81" s="4" t="s">
+        <v>1534</v>
+      </c>
+      <c r="E81" s="5" t="s">
         <v>1535</v>
-      </c>
-      <c r="E81" s="5" t="s">
-        <v>1536</v>
       </c>
       <c r="F81" s="4" t="s">
         <v>1145</v>
       </c>
       <c r="G81" s="4" t="s">
-        <v>1528</v>
+        <v>1527</v>
       </c>
       <c r="H81" s="4" t="s">
         <v>96</v>
@@ -84347,10 +84344,10 @@
         <v>37</v>
       </c>
       <c r="D82" s="4" t="s">
+        <v>1536</v>
+      </c>
+      <c r="E82" s="5" t="s">
         <v>1537</v>
-      </c>
-      <c r="E82" s="5" t="s">
-        <v>1538</v>
       </c>
       <c r="F82" s="4" t="s">
         <v>1145</v>
@@ -84389,10 +84386,10 @@
         <v>37</v>
       </c>
       <c r="D83" s="4" t="s">
+        <v>1536</v>
+      </c>
+      <c r="E83" s="5" t="s">
         <v>1537</v>
-      </c>
-      <c r="E83" s="5" t="s">
-        <v>1538</v>
       </c>
       <c r="F83" s="4" t="s">
         <v>1145</v>
@@ -84431,10 +84428,10 @@
         <v>37</v>
       </c>
       <c r="D84" s="4" t="s">
+        <v>1538</v>
+      </c>
+      <c r="E84" s="5" t="s">
         <v>1539</v>
-      </c>
-      <c r="E84" s="5" t="s">
-        <v>1540</v>
       </c>
       <c r="F84" s="4" t="s">
         <v>734</v>
@@ -84473,10 +84470,10 @@
         <v>37</v>
       </c>
       <c r="D85" s="4" t="s">
+        <v>1538</v>
+      </c>
+      <c r="E85" s="5" t="s">
         <v>1539</v>
-      </c>
-      <c r="E85" s="5" t="s">
-        <v>1540</v>
       </c>
       <c r="F85" s="4" t="s">
         <v>734</v>
@@ -84515,10 +84512,10 @@
         <v>593</v>
       </c>
       <c r="D86" s="4" t="s">
+        <v>1540</v>
+      </c>
+      <c r="E86" s="5" t="s">
         <v>1541</v>
-      </c>
-      <c r="E86" s="5" t="s">
-        <v>1542</v>
       </c>
       <c r="F86" s="4" t="s">
         <v>710</v>
@@ -84557,10 +84554,10 @@
         <v>593</v>
       </c>
       <c r="D87" s="4" t="s">
+        <v>1540</v>
+      </c>
+      <c r="E87" s="5" t="s">
         <v>1541</v>
-      </c>
-      <c r="E87" s="5" t="s">
-        <v>1542</v>
       </c>
       <c r="F87" s="4" t="s">
         <v>710</v>
@@ -84599,10 +84596,10 @@
         <v>593</v>
       </c>
       <c r="D88" s="4" t="s">
+        <v>1542</v>
+      </c>
+      <c r="E88" s="5" t="s">
         <v>1543</v>
-      </c>
-      <c r="E88" s="5" t="s">
-        <v>1544</v>
       </c>
       <c r="F88" s="4" t="s">
         <v>710</v>
@@ -84641,10 +84638,10 @@
         <v>593</v>
       </c>
       <c r="D89" s="4" t="s">
+        <v>1542</v>
+      </c>
+      <c r="E89" s="5" t="s">
         <v>1543</v>
-      </c>
-      <c r="E89" s="5" t="s">
-        <v>1544</v>
       </c>
       <c r="F89" s="4" t="s">
         <v>710</v>

--- a/Produtos.xlsx
+++ b/Produtos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\NOT-MARCOS\Documents\GitHub\Catalogo-Olympikus_2.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAE9BE32-1AB3-4DF8-9282-66646E2FEC19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{502EC421-A11B-4414-8D97-7E89EE3A290B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12106" uniqueCount="1545">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12106" uniqueCount="1543">
   <si>
     <t>IMAGEM</t>
   </si>
@@ -4663,12 +4663,6 @@
   </si>
   <si>
     <t>CAMISETA CORRE PISTA M</t>
-  </si>
-  <si>
-    <t>TREINO MASCULINO</t>
-  </si>
-  <si>
-    <t>TREINO FEMININO</t>
   </si>
   <si>
     <t>OIWB241828_NAVAL</t>
@@ -5116,6 +5110,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:AI921"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -5237,7 +5232,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>35</v>
       </c>
@@ -5344,7 +5339,7 @@
         <v>265.43</v>
       </c>
     </row>
-    <row r="3" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>45</v>
       </c>
@@ -5451,7 +5446,7 @@
         <v>265.43</v>
       </c>
     </row>
-    <row r="4" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>48</v>
       </c>
@@ -5558,7 +5553,7 @@
         <v>265.43</v>
       </c>
     </row>
-    <row r="5" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>50</v>
       </c>
@@ -5665,7 +5660,7 @@
         <v>265.43</v>
       </c>
     </row>
-    <row r="6" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>52</v>
       </c>
@@ -5772,7 +5767,7 @@
         <v>265.43</v>
       </c>
     </row>
-    <row r="7" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>54</v>
       </c>
@@ -5879,7 +5874,7 @@
         <v>238.88</v>
       </c>
     </row>
-    <row r="8" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>57</v>
       </c>
@@ -5986,7 +5981,7 @@
         <v>238.88</v>
       </c>
     </row>
-    <row r="9" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>59</v>
       </c>
@@ -6093,7 +6088,7 @@
         <v>238.88</v>
       </c>
     </row>
-    <row r="10" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>61</v>
       </c>
@@ -6200,7 +6195,7 @@
         <v>238.88</v>
       </c>
     </row>
-    <row r="11" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>63</v>
       </c>
@@ -6307,7 +6302,7 @@
         <v>238.88</v>
       </c>
     </row>
-    <row r="12" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>65</v>
       </c>
@@ -6414,7 +6409,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="13" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>68</v>
       </c>
@@ -6521,7 +6516,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="14" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>70</v>
       </c>
@@ -6628,7 +6623,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="15" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>72</v>
       </c>
@@ -6735,7 +6730,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="16" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>74</v>
       </c>
@@ -6842,7 +6837,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="17" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>76</v>
       </c>
@@ -6949,7 +6944,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="18" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>78</v>
       </c>
@@ -7056,7 +7051,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="19" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>80</v>
       </c>
@@ -7163,7 +7158,7 @@
         <v>201.72</v>
       </c>
     </row>
-    <row r="20" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>83</v>
       </c>
@@ -7270,7 +7265,7 @@
         <v>201.72</v>
       </c>
     </row>
-    <row r="21" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>84</v>
       </c>
@@ -7377,7 +7372,7 @@
         <v>201.72</v>
       </c>
     </row>
-    <row r="22" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>86</v>
       </c>
@@ -7484,7 +7479,7 @@
         <v>201.72</v>
       </c>
     </row>
-    <row r="23" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>88</v>
       </c>
@@ -7591,7 +7586,7 @@
         <v>201.72</v>
       </c>
     </row>
-    <row r="24" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>89</v>
       </c>
@@ -7698,7 +7693,7 @@
         <v>201.72</v>
       </c>
     </row>
-    <row r="25" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>90</v>
       </c>
@@ -7805,7 +7800,7 @@
         <v>185.8</v>
       </c>
     </row>
-    <row r="26" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>94</v>
       </c>
@@ -7912,7 +7907,7 @@
         <v>185.8</v>
       </c>
     </row>
-    <row r="27" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>97</v>
       </c>
@@ -8019,7 +8014,7 @@
         <v>185.8</v>
       </c>
     </row>
-    <row r="28" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>99</v>
       </c>
@@ -8126,7 +8121,7 @@
         <v>185.8</v>
       </c>
     </row>
-    <row r="29" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>101</v>
       </c>
@@ -8233,7 +8228,7 @@
         <v>185.8</v>
       </c>
     </row>
-    <row r="30" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>102</v>
       </c>
@@ -8340,7 +8335,7 @@
         <v>185.8</v>
       </c>
     </row>
-    <row r="31" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>104</v>
       </c>
@@ -8447,7 +8442,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="32" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>106</v>
       </c>
@@ -8554,7 +8549,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="33" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>107</v>
       </c>
@@ -8661,7 +8656,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="34" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>109</v>
       </c>
@@ -8768,7 +8763,7 @@
         <v>291.97000000000003</v>
       </c>
     </row>
-    <row r="35" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>114</v>
       </c>
@@ -8875,7 +8870,7 @@
         <v>291.97000000000003</v>
       </c>
     </row>
-    <row r="36" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>115</v>
       </c>
@@ -8996,7 +8991,7 @@
         <v>43210417</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>1542</v>
+        <v>691</v>
       </c>
       <c r="F37" s="4" t="s">
         <v>46</v>
@@ -9103,7 +9098,7 @@
         <v>43210417</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>1542</v>
+        <v>691</v>
       </c>
       <c r="F38" s="2" t="s">
         <v>46</v>
@@ -9210,7 +9205,7 @@
         <v>43210417</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>1543</v>
+        <v>691</v>
       </c>
       <c r="F39" s="4" t="s">
         <v>39</v>
@@ -9317,7 +9312,7 @@
         <v>43210417</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>1542</v>
+        <v>691</v>
       </c>
       <c r="F40" s="2" t="s">
         <v>46</v>
@@ -9410,7 +9405,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="41" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>123</v>
       </c>
@@ -9517,7 +9512,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="42" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>127</v>
       </c>
@@ -9624,7 +9619,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="43" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>129</v>
       </c>
@@ -9731,7 +9726,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="44" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>130</v>
       </c>
@@ -9838,7 +9833,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="45" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>132</v>
       </c>
@@ -9945,7 +9940,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="46" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>133</v>
       </c>
@@ -10052,7 +10047,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="47" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>135</v>
       </c>
@@ -10159,7 +10154,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="48" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>137</v>
       </c>
@@ -10266,7 +10261,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="49" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>139</v>
       </c>
@@ -10373,7 +10368,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="50" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>141</v>
       </c>
@@ -10480,7 +10475,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="51" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>142</v>
       </c>
@@ -10587,7 +10582,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="52" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>146</v>
       </c>
@@ -10694,7 +10689,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="53" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>147</v>
       </c>
@@ -10801,7 +10796,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="54" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>148</v>
       </c>
@@ -10908,7 +10903,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="55" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>150</v>
       </c>
@@ -11015,7 +11010,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="56" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>151</v>
       </c>
@@ -11122,7 +11117,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="57" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>153</v>
       </c>
@@ -11229,7 +11224,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="58" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>155</v>
       </c>
@@ -11336,7 +11331,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="59" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>157</v>
       </c>
@@ -11443,7 +11438,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="60" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>159</v>
       </c>
@@ -11550,7 +11545,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="61" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>161</v>
       </c>
@@ -11657,7 +11652,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="62" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>162</v>
       </c>
@@ -11764,7 +11759,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="63" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>164</v>
       </c>
@@ -11871,7 +11866,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="64" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>167</v>
       </c>
@@ -11978,7 +11973,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="65" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>169</v>
       </c>
@@ -12085,7 +12080,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="66" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
         <v>171</v>
       </c>
@@ -12192,7 +12187,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="67" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>173</v>
       </c>
@@ -12299,7 +12294,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="68" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
         <v>174</v>
       </c>
@@ -12406,7 +12401,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="69" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>176</v>
       </c>
@@ -12513,7 +12508,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="70" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
         <v>179</v>
       </c>
@@ -12620,7 +12615,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="71" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
         <v>180</v>
       </c>
@@ -12727,7 +12722,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="72" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
         <v>181</v>
       </c>
@@ -12834,7 +12829,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="73" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
         <v>182</v>
       </c>
@@ -12941,7 +12936,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="74" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
         <v>185</v>
       </c>
@@ -13048,7 +13043,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="75" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
         <v>187</v>
       </c>
@@ -13155,7 +13150,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="76" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
         <v>189</v>
       </c>
@@ -13262,7 +13257,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="77" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
         <v>191</v>
       </c>
@@ -13369,7 +13364,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="78" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
         <v>192</v>
       </c>
@@ -13476,7 +13471,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="79" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
         <v>195</v>
       </c>
@@ -13583,7 +13578,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="80" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
         <v>197</v>
       </c>
@@ -13690,7 +13685,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="81" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
         <v>198</v>
       </c>
@@ -13797,7 +13792,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="82" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
         <v>201</v>
       </c>
@@ -13904,7 +13899,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="83" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
         <v>202</v>
       </c>
@@ -14011,7 +14006,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="84" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
         <v>203</v>
       </c>
@@ -14118,7 +14113,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="85" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
         <v>206</v>
       </c>
@@ -14225,7 +14220,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="86" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
         <v>207</v>
       </c>
@@ -14332,7 +14327,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="87" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
         <v>209</v>
       </c>
@@ -14439,7 +14434,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="88" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
         <v>211</v>
       </c>
@@ -14546,7 +14541,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="89" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
         <v>214</v>
       </c>
@@ -14653,7 +14648,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="90" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
         <v>216</v>
       </c>
@@ -14760,7 +14755,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="91" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
         <v>217</v>
       </c>
@@ -14867,7 +14862,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="92" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
         <v>218</v>
       </c>
@@ -14974,7 +14969,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="93" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
         <v>221</v>
       </c>
@@ -15081,7 +15076,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="94" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
         <v>222</v>
       </c>
@@ -15188,7 +15183,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="95" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
         <v>224</v>
       </c>
@@ -15295,7 +15290,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="96" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
         <v>226</v>
       </c>
@@ -15402,7 +15397,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="97" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
         <v>230</v>
       </c>
@@ -15509,7 +15504,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="98" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
         <v>232</v>
       </c>
@@ -15616,7 +15611,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="99" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
         <v>234</v>
       </c>
@@ -15723,7 +15718,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="100" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
         <v>235</v>
       </c>
@@ -15830,7 +15825,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="101" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
         <v>238</v>
       </c>
@@ -15937,7 +15932,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="102" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
         <v>240</v>
       </c>
@@ -16044,7 +16039,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="103" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
         <v>241</v>
       </c>
@@ -16151,7 +16146,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="104" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
         <v>242</v>
       </c>
@@ -16258,7 +16253,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="105" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
         <v>244</v>
       </c>
@@ -16365,7 +16360,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="106" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
         <v>246</v>
       </c>
@@ -16472,7 +16467,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="107" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
         <v>249</v>
       </c>
@@ -16579,7 +16574,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="108" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
         <v>250</v>
       </c>
@@ -16686,7 +16681,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="109" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
         <v>251</v>
       </c>
@@ -16793,7 +16788,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="110" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
         <v>253</v>
       </c>
@@ -16900,7 +16895,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="111" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
         <v>254</v>
       </c>
@@ -17007,7 +17002,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="112" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
         <v>256</v>
       </c>
@@ -17114,7 +17109,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="113" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
         <v>258</v>
       </c>
@@ -17221,7 +17216,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="114" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
         <v>260</v>
       </c>
@@ -17328,7 +17323,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="115" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
         <v>261</v>
       </c>
@@ -17435,7 +17430,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="116" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
         <v>263</v>
       </c>
@@ -17542,7 +17537,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="117" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
         <v>265</v>
       </c>
@@ -17649,7 +17644,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="118" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
         <v>267</v>
       </c>
@@ -17756,7 +17751,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="119" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
         <v>269</v>
       </c>
@@ -17863,7 +17858,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="120" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
         <v>271</v>
       </c>
@@ -17970,7 +17965,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="121" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
         <v>272</v>
       </c>
@@ -18077,7 +18072,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="122" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
         <v>274</v>
       </c>
@@ -18184,7 +18179,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="123" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
         <v>276</v>
       </c>
@@ -18291,7 +18286,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="124" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
         <v>278</v>
       </c>
@@ -18398,7 +18393,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="125" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
         <v>279</v>
       </c>
@@ -18505,7 +18500,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="126" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
         <v>282</v>
       </c>
@@ -18612,7 +18607,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="127" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
         <v>283</v>
       </c>
@@ -18719,7 +18714,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="128" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
         <v>284</v>
       </c>
@@ -18826,7 +18821,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="129" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
         <v>285</v>
       </c>
@@ -18933,7 +18928,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="130" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
         <v>287</v>
       </c>
@@ -19040,7 +19035,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="131" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
         <v>289</v>
       </c>
@@ -19147,7 +19142,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="132" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
         <v>291</v>
       </c>
@@ -19254,7 +19249,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="133" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
         <v>292</v>
       </c>
@@ -19361,7 +19356,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="134" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
         <v>294</v>
       </c>
@@ -19468,7 +19463,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="135" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
         <v>295</v>
       </c>
@@ -19575,7 +19570,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="136" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
         <v>296</v>
       </c>
@@ -19682,7 +19677,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="137" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
         <v>297</v>
       </c>
@@ -19789,7 +19784,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="138" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
         <v>300</v>
       </c>
@@ -19896,7 +19891,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="139" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
         <v>301</v>
       </c>
@@ -20003,7 +19998,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="140" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
         <v>302</v>
       </c>
@@ -20110,7 +20105,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="141" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
         <v>303</v>
       </c>
@@ -20217,7 +20212,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="142" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
         <v>306</v>
       </c>
@@ -20324,7 +20319,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="143" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
         <v>308</v>
       </c>
@@ -20431,7 +20426,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="144" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
         <v>309</v>
       </c>
@@ -20538,7 +20533,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="145" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
         <v>311</v>
       </c>
@@ -20645,7 +20640,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="146" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
         <v>313</v>
       </c>
@@ -20752,7 +20747,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="147" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
         <v>314</v>
       </c>
@@ -20859,7 +20854,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="148" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
         <v>315</v>
       </c>
@@ -20966,7 +20961,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="149" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
         <v>317</v>
       </c>
@@ -21073,7 +21068,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="150" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="2" t="s">
         <v>318</v>
       </c>
@@ -21180,7 +21175,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="151" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="s">
         <v>319</v>
       </c>
@@ -21287,7 +21282,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="152" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="2" t="s">
         <v>322</v>
       </c>
@@ -21394,7 +21389,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="153" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="s">
         <v>323</v>
       </c>
@@ -21501,7 +21496,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="154" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="s">
         <v>325</v>
       </c>
@@ -21608,7 +21603,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="155" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="2" t="s">
         <v>326</v>
       </c>
@@ -21715,7 +21710,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="156" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="2" t="s">
         <v>328</v>
       </c>
@@ -21822,7 +21817,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="157" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="2" t="s">
         <v>329</v>
       </c>
@@ -21929,7 +21924,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="158" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="2" t="s">
         <v>330</v>
       </c>
@@ -22036,7 +22031,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="159" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="s">
         <v>331</v>
       </c>
@@ -22143,7 +22138,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="160" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="2" t="s">
         <v>333</v>
       </c>
@@ -22250,7 +22245,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="161" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="2" t="s">
         <v>335</v>
       </c>
@@ -22357,7 +22352,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="162" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="2" t="s">
         <v>337</v>
       </c>
@@ -22464,7 +22459,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="163" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="2" t="s">
         <v>338</v>
       </c>
@@ -22571,7 +22566,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="164" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="2" t="s">
         <v>341</v>
       </c>
@@ -22678,7 +22673,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="165" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="2" t="s">
         <v>343</v>
       </c>
@@ -22785,7 +22780,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="166" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="2" t="s">
         <v>345</v>
       </c>
@@ -22892,7 +22887,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="167" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="2" t="s">
         <v>347</v>
       </c>
@@ -22999,7 +22994,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="168" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="2" t="s">
         <v>349</v>
       </c>
@@ -23106,7 +23101,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="169" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="2" t="s">
         <v>350</v>
       </c>
@@ -23213,7 +23208,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="170" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="2" t="s">
         <v>352</v>
       </c>
@@ -23320,7 +23315,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="171" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="2" t="s">
         <v>353</v>
       </c>
@@ -23427,7 +23422,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="172" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="2" t="s">
         <v>356</v>
       </c>
@@ -23534,7 +23529,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="173" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="2" t="s">
         <v>357</v>
       </c>
@@ -23641,7 +23636,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="174" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="2" t="s">
         <v>358</v>
       </c>
@@ -23748,7 +23743,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="175" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="2" t="s">
         <v>359</v>
       </c>
@@ -23855,7 +23850,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="176" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="2" t="s">
         <v>361</v>
       </c>
@@ -23962,7 +23957,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="177" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="2" t="s">
         <v>362</v>
       </c>
@@ -24069,7 +24064,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="178" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="2" t="s">
         <v>363</v>
       </c>
@@ -24176,7 +24171,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="179" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="2" t="s">
         <v>366</v>
       </c>
@@ -24283,7 +24278,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="180" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="2" t="s">
         <v>368</v>
       </c>
@@ -24390,7 +24385,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="181" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="2" t="s">
         <v>369</v>
       </c>
@@ -24497,7 +24492,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="182" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="2" t="s">
         <v>370</v>
       </c>
@@ -24604,7 +24599,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="183" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" s="2" t="s">
         <v>373</v>
       </c>
@@ -24711,7 +24706,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="184" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="2" t="s">
         <v>375</v>
       </c>
@@ -24818,7 +24813,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="185" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="2" t="s">
         <v>377</v>
       </c>
@@ -24925,7 +24920,7 @@
         <v>100.86</v>
       </c>
     </row>
-    <row r="186" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="2" t="s">
         <v>380</v>
       </c>
@@ -25032,7 +25027,7 @@
         <v>100.86</v>
       </c>
     </row>
-    <row r="187" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="2" t="s">
         <v>381</v>
       </c>
@@ -25139,7 +25134,7 @@
         <v>100.86</v>
       </c>
     </row>
-    <row r="188" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="2" t="s">
         <v>382</v>
       </c>
@@ -25246,7 +25241,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="189" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="2" t="s">
         <v>386</v>
       </c>
@@ -25353,7 +25348,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="190" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="2" t="s">
         <v>388</v>
       </c>
@@ -25460,7 +25455,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="191" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="2" t="s">
         <v>390</v>
       </c>
@@ -25567,7 +25562,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="192" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="2" t="s">
         <v>392</v>
       </c>
@@ -25674,7 +25669,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="193" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="2" t="s">
         <v>393</v>
       </c>
@@ -25781,7 +25776,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="194" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="2" t="s">
         <v>394</v>
       </c>
@@ -25888,7 +25883,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="195" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" s="2" t="s">
         <v>397</v>
       </c>
@@ -25995,7 +25990,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="196" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" s="2" t="s">
         <v>398</v>
       </c>
@@ -26102,7 +26097,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="197" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="2" t="s">
         <v>401</v>
       </c>
@@ -26209,7 +26204,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="198" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" s="2" t="s">
         <v>402</v>
       </c>
@@ -26316,7 +26311,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="199" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" s="2" t="s">
         <v>403</v>
       </c>
@@ -26423,7 +26418,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="200" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="2" t="s">
         <v>404</v>
       </c>
@@ -26530,7 +26525,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="201" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="2" t="s">
         <v>405</v>
       </c>
@@ -26637,7 +26632,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="202" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" s="2" t="s">
         <v>407</v>
       </c>
@@ -26744,7 +26739,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="203" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" s="2" t="s">
         <v>409</v>
       </c>
@@ -26851,7 +26846,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="204" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" s="2" t="s">
         <v>410</v>
       </c>
@@ -26958,7 +26953,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="205" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" s="2" t="s">
         <v>411</v>
       </c>
@@ -27065,7 +27060,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="206" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" s="2" t="s">
         <v>412</v>
       </c>
@@ -27172,7 +27167,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="207" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207" s="2" t="s">
         <v>413</v>
       </c>
@@ -27279,7 +27274,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="208" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" s="2" t="s">
         <v>414</v>
       </c>
@@ -27386,7 +27381,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="209" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" s="2" t="s">
         <v>418</v>
       </c>
@@ -27493,7 +27488,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="210" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A210" s="2" t="s">
         <v>419</v>
       </c>
@@ -27600,7 +27595,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="211" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" s="2" t="s">
         <v>420</v>
       </c>
@@ -27707,7 +27702,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="212" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" s="2" t="s">
         <v>421</v>
       </c>
@@ -27814,7 +27809,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="213" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213" s="2" t="s">
         <v>422</v>
       </c>
@@ -27921,7 +27916,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="214" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214" s="2" t="s">
         <v>424</v>
       </c>
@@ -28028,7 +28023,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="215" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" s="2" t="s">
         <v>425</v>
       </c>
@@ -28135,7 +28130,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="216" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216" s="2" t="s">
         <v>426</v>
       </c>
@@ -28242,7 +28237,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="217" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A217" s="2" t="s">
         <v>427</v>
       </c>
@@ -28349,7 +28344,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="218" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A218" s="2" t="s">
         <v>428</v>
       </c>
@@ -28456,7 +28451,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="219" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219" s="2" t="s">
         <v>429</v>
       </c>
@@ -28563,7 +28558,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="220" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="2" t="s">
         <v>431</v>
       </c>
@@ -28670,7 +28665,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="221" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A221" s="2" t="s">
         <v>433</v>
       </c>
@@ -28777,7 +28772,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="222" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A222" s="2" t="s">
         <v>435</v>
       </c>
@@ -28884,7 +28879,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="223" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A223" s="2" t="s">
         <v>436</v>
       </c>
@@ -28991,7 +28986,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="224" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A224" s="2" t="s">
         <v>437</v>
       </c>
@@ -29098,7 +29093,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="225" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225" s="2" t="s">
         <v>439</v>
       </c>
@@ -29205,7 +29200,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="226" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A226" s="2" t="s">
         <v>440</v>
       </c>
@@ -29312,7 +29307,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="227" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A227" s="2" t="s">
         <v>441</v>
       </c>
@@ -29419,7 +29414,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="228" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A228" s="2" t="s">
         <v>442</v>
       </c>
@@ -29526,7 +29521,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="229" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A229" s="2" t="s">
         <v>443</v>
       </c>
@@ -29633,7 +29628,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="230" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A230" s="2" t="s">
         <v>444</v>
       </c>
@@ -29740,7 +29735,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="231" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A231" s="2" t="s">
         <v>446</v>
       </c>
@@ -29847,7 +29842,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="232" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A232" s="2" t="s">
         <v>447</v>
       </c>
@@ -29954,7 +29949,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="233" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A233" s="2" t="s">
         <v>448</v>
       </c>
@@ -30061,7 +30056,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="234" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A234" s="2" t="s">
         <v>449</v>
       </c>
@@ -30168,7 +30163,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="235" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A235" s="2" t="s">
         <v>450</v>
       </c>
@@ -30275,7 +30270,7 @@
         <v>95.55</v>
       </c>
     </row>
-    <row r="236" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A236" s="2" t="s">
         <v>456</v>
       </c>
@@ -30382,7 +30377,7 @@
         <v>95.55</v>
       </c>
     </row>
-    <row r="237" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="2" t="s">
         <v>457</v>
       </c>
@@ -30489,7 +30484,7 @@
         <v>95.55</v>
       </c>
     </row>
-    <row r="238" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" s="2" t="s">
         <v>459</v>
       </c>
@@ -30596,7 +30591,7 @@
         <v>95.55</v>
       </c>
     </row>
-    <row r="239" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A239" s="2" t="s">
         <v>461</v>
       </c>
@@ -30703,7 +30698,7 @@
         <v>95.55</v>
       </c>
     </row>
-    <row r="240" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A240" s="2" t="s">
         <v>462</v>
       </c>
@@ -30810,7 +30805,7 @@
         <v>95.55</v>
       </c>
     </row>
-    <row r="241" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A241" s="2" t="s">
         <v>463</v>
       </c>
@@ -30917,7 +30912,7 @@
         <v>84.94</v>
       </c>
     </row>
-    <row r="242" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A242" s="2" t="s">
         <v>466</v>
       </c>
@@ -31024,7 +31019,7 @@
         <v>84.94</v>
       </c>
     </row>
-    <row r="243" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A243" s="2" t="s">
         <v>467</v>
       </c>
@@ -31131,7 +31126,7 @@
         <v>84.94</v>
       </c>
     </row>
-    <row r="244" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A244" s="2" t="s">
         <v>469</v>
       </c>
@@ -31238,7 +31233,7 @@
         <v>84.94</v>
       </c>
     </row>
-    <row r="245" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A245" s="2" t="s">
         <v>470</v>
       </c>
@@ -31345,7 +31340,7 @@
         <v>79.63</v>
       </c>
     </row>
-    <row r="246" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A246" s="2" t="s">
         <v>472</v>
       </c>
@@ -31452,7 +31447,7 @@
         <v>79.63</v>
       </c>
     </row>
-    <row r="247" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A247" s="2" t="s">
         <v>473</v>
       </c>
@@ -31559,7 +31554,7 @@
         <v>79.63</v>
       </c>
     </row>
-    <row r="248" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A248" s="2" t="s">
         <v>474</v>
       </c>
@@ -31666,7 +31661,7 @@
         <v>79.63</v>
       </c>
     </row>
-    <row r="249" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A249" s="2" t="s">
         <v>475</v>
       </c>
@@ -31773,7 +31768,7 @@
         <v>79.63</v>
       </c>
     </row>
-    <row r="250" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A250" s="2" t="s">
         <v>476</v>
       </c>
@@ -31880,7 +31875,7 @@
         <v>69.010000000000005</v>
       </c>
     </row>
-    <row r="251" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A251" s="2" t="s">
         <v>479</v>
       </c>
@@ -31987,7 +31982,7 @@
         <v>69.010000000000005</v>
       </c>
     </row>
-    <row r="252" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A252" s="2" t="s">
         <v>480</v>
       </c>
@@ -32094,7 +32089,7 @@
         <v>69.010000000000005</v>
       </c>
     </row>
-    <row r="253" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A253" s="2" t="s">
         <v>482</v>
       </c>
@@ -32201,7 +32196,7 @@
         <v>69.010000000000005</v>
       </c>
     </row>
-    <row r="254" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A254" s="2" t="s">
         <v>483</v>
       </c>
@@ -32308,7 +32303,7 @@
         <v>53.09</v>
       </c>
     </row>
-    <row r="255" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255" s="2" t="s">
         <v>486</v>
       </c>
@@ -32415,7 +32410,7 @@
         <v>53.09</v>
       </c>
     </row>
-    <row r="256" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A256" s="2" t="s">
         <v>488</v>
       </c>
@@ -32522,7 +32517,7 @@
         <v>53.09</v>
       </c>
     </row>
-    <row r="257" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A257" s="2" t="s">
         <v>490</v>
       </c>
@@ -32629,7 +32624,7 @@
         <v>53.09</v>
       </c>
     </row>
-    <row r="258" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A258" s="2" t="s">
         <v>491</v>
       </c>
@@ -32736,7 +32731,7 @@
         <v>53.09</v>
       </c>
     </row>
-    <row r="259" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A259" s="2" t="s">
         <v>493</v>
       </c>
@@ -32831,7 +32826,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="260" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A260" s="2" t="s">
         <v>496</v>
       </c>
@@ -32926,7 +32921,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="261" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A261" s="2" t="s">
         <v>497</v>
       </c>
@@ -33021,7 +33016,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="262" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A262" s="2" t="s">
         <v>499</v>
       </c>
@@ -33116,7 +33111,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="263" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A263" s="2" t="s">
         <v>500</v>
       </c>
@@ -33211,7 +33206,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="264" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A264" s="2" t="s">
         <v>502</v>
       </c>
@@ -33306,7 +33301,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="265" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A265" s="2" t="s">
         <v>504</v>
       </c>
@@ -33401,7 +33396,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="266" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A266" s="2" t="s">
         <v>506</v>
       </c>
@@ -33496,7 +33491,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="267" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A267" s="2" t="s">
         <v>507</v>
       </c>
@@ -33591,7 +33586,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="268" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A268" s="2" t="s">
         <v>508</v>
       </c>
@@ -33686,7 +33681,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="269" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A269" s="2" t="s">
         <v>509</v>
       </c>
@@ -33781,7 +33776,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="270" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A270" s="2" t="s">
         <v>511</v>
       </c>
@@ -33876,7 +33871,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="271" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A271" s="2" t="s">
         <v>512</v>
       </c>
@@ -33971,7 +33966,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="272" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A272" s="2" t="s">
         <v>513</v>
       </c>
@@ -34066,7 +34061,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="273" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A273" s="2" t="s">
         <v>514</v>
       </c>
@@ -34127,7 +34122,7 @@
       <c r="AH273" s="4"/>
       <c r="AI273" s="4"/>
     </row>
-    <row r="274" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A274" s="2" t="s">
         <v>516</v>
       </c>
@@ -34188,7 +34183,7 @@
       <c r="AH274" s="4"/>
       <c r="AI274" s="4"/>
     </row>
-    <row r="275" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A275" s="2" t="s">
         <v>517</v>
       </c>
@@ -34249,7 +34244,7 @@
       <c r="AH275" s="4"/>
       <c r="AI275" s="4"/>
     </row>
-    <row r="276" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A276" s="2" t="s">
         <v>518</v>
       </c>
@@ -34310,7 +34305,7 @@
       <c r="AH276" s="4"/>
       <c r="AI276" s="4"/>
     </row>
-    <row r="277" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A277" s="2" t="s">
         <v>519</v>
       </c>
@@ -34371,7 +34366,7 @@
       <c r="AH277" s="4"/>
       <c r="AI277" s="4"/>
     </row>
-    <row r="278" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A278" s="2" t="s">
         <v>521</v>
       </c>
@@ -34466,7 +34461,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="279" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A279" s="2" t="s">
         <v>523</v>
       </c>
@@ -34561,7 +34556,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="280" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A280" s="2" t="s">
         <v>525</v>
       </c>
@@ -34656,7 +34651,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="281" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A281" s="2" t="s">
         <v>526</v>
       </c>
@@ -34751,7 +34746,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="282" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A282" s="2" t="s">
         <v>181</v>
       </c>
@@ -34846,7 +34841,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="283" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A283" s="2" t="s">
         <v>180</v>
       </c>
@@ -34941,7 +34936,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="284" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A284" s="2" t="s">
         <v>179</v>
       </c>
@@ -35036,7 +35031,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="285" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A285" s="2" t="s">
         <v>176</v>
       </c>
@@ -35131,7 +35126,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="286" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A286" s="2" t="s">
         <v>191</v>
       </c>
@@ -35226,7 +35221,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="287" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A287" s="2" t="s">
         <v>527</v>
       </c>
@@ -35321,7 +35316,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="288" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A288" s="2" t="s">
         <v>187</v>
       </c>
@@ -35416,7 +35411,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="289" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A289" s="2" t="s">
         <v>182</v>
       </c>
@@ -35511,7 +35506,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="290" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A290" s="2" t="s">
         <v>185</v>
       </c>
@@ -35606,7 +35601,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="291" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A291" s="2" t="s">
         <v>529</v>
       </c>
@@ -35701,7 +35696,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="292" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A292" s="2" t="s">
         <v>531</v>
       </c>
@@ -35796,7 +35791,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="293" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A293" s="2" t="s">
         <v>532</v>
       </c>
@@ -35891,7 +35886,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="294" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A294" s="2" t="s">
         <v>534</v>
       </c>
@@ -35952,7 +35947,7 @@
       <c r="AH294" s="4"/>
       <c r="AI294" s="4"/>
     </row>
-    <row r="295" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A295" s="2" t="s">
         <v>536</v>
       </c>
@@ -36013,7 +36008,7 @@
       <c r="AH295" s="4"/>
       <c r="AI295" s="4"/>
     </row>
-    <row r="296" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A296" s="2" t="s">
         <v>537</v>
       </c>
@@ -36074,7 +36069,7 @@
       <c r="AH296" s="4"/>
       <c r="AI296" s="4"/>
     </row>
-    <row r="297" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A297" s="2" t="s">
         <v>221</v>
       </c>
@@ -36169,7 +36164,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="298" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A298" s="2" t="s">
         <v>222</v>
       </c>
@@ -36264,7 +36259,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="299" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A299" s="2" t="s">
         <v>218</v>
       </c>
@@ -36359,7 +36354,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="300" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A300" s="2" t="s">
         <v>224</v>
       </c>
@@ -36454,7 +36449,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="301" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A301" s="2" t="s">
         <v>206</v>
       </c>
@@ -36549,7 +36544,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="302" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A302" s="2" t="s">
         <v>203</v>
       </c>
@@ -36644,7 +36639,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="303" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A303" s="2" t="s">
         <v>538</v>
       </c>
@@ -36739,7 +36734,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="304" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A304" s="2" t="s">
         <v>540</v>
       </c>
@@ -36834,7 +36829,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="305" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A305" s="2" t="s">
         <v>542</v>
       </c>
@@ -36929,7 +36924,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="306" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A306" s="2" t="s">
         <v>253</v>
       </c>
@@ -37024,7 +37019,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="307" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A307" s="2" t="s">
         <v>251</v>
       </c>
@@ -37119,7 +37114,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="308" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A308" s="2" t="s">
         <v>249</v>
       </c>
@@ -37214,7 +37209,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="309" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A309" s="2" t="s">
         <v>246</v>
       </c>
@@ -37309,7 +37304,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="310" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A310" s="2" t="s">
         <v>250</v>
       </c>
@@ -37404,7 +37399,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="311" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A311" s="2" t="s">
         <v>258</v>
       </c>
@@ -37499,7 +37494,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="312" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A312" s="2" t="s">
         <v>260</v>
       </c>
@@ -37594,7 +37589,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="313" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A313" s="2" t="s">
         <v>256</v>
       </c>
@@ -37689,7 +37684,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="314" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A314" s="2" t="s">
         <v>254</v>
       </c>
@@ -37784,7 +37779,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="315" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A315" s="2" t="s">
         <v>544</v>
       </c>
@@ -37879,7 +37874,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="316" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A316" s="2" t="s">
         <v>283</v>
       </c>
@@ -37974,7 +37969,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="317" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A317" s="2" t="s">
         <v>282</v>
       </c>
@@ -38069,7 +38064,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="318" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A318" s="2" t="s">
         <v>279</v>
       </c>
@@ -38164,7 +38159,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="319" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A319" s="2" t="s">
         <v>291</v>
       </c>
@@ -38259,7 +38254,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="320" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A320" s="2" t="s">
         <v>287</v>
       </c>
@@ -38354,7 +38349,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="321" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A321" s="2" t="s">
         <v>285</v>
       </c>
@@ -38449,7 +38444,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="322" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A322" s="2" t="s">
         <v>289</v>
       </c>
@@ -38544,7 +38539,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="323" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A323" s="2" t="s">
         <v>545</v>
       </c>
@@ -38639,7 +38634,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="324" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A324" s="2" t="s">
         <v>547</v>
       </c>
@@ -38734,7 +38729,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="325" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A325" s="2" t="s">
         <v>549</v>
       </c>
@@ -38829,7 +38824,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="326" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A326" s="2" t="s">
         <v>551</v>
       </c>
@@ -38924,7 +38919,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="327" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A327" s="2" t="s">
         <v>552</v>
       </c>
@@ -39019,7 +39014,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="328" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A328" s="2" t="s">
         <v>555</v>
       </c>
@@ -39114,7 +39109,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="329" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A329" s="2" t="s">
         <v>556</v>
       </c>
@@ -39209,7 +39204,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="330" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A330" s="2" t="s">
         <v>295</v>
       </c>
@@ -39304,7 +39299,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="331" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A331" s="2" t="s">
         <v>294</v>
       </c>
@@ -39399,7 +39394,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="332" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A332" s="2" t="s">
         <v>292</v>
       </c>
@@ -39494,7 +39489,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="333" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A333" s="2" t="s">
         <v>296</v>
       </c>
@@ -39589,7 +39584,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="334" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A334" s="2" t="s">
         <v>330</v>
       </c>
@@ -39684,7 +39679,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="335" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A335" s="2" t="s">
         <v>328</v>
       </c>
@@ -39779,7 +39774,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="336" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A336" s="2" t="s">
         <v>326</v>
       </c>
@@ -39874,7 +39869,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="337" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A337" s="2" t="s">
         <v>329</v>
       </c>
@@ -39969,7 +39964,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="338" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A338" s="2" t="s">
         <v>319</v>
       </c>
@@ -40064,7 +40059,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="339" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A339" s="2" t="s">
         <v>323</v>
       </c>
@@ -40159,7 +40154,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="340" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A340" s="2" t="s">
         <v>322</v>
       </c>
@@ -40254,7 +40249,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="341" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A341" s="2" t="s">
         <v>325</v>
       </c>
@@ -40349,7 +40344,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="342" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A342" s="2" t="s">
         <v>331</v>
       </c>
@@ -40444,7 +40439,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="343" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A343" s="2" t="s">
         <v>337</v>
       </c>
@@ -40539,7 +40534,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="344" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A344" s="2" t="s">
         <v>333</v>
       </c>
@@ -40634,7 +40629,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="345" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A345" s="2" t="s">
         <v>558</v>
       </c>
@@ -40729,7 +40724,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="346" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A346" s="2" t="s">
         <v>341</v>
       </c>
@@ -40824,7 +40819,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="347" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A347" s="2" t="s">
         <v>345</v>
       </c>
@@ -40919,7 +40914,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="348" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A348" s="2" t="s">
         <v>343</v>
       </c>
@@ -41014,7 +41009,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="349" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A349" s="2" t="s">
         <v>338</v>
       </c>
@@ -41109,7 +41104,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="350" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A350" s="2" t="s">
         <v>560</v>
       </c>
@@ -41216,7 +41211,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="351" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A351" s="2" t="s">
         <v>562</v>
       </c>
@@ -41323,7 +41318,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="352" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A352" s="2" t="s">
         <v>563</v>
       </c>
@@ -41430,7 +41425,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="353" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A353" s="2" t="s">
         <v>565</v>
       </c>
@@ -41525,7 +41520,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="354" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A354" s="2" t="s">
         <v>370</v>
       </c>
@@ -41620,7 +41615,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="355" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A355" s="2" t="s">
         <v>373</v>
       </c>
@@ -41715,7 +41710,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="356" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A356" s="2" t="s">
         <v>566</v>
       </c>
@@ -41810,7 +41805,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="357" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A357" s="2" t="s">
         <v>366</v>
       </c>
@@ -41905,7 +41900,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="358" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A358" s="2" t="s">
         <v>567</v>
       </c>
@@ -42000,7 +41995,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="359" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A359" s="2" t="s">
         <v>363</v>
       </c>
@@ -42095,7 +42090,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="360" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A360" s="2" t="s">
         <v>568</v>
       </c>
@@ -42190,7 +42185,7 @@
         <v>100.86</v>
       </c>
     </row>
-    <row r="361" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A361" s="2" t="s">
         <v>569</v>
       </c>
@@ -42285,7 +42280,7 @@
         <v>100.86</v>
       </c>
     </row>
-    <row r="362" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A362" s="2" t="s">
         <v>377</v>
       </c>
@@ -42380,7 +42375,7 @@
         <v>100.86</v>
       </c>
     </row>
-    <row r="363" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A363" s="2" t="s">
         <v>148</v>
       </c>
@@ -42475,7 +42470,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="364" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A364" s="2" t="s">
         <v>571</v>
       </c>
@@ -42570,7 +42565,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="365" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A365" s="2" t="s">
         <v>151</v>
       </c>
@@ -42665,7 +42660,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="366" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A366" s="2" t="s">
         <v>150</v>
       </c>
@@ -42760,7 +42755,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="367" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A367" s="2" t="s">
         <v>142</v>
       </c>
@@ -42855,7 +42850,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="368" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A368" s="2" t="s">
         <v>146</v>
       </c>
@@ -42950,7 +42945,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="369" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A369" s="2" t="s">
         <v>147</v>
       </c>
@@ -43045,7 +43040,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="370" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A370" s="2" t="s">
         <v>155</v>
       </c>
@@ -43140,7 +43135,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="371" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A371" s="2" t="s">
         <v>572</v>
       </c>
@@ -43235,7 +43230,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="372" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A372" s="2" t="s">
         <v>573</v>
       </c>
@@ -43330,7 +43325,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="373" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A373" s="2" t="s">
         <v>574</v>
       </c>
@@ -43425,7 +43420,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="374" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A374" s="2" t="s">
         <v>576</v>
       </c>
@@ -43520,7 +43515,7 @@
         <v>148.63999999999999</v>
       </c>
     </row>
-    <row r="375" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A375" s="2" t="s">
         <v>230</v>
       </c>
@@ -43615,7 +43610,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="376" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A376" s="2" t="s">
         <v>234</v>
       </c>
@@ -43710,7 +43705,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="377" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A377" s="2" t="s">
         <v>226</v>
       </c>
@@ -43805,7 +43800,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="378" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A378" s="2" t="s">
         <v>232</v>
       </c>
@@ -43900,7 +43895,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="379" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A379" s="2" t="s">
         <v>313</v>
       </c>
@@ -43995,7 +43990,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="380" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A380" s="2" t="s">
         <v>314</v>
       </c>
@@ -44090,7 +44085,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="381" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A381" s="2" t="s">
         <v>311</v>
       </c>
@@ -44185,7 +44180,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="382" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A382" s="2" t="s">
         <v>309</v>
       </c>
@@ -44280,7 +44275,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="383" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A383" s="2" t="s">
         <v>578</v>
       </c>
@@ -44375,7 +44370,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="384" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A384" s="2" t="s">
         <v>580</v>
       </c>
@@ -44470,7 +44465,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="385" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A385" s="2" t="s">
         <v>582</v>
       </c>
@@ -44565,7 +44560,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="386" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A386" s="2" t="s">
         <v>584</v>
       </c>
@@ -44660,7 +44655,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="387" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A387" s="2" t="s">
         <v>435</v>
       </c>
@@ -44755,7 +44750,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="388" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A388" s="2" t="s">
         <v>433</v>
       </c>
@@ -44850,7 +44845,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="389" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A389" s="2" t="s">
         <v>436</v>
       </c>
@@ -44945,7 +44940,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="390" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A390" s="2" t="s">
         <v>429</v>
       </c>
@@ -45040,7 +45035,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="391" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A391" s="2" t="s">
         <v>431</v>
       </c>
@@ -45135,7 +45130,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="392" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A392" s="2" t="s">
         <v>448</v>
       </c>
@@ -45230,7 +45225,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="393" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A393" s="2" t="s">
         <v>446</v>
       </c>
@@ -45325,7 +45320,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="394" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A394" s="2" t="s">
         <v>444</v>
       </c>
@@ -45420,7 +45415,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="395" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A395" s="2" t="s">
         <v>586</v>
       </c>
@@ -45515,7 +45510,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="396" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A396" s="2" t="s">
         <v>588</v>
       </c>
@@ -45610,7 +45605,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="397" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A397" s="2" t="s">
         <v>589</v>
       </c>
@@ -45705,7 +45700,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="398" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A398" s="2" t="s">
         <v>590</v>
       </c>
@@ -45800,7 +45795,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="399" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A399" s="2" t="s">
         <v>591</v>
       </c>
@@ -45861,7 +45856,7 @@
       <c r="AH399" s="4"/>
       <c r="AI399" s="4"/>
     </row>
-    <row r="400" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A400" s="2" t="s">
         <v>595</v>
       </c>
@@ -45922,7 +45917,7 @@
       <c r="AH400" s="4"/>
       <c r="AI400" s="4"/>
     </row>
-    <row r="401" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A401" s="2" t="s">
         <v>597</v>
       </c>
@@ -45983,7 +45978,7 @@
       <c r="AH401" s="4"/>
       <c r="AI401" s="4"/>
     </row>
-    <row r="402" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A402" s="2" t="s">
         <v>599</v>
       </c>
@@ -46044,7 +46039,7 @@
       <c r="AH402" s="4"/>
       <c r="AI402" s="4"/>
     </row>
-    <row r="403" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A403" s="2" t="s">
         <v>382</v>
       </c>
@@ -46139,7 +46134,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="404" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A404" s="2" t="s">
         <v>393</v>
       </c>
@@ -46234,7 +46229,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="405" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A405" s="2" t="s">
         <v>392</v>
       </c>
@@ -46329,7 +46324,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="406" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A406" s="2" t="s">
         <v>390</v>
       </c>
@@ -46424,7 +46419,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="407" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A407" s="2" t="s">
         <v>386</v>
       </c>
@@ -46519,7 +46514,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="408" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A408" s="2" t="s">
         <v>388</v>
       </c>
@@ -46614,7 +46609,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="409" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A409" s="2" t="s">
         <v>197</v>
       </c>
@@ -46709,7 +46704,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="410" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A410" s="2" t="s">
         <v>192</v>
       </c>
@@ -46804,7 +46799,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="411" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A411" s="2" t="s">
         <v>195</v>
       </c>
@@ -46899,7 +46894,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="412" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A412" s="2" t="s">
         <v>601</v>
       </c>
@@ -46994,7 +46989,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="413" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A413" s="2" t="s">
         <v>603</v>
       </c>
@@ -47089,7 +47084,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="414" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A414" s="2" t="s">
         <v>604</v>
       </c>
@@ -47184,7 +47179,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="415" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A415" s="2" t="s">
         <v>605</v>
       </c>
@@ -47279,7 +47274,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="416" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A416" s="2" t="s">
         <v>606</v>
       </c>
@@ -47374,7 +47369,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="417" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A417" s="2" t="s">
         <v>608</v>
       </c>
@@ -47469,7 +47464,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="418" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A418" s="2" t="s">
         <v>609</v>
       </c>
@@ -47564,7 +47559,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="419" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A419" s="2" t="s">
         <v>610</v>
       </c>
@@ -47659,7 +47654,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="420" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A420" s="2" t="s">
         <v>362</v>
       </c>
@@ -47754,7 +47749,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="421" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A421" s="2" t="s">
         <v>361</v>
       </c>
@@ -47849,7 +47844,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="422" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A422" s="2" t="s">
         <v>359</v>
       </c>
@@ -47944,7 +47939,7 @@
         <v>122.1</v>
       </c>
     </row>
-    <row r="423" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A423" s="2" t="s">
         <v>358</v>
       </c>
@@ -48039,7 +48034,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="424" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A424" s="2" t="s">
         <v>357</v>
       </c>
@@ -48134,7 +48129,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="425" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A425" s="2" t="s">
         <v>356</v>
       </c>
@@ -48229,7 +48224,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="426" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A426" s="2" t="s">
         <v>353</v>
       </c>
@@ -48324,7 +48319,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="427" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A427" s="2" t="s">
         <v>611</v>
       </c>
@@ -48419,7 +48414,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="428" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A428" s="2" t="s">
         <v>614</v>
       </c>
@@ -48514,7 +48509,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="429" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A429" s="2" t="s">
         <v>615</v>
       </c>
@@ -48609,7 +48604,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="430" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A430" s="2" t="s">
         <v>617</v>
       </c>
@@ -48704,7 +48699,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="431" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A431" s="2" t="s">
         <v>407</v>
       </c>
@@ -48799,7 +48794,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="432" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A432" s="2" t="s">
         <v>413</v>
       </c>
@@ -48894,7 +48889,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="433" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A433" s="2" t="s">
         <v>412</v>
       </c>
@@ -48989,7 +48984,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="434" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A434" s="2" t="s">
         <v>410</v>
       </c>
@@ -49084,7 +49079,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="435" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A435" s="2" t="s">
         <v>618</v>
       </c>
@@ -49179,7 +49174,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="436" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A436" s="2" t="s">
         <v>411</v>
       </c>
@@ -49274,7 +49269,7 @@
         <v>132.71</v>
       </c>
     </row>
-    <row r="437" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A437" s="2" t="s">
         <v>397</v>
       </c>
@@ -49369,7 +49364,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="438" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A438" s="2" t="s">
         <v>394</v>
       </c>
@@ -49464,7 +49459,7 @@
         <v>138.02000000000001</v>
       </c>
     </row>
-    <row r="439" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A439" s="2" t="s">
         <v>437</v>
       </c>
@@ -49559,7 +49554,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="440" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A440" s="2" t="s">
         <v>443</v>
       </c>
@@ -49654,7 +49649,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="441" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A441" s="2" t="s">
         <v>442</v>
       </c>
@@ -49749,7 +49744,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="442" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A442" s="2" t="s">
         <v>440</v>
       </c>
@@ -49844,7 +49839,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="443" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A443" s="2" t="s">
         <v>441</v>
       </c>
@@ -49939,7 +49934,7 @@
         <v>106.17</v>
       </c>
     </row>
-    <row r="444" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A444" s="2" t="s">
         <v>491</v>
       </c>
@@ -50034,7 +50029,7 @@
         <v>53.09</v>
       </c>
     </row>
-    <row r="445" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A445" s="2" t="s">
         <v>490</v>
       </c>
@@ -50129,7 +50124,7 @@
         <v>53.09</v>
       </c>
     </row>
-    <row r="446" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A446" s="2" t="s">
         <v>488</v>
       </c>
@@ -50224,7 +50219,7 @@
         <v>53.09</v>
       </c>
     </row>
-    <row r="447" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A447" s="2" t="s">
         <v>486</v>
       </c>
@@ -50319,7 +50314,7 @@
         <v>53.09</v>
       </c>
     </row>
-    <row r="448" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A448" s="2" t="s">
         <v>483</v>
       </c>
@@ -50414,7 +50409,7 @@
         <v>53.09</v>
       </c>
     </row>
-    <row r="449" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A449" s="2" t="s">
         <v>462</v>
       </c>
@@ -50509,7 +50504,7 @@
         <v>95.55</v>
       </c>
     </row>
-    <row r="450" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A450" s="2" t="s">
         <v>461</v>
       </c>
@@ -50604,7 +50599,7 @@
         <v>95.55</v>
       </c>
     </row>
-    <row r="451" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A451" s="2" t="s">
         <v>459</v>
       </c>
@@ -50699,7 +50694,7 @@
         <v>95.55</v>
       </c>
     </row>
-    <row r="452" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A452" s="2" t="s">
         <v>456</v>
       </c>
@@ -50794,7 +50789,7 @@
         <v>95.55</v>
       </c>
     </row>
-    <row r="453" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A453" s="2" t="s">
         <v>457</v>
       </c>
@@ -50889,7 +50884,7 @@
         <v>95.55</v>
       </c>
     </row>
-    <row r="454" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A454" s="2" t="s">
         <v>450</v>
       </c>
@@ -50984,7 +50979,7 @@
         <v>95.55</v>
       </c>
     </row>
-    <row r="455" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A455" s="2" t="s">
         <v>621</v>
       </c>
@@ -51045,7 +51040,7 @@
       <c r="AH455" s="4"/>
       <c r="AI455" s="4"/>
     </row>
-    <row r="456" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A456" s="2" t="s">
         <v>624</v>
       </c>
@@ -51106,7 +51101,7 @@
       <c r="AH456" s="4"/>
       <c r="AI456" s="4"/>
     </row>
-    <row r="457" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A457" s="2" t="s">
         <v>626</v>
       </c>
@@ -51167,7 +51162,7 @@
       <c r="AH457" s="4"/>
       <c r="AI457" s="4"/>
     </row>
-    <row r="458" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A458" s="2" t="s">
         <v>628</v>
       </c>
@@ -51228,7 +51223,7 @@
       <c r="AH458" s="4"/>
       <c r="AI458" s="4"/>
     </row>
-    <row r="459" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A459" s="2" t="s">
         <v>475</v>
       </c>
@@ -51323,7 +51318,7 @@
         <v>79.63</v>
       </c>
     </row>
-    <row r="460" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A460" s="2" t="s">
         <v>474</v>
       </c>
@@ -51418,7 +51413,7 @@
         <v>79.63</v>
       </c>
     </row>
-    <row r="461" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A461" s="2" t="s">
         <v>470</v>
       </c>
@@ -51513,7 +51508,7 @@
         <v>79.63</v>
       </c>
     </row>
-    <row r="462" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A462" s="2" t="s">
         <v>472</v>
       </c>
@@ -51608,7 +51603,7 @@
         <v>79.63</v>
       </c>
     </row>
-    <row r="463" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A463" s="2" t="s">
         <v>473</v>
       </c>
@@ -51703,7 +51698,7 @@
         <v>79.63</v>
       </c>
     </row>
-    <row r="464" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A464" s="2" t="s">
         <v>629</v>
       </c>
@@ -51798,7 +51793,7 @@
         <v>69.010000000000005</v>
       </c>
     </row>
-    <row r="465" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A465" s="2" t="s">
         <v>476</v>
       </c>
@@ -51893,7 +51888,7 @@
         <v>69.010000000000005</v>
       </c>
     </row>
-    <row r="466" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A466" s="2" t="s">
         <v>631</v>
       </c>
@@ -51988,7 +51983,7 @@
         <v>69.010000000000005</v>
       </c>
     </row>
-    <row r="467" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A467" s="2" t="s">
         <v>632</v>
       </c>
@@ -52083,7 +52078,7 @@
         <v>69.010000000000005</v>
       </c>
     </row>
-    <row r="468" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A468" s="2" t="s">
         <v>633</v>
       </c>
@@ -52178,7 +52173,7 @@
         <v>69.010000000000005</v>
       </c>
     </row>
-    <row r="469" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A469" s="2" t="s">
         <v>634</v>
       </c>
@@ -52273,7 +52268,7 @@
         <v>74.319999999999993</v>
       </c>
     </row>
-    <row r="470" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A470" s="2" t="s">
         <v>636</v>
       </c>
@@ -52368,7 +52363,7 @@
         <v>74.319999999999993</v>
       </c>
     </row>
-    <row r="471" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A471" s="2" t="s">
         <v>638</v>
       </c>
@@ -52463,7 +52458,7 @@
         <v>74.319999999999993</v>
       </c>
     </row>
-    <row r="472" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A472" s="2" t="s">
         <v>640</v>
       </c>
@@ -52558,7 +52553,7 @@
         <v>74.319999999999993</v>
       </c>
     </row>
-    <row r="473" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A473" s="2" t="s">
         <v>642</v>
       </c>
@@ -52619,7 +52614,7 @@
       <c r="AH473" s="4"/>
       <c r="AI473" s="4"/>
     </row>
-    <row r="474" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A474" s="2" t="s">
         <v>645</v>
       </c>
@@ -52680,7 +52675,7 @@
       <c r="AH474" s="4"/>
       <c r="AI474" s="4"/>
     </row>
-    <row r="475" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A475" s="2" t="s">
         <v>646</v>
       </c>
@@ -52741,7 +52736,7 @@
       <c r="AH475" s="4"/>
       <c r="AI475" s="4"/>
     </row>
-    <row r="476" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A476" s="2" t="s">
         <v>648</v>
       </c>
@@ -52802,7 +52797,7 @@
       <c r="AH476" s="4"/>
       <c r="AI476" s="4"/>
     </row>
-    <row r="477" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A477" s="2" t="s">
         <v>650</v>
       </c>
@@ -52863,7 +52858,7 @@
       <c r="AH477" s="4"/>
       <c r="AI477" s="4"/>
     </row>
-    <row r="478" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A478" s="2" t="s">
         <v>651</v>
       </c>
@@ -52924,7 +52919,7 @@
       <c r="AH478" s="4"/>
       <c r="AI478" s="4"/>
     </row>
-    <row r="479" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A479" s="2" t="s">
         <v>655</v>
       </c>
@@ -52985,7 +52980,7 @@
       <c r="AH479" s="4"/>
       <c r="AI479" s="4"/>
     </row>
-    <row r="480" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A480" s="2" t="s">
         <v>658</v>
       </c>
@@ -53046,7 +53041,7 @@
       <c r="AH480" s="4"/>
       <c r="AI480" s="4"/>
     </row>
-    <row r="481" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A481" s="2" t="s">
         <v>660</v>
       </c>
@@ -53107,7 +53102,7 @@
       <c r="AH481" s="4"/>
       <c r="AI481" s="4"/>
     </row>
-    <row r="482" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A482" s="2" t="s">
         <v>662</v>
       </c>
@@ -53168,7 +53163,7 @@
       <c r="AH482" s="4"/>
       <c r="AI482" s="4"/>
     </row>
-    <row r="483" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A483" s="2" t="s">
         <v>663</v>
       </c>
@@ -53229,7 +53224,7 @@
       <c r="AH483" s="4"/>
       <c r="AI483" s="4"/>
     </row>
-    <row r="484" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A484" s="2" t="s">
         <v>78</v>
       </c>
@@ -53324,7 +53319,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="485" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A485" s="2" t="s">
         <v>76</v>
       </c>
@@ -53419,7 +53414,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="486" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A486" s="2" t="s">
         <v>74</v>
       </c>
@@ -53514,7 +53509,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="487" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A487" s="2" t="s">
         <v>70</v>
       </c>
@@ -53609,7 +53604,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="488" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A488" s="2" t="s">
         <v>65</v>
       </c>
@@ -53704,7 +53699,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="489" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A489" s="2" t="s">
         <v>72</v>
       </c>
@@ -53799,7 +53794,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="490" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A490" s="2" t="s">
         <v>68</v>
       </c>
@@ -53894,7 +53889,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="491" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A491" s="2" t="s">
         <v>664</v>
       </c>
@@ -53955,7 +53950,7 @@
       <c r="AH491" s="4"/>
       <c r="AI491" s="4"/>
     </row>
-    <row r="492" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A492" s="2" t="s">
         <v>666</v>
       </c>
@@ -54016,7 +54011,7 @@
       <c r="AH492" s="4"/>
       <c r="AI492" s="4"/>
     </row>
-    <row r="493" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A493" s="2" t="s">
         <v>668</v>
       </c>
@@ -54077,7 +54072,7 @@
       <c r="AH493" s="4"/>
       <c r="AI493" s="4"/>
     </row>
-    <row r="494" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A494" s="2" t="s">
         <v>669</v>
       </c>
@@ -54138,7 +54133,7 @@
       <c r="AH494" s="4"/>
       <c r="AI494" s="4"/>
     </row>
-    <row r="495" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A495" s="2" t="s">
         <v>670</v>
       </c>
@@ -54199,7 +54194,7 @@
       <c r="AH495" s="4"/>
       <c r="AI495" s="4"/>
     </row>
-    <row r="496" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A496" s="2" t="s">
         <v>671</v>
       </c>
@@ -54260,7 +54255,7 @@
       <c r="AH496" s="4"/>
       <c r="AI496" s="4"/>
     </row>
-    <row r="497" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A497" s="2" t="s">
         <v>672</v>
       </c>
@@ -54321,7 +54316,7 @@
       <c r="AH497" s="4"/>
       <c r="AI497" s="4"/>
     </row>
-    <row r="498" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A498" s="2" t="s">
         <v>674</v>
       </c>
@@ -54382,7 +54377,7 @@
       <c r="AH498" s="4"/>
       <c r="AI498" s="4"/>
     </row>
-    <row r="499" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A499" s="2" t="s">
         <v>675</v>
       </c>
@@ -54443,7 +54438,7 @@
       <c r="AH499" s="4"/>
       <c r="AI499" s="4"/>
     </row>
-    <row r="500" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A500" s="2" t="s">
         <v>676</v>
       </c>
@@ -54504,7 +54499,7 @@
       <c r="AH500" s="4"/>
       <c r="AI500" s="4"/>
     </row>
-    <row r="501" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A501" s="2" t="s">
         <v>271</v>
       </c>
@@ -54599,7 +54594,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="502" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A502" s="2" t="s">
         <v>267</v>
       </c>
@@ -54694,7 +54689,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="503" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A503" s="2" t="s">
         <v>269</v>
       </c>
@@ -54789,7 +54784,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="504" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A504" s="2" t="s">
         <v>263</v>
       </c>
@@ -54884,7 +54879,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="505" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A505" s="2" t="s">
         <v>265</v>
       </c>
@@ -54979,7 +54974,7 @@
         <v>175.18</v>
       </c>
     </row>
-    <row r="506" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A506" s="2" t="s">
         <v>677</v>
       </c>
@@ -55074,7 +55069,7 @@
         <v>185.8</v>
       </c>
     </row>
-    <row r="507" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A507" s="2" t="s">
         <v>94</v>
       </c>
@@ -55169,7 +55164,7 @@
         <v>185.8</v>
       </c>
     </row>
-    <row r="508" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A508" s="2" t="s">
         <v>90</v>
       </c>
@@ -55264,7 +55259,7 @@
         <v>185.8</v>
       </c>
     </row>
-    <row r="509" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A509" s="2" t="s">
         <v>678</v>
       </c>
@@ -55359,7 +55354,7 @@
         <v>185.8</v>
       </c>
     </row>
-    <row r="510" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A510" s="2" t="s">
         <v>680</v>
       </c>
@@ -55454,7 +55449,7 @@
         <v>185.8</v>
       </c>
     </row>
-    <row r="511" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A511" s="2" t="s">
         <v>681</v>
       </c>
@@ -55549,7 +55544,7 @@
         <v>185.8</v>
       </c>
     </row>
-    <row r="512" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A512" s="2" t="s">
         <v>682</v>
       </c>
@@ -55644,7 +55639,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="513" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A513" s="2" t="s">
         <v>684</v>
       </c>
@@ -55739,7 +55734,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="514" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A514" s="2" t="s">
         <v>686</v>
       </c>
@@ -55834,7 +55829,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="515" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A515" s="2" t="s">
         <v>688</v>
       </c>
@@ -55929,7 +55924,7 @@
         <v>159.26</v>
       </c>
     </row>
-    <row r="516" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A516" s="2" t="s">
         <v>689</v>
       </c>
@@ -56309,7 +56304,7 @@
         <v>212.34</v>
       </c>
     </row>
-    <row r="520" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A520" s="2" t="s">
         <v>695</v>
       </c>
@@ -56404,7 +56399,7 @@
         <v>291.97000000000003</v>
       </c>
     </row>
-    <row r="521" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A521" s="2" t="s">
         <v>696</v>
       </c>
@@ -56499,7 +56494,7 @@
         <v>291.97000000000003</v>
       </c>
     </row>
-    <row r="522" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A522" s="2" t="s">
         <v>698</v>
       </c>
@@ -56560,7 +56555,7 @@
       <c r="AH522" s="4"/>
       <c r="AI522" s="4"/>
     </row>
-    <row r="523" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A523" s="2" t="s">
         <v>704</v>
       </c>
@@ -56621,7 +56616,7 @@
       <c r="AH523" s="4"/>
       <c r="AI523" s="4"/>
     </row>
-    <row r="524" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A524" s="2" t="s">
         <v>706</v>
       </c>
@@ -56682,7 +56677,7 @@
       <c r="AH524" s="4"/>
       <c r="AI524" s="4"/>
     </row>
-    <row r="525" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A525" s="2" t="s">
         <v>711</v>
       </c>
@@ -56743,7 +56738,7 @@
       <c r="AH525" s="4"/>
       <c r="AI525" s="4"/>
     </row>
-    <row r="526" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A526" s="2" t="s">
         <v>712</v>
       </c>
@@ -56804,7 +56799,7 @@
       <c r="AH526" s="4"/>
       <c r="AI526" s="4"/>
     </row>
-    <row r="527" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A527" s="2" t="s">
         <v>713</v>
       </c>
@@ -56865,7 +56860,7 @@
       <c r="AH527" s="4"/>
       <c r="AI527" s="4"/>
     </row>
-    <row r="528" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A528" s="2" t="s">
         <v>716</v>
       </c>
@@ -56926,7 +56921,7 @@
       <c r="AH528" s="4"/>
       <c r="AI528" s="4"/>
     </row>
-    <row r="529" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A529" s="2" t="s">
         <v>717</v>
       </c>
@@ -56987,7 +56982,7 @@
       <c r="AH529" s="4"/>
       <c r="AI529" s="4"/>
     </row>
-    <row r="530" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A530" s="2" t="s">
         <v>720</v>
       </c>
@@ -57048,7 +57043,7 @@
       <c r="AH530" s="4"/>
       <c r="AI530" s="4"/>
     </row>
-    <row r="531" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A531" s="2" t="s">
         <v>721</v>
       </c>
@@ -57109,7 +57104,7 @@
       <c r="AH531" s="4"/>
       <c r="AI531" s="4"/>
     </row>
-    <row r="532" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A532" s="2" t="s">
         <v>723</v>
       </c>
@@ -57170,7 +57165,7 @@
       <c r="AH532" s="4"/>
       <c r="AI532" s="4"/>
     </row>
-    <row r="533" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A533" s="2" t="s">
         <v>724</v>
       </c>
@@ -57231,7 +57226,7 @@
       <c r="AH533" s="4"/>
       <c r="AI533" s="4"/>
     </row>
-    <row r="534" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A534" s="2" t="s">
         <v>727</v>
       </c>
@@ -57292,7 +57287,7 @@
       <c r="AH534" s="4"/>
       <c r="AI534" s="4"/>
     </row>
-    <row r="535" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A535" s="2" t="s">
         <v>728</v>
       </c>
@@ -57353,7 +57348,7 @@
       <c r="AH535" s="4"/>
       <c r="AI535" s="4"/>
     </row>
-    <row r="536" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A536" s="2" t="s">
         <v>729</v>
       </c>
@@ -57414,9 +57409,9 @@
       <c r="AH536" s="4"/>
       <c r="AI536" s="4"/>
     </row>
-    <row r="537" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A537" s="2" t="s">
-        <v>1544</v>
+        <v>1542</v>
       </c>
       <c r="B537" s="2" t="s">
         <v>730</v>
@@ -57475,7 +57470,7 @@
       <c r="AH537" s="4"/>
       <c r="AI537" s="4"/>
     </row>
-    <row r="538" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A538" s="2" t="s">
         <v>735</v>
       </c>
@@ -57536,7 +57531,7 @@
       <c r="AH538" s="4"/>
       <c r="AI538" s="4"/>
     </row>
-    <row r="539" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A539" s="2" t="s">
         <v>736</v>
       </c>
@@ -57597,7 +57592,7 @@
       <c r="AH539" s="4"/>
       <c r="AI539" s="4"/>
     </row>
-    <row r="540" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A540" s="2" t="s">
         <v>740</v>
       </c>
@@ -57658,7 +57653,7 @@
       <c r="AH540" s="4"/>
       <c r="AI540" s="4"/>
     </row>
-    <row r="541" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A541" s="2" t="s">
         <v>743</v>
       </c>
@@ -57719,7 +57714,7 @@
       <c r="AH541" s="4"/>
       <c r="AI541" s="4"/>
     </row>
-    <row r="542" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A542" s="2" t="s">
         <v>745</v>
       </c>
@@ -57780,7 +57775,7 @@
       <c r="AH542" s="4"/>
       <c r="AI542" s="4"/>
     </row>
-    <row r="543" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A543" s="2" t="s">
         <v>747</v>
       </c>
@@ -57841,7 +57836,7 @@
       <c r="AH543" s="4"/>
       <c r="AI543" s="4"/>
     </row>
-    <row r="544" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A544" s="2" t="s">
         <v>749</v>
       </c>
@@ -57902,7 +57897,7 @@
       <c r="AH544" s="4"/>
       <c r="AI544" s="4"/>
     </row>
-    <row r="545" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A545" s="2" t="s">
         <v>750</v>
       </c>
@@ -57963,7 +57958,7 @@
       <c r="AH545" s="4"/>
       <c r="AI545" s="4"/>
     </row>
-    <row r="546" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A546" s="2" t="s">
         <v>751</v>
       </c>
@@ -58024,7 +58019,7 @@
       <c r="AH546" s="4"/>
       <c r="AI546" s="4"/>
     </row>
-    <row r="547" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A547" s="2" t="s">
         <v>754</v>
       </c>
@@ -58085,7 +58080,7 @@
       <c r="AH547" s="4"/>
       <c r="AI547" s="4"/>
     </row>
-    <row r="548" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A548" s="2" t="s">
         <v>755</v>
       </c>
@@ -58146,7 +58141,7 @@
       <c r="AH548" s="4"/>
       <c r="AI548" s="4"/>
     </row>
-    <row r="549" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A549" s="2" t="s">
         <v>757</v>
       </c>
@@ -58207,7 +58202,7 @@
       <c r="AH549" s="4"/>
       <c r="AI549" s="4"/>
     </row>
-    <row r="550" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A550" s="2" t="s">
         <v>759</v>
       </c>
@@ -58268,7 +58263,7 @@
       <c r="AH550" s="4"/>
       <c r="AI550" s="4"/>
     </row>
-    <row r="551" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A551" s="2" t="s">
         <v>760</v>
       </c>
@@ -58329,7 +58324,7 @@
       <c r="AH551" s="4"/>
       <c r="AI551" s="4"/>
     </row>
-    <row r="552" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A552" s="2" t="s">
         <v>762</v>
       </c>
@@ -58390,7 +58385,7 @@
       <c r="AH552" s="4"/>
       <c r="AI552" s="4"/>
     </row>
-    <row r="553" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A553" s="2" t="s">
         <v>764</v>
       </c>
@@ -58451,7 +58446,7 @@
       <c r="AH553" s="4"/>
       <c r="AI553" s="4"/>
     </row>
-    <row r="554" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A554" s="2" t="s">
         <v>767</v>
       </c>
@@ -58512,7 +58507,7 @@
       <c r="AH554" s="4"/>
       <c r="AI554" s="4"/>
     </row>
-    <row r="555" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A555" s="2" t="s">
         <v>769</v>
       </c>
@@ -58573,7 +58568,7 @@
       <c r="AH555" s="4"/>
       <c r="AI555" s="4"/>
     </row>
-    <row r="556" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A556" s="2" t="s">
         <v>770</v>
       </c>
@@ -58634,7 +58629,7 @@
       <c r="AH556" s="4"/>
       <c r="AI556" s="4"/>
     </row>
-    <row r="557" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A557" s="2" t="s">
         <v>773</v>
       </c>
@@ -58695,7 +58690,7 @@
       <c r="AH557" s="4"/>
       <c r="AI557" s="4"/>
     </row>
-    <row r="558" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A558" s="2" t="s">
         <v>774</v>
       </c>
@@ -58756,7 +58751,7 @@
       <c r="AH558" s="4"/>
       <c r="AI558" s="4"/>
     </row>
-    <row r="559" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A559" s="2" t="s">
         <v>777</v>
       </c>
@@ -58817,7 +58812,7 @@
       <c r="AH559" s="4"/>
       <c r="AI559" s="4"/>
     </row>
-    <row r="560" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A560" s="2" t="s">
         <v>778</v>
       </c>
@@ -58878,7 +58873,7 @@
       <c r="AH560" s="4"/>
       <c r="AI560" s="4"/>
     </row>
-    <row r="561" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A561" s="2" t="s">
         <v>780</v>
       </c>
@@ -58939,7 +58934,7 @@
       <c r="AH561" s="4"/>
       <c r="AI561" s="4"/>
     </row>
-    <row r="562" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A562" s="2" t="s">
         <v>783</v>
       </c>
@@ -59000,7 +58995,7 @@
       <c r="AH562" s="4"/>
       <c r="AI562" s="4"/>
     </row>
-    <row r="563" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A563" s="2" t="s">
         <v>784</v>
       </c>
@@ -59061,7 +59056,7 @@
       <c r="AH563" s="4"/>
       <c r="AI563" s="4"/>
     </row>
-    <row r="564" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A564" s="2" t="s">
         <v>787</v>
       </c>
@@ -59122,7 +59117,7 @@
       <c r="AH564" s="4"/>
       <c r="AI564" s="4"/>
     </row>
-    <row r="565" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A565" s="2" t="s">
         <v>788</v>
       </c>
@@ -59183,7 +59178,7 @@
       <c r="AH565" s="4"/>
       <c r="AI565" s="4"/>
     </row>
-    <row r="566" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A566" s="2" t="s">
         <v>792</v>
       </c>
@@ -59244,7 +59239,7 @@
       <c r="AH566" s="4"/>
       <c r="AI566" s="4"/>
     </row>
-    <row r="567" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A567" s="2" t="s">
         <v>795</v>
       </c>
@@ -59305,7 +59300,7 @@
       <c r="AH567" s="4"/>
       <c r="AI567" s="4"/>
     </row>
-    <row r="568" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A568" s="2" t="s">
         <v>801</v>
       </c>
@@ -59366,7 +59361,7 @@
       <c r="AH568" s="4"/>
       <c r="AI568" s="4"/>
     </row>
-    <row r="569" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A569" s="2" t="s">
         <v>802</v>
       </c>
@@ -59427,7 +59422,7 @@
       <c r="AH569" s="4"/>
       <c r="AI569" s="4"/>
     </row>
-    <row r="570" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A570" s="2" t="s">
         <v>804</v>
       </c>
@@ -59488,7 +59483,7 @@
       <c r="AH570" s="4"/>
       <c r="AI570" s="4"/>
     </row>
-    <row r="571" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A571" s="2" t="s">
         <v>806</v>
       </c>
@@ -59549,7 +59544,7 @@
       <c r="AH571" s="4"/>
       <c r="AI571" s="4"/>
     </row>
-    <row r="572" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A572" s="2" t="s">
         <v>808</v>
       </c>
@@ -59610,7 +59605,7 @@
       <c r="AH572" s="4"/>
       <c r="AI572" s="4"/>
     </row>
-    <row r="573" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A573" s="2" t="s">
         <v>811</v>
       </c>
@@ -59671,7 +59666,7 @@
       <c r="AH573" s="4"/>
       <c r="AI573" s="4"/>
     </row>
-    <row r="574" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A574" s="2" t="s">
         <v>812</v>
       </c>
@@ -59732,7 +59727,7 @@
       <c r="AH574" s="4"/>
       <c r="AI574" s="4"/>
     </row>
-    <row r="575" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A575" s="2" t="s">
         <v>813</v>
       </c>
@@ -59793,7 +59788,7 @@
       <c r="AH575" s="4"/>
       <c r="AI575" s="4"/>
     </row>
-    <row r="576" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A576" s="2" t="s">
         <v>816</v>
       </c>
@@ -59854,7 +59849,7 @@
       <c r="AH576" s="4"/>
       <c r="AI576" s="4"/>
     </row>
-    <row r="577" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A577" s="2" t="s">
         <v>817</v>
       </c>
@@ -59915,7 +59910,7 @@
       <c r="AH577" s="4"/>
       <c r="AI577" s="4"/>
     </row>
-    <row r="578" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A578" s="2" t="s">
         <v>818</v>
       </c>
@@ -59976,7 +59971,7 @@
       <c r="AH578" s="4"/>
       <c r="AI578" s="4"/>
     </row>
-    <row r="579" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A579" s="2" t="s">
         <v>821</v>
       </c>
@@ -60037,7 +60032,7 @@
       <c r="AH579" s="4"/>
       <c r="AI579" s="4"/>
     </row>
-    <row r="580" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A580" s="2" t="s">
         <v>822</v>
       </c>
@@ -60098,7 +60093,7 @@
       <c r="AH580" s="4"/>
       <c r="AI580" s="4"/>
     </row>
-    <row r="581" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A581" s="2" t="s">
         <v>823</v>
       </c>
@@ -60159,7 +60154,7 @@
       <c r="AH581" s="4"/>
       <c r="AI581" s="4"/>
     </row>
-    <row r="582" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A582" s="2" t="s">
         <v>826</v>
       </c>
@@ -60220,7 +60215,7 @@
       <c r="AH582" s="4"/>
       <c r="AI582" s="4"/>
     </row>
-    <row r="583" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A583" s="2" t="s">
         <v>827</v>
       </c>
@@ -60281,7 +60276,7 @@
       <c r="AH583" s="4"/>
       <c r="AI583" s="4"/>
     </row>
-    <row r="584" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A584" s="2" t="s">
         <v>828</v>
       </c>
@@ -60342,7 +60337,7 @@
       <c r="AH584" s="4"/>
       <c r="AI584" s="4"/>
     </row>
-    <row r="585" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A585" s="2" t="s">
         <v>832</v>
       </c>
@@ -60403,7 +60398,7 @@
       <c r="AH585" s="4"/>
       <c r="AI585" s="4"/>
     </row>
-    <row r="586" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A586" s="2" t="s">
         <v>833</v>
       </c>
@@ -60464,7 +60459,7 @@
       <c r="AH586" s="4"/>
       <c r="AI586" s="4"/>
     </row>
-    <row r="587" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A587" s="2" t="s">
         <v>834</v>
       </c>
@@ -60525,7 +60520,7 @@
       <c r="AH587" s="4"/>
       <c r="AI587" s="4"/>
     </row>
-    <row r="588" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A588" s="2" t="s">
         <v>837</v>
       </c>
@@ -60586,7 +60581,7 @@
       <c r="AH588" s="4"/>
       <c r="AI588" s="4"/>
     </row>
-    <row r="589" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A589" s="2" t="s">
         <v>838</v>
       </c>
@@ -60647,7 +60642,7 @@
       <c r="AH589" s="4"/>
       <c r="AI589" s="4"/>
     </row>
-    <row r="590" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A590" s="2" t="s">
         <v>839</v>
       </c>
@@ -60708,7 +60703,7 @@
       <c r="AH590" s="4"/>
       <c r="AI590" s="4"/>
     </row>
-    <row r="591" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A591" s="2" t="s">
         <v>842</v>
       </c>
@@ -60769,7 +60764,7 @@
       <c r="AH591" s="4"/>
       <c r="AI591" s="4"/>
     </row>
-    <row r="592" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A592" s="2" t="s">
         <v>843</v>
       </c>
@@ -60830,7 +60825,7 @@
       <c r="AH592" s="4"/>
       <c r="AI592" s="4"/>
     </row>
-    <row r="593" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A593" s="2" t="s">
         <v>844</v>
       </c>
@@ -60891,7 +60886,7 @@
       <c r="AH593" s="4"/>
       <c r="AI593" s="4"/>
     </row>
-    <row r="594" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A594" s="2" t="s">
         <v>847</v>
       </c>
@@ -60952,7 +60947,7 @@
       <c r="AH594" s="4"/>
       <c r="AI594" s="4"/>
     </row>
-    <row r="595" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A595" s="2" t="s">
         <v>848</v>
       </c>
@@ -61013,7 +61008,7 @@
       <c r="AH595" s="4"/>
       <c r="AI595" s="4"/>
     </row>
-    <row r="596" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A596" s="2" t="s">
         <v>849</v>
       </c>
@@ -61074,7 +61069,7 @@
       <c r="AH596" s="4"/>
       <c r="AI596" s="4"/>
     </row>
-    <row r="597" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A597" s="2" t="s">
         <v>850</v>
       </c>
@@ -61135,7 +61130,7 @@
       <c r="AH597" s="4"/>
       <c r="AI597" s="4"/>
     </row>
-    <row r="598" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A598" s="2" t="s">
         <v>854</v>
       </c>
@@ -61196,7 +61191,7 @@
       <c r="AH598" s="4"/>
       <c r="AI598" s="4"/>
     </row>
-    <row r="599" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A599" s="2" t="s">
         <v>855</v>
       </c>
@@ -61257,7 +61252,7 @@
       <c r="AH599" s="4"/>
       <c r="AI599" s="4"/>
     </row>
-    <row r="600" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A600" s="2" t="s">
         <v>856</v>
       </c>
@@ -61318,7 +61313,7 @@
       <c r="AH600" s="4"/>
       <c r="AI600" s="4"/>
     </row>
-    <row r="601" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A601" s="2" t="s">
         <v>857</v>
       </c>
@@ -61379,7 +61374,7 @@
       <c r="AH601" s="4"/>
       <c r="AI601" s="4"/>
     </row>
-    <row r="602" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A602" s="2" t="s">
         <v>858</v>
       </c>
@@ -61440,7 +61435,7 @@
       <c r="AH602" s="4"/>
       <c r="AI602" s="4"/>
     </row>
-    <row r="603" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A603" s="2" t="s">
         <v>861</v>
       </c>
@@ -61501,7 +61496,7 @@
       <c r="AH603" s="4"/>
       <c r="AI603" s="4"/>
     </row>
-    <row r="604" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A604" s="2" t="s">
         <v>862</v>
       </c>
@@ -61562,7 +61557,7 @@
       <c r="AH604" s="4"/>
       <c r="AI604" s="4"/>
     </row>
-    <row r="605" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A605" s="2" t="s">
         <v>863</v>
       </c>
@@ -61623,7 +61618,7 @@
       <c r="AH605" s="4"/>
       <c r="AI605" s="4"/>
     </row>
-    <row r="606" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A606" s="2" t="s">
         <v>866</v>
       </c>
@@ -61684,7 +61679,7 @@
       <c r="AH606" s="4"/>
       <c r="AI606" s="4"/>
     </row>
-    <row r="607" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A607" s="2" t="s">
         <v>867</v>
       </c>
@@ -61745,7 +61740,7 @@
       <c r="AH607" s="4"/>
       <c r="AI607" s="4"/>
     </row>
-    <row r="608" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A608" s="2" t="s">
         <v>868</v>
       </c>
@@ -61806,7 +61801,7 @@
       <c r="AH608" s="4"/>
       <c r="AI608" s="4"/>
     </row>
-    <row r="609" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A609" s="2" t="s">
         <v>871</v>
       </c>
@@ -61867,7 +61862,7 @@
       <c r="AH609" s="4"/>
       <c r="AI609" s="4"/>
     </row>
-    <row r="610" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A610" s="2" t="s">
         <v>872</v>
       </c>
@@ -61928,7 +61923,7 @@
       <c r="AH610" s="4"/>
       <c r="AI610" s="4"/>
     </row>
-    <row r="611" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A611" s="2" t="s">
         <v>873</v>
       </c>
@@ -61989,7 +61984,7 @@
       <c r="AH611" s="4"/>
       <c r="AI611" s="4"/>
     </row>
-    <row r="612" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A612" s="2" t="s">
         <v>876</v>
       </c>
@@ -62050,7 +62045,7 @@
       <c r="AH612" s="4"/>
       <c r="AI612" s="4"/>
     </row>
-    <row r="613" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A613" s="2" t="s">
         <v>877</v>
       </c>
@@ -62111,7 +62106,7 @@
       <c r="AH613" s="4"/>
       <c r="AI613" s="4"/>
     </row>
-    <row r="614" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A614" s="2" t="s">
         <v>878</v>
       </c>
@@ -62172,7 +62167,7 @@
       <c r="AH614" s="4"/>
       <c r="AI614" s="4"/>
     </row>
-    <row r="615" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A615" s="2" t="s">
         <v>881</v>
       </c>
@@ -62233,7 +62228,7 @@
       <c r="AH615" s="4"/>
       <c r="AI615" s="4"/>
     </row>
-    <row r="616" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A616" s="2" t="s">
         <v>882</v>
       </c>
@@ -62294,7 +62289,7 @@
       <c r="AH616" s="4"/>
       <c r="AI616" s="4"/>
     </row>
-    <row r="617" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A617" s="2" t="s">
         <v>883</v>
       </c>
@@ -62355,7 +62350,7 @@
       <c r="AH617" s="4"/>
       <c r="AI617" s="4"/>
     </row>
-    <row r="618" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A618" s="2" t="s">
         <v>886</v>
       </c>
@@ -62416,7 +62411,7 @@
       <c r="AH618" s="4"/>
       <c r="AI618" s="4"/>
     </row>
-    <row r="619" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A619" s="2" t="s">
         <v>887</v>
       </c>
@@ -62477,7 +62472,7 @@
       <c r="AH619" s="4"/>
       <c r="AI619" s="4"/>
     </row>
-    <row r="620" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A620" s="2" t="s">
         <v>888</v>
       </c>
@@ -62538,7 +62533,7 @@
       <c r="AH620" s="4"/>
       <c r="AI620" s="4"/>
     </row>
-    <row r="621" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A621" s="2" t="s">
         <v>891</v>
       </c>
@@ -62599,7 +62594,7 @@
       <c r="AH621" s="4"/>
       <c r="AI621" s="4"/>
     </row>
-    <row r="622" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A622" s="2" t="s">
         <v>892</v>
       </c>
@@ -62660,7 +62655,7 @@
       <c r="AH622" s="4"/>
       <c r="AI622" s="4"/>
     </row>
-    <row r="623" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A623" s="2" t="s">
         <v>893</v>
       </c>
@@ -62721,7 +62716,7 @@
       <c r="AH623" s="4"/>
       <c r="AI623" s="4"/>
     </row>
-    <row r="624" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A624" s="2" t="s">
         <v>896</v>
       </c>
@@ -62782,7 +62777,7 @@
       <c r="AH624" s="4"/>
       <c r="AI624" s="4"/>
     </row>
-    <row r="625" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A625" s="2" t="s">
         <v>897</v>
       </c>
@@ -62843,7 +62838,7 @@
       <c r="AH625" s="4"/>
       <c r="AI625" s="4"/>
     </row>
-    <row r="626" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A626" s="2" t="s">
         <v>898</v>
       </c>
@@ -62904,7 +62899,7 @@
       <c r="AH626" s="4"/>
       <c r="AI626" s="4"/>
     </row>
-    <row r="627" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A627" s="2" t="s">
         <v>899</v>
       </c>
@@ -62965,7 +62960,7 @@
       <c r="AH627" s="4"/>
       <c r="AI627" s="4"/>
     </row>
-    <row r="628" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A628" s="2" t="s">
         <v>902</v>
       </c>
@@ -63026,7 +63021,7 @@
       <c r="AH628" s="4"/>
       <c r="AI628" s="4"/>
     </row>
-    <row r="629" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A629" s="2" t="s">
         <v>904</v>
       </c>
@@ -63087,7 +63082,7 @@
       <c r="AH629" s="4"/>
       <c r="AI629" s="4"/>
     </row>
-    <row r="630" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A630" s="2" t="s">
         <v>906</v>
       </c>
@@ -63148,7 +63143,7 @@
       <c r="AH630" s="4"/>
       <c r="AI630" s="4"/>
     </row>
-    <row r="631" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A631" s="2" t="s">
         <v>908</v>
       </c>
@@ -63209,7 +63204,7 @@
       <c r="AH631" s="4"/>
       <c r="AI631" s="4"/>
     </row>
-    <row r="632" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A632" s="2" t="s">
         <v>912</v>
       </c>
@@ -63270,7 +63265,7 @@
       <c r="AH632" s="4"/>
       <c r="AI632" s="4"/>
     </row>
-    <row r="633" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A633" s="2" t="s">
         <v>914</v>
       </c>
@@ -63331,7 +63326,7 @@
       <c r="AH633" s="4"/>
       <c r="AI633" s="4"/>
     </row>
-    <row r="634" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A634" s="2" t="s">
         <v>916</v>
       </c>
@@ -63392,7 +63387,7 @@
       <c r="AH634" s="4"/>
       <c r="AI634" s="4"/>
     </row>
-    <row r="635" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A635" s="2" t="s">
         <v>918</v>
       </c>
@@ -63453,7 +63448,7 @@
       <c r="AH635" s="4"/>
       <c r="AI635" s="4"/>
     </row>
-    <row r="636" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A636" s="2" t="s">
         <v>920</v>
       </c>
@@ -63514,7 +63509,7 @@
       <c r="AH636" s="4"/>
       <c r="AI636" s="4"/>
     </row>
-    <row r="637" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A637" s="2" t="s">
         <v>923</v>
       </c>
@@ -63575,7 +63570,7 @@
       <c r="AH637" s="4"/>
       <c r="AI637" s="4"/>
     </row>
-    <row r="638" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A638" s="2" t="s">
         <v>924</v>
       </c>
@@ -63636,7 +63631,7 @@
       <c r="AH638" s="4"/>
       <c r="AI638" s="4"/>
     </row>
-    <row r="639" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A639" s="2" t="s">
         <v>925</v>
       </c>
@@ -63697,7 +63692,7 @@
       <c r="AH639" s="4"/>
       <c r="AI639" s="4"/>
     </row>
-    <row r="640" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A640" s="2" t="s">
         <v>926</v>
       </c>
@@ -63758,7 +63753,7 @@
       <c r="AH640" s="4"/>
       <c r="AI640" s="4"/>
     </row>
-    <row r="641" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A641" s="2" t="s">
         <v>927</v>
       </c>
@@ -63819,7 +63814,7 @@
       <c r="AH641" s="4"/>
       <c r="AI641" s="4"/>
     </row>
-    <row r="642" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A642" s="2" t="s">
         <v>930</v>
       </c>
@@ -63880,7 +63875,7 @@
       <c r="AH642" s="4"/>
       <c r="AI642" s="4"/>
     </row>
-    <row r="643" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A643" s="2" t="s">
         <v>934</v>
       </c>
@@ -63941,7 +63936,7 @@
       <c r="AH643" s="4"/>
       <c r="AI643" s="4"/>
     </row>
-    <row r="644" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A644" s="2" t="s">
         <v>935</v>
       </c>
@@ -64002,7 +63997,7 @@
       <c r="AH644" s="4"/>
       <c r="AI644" s="4"/>
     </row>
-    <row r="645" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A645" s="2" t="s">
         <v>938</v>
       </c>
@@ -64063,7 +64058,7 @@
       <c r="AH645" s="4"/>
       <c r="AI645" s="4"/>
     </row>
-    <row r="646" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A646" s="2" t="s">
         <v>939</v>
       </c>
@@ -64124,7 +64119,7 @@
       <c r="AH646" s="4"/>
       <c r="AI646" s="4"/>
     </row>
-    <row r="647" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A647" s="2" t="s">
         <v>942</v>
       </c>
@@ -64185,7 +64180,7 @@
       <c r="AH647" s="4"/>
       <c r="AI647" s="4"/>
     </row>
-    <row r="648" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A648" s="2" t="s">
         <v>945</v>
       </c>
@@ -64246,7 +64241,7 @@
       <c r="AH648" s="4"/>
       <c r="AI648" s="4"/>
     </row>
-    <row r="649" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A649" s="2" t="s">
         <v>947</v>
       </c>
@@ -64307,7 +64302,7 @@
       <c r="AH649" s="4"/>
       <c r="AI649" s="4"/>
     </row>
-    <row r="650" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A650" s="2" t="s">
         <v>950</v>
       </c>
@@ -64368,7 +64363,7 @@
       <c r="AH650" s="4"/>
       <c r="AI650" s="4"/>
     </row>
-    <row r="651" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A651" s="2" t="s">
         <v>953</v>
       </c>
@@ -64429,7 +64424,7 @@
       <c r="AH651" s="4"/>
       <c r="AI651" s="4"/>
     </row>
-    <row r="652" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A652" s="2" t="s">
         <v>956</v>
       </c>
@@ -64490,7 +64485,7 @@
       <c r="AH652" s="4"/>
       <c r="AI652" s="4"/>
     </row>
-    <row r="653" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A653" s="2" t="s">
         <v>957</v>
       </c>
@@ -64551,7 +64546,7 @@
       <c r="AH653" s="4"/>
       <c r="AI653" s="4"/>
     </row>
-    <row r="654" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A654" s="2" t="s">
         <v>958</v>
       </c>
@@ -64612,7 +64607,7 @@
       <c r="AH654" s="4"/>
       <c r="AI654" s="4"/>
     </row>
-    <row r="655" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A655" s="2" t="s">
         <v>961</v>
       </c>
@@ -64673,7 +64668,7 @@
       <c r="AH655" s="4"/>
       <c r="AI655" s="4"/>
     </row>
-    <row r="656" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A656" s="2" t="s">
         <v>963</v>
       </c>
@@ -64734,7 +64729,7 @@
       <c r="AH656" s="4"/>
       <c r="AI656" s="4"/>
     </row>
-    <row r="657" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A657" s="2" t="s">
         <v>964</v>
       </c>
@@ -64795,7 +64790,7 @@
       <c r="AH657" s="4"/>
       <c r="AI657" s="4"/>
     </row>
-    <row r="658" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A658" s="2" t="s">
         <v>965</v>
       </c>
@@ -64856,7 +64851,7 @@
       <c r="AH658" s="4"/>
       <c r="AI658" s="4"/>
     </row>
-    <row r="659" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A659" s="2" t="s">
         <v>966</v>
       </c>
@@ -64917,7 +64912,7 @@
       <c r="AH659" s="4"/>
       <c r="AI659" s="4"/>
     </row>
-    <row r="660" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A660" s="2" t="s">
         <v>969</v>
       </c>
@@ -64978,7 +64973,7 @@
       <c r="AH660" s="4"/>
       <c r="AI660" s="4"/>
     </row>
-    <row r="661" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A661" s="2" t="s">
         <v>970</v>
       </c>
@@ -65039,7 +65034,7 @@
       <c r="AH661" s="4"/>
       <c r="AI661" s="4"/>
     </row>
-    <row r="662" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A662" s="2" t="s">
         <v>972</v>
       </c>
@@ -65100,7 +65095,7 @@
       <c r="AH662" s="4"/>
       <c r="AI662" s="4"/>
     </row>
-    <row r="663" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A663" s="2" t="s">
         <v>973</v>
       </c>
@@ -65161,7 +65156,7 @@
       <c r="AH663" s="4"/>
       <c r="AI663" s="4"/>
     </row>
-    <row r="664" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A664" s="2" t="s">
         <v>974</v>
       </c>
@@ -65222,7 +65217,7 @@
       <c r="AH664" s="4"/>
       <c r="AI664" s="4"/>
     </row>
-    <row r="665" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A665" s="2" t="s">
         <v>977</v>
       </c>
@@ -65283,7 +65278,7 @@
       <c r="AH665" s="4"/>
       <c r="AI665" s="4"/>
     </row>
-    <row r="666" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A666" s="2" t="s">
         <v>979</v>
       </c>
@@ -65344,7 +65339,7 @@
       <c r="AH666" s="4"/>
       <c r="AI666" s="4"/>
     </row>
-    <row r="667" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="667" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A667" s="2" t="s">
         <v>981</v>
       </c>
@@ -65405,7 +65400,7 @@
       <c r="AH667" s="4"/>
       <c r="AI667" s="4"/>
     </row>
-    <row r="668" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A668" s="2" t="s">
         <v>984</v>
       </c>
@@ -65466,7 +65461,7 @@
       <c r="AH668" s="4"/>
       <c r="AI668" s="4"/>
     </row>
-    <row r="669" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A669" s="2" t="s">
         <v>987</v>
       </c>
@@ -65527,7 +65522,7 @@
       <c r="AH669" s="4"/>
       <c r="AI669" s="4"/>
     </row>
-    <row r="670" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="670" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A670" s="2" t="s">
         <v>990</v>
       </c>
@@ -65588,7 +65583,7 @@
       <c r="AH670" s="4"/>
       <c r="AI670" s="4"/>
     </row>
-    <row r="671" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A671" s="2" t="s">
         <v>991</v>
       </c>
@@ -65649,7 +65644,7 @@
       <c r="AH671" s="4"/>
       <c r="AI671" s="4"/>
     </row>
-    <row r="672" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="672" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A672" s="2" t="s">
         <v>994</v>
       </c>
@@ -65710,7 +65705,7 @@
       <c r="AH672" s="4"/>
       <c r="AI672" s="4"/>
     </row>
-    <row r="673" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A673" s="2" t="s">
         <v>995</v>
       </c>
@@ -65771,7 +65766,7 @@
       <c r="AH673" s="4"/>
       <c r="AI673" s="4"/>
     </row>
-    <row r="674" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A674" s="2" t="s">
         <v>996</v>
       </c>
@@ -65832,7 +65827,7 @@
       <c r="AH674" s="4"/>
       <c r="AI674" s="4"/>
     </row>
-    <row r="675" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="675" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A675" s="2" t="s">
         <v>997</v>
       </c>
@@ -65893,7 +65888,7 @@
       <c r="AH675" s="4"/>
       <c r="AI675" s="4"/>
     </row>
-    <row r="676" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="676" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A676" s="2" t="s">
         <v>1000</v>
       </c>
@@ -65954,7 +65949,7 @@
       <c r="AH676" s="4"/>
       <c r="AI676" s="4"/>
     </row>
-    <row r="677" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A677" s="2" t="s">
         <v>1001</v>
       </c>
@@ -66015,7 +66010,7 @@
       <c r="AH677" s="4"/>
       <c r="AI677" s="4"/>
     </row>
-    <row r="678" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="678" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A678" s="2" t="s">
         <v>1002</v>
       </c>
@@ -66076,7 +66071,7 @@
       <c r="AH678" s="4"/>
       <c r="AI678" s="4"/>
     </row>
-    <row r="679" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A679" s="2" t="s">
         <v>1003</v>
       </c>
@@ -66137,7 +66132,7 @@
       <c r="AH679" s="4"/>
       <c r="AI679" s="4"/>
     </row>
-    <row r="680" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="680" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A680" s="2" t="s">
         <v>1006</v>
       </c>
@@ -66198,7 +66193,7 @@
       <c r="AH680" s="4"/>
       <c r="AI680" s="4"/>
     </row>
-    <row r="681" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="681" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A681" s="2" t="s">
         <v>1009</v>
       </c>
@@ -66259,7 +66254,7 @@
       <c r="AH681" s="4"/>
       <c r="AI681" s="4"/>
     </row>
-    <row r="682" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="682" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A682" s="2" t="s">
         <v>1010</v>
       </c>
@@ -66320,7 +66315,7 @@
       <c r="AH682" s="4"/>
       <c r="AI682" s="4"/>
     </row>
-    <row r="683" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="683" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A683" s="2" t="s">
         <v>1011</v>
       </c>
@@ -66381,7 +66376,7 @@
       <c r="AH683" s="4"/>
       <c r="AI683" s="4"/>
     </row>
-    <row r="684" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="684" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A684" s="2" t="s">
         <v>1012</v>
       </c>
@@ -66442,7 +66437,7 @@
       <c r="AH684" s="4"/>
       <c r="AI684" s="4"/>
     </row>
-    <row r="685" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="685" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A685" s="2" t="s">
         <v>1013</v>
       </c>
@@ -66503,7 +66498,7 @@
       <c r="AH685" s="4"/>
       <c r="AI685" s="4"/>
     </row>
-    <row r="686" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="686" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A686" s="2" t="s">
         <v>1016</v>
       </c>
@@ -66564,7 +66559,7 @@
       <c r="AH686" s="4"/>
       <c r="AI686" s="4"/>
     </row>
-    <row r="687" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="687" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A687" s="2" t="s">
         <v>1017</v>
       </c>
@@ -66625,7 +66620,7 @@
       <c r="AH687" s="4"/>
       <c r="AI687" s="4"/>
     </row>
-    <row r="688" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="688" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A688" s="2" t="s">
         <v>1020</v>
       </c>
@@ -66686,7 +66681,7 @@
       <c r="AH688" s="4"/>
       <c r="AI688" s="4"/>
     </row>
-    <row r="689" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A689" s="2" t="s">
         <v>1021</v>
       </c>
@@ -66747,7 +66742,7 @@
       <c r="AH689" s="4"/>
       <c r="AI689" s="4"/>
     </row>
-    <row r="690" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A690" s="2" t="s">
         <v>1023</v>
       </c>
@@ -66808,7 +66803,7 @@
       <c r="AH690" s="4"/>
       <c r="AI690" s="4"/>
     </row>
-    <row r="691" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A691" s="2" t="s">
         <v>1028</v>
       </c>
@@ -66869,7 +66864,7 @@
       <c r="AH691" s="4"/>
       <c r="AI691" s="4"/>
     </row>
-    <row r="692" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="692" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A692" s="2" t="s">
         <v>1030</v>
       </c>
@@ -66930,7 +66925,7 @@
       <c r="AH692" s="4"/>
       <c r="AI692" s="4"/>
     </row>
-    <row r="693" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A693" s="2" t="s">
         <v>1034</v>
       </c>
@@ -66991,7 +66986,7 @@
       <c r="AH693" s="4"/>
       <c r="AI693" s="4"/>
     </row>
-    <row r="694" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="694" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A694" s="2" t="s">
         <v>1035</v>
       </c>
@@ -67052,7 +67047,7 @@
       <c r="AH694" s="4"/>
       <c r="AI694" s="4"/>
     </row>
-    <row r="695" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="695" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A695" s="2" t="s">
         <v>1037</v>
       </c>
@@ -67113,7 +67108,7 @@
       <c r="AH695" s="4"/>
       <c r="AI695" s="4"/>
     </row>
-    <row r="696" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="696" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A696" s="2" t="s">
         <v>1040</v>
       </c>
@@ -67174,7 +67169,7 @@
       <c r="AH696" s="4"/>
       <c r="AI696" s="4"/>
     </row>
-    <row r="697" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="697" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A697" s="2" t="s">
         <v>1041</v>
       </c>
@@ -67235,7 +67230,7 @@
       <c r="AH697" s="4"/>
       <c r="AI697" s="4"/>
     </row>
-    <row r="698" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="698" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A698" s="2" t="s">
         <v>1042</v>
       </c>
@@ -67296,7 +67291,7 @@
       <c r="AH698" s="4"/>
       <c r="AI698" s="4"/>
     </row>
-    <row r="699" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="699" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A699" s="2" t="s">
         <v>1044</v>
       </c>
@@ -67357,7 +67352,7 @@
       <c r="AH699" s="4"/>
       <c r="AI699" s="4"/>
     </row>
-    <row r="700" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="700" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A700" s="2" t="s">
         <v>1048</v>
       </c>
@@ -67418,7 +67413,7 @@
       <c r="AH700" s="4"/>
       <c r="AI700" s="4"/>
     </row>
-    <row r="701" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="701" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A701" s="2" t="s">
         <v>1050</v>
       </c>
@@ -67479,7 +67474,7 @@
       <c r="AH701" s="4"/>
       <c r="AI701" s="4"/>
     </row>
-    <row r="702" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="702" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A702" s="2" t="s">
         <v>1053</v>
       </c>
@@ -67540,7 +67535,7 @@
       <c r="AH702" s="4"/>
       <c r="AI702" s="4"/>
     </row>
-    <row r="703" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="703" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A703" s="2" t="s">
         <v>1054</v>
       </c>
@@ -67601,7 +67596,7 @@
       <c r="AH703" s="4"/>
       <c r="AI703" s="4"/>
     </row>
-    <row r="704" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="704" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A704" s="2" t="s">
         <v>1057</v>
       </c>
@@ -67662,7 +67657,7 @@
       <c r="AH704" s="4"/>
       <c r="AI704" s="4"/>
     </row>
-    <row r="705" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="705" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A705" s="2" t="s">
         <v>1058</v>
       </c>
@@ -67723,7 +67718,7 @@
       <c r="AH705" s="4"/>
       <c r="AI705" s="4"/>
     </row>
-    <row r="706" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="706" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A706" s="2" t="s">
         <v>1059</v>
       </c>
@@ -67784,7 +67779,7 @@
       <c r="AH706" s="4"/>
       <c r="AI706" s="4"/>
     </row>
-    <row r="707" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="707" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A707" s="2" t="s">
         <v>1061</v>
       </c>
@@ -67845,7 +67840,7 @@
       <c r="AH707" s="4"/>
       <c r="AI707" s="4"/>
     </row>
-    <row r="708" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="708" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A708" s="2" t="s">
         <v>1062</v>
       </c>
@@ -67906,7 +67901,7 @@
       <c r="AH708" s="4"/>
       <c r="AI708" s="4"/>
     </row>
-    <row r="709" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="709" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A709" s="2" t="s">
         <v>1063</v>
       </c>
@@ -67967,7 +67962,7 @@
       <c r="AH709" s="4"/>
       <c r="AI709" s="4"/>
     </row>
-    <row r="710" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="710" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A710" s="2" t="s">
         <v>1067</v>
       </c>
@@ -68028,7 +68023,7 @@
       <c r="AH710" s="4"/>
       <c r="AI710" s="4"/>
     </row>
-    <row r="711" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="711" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A711" s="2" t="s">
         <v>1069</v>
       </c>
@@ -68089,7 +68084,7 @@
       <c r="AH711" s="4"/>
       <c r="AI711" s="4"/>
     </row>
-    <row r="712" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="712" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A712" s="2" t="s">
         <v>1071</v>
       </c>
@@ -68150,7 +68145,7 @@
       <c r="AH712" s="4"/>
       <c r="AI712" s="4"/>
     </row>
-    <row r="713" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="713" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A713" s="2" t="s">
         <v>1072</v>
       </c>
@@ -68211,7 +68206,7 @@
       <c r="AH713" s="4"/>
       <c r="AI713" s="4"/>
     </row>
-    <row r="714" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="714" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A714" s="2" t="s">
         <v>1075</v>
       </c>
@@ -68272,7 +68267,7 @@
       <c r="AH714" s="4"/>
       <c r="AI714" s="4"/>
     </row>
-    <row r="715" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="715" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A715" s="2" t="s">
         <v>1078</v>
       </c>
@@ -68333,7 +68328,7 @@
       <c r="AH715" s="4"/>
       <c r="AI715" s="4"/>
     </row>
-    <row r="716" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="716" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A716" s="2" t="s">
         <v>1079</v>
       </c>
@@ -68638,7 +68633,7 @@
       <c r="AH720" s="4"/>
       <c r="AI720" s="4"/>
     </row>
-    <row r="721" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="721" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A721" s="2" t="s">
         <v>1090</v>
       </c>
@@ -68699,7 +68694,7 @@
       <c r="AH721" s="4"/>
       <c r="AI721" s="4"/>
     </row>
-    <row r="722" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="722" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A722" s="2" t="s">
         <v>1093</v>
       </c>
@@ -68760,7 +68755,7 @@
       <c r="AH722" s="4"/>
       <c r="AI722" s="4"/>
     </row>
-    <row r="723" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="723" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A723" s="2" t="s">
         <v>1094</v>
       </c>
@@ -68821,7 +68816,7 @@
       <c r="AH723" s="4"/>
       <c r="AI723" s="4"/>
     </row>
-    <row r="724" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="724" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A724" s="2" t="s">
         <v>1095</v>
       </c>
@@ -68882,7 +68877,7 @@
       <c r="AH724" s="4"/>
       <c r="AI724" s="4"/>
     </row>
-    <row r="725" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="725" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A725" s="2" t="s">
         <v>1097</v>
       </c>
@@ -68943,7 +68938,7 @@
       <c r="AH725" s="4"/>
       <c r="AI725" s="4"/>
     </row>
-    <row r="726" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="726" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A726" s="2" t="s">
         <v>1098</v>
       </c>
@@ -69004,7 +68999,7 @@
       <c r="AH726" s="4"/>
       <c r="AI726" s="4"/>
     </row>
-    <row r="727" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="727" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A727" s="2" t="s">
         <v>1099</v>
       </c>
@@ -69065,7 +69060,7 @@
       <c r="AH727" s="4"/>
       <c r="AI727" s="4"/>
     </row>
-    <row r="728" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="728" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A728" s="2" t="s">
         <v>1100</v>
       </c>
@@ -69126,7 +69121,7 @@
       <c r="AH728" s="4"/>
       <c r="AI728" s="4"/>
     </row>
-    <row r="729" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="729" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A729" s="2" t="s">
         <v>1101</v>
       </c>
@@ -69187,7 +69182,7 @@
       <c r="AH729" s="4"/>
       <c r="AI729" s="4"/>
     </row>
-    <row r="730" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="730" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A730" s="2" t="s">
         <v>1104</v>
       </c>
@@ -69248,7 +69243,7 @@
       <c r="AH730" s="4"/>
       <c r="AI730" s="4"/>
     </row>
-    <row r="731" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="731" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A731" s="2" t="s">
         <v>1105</v>
       </c>
@@ -69309,7 +69304,7 @@
       <c r="AH731" s="4"/>
       <c r="AI731" s="4"/>
     </row>
-    <row r="732" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="732" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A732" s="2" t="s">
         <v>1106</v>
       </c>
@@ -69370,7 +69365,7 @@
       <c r="AH732" s="4"/>
       <c r="AI732" s="4"/>
     </row>
-    <row r="733" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="733" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A733" s="2" t="s">
         <v>1109</v>
       </c>
@@ -69431,7 +69426,7 @@
       <c r="AH733" s="4"/>
       <c r="AI733" s="4"/>
     </row>
-    <row r="734" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="734" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A734" s="2" t="s">
         <v>1111</v>
       </c>
@@ -69492,7 +69487,7 @@
       <c r="AH734" s="4"/>
       <c r="AI734" s="4"/>
     </row>
-    <row r="735" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="735" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A735" s="2" t="s">
         <v>1112</v>
       </c>
@@ -69553,7 +69548,7 @@
       <c r="AH735" s="4"/>
       <c r="AI735" s="4"/>
     </row>
-    <row r="736" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="736" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A736" s="2" t="s">
         <v>1115</v>
       </c>
@@ -69614,7 +69609,7 @@
       <c r="AH736" s="4"/>
       <c r="AI736" s="4"/>
     </row>
-    <row r="737" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="737" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A737" s="2" t="s">
         <v>1117</v>
       </c>
@@ -69675,7 +69670,7 @@
       <c r="AH737" s="4"/>
       <c r="AI737" s="4"/>
     </row>
-    <row r="738" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="738" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A738" s="2" t="s">
         <v>1118</v>
       </c>
@@ -69736,7 +69731,7 @@
       <c r="AH738" s="4"/>
       <c r="AI738" s="4"/>
     </row>
-    <row r="739" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="739" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A739" s="2" t="s">
         <v>1119</v>
       </c>
@@ -69797,7 +69792,7 @@
       <c r="AH739" s="4"/>
       <c r="AI739" s="4"/>
     </row>
-    <row r="740" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="740" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A740" s="2" t="s">
         <v>1122</v>
       </c>
@@ -69858,7 +69853,7 @@
       <c r="AH740" s="4"/>
       <c r="AI740" s="4"/>
     </row>
-    <row r="741" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="741" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A741" s="2" t="s">
         <v>1123</v>
       </c>
@@ -69919,7 +69914,7 @@
       <c r="AH741" s="4"/>
       <c r="AI741" s="4"/>
     </row>
-    <row r="742" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="742" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A742" s="2" t="s">
         <v>1126</v>
       </c>
@@ -69980,7 +69975,7 @@
       <c r="AH742" s="4"/>
       <c r="AI742" s="4"/>
     </row>
-    <row r="743" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="743" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A743" s="2" t="s">
         <v>1127</v>
       </c>
@@ -70041,7 +70036,7 @@
       <c r="AH743" s="4"/>
       <c r="AI743" s="4"/>
     </row>
-    <row r="744" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="744" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A744" s="2" t="s">
         <v>1130</v>
       </c>
@@ -70102,7 +70097,7 @@
       <c r="AH744" s="4"/>
       <c r="AI744" s="4"/>
     </row>
-    <row r="745" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="745" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A745" s="2" t="s">
         <v>1132</v>
       </c>
@@ -70163,7 +70158,7 @@
       <c r="AH745" s="4"/>
       <c r="AI745" s="4"/>
     </row>
-    <row r="746" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="746" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A746" s="2" t="s">
         <v>1135</v>
       </c>
@@ -70224,7 +70219,7 @@
       <c r="AH746" s="4"/>
       <c r="AI746" s="4"/>
     </row>
-    <row r="747" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="747" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A747" s="2" t="s">
         <v>1136</v>
       </c>
@@ -70285,7 +70280,7 @@
       <c r="AH747" s="4"/>
       <c r="AI747" s="4"/>
     </row>
-    <row r="748" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="748" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A748" s="2" t="s">
         <v>1139</v>
       </c>
@@ -70346,7 +70341,7 @@
       <c r="AH748" s="4"/>
       <c r="AI748" s="4"/>
     </row>
-    <row r="749" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="749" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A749" s="2" t="s">
         <v>1140</v>
       </c>
@@ -70407,7 +70402,7 @@
       <c r="AH749" s="4"/>
       <c r="AI749" s="4"/>
     </row>
-    <row r="750" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="750" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A750" s="2" t="s">
         <v>1144</v>
       </c>
@@ -70468,7 +70463,7 @@
       <c r="AH750" s="4"/>
       <c r="AI750" s="4"/>
     </row>
-    <row r="751" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="751" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A751" s="2" t="s">
         <v>1145</v>
       </c>
@@ -70529,7 +70524,7 @@
       <c r="AH751" s="4"/>
       <c r="AI751" s="4"/>
     </row>
-    <row r="752" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="752" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A752" s="2" t="s">
         <v>1146</v>
       </c>
@@ -70590,7 +70585,7 @@
       <c r="AH752" s="4"/>
       <c r="AI752" s="4"/>
     </row>
-    <row r="753" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="753" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A753" s="2" t="s">
         <v>1148</v>
       </c>
@@ -70651,7 +70646,7 @@
       <c r="AH753" s="4"/>
       <c r="AI753" s="4"/>
     </row>
-    <row r="754" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="754" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A754" s="2" t="s">
         <v>1149</v>
       </c>
@@ -70712,7 +70707,7 @@
       <c r="AH754" s="4"/>
       <c r="AI754" s="4"/>
     </row>
-    <row r="755" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="755" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A755" s="2" t="s">
         <v>1151</v>
       </c>
@@ -70773,7 +70768,7 @@
       <c r="AH755" s="4"/>
       <c r="AI755" s="4"/>
     </row>
-    <row r="756" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="756" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A756" s="2" t="s">
         <v>1152</v>
       </c>
@@ -70834,7 +70829,7 @@
       <c r="AH756" s="4"/>
       <c r="AI756" s="4"/>
     </row>
-    <row r="757" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="757" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A757" s="2" t="s">
         <v>1155</v>
       </c>
@@ -70895,7 +70890,7 @@
       <c r="AH757" s="4"/>
       <c r="AI757" s="4"/>
     </row>
-    <row r="758" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="758" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A758" s="2" t="s">
         <v>1157</v>
       </c>
@@ -70956,7 +70951,7 @@
       <c r="AH758" s="4"/>
       <c r="AI758" s="4"/>
     </row>
-    <row r="759" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="759" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A759" s="2" t="s">
         <v>1158</v>
       </c>
@@ -71017,7 +71012,7 @@
       <c r="AH759" s="4"/>
       <c r="AI759" s="4"/>
     </row>
-    <row r="760" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="760" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A760" s="2" t="s">
         <v>1161</v>
       </c>
@@ -71078,7 +71073,7 @@
       <c r="AH760" s="4"/>
       <c r="AI760" s="4"/>
     </row>
-    <row r="761" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="761" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A761" s="2" t="s">
         <v>1162</v>
       </c>
@@ -71139,7 +71134,7 @@
       <c r="AH761" s="4"/>
       <c r="AI761" s="4"/>
     </row>
-    <row r="762" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="762" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A762" s="2" t="s">
         <v>1163</v>
       </c>
@@ -71200,7 +71195,7 @@
       <c r="AH762" s="4"/>
       <c r="AI762" s="4"/>
     </row>
-    <row r="763" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="763" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A763" s="2" t="s">
         <v>1165</v>
       </c>
@@ -71261,7 +71256,7 @@
       <c r="AH763" s="4"/>
       <c r="AI763" s="4"/>
     </row>
-    <row r="764" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="764" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A764" s="2" t="s">
         <v>1166</v>
       </c>
@@ -71322,7 +71317,7 @@
       <c r="AH764" s="4"/>
       <c r="AI764" s="4"/>
     </row>
-    <row r="765" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="765" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A765" s="2" t="s">
         <v>1169</v>
       </c>
@@ -71383,7 +71378,7 @@
       <c r="AH765" s="4"/>
       <c r="AI765" s="4"/>
     </row>
-    <row r="766" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="766" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A766" s="2" t="s">
         <v>1170</v>
       </c>
@@ -71444,7 +71439,7 @@
       <c r="AH766" s="4"/>
       <c r="AI766" s="4"/>
     </row>
-    <row r="767" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="767" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A767" s="2" t="s">
         <v>1171</v>
       </c>
@@ -71505,7 +71500,7 @@
       <c r="AH767" s="4"/>
       <c r="AI767" s="4"/>
     </row>
-    <row r="768" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="768" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A768" s="2" t="s">
         <v>1173</v>
       </c>
@@ -71566,7 +71561,7 @@
       <c r="AH768" s="4"/>
       <c r="AI768" s="4"/>
     </row>
-    <row r="769" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="769" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A769" s="2" t="s">
         <v>1174</v>
       </c>
@@ -71627,7 +71622,7 @@
       <c r="AH769" s="4"/>
       <c r="AI769" s="4"/>
     </row>
-    <row r="770" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="770" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A770" s="2" t="s">
         <v>1175</v>
       </c>
@@ -71688,7 +71683,7 @@
       <c r="AH770" s="4"/>
       <c r="AI770" s="4"/>
     </row>
-    <row r="771" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="771" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A771" s="2" t="s">
         <v>1178</v>
       </c>
@@ -71749,7 +71744,7 @@
       <c r="AH771" s="4"/>
       <c r="AI771" s="4"/>
     </row>
-    <row r="772" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="772" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A772" s="2" t="s">
         <v>1179</v>
       </c>
@@ -71810,7 +71805,7 @@
       <c r="AH772" s="4"/>
       <c r="AI772" s="4"/>
     </row>
-    <row r="773" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="773" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A773" s="2" t="s">
         <v>1180</v>
       </c>
@@ -71871,7 +71866,7 @@
       <c r="AH773" s="4"/>
       <c r="AI773" s="4"/>
     </row>
-    <row r="774" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="774" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A774" s="2" t="s">
         <v>1181</v>
       </c>
@@ -71932,7 +71927,7 @@
       <c r="AH774" s="4"/>
       <c r="AI774" s="4"/>
     </row>
-    <row r="775" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="775" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A775" s="2" t="s">
         <v>1184</v>
       </c>
@@ -71993,7 +71988,7 @@
       <c r="AH775" s="4"/>
       <c r="AI775" s="4"/>
     </row>
-    <row r="776" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="776" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A776" s="2" t="s">
         <v>1185</v>
       </c>
@@ -72054,7 +72049,7 @@
       <c r="AH776" s="4"/>
       <c r="AI776" s="4"/>
     </row>
-    <row r="777" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="777" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A777" s="2" t="s">
         <v>1186</v>
       </c>
@@ -72115,7 +72110,7 @@
       <c r="AH777" s="4"/>
       <c r="AI777" s="4"/>
     </row>
-    <row r="778" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="778" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A778" s="2" t="s">
         <v>1187</v>
       </c>
@@ -72176,7 +72171,7 @@
       <c r="AH778" s="4"/>
       <c r="AI778" s="4"/>
     </row>
-    <row r="779" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="779" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A779" s="2" t="s">
         <v>1188</v>
       </c>
@@ -72237,7 +72232,7 @@
       <c r="AH779" s="4"/>
       <c r="AI779" s="4"/>
     </row>
-    <row r="780" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="780" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A780" s="2" t="s">
         <v>1189</v>
       </c>
@@ -72298,7 +72293,7 @@
       <c r="AH780" s="4"/>
       <c r="AI780" s="4"/>
     </row>
-    <row r="781" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="781" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A781" s="2" t="s">
         <v>1192</v>
       </c>
@@ -72359,7 +72354,7 @@
       <c r="AH781" s="4"/>
       <c r="AI781" s="4"/>
     </row>
-    <row r="782" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="782" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A782" s="2" t="s">
         <v>1195</v>
       </c>
@@ -72420,7 +72415,7 @@
       <c r="AH782" s="4"/>
       <c r="AI782" s="4"/>
     </row>
-    <row r="783" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="783" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A783" s="2" t="s">
         <v>1196</v>
       </c>
@@ -72481,7 +72476,7 @@
       <c r="AH783" s="4"/>
       <c r="AI783" s="4"/>
     </row>
-    <row r="784" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="784" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A784" s="2" t="s">
         <v>1197</v>
       </c>
@@ -72542,7 +72537,7 @@
       <c r="AH784" s="4"/>
       <c r="AI784" s="4"/>
     </row>
-    <row r="785" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="785" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A785" s="2" t="s">
         <v>1198</v>
       </c>
@@ -72603,7 +72598,7 @@
       <c r="AH785" s="4"/>
       <c r="AI785" s="4"/>
     </row>
-    <row r="786" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="786" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A786" s="2" t="s">
         <v>1201</v>
       </c>
@@ -72664,7 +72659,7 @@
       <c r="AH786" s="4"/>
       <c r="AI786" s="4"/>
     </row>
-    <row r="787" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="787" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A787" s="2" t="s">
         <v>1202</v>
       </c>
@@ -72725,7 +72720,7 @@
       <c r="AH787" s="4"/>
       <c r="AI787" s="4"/>
     </row>
-    <row r="788" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="788" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A788" s="2" t="s">
         <v>1203</v>
       </c>
@@ -72786,7 +72781,7 @@
       <c r="AH788" s="4"/>
       <c r="AI788" s="4"/>
     </row>
-    <row r="789" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="789" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A789" s="2" t="s">
         <v>1204</v>
       </c>
@@ -72847,7 +72842,7 @@
       <c r="AH789" s="4"/>
       <c r="AI789" s="4"/>
     </row>
-    <row r="790" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="790" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A790" s="2" t="s">
         <v>1207</v>
       </c>
@@ -72908,7 +72903,7 @@
       <c r="AH790" s="4"/>
       <c r="AI790" s="4"/>
     </row>
-    <row r="791" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="791" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A791" s="2" t="s">
         <v>1208</v>
       </c>
@@ -72969,7 +72964,7 @@
       <c r="AH791" s="4"/>
       <c r="AI791" s="4"/>
     </row>
-    <row r="792" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="792" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A792" s="2" t="s">
         <v>1211</v>
       </c>
@@ -73030,7 +73025,7 @@
       <c r="AH792" s="4"/>
       <c r="AI792" s="4"/>
     </row>
-    <row r="793" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="793" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A793" s="2" t="s">
         <v>1212</v>
       </c>
@@ -73091,7 +73086,7 @@
       <c r="AH793" s="4"/>
       <c r="AI793" s="4"/>
     </row>
-    <row r="794" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="794" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A794" s="2" t="s">
         <v>1215</v>
       </c>
@@ -73152,7 +73147,7 @@
       <c r="AH794" s="4"/>
       <c r="AI794" s="4"/>
     </row>
-    <row r="795" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="795" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A795" s="2" t="s">
         <v>1218</v>
       </c>
@@ -73213,7 +73208,7 @@
       <c r="AH795" s="4"/>
       <c r="AI795" s="4"/>
     </row>
-    <row r="796" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="796" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A796" s="2" t="s">
         <v>1219</v>
       </c>
@@ -73274,7 +73269,7 @@
       <c r="AH796" s="4"/>
       <c r="AI796" s="4"/>
     </row>
-    <row r="797" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="797" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A797" s="2" t="s">
         <v>1223</v>
       </c>
@@ -73335,7 +73330,7 @@
       <c r="AH797" s="4"/>
       <c r="AI797" s="4"/>
     </row>
-    <row r="798" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="798" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A798" s="2" t="s">
         <v>1224</v>
       </c>
@@ -73396,7 +73391,7 @@
       <c r="AH798" s="4"/>
       <c r="AI798" s="4"/>
     </row>
-    <row r="799" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="799" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A799" s="2" t="s">
         <v>1226</v>
       </c>
@@ -73457,7 +73452,7 @@
       <c r="AH799" s="4"/>
       <c r="AI799" s="4"/>
     </row>
-    <row r="800" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="800" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A800" s="2" t="s">
         <v>1229</v>
       </c>
@@ -73518,7 +73513,7 @@
       <c r="AH800" s="4"/>
       <c r="AI800" s="4"/>
     </row>
-    <row r="801" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="801" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A801" s="2" t="s">
         <v>1230</v>
       </c>
@@ -73579,7 +73574,7 @@
       <c r="AH801" s="4"/>
       <c r="AI801" s="4"/>
     </row>
-    <row r="802" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="802" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A802" s="2" t="s">
         <v>1231</v>
       </c>
@@ -73640,7 +73635,7 @@
       <c r="AH802" s="4"/>
       <c r="AI802" s="4"/>
     </row>
-    <row r="803" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="803" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A803" s="2" t="s">
         <v>1232</v>
       </c>
@@ -73701,7 +73696,7 @@
       <c r="AH803" s="4"/>
       <c r="AI803" s="4"/>
     </row>
-    <row r="804" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="804" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A804" s="2" t="s">
         <v>1235</v>
       </c>
@@ -73762,7 +73757,7 @@
       <c r="AH804" s="4"/>
       <c r="AI804" s="4"/>
     </row>
-    <row r="805" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="805" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A805" s="2" t="s">
         <v>1236</v>
       </c>
@@ -73823,7 +73818,7 @@
       <c r="AH805" s="4"/>
       <c r="AI805" s="4"/>
     </row>
-    <row r="806" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="806" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A806" s="2" t="s">
         <v>1237</v>
       </c>
@@ -73884,7 +73879,7 @@
       <c r="AH806" s="4"/>
       <c r="AI806" s="4"/>
     </row>
-    <row r="807" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="807" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A807" s="2" t="s">
         <v>1240</v>
       </c>
@@ -73945,7 +73940,7 @@
       <c r="AH807" s="4"/>
       <c r="AI807" s="4"/>
     </row>
-    <row r="808" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="808" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A808" s="2" t="s">
         <v>1241</v>
       </c>
@@ -74006,7 +74001,7 @@
       <c r="AH808" s="4"/>
       <c r="AI808" s="4"/>
     </row>
-    <row r="809" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="809" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A809" s="2" t="s">
         <v>1242</v>
       </c>
@@ -74067,7 +74062,7 @@
       <c r="AH809" s="4"/>
       <c r="AI809" s="4"/>
     </row>
-    <row r="810" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="810" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A810" s="2" t="s">
         <v>1245</v>
       </c>
@@ -74128,7 +74123,7 @@
       <c r="AH810" s="4"/>
       <c r="AI810" s="4"/>
     </row>
-    <row r="811" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="811" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A811" s="2" t="s">
         <v>1246</v>
       </c>
@@ -74189,7 +74184,7 @@
       <c r="AH811" s="4"/>
       <c r="AI811" s="4"/>
     </row>
-    <row r="812" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="812" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A812" s="2" t="s">
         <v>1248</v>
       </c>
@@ -74250,7 +74245,7 @@
       <c r="AH812" s="4"/>
       <c r="AI812" s="4"/>
     </row>
-    <row r="813" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="813" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A813" s="2" t="s">
         <v>1249</v>
       </c>
@@ -74311,7 +74306,7 @@
       <c r="AH813" s="4"/>
       <c r="AI813" s="4"/>
     </row>
-    <row r="814" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="814" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A814" s="2" t="s">
         <v>1253</v>
       </c>
@@ -74372,7 +74367,7 @@
       <c r="AH814" s="4"/>
       <c r="AI814" s="4"/>
     </row>
-    <row r="815" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="815" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A815" s="2" t="s">
         <v>1254</v>
       </c>
@@ -74433,7 +74428,7 @@
       <c r="AH815" s="4"/>
       <c r="AI815" s="4"/>
     </row>
-    <row r="816" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="816" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A816" s="2" t="s">
         <v>1256</v>
       </c>
@@ -74494,7 +74489,7 @@
       <c r="AH816" s="4"/>
       <c r="AI816" s="4"/>
     </row>
-    <row r="817" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="817" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A817" s="2" t="s">
         <v>1257</v>
       </c>
@@ -74555,7 +74550,7 @@
       <c r="AH817" s="4"/>
       <c r="AI817" s="4"/>
     </row>
-    <row r="818" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="818" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A818" s="2" t="s">
         <v>1258</v>
       </c>
@@ -74616,7 +74611,7 @@
       <c r="AH818" s="4"/>
       <c r="AI818" s="4"/>
     </row>
-    <row r="819" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="819" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A819" s="2" t="s">
         <v>1259</v>
       </c>
@@ -74677,7 +74672,7 @@
       <c r="AH819" s="4"/>
       <c r="AI819" s="4"/>
     </row>
-    <row r="820" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="820" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A820" s="2" t="s">
         <v>1262</v>
       </c>
@@ -74738,7 +74733,7 @@
       <c r="AH820" s="4"/>
       <c r="AI820" s="4"/>
     </row>
-    <row r="821" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="821" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A821" s="2" t="s">
         <v>1263</v>
       </c>
@@ -74799,7 +74794,7 @@
       <c r="AH821" s="4"/>
       <c r="AI821" s="4"/>
     </row>
-    <row r="822" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="822" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A822" s="2" t="s">
         <v>1264</v>
       </c>
@@ -74860,7 +74855,7 @@
       <c r="AH822" s="4"/>
       <c r="AI822" s="4"/>
     </row>
-    <row r="823" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="823" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A823" s="2" t="s">
         <v>1267</v>
       </c>
@@ -74921,7 +74916,7 @@
       <c r="AH823" s="4"/>
       <c r="AI823" s="4"/>
     </row>
-    <row r="824" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="824" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A824" s="2" t="s">
         <v>1269</v>
       </c>
@@ -74982,7 +74977,7 @@
       <c r="AH824" s="4"/>
       <c r="AI824" s="4"/>
     </row>
-    <row r="825" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="825" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A825" s="2" t="s">
         <v>1270</v>
       </c>
@@ -75043,7 +75038,7 @@
       <c r="AH825" s="4"/>
       <c r="AI825" s="4"/>
     </row>
-    <row r="826" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="826" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A826" s="2" t="s">
         <v>1273</v>
       </c>
@@ -75104,7 +75099,7 @@
       <c r="AH826" s="4"/>
       <c r="AI826" s="4"/>
     </row>
-    <row r="827" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="827" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A827" s="2" t="s">
         <v>1274</v>
       </c>
@@ -75165,7 +75160,7 @@
       <c r="AH827" s="4"/>
       <c r="AI827" s="4"/>
     </row>
-    <row r="828" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="828" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A828" s="2" t="s">
         <v>1277</v>
       </c>
@@ -75226,7 +75221,7 @@
       <c r="AH828" s="4"/>
       <c r="AI828" s="4"/>
     </row>
-    <row r="829" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="829" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A829" s="2" t="s">
         <v>1278</v>
       </c>
@@ -75287,7 +75282,7 @@
       <c r="AH829" s="4"/>
       <c r="AI829" s="4"/>
     </row>
-    <row r="830" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="830" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A830" s="2" t="s">
         <v>1280</v>
       </c>
@@ -75348,7 +75343,7 @@
       <c r="AH830" s="4"/>
       <c r="AI830" s="4"/>
     </row>
-    <row r="831" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="831" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A831" s="2" t="s">
         <v>1281</v>
       </c>
@@ -75409,7 +75404,7 @@
       <c r="AH831" s="4"/>
       <c r="AI831" s="4"/>
     </row>
-    <row r="832" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="832" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A832" s="2" t="s">
         <v>1282</v>
       </c>
@@ -75470,7 +75465,7 @@
       <c r="AH832" s="4"/>
       <c r="AI832" s="4"/>
     </row>
-    <row r="833" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="833" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A833" s="2" t="s">
         <v>1283</v>
       </c>
@@ -75531,7 +75526,7 @@
       <c r="AH833" s="4"/>
       <c r="AI833" s="4"/>
     </row>
-    <row r="834" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="834" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A834" s="2" t="s">
         <v>1284</v>
       </c>
@@ -75592,7 +75587,7 @@
       <c r="AH834" s="4"/>
       <c r="AI834" s="4"/>
     </row>
-    <row r="835" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="835" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A835" s="2" t="s">
         <v>1287</v>
       </c>
@@ -75653,7 +75648,7 @@
       <c r="AH835" s="4"/>
       <c r="AI835" s="4"/>
     </row>
-    <row r="836" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="836" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A836" s="2" t="s">
         <v>1290</v>
       </c>
@@ -75714,7 +75709,7 @@
       <c r="AH836" s="4"/>
       <c r="AI836" s="4"/>
     </row>
-    <row r="837" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="837" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A837" s="2" t="s">
         <v>1291</v>
       </c>
@@ -75775,7 +75770,7 @@
       <c r="AH837" s="4"/>
       <c r="AI837" s="4"/>
     </row>
-    <row r="838" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="838" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A838" s="2" t="s">
         <v>1292</v>
       </c>
@@ -75836,7 +75831,7 @@
       <c r="AH838" s="4"/>
       <c r="AI838" s="4"/>
     </row>
-    <row r="839" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="839" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A839" s="2" t="s">
         <v>1293</v>
       </c>
@@ -75897,7 +75892,7 @@
       <c r="AH839" s="4"/>
       <c r="AI839" s="4"/>
     </row>
-    <row r="840" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="840" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A840" s="2" t="s">
         <v>1294</v>
       </c>
@@ -75958,7 +75953,7 @@
       <c r="AH840" s="4"/>
       <c r="AI840" s="4"/>
     </row>
-    <row r="841" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="841" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A841" s="2" t="s">
         <v>1298</v>
       </c>
@@ -76019,7 +76014,7 @@
       <c r="AH841" s="4"/>
       <c r="AI841" s="4"/>
     </row>
-    <row r="842" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="842" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A842" s="2" t="s">
         <v>1299</v>
       </c>
@@ -76080,7 +76075,7 @@
       <c r="AH842" s="4"/>
       <c r="AI842" s="4"/>
     </row>
-    <row r="843" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="843" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A843" s="2" t="s">
         <v>1300</v>
       </c>
@@ -76141,7 +76136,7 @@
       <c r="AH843" s="4"/>
       <c r="AI843" s="4"/>
     </row>
-    <row r="844" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="844" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A844" s="2" t="s">
         <v>1301</v>
       </c>
@@ -76202,7 +76197,7 @@
       <c r="AH844" s="4"/>
       <c r="AI844" s="4"/>
     </row>
-    <row r="845" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="845" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A845" s="2" t="s">
         <v>1302</v>
       </c>
@@ -76263,7 +76258,7 @@
       <c r="AH845" s="4"/>
       <c r="AI845" s="4"/>
     </row>
-    <row r="846" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="846" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A846" s="2" t="s">
         <v>1303</v>
       </c>
@@ -76324,7 +76319,7 @@
       <c r="AH846" s="4"/>
       <c r="AI846" s="4"/>
     </row>
-    <row r="847" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="847" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A847" s="2" t="s">
         <v>1304</v>
       </c>
@@ -76385,7 +76380,7 @@
       <c r="AH847" s="4"/>
       <c r="AI847" s="4"/>
     </row>
-    <row r="848" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="848" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A848" s="2" t="s">
         <v>1307</v>
       </c>
@@ -76446,7 +76441,7 @@
       <c r="AH848" s="4"/>
       <c r="AI848" s="4"/>
     </row>
-    <row r="849" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="849" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A849" s="2" t="s">
         <v>1309</v>
       </c>
@@ -76507,7 +76502,7 @@
       <c r="AH849" s="4"/>
       <c r="AI849" s="4"/>
     </row>
-    <row r="850" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="850" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A850" s="2" t="s">
         <v>1310</v>
       </c>
@@ -76568,7 +76563,7 @@
       <c r="AH850" s="4"/>
       <c r="AI850" s="4"/>
     </row>
-    <row r="851" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="851" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A851" s="2" t="s">
         <v>1312</v>
       </c>
@@ -76629,7 +76624,7 @@
       <c r="AH851" s="4"/>
       <c r="AI851" s="4"/>
     </row>
-    <row r="852" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="852" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A852" s="2" t="s">
         <v>1313</v>
       </c>
@@ -76690,7 +76685,7 @@
       <c r="AH852" s="4"/>
       <c r="AI852" s="4"/>
     </row>
-    <row r="853" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="853" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A853" s="2" t="s">
         <v>1315</v>
       </c>
@@ -76751,7 +76746,7 @@
       <c r="AH853" s="4"/>
       <c r="AI853" s="4"/>
     </row>
-    <row r="854" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="854" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A854" s="2" t="s">
         <v>1316</v>
       </c>
@@ -76812,7 +76807,7 @@
       <c r="AH854" s="4"/>
       <c r="AI854" s="4"/>
     </row>
-    <row r="855" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="855" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A855" s="2" t="s">
         <v>1318</v>
       </c>
@@ -76873,7 +76868,7 @@
       <c r="AH855" s="4"/>
       <c r="AI855" s="4"/>
     </row>
-    <row r="856" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="856" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A856" s="2" t="s">
         <v>1320</v>
       </c>
@@ -76934,7 +76929,7 @@
       <c r="AH856" s="4"/>
       <c r="AI856" s="4"/>
     </row>
-    <row r="857" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="857" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A857" s="2" t="s">
         <v>1323</v>
       </c>
@@ -76995,7 +76990,7 @@
       <c r="AH857" s="4"/>
       <c r="AI857" s="4"/>
     </row>
-    <row r="858" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="858" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A858" s="2" t="s">
         <v>1325</v>
       </c>
@@ -77056,7 +77051,7 @@
       <c r="AH858" s="4"/>
       <c r="AI858" s="4"/>
     </row>
-    <row r="859" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="859" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A859" s="2" t="s">
         <v>1327</v>
       </c>
@@ -77117,7 +77112,7 @@
       <c r="AH859" s="4"/>
       <c r="AI859" s="4"/>
     </row>
-    <row r="860" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="860" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A860" s="2" t="s">
         <v>1328</v>
       </c>
@@ -77178,7 +77173,7 @@
       <c r="AH860" s="4"/>
       <c r="AI860" s="4"/>
     </row>
-    <row r="861" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="861" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A861" s="2" t="s">
         <v>1330</v>
       </c>
@@ -77239,7 +77234,7 @@
       <c r="AH861" s="4"/>
       <c r="AI861" s="4"/>
     </row>
-    <row r="862" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="862" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A862" s="2" t="s">
         <v>1331</v>
       </c>
@@ -77300,7 +77295,7 @@
       <c r="AH862" s="4"/>
       <c r="AI862" s="4"/>
     </row>
-    <row r="863" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="863" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A863" s="2" t="s">
         <v>1333</v>
       </c>
@@ -77361,7 +77356,7 @@
       <c r="AH863" s="4"/>
       <c r="AI863" s="4"/>
     </row>
-    <row r="864" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="864" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A864" s="2" t="s">
         <v>1335</v>
       </c>
@@ -77422,7 +77417,7 @@
       <c r="AH864" s="4"/>
       <c r="AI864" s="4"/>
     </row>
-    <row r="865" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="865" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A865" s="2" t="s">
         <v>1338</v>
       </c>
@@ -77483,7 +77478,7 @@
       <c r="AH865" s="4"/>
       <c r="AI865" s="4"/>
     </row>
-    <row r="866" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="866" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A866" s="2" t="s">
         <v>1339</v>
       </c>
@@ -77544,7 +77539,7 @@
       <c r="AH866" s="4"/>
       <c r="AI866" s="4"/>
     </row>
-    <row r="867" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="867" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A867" s="2" t="s">
         <v>1342</v>
       </c>
@@ -77605,7 +77600,7 @@
       <c r="AH867" s="4"/>
       <c r="AI867" s="4"/>
     </row>
-    <row r="868" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="868" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A868" s="2" t="s">
         <v>1345</v>
       </c>
@@ -77666,7 +77661,7 @@
       <c r="AH868" s="4"/>
       <c r="AI868" s="4"/>
     </row>
-    <row r="869" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="869" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A869" s="2" t="s">
         <v>1346</v>
       </c>
@@ -77727,7 +77722,7 @@
       <c r="AH869" s="4"/>
       <c r="AI869" s="4"/>
     </row>
-    <row r="870" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="870" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A870" s="2" t="s">
         <v>1348</v>
       </c>
@@ -77788,7 +77783,7 @@
       <c r="AH870" s="4"/>
       <c r="AI870" s="4"/>
     </row>
-    <row r="871" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="871" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A871" s="2" t="s">
         <v>1350</v>
       </c>
@@ -77849,7 +77844,7 @@
       <c r="AH871" s="4"/>
       <c r="AI871" s="4"/>
     </row>
-    <row r="872" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="872" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A872" s="2" t="s">
         <v>1353</v>
       </c>
@@ -77910,7 +77905,7 @@
       <c r="AH872" s="4"/>
       <c r="AI872" s="4"/>
     </row>
-    <row r="873" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="873" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A873" s="2" t="s">
         <v>1354</v>
       </c>
@@ -78093,7 +78088,7 @@
       <c r="AH875" s="4"/>
       <c r="AI875" s="4"/>
     </row>
-    <row r="876" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="876" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A876" s="2" t="s">
         <v>1360</v>
       </c>
@@ -78154,7 +78149,7 @@
       <c r="AH876" s="4"/>
       <c r="AI876" s="4"/>
     </row>
-    <row r="877" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="877" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A877" s="2" t="s">
         <v>1363</v>
       </c>
@@ -78215,7 +78210,7 @@
       <c r="AH877" s="4"/>
       <c r="AI877" s="4"/>
     </row>
-    <row r="878" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="878" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A878" s="2" t="s">
         <v>1365</v>
       </c>
@@ -78276,7 +78271,7 @@
       <c r="AH878" s="4"/>
       <c r="AI878" s="4"/>
     </row>
-    <row r="879" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="879" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A879" s="2" t="s">
         <v>1366</v>
       </c>
@@ -78337,7 +78332,7 @@
       <c r="AH879" s="4"/>
       <c r="AI879" s="4"/>
     </row>
-    <row r="880" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="880" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A880" s="2" t="s">
         <v>1367</v>
       </c>
@@ -78398,7 +78393,7 @@
       <c r="AH880" s="4"/>
       <c r="AI880" s="4"/>
     </row>
-    <row r="881" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="881" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A881" s="2" t="s">
         <v>1368</v>
       </c>
@@ -78459,7 +78454,7 @@
       <c r="AH881" s="4"/>
       <c r="AI881" s="4"/>
     </row>
-    <row r="882" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="882" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A882" s="2" t="s">
         <v>1371</v>
       </c>
@@ -78520,7 +78515,7 @@
       <c r="AH882" s="4"/>
       <c r="AI882" s="4"/>
     </row>
-    <row r="883" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="883" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A883" s="2" t="s">
         <v>1372</v>
       </c>
@@ -78581,7 +78576,7 @@
       <c r="AH883" s="4"/>
       <c r="AI883" s="4"/>
     </row>
-    <row r="884" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="884" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A884" s="2" t="s">
         <v>1373</v>
       </c>
@@ -78642,7 +78637,7 @@
       <c r="AH884" s="4"/>
       <c r="AI884" s="4"/>
     </row>
-    <row r="885" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="885" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A885" s="2" t="s">
         <v>1374</v>
       </c>
@@ -78703,7 +78698,7 @@
       <c r="AH885" s="4"/>
       <c r="AI885" s="4"/>
     </row>
-    <row r="886" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="886" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A886" s="2" t="s">
         <v>1376</v>
       </c>
@@ -78764,7 +78759,7 @@
       <c r="AH886" s="4"/>
       <c r="AI886" s="4"/>
     </row>
-    <row r="887" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="887" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A887" s="2" t="s">
         <v>1379</v>
       </c>
@@ -78825,7 +78820,7 @@
       <c r="AH887" s="4"/>
       <c r="AI887" s="4"/>
     </row>
-    <row r="888" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="888" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A888" s="2" t="s">
         <v>1381</v>
       </c>
@@ -78886,7 +78881,7 @@
       <c r="AH888" s="4"/>
       <c r="AI888" s="4"/>
     </row>
-    <row r="889" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="889" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A889" s="2" t="s">
         <v>1384</v>
       </c>
@@ -78947,7 +78942,7 @@
       <c r="AH889" s="4"/>
       <c r="AI889" s="4"/>
     </row>
-    <row r="890" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="890" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A890" s="2" t="s">
         <v>1385</v>
       </c>
@@ -79008,7 +79003,7 @@
       <c r="AH890" s="4"/>
       <c r="AI890" s="4"/>
     </row>
-    <row r="891" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="891" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A891" s="2" t="s">
         <v>1386</v>
       </c>
@@ -79069,7 +79064,7 @@
       <c r="AH891" s="4"/>
       <c r="AI891" s="4"/>
     </row>
-    <row r="892" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="892" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A892" s="2" t="s">
         <v>1388</v>
       </c>
@@ -79130,7 +79125,7 @@
       <c r="AH892" s="4"/>
       <c r="AI892" s="4"/>
     </row>
-    <row r="893" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="893" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A893" s="2" t="s">
         <v>1391</v>
       </c>
@@ -79191,7 +79186,7 @@
       <c r="AH893" s="4"/>
       <c r="AI893" s="4"/>
     </row>
-    <row r="894" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="894" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A894" s="2" t="s">
         <v>1392</v>
       </c>
@@ -79252,7 +79247,7 @@
       <c r="AH894" s="4"/>
       <c r="AI894" s="4"/>
     </row>
-    <row r="895" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="895" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A895" s="2" t="s">
         <v>1395</v>
       </c>
@@ -79313,7 +79308,7 @@
       <c r="AH895" s="4"/>
       <c r="AI895" s="4"/>
     </row>
-    <row r="896" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="896" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A896" s="2" t="s">
         <v>1397</v>
       </c>
@@ -79374,7 +79369,7 @@
       <c r="AH896" s="4"/>
       <c r="AI896" s="4"/>
     </row>
-    <row r="897" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="897" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A897" s="2" t="s">
         <v>1400</v>
       </c>
@@ -79435,7 +79430,7 @@
       <c r="AH897" s="4"/>
       <c r="AI897" s="4"/>
     </row>
-    <row r="898" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="898" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A898" s="2" t="s">
         <v>1402</v>
       </c>
@@ -79496,7 +79491,7 @@
       <c r="AH898" s="4"/>
       <c r="AI898" s="4"/>
     </row>
-    <row r="899" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="899" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A899" s="2" t="s">
         <v>1404</v>
       </c>
@@ -79557,7 +79552,7 @@
       <c r="AH899" s="4"/>
       <c r="AI899" s="4"/>
     </row>
-    <row r="900" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="900" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A900" s="2" t="s">
         <v>1405</v>
       </c>
@@ -79618,7 +79613,7 @@
       <c r="AH900" s="4"/>
       <c r="AI900" s="4"/>
     </row>
-    <row r="901" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="901" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A901" s="2" t="s">
         <v>1408</v>
       </c>
@@ -79679,7 +79674,7 @@
       <c r="AH901" s="4"/>
       <c r="AI901" s="4"/>
     </row>
-    <row r="902" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="902" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A902" s="2" t="s">
         <v>1409</v>
       </c>
@@ -79740,7 +79735,7 @@
       <c r="AH902" s="4"/>
       <c r="AI902" s="4"/>
     </row>
-    <row r="903" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="903" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A903" s="2" t="s">
         <v>1413</v>
       </c>
@@ -79801,7 +79796,7 @@
       <c r="AH903" s="4"/>
       <c r="AI903" s="4"/>
     </row>
-    <row r="904" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="904" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A904" s="2" t="s">
         <v>1415</v>
       </c>
@@ -79862,7 +79857,7 @@
       <c r="AH904" s="4"/>
       <c r="AI904" s="4"/>
     </row>
-    <row r="905" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="905" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A905" s="2" t="s">
         <v>1419</v>
       </c>
@@ -79923,7 +79918,7 @@
       <c r="AH905" s="4"/>
       <c r="AI905" s="4"/>
     </row>
-    <row r="906" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="906" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A906" s="2" t="s">
         <v>1421</v>
       </c>
@@ -79984,7 +79979,7 @@
       <c r="AH906" s="4"/>
       <c r="AI906" s="4"/>
     </row>
-    <row r="907" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="907" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A907" s="2" t="s">
         <v>1423</v>
       </c>
@@ -80045,7 +80040,7 @@
       <c r="AH907" s="4"/>
       <c r="AI907" s="4"/>
     </row>
-    <row r="908" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="908" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A908" s="2" t="s">
         <v>1427</v>
       </c>
@@ -80106,7 +80101,7 @@
       <c r="AH908" s="4"/>
       <c r="AI908" s="4"/>
     </row>
-    <row r="909" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="909" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A909" s="2" t="s">
         <v>1429</v>
       </c>
@@ -80167,7 +80162,7 @@
       <c r="AH909" s="4"/>
       <c r="AI909" s="4"/>
     </row>
-    <row r="910" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="910" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A910" s="2" t="s">
         <v>1431</v>
       </c>
@@ -80228,7 +80223,7 @@
       <c r="AH910" s="4"/>
       <c r="AI910" s="4"/>
     </row>
-    <row r="911" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="911" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A911" s="2" t="s">
         <v>1433</v>
       </c>
@@ -80289,7 +80284,7 @@
       <c r="AH911" s="4"/>
       <c r="AI911" s="4"/>
     </row>
-    <row r="912" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="912" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A912" s="2" t="s">
         <v>1436</v>
       </c>
@@ -80350,7 +80345,7 @@
       <c r="AH912" s="4"/>
       <c r="AI912" s="4"/>
     </row>
-    <row r="913" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="913" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A913" s="2" t="s">
         <v>1437</v>
       </c>
@@ -80411,7 +80406,7 @@
       <c r="AH913" s="4"/>
       <c r="AI913" s="4"/>
     </row>
-    <row r="914" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="914" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A914" s="2" t="s">
         <v>1438</v>
       </c>
@@ -80472,7 +80467,7 @@
       <c r="AH914" s="4"/>
       <c r="AI914" s="4"/>
     </row>
-    <row r="915" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="915" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A915" s="2" t="s">
         <v>1439</v>
       </c>
@@ -80533,7 +80528,7 @@
       <c r="AH915" s="4"/>
       <c r="AI915" s="4"/>
     </row>
-    <row r="916" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="916" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A916" s="2" t="s">
         <v>1442</v>
       </c>
@@ -80594,7 +80589,7 @@
       <c r="AH916" s="4"/>
       <c r="AI916" s="4"/>
     </row>
-    <row r="917" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="917" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A917" s="2" t="s">
         <v>1443</v>
       </c>
@@ -80655,7 +80650,7 @@
       <c r="AH917" s="4"/>
       <c r="AI917" s="4"/>
     </row>
-    <row r="918" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="918" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A918" s="2" t="s">
         <v>1446</v>
       </c>
@@ -80716,7 +80711,7 @@
       <c r="AH918" s="4"/>
       <c r="AI918" s="4"/>
     </row>
-    <row r="919" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="919" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A919" s="2" t="s">
         <v>1447</v>
       </c>
@@ -80777,7 +80772,7 @@
       <c r="AH919" s="4"/>
       <c r="AI919" s="4"/>
     </row>
-    <row r="920" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="920" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A920" s="2" t="s">
         <v>1450</v>
       </c>
@@ -80838,7 +80833,7 @@
       <c r="AH920" s="4"/>
       <c r="AI920" s="4"/>
     </row>
-    <row r="921" spans="1:35" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="921" spans="1:35" ht="18.95" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A921" s="2" t="s">
         <v>1451</v>
       </c>
@@ -80900,7 +80895,16 @@
       <c r="AI921" s="4"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:R921" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:R921" xr:uid="{00000000-0009-0000-0000-000000000000}">
+    <filterColumn colId="4">
+      <filters>
+        <filter val="BERMUDA TREINO 7 M"/>
+        <filter val="TREINO"/>
+        <filter val="TREINO FEMININO"/>
+        <filter val="TREINO MASCULINO"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
